--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataQAseverupdate\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataQAsevernee\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645E20DE-3F96-48A0-95DB-D1E6A3ABE958}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E585C47B-F831-4783-BA36-5C22E4970BB4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8693" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8732" uniqueCount="930">
   <si>
     <t>S.No</t>
   </si>
@@ -2804,6 +2804,18 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_CP_21</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_13</t>
+  </si>
+  <si>
+    <t>Verify that a newsletter email is received after subscribing to the newsletter</t>
+  </si>
+  <si>
+    <t>TD_UI_Admin_OEV_13</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/subscriber</t>
   </si>
 </sst>
 </file>
@@ -4310,7 +4322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z261"/>
+  <dimension ref="A1:Z262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
@@ -12608,70 +12620,70 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="87" t="s">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A253" s="48">
+        <v>13</v>
+      </c>
+      <c r="B253" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C253" s="79" t="s">
+        <v>926</v>
+      </c>
+      <c r="D253" s="78" t="s">
+        <v>927</v>
+      </c>
+      <c r="E253" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F253" s="79" t="s">
+        <v>928</v>
+      </c>
+      <c r="G253" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H253" s="48" t="s">
+        <v>795</v>
+      </c>
+      <c r="I253" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J253" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="87" t="s">
         <v>837</v>
       </c>
-      <c r="B253" s="87"/>
-      <c r="C253" s="87"/>
-      <c r="D253" s="87"/>
-      <c r="E253" s="87"/>
-      <c r="F253" s="87"/>
-      <c r="G253" s="87"/>
-      <c r="H253" s="87"/>
-      <c r="I253" s="87"/>
-      <c r="J253" s="87"/>
-    </row>
-    <row r="254" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="48">
-        <v>1</v>
-      </c>
-      <c r="B254" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C254" s="79" t="s">
-        <v>871</v>
-      </c>
-      <c r="D254" s="78" t="s">
-        <v>872</v>
-      </c>
-      <c r="E254" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="F254" s="70" t="s">
-        <v>870</v>
-      </c>
-      <c r="G254" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="H254" s="48" t="s">
-        <v>873</v>
-      </c>
-      <c r="I254" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="J254" s="48" t="s">
-        <v>13</v>
-      </c>
+      <c r="B254" s="87"/>
+      <c r="C254" s="87"/>
+      <c r="D254" s="87"/>
+      <c r="E254" s="87"/>
+      <c r="F254" s="87"/>
+      <c r="G254" s="87"/>
+      <c r="H254" s="87"/>
+      <c r="I254" s="87"/>
+      <c r="J254" s="87"/>
     </row>
     <row r="255" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B255" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C255" s="79" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D255" s="78" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="E255" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F255" s="70" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="G255" s="48" t="s">
         <v>11</v>
@@ -12687,69 +12699,69 @@
       </c>
     </row>
     <row r="256" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="87" t="s">
+      <c r="A256" s="48">
+        <v>2</v>
+      </c>
+      <c r="B256" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C256" s="79" t="s">
+        <v>875</v>
+      </c>
+      <c r="D256" s="78" t="s">
+        <v>876</v>
+      </c>
+      <c r="E256" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F256" s="70" t="s">
+        <v>874</v>
+      </c>
+      <c r="G256" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H256" s="48" t="s">
+        <v>873</v>
+      </c>
+      <c r="I256" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J256" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="87" t="s">
         <v>838</v>
       </c>
-      <c r="B256" s="87"/>
-      <c r="C256" s="87"/>
-      <c r="D256" s="87"/>
-      <c r="E256" s="87"/>
-      <c r="F256" s="87"/>
-      <c r="G256" s="87"/>
-      <c r="H256" s="87"/>
-      <c r="I256" s="87"/>
-      <c r="J256" s="87"/>
-    </row>
-    <row r="257" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="48">
-        <v>1</v>
-      </c>
-      <c r="B257" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C257" s="79" t="s">
-        <v>839</v>
-      </c>
-      <c r="D257" s="78" t="s">
-        <v>842</v>
-      </c>
-      <c r="E257" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="F257" s="70" t="s">
-        <v>840</v>
-      </c>
-      <c r="G257" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="H257" s="48" t="s">
-        <v>841</v>
-      </c>
-      <c r="I257" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="J257" s="48" t="s">
-        <v>13</v>
-      </c>
+      <c r="B257" s="87"/>
+      <c r="C257" s="87"/>
+      <c r="D257" s="87"/>
+      <c r="E257" s="87"/>
+      <c r="F257" s="87"/>
+      <c r="G257" s="87"/>
+      <c r="H257" s="87"/>
+      <c r="I257" s="87"/>
+      <c r="J257" s="87"/>
     </row>
     <row r="258" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B258" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C258" s="79" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D258" s="78" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="E258" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F258" s="70" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="G258" s="48" t="s">
         <v>11</v>
@@ -12766,22 +12778,22 @@
     </row>
     <row r="259" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B259" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C259" s="79" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="D259" s="78" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E259" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F259" s="70" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="G259" s="48" t="s">
         <v>11</v>
@@ -12798,22 +12810,22 @@
     </row>
     <row r="260" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B260" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C260" s="79" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="D260" s="78" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="E260" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F260" s="70" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="G260" s="48" t="s">
         <v>11</v>
@@ -12830,22 +12842,22 @@
     </row>
     <row r="261" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B261" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C261" s="79" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="D261" s="78" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="E261" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F261" s="70" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G261" s="48" t="s">
         <v>11</v>
@@ -12860,16 +12872,48 @@
         <v>13</v>
       </c>
     </row>
+    <row r="262" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="48">
+        <v>5</v>
+      </c>
+      <c r="B262" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C262" s="79" t="s">
+        <v>862</v>
+      </c>
+      <c r="D262" s="78" t="s">
+        <v>863</v>
+      </c>
+      <c r="E262" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F262" s="70" t="s">
+        <v>861</v>
+      </c>
+      <c r="G262" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H262" s="48" t="s">
+        <v>841</v>
+      </c>
+      <c r="I262" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J262" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A257:J257"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A123:J123"/>
     <mergeCell ref="A125:J125"/>
     <mergeCell ref="A203:J203"/>
     <mergeCell ref="A198:J198"/>
-    <mergeCell ref="A253:J253"/>
+    <mergeCell ref="A254:J254"/>
     <mergeCell ref="A240:J240"/>
     <mergeCell ref="A133:J133"/>
     <mergeCell ref="A190:J190"/>
@@ -12983,7 +13027,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AF245"/>
+  <dimension ref="A1:AF246"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -33130,9 +33174,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="70" t="s">
-        <v>870</v>
+        <v>928</v>
       </c>
       <c r="B237" s="48" t="s">
         <v>22</v>
@@ -33185,11 +33229,11 @@
       <c r="R237" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="S237" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T237" s="48" t="s">
-        <v>22</v>
+      <c r="S237" s="49" t="s">
+        <v>929</v>
+      </c>
+      <c r="T237" s="49" t="s">
+        <v>908</v>
       </c>
       <c r="U237" s="48" t="s">
         <v>22</v>
@@ -33215,8 +33259,8 @@
       <c r="AB237" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="AC237" s="48" t="s">
-        <v>22</v>
+      <c r="AC237" s="73" t="s">
+        <v>831</v>
       </c>
       <c r="AD237" s="48" t="s">
         <v>22</v>
@@ -33224,7 +33268,7 @@
     </row>
     <row r="238" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="70" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="B238" s="48" t="s">
         <v>22</v>
@@ -33316,7 +33360,7 @@
     </row>
     <row r="239" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="70" t="s">
-        <v>840</v>
+        <v>874</v>
       </c>
       <c r="B239" s="48" t="s">
         <v>22</v>
@@ -33408,7 +33452,7 @@
     </row>
     <row r="240" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="70" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B240" s="48" t="s">
         <v>22</v>
@@ -33461,8 +33505,8 @@
       <c r="R240" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="S240" s="49" t="s">
-        <v>906</v>
+      <c r="S240" s="48" t="s">
+        <v>22</v>
       </c>
       <c r="T240" s="48" t="s">
         <v>22</v>
@@ -33500,7 +33544,7 @@
     </row>
     <row r="241" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="70" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B241" s="48" t="s">
         <v>22</v>
@@ -33553,8 +33597,8 @@
       <c r="R241" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="S241" s="48" t="s">
-        <v>22</v>
+      <c r="S241" s="49" t="s">
+        <v>906</v>
       </c>
       <c r="T241" s="48" t="s">
         <v>22</v>
@@ -33583,8 +33627,8 @@
       <c r="AB241" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="AC241" s="73" t="s">
-        <v>831</v>
+      <c r="AC241" s="48" t="s">
+        <v>22</v>
       </c>
       <c r="AD241" s="48" t="s">
         <v>22</v>
@@ -33592,7 +33636,7 @@
     </row>
     <row r="242" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="70" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="B242" s="48" t="s">
         <v>22</v>
@@ -33676,7 +33720,7 @@
         <v>22</v>
       </c>
       <c r="AC242" s="73" t="s">
-        <v>860</v>
+        <v>831</v>
       </c>
       <c r="AD242" s="48" t="s">
         <v>22</v>
@@ -33684,7 +33728,7 @@
     </row>
     <row r="243" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="70" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B243" s="48" t="s">
         <v>22</v>
@@ -33774,101 +33818,101 @@
         <v>22</v>
       </c>
     </row>
-    <row r="244" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>887</v>
-      </c>
-      <c r="B244" t="s">
-        <v>22</v>
-      </c>
-      <c r="C244" t="s">
-        <v>22</v>
-      </c>
-      <c r="D244" t="s">
-        <v>22</v>
-      </c>
-      <c r="E244" t="s">
-        <v>22</v>
-      </c>
-      <c r="F244" t="s">
-        <v>22</v>
-      </c>
-      <c r="G244" t="s">
-        <v>22</v>
-      </c>
-      <c r="H244" t="s">
-        <v>22</v>
-      </c>
-      <c r="I244" t="s">
-        <v>22</v>
-      </c>
-      <c r="J244" t="s">
-        <v>22</v>
-      </c>
-      <c r="K244" t="s">
-        <v>22</v>
-      </c>
-      <c r="L244" t="s">
-        <v>22</v>
-      </c>
-      <c r="M244" t="s">
-        <v>22</v>
-      </c>
-      <c r="N244" t="s">
-        <v>22</v>
-      </c>
-      <c r="O244" t="s">
-        <v>22</v>
-      </c>
-      <c r="P244" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q244" t="s">
-        <v>22</v>
-      </c>
-      <c r="R244" t="s">
-        <v>22</v>
-      </c>
-      <c r="S244" t="s">
-        <v>896</v>
-      </c>
-      <c r="T244" t="s">
-        <v>22</v>
-      </c>
-      <c r="U244" t="s">
-        <v>22</v>
-      </c>
-      <c r="V244" t="s">
-        <v>22</v>
-      </c>
-      <c r="W244" t="s">
-        <v>22</v>
-      </c>
-      <c r="X244" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y244" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z244" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA244" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB244" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC244" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD244" t="s">
+    <row r="244" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="70" t="s">
+        <v>861</v>
+      </c>
+      <c r="B244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V244" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W244" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X244" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB244" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC244" s="73" t="s">
+        <v>860</v>
+      </c>
+      <c r="AD244" s="48" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="245" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="B245" t="s">
         <v>22</v>
@@ -33955,6 +33999,98 @@
         <v>22</v>
       </c>
       <c r="AD245" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="246" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>894</v>
+      </c>
+      <c r="B246" t="s">
+        <v>22</v>
+      </c>
+      <c r="C246" t="s">
+        <v>22</v>
+      </c>
+      <c r="D246" t="s">
+        <v>22</v>
+      </c>
+      <c r="E246" t="s">
+        <v>22</v>
+      </c>
+      <c r="F246" t="s">
+        <v>22</v>
+      </c>
+      <c r="G246" t="s">
+        <v>22</v>
+      </c>
+      <c r="H246" t="s">
+        <v>22</v>
+      </c>
+      <c r="I246" t="s">
+        <v>22</v>
+      </c>
+      <c r="J246" t="s">
+        <v>22</v>
+      </c>
+      <c r="K246" t="s">
+        <v>22</v>
+      </c>
+      <c r="L246" t="s">
+        <v>22</v>
+      </c>
+      <c r="M246" t="s">
+        <v>22</v>
+      </c>
+      <c r="N246" t="s">
+        <v>22</v>
+      </c>
+      <c r="O246" t="s">
+        <v>22</v>
+      </c>
+      <c r="P246" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>22</v>
+      </c>
+      <c r="R246" t="s">
+        <v>22</v>
+      </c>
+      <c r="S246" t="s">
+        <v>896</v>
+      </c>
+      <c r="T246" t="s">
+        <v>22</v>
+      </c>
+      <c r="U246" t="s">
+        <v>22</v>
+      </c>
+      <c r="V246" t="s">
+        <v>22</v>
+      </c>
+      <c r="W246" t="s">
+        <v>22</v>
+      </c>
+      <c r="X246" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y246" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z246" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA246" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB246" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC246" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD246" t="s">
         <v>22</v>
       </c>
     </row>
@@ -34113,18 +34249,18 @@
     <hyperlink ref="AC177" r:id="rId46" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{7BE8FE18-5C75-431B-8488-FBDEF16485E5}"/>
     <hyperlink ref="AC178" r:id="rId47" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{FF640DAE-0F42-4B2A-A086-F1C73287AD75}"/>
     <hyperlink ref="AC181" r:id="rId48" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{B625AA61-E1E0-4964-9CDD-901824C6555F}"/>
-    <hyperlink ref="AC241" r:id="rId49" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
+    <hyperlink ref="AC242" r:id="rId49" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
     <hyperlink ref="T211" r:id="rId50" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
     <hyperlink ref="T212" r:id="rId51" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
     <hyperlink ref="S199" r:id="rId52" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
     <hyperlink ref="AC225" r:id="rId53" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{CD96CCCF-BE60-40A1-BA2F-93729430B99A}"/>
-    <hyperlink ref="AC226:AC236" r:id="rId54" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
+    <hyperlink ref="AC226:AC237" r:id="rId54" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
     <hyperlink ref="S219" r:id="rId55" display="https://qa.zlta.testingserver8.com/admin/payment-pending" xr:uid="{37E5E50E-434D-4FC0-B9A6-C0648E88FF97}"/>
     <hyperlink ref="S206" r:id="rId56" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
     <hyperlink ref="S204" r:id="rId57" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
     <hyperlink ref="S205" r:id="rId58" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
     <hyperlink ref="S196" r:id="rId59" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
-    <hyperlink ref="S240" r:id="rId60" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
+    <hyperlink ref="S241" r:id="rId60" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
     <hyperlink ref="T236" r:id="rId61" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
     <hyperlink ref="S226" r:id="rId62" display="https://console.zlaata.com/admin/cancel-order" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
   </hyperlinks>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataQAsevernee\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever654\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E585C47B-F831-4783-BA36-5C22E4970BB4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360DA765-C095-47C4-8204-244D0D4608FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -3475,24 +3475,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3519,6 +3501,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4323,20 +4323,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
   <dimension ref="A1:Z262"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
-    <col min="4" max="4" width="118.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="118.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="28">
         <v>1</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="28">
         <v>2</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="28">
         <v>3</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="28">
         <v>4</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="28">
         <v>5</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="28">
         <v>6</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="28">
         <v>7</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="28">
         <v>8</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="28">
         <v>9</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="28">
         <v>10</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="28">
         <v>11</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="28">
         <v>12</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="28">
         <v>13</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="28">
         <v>14</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="28">
         <v>15</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="28">
         <v>16</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="28">
         <v>17</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="28">
         <v>18</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="28">
         <v>19</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="28">
         <v>20</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="28">
         <v>21</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="45">
         <v>22</v>
       </c>
@@ -5072,21 +5072,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="88" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="97" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="98"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="99"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>1</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>2</v>
       </c>
@@ -5150,7 +5150,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>3</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>4</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>5</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>6</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>7</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>8</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>9</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>10</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>11</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>12</v>
       </c>
@@ -5470,21 +5470,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="91" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="100" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="92"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="93"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="101"/>
+      <c r="C37" s="101"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="101"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="102"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>1</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>3</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>4</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>5</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>6</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>7</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>8</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>9</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>10</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>11</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>12</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>13</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>14</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>15</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>16</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>16</v>
       </c>
@@ -6028,21 +6028,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="91" t="s">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="100" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="92"/>
-      <c r="C55" s="92"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="92"/>
-      <c r="F55" s="92"/>
-      <c r="G55" s="92"/>
-      <c r="H55" s="92"/>
-      <c r="I55" s="92"/>
-      <c r="J55" s="93"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="101"/>
+      <c r="C55" s="101"/>
+      <c r="D55" s="101"/>
+      <c r="E55" s="101"/>
+      <c r="F55" s="101"/>
+      <c r="G55" s="101"/>
+      <c r="H55" s="101"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="102"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
         <v>1</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="25">
         <v>2</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="25">
         <v>3</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="25">
         <v>4</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="25">
         <v>5</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="25">
         <v>6</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="25">
         <v>7</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="25">
         <v>8</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="25">
         <v>9</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="25">
         <v>10</v>
       </c>
@@ -6362,21 +6362,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="91" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="100" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="92"/>
-      <c r="C66" s="92"/>
-      <c r="D66" s="92"/>
-      <c r="E66" s="92"/>
-      <c r="F66" s="92"/>
-      <c r="G66" s="92"/>
-      <c r="H66" s="92"/>
-      <c r="I66" s="92"/>
-      <c r="J66" s="93"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="101"/>
+      <c r="C66" s="101"/>
+      <c r="D66" s="101"/>
+      <c r="E66" s="101"/>
+      <c r="F66" s="101"/>
+      <c r="G66" s="101"/>
+      <c r="H66" s="101"/>
+      <c r="I66" s="101"/>
+      <c r="J66" s="102"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
         <v>1</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="25">
         <v>2</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="25">
         <v>3</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="25">
         <v>4</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="25">
         <v>5</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="25">
         <v>6</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="25">
         <v>7</v>
       </c>
@@ -6600,7 +6600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="25">
         <v>8</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="25">
         <v>9</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="25">
         <v>10</v>
       </c>
@@ -6696,7 +6696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="25">
         <v>11</v>
       </c>
@@ -6728,21 +6728,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="91" t="s">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="100" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="92"/>
-      <c r="C78" s="92"/>
-      <c r="D78" s="92"/>
-      <c r="E78" s="92"/>
-      <c r="F78" s="92"/>
-      <c r="G78" s="92"/>
-      <c r="H78" s="92"/>
-      <c r="I78" s="92"/>
-      <c r="J78" s="93"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B78" s="101"/>
+      <c r="C78" s="101"/>
+      <c r="D78" s="101"/>
+      <c r="E78" s="101"/>
+      <c r="F78" s="101"/>
+      <c r="G78" s="101"/>
+      <c r="H78" s="101"/>
+      <c r="I78" s="101"/>
+      <c r="J78" s="102"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
         <v>1</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="25">
         <v>2</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="25">
         <v>3</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="25">
         <v>4</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="25">
         <v>5</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="25">
         <v>6</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="25">
         <v>7</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="25">
         <v>8</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="25">
         <v>9</v>
       </c>
@@ -7030,7 +7030,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="25">
         <v>10</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="25">
         <v>11</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="25">
         <v>12</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="25">
         <v>13</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="25">
         <v>14</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="25">
         <v>15</v>
       </c>
@@ -7222,7 +7222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="25">
         <v>16</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="25">
         <v>17</v>
       </c>
@@ -7286,7 +7286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="25">
         <v>18</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="25">
         <v>19</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="25">
         <v>20</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="25">
         <v>21</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="25">
         <v>22</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="25">
         <v>23</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="25">
         <v>24</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="25">
         <v>25</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="25">
         <v>27</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="25">
         <v>28</v>
       </c>
@@ -7606,21 +7606,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="94" t="s">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" s="88" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="94"/>
-      <c r="C106" s="94"/>
-      <c r="D106" s="94"/>
-      <c r="E106" s="94"/>
-      <c r="F106" s="94"/>
-      <c r="G106" s="94"/>
-      <c r="H106" s="94"/>
-      <c r="I106" s="94"/>
-      <c r="J106" s="94"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B106" s="88"/>
+      <c r="C106" s="88"/>
+      <c r="D106" s="88"/>
+      <c r="E106" s="88"/>
+      <c r="F106" s="88"/>
+      <c r="G106" s="88"/>
+      <c r="H106" s="88"/>
+      <c r="I106" s="88"/>
+      <c r="J106" s="88"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
         <v>1</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="25">
         <v>2</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="25">
         <v>3</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="25">
         <v>4</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="25">
         <v>5</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="25">
         <v>6</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="25">
         <v>7</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="25">
         <v>8</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="25">
         <v>9</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="25">
         <v>10</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="25">
         <v>11</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="25">
         <v>12</v>
       </c>
@@ -8018,7 +8018,7 @@
       <c r="W118" s="58"/>
       <c r="X118" s="58"/>
     </row>
-    <row r="119" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="25">
         <v>13</v>
       </c>
@@ -8064,7 +8064,7 @@
       <c r="W119" s="58"/>
       <c r="X119" s="58"/>
     </row>
-    <row r="120" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="25">
         <v>14</v>
       </c>
@@ -8110,19 +8110,19 @@
       <c r="W120" s="58"/>
       <c r="X120" s="58"/>
     </row>
-    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="95" t="s">
+    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="89" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="95"/>
-      <c r="C121" s="95"/>
-      <c r="D121" s="95"/>
-      <c r="E121" s="95"/>
-      <c r="F121" s="95"/>
-      <c r="G121" s="95"/>
-      <c r="H121" s="95"/>
-      <c r="I121" s="95"/>
-      <c r="J121" s="95"/>
+      <c r="B121" s="89"/>
+      <c r="C121" s="89"/>
+      <c r="D121" s="89"/>
+      <c r="E121" s="89"/>
+      <c r="F121" s="89"/>
+      <c r="G121" s="89"/>
+      <c r="H121" s="89"/>
+      <c r="I121" s="89"/>
+      <c r="J121" s="89"/>
       <c r="K121" s="57"/>
       <c r="L121" s="58"/>
       <c r="M121" s="58"/>
@@ -8138,7 +8138,7 @@
       <c r="W121" s="58"/>
       <c r="X121" s="58"/>
     </row>
-    <row r="122" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="25">
         <v>1</v>
       </c>
@@ -8184,19 +8184,19 @@
       <c r="W122" s="58"/>
       <c r="X122" s="58"/>
     </row>
-    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="95" t="s">
+    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="89" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="95"/>
-      <c r="C123" s="95"/>
-      <c r="D123" s="95"/>
-      <c r="E123" s="95"/>
-      <c r="F123" s="95"/>
-      <c r="G123" s="95"/>
-      <c r="H123" s="95"/>
-      <c r="I123" s="95"/>
-      <c r="J123" s="95"/>
+      <c r="B123" s="89"/>
+      <c r="C123" s="89"/>
+      <c r="D123" s="89"/>
+      <c r="E123" s="89"/>
+      <c r="F123" s="89"/>
+      <c r="G123" s="89"/>
+      <c r="H123" s="89"/>
+      <c r="I123" s="89"/>
+      <c r="J123" s="89"/>
       <c r="K123" s="57"/>
       <c r="L123" s="58"/>
       <c r="M123" s="58"/>
@@ -8212,7 +8212,7 @@
       <c r="W123" s="58"/>
       <c r="X123" s="58"/>
     </row>
-    <row r="124" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="25">
         <v>1</v>
       </c>
@@ -8258,21 +8258,21 @@
       <c r="W124" s="58"/>
       <c r="X124" s="58"/>
     </row>
-    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="95" t="s">
+    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="89" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="95"/>
-      <c r="C125" s="95"/>
-      <c r="D125" s="95"/>
-      <c r="E125" s="95"/>
-      <c r="F125" s="95"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="95"/>
-      <c r="I125" s="95"/>
-      <c r="J125" s="95"/>
-    </row>
-    <row r="126" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="89"/>
+      <c r="C125" s="89"/>
+      <c r="D125" s="89"/>
+      <c r="E125" s="89"/>
+      <c r="F125" s="89"/>
+      <c r="G125" s="89"/>
+      <c r="H125" s="89"/>
+      <c r="I125" s="89"/>
+      <c r="J125" s="89"/>
+    </row>
+    <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
         <v>1</v>
       </c>
@@ -8318,7 +8318,7 @@
       <c r="W126" s="61"/>
       <c r="X126" s="61"/>
     </row>
-    <row r="127" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="25">
         <v>2</v>
       </c>
@@ -8364,7 +8364,7 @@
       <c r="W127" s="58"/>
       <c r="X127" s="58"/>
     </row>
-    <row r="128" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="25">
         <v>3</v>
       </c>
@@ -8410,7 +8410,7 @@
       <c r="W128" s="58"/>
       <c r="X128" s="58"/>
     </row>
-    <row r="129" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="25">
         <v>4</v>
       </c>
@@ -8456,7 +8456,7 @@
       <c r="W129" s="58"/>
       <c r="X129" s="58"/>
     </row>
-    <row r="130" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="25">
         <v>5</v>
       </c>
@@ -8502,7 +8502,7 @@
       <c r="W130" s="58"/>
       <c r="X130" s="58"/>
     </row>
-    <row r="131" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="25">
         <v>6</v>
       </c>
@@ -8548,7 +8548,7 @@
       <c r="W131" s="58"/>
       <c r="X131" s="58"/>
     </row>
-    <row r="132" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="25">
         <v>7</v>
       </c>
@@ -8594,19 +8594,19 @@
       <c r="W132" s="58"/>
       <c r="X132" s="58"/>
     </row>
-    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="95" t="s">
+    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="89" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="95"/>
-      <c r="C133" s="95"/>
-      <c r="D133" s="96"/>
-      <c r="E133" s="96"/>
-      <c r="F133" s="96"/>
-      <c r="G133" s="96"/>
-      <c r="H133" s="96"/>
-      <c r="I133" s="96"/>
-      <c r="J133" s="96"/>
+      <c r="B133" s="89"/>
+      <c r="C133" s="89"/>
+      <c r="D133" s="90"/>
+      <c r="E133" s="90"/>
+      <c r="F133" s="90"/>
+      <c r="G133" s="90"/>
+      <c r="H133" s="90"/>
+      <c r="I133" s="90"/>
+      <c r="J133" s="90"/>
       <c r="K133" s="58"/>
       <c r="L133" s="58"/>
       <c r="M133" s="58"/>
@@ -8622,7 +8622,7 @@
       <c r="W133" s="58"/>
       <c r="X133" s="58"/>
     </row>
-    <row r="134" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="59">
         <v>11</v>
       </c>
@@ -8668,7 +8668,7 @@
       <c r="W134" s="58"/>
       <c r="X134" s="58"/>
     </row>
-    <row r="135" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="26">
         <v>2</v>
       </c>
@@ -8714,7 +8714,7 @@
       <c r="W135" s="58"/>
       <c r="X135" s="58"/>
     </row>
-    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="26">
         <v>3</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="26">
         <v>4</v>
       </c>
@@ -8792,7 +8792,7 @@
       <c r="W137" s="58"/>
       <c r="X137" s="58"/>
     </row>
-    <row r="138" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="26">
         <v>5</v>
       </c>
@@ -8838,7 +8838,7 @@
       <c r="W138" s="58"/>
       <c r="X138" s="58"/>
     </row>
-    <row r="139" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="26">
         <v>6</v>
       </c>
@@ -8884,7 +8884,7 @@
       <c r="W139" s="58"/>
       <c r="X139" s="58"/>
     </row>
-    <row r="140" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="26">
         <v>7</v>
       </c>
@@ -8916,7 +8916,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="26">
         <v>8</v>
       </c>
@@ -8962,7 +8962,7 @@
       <c r="W141" s="58"/>
       <c r="X141" s="58"/>
     </row>
-    <row r="142" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="26">
         <v>9</v>
       </c>
@@ -9008,7 +9008,7 @@
       <c r="W142" s="58"/>
       <c r="X142" s="58"/>
     </row>
-    <row r="143" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="26">
         <v>10</v>
       </c>
@@ -9054,7 +9054,7 @@
       <c r="W143" s="58"/>
       <c r="X143" s="58"/>
     </row>
-    <row r="144" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="26">
         <v>11</v>
       </c>
@@ -9100,19 +9100,19 @@
       <c r="W144" s="58"/>
       <c r="X144" s="58"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="100" t="s">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="94" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="101"/>
-      <c r="C145" s="101"/>
-      <c r="D145" s="101"/>
-      <c r="E145" s="101"/>
-      <c r="F145" s="101"/>
-      <c r="G145" s="101"/>
-      <c r="H145" s="101"/>
-      <c r="I145" s="101"/>
-      <c r="J145" s="102"/>
+      <c r="B145" s="95"/>
+      <c r="C145" s="95"/>
+      <c r="D145" s="95"/>
+      <c r="E145" s="95"/>
+      <c r="F145" s="95"/>
+      <c r="G145" s="95"/>
+      <c r="H145" s="95"/>
+      <c r="I145" s="95"/>
+      <c r="J145" s="96"/>
       <c r="K145" s="58"/>
       <c r="L145" s="58"/>
       <c r="M145" s="58"/>
@@ -9128,7 +9128,7 @@
       <c r="W145" s="58"/>
       <c r="X145" s="58"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="25">
         <v>1</v>
       </c>
@@ -9174,7 +9174,7 @@
       <c r="W146" s="58"/>
       <c r="X146" s="58"/>
     </row>
-    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="25">
         <v>2</v>
       </c>
@@ -9206,7 +9206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A148" s="25">
         <v>3</v>
       </c>
@@ -9238,7 +9238,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="25">
         <v>4</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="25">
         <v>5</v>
       </c>
@@ -9318,7 +9318,7 @@
       <c r="Y150" s="58"/>
       <c r="Z150" s="58"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="25">
         <v>6</v>
       </c>
@@ -9366,7 +9366,7 @@
       <c r="Y151" s="58"/>
       <c r="Z151" s="58"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="25">
         <v>7</v>
       </c>
@@ -9414,7 +9414,7 @@
       <c r="Y152" s="58"/>
       <c r="Z152" s="58"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="25">
         <v>8</v>
       </c>
@@ -9462,7 +9462,7 @@
       <c r="Y153" s="58"/>
       <c r="Z153" s="58"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="25">
         <v>9</v>
       </c>
@@ -9510,7 +9510,7 @@
       <c r="Y154" s="58"/>
       <c r="Z154" s="58"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="25">
         <v>10</v>
       </c>
@@ -9558,19 +9558,19 @@
       <c r="Y155" s="58"/>
       <c r="Z155" s="58"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="95" t="s">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="95"/>
-      <c r="C156" s="95"/>
-      <c r="D156" s="95"/>
-      <c r="E156" s="95"/>
-      <c r="F156" s="95"/>
-      <c r="G156" s="95"/>
-      <c r="H156" s="95"/>
-      <c r="I156" s="95"/>
-      <c r="J156" s="95"/>
+      <c r="B156" s="89"/>
+      <c r="C156" s="89"/>
+      <c r="D156" s="89"/>
+      <c r="E156" s="89"/>
+      <c r="F156" s="89"/>
+      <c r="G156" s="89"/>
+      <c r="H156" s="89"/>
+      <c r="I156" s="89"/>
+      <c r="J156" s="89"/>
       <c r="K156" s="58"/>
       <c r="L156" s="58"/>
       <c r="M156" s="58"/>
@@ -9588,7 +9588,7 @@
       <c r="Y156" s="58"/>
       <c r="Z156" s="58"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="25">
         <v>1</v>
       </c>
@@ -9636,19 +9636,19 @@
       <c r="Y157" s="58"/>
       <c r="Z157" s="58"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="95" t="s">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="89" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="95"/>
-      <c r="C158" s="95"/>
-      <c r="D158" s="95"/>
-      <c r="E158" s="95"/>
-      <c r="F158" s="95"/>
-      <c r="G158" s="95"/>
-      <c r="H158" s="95"/>
-      <c r="I158" s="95"/>
-      <c r="J158" s="95"/>
+      <c r="B158" s="89"/>
+      <c r="C158" s="89"/>
+      <c r="D158" s="89"/>
+      <c r="E158" s="89"/>
+      <c r="F158" s="89"/>
+      <c r="G158" s="89"/>
+      <c r="H158" s="89"/>
+      <c r="I158" s="89"/>
+      <c r="J158" s="89"/>
       <c r="K158" s="58"/>
       <c r="L158" s="58"/>
       <c r="M158" s="58"/>
@@ -9666,7 +9666,7 @@
       <c r="Y158" s="58"/>
       <c r="Z158" s="58"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="67">
         <v>1</v>
       </c>
@@ -9714,7 +9714,7 @@
       <c r="Y159" s="58"/>
       <c r="Z159" s="58"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="68">
         <v>2</v>
       </c>
@@ -9762,7 +9762,7 @@
       <c r="Y160" s="58"/>
       <c r="Z160" s="58"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="68">
         <v>3</v>
       </c>
@@ -9810,7 +9810,7 @@
       <c r="Y161" s="58"/>
       <c r="Z161" s="58"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="68">
         <v>4</v>
       </c>
@@ -9858,7 +9858,7 @@
       <c r="Y162" s="58"/>
       <c r="Z162" s="58"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="68">
         <v>5</v>
       </c>
@@ -9906,7 +9906,7 @@
       <c r="Y163" s="58"/>
       <c r="Z163" s="58"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="68">
         <v>6</v>
       </c>
@@ -9954,7 +9954,7 @@
       <c r="Y164" s="58"/>
       <c r="Z164" s="58"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="68">
         <v>7</v>
       </c>
@@ -10002,7 +10002,7 @@
       <c r="Y165" s="58"/>
       <c r="Z165" s="58"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="68">
         <v>8</v>
       </c>
@@ -10050,7 +10050,7 @@
       <c r="Y166" s="58"/>
       <c r="Z166" s="58"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="67">
         <v>9</v>
       </c>
@@ -10098,7 +10098,7 @@
       <c r="Y167" s="58"/>
       <c r="Z167" s="58"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="68">
         <v>10</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="67">
         <v>11</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="68">
         <v>12</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="67">
         <v>13</v>
       </c>
@@ -10226,7 +10226,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="68">
         <v>14</v>
       </c>
@@ -10258,7 +10258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="67">
         <v>15</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="68">
         <v>16</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="175" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="67">
         <v>17</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="68">
         <v>18</v>
       </c>
@@ -10386,7 +10386,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="86">
         <v>19</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="86">
         <v>20</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="86">
         <v>21</v>
       </c>
@@ -10482,21 +10482,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="95" t="s">
+    <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="89" t="s">
         <v>715</v>
       </c>
-      <c r="B180" s="95"/>
-      <c r="C180" s="95"/>
+      <c r="B180" s="89"/>
+      <c r="C180" s="89"/>
       <c r="D180" s="87"/>
-      <c r="E180" s="95"/>
-      <c r="F180" s="95"/>
-      <c r="G180" s="95"/>
-      <c r="H180" s="95"/>
-      <c r="I180" s="95"/>
-      <c r="J180" s="95"/>
-    </row>
-    <row r="181" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E180" s="89"/>
+      <c r="F180" s="89"/>
+      <c r="G180" s="89"/>
+      <c r="H180" s="89"/>
+      <c r="I180" s="89"/>
+      <c r="J180" s="89"/>
+    </row>
+    <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="68">
         <v>1</v>
       </c>
@@ -10528,7 +10528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="68">
         <v>2</v>
       </c>
@@ -10560,7 +10560,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="68">
         <v>3</v>
       </c>
@@ -10592,7 +10592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="68">
         <v>4</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="68">
         <v>5</v>
       </c>
@@ -10656,7 +10656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="68">
         <v>6</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="68">
         <v>7</v>
       </c>
@@ -10720,7 +10720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="68">
         <v>8</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="1:10" s="28" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="68">
         <v>9</v>
       </c>
@@ -10784,21 +10784,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="97" t="s">
+    <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="91" t="s">
         <v>617</v>
       </c>
-      <c r="B190" s="98"/>
-      <c r="C190" s="98"/>
-      <c r="D190" s="98"/>
-      <c r="E190" s="98"/>
-      <c r="F190" s="98"/>
-      <c r="G190" s="98"/>
-      <c r="H190" s="98"/>
-      <c r="I190" s="98"/>
-      <c r="J190" s="99"/>
-    </row>
-    <row r="191" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B190" s="92"/>
+      <c r="C190" s="92"/>
+      <c r="D190" s="92"/>
+      <c r="E190" s="92"/>
+      <c r="F190" s="92"/>
+      <c r="G190" s="92"/>
+      <c r="H190" s="92"/>
+      <c r="I190" s="92"/>
+      <c r="J190" s="93"/>
+    </row>
+    <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="68">
         <v>1</v>
       </c>
@@ -10830,7 +10830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="68">
         <v>2</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="68">
         <v>3</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="68">
         <v>4</v>
       </c>
@@ -10926,7 +10926,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="68">
         <v>5</v>
       </c>
@@ -10958,7 +10958,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="68">
         <v>6</v>
       </c>
@@ -10990,7 +10990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="68">
         <v>7</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="87" t="s">
         <v>638</v>
       </c>
@@ -11036,7 +11036,7 @@
       <c r="I198" s="87"/>
       <c r="J198" s="87"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="48">
         <v>1</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="48">
         <v>2</v>
       </c>
@@ -11100,7 +11100,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="48">
         <v>3</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="48">
         <v>4</v>
       </c>
@@ -11164,7 +11164,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="87" t="s">
         <v>651</v>
       </c>
@@ -11178,7 +11178,7 @@
       <c r="I203" s="87"/>
       <c r="J203" s="87"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="48">
         <v>1</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="87" t="s">
         <v>657</v>
       </c>
@@ -11224,7 +11224,7 @@
       <c r="I205" s="87"/>
       <c r="J205" s="87"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="48">
         <v>1</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="48">
         <v>2</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="48">
         <v>3</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="48">
         <v>4</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="48">
         <v>5</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="48">
         <v>6</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="48">
         <v>7</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="48">
         <v>8</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="48">
         <v>9</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="85"/>
       <c r="B215" s="85"/>
       <c r="C215" s="85"/>
@@ -11526,7 +11526,7 @@
       <c r="I215" s="85"/>
       <c r="J215" s="85"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="48">
         <v>1</v>
       </c>
@@ -11558,7 +11558,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="83"/>
       <c r="B217" s="83"/>
       <c r="C217" s="83"/>
@@ -11572,7 +11572,7 @@
       <c r="I217" s="83"/>
       <c r="J217" s="83"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="48">
         <v>1</v>
       </c>
@@ -11604,7 +11604,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="48">
         <v>2</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="87" t="s">
         <v>733</v>
       </c>
@@ -11650,7 +11650,7 @@
       <c r="I220" s="87"/>
       <c r="J220" s="87"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="48">
         <v>1</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="48">
         <v>2</v>
       </c>
@@ -11714,7 +11714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="48">
         <v>3</v>
       </c>
@@ -11746,7 +11746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="48">
         <v>4</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="48">
         <v>5</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="87" t="s">
         <v>743</v>
       </c>
@@ -11824,7 +11824,7 @@
       <c r="I226" s="87"/>
       <c r="J226" s="87"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="48">
         <v>1</v>
       </c>
@@ -11856,7 +11856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="48">
         <v>2</v>
       </c>
@@ -11888,7 +11888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="48">
         <v>3</v>
       </c>
@@ -11920,7 +11920,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="48">
         <v>4</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="48">
         <v>5</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="48">
         <v>6</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="48">
         <v>7</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="48">
         <v>8</v>
       </c>
@@ -12080,7 +12080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="48">
         <v>9</v>
       </c>
@@ -12112,7 +12112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="48">
         <v>10</v>
       </c>
@@ -12144,7 +12144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="48">
         <v>11</v>
       </c>
@@ -12176,7 +12176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="87" t="s">
         <v>780</v>
       </c>
@@ -12190,7 +12190,7 @@
       <c r="I238" s="87"/>
       <c r="J238" s="87"/>
     </row>
-    <row r="239" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="48">
         <v>1</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="87" t="s">
         <v>792</v>
       </c>
@@ -12236,7 +12236,7 @@
       <c r="I240" s="87"/>
       <c r="J240" s="87"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="48">
         <v>1</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="48">
         <v>2</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="48">
         <v>3</v>
       </c>
@@ -12332,7 +12332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="48">
         <v>4</v>
       </c>
@@ -12364,7 +12364,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="48">
         <v>5</v>
       </c>
@@ -12396,7 +12396,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="48">
         <v>6</v>
       </c>
@@ -12428,7 +12428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="48">
         <v>7</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="48">
         <v>8</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="48">
         <v>9</v>
       </c>
@@ -12524,7 +12524,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="48">
         <v>10</v>
       </c>
@@ -12556,7 +12556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="48">
         <v>11</v>
       </c>
@@ -12588,7 +12588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="48">
         <v>12</v>
       </c>
@@ -12620,7 +12620,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="48">
         <v>13</v>
       </c>
@@ -12652,7 +12652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="87" t="s">
         <v>837</v>
       </c>
@@ -12666,7 +12666,7 @@
       <c r="I254" s="87"/>
       <c r="J254" s="87"/>
     </row>
-    <row r="255" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="48">
         <v>1</v>
       </c>
@@ -12698,7 +12698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="48">
         <v>2</v>
       </c>
@@ -12730,7 +12730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="87" t="s">
         <v>838</v>
       </c>
@@ -12744,7 +12744,7 @@
       <c r="I257" s="87"/>
       <c r="J257" s="87"/>
     </row>
-    <row r="258" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="48">
         <v>1</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="48">
         <v>2</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="48">
         <v>3</v>
       </c>
@@ -12840,7 +12840,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="48">
         <v>4</v>
       </c>
@@ -12872,7 +12872,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="48">
         <v>5</v>
       </c>
@@ -12906,6 +12906,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
     <mergeCell ref="A257:J257"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
@@ -12922,14 +12930,6 @@
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
     <mergeCell ref="A238:J238"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13028,35 +13028,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
   <dimension ref="A1:AF246"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="45.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="54.28515625" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="54.33203125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" customWidth="1"/>
-    <col min="12" max="12" width="53.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" customWidth="1"/>
+    <col min="12" max="12" width="53.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="52.28515625" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" customWidth="1"/>
+    <col min="17" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="71.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="52.33203125" customWidth="1"/>
+    <col min="21" max="21" width="20.88671875" customWidth="1"/>
     <col min="22" max="22" width="27" customWidth="1"/>
     <col min="24" max="25" width="29" customWidth="1"/>
-    <col min="26" max="26" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.42578125" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" customWidth="1"/>
+    <col min="26" max="26" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.44140625" customWidth="1"/>
+    <col min="29" max="29" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.6640625" customWidth="1"/>
+    <col min="31" max="31" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>5</v>
       </c>
@@ -13148,7 +13148,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>23</v>
       </c>
@@ -13228,7 +13228,7 @@
       <c r="AC2" s="28"/>
       <c r="AD2" s="28"/>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
         <v>25</v>
       </c>
@@ -13308,7 +13308,7 @@
       <c r="AC3" s="28"/>
       <c r="AD3" s="28"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>28</v>
       </c>
@@ -13388,7 +13388,7 @@
       <c r="AC4" s="28"/>
       <c r="AD4" s="28"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>58</v>
       </c>
@@ -13468,7 +13468,7 @@
       <c r="AC5" s="28"/>
       <c r="AD5" s="28"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>69</v>
       </c>
@@ -13548,7 +13548,7 @@
       <c r="AC6" s="28"/>
       <c r="AD6" s="28"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
         <v>73</v>
       </c>
@@ -13628,7 +13628,7 @@
       <c r="AC7" s="28"/>
       <c r="AD7" s="28"/>
     </row>
-    <row r="8" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="s">
         <v>77</v>
       </c>
@@ -13708,7 +13708,7 @@
       <c r="AC8" s="28"/>
       <c r="AD8" s="28"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="38" t="s">
         <v>79</v>
       </c>
@@ -13788,7 +13788,7 @@
       <c r="AC9" s="28"/>
       <c r="AD9" s="28"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="38" t="s">
         <v>80</v>
       </c>
@@ -13868,7 +13868,7 @@
       <c r="AC10" s="28"/>
       <c r="AD10" s="28"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="38" t="s">
         <v>81</v>
       </c>
@@ -13948,7 +13948,7 @@
       <c r="AC11" s="28"/>
       <c r="AD11" s="28"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="s">
         <v>83</v>
       </c>
@@ -14028,7 +14028,7 @@
       <c r="AC12" s="28"/>
       <c r="AD12" s="28"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
         <v>84</v>
       </c>
@@ -14108,7 +14108,7 @@
       <c r="AC13" s="28"/>
       <c r="AD13" s="28"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="38" t="s">
         <v>85</v>
       </c>
@@ -14188,7 +14188,7 @@
       <c r="AC14" s="28"/>
       <c r="AD14" s="28"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="38" t="s">
         <v>86</v>
       </c>
@@ -14268,7 +14268,7 @@
       <c r="AC15" s="28"/>
       <c r="AD15" s="28"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="s">
         <v>87</v>
       </c>
@@ -14348,7 +14348,7 @@
       <c r="AC16" s="28"/>
       <c r="AD16" s="28"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
         <v>88</v>
       </c>
@@ -14428,7 +14428,7 @@
       <c r="AC17" s="28"/>
       <c r="AD17" s="28"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="38" t="s">
         <v>89</v>
       </c>
@@ -14508,7 +14508,7 @@
       <c r="AC18" s="28"/>
       <c r="AD18" s="28"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
         <v>91</v>
       </c>
@@ -14588,7 +14588,7 @@
       <c r="AC19" s="28"/>
       <c r="AD19" s="28"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="s">
         <v>93</v>
       </c>
@@ -14668,7 +14668,7 @@
       <c r="AC20" s="28"/>
       <c r="AD20" s="28"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
         <v>94</v>
       </c>
@@ -14748,7 +14748,7 @@
       <c r="AC21" s="28"/>
       <c r="AD21" s="28"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="s">
         <v>135</v>
       </c>
@@ -14828,7 +14828,7 @@
       <c r="AC22" s="28"/>
       <c r="AD22" s="28"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" s="42" t="s">
         <v>140</v>
       </c>
@@ -14908,7 +14908,7 @@
       <c r="AC23" s="28"/>
       <c r="AD23" s="28"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="53" t="s">
         <v>63</v>
       </c>
@@ -14988,7 +14988,7 @@
       <c r="AC24" s="28"/>
       <c r="AD24" s="28"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
         <v>144</v>
       </c>
@@ -15068,7 +15068,7 @@
       <c r="AC25" s="28"/>
       <c r="AD25" s="28"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
         <v>145</v>
       </c>
@@ -15148,7 +15148,7 @@
       <c r="AC26" s="28"/>
       <c r="AD26" s="28"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
         <v>146</v>
       </c>
@@ -15228,7 +15228,7 @@
       <c r="AC27" s="28"/>
       <c r="AD27" s="28"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="s">
         <v>147</v>
       </c>
@@ -15308,7 +15308,7 @@
       <c r="AC28" s="28"/>
       <c r="AD28" s="28"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" s="46" t="s">
         <v>148</v>
       </c>
@@ -15388,7 +15388,7 @@
       <c r="AC29" s="28"/>
       <c r="AD29" s="28"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" s="46" t="s">
         <v>150</v>
       </c>
@@ -15468,7 +15468,7 @@
       <c r="AC30" s="28"/>
       <c r="AD30" s="28"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" s="46" t="s">
         <v>151</v>
       </c>
@@ -15548,7 +15548,7 @@
       <c r="AC31" s="28"/>
       <c r="AD31" s="28"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" s="46" t="s">
         <v>152</v>
       </c>
@@ -15628,7 +15628,7 @@
       <c r="AC32" s="28"/>
       <c r="AD32" s="28"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33" s="46" t="s">
         <v>153</v>
       </c>
@@ -15708,7 +15708,7 @@
       <c r="AC33" s="28"/>
       <c r="AD33" s="28"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34" s="46" t="s">
         <v>154</v>
       </c>
@@ -15788,7 +15788,7 @@
       <c r="AC34" s="28"/>
       <c r="AD34" s="28"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35" s="46" t="s">
         <v>155</v>
       </c>
@@ -15868,7 +15868,7 @@
       <c r="AC35" s="28"/>
       <c r="AD35" s="28"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
         <v>64</v>
       </c>
@@ -15948,7 +15948,7 @@
       <c r="AC36" s="28"/>
       <c r="AD36" s="28"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A37" s="54" t="s">
         <v>175</v>
       </c>
@@ -16030,7 +16030,7 @@
       <c r="AC37" s="28"/>
       <c r="AD37" s="28"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
         <v>179</v>
       </c>
@@ -16112,7 +16112,7 @@
       <c r="AC38" s="28"/>
       <c r="AD38" s="28"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
         <v>182</v>
       </c>
@@ -16194,7 +16194,7 @@
       <c r="AC39" s="28"/>
       <c r="AD39" s="28"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40" s="47" t="s">
         <v>185</v>
       </c>
@@ -16276,7 +16276,7 @@
       <c r="AC40" s="28"/>
       <c r="AD40" s="28"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" s="47" t="s">
         <v>188</v>
       </c>
@@ -16358,7 +16358,7 @@
       <c r="AC41" s="28"/>
       <c r="AD41" s="28"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="47" t="s">
         <v>190</v>
       </c>
@@ -16440,7 +16440,7 @@
       <c r="AC42" s="28"/>
       <c r="AD42" s="28"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" s="47" t="s">
         <v>193</v>
       </c>
@@ -16522,7 +16522,7 @@
       <c r="AC43" s="28"/>
       <c r="AD43" s="28"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" s="47" t="s">
         <v>196</v>
       </c>
@@ -16604,7 +16604,7 @@
       <c r="AC44" s="28"/>
       <c r="AD44" s="28"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" s="47" t="s">
         <v>198</v>
       </c>
@@ -16686,7 +16686,7 @@
       <c r="AC45" s="28"/>
       <c r="AD45" s="28"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46" s="47" t="s">
         <v>200</v>
       </c>
@@ -16768,7 +16768,7 @@
       <c r="AC46" s="28"/>
       <c r="AD46" s="28"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A47" s="47" t="s">
         <v>202</v>
       </c>
@@ -16850,7 +16850,7 @@
       <c r="AC47" s="28"/>
       <c r="AD47" s="28"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48" s="47" t="s">
         <v>204</v>
       </c>
@@ -16932,7 +16932,7 @@
       <c r="AC48" s="28"/>
       <c r="AD48" s="28"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A49" s="47" t="s">
         <v>206</v>
       </c>
@@ -17014,7 +17014,7 @@
       <c r="AC49" s="28"/>
       <c r="AD49" s="28"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A50" s="47" t="s">
         <v>208</v>
       </c>
@@ -17096,7 +17096,7 @@
       <c r="AC50" s="28"/>
       <c r="AD50" s="28"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A51" s="47" t="s">
         <v>210</v>
       </c>
@@ -17178,7 +17178,7 @@
       <c r="AC51" s="28"/>
       <c r="AD51" s="28"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A52" s="47" t="s">
         <v>212</v>
       </c>
@@ -17260,7 +17260,7 @@
       <c r="AC52" s="28"/>
       <c r="AD52" s="28"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A53" s="47" t="s">
         <v>687</v>
       </c>
@@ -17342,7 +17342,7 @@
       <c r="AC53" s="28"/>
       <c r="AD53" s="28"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A54" s="55" t="s">
         <v>213</v>
       </c>
@@ -17424,7 +17424,7 @@
       <c r="AC54" s="28"/>
       <c r="AD54" s="28"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A55" s="48" t="s">
         <v>214</v>
       </c>
@@ -17506,7 +17506,7 @@
       <c r="AC55" s="28"/>
       <c r="AD55" s="28"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A56" s="48" t="s">
         <v>215</v>
       </c>
@@ -17588,7 +17588,7 @@
       <c r="AC56" s="28"/>
       <c r="AD56" s="28"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A57" s="48" t="s">
         <v>216</v>
       </c>
@@ -17670,7 +17670,7 @@
       <c r="AC57" s="28"/>
       <c r="AD57" s="28"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A58" s="48" t="s">
         <v>217</v>
       </c>
@@ -17752,7 +17752,7 @@
       <c r="AC58" s="28"/>
       <c r="AD58" s="28"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A59" s="48" t="s">
         <v>218</v>
       </c>
@@ -17834,7 +17834,7 @@
       <c r="AC59" s="28"/>
       <c r="AD59" s="28"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A60" s="48" t="s">
         <v>219</v>
       </c>
@@ -17916,7 +17916,7 @@
       <c r="AC60" s="28"/>
       <c r="AD60" s="28"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A61" s="48" t="s">
         <v>220</v>
       </c>
@@ -17998,7 +17998,7 @@
       <c r="AC61" s="28"/>
       <c r="AD61" s="28"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A62" s="48" t="s">
         <v>221</v>
       </c>
@@ -18080,7 +18080,7 @@
       <c r="AC62" s="28"/>
       <c r="AD62" s="28"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A63" s="51" t="s">
         <v>222</v>
       </c>
@@ -18162,7 +18162,7 @@
       <c r="AC63" s="28"/>
       <c r="AD63" s="28"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A64" s="56" t="s">
         <v>249</v>
       </c>
@@ -18244,7 +18244,7 @@
       <c r="AC64" s="28"/>
       <c r="AD64" s="28"/>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A65" s="48" t="s">
         <v>253</v>
       </c>
@@ -18326,7 +18326,7 @@
       <c r="AC65" s="28"/>
       <c r="AD65" s="28"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A66" s="48" t="s">
         <v>256</v>
       </c>
@@ -18408,7 +18408,7 @@
       <c r="AC66" s="28"/>
       <c r="AD66" s="28"/>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A67" s="48" t="s">
         <v>259</v>
       </c>
@@ -18490,7 +18490,7 @@
       <c r="AC67" s="28"/>
       <c r="AD67" s="28"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A68" s="48" t="s">
         <v>262</v>
       </c>
@@ -18572,7 +18572,7 @@
       <c r="AC68" s="28"/>
       <c r="AD68" s="28"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A69" s="48" t="s">
         <v>265</v>
       </c>
@@ -18654,7 +18654,7 @@
       <c r="AC69" s="28"/>
       <c r="AD69" s="28"/>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A70" s="48" t="s">
         <v>268</v>
       </c>
@@ -18736,7 +18736,7 @@
       <c r="AC70" s="28"/>
       <c r="AD70" s="28"/>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A71" s="48" t="s">
         <v>271</v>
       </c>
@@ -18818,7 +18818,7 @@
       <c r="AC71" s="28"/>
       <c r="AD71" s="28"/>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A72" s="48" t="s">
         <v>274</v>
       </c>
@@ -18900,7 +18900,7 @@
       <c r="AC72" s="28"/>
       <c r="AD72" s="28"/>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A73" s="48" t="s">
         <v>277</v>
       </c>
@@ -18982,7 +18982,7 @@
       <c r="AC73" s="28"/>
       <c r="AD73" s="28"/>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A74" s="51" t="s">
         <v>280</v>
       </c>
@@ -19066,7 +19066,7 @@
       <c r="AC74" s="28"/>
       <c r="AD74" s="28"/>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A75" s="62" t="s">
         <v>282</v>
       </c>
@@ -19150,7 +19150,7 @@
       <c r="AC75" s="28"/>
       <c r="AD75" s="28"/>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A76" s="48" t="s">
         <v>285</v>
       </c>
@@ -19234,7 +19234,7 @@
       <c r="AC76" s="28"/>
       <c r="AD76" s="28"/>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A77" s="48" t="s">
         <v>287</v>
       </c>
@@ -19318,7 +19318,7 @@
       <c r="AC77" s="28"/>
       <c r="AD77" s="28"/>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A78" s="48" t="s">
         <v>289</v>
       </c>
@@ -19402,7 +19402,7 @@
       <c r="AC78" s="28"/>
       <c r="AD78" s="28"/>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A79" s="48" t="s">
         <v>292</v>
       </c>
@@ -19486,7 +19486,7 @@
       <c r="AC79" s="28"/>
       <c r="AD79" s="28"/>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A80" s="48" t="s">
         <v>295</v>
       </c>
@@ -19570,7 +19570,7 @@
       <c r="AC80" s="28"/>
       <c r="AD80" s="28"/>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="s">
         <v>298</v>
       </c>
@@ -19654,7 +19654,7 @@
       <c r="AC81" s="28"/>
       <c r="AD81" s="28"/>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A82" s="48" t="s">
         <v>301</v>
       </c>
@@ -19738,7 +19738,7 @@
       <c r="AC82" s="28"/>
       <c r="AD82" s="28"/>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A83" s="48" t="s">
         <v>304</v>
       </c>
@@ -19822,7 +19822,7 @@
       <c r="AC83" s="28"/>
       <c r="AD83" s="28"/>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A84" s="48" t="s">
         <v>306</v>
       </c>
@@ -19906,7 +19906,7 @@
       <c r="AC84" s="28"/>
       <c r="AD84" s="28"/>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A85" s="48" t="s">
         <v>308</v>
       </c>
@@ -19990,7 +19990,7 @@
       <c r="AC85" s="28"/>
       <c r="AD85" s="28"/>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A86" s="48" t="s">
         <v>310</v>
       </c>
@@ -20074,7 +20074,7 @@
       <c r="AC86" s="28"/>
       <c r="AD86" s="28"/>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A87" s="48" t="s">
         <v>313</v>
       </c>
@@ -20158,7 +20158,7 @@
       <c r="AC87" s="28"/>
       <c r="AD87" s="28"/>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A88" s="48" t="s">
         <v>316</v>
       </c>
@@ -20242,7 +20242,7 @@
       <c r="AC88" s="28"/>
       <c r="AD88" s="28"/>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A89" s="48" t="s">
         <v>319</v>
       </c>
@@ -20326,7 +20326,7 @@
       <c r="AC89" s="28"/>
       <c r="AD89" s="28"/>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A90" s="48" t="s">
         <v>322</v>
       </c>
@@ -20410,7 +20410,7 @@
       <c r="AC90" s="28"/>
       <c r="AD90" s="28"/>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A91" s="48" t="s">
         <v>324</v>
       </c>
@@ -20494,7 +20494,7 @@
       <c r="AC91" s="28"/>
       <c r="AD91" s="28"/>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A92" s="48" t="s">
         <v>327</v>
       </c>
@@ -20578,7 +20578,7 @@
       <c r="AC92" s="28"/>
       <c r="AD92" s="28"/>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A93" s="48" t="s">
         <v>330</v>
       </c>
@@ -20662,7 +20662,7 @@
       <c r="AC93" s="28"/>
       <c r="AD93" s="28"/>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A94" s="48" t="s">
         <v>332</v>
       </c>
@@ -20746,7 +20746,7 @@
       <c r="AC94" s="28"/>
       <c r="AD94" s="28"/>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A95" s="48" t="s">
         <v>334</v>
       </c>
@@ -20830,7 +20830,7 @@
       <c r="AC95" s="28"/>
       <c r="AD95" s="28"/>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A96" s="48" t="s">
         <v>336</v>
       </c>
@@ -20914,7 +20914,7 @@
       <c r="AC96" s="28"/>
       <c r="AD96" s="28"/>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A97" s="48" t="s">
         <v>338</v>
       </c>
@@ -20998,7 +20998,7 @@
       <c r="AC97" s="28"/>
       <c r="AD97" s="28"/>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A98" s="48" t="s">
         <v>340</v>
       </c>
@@ -21082,7 +21082,7 @@
       <c r="AC98" s="28"/>
       <c r="AD98" s="28"/>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A99" s="48" t="s">
         <v>342</v>
       </c>
@@ -21166,7 +21166,7 @@
       <c r="AC99" s="28"/>
       <c r="AD99" s="28"/>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A100" s="48" t="s">
         <v>344</v>
       </c>
@@ -21250,7 +21250,7 @@
       <c r="AC100" s="28"/>
       <c r="AD100" s="28"/>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A101" s="48" t="s">
         <v>597</v>
       </c>
@@ -21334,7 +21334,7 @@
       <c r="AC101" s="28"/>
       <c r="AD101" s="28"/>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A102" s="48" t="s">
         <v>348</v>
       </c>
@@ -21418,7 +21418,7 @@
       <c r="AC102" s="28"/>
       <c r="AD102" s="28"/>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A103" s="48" t="s">
         <v>352</v>
       </c>
@@ -21502,7 +21502,7 @@
       <c r="AC103" s="28"/>
       <c r="AD103" s="28"/>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A104" s="48" t="s">
         <v>355</v>
       </c>
@@ -21586,7 +21586,7 @@
       <c r="AC104" s="28"/>
       <c r="AD104" s="28"/>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A105" s="48" t="s">
         <v>358</v>
       </c>
@@ -21670,7 +21670,7 @@
       <c r="AC105" s="28"/>
       <c r="AD105" s="28"/>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A106" s="48" t="s">
         <v>361</v>
       </c>
@@ -21754,7 +21754,7 @@
       <c r="AC106" s="28"/>
       <c r="AD106" s="28"/>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A107" s="48" t="s">
         <v>364</v>
       </c>
@@ -21838,7 +21838,7 @@
       <c r="AC107" s="28"/>
       <c r="AD107" s="28"/>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A108" s="48" t="s">
         <v>367</v>
       </c>
@@ -21922,7 +21922,7 @@
       <c r="AC108" s="28"/>
       <c r="AD108" s="28"/>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A109" s="48" t="s">
         <v>369</v>
       </c>
@@ -22006,7 +22006,7 @@
       <c r="AC109" s="28"/>
       <c r="AD109" s="28"/>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A110" s="48" t="s">
         <v>371</v>
       </c>
@@ -22090,7 +22090,7 @@
       <c r="AC110" s="28"/>
       <c r="AD110" s="28"/>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A111" s="48" t="s">
         <v>598</v>
       </c>
@@ -22174,7 +22174,7 @@
       <c r="AC111" s="28"/>
       <c r="AD111" s="28"/>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A112" s="48" t="s">
         <v>690</v>
       </c>
@@ -22258,7 +22258,7 @@
       <c r="AC112" s="28"/>
       <c r="AD112" s="28"/>
     </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
         <v>693</v>
       </c>
@@ -22342,7 +22342,7 @@
       <c r="AC113" s="28"/>
       <c r="AD113" s="28"/>
     </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A114" s="48" t="s">
         <v>696</v>
       </c>
@@ -22426,7 +22426,7 @@
       <c r="AC114" s="28"/>
       <c r="AD114" s="28"/>
     </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A115" s="48" t="s">
         <v>699</v>
       </c>
@@ -22510,7 +22510,7 @@
       <c r="AC115" s="28"/>
       <c r="AD115" s="28"/>
     </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A116" s="48" t="s">
         <v>378</v>
       </c>
@@ -22594,7 +22594,7 @@
       <c r="AC116" s="28"/>
       <c r="AD116" s="28"/>
     </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A117" s="48" t="s">
         <v>383</v>
       </c>
@@ -22678,7 +22678,7 @@
       <c r="AC117" s="28"/>
       <c r="AD117" s="28"/>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A118" s="48" t="s">
         <v>397</v>
       </c>
@@ -22762,7 +22762,7 @@
       <c r="AC118" s="28"/>
       <c r="AD118" s="28"/>
     </row>
-    <row r="119" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A119" s="48" t="s">
         <v>399</v>
       </c>
@@ -22846,7 +22846,7 @@
       <c r="AC119" s="28"/>
       <c r="AD119" s="28"/>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A120" s="48" t="s">
         <v>400</v>
       </c>
@@ -22930,7 +22930,7 @@
       <c r="AC120" s="28"/>
       <c r="AD120" s="28"/>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A121" s="48" t="s">
         <v>401</v>
       </c>
@@ -23014,7 +23014,7 @@
       <c r="AC121" s="28"/>
       <c r="AD121" s="28"/>
     </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A122" s="48" t="s">
         <v>402</v>
       </c>
@@ -23098,7 +23098,7 @@
       <c r="AC122" s="28"/>
       <c r="AD122" s="28"/>
     </row>
-    <row r="123" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A123" s="48" t="s">
         <v>403</v>
       </c>
@@ -23182,7 +23182,7 @@
       <c r="AC123" s="28"/>
       <c r="AD123" s="28"/>
     </row>
-    <row r="124" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A124" s="48" t="s">
         <v>405</v>
       </c>
@@ -23266,7 +23266,7 @@
       <c r="AC124" s="28"/>
       <c r="AD124" s="28"/>
     </row>
-    <row r="125" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A125" s="48" t="s">
         <v>407</v>
       </c>
@@ -23350,7 +23350,7 @@
       <c r="AC125" s="28"/>
       <c r="AD125" s="28"/>
     </row>
-    <row r="126" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:30" ht="27" x14ac:dyDescent="0.3">
       <c r="A126" s="62" t="s">
         <v>413</v>
       </c>
@@ -23434,7 +23434,7 @@
       <c r="AC126" s="28"/>
       <c r="AD126" s="28"/>
     </row>
-    <row r="127" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A127" s="48" t="s">
         <v>417</v>
       </c>
@@ -23518,7 +23518,7 @@
       <c r="AC127" s="28"/>
       <c r="AD127" s="28"/>
     </row>
-    <row r="128" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A128" s="48" t="s">
         <v>420</v>
       </c>
@@ -23602,7 +23602,7 @@
       <c r="AC128" s="28"/>
       <c r="AD128" s="28"/>
     </row>
-    <row r="129" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:30" ht="27" x14ac:dyDescent="0.3">
       <c r="A129" s="48" t="s">
         <v>422</v>
       </c>
@@ -23686,7 +23686,7 @@
       <c r="AC129" s="28"/>
       <c r="AD129" s="28"/>
     </row>
-    <row r="130" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:30" ht="27" x14ac:dyDescent="0.3">
       <c r="A130" s="48" t="s">
         <v>424</v>
       </c>
@@ -23770,7 +23770,7 @@
       <c r="AC130" s="28"/>
       <c r="AD130" s="28"/>
     </row>
-    <row r="131" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A131" s="48" t="s">
         <v>427</v>
       </c>
@@ -23854,7 +23854,7 @@
       <c r="AC131" s="28"/>
       <c r="AD131" s="28"/>
     </row>
-    <row r="132" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A132" s="48" t="s">
         <v>430</v>
       </c>
@@ -23938,7 +23938,7 @@
       <c r="AC132" s="28"/>
       <c r="AD132" s="28"/>
     </row>
-    <row r="133" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A133" s="48" t="s">
         <v>433</v>
       </c>
@@ -24022,7 +24022,7 @@
       <c r="AC133" s="28"/>
       <c r="AD133" s="28"/>
     </row>
-    <row r="134" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:30" ht="27" x14ac:dyDescent="0.3">
       <c r="A134" s="48" t="s">
         <v>436</v>
       </c>
@@ -24106,7 +24106,7 @@
       <c r="AC134" s="28"/>
       <c r="AD134" s="28"/>
     </row>
-    <row r="135" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A135" s="48" t="s">
         <v>438</v>
       </c>
@@ -24190,7 +24190,7 @@
       <c r="AC135" s="28"/>
       <c r="AD135" s="28"/>
     </row>
-    <row r="136" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A136" s="48" t="s">
         <v>703</v>
       </c>
@@ -24274,7 +24274,7 @@
       <c r="AC136" s="28"/>
       <c r="AD136" s="28"/>
     </row>
-    <row r="137" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A137" s="48" t="s">
         <v>397</v>
       </c>
@@ -24358,7 +24358,7 @@
       <c r="AC137" s="28"/>
       <c r="AD137" s="28"/>
     </row>
-    <row r="138" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A138" s="48" t="s">
         <v>399</v>
       </c>
@@ -24442,7 +24442,7 @@
       <c r="AC138" s="28"/>
       <c r="AD138" s="28"/>
     </row>
-    <row r="139" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A139" s="48" t="s">
         <v>400</v>
       </c>
@@ -24526,7 +24526,7 @@
       <c r="AC139" s="28"/>
       <c r="AD139" s="28"/>
     </row>
-    <row r="140" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
         <v>401</v>
       </c>
@@ -24610,7 +24610,7 @@
       <c r="AC140" s="28"/>
       <c r="AD140" s="28"/>
     </row>
-    <row r="141" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A141" s="48" t="s">
         <v>402</v>
       </c>
@@ -24694,7 +24694,7 @@
       <c r="AC141" s="28"/>
       <c r="AD141" s="28"/>
     </row>
-    <row r="142" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A142" s="48" t="s">
         <v>403</v>
       </c>
@@ -24778,7 +24778,7 @@
       <c r="AC142" s="28"/>
       <c r="AD142" s="28"/>
     </row>
-    <row r="143" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A143" s="48" t="s">
         <v>405</v>
       </c>
@@ -24862,7 +24862,7 @@
       <c r="AC143" s="28"/>
       <c r="AD143" s="28"/>
     </row>
-    <row r="144" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A144" s="48" t="s">
         <v>442</v>
       </c>
@@ -24946,7 +24946,7 @@
       <c r="AC144" s="28"/>
       <c r="AD144" s="28"/>
     </row>
-    <row r="145" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A145" s="48" t="s">
         <v>446</v>
       </c>
@@ -25030,7 +25030,7 @@
       <c r="AC145" s="28"/>
       <c r="AD145" s="28"/>
     </row>
-    <row r="146" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A146" s="48" t="s">
         <v>449</v>
       </c>
@@ -25114,7 +25114,7 @@
       <c r="AC146" s="28"/>
       <c r="AD146" s="28"/>
     </row>
-    <row r="147" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A147" s="48" t="s">
         <v>451</v>
       </c>
@@ -25198,7 +25198,7 @@
       <c r="AC147" s="28"/>
       <c r="AD147" s="28"/>
     </row>
-    <row r="148" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A148" s="48" t="s">
         <v>454</v>
       </c>
@@ -25282,7 +25282,7 @@
       <c r="AC148" s="28"/>
       <c r="AD148" s="28"/>
     </row>
-    <row r="149" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A149" s="48" t="s">
         <v>457</v>
       </c>
@@ -25366,7 +25366,7 @@
       <c r="AC149" s="28"/>
       <c r="AD149" s="28"/>
     </row>
-    <row r="150" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A150" s="48" t="s">
         <v>460</v>
       </c>
@@ -25450,7 +25450,7 @@
       <c r="AC150" s="28"/>
       <c r="AD150" s="28"/>
     </row>
-    <row r="151" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A151" s="48" t="s">
         <v>463</v>
       </c>
@@ -25534,7 +25534,7 @@
       <c r="AC151" s="28"/>
       <c r="AD151" s="28"/>
     </row>
-    <row r="152" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="48" t="s">
         <v>466</v>
       </c>
@@ -25618,7 +25618,7 @@
       <c r="AC152" s="28"/>
       <c r="AD152" s="28"/>
     </row>
-    <row r="153" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="48" t="s">
         <v>469</v>
       </c>
@@ -25702,7 +25702,7 @@
       <c r="AC153" s="28"/>
       <c r="AD153" s="28"/>
     </row>
-    <row r="154" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="48" t="s">
         <v>509</v>
       </c>
@@ -25786,7 +25786,7 @@
       <c r="AC154" s="28"/>
       <c r="AD154" s="28"/>
     </row>
-    <row r="155" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="66" t="s">
         <v>539</v>
       </c>
@@ -25870,7 +25870,7 @@
       <c r="AC155" s="28"/>
       <c r="AD155" s="28"/>
     </row>
-    <row r="156" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="70" t="s">
         <v>543</v>
       </c>
@@ -25954,7 +25954,7 @@
       <c r="AC156" s="28"/>
       <c r="AD156" s="28"/>
     </row>
-    <row r="157" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="66" t="s">
         <v>546</v>
       </c>
@@ -26038,7 +26038,7 @@
       <c r="AC157" s="28"/>
       <c r="AD157" s="28"/>
     </row>
-    <row r="158" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="70" t="s">
         <v>549</v>
       </c>
@@ -26122,7 +26122,7 @@
       <c r="AC158" s="28"/>
       <c r="AD158" s="28"/>
     </row>
-    <row r="159" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="66" t="s">
         <v>551</v>
       </c>
@@ -26206,7 +26206,7 @@
       <c r="AC159" s="28"/>
       <c r="AD159" s="28"/>
     </row>
-    <row r="160" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="70" t="s">
         <v>553</v>
       </c>
@@ -26290,7 +26290,7 @@
       <c r="AC160" s="28"/>
       <c r="AD160" s="28"/>
     </row>
-    <row r="161" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="66" t="s">
         <v>555</v>
       </c>
@@ -26374,7 +26374,7 @@
       <c r="AC161" s="28"/>
       <c r="AD161" s="28"/>
     </row>
-    <row r="162" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="70" t="s">
         <v>557</v>
       </c>
@@ -26458,7 +26458,7 @@
       <c r="AC162" s="28"/>
       <c r="AD162" s="28"/>
     </row>
-    <row r="163" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="66" t="s">
         <v>559</v>
       </c>
@@ -26542,7 +26542,7 @@
       <c r="AC163" s="28"/>
       <c r="AD163" s="28"/>
     </row>
-    <row r="164" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="70" t="s">
         <v>562</v>
       </c>
@@ -26626,7 +26626,7 @@
       <c r="AC164" s="28"/>
       <c r="AD164" s="28"/>
     </row>
-    <row r="165" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="66" t="s">
         <v>565</v>
       </c>
@@ -26710,7 +26710,7 @@
       <c r="AC165" s="28"/>
       <c r="AD165" s="28"/>
     </row>
-    <row r="166" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="70" t="s">
         <v>568</v>
       </c>
@@ -26794,7 +26794,7 @@
       <c r="AC166" s="28"/>
       <c r="AD166" s="28"/>
     </row>
-    <row r="167" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="66" t="s">
         <v>571</v>
       </c>
@@ -26878,7 +26878,7 @@
       <c r="AC167" s="28"/>
       <c r="AD167" s="28"/>
     </row>
-    <row r="168" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="70" t="s">
         <v>574</v>
       </c>
@@ -26962,7 +26962,7 @@
       <c r="AC168" s="28"/>
       <c r="AD168" s="28"/>
     </row>
-    <row r="169" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="66" t="s">
         <v>577</v>
       </c>
@@ -27046,7 +27046,7 @@
       <c r="AC169" s="28"/>
       <c r="AD169" s="28"/>
     </row>
-    <row r="170" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="66" t="s">
         <v>579</v>
       </c>
@@ -27130,7 +27130,7 @@
       <c r="AC170" s="28"/>
       <c r="AD170" s="28"/>
     </row>
-    <row r="171" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="66" t="s">
         <v>581</v>
       </c>
@@ -27214,7 +27214,7 @@
       <c r="AC171" s="28"/>
       <c r="AD171" s="28"/>
     </row>
-    <row r="172" spans="1:30" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="66" t="s">
         <v>584</v>
       </c>
@@ -27298,7 +27298,7 @@
       <c r="AC172" s="28"/>
       <c r="AD172" s="28"/>
     </row>
-    <row r="173" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="76" t="s">
         <v>919</v>
       </c>
@@ -27382,7 +27382,7 @@
       <c r="AC173" s="28"/>
       <c r="AD173" s="28"/>
     </row>
-    <row r="174" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="76" t="s">
         <v>922</v>
       </c>
@@ -27466,7 +27466,7 @@
       <c r="AC174" s="28"/>
       <c r="AD174" s="28"/>
     </row>
-    <row r="175" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="76" t="s">
         <v>925</v>
       </c>
@@ -27550,7 +27550,7 @@
       <c r="AC175" s="48"/>
       <c r="AD175" s="48"/>
     </row>
-    <row r="176" spans="1:30" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:30" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="70" t="s">
         <v>601</v>
       </c>
@@ -27642,7 +27642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="177" spans="1:32" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="70" t="s">
         <v>604</v>
       </c>
@@ -27734,7 +27734,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="178" spans="1:32" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="70" t="s">
         <v>606</v>
       </c>
@@ -27826,7 +27826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:32" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="70" t="s">
         <v>607</v>
       </c>
@@ -27918,7 +27918,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="180" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="70" t="s">
         <v>609</v>
       </c>
@@ -28010,7 +28010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:32" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="70" t="s">
         <v>610</v>
       </c>
@@ -28102,7 +28102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="70" t="s">
         <v>611</v>
       </c>
@@ -28194,7 +28194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="70" t="s">
         <v>615</v>
       </c>
@@ -28286,7 +28286,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="184" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="70" t="s">
         <v>614</v>
       </c>
@@ -28378,7 +28378,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="185" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="70" t="s">
         <v>619</v>
       </c>
@@ -28473,7 +28473,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="186" spans="1:32" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="70" t="s">
         <v>623</v>
       </c>
@@ -28568,7 +28568,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="187" spans="1:32" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="70" t="s">
         <v>629</v>
       </c>
@@ -28663,7 +28663,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="188" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="70" t="s">
         <v>630</v>
       </c>
@@ -28758,7 +28758,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="189" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="70" t="s">
         <v>636</v>
       </c>
@@ -28850,7 +28850,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="190" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="70" t="s">
         <v>849</v>
       </c>
@@ -28942,7 +28942,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="191" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="70" t="s">
         <v>850</v>
       </c>
@@ -29034,7 +29034,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="192" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="70" t="s">
         <v>640</v>
       </c>
@@ -29126,7 +29126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="193" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="70" t="s">
         <v>642</v>
       </c>
@@ -29218,7 +29218,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="70" t="s">
         <v>648</v>
       </c>
@@ -29310,7 +29310,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="70" t="s">
         <v>649</v>
       </c>
@@ -29402,7 +29402,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="70" t="s">
         <v>654</v>
       </c>
@@ -29494,7 +29494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="197" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="70" t="s">
         <v>656</v>
       </c>
@@ -29586,7 +29586,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="70" t="s">
         <v>662</v>
       </c>
@@ -29678,7 +29678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="199" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="70" t="s">
         <v>665</v>
       </c>
@@ -29770,7 +29770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="200" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="70" t="s">
         <v>666</v>
       </c>
@@ -29862,7 +29862,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="201" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="70" t="s">
         <v>671</v>
       </c>
@@ -29954,7 +29954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="202" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="70" t="s">
         <v>676</v>
       </c>
@@ -30046,7 +30046,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="203" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="70" t="s">
         <v>677</v>
       </c>
@@ -30138,7 +30138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="204" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="70" t="s">
         <v>879</v>
       </c>
@@ -30230,7 +30230,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="205" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="70" t="s">
         <v>882</v>
       </c>
@@ -30322,7 +30322,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="206" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="70" t="s">
         <v>883</v>
       </c>
@@ -30414,7 +30414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="207" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="70" t="s">
         <v>732</v>
       </c>
@@ -30506,7 +30506,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="208" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="70" t="s">
         <v>735</v>
       </c>
@@ -30598,7 +30598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="209" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="70" t="s">
         <v>737</v>
       </c>
@@ -30690,7 +30690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="70" t="s">
         <v>777</v>
       </c>
@@ -30782,7 +30782,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="211" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="70" t="s">
         <v>866</v>
       </c>
@@ -30874,7 +30874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="212" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="70" t="s">
         <v>867</v>
       </c>
@@ -30966,7 +30966,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="213" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="70" t="s">
         <v>742</v>
       </c>
@@ -31058,7 +31058,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="214" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="70" t="s">
         <v>748</v>
       </c>
@@ -31150,7 +31150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="215" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="70" t="s">
         <v>749</v>
       </c>
@@ -31242,7 +31242,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="216" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="70" t="s">
         <v>754</v>
       </c>
@@ -31334,7 +31334,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="70" t="s">
         <v>755</v>
       </c>
@@ -31426,7 +31426,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="218" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="70" t="s">
         <v>756</v>
       </c>
@@ -31518,7 +31518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="219" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="70" t="s">
         <v>761</v>
       </c>
@@ -31610,7 +31610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="220" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="70" t="s">
         <v>764</v>
       </c>
@@ -31702,7 +31702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="221" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="70" t="s">
         <v>769</v>
       </c>
@@ -31794,7 +31794,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="222" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="70" t="s">
         <v>772</v>
       </c>
@@ -31886,7 +31886,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="223" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="70" t="s">
         <v>773</v>
       </c>
@@ -31978,7 +31978,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="224" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="70" t="s">
         <v>779</v>
       </c>
@@ -32070,7 +32070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="225" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="70" t="s">
         <v>791</v>
       </c>
@@ -32162,7 +32162,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="226" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="70" t="s">
         <v>796</v>
       </c>
@@ -32254,7 +32254,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="227" spans="1:30" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:30" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="70" t="s">
         <v>801</v>
       </c>
@@ -32346,7 +32346,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="228" spans="1:30" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:30" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="70" t="s">
         <v>803</v>
       </c>
@@ -32438,7 +32438,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="229" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="70" t="s">
         <v>805</v>
       </c>
@@ -32497,7 +32497,7 @@
         <v>906</v>
       </c>
       <c r="T229" s="48" t="s">
-        <v>22</v>
+        <v>909</v>
       </c>
       <c r="U229" s="48" t="s">
         <v>22</v>
@@ -32530,7 +32530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="70" t="s">
         <v>810</v>
       </c>
@@ -32622,7 +32622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="231" spans="1:30" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:30" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="70" t="s">
         <v>812</v>
       </c>
@@ -32714,7 +32714,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="232" spans="1:30" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:30" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="70" t="s">
         <v>816</v>
       </c>
@@ -32806,7 +32806,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="70" t="s">
         <v>821</v>
       </c>
@@ -32898,7 +32898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="70" t="s">
         <v>824</v>
       </c>
@@ -32990,7 +32990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="70" t="s">
         <v>825</v>
       </c>
@@ -33082,7 +33082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="70" t="s">
         <v>830</v>
       </c>
@@ -33174,7 +33174,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="70" t="s">
         <v>928</v>
       </c>
@@ -33266,7 +33266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="238" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="70" t="s">
         <v>870</v>
       </c>
@@ -33358,7 +33358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="239" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="70" t="s">
         <v>874</v>
       </c>
@@ -33450,7 +33450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="240" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="70" t="s">
         <v>840</v>
       </c>
@@ -33542,7 +33542,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="241" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="70" t="s">
         <v>844</v>
       </c>
@@ -33634,7 +33634,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="242" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="70" t="s">
         <v>846</v>
       </c>
@@ -33726,7 +33726,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="243" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="70" t="s">
         <v>859</v>
       </c>
@@ -33818,7 +33818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="244" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="70" t="s">
         <v>861</v>
       </c>
@@ -33910,7 +33910,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>887</v>
       </c>
@@ -34002,7 +34002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="246" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>894</v>
       </c>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever654\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataQAsever130226\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360DA765-C095-47C4-8204-244D0D4608FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10FFCD5-63E5-41F1-990E-C81AE5E856EF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -2815,7 +2815,7 @@
     <t>TD_UI_Admin_OEV_13</t>
   </si>
   <si>
-    <t>https://console.zlaata.com/admin/subscriber</t>
+    <t>https://qa.adm.testingserver8.com/admin/subscriber</t>
   </si>
 </sst>
 </file>
@@ -3475,6 +3475,24 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3501,24 +3519,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4323,20 +4323,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
   <dimension ref="A1:Z262"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.33203125" customWidth="1"/>
-    <col min="4" max="4" width="118.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="4" max="4" width="118.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="28">
         <v>1</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>2</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>3</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
         <v>4</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="28">
         <v>5</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="28">
         <v>6</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="28">
         <v>7</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="28">
         <v>8</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
         <v>9</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="28">
         <v>10</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="28">
         <v>11</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="28">
         <v>12</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="28">
         <v>13</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="28">
         <v>14</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="28">
         <v>15</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="28">
         <v>16</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="28">
         <v>17</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="28">
         <v>18</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <v>19</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <v>20</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
         <v>21</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="45">
         <v>22</v>
       </c>
@@ -5072,21 +5072,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="97" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="99"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
         <v>1</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>2</v>
       </c>
@@ -5150,7 +5150,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>3</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>4</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>5</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>6</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>7</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>8</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>9</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>10</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>11</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>12</v>
       </c>
@@ -5470,21 +5470,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="100" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="101"/>
-      <c r="H37" s="101"/>
-      <c r="I37" s="101"/>
-      <c r="J37" s="102"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B37" s="92"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="93"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>1</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>3</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>4</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>5</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>6</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>7</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>8</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>9</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>10</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>11</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>12</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>13</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>14</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>15</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>16</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>16</v>
       </c>
@@ -6028,21 +6028,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="100" t="s">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="91" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="101"/>
-      <c r="C55" s="101"/>
-      <c r="D55" s="101"/>
-      <c r="E55" s="101"/>
-      <c r="F55" s="101"/>
-      <c r="G55" s="101"/>
-      <c r="H55" s="101"/>
-      <c r="I55" s="101"/>
-      <c r="J55" s="102"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B55" s="92"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="92"/>
+      <c r="F55" s="92"/>
+      <c r="G55" s="92"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="92"/>
+      <c r="J55" s="93"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="25">
         <v>1</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="25">
         <v>2</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="25">
         <v>3</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="25">
         <v>4</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="25">
         <v>5</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="25">
         <v>6</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="25">
         <v>7</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="25">
         <v>8</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="25">
         <v>9</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="25">
         <v>10</v>
       </c>
@@ -6362,21 +6362,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="100" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="101"/>
-      <c r="C66" s="101"/>
-      <c r="D66" s="101"/>
-      <c r="E66" s="101"/>
-      <c r="F66" s="101"/>
-      <c r="G66" s="101"/>
-      <c r="H66" s="101"/>
-      <c r="I66" s="101"/>
-      <c r="J66" s="102"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B66" s="92"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="92"/>
+      <c r="E66" s="92"/>
+      <c r="F66" s="92"/>
+      <c r="G66" s="92"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="92"/>
+      <c r="J66" s="93"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="25">
         <v>1</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="25">
         <v>2</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="25">
         <v>3</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="25">
         <v>4</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="25">
         <v>5</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="25">
         <v>6</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="25">
         <v>7</v>
       </c>
@@ -6600,7 +6600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="25">
         <v>8</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="25">
         <v>9</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="25">
         <v>10</v>
       </c>
@@ -6696,7 +6696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="25">
         <v>11</v>
       </c>
@@ -6728,21 +6728,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="100" t="s">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="91" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="101"/>
-      <c r="C78" s="101"/>
-      <c r="D78" s="101"/>
-      <c r="E78" s="101"/>
-      <c r="F78" s="101"/>
-      <c r="G78" s="101"/>
-      <c r="H78" s="101"/>
-      <c r="I78" s="101"/>
-      <c r="J78" s="102"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B78" s="92"/>
+      <c r="C78" s="92"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="92"/>
+      <c r="F78" s="92"/>
+      <c r="G78" s="92"/>
+      <c r="H78" s="92"/>
+      <c r="I78" s="92"/>
+      <c r="J78" s="93"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="25">
         <v>1</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="25">
         <v>2</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="25">
         <v>3</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="25">
         <v>4</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="25">
         <v>5</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="25">
         <v>6</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="25">
         <v>7</v>
       </c>
@@ -6966,7 +6966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="25">
         <v>8</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="25">
         <v>9</v>
       </c>
@@ -7030,7 +7030,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="25">
         <v>10</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="25">
         <v>11</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="25">
         <v>12</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="25">
         <v>13</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="25">
         <v>14</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="25">
         <v>15</v>
       </c>
@@ -7222,7 +7222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="25">
         <v>16</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="25">
         <v>17</v>
       </c>
@@ -7286,7 +7286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="25">
         <v>18</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="25">
         <v>19</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="25">
         <v>20</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="25">
         <v>21</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="25">
         <v>22</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="25">
         <v>23</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="25">
         <v>24</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="25">
         <v>25</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="25">
         <v>27</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="25">
         <v>28</v>
       </c>
@@ -7606,21 +7606,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="88" t="s">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="94" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="88"/>
-      <c r="C106" s="88"/>
-      <c r="D106" s="88"/>
-      <c r="E106" s="88"/>
-      <c r="F106" s="88"/>
-      <c r="G106" s="88"/>
-      <c r="H106" s="88"/>
-      <c r="I106" s="88"/>
-      <c r="J106" s="88"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B106" s="94"/>
+      <c r="C106" s="94"/>
+      <c r="D106" s="94"/>
+      <c r="E106" s="94"/>
+      <c r="F106" s="94"/>
+      <c r="G106" s="94"/>
+      <c r="H106" s="94"/>
+      <c r="I106" s="94"/>
+      <c r="J106" s="94"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="25">
         <v>1</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="25">
         <v>2</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="25">
         <v>3</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="25">
         <v>4</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="25">
         <v>5</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="25">
         <v>6</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="25">
         <v>7</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" s="25">
         <v>8</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="25">
         <v>9</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" s="25">
         <v>10</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="25">
         <v>11</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="25">
         <v>12</v>
       </c>
@@ -8018,7 +8018,7 @@
       <c r="W118" s="58"/>
       <c r="X118" s="58"/>
     </row>
-    <row r="119" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="25">
         <v>13</v>
       </c>
@@ -8064,7 +8064,7 @@
       <c r="W119" s="58"/>
       <c r="X119" s="58"/>
     </row>
-    <row r="120" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="25">
         <v>14</v>
       </c>
@@ -8110,19 +8110,19 @@
       <c r="W120" s="58"/>
       <c r="X120" s="58"/>
     </row>
-    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="89" t="s">
+    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="95" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="89"/>
-      <c r="C121" s="89"/>
-      <c r="D121" s="89"/>
-      <c r="E121" s="89"/>
-      <c r="F121" s="89"/>
-      <c r="G121" s="89"/>
-      <c r="H121" s="89"/>
-      <c r="I121" s="89"/>
-      <c r="J121" s="89"/>
+      <c r="B121" s="95"/>
+      <c r="C121" s="95"/>
+      <c r="D121" s="95"/>
+      <c r="E121" s="95"/>
+      <c r="F121" s="95"/>
+      <c r="G121" s="95"/>
+      <c r="H121" s="95"/>
+      <c r="I121" s="95"/>
+      <c r="J121" s="95"/>
       <c r="K121" s="57"/>
       <c r="L121" s="58"/>
       <c r="M121" s="58"/>
@@ -8138,7 +8138,7 @@
       <c r="W121" s="58"/>
       <c r="X121" s="58"/>
     </row>
-    <row r="122" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="25">
         <v>1</v>
       </c>
@@ -8184,19 +8184,19 @@
       <c r="W122" s="58"/>
       <c r="X122" s="58"/>
     </row>
-    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="89" t="s">
+    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="95" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="89"/>
-      <c r="C123" s="89"/>
-      <c r="D123" s="89"/>
-      <c r="E123" s="89"/>
-      <c r="F123" s="89"/>
-      <c r="G123" s="89"/>
-      <c r="H123" s="89"/>
-      <c r="I123" s="89"/>
-      <c r="J123" s="89"/>
+      <c r="B123" s="95"/>
+      <c r="C123" s="95"/>
+      <c r="D123" s="95"/>
+      <c r="E123" s="95"/>
+      <c r="F123" s="95"/>
+      <c r="G123" s="95"/>
+      <c r="H123" s="95"/>
+      <c r="I123" s="95"/>
+      <c r="J123" s="95"/>
       <c r="K123" s="57"/>
       <c r="L123" s="58"/>
       <c r="M123" s="58"/>
@@ -8212,7 +8212,7 @@
       <c r="W123" s="58"/>
       <c r="X123" s="58"/>
     </row>
-    <row r="124" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="25">
         <v>1</v>
       </c>
@@ -8258,21 +8258,21 @@
       <c r="W124" s="58"/>
       <c r="X124" s="58"/>
     </row>
-    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="89" t="s">
+    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="95" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="89"/>
-      <c r="C125" s="89"/>
-      <c r="D125" s="89"/>
-      <c r="E125" s="89"/>
-      <c r="F125" s="89"/>
-      <c r="G125" s="89"/>
-      <c r="H125" s="89"/>
-      <c r="I125" s="89"/>
-      <c r="J125" s="89"/>
-    </row>
-    <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="95"/>
+      <c r="C125" s="95"/>
+      <c r="D125" s="95"/>
+      <c r="E125" s="95"/>
+      <c r="F125" s="95"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="95"/>
+      <c r="I125" s="95"/>
+      <c r="J125" s="95"/>
+    </row>
+    <row r="126" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="25">
         <v>1</v>
       </c>
@@ -8318,7 +8318,7 @@
       <c r="W126" s="61"/>
       <c r="X126" s="61"/>
     </row>
-    <row r="127" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="25">
         <v>2</v>
       </c>
@@ -8364,7 +8364,7 @@
       <c r="W127" s="58"/>
       <c r="X127" s="58"/>
     </row>
-    <row r="128" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="25">
         <v>3</v>
       </c>
@@ -8410,7 +8410,7 @@
       <c r="W128" s="58"/>
       <c r="X128" s="58"/>
     </row>
-    <row r="129" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="25">
         <v>4</v>
       </c>
@@ -8456,7 +8456,7 @@
       <c r="W129" s="58"/>
       <c r="X129" s="58"/>
     </row>
-    <row r="130" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="25">
         <v>5</v>
       </c>
@@ -8502,7 +8502,7 @@
       <c r="W130" s="58"/>
       <c r="X130" s="58"/>
     </row>
-    <row r="131" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="25">
         <v>6</v>
       </c>
@@ -8548,7 +8548,7 @@
       <c r="W131" s="58"/>
       <c r="X131" s="58"/>
     </row>
-    <row r="132" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="25">
         <v>7</v>
       </c>
@@ -8594,19 +8594,19 @@
       <c r="W132" s="58"/>
       <c r="X132" s="58"/>
     </row>
-    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="89" t="s">
+    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="95" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="89"/>
-      <c r="C133" s="89"/>
-      <c r="D133" s="90"/>
-      <c r="E133" s="90"/>
-      <c r="F133" s="90"/>
-      <c r="G133" s="90"/>
-      <c r="H133" s="90"/>
-      <c r="I133" s="90"/>
-      <c r="J133" s="90"/>
+      <c r="B133" s="95"/>
+      <c r="C133" s="95"/>
+      <c r="D133" s="96"/>
+      <c r="E133" s="96"/>
+      <c r="F133" s="96"/>
+      <c r="G133" s="96"/>
+      <c r="H133" s="96"/>
+      <c r="I133" s="96"/>
+      <c r="J133" s="96"/>
       <c r="K133" s="58"/>
       <c r="L133" s="58"/>
       <c r="M133" s="58"/>
@@ -8622,7 +8622,7 @@
       <c r="W133" s="58"/>
       <c r="X133" s="58"/>
     </row>
-    <row r="134" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="59">
         <v>11</v>
       </c>
@@ -8668,7 +8668,7 @@
       <c r="W134" s="58"/>
       <c r="X134" s="58"/>
     </row>
-    <row r="135" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="26">
         <v>2</v>
       </c>
@@ -8714,7 +8714,7 @@
       <c r="W135" s="58"/>
       <c r="X135" s="58"/>
     </row>
-    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="26">
         <v>3</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="26">
         <v>4</v>
       </c>
@@ -8792,7 +8792,7 @@
       <c r="W137" s="58"/>
       <c r="X137" s="58"/>
     </row>
-    <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="26">
         <v>5</v>
       </c>
@@ -8838,7 +8838,7 @@
       <c r="W138" s="58"/>
       <c r="X138" s="58"/>
     </row>
-    <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="26">
         <v>6</v>
       </c>
@@ -8884,7 +8884,7 @@
       <c r="W139" s="58"/>
       <c r="X139" s="58"/>
     </row>
-    <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="26">
         <v>7</v>
       </c>
@@ -8916,7 +8916,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="26">
         <v>8</v>
       </c>
@@ -8962,7 +8962,7 @@
       <c r="W141" s="58"/>
       <c r="X141" s="58"/>
     </row>
-    <row r="142" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="26">
         <v>9</v>
       </c>
@@ -9008,7 +9008,7 @@
       <c r="W142" s="58"/>
       <c r="X142" s="58"/>
     </row>
-    <row r="143" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="26">
         <v>10</v>
       </c>
@@ -9054,7 +9054,7 @@
       <c r="W143" s="58"/>
       <c r="X143" s="58"/>
     </row>
-    <row r="144" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="26">
         <v>11</v>
       </c>
@@ -9100,19 +9100,19 @@
       <c r="W144" s="58"/>
       <c r="X144" s="58"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="94" t="s">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="100" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="95"/>
-      <c r="C145" s="95"/>
-      <c r="D145" s="95"/>
-      <c r="E145" s="95"/>
-      <c r="F145" s="95"/>
-      <c r="G145" s="95"/>
-      <c r="H145" s="95"/>
-      <c r="I145" s="95"/>
-      <c r="J145" s="96"/>
+      <c r="B145" s="101"/>
+      <c r="C145" s="101"/>
+      <c r="D145" s="101"/>
+      <c r="E145" s="101"/>
+      <c r="F145" s="101"/>
+      <c r="G145" s="101"/>
+      <c r="H145" s="101"/>
+      <c r="I145" s="101"/>
+      <c r="J145" s="102"/>
       <c r="K145" s="58"/>
       <c r="L145" s="58"/>
       <c r="M145" s="58"/>
@@ -9128,7 +9128,7 @@
       <c r="W145" s="58"/>
       <c r="X145" s="58"/>
     </row>
-    <row r="146" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="25">
         <v>1</v>
       </c>
@@ -9174,7 +9174,7 @@
       <c r="W146" s="58"/>
       <c r="X146" s="58"/>
     </row>
-    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="25">
         <v>2</v>
       </c>
@@ -9206,7 +9206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="25">
         <v>3</v>
       </c>
@@ -9238,7 +9238,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="25">
         <v>4</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="25">
         <v>5</v>
       </c>
@@ -9318,7 +9318,7 @@
       <c r="Y150" s="58"/>
       <c r="Z150" s="58"/>
     </row>
-    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="25">
         <v>6</v>
       </c>
@@ -9366,7 +9366,7 @@
       <c r="Y151" s="58"/>
       <c r="Z151" s="58"/>
     </row>
-    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="25">
         <v>7</v>
       </c>
@@ -9414,7 +9414,7 @@
       <c r="Y152" s="58"/>
       <c r="Z152" s="58"/>
     </row>
-    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="25">
         <v>8</v>
       </c>
@@ -9462,7 +9462,7 @@
       <c r="Y153" s="58"/>
       <c r="Z153" s="58"/>
     </row>
-    <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="25">
         <v>9</v>
       </c>
@@ -9510,7 +9510,7 @@
       <c r="Y154" s="58"/>
       <c r="Z154" s="58"/>
     </row>
-    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="25">
         <v>10</v>
       </c>
@@ -9558,19 +9558,19 @@
       <c r="Y155" s="58"/>
       <c r="Z155" s="58"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="89" t="s">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="95" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="89"/>
-      <c r="C156" s="89"/>
-      <c r="D156" s="89"/>
-      <c r="E156" s="89"/>
-      <c r="F156" s="89"/>
-      <c r="G156" s="89"/>
-      <c r="H156" s="89"/>
-      <c r="I156" s="89"/>
-      <c r="J156" s="89"/>
+      <c r="B156" s="95"/>
+      <c r="C156" s="95"/>
+      <c r="D156" s="95"/>
+      <c r="E156" s="95"/>
+      <c r="F156" s="95"/>
+      <c r="G156" s="95"/>
+      <c r="H156" s="95"/>
+      <c r="I156" s="95"/>
+      <c r="J156" s="95"/>
       <c r="K156" s="58"/>
       <c r="L156" s="58"/>
       <c r="M156" s="58"/>
@@ -9588,7 +9588,7 @@
       <c r="Y156" s="58"/>
       <c r="Z156" s="58"/>
     </row>
-    <row r="157" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="25">
         <v>1</v>
       </c>
@@ -9636,19 +9636,19 @@
       <c r="Y157" s="58"/>
       <c r="Z157" s="58"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="89" t="s">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="95" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="89"/>
-      <c r="C158" s="89"/>
-      <c r="D158" s="89"/>
-      <c r="E158" s="89"/>
-      <c r="F158" s="89"/>
-      <c r="G158" s="89"/>
-      <c r="H158" s="89"/>
-      <c r="I158" s="89"/>
-      <c r="J158" s="89"/>
+      <c r="B158" s="95"/>
+      <c r="C158" s="95"/>
+      <c r="D158" s="95"/>
+      <c r="E158" s="95"/>
+      <c r="F158" s="95"/>
+      <c r="G158" s="95"/>
+      <c r="H158" s="95"/>
+      <c r="I158" s="95"/>
+      <c r="J158" s="95"/>
       <c r="K158" s="58"/>
       <c r="L158" s="58"/>
       <c r="M158" s="58"/>
@@ -9666,7 +9666,7 @@
       <c r="Y158" s="58"/>
       <c r="Z158" s="58"/>
     </row>
-    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="67">
         <v>1</v>
       </c>
@@ -9714,7 +9714,7 @@
       <c r="Y159" s="58"/>
       <c r="Z159" s="58"/>
     </row>
-    <row r="160" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="68">
         <v>2</v>
       </c>
@@ -9762,7 +9762,7 @@
       <c r="Y160" s="58"/>
       <c r="Z160" s="58"/>
     </row>
-    <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="68">
         <v>3</v>
       </c>
@@ -9810,7 +9810,7 @@
       <c r="Y161" s="58"/>
       <c r="Z161" s="58"/>
     </row>
-    <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="68">
         <v>4</v>
       </c>
@@ -9858,7 +9858,7 @@
       <c r="Y162" s="58"/>
       <c r="Z162" s="58"/>
     </row>
-    <row r="163" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="68">
         <v>5</v>
       </c>
@@ -9906,7 +9906,7 @@
       <c r="Y163" s="58"/>
       <c r="Z163" s="58"/>
     </row>
-    <row r="164" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="68">
         <v>6</v>
       </c>
@@ -9954,7 +9954,7 @@
       <c r="Y164" s="58"/>
       <c r="Z164" s="58"/>
     </row>
-    <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="68">
         <v>7</v>
       </c>
@@ -10002,7 +10002,7 @@
       <c r="Y165" s="58"/>
       <c r="Z165" s="58"/>
     </row>
-    <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="68">
         <v>8</v>
       </c>
@@ -10050,7 +10050,7 @@
       <c r="Y166" s="58"/>
       <c r="Z166" s="58"/>
     </row>
-    <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="67">
         <v>9</v>
       </c>
@@ -10098,7 +10098,7 @@
       <c r="Y167" s="58"/>
       <c r="Z167" s="58"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="68">
         <v>10</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="67">
         <v>11</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="68">
         <v>12</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="67">
         <v>13</v>
       </c>
@@ -10226,7 +10226,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="68">
         <v>14</v>
       </c>
@@ -10258,7 +10258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="67">
         <v>15</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="68">
         <v>16</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="67">
         <v>17</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="68">
         <v>18</v>
       </c>
@@ -10386,7 +10386,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="86">
         <v>19</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="86">
         <v>20</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="86">
         <v>21</v>
       </c>
@@ -10482,21 +10482,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="89" t="s">
+    <row r="180" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="95" t="s">
         <v>715</v>
       </c>
-      <c r="B180" s="89"/>
-      <c r="C180" s="89"/>
+      <c r="B180" s="95"/>
+      <c r="C180" s="95"/>
       <c r="D180" s="87"/>
-      <c r="E180" s="89"/>
-      <c r="F180" s="89"/>
-      <c r="G180" s="89"/>
-      <c r="H180" s="89"/>
-      <c r="I180" s="89"/>
-      <c r="J180" s="89"/>
-    </row>
-    <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E180" s="95"/>
+      <c r="F180" s="95"/>
+      <c r="G180" s="95"/>
+      <c r="H180" s="95"/>
+      <c r="I180" s="95"/>
+      <c r="J180" s="95"/>
+    </row>
+    <row r="181" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="68">
         <v>1</v>
       </c>
@@ -10528,7 +10528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="68">
         <v>2</v>
       </c>
@@ -10560,7 +10560,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="68">
         <v>3</v>
       </c>
@@ -10592,7 +10592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="68">
         <v>4</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="68">
         <v>5</v>
       </c>
@@ -10656,7 +10656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="68">
         <v>6</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="68">
         <v>7</v>
       </c>
@@ -10720,7 +10720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="68">
         <v>8</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="1:10" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:10" s="28" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="68">
         <v>9</v>
       </c>
@@ -10784,21 +10784,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="91" t="s">
+    <row r="190" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="97" t="s">
         <v>617</v>
       </c>
-      <c r="B190" s="92"/>
-      <c r="C190" s="92"/>
-      <c r="D190" s="92"/>
-      <c r="E190" s="92"/>
-      <c r="F190" s="92"/>
-      <c r="G190" s="92"/>
-      <c r="H190" s="92"/>
-      <c r="I190" s="92"/>
-      <c r="J190" s="93"/>
-    </row>
-    <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B190" s="98"/>
+      <c r="C190" s="98"/>
+      <c r="D190" s="98"/>
+      <c r="E190" s="98"/>
+      <c r="F190" s="98"/>
+      <c r="G190" s="98"/>
+      <c r="H190" s="98"/>
+      <c r="I190" s="98"/>
+      <c r="J190" s="99"/>
+    </row>
+    <row r="191" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="68">
         <v>1</v>
       </c>
@@ -10830,7 +10830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="68">
         <v>2</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="68">
         <v>3</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="68">
         <v>4</v>
       </c>
@@ -10926,7 +10926,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="68">
         <v>5</v>
       </c>
@@ -10958,7 +10958,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="68">
         <v>6</v>
       </c>
@@ -10990,7 +10990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="68">
         <v>7</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="87" t="s">
         <v>638</v>
       </c>
@@ -11036,7 +11036,7 @@
       <c r="I198" s="87"/>
       <c r="J198" s="87"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="48">
         <v>1</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="48">
         <v>2</v>
       </c>
@@ -11100,7 +11100,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="48">
         <v>3</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="48">
         <v>4</v>
       </c>
@@ -11164,7 +11164,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="87" t="s">
         <v>651</v>
       </c>
@@ -11178,7 +11178,7 @@
       <c r="I203" s="87"/>
       <c r="J203" s="87"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="48">
         <v>1</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="87" t="s">
         <v>657</v>
       </c>
@@ -11224,7 +11224,7 @@
       <c r="I205" s="87"/>
       <c r="J205" s="87"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="48">
         <v>1</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="48">
         <v>2</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="48">
         <v>3</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="48">
         <v>4</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="48">
         <v>5</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="48">
         <v>6</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="48">
         <v>7</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="48">
         <v>8</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="48">
         <v>9</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="85"/>
       <c r="B215" s="85"/>
       <c r="C215" s="85"/>
@@ -11526,7 +11526,7 @@
       <c r="I215" s="85"/>
       <c r="J215" s="85"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="48">
         <v>1</v>
       </c>
@@ -11558,7 +11558,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="83"/>
       <c r="B217" s="83"/>
       <c r="C217" s="83"/>
@@ -11572,7 +11572,7 @@
       <c r="I217" s="83"/>
       <c r="J217" s="83"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="48">
         <v>1</v>
       </c>
@@ -11604,7 +11604,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="48">
         <v>2</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="87" t="s">
         <v>733</v>
       </c>
@@ -11650,7 +11650,7 @@
       <c r="I220" s="87"/>
       <c r="J220" s="87"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="48">
         <v>1</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="48">
         <v>2</v>
       </c>
@@ -11714,7 +11714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="48">
         <v>3</v>
       </c>
@@ -11746,7 +11746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="48">
         <v>4</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="48">
         <v>5</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="87" t="s">
         <v>743</v>
       </c>
@@ -11824,7 +11824,7 @@
       <c r="I226" s="87"/>
       <c r="J226" s="87"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="48">
         <v>1</v>
       </c>
@@ -11856,7 +11856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="48">
         <v>2</v>
       </c>
@@ -11888,7 +11888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="48">
         <v>3</v>
       </c>
@@ -11920,7 +11920,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="48">
         <v>4</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="48">
         <v>5</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="48">
         <v>6</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="48">
         <v>7</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="48">
         <v>8</v>
       </c>
@@ -12080,7 +12080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="48">
         <v>9</v>
       </c>
@@ -12112,7 +12112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="48">
         <v>10</v>
       </c>
@@ -12144,7 +12144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="48">
         <v>11</v>
       </c>
@@ -12176,7 +12176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="87" t="s">
         <v>780</v>
       </c>
@@ -12190,7 +12190,7 @@
       <c r="I238" s="87"/>
       <c r="J238" s="87"/>
     </row>
-    <row r="239" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="48">
         <v>1</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="87" t="s">
         <v>792</v>
       </c>
@@ -12236,7 +12236,7 @@
       <c r="I240" s="87"/>
       <c r="J240" s="87"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="48">
         <v>1</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="48">
         <v>2</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="48">
         <v>3</v>
       </c>
@@ -12332,7 +12332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="48">
         <v>4</v>
       </c>
@@ -12364,7 +12364,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="48">
         <v>5</v>
       </c>
@@ -12396,7 +12396,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="48">
         <v>6</v>
       </c>
@@ -12428,7 +12428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="48">
         <v>7</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="48">
         <v>8</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="48">
         <v>9</v>
       </c>
@@ -12524,7 +12524,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="48">
         <v>10</v>
       </c>
@@ -12556,7 +12556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="48">
         <v>11</v>
       </c>
@@ -12588,7 +12588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="48">
         <v>12</v>
       </c>
@@ -12620,7 +12620,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="48">
         <v>13</v>
       </c>
@@ -12652,7 +12652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="87" t="s">
         <v>837</v>
       </c>
@@ -12666,7 +12666,7 @@
       <c r="I254" s="87"/>
       <c r="J254" s="87"/>
     </row>
-    <row r="255" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="48">
         <v>1</v>
       </c>
@@ -12698,7 +12698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="48">
         <v>2</v>
       </c>
@@ -12730,7 +12730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="87" t="s">
         <v>838</v>
       </c>
@@ -12744,7 +12744,7 @@
       <c r="I257" s="87"/>
       <c r="J257" s="87"/>
     </row>
-    <row r="258" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="48">
         <v>1</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="48">
         <v>2</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="48">
         <v>3</v>
       </c>
@@ -12840,7 +12840,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="48">
         <v>4</v>
       </c>
@@ -12872,7 +12872,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="48">
         <v>5</v>
       </c>
@@ -12906,14 +12906,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
     <mergeCell ref="A257:J257"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
@@ -12930,6 +12922,14 @@
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
     <mergeCell ref="A238:J238"/>
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13028,35 +13028,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
   <dimension ref="A1:AF246"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="45.6640625" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="54.33203125" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="54.28515625" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.44140625" customWidth="1"/>
-    <col min="12" max="12" width="53.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.42578125" customWidth="1"/>
+    <col min="12" max="12" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="71.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="52.33203125" customWidth="1"/>
-    <col min="21" max="21" width="20.88671875" customWidth="1"/>
+    <col min="17" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="71.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="52.28515625" customWidth="1"/>
+    <col min="21" max="21" width="20.85546875" customWidth="1"/>
     <col min="22" max="22" width="27" customWidth="1"/>
     <col min="24" max="25" width="29" customWidth="1"/>
-    <col min="26" max="26" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.44140625" customWidth="1"/>
-    <col min="29" max="29" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.6640625" customWidth="1"/>
-    <col min="31" max="31" width="12.33203125" customWidth="1"/>
+    <col min="26" max="26" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.42578125" customWidth="1"/>
+    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>5</v>
       </c>
@@ -13148,7 +13148,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>23</v>
       </c>
@@ -13228,7 +13228,7 @@
       <c r="AC2" s="28"/>
       <c r="AD2" s="28"/>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>25</v>
       </c>
@@ -13308,7 +13308,7 @@
       <c r="AC3" s="28"/>
       <c r="AD3" s="28"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>28</v>
       </c>
@@ -13388,7 +13388,7 @@
       <c r="AC4" s="28"/>
       <c r="AD4" s="28"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>58</v>
       </c>
@@ -13468,7 +13468,7 @@
       <c r="AC5" s="28"/>
       <c r="AD5" s="28"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>69</v>
       </c>
@@ -13548,7 +13548,7 @@
       <c r="AC6" s="28"/>
       <c r="AD6" s="28"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
         <v>73</v>
       </c>
@@ -13628,7 +13628,7 @@
       <c r="AC7" s="28"/>
       <c r="AD7" s="28"/>
     </row>
-    <row r="8" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
         <v>77</v>
       </c>
@@ -13708,7 +13708,7 @@
       <c r="AC8" s="28"/>
       <c r="AD8" s="28"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
         <v>79</v>
       </c>
@@ -13788,7 +13788,7 @@
       <c r="AC9" s="28"/>
       <c r="AD9" s="28"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
         <v>80</v>
       </c>
@@ -13868,7 +13868,7 @@
       <c r="AC10" s="28"/>
       <c r="AD10" s="28"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
         <v>81</v>
       </c>
@@ -13948,7 +13948,7 @@
       <c r="AC11" s="28"/>
       <c r="AD11" s="28"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
         <v>83</v>
       </c>
@@ -14028,7 +14028,7 @@
       <c r="AC12" s="28"/>
       <c r="AD12" s="28"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
         <v>84</v>
       </c>
@@ -14108,7 +14108,7 @@
       <c r="AC13" s="28"/>
       <c r="AD13" s="28"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="38" t="s">
         <v>85</v>
       </c>
@@ -14188,7 +14188,7 @@
       <c r="AC14" s="28"/>
       <c r="AD14" s="28"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
         <v>86</v>
       </c>
@@ -14268,7 +14268,7 @@
       <c r="AC15" s="28"/>
       <c r="AD15" s="28"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="38" t="s">
         <v>87</v>
       </c>
@@ -14348,7 +14348,7 @@
       <c r="AC16" s="28"/>
       <c r="AD16" s="28"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
         <v>88</v>
       </c>
@@ -14428,7 +14428,7 @@
       <c r="AC17" s="28"/>
       <c r="AD17" s="28"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="38" t="s">
         <v>89</v>
       </c>
@@ -14508,7 +14508,7 @@
       <c r="AC18" s="28"/>
       <c r="AD18" s="28"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
         <v>91</v>
       </c>
@@ -14588,7 +14588,7 @@
       <c r="AC19" s="28"/>
       <c r="AD19" s="28"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="38" t="s">
         <v>93</v>
       </c>
@@ -14668,7 +14668,7 @@
       <c r="AC20" s="28"/>
       <c r="AD20" s="28"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
         <v>94</v>
       </c>
@@ -14748,7 +14748,7 @@
       <c r="AC21" s="28"/>
       <c r="AD21" s="28"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="38" t="s">
         <v>135</v>
       </c>
@@ -14828,7 +14828,7 @@
       <c r="AC22" s="28"/>
       <c r="AD22" s="28"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="42" t="s">
         <v>140</v>
       </c>
@@ -14908,7 +14908,7 @@
       <c r="AC23" s="28"/>
       <c r="AD23" s="28"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="53" t="s">
         <v>63</v>
       </c>
@@ -14988,7 +14988,7 @@
       <c r="AC24" s="28"/>
       <c r="AD24" s="28"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="46" t="s">
         <v>144</v>
       </c>
@@ -15068,7 +15068,7 @@
       <c r="AC25" s="28"/>
       <c r="AD25" s="28"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="46" t="s">
         <v>145</v>
       </c>
@@ -15148,7 +15148,7 @@
       <c r="AC26" s="28"/>
       <c r="AD26" s="28"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>146</v>
       </c>
@@ -15228,7 +15228,7 @@
       <c r="AC27" s="28"/>
       <c r="AD27" s="28"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="46" t="s">
         <v>147</v>
       </c>
@@ -15308,7 +15308,7 @@
       <c r="AC28" s="28"/>
       <c r="AD28" s="28"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
         <v>148</v>
       </c>
@@ -15388,7 +15388,7 @@
       <c r="AC29" s="28"/>
       <c r="AD29" s="28"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="46" t="s">
         <v>150</v>
       </c>
@@ -15468,7 +15468,7 @@
       <c r="AC30" s="28"/>
       <c r="AD30" s="28"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="46" t="s">
         <v>151</v>
       </c>
@@ -15548,7 +15548,7 @@
       <c r="AC31" s="28"/>
       <c r="AD31" s="28"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="46" t="s">
         <v>152</v>
       </c>
@@ -15628,7 +15628,7 @@
       <c r="AC32" s="28"/>
       <c r="AD32" s="28"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="46" t="s">
         <v>153</v>
       </c>
@@ -15708,7 +15708,7 @@
       <c r="AC33" s="28"/>
       <c r="AD33" s="28"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="46" t="s">
         <v>154</v>
       </c>
@@ -15788,7 +15788,7 @@
       <c r="AC34" s="28"/>
       <c r="AD34" s="28"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="46" t="s">
         <v>155</v>
       </c>
@@ -15868,7 +15868,7 @@
       <c r="AC35" s="28"/>
       <c r="AD35" s="28"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
         <v>64</v>
       </c>
@@ -15948,7 +15948,7 @@
       <c r="AC36" s="28"/>
       <c r="AD36" s="28"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="54" t="s">
         <v>175</v>
       </c>
@@ -16030,7 +16030,7 @@
       <c r="AC37" s="28"/>
       <c r="AD37" s="28"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="47" t="s">
         <v>179</v>
       </c>
@@ -16112,7 +16112,7 @@
       <c r="AC38" s="28"/>
       <c r="AD38" s="28"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="47" t="s">
         <v>182</v>
       </c>
@@ -16194,7 +16194,7 @@
       <c r="AC39" s="28"/>
       <c r="AD39" s="28"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="47" t="s">
         <v>185</v>
       </c>
@@ -16276,7 +16276,7 @@
       <c r="AC40" s="28"/>
       <c r="AD40" s="28"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="47" t="s">
         <v>188</v>
       </c>
@@ -16358,7 +16358,7 @@
       <c r="AC41" s="28"/>
       <c r="AD41" s="28"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="47" t="s">
         <v>190</v>
       </c>
@@ -16440,7 +16440,7 @@
       <c r="AC42" s="28"/>
       <c r="AD42" s="28"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="47" t="s">
         <v>193</v>
       </c>
@@ -16522,7 +16522,7 @@
       <c r="AC43" s="28"/>
       <c r="AD43" s="28"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="47" t="s">
         <v>196</v>
       </c>
@@ -16604,7 +16604,7 @@
       <c r="AC44" s="28"/>
       <c r="AD44" s="28"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="47" t="s">
         <v>198</v>
       </c>
@@ -16686,7 +16686,7 @@
       <c r="AC45" s="28"/>
       <c r="AD45" s="28"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="47" t="s">
         <v>200</v>
       </c>
@@ -16768,7 +16768,7 @@
       <c r="AC46" s="28"/>
       <c r="AD46" s="28"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="47" t="s">
         <v>202</v>
       </c>
@@ -16850,7 +16850,7 @@
       <c r="AC47" s="28"/>
       <c r="AD47" s="28"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="47" t="s">
         <v>204</v>
       </c>
@@ -16932,7 +16932,7 @@
       <c r="AC48" s="28"/>
       <c r="AD48" s="28"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="47" t="s">
         <v>206</v>
       </c>
@@ -17014,7 +17014,7 @@
       <c r="AC49" s="28"/>
       <c r="AD49" s="28"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="47" t="s">
         <v>208</v>
       </c>
@@ -17096,7 +17096,7 @@
       <c r="AC50" s="28"/>
       <c r="AD50" s="28"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="47" t="s">
         <v>210</v>
       </c>
@@ -17178,7 +17178,7 @@
       <c r="AC51" s="28"/>
       <c r="AD51" s="28"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="47" t="s">
         <v>212</v>
       </c>
@@ -17260,7 +17260,7 @@
       <c r="AC52" s="28"/>
       <c r="AD52" s="28"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="47" t="s">
         <v>687</v>
       </c>
@@ -17342,7 +17342,7 @@
       <c r="AC53" s="28"/>
       <c r="AD53" s="28"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="55" t="s">
         <v>213</v>
       </c>
@@ -17424,7 +17424,7 @@
       <c r="AC54" s="28"/>
       <c r="AD54" s="28"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="48" t="s">
         <v>214</v>
       </c>
@@ -17506,7 +17506,7 @@
       <c r="AC55" s="28"/>
       <c r="AD55" s="28"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="48" t="s">
         <v>215</v>
       </c>
@@ -17588,7 +17588,7 @@
       <c r="AC56" s="28"/>
       <c r="AD56" s="28"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="48" t="s">
         <v>216</v>
       </c>
@@ -17670,7 +17670,7 @@
       <c r="AC57" s="28"/>
       <c r="AD57" s="28"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="48" t="s">
         <v>217</v>
       </c>
@@ -17752,7 +17752,7 @@
       <c r="AC58" s="28"/>
       <c r="AD58" s="28"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="48" t="s">
         <v>218</v>
       </c>
@@ -17834,7 +17834,7 @@
       <c r="AC59" s="28"/>
       <c r="AD59" s="28"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="48" t="s">
         <v>219</v>
       </c>
@@ -17916,7 +17916,7 @@
       <c r="AC60" s="28"/>
       <c r="AD60" s="28"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="48" t="s">
         <v>220</v>
       </c>
@@ -17998,7 +17998,7 @@
       <c r="AC61" s="28"/>
       <c r="AD61" s="28"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="48" t="s">
         <v>221</v>
       </c>
@@ -18080,7 +18080,7 @@
       <c r="AC62" s="28"/>
       <c r="AD62" s="28"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="51" t="s">
         <v>222</v>
       </c>
@@ -18162,7 +18162,7 @@
       <c r="AC63" s="28"/>
       <c r="AD63" s="28"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="56" t="s">
         <v>249</v>
       </c>
@@ -18244,7 +18244,7 @@
       <c r="AC64" s="28"/>
       <c r="AD64" s="28"/>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="48" t="s">
         <v>253</v>
       </c>
@@ -18326,7 +18326,7 @@
       <c r="AC65" s="28"/>
       <c r="AD65" s="28"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="48" t="s">
         <v>256</v>
       </c>
@@ -18408,7 +18408,7 @@
       <c r="AC66" s="28"/>
       <c r="AD66" s="28"/>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="48" t="s">
         <v>259</v>
       </c>
@@ -18490,7 +18490,7 @@
       <c r="AC67" s="28"/>
       <c r="AD67" s="28"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="48" t="s">
         <v>262</v>
       </c>
@@ -18572,7 +18572,7 @@
       <c r="AC68" s="28"/>
       <c r="AD68" s="28"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="48" t="s">
         <v>265</v>
       </c>
@@ -18654,7 +18654,7 @@
       <c r="AC69" s="28"/>
       <c r="AD69" s="28"/>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="48" t="s">
         <v>268</v>
       </c>
@@ -18736,7 +18736,7 @@
       <c r="AC70" s="28"/>
       <c r="AD70" s="28"/>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="48" t="s">
         <v>271</v>
       </c>
@@ -18818,7 +18818,7 @@
       <c r="AC71" s="28"/>
       <c r="AD71" s="28"/>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="48" t="s">
         <v>274</v>
       </c>
@@ -18900,7 +18900,7 @@
       <c r="AC72" s="28"/>
       <c r="AD72" s="28"/>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="48" t="s">
         <v>277</v>
       </c>
@@ -18982,7 +18982,7 @@
       <c r="AC73" s="28"/>
       <c r="AD73" s="28"/>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="51" t="s">
         <v>280</v>
       </c>
@@ -19066,7 +19066,7 @@
       <c r="AC74" s="28"/>
       <c r="AD74" s="28"/>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="62" t="s">
         <v>282</v>
       </c>
@@ -19150,7 +19150,7 @@
       <c r="AC75" s="28"/>
       <c r="AD75" s="28"/>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="48" t="s">
         <v>285</v>
       </c>
@@ -19234,7 +19234,7 @@
       <c r="AC76" s="28"/>
       <c r="AD76" s="28"/>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="48" t="s">
         <v>287</v>
       </c>
@@ -19318,7 +19318,7 @@
       <c r="AC77" s="28"/>
       <c r="AD77" s="28"/>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="48" t="s">
         <v>289</v>
       </c>
@@ -19402,7 +19402,7 @@
       <c r="AC78" s="28"/>
       <c r="AD78" s="28"/>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="48" t="s">
         <v>292</v>
       </c>
@@ -19486,7 +19486,7 @@
       <c r="AC79" s="28"/>
       <c r="AD79" s="28"/>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="48" t="s">
         <v>295</v>
       </c>
@@ -19570,7 +19570,7 @@
       <c r="AC80" s="28"/>
       <c r="AD80" s="28"/>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="48" t="s">
         <v>298</v>
       </c>
@@ -19654,7 +19654,7 @@
       <c r="AC81" s="28"/>
       <c r="AD81" s="28"/>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="48" t="s">
         <v>301</v>
       </c>
@@ -19738,7 +19738,7 @@
       <c r="AC82" s="28"/>
       <c r="AD82" s="28"/>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="48" t="s">
         <v>304</v>
       </c>
@@ -19822,7 +19822,7 @@
       <c r="AC83" s="28"/>
       <c r="AD83" s="28"/>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="48" t="s">
         <v>306</v>
       </c>
@@ -19906,7 +19906,7 @@
       <c r="AC84" s="28"/>
       <c r="AD84" s="28"/>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="48" t="s">
         <v>308</v>
       </c>
@@ -19990,7 +19990,7 @@
       <c r="AC85" s="28"/>
       <c r="AD85" s="28"/>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="48" t="s">
         <v>310</v>
       </c>
@@ -20074,7 +20074,7 @@
       <c r="AC86" s="28"/>
       <c r="AD86" s="28"/>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="48" t="s">
         <v>313</v>
       </c>
@@ -20158,7 +20158,7 @@
       <c r="AC87" s="28"/>
       <c r="AD87" s="28"/>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="48" t="s">
         <v>316</v>
       </c>
@@ -20242,7 +20242,7 @@
       <c r="AC88" s="28"/>
       <c r="AD88" s="28"/>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="48" t="s">
         <v>319</v>
       </c>
@@ -20326,7 +20326,7 @@
       <c r="AC89" s="28"/>
       <c r="AD89" s="28"/>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="48" t="s">
         <v>322</v>
       </c>
@@ -20410,7 +20410,7 @@
       <c r="AC90" s="28"/>
       <c r="AD90" s="28"/>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="48" t="s">
         <v>324</v>
       </c>
@@ -20494,7 +20494,7 @@
       <c r="AC91" s="28"/>
       <c r="AD91" s="28"/>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="48" t="s">
         <v>327</v>
       </c>
@@ -20578,7 +20578,7 @@
       <c r="AC92" s="28"/>
       <c r="AD92" s="28"/>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="48" t="s">
         <v>330</v>
       </c>
@@ -20662,7 +20662,7 @@
       <c r="AC93" s="28"/>
       <c r="AD93" s="28"/>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="48" t="s">
         <v>332</v>
       </c>
@@ -20746,7 +20746,7 @@
       <c r="AC94" s="28"/>
       <c r="AD94" s="28"/>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="48" t="s">
         <v>334</v>
       </c>
@@ -20830,7 +20830,7 @@
       <c r="AC95" s="28"/>
       <c r="AD95" s="28"/>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="48" t="s">
         <v>336</v>
       </c>
@@ -20914,7 +20914,7 @@
       <c r="AC96" s="28"/>
       <c r="AD96" s="28"/>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="48" t="s">
         <v>338</v>
       </c>
@@ -20998,7 +20998,7 @@
       <c r="AC97" s="28"/>
       <c r="AD97" s="28"/>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="48" t="s">
         <v>340</v>
       </c>
@@ -21082,7 +21082,7 @@
       <c r="AC98" s="28"/>
       <c r="AD98" s="28"/>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="48" t="s">
         <v>342</v>
       </c>
@@ -21166,7 +21166,7 @@
       <c r="AC99" s="28"/>
       <c r="AD99" s="28"/>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="48" t="s">
         <v>344</v>
       </c>
@@ -21250,7 +21250,7 @@
       <c r="AC100" s="28"/>
       <c r="AD100" s="28"/>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="48" t="s">
         <v>597</v>
       </c>
@@ -21334,7 +21334,7 @@
       <c r="AC101" s="28"/>
       <c r="AD101" s="28"/>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="48" t="s">
         <v>348</v>
       </c>
@@ -21418,7 +21418,7 @@
       <c r="AC102" s="28"/>
       <c r="AD102" s="28"/>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="48" t="s">
         <v>352</v>
       </c>
@@ -21502,7 +21502,7 @@
       <c r="AC103" s="28"/>
       <c r="AD103" s="28"/>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="48" t="s">
         <v>355</v>
       </c>
@@ -21586,7 +21586,7 @@
       <c r="AC104" s="28"/>
       <c r="AD104" s="28"/>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="48" t="s">
         <v>358</v>
       </c>
@@ -21670,7 +21670,7 @@
       <c r="AC105" s="28"/>
       <c r="AD105" s="28"/>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="48" t="s">
         <v>361</v>
       </c>
@@ -21754,7 +21754,7 @@
       <c r="AC106" s="28"/>
       <c r="AD106" s="28"/>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="48" t="s">
         <v>364</v>
       </c>
@@ -21838,7 +21838,7 @@
       <c r="AC107" s="28"/>
       <c r="AD107" s="28"/>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="48" t="s">
         <v>367</v>
       </c>
@@ -21922,7 +21922,7 @@
       <c r="AC108" s="28"/>
       <c r="AD108" s="28"/>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="48" t="s">
         <v>369</v>
       </c>
@@ -22006,7 +22006,7 @@
       <c r="AC109" s="28"/>
       <c r="AD109" s="28"/>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" s="48" t="s">
         <v>371</v>
       </c>
@@ -22090,7 +22090,7 @@
       <c r="AC110" s="28"/>
       <c r="AD110" s="28"/>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A111" s="48" t="s">
         <v>598</v>
       </c>
@@ -22174,7 +22174,7 @@
       <c r="AC111" s="28"/>
       <c r="AD111" s="28"/>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A112" s="48" t="s">
         <v>690</v>
       </c>
@@ -22258,7 +22258,7 @@
       <c r="AC112" s="28"/>
       <c r="AD112" s="28"/>
     </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A113" s="48" t="s">
         <v>693</v>
       </c>
@@ -22342,7 +22342,7 @@
       <c r="AC113" s="28"/>
       <c r="AD113" s="28"/>
     </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A114" s="48" t="s">
         <v>696</v>
       </c>
@@ -22426,7 +22426,7 @@
       <c r="AC114" s="28"/>
       <c r="AD114" s="28"/>
     </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A115" s="48" t="s">
         <v>699</v>
       </c>
@@ -22510,7 +22510,7 @@
       <c r="AC115" s="28"/>
       <c r="AD115" s="28"/>
     </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A116" s="48" t="s">
         <v>378</v>
       </c>
@@ -22594,7 +22594,7 @@
       <c r="AC116" s="28"/>
       <c r="AD116" s="28"/>
     </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A117" s="48" t="s">
         <v>383</v>
       </c>
@@ -22678,7 +22678,7 @@
       <c r="AC117" s="28"/>
       <c r="AD117" s="28"/>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A118" s="48" t="s">
         <v>397</v>
       </c>
@@ -22762,7 +22762,7 @@
       <c r="AC118" s="28"/>
       <c r="AD118" s="28"/>
     </row>
-    <row r="119" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A119" s="48" t="s">
         <v>399</v>
       </c>
@@ -22846,7 +22846,7 @@
       <c r="AC119" s="28"/>
       <c r="AD119" s="28"/>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A120" s="48" t="s">
         <v>400</v>
       </c>
@@ -22930,7 +22930,7 @@
       <c r="AC120" s="28"/>
       <c r="AD120" s="28"/>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A121" s="48" t="s">
         <v>401</v>
       </c>
@@ -23014,7 +23014,7 @@
       <c r="AC121" s="28"/>
       <c r="AD121" s="28"/>
     </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A122" s="48" t="s">
         <v>402</v>
       </c>
@@ -23098,7 +23098,7 @@
       <c r="AC122" s="28"/>
       <c r="AD122" s="28"/>
     </row>
-    <row r="123" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A123" s="48" t="s">
         <v>403</v>
       </c>
@@ -23182,7 +23182,7 @@
       <c r="AC123" s="28"/>
       <c r="AD123" s="28"/>
     </row>
-    <row r="124" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A124" s="48" t="s">
         <v>405</v>
       </c>
@@ -23266,7 +23266,7 @@
       <c r="AC124" s="28"/>
       <c r="AD124" s="28"/>
     </row>
-    <row r="125" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A125" s="48" t="s">
         <v>407</v>
       </c>
@@ -23350,7 +23350,7 @@
       <c r="AC125" s="28"/>
       <c r="AD125" s="28"/>
     </row>
-    <row r="126" spans="1:30" ht="27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A126" s="62" t="s">
         <v>413</v>
       </c>
@@ -23434,7 +23434,7 @@
       <c r="AC126" s="28"/>
       <c r="AD126" s="28"/>
     </row>
-    <row r="127" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A127" s="48" t="s">
         <v>417</v>
       </c>
@@ -23518,7 +23518,7 @@
       <c r="AC127" s="28"/>
       <c r="AD127" s="28"/>
     </row>
-    <row r="128" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A128" s="48" t="s">
         <v>420</v>
       </c>
@@ -23602,7 +23602,7 @@
       <c r="AC128" s="28"/>
       <c r="AD128" s="28"/>
     </row>
-    <row r="129" spans="1:30" ht="27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A129" s="48" t="s">
         <v>422</v>
       </c>
@@ -23686,7 +23686,7 @@
       <c r="AC129" s="28"/>
       <c r="AD129" s="28"/>
     </row>
-    <row r="130" spans="1:30" ht="27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A130" s="48" t="s">
         <v>424</v>
       </c>
@@ -23770,7 +23770,7 @@
       <c r="AC130" s="28"/>
       <c r="AD130" s="28"/>
     </row>
-    <row r="131" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A131" s="48" t="s">
         <v>427</v>
       </c>
@@ -23854,7 +23854,7 @@
       <c r="AC131" s="28"/>
       <c r="AD131" s="28"/>
     </row>
-    <row r="132" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A132" s="48" t="s">
         <v>430</v>
       </c>
@@ -23938,7 +23938,7 @@
       <c r="AC132" s="28"/>
       <c r="AD132" s="28"/>
     </row>
-    <row r="133" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A133" s="48" t="s">
         <v>433</v>
       </c>
@@ -24022,7 +24022,7 @@
       <c r="AC133" s="28"/>
       <c r="AD133" s="28"/>
     </row>
-    <row r="134" spans="1:30" ht="27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A134" s="48" t="s">
         <v>436</v>
       </c>
@@ -24106,7 +24106,7 @@
       <c r="AC134" s="28"/>
       <c r="AD134" s="28"/>
     </row>
-    <row r="135" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A135" s="48" t="s">
         <v>438</v>
       </c>
@@ -24190,7 +24190,7 @@
       <c r="AC135" s="28"/>
       <c r="AD135" s="28"/>
     </row>
-    <row r="136" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A136" s="48" t="s">
         <v>703</v>
       </c>
@@ -24274,7 +24274,7 @@
       <c r="AC136" s="28"/>
       <c r="AD136" s="28"/>
     </row>
-    <row r="137" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A137" s="48" t="s">
         <v>397</v>
       </c>
@@ -24358,7 +24358,7 @@
       <c r="AC137" s="28"/>
       <c r="AD137" s="28"/>
     </row>
-    <row r="138" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A138" s="48" t="s">
         <v>399</v>
       </c>
@@ -24442,7 +24442,7 @@
       <c r="AC138" s="28"/>
       <c r="AD138" s="28"/>
     </row>
-    <row r="139" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A139" s="48" t="s">
         <v>400</v>
       </c>
@@ -24526,7 +24526,7 @@
       <c r="AC139" s="28"/>
       <c r="AD139" s="28"/>
     </row>
-    <row r="140" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A140" s="48" t="s">
         <v>401</v>
       </c>
@@ -24610,7 +24610,7 @@
       <c r="AC140" s="28"/>
       <c r="AD140" s="28"/>
     </row>
-    <row r="141" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A141" s="48" t="s">
         <v>402</v>
       </c>
@@ -24694,7 +24694,7 @@
       <c r="AC141" s="28"/>
       <c r="AD141" s="28"/>
     </row>
-    <row r="142" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A142" s="48" t="s">
         <v>403</v>
       </c>
@@ -24778,7 +24778,7 @@
       <c r="AC142" s="28"/>
       <c r="AD142" s="28"/>
     </row>
-    <row r="143" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A143" s="48" t="s">
         <v>405</v>
       </c>
@@ -24862,7 +24862,7 @@
       <c r="AC143" s="28"/>
       <c r="AD143" s="28"/>
     </row>
-    <row r="144" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A144" s="48" t="s">
         <v>442</v>
       </c>
@@ -24946,7 +24946,7 @@
       <c r="AC144" s="28"/>
       <c r="AD144" s="28"/>
     </row>
-    <row r="145" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A145" s="48" t="s">
         <v>446</v>
       </c>
@@ -25030,7 +25030,7 @@
       <c r="AC145" s="28"/>
       <c r="AD145" s="28"/>
     </row>
-    <row r="146" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A146" s="48" t="s">
         <v>449</v>
       </c>
@@ -25114,7 +25114,7 @@
       <c r="AC146" s="28"/>
       <c r="AD146" s="28"/>
     </row>
-    <row r="147" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A147" s="48" t="s">
         <v>451</v>
       </c>
@@ -25198,7 +25198,7 @@
       <c r="AC147" s="28"/>
       <c r="AD147" s="28"/>
     </row>
-    <row r="148" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A148" s="48" t="s">
         <v>454</v>
       </c>
@@ -25282,7 +25282,7 @@
       <c r="AC148" s="28"/>
       <c r="AD148" s="28"/>
     </row>
-    <row r="149" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A149" s="48" t="s">
         <v>457</v>
       </c>
@@ -25366,7 +25366,7 @@
       <c r="AC149" s="28"/>
       <c r="AD149" s="28"/>
     </row>
-    <row r="150" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A150" s="48" t="s">
         <v>460</v>
       </c>
@@ -25450,7 +25450,7 @@
       <c r="AC150" s="28"/>
       <c r="AD150" s="28"/>
     </row>
-    <row r="151" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A151" s="48" t="s">
         <v>463</v>
       </c>
@@ -25534,7 +25534,7 @@
       <c r="AC151" s="28"/>
       <c r="AD151" s="28"/>
     </row>
-    <row r="152" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="48" t="s">
         <v>466</v>
       </c>
@@ -25618,7 +25618,7 @@
       <c r="AC152" s="28"/>
       <c r="AD152" s="28"/>
     </row>
-    <row r="153" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="48" t="s">
         <v>469</v>
       </c>
@@ -25702,7 +25702,7 @@
       <c r="AC153" s="28"/>
       <c r="AD153" s="28"/>
     </row>
-    <row r="154" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="48" t="s">
         <v>509</v>
       </c>
@@ -25786,7 +25786,7 @@
       <c r="AC154" s="28"/>
       <c r="AD154" s="28"/>
     </row>
-    <row r="155" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="66" t="s">
         <v>539</v>
       </c>
@@ -25870,7 +25870,7 @@
       <c r="AC155" s="28"/>
       <c r="AD155" s="28"/>
     </row>
-    <row r="156" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="70" t="s">
         <v>543</v>
       </c>
@@ -25954,7 +25954,7 @@
       <c r="AC156" s="28"/>
       <c r="AD156" s="28"/>
     </row>
-    <row r="157" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="66" t="s">
         <v>546</v>
       </c>
@@ -26038,7 +26038,7 @@
       <c r="AC157" s="28"/>
       <c r="AD157" s="28"/>
     </row>
-    <row r="158" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="70" t="s">
         <v>549</v>
       </c>
@@ -26122,7 +26122,7 @@
       <c r="AC158" s="28"/>
       <c r="AD158" s="28"/>
     </row>
-    <row r="159" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="66" t="s">
         <v>551</v>
       </c>
@@ -26206,7 +26206,7 @@
       <c r="AC159" s="28"/>
       <c r="AD159" s="28"/>
     </row>
-    <row r="160" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="70" t="s">
         <v>553</v>
       </c>
@@ -26290,7 +26290,7 @@
       <c r="AC160" s="28"/>
       <c r="AD160" s="28"/>
     </row>
-    <row r="161" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="66" t="s">
         <v>555</v>
       </c>
@@ -26374,7 +26374,7 @@
       <c r="AC161" s="28"/>
       <c r="AD161" s="28"/>
     </row>
-    <row r="162" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="70" t="s">
         <v>557</v>
       </c>
@@ -26458,7 +26458,7 @@
       <c r="AC162" s="28"/>
       <c r="AD162" s="28"/>
     </row>
-    <row r="163" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="66" t="s">
         <v>559</v>
       </c>
@@ -26542,7 +26542,7 @@
       <c r="AC163" s="28"/>
       <c r="AD163" s="28"/>
     </row>
-    <row r="164" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="70" t="s">
         <v>562</v>
       </c>
@@ -26626,7 +26626,7 @@
       <c r="AC164" s="28"/>
       <c r="AD164" s="28"/>
     </row>
-    <row r="165" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="66" t="s">
         <v>565</v>
       </c>
@@ -26710,7 +26710,7 @@
       <c r="AC165" s="28"/>
       <c r="AD165" s="28"/>
     </row>
-    <row r="166" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="70" t="s">
         <v>568</v>
       </c>
@@ -26794,7 +26794,7 @@
       <c r="AC166" s="28"/>
       <c r="AD166" s="28"/>
     </row>
-    <row r="167" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="66" t="s">
         <v>571</v>
       </c>
@@ -26878,7 +26878,7 @@
       <c r="AC167" s="28"/>
       <c r="AD167" s="28"/>
     </row>
-    <row r="168" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="70" t="s">
         <v>574</v>
       </c>
@@ -26962,7 +26962,7 @@
       <c r="AC168" s="28"/>
       <c r="AD168" s="28"/>
     </row>
-    <row r="169" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="66" t="s">
         <v>577</v>
       </c>
@@ -27046,7 +27046,7 @@
       <c r="AC169" s="28"/>
       <c r="AD169" s="28"/>
     </row>
-    <row r="170" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="66" t="s">
         <v>579</v>
       </c>
@@ -27130,7 +27130,7 @@
       <c r="AC170" s="28"/>
       <c r="AD170" s="28"/>
     </row>
-    <row r="171" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="66" t="s">
         <v>581</v>
       </c>
@@ -27214,7 +27214,7 @@
       <c r="AC171" s="28"/>
       <c r="AD171" s="28"/>
     </row>
-    <row r="172" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:30" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="66" t="s">
         <v>584</v>
       </c>
@@ -27298,7 +27298,7 @@
       <c r="AC172" s="28"/>
       <c r="AD172" s="28"/>
     </row>
-    <row r="173" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:30" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="76" t="s">
         <v>919</v>
       </c>
@@ -27382,7 +27382,7 @@
       <c r="AC173" s="28"/>
       <c r="AD173" s="28"/>
     </row>
-    <row r="174" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:30" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="76" t="s">
         <v>922</v>
       </c>
@@ -27466,7 +27466,7 @@
       <c r="AC174" s="28"/>
       <c r="AD174" s="28"/>
     </row>
-    <row r="175" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:30" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="76" t="s">
         <v>925</v>
       </c>
@@ -27550,7 +27550,7 @@
       <c r="AC175" s="48"/>
       <c r="AD175" s="48"/>
     </row>
-    <row r="176" spans="1:30" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:30" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="70" t="s">
         <v>601</v>
       </c>
@@ -27642,7 +27642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="177" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:32" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="70" t="s">
         <v>604</v>
       </c>
@@ -27734,7 +27734,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="178" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:32" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="70" t="s">
         <v>606</v>
       </c>
@@ -27826,7 +27826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:32" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="70" t="s">
         <v>607</v>
       </c>
@@ -27918,7 +27918,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="180" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="70" t="s">
         <v>609</v>
       </c>
@@ -28010,7 +28010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:32" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="70" t="s">
         <v>610</v>
       </c>
@@ -28102,7 +28102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="70" t="s">
         <v>611</v>
       </c>
@@ -28194,7 +28194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="70" t="s">
         <v>615</v>
       </c>
@@ -28286,7 +28286,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="184" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="70" t="s">
         <v>614</v>
       </c>
@@ -28378,7 +28378,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="185" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="70" t="s">
         <v>619</v>
       </c>
@@ -28473,7 +28473,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="186" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:32" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="70" t="s">
         <v>623</v>
       </c>
@@ -28568,7 +28568,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="187" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:32" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="70" t="s">
         <v>629</v>
       </c>
@@ -28663,7 +28663,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="188" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="70" t="s">
         <v>630</v>
       </c>
@@ -28758,7 +28758,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="189" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="70" t="s">
         <v>636</v>
       </c>
@@ -28850,7 +28850,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="190" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="70" t="s">
         <v>849</v>
       </c>
@@ -28942,7 +28942,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="191" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="70" t="s">
         <v>850</v>
       </c>
@@ -29034,7 +29034,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="192" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="70" t="s">
         <v>640</v>
       </c>
@@ -29126,7 +29126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="193" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="70" t="s">
         <v>642</v>
       </c>
@@ -29218,7 +29218,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="70" t="s">
         <v>648</v>
       </c>
@@ -29310,7 +29310,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="70" t="s">
         <v>649</v>
       </c>
@@ -29402,7 +29402,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="70" t="s">
         <v>654</v>
       </c>
@@ -29494,7 +29494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="197" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="70" t="s">
         <v>656</v>
       </c>
@@ -29586,7 +29586,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="70" t="s">
         <v>662</v>
       </c>
@@ -29678,7 +29678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="199" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="70" t="s">
         <v>665</v>
       </c>
@@ -29770,7 +29770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="200" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="70" t="s">
         <v>666</v>
       </c>
@@ -29862,7 +29862,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="201" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="70" t="s">
         <v>671</v>
       </c>
@@ -29954,7 +29954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="202" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="70" t="s">
         <v>676</v>
       </c>
@@ -30046,7 +30046,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="203" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="70" t="s">
         <v>677</v>
       </c>
@@ -30138,7 +30138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="204" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="70" t="s">
         <v>879</v>
       </c>
@@ -30230,7 +30230,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="205" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="70" t="s">
         <v>882</v>
       </c>
@@ -30322,7 +30322,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="206" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="70" t="s">
         <v>883</v>
       </c>
@@ -30414,7 +30414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="207" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="70" t="s">
         <v>732</v>
       </c>
@@ -30506,7 +30506,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="208" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="70" t="s">
         <v>735</v>
       </c>
@@ -30598,7 +30598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="209" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="70" t="s">
         <v>737</v>
       </c>
@@ -30690,7 +30690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="70" t="s">
         <v>777</v>
       </c>
@@ -30782,7 +30782,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="211" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="70" t="s">
         <v>866</v>
       </c>
@@ -30874,7 +30874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="212" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="70" t="s">
         <v>867</v>
       </c>
@@ -30966,7 +30966,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="213" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="70" t="s">
         <v>742</v>
       </c>
@@ -31058,7 +31058,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="214" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="70" t="s">
         <v>748</v>
       </c>
@@ -31150,7 +31150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="215" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="70" t="s">
         <v>749</v>
       </c>
@@ -31242,7 +31242,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="216" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="70" t="s">
         <v>754</v>
       </c>
@@ -31334,7 +31334,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="70" t="s">
         <v>755</v>
       </c>
@@ -31426,7 +31426,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="218" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="70" t="s">
         <v>756</v>
       </c>
@@ -31518,7 +31518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="219" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="70" t="s">
         <v>761</v>
       </c>
@@ -31610,7 +31610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="220" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="70" t="s">
         <v>764</v>
       </c>
@@ -31702,7 +31702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="221" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="70" t="s">
         <v>769</v>
       </c>
@@ -31794,7 +31794,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="222" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="70" t="s">
         <v>772</v>
       </c>
@@ -31886,7 +31886,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="223" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="70" t="s">
         <v>773</v>
       </c>
@@ -31978,7 +31978,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="224" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="70" t="s">
         <v>779</v>
       </c>
@@ -32070,7 +32070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="225" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="70" t="s">
         <v>791</v>
       </c>
@@ -32162,7 +32162,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="226" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="70" t="s">
         <v>796</v>
       </c>
@@ -32254,7 +32254,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="227" spans="1:30" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:30" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="70" t="s">
         <v>801</v>
       </c>
@@ -32346,7 +32346,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="228" spans="1:30" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:30" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="70" t="s">
         <v>803</v>
       </c>
@@ -32438,7 +32438,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="229" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="70" t="s">
         <v>805</v>
       </c>
@@ -32530,7 +32530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="70" t="s">
         <v>810</v>
       </c>
@@ -32622,7 +32622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="231" spans="1:30" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:30" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="70" t="s">
         <v>812</v>
       </c>
@@ -32714,7 +32714,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="232" spans="1:30" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:30" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="70" t="s">
         <v>816</v>
       </c>
@@ -32806,7 +32806,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="70" t="s">
         <v>821</v>
       </c>
@@ -32898,7 +32898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="70" t="s">
         <v>824</v>
       </c>
@@ -32990,7 +32990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="70" t="s">
         <v>825</v>
       </c>
@@ -33082,7 +33082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="70" t="s">
         <v>830</v>
       </c>
@@ -33174,7 +33174,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="70" t="s">
         <v>928</v>
       </c>
@@ -33266,7 +33266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="238" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="70" t="s">
         <v>870</v>
       </c>
@@ -33358,7 +33358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="239" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="70" t="s">
         <v>874</v>
       </c>
@@ -33450,7 +33450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="240" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="70" t="s">
         <v>840</v>
       </c>
@@ -33542,7 +33542,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="241" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="70" t="s">
         <v>844</v>
       </c>
@@ -33634,7 +33634,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="242" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="70" t="s">
         <v>846</v>
       </c>
@@ -33726,7 +33726,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="243" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="70" t="s">
         <v>859</v>
       </c>
@@ -33818,7 +33818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="244" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="70" t="s">
         <v>861</v>
       </c>
@@ -33910,7 +33910,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>887</v>
       </c>
@@ -34002,7 +34002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="246" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>894</v>
       </c>
@@ -34263,8 +34263,9 @@
     <hyperlink ref="S241" r:id="rId60" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
     <hyperlink ref="T236" r:id="rId61" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
     <hyperlink ref="S226" r:id="rId62" display="https://console.zlaata.com/admin/cancel-order" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
+    <hyperlink ref="S237" r:id="rId63" xr:uid="{34D22F7E-DB9E-4075-BA35-4715BDF656B0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId63"/>
+  <pageSetup orientation="portrait" r:id="rId64"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataQAsever130226\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever33\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10FFCD5-63E5-41F1-990E-C81AE5E856EF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E36DF9F-D7F0-46FC-A476-9C8DD4D9A55E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8732" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8810" uniqueCount="936">
   <si>
     <t>S.No</t>
   </si>
@@ -2816,6 +2816,24 @@
   </si>
   <si>
     <t>https://qa.adm.testingserver8.com/admin/subscriber</t>
+  </si>
+  <si>
+    <t>TD_UI_Admin_OEV_14</t>
+  </si>
+  <si>
+    <t>TD_UI_Admin_OEV_15</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_14</t>
+  </si>
+  <si>
+    <t>Verify the RTO Order Flow before the order is delivered.</t>
+  </si>
+  <si>
+    <t>TC_UI_Admin_OEV_15</t>
+  </si>
+  <si>
+    <t>Verify the RTO Order Flow for an exchange order before delivered.</t>
   </si>
 </sst>
 </file>
@@ -4322,21 +4340,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z262"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z264"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
-    <col min="4" max="4" width="118.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="118.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4368,7 +4386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="28">
         <v>1</v>
       </c>
@@ -4400,7 +4418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="28">
         <v>2</v>
       </c>
@@ -4432,7 +4450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="28">
         <v>3</v>
       </c>
@@ -4464,7 +4482,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="28">
         <v>4</v>
       </c>
@@ -4496,7 +4514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="28">
         <v>5</v>
       </c>
@@ -4528,7 +4546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="28">
         <v>6</v>
       </c>
@@ -4560,7 +4578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="28">
         <v>7</v>
       </c>
@@ -4592,7 +4610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="28">
         <v>8</v>
       </c>
@@ -4624,7 +4642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="28">
         <v>9</v>
       </c>
@@ -4656,7 +4674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="28">
         <v>10</v>
       </c>
@@ -4688,7 +4706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="28">
         <v>11</v>
       </c>
@@ -4720,7 +4738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="28">
         <v>12</v>
       </c>
@@ -4752,7 +4770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="28">
         <v>13</v>
       </c>
@@ -4784,7 +4802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="28">
         <v>14</v>
       </c>
@@ -4816,7 +4834,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="28">
         <v>15</v>
       </c>
@@ -4848,7 +4866,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="28">
         <v>16</v>
       </c>
@@ -4880,7 +4898,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="28">
         <v>17</v>
       </c>
@@ -4912,7 +4930,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="28">
         <v>18</v>
       </c>
@@ -4944,7 +4962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="28">
         <v>19</v>
       </c>
@@ -4976,7 +4994,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="28">
         <v>20</v>
       </c>
@@ -5008,7 +5026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="28">
         <v>21</v>
       </c>
@@ -5040,7 +5058,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="45">
         <v>22</v>
       </c>
@@ -5072,7 +5090,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="88" t="s">
         <v>156</v>
       </c>
@@ -5086,7 +5104,7 @@
       <c r="I24" s="89"/>
       <c r="J24" s="90"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>1</v>
       </c>
@@ -5118,7 +5136,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>2</v>
       </c>
@@ -5150,7 +5168,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>3</v>
       </c>
@@ -5182,7 +5200,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>4</v>
       </c>
@@ -5214,7 +5232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>5</v>
       </c>
@@ -5246,7 +5264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>6</v>
       </c>
@@ -5278,7 +5296,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>7</v>
       </c>
@@ -5310,7 +5328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>8</v>
       </c>
@@ -5342,7 +5360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>9</v>
       </c>
@@ -5374,7 +5392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>10</v>
       </c>
@@ -5406,7 +5424,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>11</v>
       </c>
@@ -5438,7 +5456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>12</v>
       </c>
@@ -5470,7 +5488,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="91" t="s">
         <v>172</v>
       </c>
@@ -5484,7 +5502,7 @@
       <c r="I37" s="92"/>
       <c r="J37" s="93"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>1</v>
       </c>
@@ -5516,7 +5534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -5548,7 +5566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>3</v>
       </c>
@@ -5580,7 +5598,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>4</v>
       </c>
@@ -5612,7 +5630,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>5</v>
       </c>
@@ -5644,7 +5662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>6</v>
       </c>
@@ -5676,7 +5694,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>7</v>
       </c>
@@ -5708,7 +5726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>8</v>
       </c>
@@ -5740,7 +5758,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>9</v>
       </c>
@@ -5772,7 +5790,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>10</v>
       </c>
@@ -5804,7 +5822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>11</v>
       </c>
@@ -5836,7 +5854,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>12</v>
       </c>
@@ -5868,7 +5886,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>13</v>
       </c>
@@ -5900,7 +5918,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>14</v>
       </c>
@@ -5932,7 +5950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>15</v>
       </c>
@@ -5964,7 +5982,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>16</v>
       </c>
@@ -5996,7 +6014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>16</v>
       </c>
@@ -6028,7 +6046,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="91" t="s">
         <v>244</v>
       </c>
@@ -6042,7 +6060,7 @@
       <c r="I55" s="92"/>
       <c r="J55" s="93"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
         <v>1</v>
       </c>
@@ -6074,7 +6092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="25">
         <v>2</v>
       </c>
@@ -6106,7 +6124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="25">
         <v>3</v>
       </c>
@@ -6138,7 +6156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="25">
         <v>4</v>
       </c>
@@ -6170,7 +6188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="25">
         <v>5</v>
       </c>
@@ -6202,7 +6220,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="25">
         <v>6</v>
       </c>
@@ -6234,7 +6252,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="25">
         <v>7</v>
       </c>
@@ -6266,7 +6284,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="25">
         <v>8</v>
       </c>
@@ -6298,7 +6316,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="25">
         <v>9</v>
       </c>
@@ -6330,7 +6348,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="25">
         <v>10</v>
       </c>
@@ -6362,7 +6380,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="91" t="s">
         <v>246</v>
       </c>
@@ -6376,7 +6394,7 @@
       <c r="I66" s="92"/>
       <c r="J66" s="93"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
         <v>1</v>
       </c>
@@ -6408,7 +6426,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="25">
         <v>2</v>
       </c>
@@ -6440,7 +6458,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="25">
         <v>3</v>
       </c>
@@ -6472,7 +6490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="25">
         <v>4</v>
       </c>
@@ -6504,7 +6522,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="25">
         <v>5</v>
       </c>
@@ -6536,7 +6554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="25">
         <v>6</v>
       </c>
@@ -6568,7 +6586,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="25">
         <v>7</v>
       </c>
@@ -6600,7 +6618,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="25">
         <v>8</v>
       </c>
@@ -6632,7 +6650,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="25">
         <v>9</v>
       </c>
@@ -6664,7 +6682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="25">
         <v>10</v>
       </c>
@@ -6696,7 +6714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="25">
         <v>11</v>
       </c>
@@ -6728,7 +6746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="91" t="s">
         <v>345</v>
       </c>
@@ -6742,7 +6760,7 @@
       <c r="I78" s="92"/>
       <c r="J78" s="93"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
         <v>1</v>
       </c>
@@ -6774,7 +6792,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="25">
         <v>2</v>
       </c>
@@ -6806,7 +6824,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="25">
         <v>3</v>
       </c>
@@ -6838,7 +6856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="25">
         <v>4</v>
       </c>
@@ -6870,7 +6888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="25">
         <v>5</v>
       </c>
@@ -6902,7 +6920,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="25">
         <v>6</v>
       </c>
@@ -6934,7 +6952,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="25">
         <v>7</v>
       </c>
@@ -6966,7 +6984,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="25">
         <v>8</v>
       </c>
@@ -6998,7 +7016,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="25">
         <v>9</v>
       </c>
@@ -7030,7 +7048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="25">
         <v>10</v>
       </c>
@@ -7062,7 +7080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="25">
         <v>11</v>
       </c>
@@ -7094,7 +7112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="25">
         <v>12</v>
       </c>
@@ -7126,7 +7144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="25">
         <v>13</v>
       </c>
@@ -7158,7 +7176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="25">
         <v>14</v>
       </c>
@@ -7190,7 +7208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="25">
         <v>15</v>
       </c>
@@ -7222,7 +7240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="25">
         <v>16</v>
       </c>
@@ -7254,7 +7272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="25">
         <v>17</v>
       </c>
@@ -7286,7 +7304,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="25">
         <v>18</v>
       </c>
@@ -7318,7 +7336,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="25">
         <v>19</v>
       </c>
@@ -7350,7 +7368,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="25">
         <v>20</v>
       </c>
@@ -7382,7 +7400,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="25">
         <v>21</v>
       </c>
@@ -7414,7 +7432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="25">
         <v>22</v>
       </c>
@@ -7446,7 +7464,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="25">
         <v>23</v>
       </c>
@@ -7478,7 +7496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="25">
         <v>24</v>
       </c>
@@ -7510,7 +7528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="25">
         <v>25</v>
       </c>
@@ -7542,7 +7560,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="25">
         <v>27</v>
       </c>
@@ -7574,7 +7592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="25">
         <v>28</v>
       </c>
@@ -7606,7 +7624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="94" t="s">
         <v>374</v>
       </c>
@@ -7620,7 +7638,7 @@
       <c r="I106" s="94"/>
       <c r="J106" s="94"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
         <v>1</v>
       </c>
@@ -7652,7 +7670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="25">
         <v>2</v>
       </c>
@@ -7684,7 +7702,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="25">
         <v>3</v>
       </c>
@@ -7716,7 +7734,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="25">
         <v>4</v>
       </c>
@@ -7748,7 +7766,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="25">
         <v>5</v>
       </c>
@@ -7780,7 +7798,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="25">
         <v>6</v>
       </c>
@@ -7812,7 +7830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="25">
         <v>7</v>
       </c>
@@ -7844,7 +7862,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="25">
         <v>8</v>
       </c>
@@ -7876,7 +7894,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="25">
         <v>9</v>
       </c>
@@ -7908,7 +7926,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="25">
         <v>10</v>
       </c>
@@ -7940,7 +7958,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="25">
         <v>11</v>
       </c>
@@ -7972,7 +7990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="25">
         <v>12</v>
       </c>
@@ -8018,7 +8036,7 @@
       <c r="W118" s="58"/>
       <c r="X118" s="58"/>
     </row>
-    <row r="119" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="25">
         <v>13</v>
       </c>
@@ -8064,7 +8082,7 @@
       <c r="W119" s="58"/>
       <c r="X119" s="58"/>
     </row>
-    <row r="120" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="25">
         <v>14</v>
       </c>
@@ -8110,7 +8128,7 @@
       <c r="W120" s="58"/>
       <c r="X120" s="58"/>
     </row>
-    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="95" t="s">
         <v>376</v>
       </c>
@@ -8138,7 +8156,7 @@
       <c r="W121" s="58"/>
       <c r="X121" s="58"/>
     </row>
-    <row r="122" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="25">
         <v>1</v>
       </c>
@@ -8184,7 +8202,7 @@
       <c r="W122" s="58"/>
       <c r="X122" s="58"/>
     </row>
-    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="95" t="s">
         <v>381</v>
       </c>
@@ -8212,7 +8230,7 @@
       <c r="W123" s="58"/>
       <c r="X123" s="58"/>
     </row>
-    <row r="124" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="25">
         <v>1</v>
       </c>
@@ -8258,7 +8276,7 @@
       <c r="W124" s="58"/>
       <c r="X124" s="58"/>
     </row>
-    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="95" t="s">
         <v>394</v>
       </c>
@@ -8272,7 +8290,7 @@
       <c r="I125" s="95"/>
       <c r="J125" s="95"/>
     </row>
-    <row r="126" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
         <v>1</v>
       </c>
@@ -8318,7 +8336,7 @@
       <c r="W126" s="61"/>
       <c r="X126" s="61"/>
     </row>
-    <row r="127" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="25">
         <v>2</v>
       </c>
@@ -8364,7 +8382,7 @@
       <c r="W127" s="58"/>
       <c r="X127" s="58"/>
     </row>
-    <row r="128" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="25">
         <v>3</v>
       </c>
@@ -8410,7 +8428,7 @@
       <c r="W128" s="58"/>
       <c r="X128" s="58"/>
     </row>
-    <row r="129" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="25">
         <v>4</v>
       </c>
@@ -8456,7 +8474,7 @@
       <c r="W129" s="58"/>
       <c r="X129" s="58"/>
     </row>
-    <row r="130" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="25">
         <v>5</v>
       </c>
@@ -8502,7 +8520,7 @@
       <c r="W130" s="58"/>
       <c r="X130" s="58"/>
     </row>
-    <row r="131" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="25">
         <v>6</v>
       </c>
@@ -8548,7 +8566,7 @@
       <c r="W131" s="58"/>
       <c r="X131" s="58"/>
     </row>
-    <row r="132" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="25">
         <v>7</v>
       </c>
@@ -8594,7 +8612,7 @@
       <c r="W132" s="58"/>
       <c r="X132" s="58"/>
     </row>
-    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="95" t="s">
         <v>411</v>
       </c>
@@ -8622,7 +8640,7 @@
       <c r="W133" s="58"/>
       <c r="X133" s="58"/>
     </row>
-    <row r="134" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="59">
         <v>11</v>
       </c>
@@ -8668,7 +8686,7 @@
       <c r="W134" s="58"/>
       <c r="X134" s="58"/>
     </row>
-    <row r="135" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="26">
         <v>2</v>
       </c>
@@ -8714,7 +8732,7 @@
       <c r="W135" s="58"/>
       <c r="X135" s="58"/>
     </row>
-    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="26">
         <v>3</v>
       </c>
@@ -8746,7 +8764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="26">
         <v>4</v>
       </c>
@@ -8792,7 +8810,7 @@
       <c r="W137" s="58"/>
       <c r="X137" s="58"/>
     </row>
-    <row r="138" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="26">
         <v>5</v>
       </c>
@@ -8838,7 +8856,7 @@
       <c r="W138" s="58"/>
       <c r="X138" s="58"/>
     </row>
-    <row r="139" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="26">
         <v>6</v>
       </c>
@@ -8884,7 +8902,7 @@
       <c r="W139" s="58"/>
       <c r="X139" s="58"/>
     </row>
-    <row r="140" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="26">
         <v>7</v>
       </c>
@@ -8916,7 +8934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="26">
         <v>8</v>
       </c>
@@ -8962,7 +8980,7 @@
       <c r="W141" s="58"/>
       <c r="X141" s="58"/>
     </row>
-    <row r="142" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="26">
         <v>9</v>
       </c>
@@ -9008,7 +9026,7 @@
       <c r="W142" s="58"/>
       <c r="X142" s="58"/>
     </row>
-    <row r="143" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="26">
         <v>10</v>
       </c>
@@ -9054,7 +9072,7 @@
       <c r="W143" s="58"/>
       <c r="X143" s="58"/>
     </row>
-    <row r="144" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="26">
         <v>11</v>
       </c>
@@ -9100,7 +9118,7 @@
       <c r="W144" s="58"/>
       <c r="X144" s="58"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="100" t="s">
         <v>439</v>
       </c>
@@ -9128,7 +9146,7 @@
       <c r="W145" s="58"/>
       <c r="X145" s="58"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="25">
         <v>1</v>
       </c>
@@ -9174,7 +9192,7 @@
       <c r="W146" s="58"/>
       <c r="X146" s="58"/>
     </row>
-    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="25">
         <v>2</v>
       </c>
@@ -9206,7 +9224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A148" s="25">
         <v>3</v>
       </c>
@@ -9238,7 +9256,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="25">
         <v>4</v>
       </c>
@@ -9270,7 +9288,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="25">
         <v>5</v>
       </c>
@@ -9318,7 +9336,7 @@
       <c r="Y150" s="58"/>
       <c r="Z150" s="58"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="25">
         <v>6</v>
       </c>
@@ -9366,7 +9384,7 @@
       <c r="Y151" s="58"/>
       <c r="Z151" s="58"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="25">
         <v>7</v>
       </c>
@@ -9414,7 +9432,7 @@
       <c r="Y152" s="58"/>
       <c r="Z152" s="58"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="25">
         <v>8</v>
       </c>
@@ -9462,7 +9480,7 @@
       <c r="Y153" s="58"/>
       <c r="Z153" s="58"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="25">
         <v>9</v>
       </c>
@@ -9510,7 +9528,7 @@
       <c r="Y154" s="58"/>
       <c r="Z154" s="58"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="25">
         <v>10</v>
       </c>
@@ -9558,7 +9576,7 @@
       <c r="Y155" s="58"/>
       <c r="Z155" s="58"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="95" t="s">
         <v>510</v>
       </c>
@@ -9588,7 +9606,7 @@
       <c r="Y156" s="58"/>
       <c r="Z156" s="58"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="25">
         <v>1</v>
       </c>
@@ -9636,7 +9654,7 @@
       <c r="Y157" s="58"/>
       <c r="Z157" s="58"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="95" t="s">
         <v>536</v>
       </c>
@@ -9666,7 +9684,7 @@
       <c r="Y158" s="58"/>
       <c r="Z158" s="58"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="67">
         <v>1</v>
       </c>
@@ -9714,7 +9732,7 @@
       <c r="Y159" s="58"/>
       <c r="Z159" s="58"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="68">
         <v>2</v>
       </c>
@@ -9762,7 +9780,7 @@
       <c r="Y160" s="58"/>
       <c r="Z160" s="58"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="68">
         <v>3</v>
       </c>
@@ -9810,7 +9828,7 @@
       <c r="Y161" s="58"/>
       <c r="Z161" s="58"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="68">
         <v>4</v>
       </c>
@@ -9858,7 +9876,7 @@
       <c r="Y162" s="58"/>
       <c r="Z162" s="58"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="68">
         <v>5</v>
       </c>
@@ -9906,7 +9924,7 @@
       <c r="Y163" s="58"/>
       <c r="Z163" s="58"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="68">
         <v>6</v>
       </c>
@@ -9954,7 +9972,7 @@
       <c r="Y164" s="58"/>
       <c r="Z164" s="58"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="68">
         <v>7</v>
       </c>
@@ -10002,7 +10020,7 @@
       <c r="Y165" s="58"/>
       <c r="Z165" s="58"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="68">
         <v>8</v>
       </c>
@@ -10050,7 +10068,7 @@
       <c r="Y166" s="58"/>
       <c r="Z166" s="58"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="67">
         <v>9</v>
       </c>
@@ -10098,7 +10116,7 @@
       <c r="Y167" s="58"/>
       <c r="Z167" s="58"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="68">
         <v>10</v>
       </c>
@@ -10130,7 +10148,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="67">
         <v>11</v>
       </c>
@@ -10162,7 +10180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="68">
         <v>12</v>
       </c>
@@ -10194,7 +10212,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="67">
         <v>13</v>
       </c>
@@ -10226,7 +10244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="68">
         <v>14</v>
       </c>
@@ -10258,7 +10276,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="67">
         <v>15</v>
       </c>
@@ -10290,7 +10308,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="68">
         <v>16</v>
       </c>
@@ -10322,7 +10340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="175" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="67">
         <v>17</v>
       </c>
@@ -10354,7 +10372,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="68">
         <v>18</v>
       </c>
@@ -10386,7 +10404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="86">
         <v>19</v>
       </c>
@@ -10418,7 +10436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="86">
         <v>20</v>
       </c>
@@ -10450,7 +10468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="86">
         <v>21</v>
       </c>
@@ -10482,7 +10500,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="95" t="s">
         <v>715</v>
       </c>
@@ -10496,7 +10514,7 @@
       <c r="I180" s="95"/>
       <c r="J180" s="95"/>
     </row>
-    <row r="181" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="68">
         <v>1</v>
       </c>
@@ -10528,7 +10546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="68">
         <v>2</v>
       </c>
@@ -10560,7 +10578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="68">
         <v>3</v>
       </c>
@@ -10592,7 +10610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="68">
         <v>4</v>
       </c>
@@ -10624,7 +10642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="68">
         <v>5</v>
       </c>
@@ -10656,7 +10674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="68">
         <v>6</v>
       </c>
@@ -10688,7 +10706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="68">
         <v>7</v>
       </c>
@@ -10720,7 +10738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="68">
         <v>8</v>
       </c>
@@ -10752,7 +10770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="1:10" s="28" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="68">
         <v>9</v>
       </c>
@@ -10784,7 +10802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="97" t="s">
         <v>617</v>
       </c>
@@ -10798,7 +10816,7 @@
       <c r="I190" s="98"/>
       <c r="J190" s="99"/>
     </row>
-    <row r="191" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="68">
         <v>1</v>
       </c>
@@ -10830,7 +10848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="68">
         <v>2</v>
       </c>
@@ -10862,7 +10880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="68">
         <v>3</v>
       </c>
@@ -10894,7 +10912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="68">
         <v>4</v>
       </c>
@@ -10926,7 +10944,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="68">
         <v>5</v>
       </c>
@@ -10958,7 +10976,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="68">
         <v>6</v>
       </c>
@@ -10990,7 +11008,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="68">
         <v>7</v>
       </c>
@@ -11022,7 +11040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="87" t="s">
         <v>638</v>
       </c>
@@ -11036,7 +11054,7 @@
       <c r="I198" s="87"/>
       <c r="J198" s="87"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="48">
         <v>1</v>
       </c>
@@ -11068,7 +11086,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="48">
         <v>2</v>
       </c>
@@ -11100,7 +11118,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="48">
         <v>3</v>
       </c>
@@ -11132,7 +11150,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="48">
         <v>4</v>
       </c>
@@ -11164,7 +11182,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="87" t="s">
         <v>651</v>
       </c>
@@ -11178,7 +11196,7 @@
       <c r="I203" s="87"/>
       <c r="J203" s="87"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="48">
         <v>1</v>
       </c>
@@ -11210,7 +11228,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="87" t="s">
         <v>657</v>
       </c>
@@ -11224,7 +11242,7 @@
       <c r="I205" s="87"/>
       <c r="J205" s="87"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="48">
         <v>1</v>
       </c>
@@ -11256,7 +11274,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="48">
         <v>2</v>
       </c>
@@ -11288,7 +11306,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="48">
         <v>3</v>
       </c>
@@ -11320,7 +11338,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="48">
         <v>4</v>
       </c>
@@ -11352,7 +11370,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="48">
         <v>5</v>
       </c>
@@ -11384,7 +11402,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="48">
         <v>6</v>
       </c>
@@ -11416,7 +11434,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="48">
         <v>7</v>
       </c>
@@ -11448,7 +11466,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="48">
         <v>8</v>
       </c>
@@ -11480,7 +11498,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="48">
         <v>9</v>
       </c>
@@ -11512,7 +11530,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="85"/>
       <c r="B215" s="85"/>
       <c r="C215" s="85"/>
@@ -11526,7 +11544,7 @@
       <c r="I215" s="85"/>
       <c r="J215" s="85"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="48">
         <v>1</v>
       </c>
@@ -11558,7 +11576,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" s="84" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="83"/>
       <c r="B217" s="83"/>
       <c r="C217" s="83"/>
@@ -11572,7 +11590,7 @@
       <c r="I217" s="83"/>
       <c r="J217" s="83"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="48">
         <v>1</v>
       </c>
@@ -11604,7 +11622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="48">
         <v>2</v>
       </c>
@@ -11636,7 +11654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="87" t="s">
         <v>733</v>
       </c>
@@ -11650,7 +11668,7 @@
       <c r="I220" s="87"/>
       <c r="J220" s="87"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="48">
         <v>1</v>
       </c>
@@ -11682,7 +11700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="48">
         <v>2</v>
       </c>
@@ -11714,7 +11732,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="48">
         <v>3</v>
       </c>
@@ -11746,7 +11764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="48">
         <v>4</v>
       </c>
@@ -11778,7 +11796,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="48">
         <v>5</v>
       </c>
@@ -11810,7 +11828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="87" t="s">
         <v>743</v>
       </c>
@@ -11824,7 +11842,7 @@
       <c r="I226" s="87"/>
       <c r="J226" s="87"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="48">
         <v>1</v>
       </c>
@@ -11856,7 +11874,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="48">
         <v>2</v>
       </c>
@@ -11888,7 +11906,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="48">
         <v>3</v>
       </c>
@@ -11920,7 +11938,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="48">
         <v>4</v>
       </c>
@@ -11952,7 +11970,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="48">
         <v>5</v>
       </c>
@@ -11984,7 +12002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="48">
         <v>6</v>
       </c>
@@ -12016,7 +12034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="48">
         <v>7</v>
       </c>
@@ -12048,7 +12066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="48">
         <v>8</v>
       </c>
@@ -12080,7 +12098,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="48">
         <v>9</v>
       </c>
@@ -12112,7 +12130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="48">
         <v>10</v>
       </c>
@@ -12144,7 +12162,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="48">
         <v>11</v>
       </c>
@@ -12176,7 +12194,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="87" t="s">
         <v>780</v>
       </c>
@@ -12190,7 +12208,7 @@
       <c r="I238" s="87"/>
       <c r="J238" s="87"/>
     </row>
-    <row r="239" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="48">
         <v>1</v>
       </c>
@@ -12222,7 +12240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="87" t="s">
         <v>792</v>
       </c>
@@ -12236,7 +12254,7 @@
       <c r="I240" s="87"/>
       <c r="J240" s="87"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="48">
         <v>1</v>
       </c>
@@ -12268,7 +12286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="48">
         <v>2</v>
       </c>
@@ -12300,7 +12318,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="48">
         <v>3</v>
       </c>
@@ -12332,7 +12350,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="48">
         <v>4</v>
       </c>
@@ -12364,7 +12382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="48">
         <v>5</v>
       </c>
@@ -12396,7 +12414,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="48">
         <v>6</v>
       </c>
@@ -12428,7 +12446,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="48">
         <v>7</v>
       </c>
@@ -12460,7 +12478,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="48">
         <v>8</v>
       </c>
@@ -12492,7 +12510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="48">
         <v>9</v>
       </c>
@@ -12524,7 +12542,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="48">
         <v>10</v>
       </c>
@@ -12556,7 +12574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="48">
         <v>11</v>
       </c>
@@ -12588,7 +12606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="48">
         <v>12</v>
       </c>
@@ -12620,7 +12638,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="48">
         <v>13</v>
       </c>
@@ -12652,44 +12670,62 @@
         <v>13</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="87" t="s">
-        <v>837</v>
-      </c>
-      <c r="B254" s="87"/>
-      <c r="C254" s="87"/>
-      <c r="D254" s="87"/>
-      <c r="E254" s="87"/>
-      <c r="F254" s="87"/>
-      <c r="G254" s="87"/>
-      <c r="H254" s="87"/>
-      <c r="I254" s="87"/>
-      <c r="J254" s="87"/>
-    </row>
-    <row r="255" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A254" s="48">
+        <v>14</v>
+      </c>
+      <c r="B254" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C254" s="79" t="s">
+        <v>932</v>
+      </c>
+      <c r="D254" s="78" t="s">
+        <v>933</v>
+      </c>
+      <c r="E254" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F254" s="79" t="s">
+        <v>930</v>
+      </c>
+      <c r="G254" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H254" s="48" t="s">
+        <v>795</v>
+      </c>
+      <c r="I254" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J254" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="48">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B255" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C255" s="79" t="s">
-        <v>871</v>
+        <v>934</v>
       </c>
       <c r="D255" s="78" t="s">
-        <v>872</v>
+        <v>935</v>
       </c>
       <c r="E255" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F255" s="70" t="s">
-        <v>870</v>
+      <c r="F255" s="79" t="s">
+        <v>931</v>
       </c>
       <c r="G255" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H255" s="48" t="s">
-        <v>873</v>
+        <v>795</v>
       </c>
       <c r="I255" s="48" t="s">
         <v>12</v>
@@ -12698,76 +12734,76 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="48">
+    <row r="256" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A256" s="87" t="s">
+        <v>837</v>
+      </c>
+      <c r="B256" s="87"/>
+      <c r="C256" s="87"/>
+      <c r="D256" s="87"/>
+      <c r="E256" s="87"/>
+      <c r="F256" s="87"/>
+      <c r="G256" s="87"/>
+      <c r="H256" s="87"/>
+      <c r="I256" s="87"/>
+      <c r="J256" s="87"/>
+    </row>
+    <row r="257" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A257" s="48">
+        <v>1</v>
+      </c>
+      <c r="B257" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C257" s="79" t="s">
+        <v>871</v>
+      </c>
+      <c r="D257" s="78" t="s">
+        <v>872</v>
+      </c>
+      <c r="E257" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F257" s="70" t="s">
+        <v>870</v>
+      </c>
+      <c r="G257" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H257" s="48" t="s">
+        <v>873</v>
+      </c>
+      <c r="I257" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J257" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A258" s="48">
         <v>2</v>
-      </c>
-      <c r="B256" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C256" s="79" t="s">
-        <v>875</v>
-      </c>
-      <c r="D256" s="78" t="s">
-        <v>876</v>
-      </c>
-      <c r="E256" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="F256" s="70" t="s">
-        <v>874</v>
-      </c>
-      <c r="G256" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="H256" s="48" t="s">
-        <v>873</v>
-      </c>
-      <c r="I256" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="J256" s="48" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="87" t="s">
-        <v>838</v>
-      </c>
-      <c r="B257" s="87"/>
-      <c r="C257" s="87"/>
-      <c r="D257" s="87"/>
-      <c r="E257" s="87"/>
-      <c r="F257" s="87"/>
-      <c r="G257" s="87"/>
-      <c r="H257" s="87"/>
-      <c r="I257" s="87"/>
-      <c r="J257" s="87"/>
-    </row>
-    <row r="258" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="48">
-        <v>1</v>
       </c>
       <c r="B258" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C258" s="79" t="s">
-        <v>839</v>
+        <v>875</v>
       </c>
       <c r="D258" s="78" t="s">
-        <v>842</v>
+        <v>876</v>
       </c>
       <c r="E258" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F258" s="70" t="s">
-        <v>840</v>
+        <v>874</v>
       </c>
       <c r="G258" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H258" s="48" t="s">
-        <v>841</v>
+        <v>873</v>
       </c>
       <c r="I258" s="48" t="s">
         <v>12</v>
@@ -12776,56 +12812,38 @@
         <v>13</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="48">
-        <v>2</v>
-      </c>
-      <c r="B259" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C259" s="79" t="s">
-        <v>843</v>
-      </c>
-      <c r="D259" s="78" t="s">
-        <v>845</v>
-      </c>
-      <c r="E259" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="F259" s="70" t="s">
-        <v>844</v>
-      </c>
-      <c r="G259" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="H259" s="48" t="s">
-        <v>841</v>
-      </c>
-      <c r="I259" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="J259" s="48" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A259" s="87" t="s">
+        <v>838</v>
+      </c>
+      <c r="B259" s="87"/>
+      <c r="C259" s="87"/>
+      <c r="D259" s="87"/>
+      <c r="E259" s="87"/>
+      <c r="F259" s="87"/>
+      <c r="G259" s="87"/>
+      <c r="H259" s="87"/>
+      <c r="I259" s="87"/>
+      <c r="J259" s="87"/>
+    </row>
+    <row r="260" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B260" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C260" s="79" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="D260" s="78" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="E260" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F260" s="70" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="G260" s="48" t="s">
         <v>11</v>
@@ -12840,24 +12858,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B261" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C261" s="79" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="D261" s="78" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="E261" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F261" s="70" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="G261" s="48" t="s">
         <v>11</v>
@@ -12872,24 +12890,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B262" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C262" s="79" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="D262" s="78" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="E262" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F262" s="70" t="s">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="G262" s="48" t="s">
         <v>11</v>
@@ -12904,16 +12922,80 @@
         <v>13</v>
       </c>
     </row>
+    <row r="263" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A263" s="48">
+        <v>4</v>
+      </c>
+      <c r="B263" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C263" s="79" t="s">
+        <v>857</v>
+      </c>
+      <c r="D263" s="78" t="s">
+        <v>858</v>
+      </c>
+      <c r="E263" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F263" s="70" t="s">
+        <v>859</v>
+      </c>
+      <c r="G263" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H263" s="48" t="s">
+        <v>841</v>
+      </c>
+      <c r="I263" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J263" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A264" s="48">
+        <v>5</v>
+      </c>
+      <c r="B264" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C264" s="79" t="s">
+        <v>862</v>
+      </c>
+      <c r="D264" s="78" t="s">
+        <v>863</v>
+      </c>
+      <c r="E264" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F264" s="70" t="s">
+        <v>861</v>
+      </c>
+      <c r="G264" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H264" s="48" t="s">
+        <v>841</v>
+      </c>
+      <c r="I264" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J264" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A257:J257"/>
+    <mergeCell ref="A259:J259"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A123:J123"/>
     <mergeCell ref="A125:J125"/>
     <mergeCell ref="A203:J203"/>
     <mergeCell ref="A198:J198"/>
-    <mergeCell ref="A254:J254"/>
+    <mergeCell ref="A256:J256"/>
     <mergeCell ref="A240:J240"/>
     <mergeCell ref="A133:J133"/>
     <mergeCell ref="A190:J190"/>
@@ -13027,36 +13109,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AF246"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF248"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="45.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="54.28515625" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="54.33203125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" customWidth="1"/>
-    <col min="12" max="12" width="53.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" customWidth="1"/>
+    <col min="12" max="12" width="53.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="52.28515625" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" customWidth="1"/>
+    <col min="17" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="71.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="52.33203125" customWidth="1"/>
+    <col min="21" max="21" width="20.88671875" customWidth="1"/>
     <col min="22" max="22" width="27" customWidth="1"/>
     <col min="24" max="25" width="29" customWidth="1"/>
-    <col min="26" max="26" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.42578125" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" customWidth="1"/>
+    <col min="26" max="26" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.44140625" customWidth="1"/>
+    <col min="29" max="29" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.6640625" customWidth="1"/>
+    <col min="31" max="31" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>5</v>
       </c>
@@ -13148,7 +13230,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>23</v>
       </c>
@@ -13228,7 +13310,7 @@
       <c r="AC2" s="28"/>
       <c r="AD2" s="28"/>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
         <v>25</v>
       </c>
@@ -13308,7 +13390,7 @@
       <c r="AC3" s="28"/>
       <c r="AD3" s="28"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>28</v>
       </c>
@@ -13388,7 +13470,7 @@
       <c r="AC4" s="28"/>
       <c r="AD4" s="28"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>58</v>
       </c>
@@ -13468,7 +13550,7 @@
       <c r="AC5" s="28"/>
       <c r="AD5" s="28"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>69</v>
       </c>
@@ -13548,7 +13630,7 @@
       <c r="AC6" s="28"/>
       <c r="AD6" s="28"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
         <v>73</v>
       </c>
@@ -13628,7 +13710,7 @@
       <c r="AC7" s="28"/>
       <c r="AD7" s="28"/>
     </row>
-    <row r="8" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="s">
         <v>77</v>
       </c>
@@ -13708,7 +13790,7 @@
       <c r="AC8" s="28"/>
       <c r="AD8" s="28"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="38" t="s">
         <v>79</v>
       </c>
@@ -13788,7 +13870,7 @@
       <c r="AC9" s="28"/>
       <c r="AD9" s="28"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="38" t="s">
         <v>80</v>
       </c>
@@ -13868,7 +13950,7 @@
       <c r="AC10" s="28"/>
       <c r="AD10" s="28"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="38" t="s">
         <v>81</v>
       </c>
@@ -13948,7 +14030,7 @@
       <c r="AC11" s="28"/>
       <c r="AD11" s="28"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="38" t="s">
         <v>83</v>
       </c>
@@ -14028,7 +14110,7 @@
       <c r="AC12" s="28"/>
       <c r="AD12" s="28"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
         <v>84</v>
       </c>
@@ -14108,7 +14190,7 @@
       <c r="AC13" s="28"/>
       <c r="AD13" s="28"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="38" t="s">
         <v>85</v>
       </c>
@@ -14188,7 +14270,7 @@
       <c r="AC14" s="28"/>
       <c r="AD14" s="28"/>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="38" t="s">
         <v>86</v>
       </c>
@@ -14268,7 +14350,7 @@
       <c r="AC15" s="28"/>
       <c r="AD15" s="28"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="s">
         <v>87</v>
       </c>
@@ -14348,7 +14430,7 @@
       <c r="AC16" s="28"/>
       <c r="AD16" s="28"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="s">
         <v>88</v>
       </c>
@@ -14428,7 +14510,7 @@
       <c r="AC17" s="28"/>
       <c r="AD17" s="28"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="38" t="s">
         <v>89</v>
       </c>
@@ -14508,7 +14590,7 @@
       <c r="AC18" s="28"/>
       <c r="AD18" s="28"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
         <v>91</v>
       </c>
@@ -14588,7 +14670,7 @@
       <c r="AC19" s="28"/>
       <c r="AD19" s="28"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="s">
         <v>93</v>
       </c>
@@ -14668,7 +14750,7 @@
       <c r="AC20" s="28"/>
       <c r="AD20" s="28"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
         <v>94</v>
       </c>
@@ -14748,7 +14830,7 @@
       <c r="AC21" s="28"/>
       <c r="AD21" s="28"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="s">
         <v>135</v>
       </c>
@@ -14828,7 +14910,7 @@
       <c r="AC22" s="28"/>
       <c r="AD22" s="28"/>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" s="42" t="s">
         <v>140</v>
       </c>
@@ -14908,7 +14990,7 @@
       <c r="AC23" s="28"/>
       <c r="AD23" s="28"/>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="53" t="s">
         <v>63</v>
       </c>
@@ -14988,7 +15070,7 @@
       <c r="AC24" s="28"/>
       <c r="AD24" s="28"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="46" t="s">
         <v>144</v>
       </c>
@@ -15068,7 +15150,7 @@
       <c r="AC25" s="28"/>
       <c r="AD25" s="28"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" s="46" t="s">
         <v>145</v>
       </c>
@@ -15148,7 +15230,7 @@
       <c r="AC26" s="28"/>
       <c r="AD26" s="28"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
         <v>146</v>
       </c>
@@ -15228,7 +15310,7 @@
       <c r="AC27" s="28"/>
       <c r="AD27" s="28"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" s="46" t="s">
         <v>147</v>
       </c>
@@ -15308,7 +15390,7 @@
       <c r="AC28" s="28"/>
       <c r="AD28" s="28"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" s="46" t="s">
         <v>148</v>
       </c>
@@ -15388,7 +15470,7 @@
       <c r="AC29" s="28"/>
       <c r="AD29" s="28"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" s="46" t="s">
         <v>150</v>
       </c>
@@ -15468,7 +15550,7 @@
       <c r="AC30" s="28"/>
       <c r="AD30" s="28"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" s="46" t="s">
         <v>151</v>
       </c>
@@ -15548,7 +15630,7 @@
       <c r="AC31" s="28"/>
       <c r="AD31" s="28"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" s="46" t="s">
         <v>152</v>
       </c>
@@ -15628,7 +15710,7 @@
       <c r="AC32" s="28"/>
       <c r="AD32" s="28"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33" s="46" t="s">
         <v>153</v>
       </c>
@@ -15708,7 +15790,7 @@
       <c r="AC33" s="28"/>
       <c r="AD33" s="28"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34" s="46" t="s">
         <v>154</v>
       </c>
@@ -15788,7 +15870,7 @@
       <c r="AC34" s="28"/>
       <c r="AD34" s="28"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35" s="46" t="s">
         <v>155</v>
       </c>
@@ -15868,7 +15950,7 @@
       <c r="AC35" s="28"/>
       <c r="AD35" s="28"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A36" s="33" t="s">
         <v>64</v>
       </c>
@@ -15948,7 +16030,7 @@
       <c r="AC36" s="28"/>
       <c r="AD36" s="28"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A37" s="54" t="s">
         <v>175</v>
       </c>
@@ -16030,7 +16112,7 @@
       <c r="AC37" s="28"/>
       <c r="AD37" s="28"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
         <v>179</v>
       </c>
@@ -16112,7 +16194,7 @@
       <c r="AC38" s="28"/>
       <c r="AD38" s="28"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
         <v>182</v>
       </c>
@@ -16194,7 +16276,7 @@
       <c r="AC39" s="28"/>
       <c r="AD39" s="28"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40" s="47" t="s">
         <v>185</v>
       </c>
@@ -16276,7 +16358,7 @@
       <c r="AC40" s="28"/>
       <c r="AD40" s="28"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" s="47" t="s">
         <v>188</v>
       </c>
@@ -16358,7 +16440,7 @@
       <c r="AC41" s="28"/>
       <c r="AD41" s="28"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="47" t="s">
         <v>190</v>
       </c>
@@ -16440,7 +16522,7 @@
       <c r="AC42" s="28"/>
       <c r="AD42" s="28"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" s="47" t="s">
         <v>193</v>
       </c>
@@ -16522,7 +16604,7 @@
       <c r="AC43" s="28"/>
       <c r="AD43" s="28"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" s="47" t="s">
         <v>196</v>
       </c>
@@ -16604,7 +16686,7 @@
       <c r="AC44" s="28"/>
       <c r="AD44" s="28"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" s="47" t="s">
         <v>198</v>
       </c>
@@ -16686,7 +16768,7 @@
       <c r="AC45" s="28"/>
       <c r="AD45" s="28"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46" s="47" t="s">
         <v>200</v>
       </c>
@@ -16768,7 +16850,7 @@
       <c r="AC46" s="28"/>
       <c r="AD46" s="28"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A47" s="47" t="s">
         <v>202</v>
       </c>
@@ -16850,7 +16932,7 @@
       <c r="AC47" s="28"/>
       <c r="AD47" s="28"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48" s="47" t="s">
         <v>204</v>
       </c>
@@ -16932,7 +17014,7 @@
       <c r="AC48" s="28"/>
       <c r="AD48" s="28"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A49" s="47" t="s">
         <v>206</v>
       </c>
@@ -17014,7 +17096,7 @@
       <c r="AC49" s="28"/>
       <c r="AD49" s="28"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A50" s="47" t="s">
         <v>208</v>
       </c>
@@ -17096,7 +17178,7 @@
       <c r="AC50" s="28"/>
       <c r="AD50" s="28"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A51" s="47" t="s">
         <v>210</v>
       </c>
@@ -17178,7 +17260,7 @@
       <c r="AC51" s="28"/>
       <c r="AD51" s="28"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A52" s="47" t="s">
         <v>212</v>
       </c>
@@ -17260,7 +17342,7 @@
       <c r="AC52" s="28"/>
       <c r="AD52" s="28"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A53" s="47" t="s">
         <v>687</v>
       </c>
@@ -17342,7 +17424,7 @@
       <c r="AC53" s="28"/>
       <c r="AD53" s="28"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A54" s="55" t="s">
         <v>213</v>
       </c>
@@ -17424,7 +17506,7 @@
       <c r="AC54" s="28"/>
       <c r="AD54" s="28"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A55" s="48" t="s">
         <v>214</v>
       </c>
@@ -17506,7 +17588,7 @@
       <c r="AC55" s="28"/>
       <c r="AD55" s="28"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A56" s="48" t="s">
         <v>215</v>
       </c>
@@ -17588,7 +17670,7 @@
       <c r="AC56" s="28"/>
       <c r="AD56" s="28"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A57" s="48" t="s">
         <v>216</v>
       </c>
@@ -17670,7 +17752,7 @@
       <c r="AC57" s="28"/>
       <c r="AD57" s="28"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A58" s="48" t="s">
         <v>217</v>
       </c>
@@ -17752,7 +17834,7 @@
       <c r="AC58" s="28"/>
       <c r="AD58" s="28"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A59" s="48" t="s">
         <v>218</v>
       </c>
@@ -17834,7 +17916,7 @@
       <c r="AC59" s="28"/>
       <c r="AD59" s="28"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A60" s="48" t="s">
         <v>219</v>
       </c>
@@ -17916,7 +17998,7 @@
       <c r="AC60" s="28"/>
       <c r="AD60" s="28"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A61" s="48" t="s">
         <v>220</v>
       </c>
@@ -17998,7 +18080,7 @@
       <c r="AC61" s="28"/>
       <c r="AD61" s="28"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A62" s="48" t="s">
         <v>221</v>
       </c>
@@ -18080,7 +18162,7 @@
       <c r="AC62" s="28"/>
       <c r="AD62" s="28"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A63" s="51" t="s">
         <v>222</v>
       </c>
@@ -18162,7 +18244,7 @@
       <c r="AC63" s="28"/>
       <c r="AD63" s="28"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A64" s="56" t="s">
         <v>249</v>
       </c>
@@ -18244,7 +18326,7 @@
       <c r="AC64" s="28"/>
       <c r="AD64" s="28"/>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A65" s="48" t="s">
         <v>253</v>
       </c>
@@ -18326,7 +18408,7 @@
       <c r="AC65" s="28"/>
       <c r="AD65" s="28"/>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A66" s="48" t="s">
         <v>256</v>
       </c>
@@ -18408,7 +18490,7 @@
       <c r="AC66" s="28"/>
       <c r="AD66" s="28"/>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A67" s="48" t="s">
         <v>259</v>
       </c>
@@ -18490,7 +18572,7 @@
       <c r="AC67" s="28"/>
       <c r="AD67" s="28"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A68" s="48" t="s">
         <v>262</v>
       </c>
@@ -18572,7 +18654,7 @@
       <c r="AC68" s="28"/>
       <c r="AD68" s="28"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A69" s="48" t="s">
         <v>265</v>
       </c>
@@ -18654,7 +18736,7 @@
       <c r="AC69" s="28"/>
       <c r="AD69" s="28"/>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A70" s="48" t="s">
         <v>268</v>
       </c>
@@ -18736,7 +18818,7 @@
       <c r="AC70" s="28"/>
       <c r="AD70" s="28"/>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A71" s="48" t="s">
         <v>271</v>
       </c>
@@ -18818,7 +18900,7 @@
       <c r="AC71" s="28"/>
       <c r="AD71" s="28"/>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A72" s="48" t="s">
         <v>274</v>
       </c>
@@ -18900,7 +18982,7 @@
       <c r="AC72" s="28"/>
       <c r="AD72" s="28"/>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A73" s="48" t="s">
         <v>277</v>
       </c>
@@ -18982,7 +19064,7 @@
       <c r="AC73" s="28"/>
       <c r="AD73" s="28"/>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A74" s="51" t="s">
         <v>280</v>
       </c>
@@ -19066,7 +19148,7 @@
       <c r="AC74" s="28"/>
       <c r="AD74" s="28"/>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A75" s="62" t="s">
         <v>282</v>
       </c>
@@ -19150,7 +19232,7 @@
       <c r="AC75" s="28"/>
       <c r="AD75" s="28"/>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A76" s="48" t="s">
         <v>285</v>
       </c>
@@ -19234,7 +19316,7 @@
       <c r="AC76" s="28"/>
       <c r="AD76" s="28"/>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A77" s="48" t="s">
         <v>287</v>
       </c>
@@ -19318,7 +19400,7 @@
       <c r="AC77" s="28"/>
       <c r="AD77" s="28"/>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A78" s="48" t="s">
         <v>289</v>
       </c>
@@ -19402,7 +19484,7 @@
       <c r="AC78" s="28"/>
       <c r="AD78" s="28"/>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A79" s="48" t="s">
         <v>292</v>
       </c>
@@ -19486,7 +19568,7 @@
       <c r="AC79" s="28"/>
       <c r="AD79" s="28"/>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A80" s="48" t="s">
         <v>295</v>
       </c>
@@ -19570,7 +19652,7 @@
       <c r="AC80" s="28"/>
       <c r="AD80" s="28"/>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="s">
         <v>298</v>
       </c>
@@ -19654,7 +19736,7 @@
       <c r="AC81" s="28"/>
       <c r="AD81" s="28"/>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A82" s="48" t="s">
         <v>301</v>
       </c>
@@ -19738,7 +19820,7 @@
       <c r="AC82" s="28"/>
       <c r="AD82" s="28"/>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A83" s="48" t="s">
         <v>304</v>
       </c>
@@ -19822,7 +19904,7 @@
       <c r="AC83" s="28"/>
       <c r="AD83" s="28"/>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A84" s="48" t="s">
         <v>306</v>
       </c>
@@ -19906,7 +19988,7 @@
       <c r="AC84" s="28"/>
       <c r="AD84" s="28"/>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A85" s="48" t="s">
         <v>308</v>
       </c>
@@ -19990,7 +20072,7 @@
       <c r="AC85" s="28"/>
       <c r="AD85" s="28"/>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A86" s="48" t="s">
         <v>310</v>
       </c>
@@ -20074,7 +20156,7 @@
       <c r="AC86" s="28"/>
       <c r="AD86" s="28"/>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A87" s="48" t="s">
         <v>313</v>
       </c>
@@ -20158,7 +20240,7 @@
       <c r="AC87" s="28"/>
       <c r="AD87" s="28"/>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A88" s="48" t="s">
         <v>316</v>
       </c>
@@ -20242,7 +20324,7 @@
       <c r="AC88" s="28"/>
       <c r="AD88" s="28"/>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A89" s="48" t="s">
         <v>319</v>
       </c>
@@ -20326,7 +20408,7 @@
       <c r="AC89" s="28"/>
       <c r="AD89" s="28"/>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A90" s="48" t="s">
         <v>322</v>
       </c>
@@ -20410,7 +20492,7 @@
       <c r="AC90" s="28"/>
       <c r="AD90" s="28"/>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A91" s="48" t="s">
         <v>324</v>
       </c>
@@ -20494,7 +20576,7 @@
       <c r="AC91" s="28"/>
       <c r="AD91" s="28"/>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A92" s="48" t="s">
         <v>327</v>
       </c>
@@ -20578,7 +20660,7 @@
       <c r="AC92" s="28"/>
       <c r="AD92" s="28"/>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A93" s="48" t="s">
         <v>330</v>
       </c>
@@ -20662,7 +20744,7 @@
       <c r="AC93" s="28"/>
       <c r="AD93" s="28"/>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A94" s="48" t="s">
         <v>332</v>
       </c>
@@ -20746,7 +20828,7 @@
       <c r="AC94" s="28"/>
       <c r="AD94" s="28"/>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A95" s="48" t="s">
         <v>334</v>
       </c>
@@ -20830,7 +20912,7 @@
       <c r="AC95" s="28"/>
       <c r="AD95" s="28"/>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A96" s="48" t="s">
         <v>336</v>
       </c>
@@ -20914,7 +20996,7 @@
       <c r="AC96" s="28"/>
       <c r="AD96" s="28"/>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A97" s="48" t="s">
         <v>338</v>
       </c>
@@ -20998,7 +21080,7 @@
       <c r="AC97" s="28"/>
       <c r="AD97" s="28"/>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A98" s="48" t="s">
         <v>340</v>
       </c>
@@ -21082,7 +21164,7 @@
       <c r="AC98" s="28"/>
       <c r="AD98" s="28"/>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A99" s="48" t="s">
         <v>342</v>
       </c>
@@ -21166,7 +21248,7 @@
       <c r="AC99" s="28"/>
       <c r="AD99" s="28"/>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A100" s="48" t="s">
         <v>344</v>
       </c>
@@ -21250,7 +21332,7 @@
       <c r="AC100" s="28"/>
       <c r="AD100" s="28"/>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A101" s="48" t="s">
         <v>597</v>
       </c>
@@ -21334,7 +21416,7 @@
       <c r="AC101" s="28"/>
       <c r="AD101" s="28"/>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A102" s="48" t="s">
         <v>348</v>
       </c>
@@ -21418,7 +21500,7 @@
       <c r="AC102" s="28"/>
       <c r="AD102" s="28"/>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A103" s="48" t="s">
         <v>352</v>
       </c>
@@ -21502,7 +21584,7 @@
       <c r="AC103" s="28"/>
       <c r="AD103" s="28"/>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A104" s="48" t="s">
         <v>355</v>
       </c>
@@ -21586,7 +21668,7 @@
       <c r="AC104" s="28"/>
       <c r="AD104" s="28"/>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A105" s="48" t="s">
         <v>358</v>
       </c>
@@ -21670,7 +21752,7 @@
       <c r="AC105" s="28"/>
       <c r="AD105" s="28"/>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A106" s="48" t="s">
         <v>361</v>
       </c>
@@ -21754,7 +21836,7 @@
       <c r="AC106" s="28"/>
       <c r="AD106" s="28"/>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A107" s="48" t="s">
         <v>364</v>
       </c>
@@ -21838,7 +21920,7 @@
       <c r="AC107" s="28"/>
       <c r="AD107" s="28"/>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A108" s="48" t="s">
         <v>367</v>
       </c>
@@ -21922,7 +22004,7 @@
       <c r="AC108" s="28"/>
       <c r="AD108" s="28"/>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A109" s="48" t="s">
         <v>369</v>
       </c>
@@ -22006,7 +22088,7 @@
       <c r="AC109" s="28"/>
       <c r="AD109" s="28"/>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A110" s="48" t="s">
         <v>371</v>
       </c>
@@ -22090,7 +22172,7 @@
       <c r="AC110" s="28"/>
       <c r="AD110" s="28"/>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A111" s="48" t="s">
         <v>598</v>
       </c>
@@ -22174,7 +22256,7 @@
       <c r="AC111" s="28"/>
       <c r="AD111" s="28"/>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A112" s="48" t="s">
         <v>690</v>
       </c>
@@ -22258,7 +22340,7 @@
       <c r="AC112" s="28"/>
       <c r="AD112" s="28"/>
     </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
         <v>693</v>
       </c>
@@ -22342,7 +22424,7 @@
       <c r="AC113" s="28"/>
       <c r="AD113" s="28"/>
     </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A114" s="48" t="s">
         <v>696</v>
       </c>
@@ -22426,7 +22508,7 @@
       <c r="AC114" s="28"/>
       <c r="AD114" s="28"/>
     </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A115" s="48" t="s">
         <v>699</v>
       </c>
@@ -22510,7 +22592,7 @@
       <c r="AC115" s="28"/>
       <c r="AD115" s="28"/>
     </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A116" s="48" t="s">
         <v>378</v>
       </c>
@@ -22594,7 +22676,7 @@
       <c r="AC116" s="28"/>
       <c r="AD116" s="28"/>
     </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A117" s="48" t="s">
         <v>383</v>
       </c>
@@ -22678,7 +22760,7 @@
       <c r="AC117" s="28"/>
       <c r="AD117" s="28"/>
     </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A118" s="48" t="s">
         <v>397</v>
       </c>
@@ -22762,7 +22844,7 @@
       <c r="AC118" s="28"/>
       <c r="AD118" s="28"/>
     </row>
-    <row r="119" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A119" s="48" t="s">
         <v>399</v>
       </c>
@@ -22846,7 +22928,7 @@
       <c r="AC119" s="28"/>
       <c r="AD119" s="28"/>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A120" s="48" t="s">
         <v>400</v>
       </c>
@@ -22930,7 +23012,7 @@
       <c r="AC120" s="28"/>
       <c r="AD120" s="28"/>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A121" s="48" t="s">
         <v>401</v>
       </c>
@@ -23014,7 +23096,7 @@
       <c r="AC121" s="28"/>
       <c r="AD121" s="28"/>
     </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A122" s="48" t="s">
         <v>402</v>
       </c>
@@ -23098,7 +23180,7 @@
       <c r="AC122" s="28"/>
       <c r="AD122" s="28"/>
     </row>
-    <row r="123" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A123" s="48" t="s">
         <v>403</v>
       </c>
@@ -23182,7 +23264,7 @@
       <c r="AC123" s="28"/>
       <c r="AD123" s="28"/>
     </row>
-    <row r="124" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A124" s="48" t="s">
         <v>405</v>
       </c>
@@ -23266,7 +23348,7 @@
       <c r="AC124" s="28"/>
       <c r="AD124" s="28"/>
     </row>
-    <row r="125" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A125" s="48" t="s">
         <v>407</v>
       </c>
@@ -23350,7 +23432,7 @@
       <c r="AC125" s="28"/>
       <c r="AD125" s="28"/>
     </row>
-    <row r="126" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:30" ht="27" x14ac:dyDescent="0.3">
       <c r="A126" s="62" t="s">
         <v>413</v>
       </c>
@@ -23434,7 +23516,7 @@
       <c r="AC126" s="28"/>
       <c r="AD126" s="28"/>
     </row>
-    <row r="127" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A127" s="48" t="s">
         <v>417</v>
       </c>
@@ -23518,7 +23600,7 @@
       <c r="AC127" s="28"/>
       <c r="AD127" s="28"/>
     </row>
-    <row r="128" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A128" s="48" t="s">
         <v>420</v>
       </c>
@@ -23602,7 +23684,7 @@
       <c r="AC128" s="28"/>
       <c r="AD128" s="28"/>
     </row>
-    <row r="129" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:30" ht="27" x14ac:dyDescent="0.3">
       <c r="A129" s="48" t="s">
         <v>422</v>
       </c>
@@ -23686,7 +23768,7 @@
       <c r="AC129" s="28"/>
       <c r="AD129" s="28"/>
     </row>
-    <row r="130" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:30" ht="27" x14ac:dyDescent="0.3">
       <c r="A130" s="48" t="s">
         <v>424</v>
       </c>
@@ -23770,7 +23852,7 @@
       <c r="AC130" s="28"/>
       <c r="AD130" s="28"/>
     </row>
-    <row r="131" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A131" s="48" t="s">
         <v>427</v>
       </c>
@@ -23854,7 +23936,7 @@
       <c r="AC131" s="28"/>
       <c r="AD131" s="28"/>
     </row>
-    <row r="132" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A132" s="48" t="s">
         <v>430</v>
       </c>
@@ -23938,7 +24020,7 @@
       <c r="AC132" s="28"/>
       <c r="AD132" s="28"/>
     </row>
-    <row r="133" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A133" s="48" t="s">
         <v>433</v>
       </c>
@@ -24022,7 +24104,7 @@
       <c r="AC133" s="28"/>
       <c r="AD133" s="28"/>
     </row>
-    <row r="134" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:30" ht="27" x14ac:dyDescent="0.3">
       <c r="A134" s="48" t="s">
         <v>436</v>
       </c>
@@ -24106,7 +24188,7 @@
       <c r="AC134" s="28"/>
       <c r="AD134" s="28"/>
     </row>
-    <row r="135" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A135" s="48" t="s">
         <v>438</v>
       </c>
@@ -24190,7 +24272,7 @@
       <c r="AC135" s="28"/>
       <c r="AD135" s="28"/>
     </row>
-    <row r="136" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A136" s="48" t="s">
         <v>703</v>
       </c>
@@ -24274,7 +24356,7 @@
       <c r="AC136" s="28"/>
       <c r="AD136" s="28"/>
     </row>
-    <row r="137" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A137" s="48" t="s">
         <v>397</v>
       </c>
@@ -24358,7 +24440,7 @@
       <c r="AC137" s="28"/>
       <c r="AD137" s="28"/>
     </row>
-    <row r="138" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A138" s="48" t="s">
         <v>399</v>
       </c>
@@ -24442,7 +24524,7 @@
       <c r="AC138" s="28"/>
       <c r="AD138" s="28"/>
     </row>
-    <row r="139" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A139" s="48" t="s">
         <v>400</v>
       </c>
@@ -24526,7 +24608,7 @@
       <c r="AC139" s="28"/>
       <c r="AD139" s="28"/>
     </row>
-    <row r="140" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
         <v>401</v>
       </c>
@@ -24610,7 +24692,7 @@
       <c r="AC140" s="28"/>
       <c r="AD140" s="28"/>
     </row>
-    <row r="141" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A141" s="48" t="s">
         <v>402</v>
       </c>
@@ -24694,7 +24776,7 @@
       <c r="AC141" s="28"/>
       <c r="AD141" s="28"/>
     </row>
-    <row r="142" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A142" s="48" t="s">
         <v>403</v>
       </c>
@@ -24778,7 +24860,7 @@
       <c r="AC142" s="28"/>
       <c r="AD142" s="28"/>
     </row>
-    <row r="143" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A143" s="48" t="s">
         <v>405</v>
       </c>
@@ -24862,7 +24944,7 @@
       <c r="AC143" s="28"/>
       <c r="AD143" s="28"/>
     </row>
-    <row r="144" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A144" s="48" t="s">
         <v>442</v>
       </c>
@@ -24946,7 +25028,7 @@
       <c r="AC144" s="28"/>
       <c r="AD144" s="28"/>
     </row>
-    <row r="145" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A145" s="48" t="s">
         <v>446</v>
       </c>
@@ -25030,7 +25112,7 @@
       <c r="AC145" s="28"/>
       <c r="AD145" s="28"/>
     </row>
-    <row r="146" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A146" s="48" t="s">
         <v>449</v>
       </c>
@@ -25114,7 +25196,7 @@
       <c r="AC146" s="28"/>
       <c r="AD146" s="28"/>
     </row>
-    <row r="147" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A147" s="48" t="s">
         <v>451</v>
       </c>
@@ -25198,7 +25280,7 @@
       <c r="AC147" s="28"/>
       <c r="AD147" s="28"/>
     </row>
-    <row r="148" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A148" s="48" t="s">
         <v>454</v>
       </c>
@@ -25282,7 +25364,7 @@
       <c r="AC148" s="28"/>
       <c r="AD148" s="28"/>
     </row>
-    <row r="149" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A149" s="48" t="s">
         <v>457</v>
       </c>
@@ -25366,7 +25448,7 @@
       <c r="AC149" s="28"/>
       <c r="AD149" s="28"/>
     </row>
-    <row r="150" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A150" s="48" t="s">
         <v>460</v>
       </c>
@@ -25450,7 +25532,7 @@
       <c r="AC150" s="28"/>
       <c r="AD150" s="28"/>
     </row>
-    <row r="151" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A151" s="48" t="s">
         <v>463</v>
       </c>
@@ -25534,7 +25616,7 @@
       <c r="AC151" s="28"/>
       <c r="AD151" s="28"/>
     </row>
-    <row r="152" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:30" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="48" t="s">
         <v>466</v>
       </c>
@@ -25618,7 +25700,7 @@
       <c r="AC152" s="28"/>
       <c r="AD152" s="28"/>
     </row>
-    <row r="153" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="48" t="s">
         <v>469</v>
       </c>
@@ -25702,7 +25784,7 @@
       <c r="AC153" s="28"/>
       <c r="AD153" s="28"/>
     </row>
-    <row r="154" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="48" t="s">
         <v>509</v>
       </c>
@@ -25786,7 +25868,7 @@
       <c r="AC154" s="28"/>
       <c r="AD154" s="28"/>
     </row>
-    <row r="155" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="66" t="s">
         <v>539</v>
       </c>
@@ -25870,7 +25952,7 @@
       <c r="AC155" s="28"/>
       <c r="AD155" s="28"/>
     </row>
-    <row r="156" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="70" t="s">
         <v>543</v>
       </c>
@@ -25954,7 +26036,7 @@
       <c r="AC156" s="28"/>
       <c r="AD156" s="28"/>
     </row>
-    <row r="157" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="66" t="s">
         <v>546</v>
       </c>
@@ -26038,7 +26120,7 @@
       <c r="AC157" s="28"/>
       <c r="AD157" s="28"/>
     </row>
-    <row r="158" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="70" t="s">
         <v>549</v>
       </c>
@@ -26122,7 +26204,7 @@
       <c r="AC158" s="28"/>
       <c r="AD158" s="28"/>
     </row>
-    <row r="159" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="66" t="s">
         <v>551</v>
       </c>
@@ -26206,7 +26288,7 @@
       <c r="AC159" s="28"/>
       <c r="AD159" s="28"/>
     </row>
-    <row r="160" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="70" t="s">
         <v>553</v>
       </c>
@@ -26290,7 +26372,7 @@
       <c r="AC160" s="28"/>
       <c r="AD160" s="28"/>
     </row>
-    <row r="161" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="66" t="s">
         <v>555</v>
       </c>
@@ -26374,7 +26456,7 @@
       <c r="AC161" s="28"/>
       <c r="AD161" s="28"/>
     </row>
-    <row r="162" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="70" t="s">
         <v>557</v>
       </c>
@@ -26458,7 +26540,7 @@
       <c r="AC162" s="28"/>
       <c r="AD162" s="28"/>
     </row>
-    <row r="163" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="66" t="s">
         <v>559</v>
       </c>
@@ -26542,7 +26624,7 @@
       <c r="AC163" s="28"/>
       <c r="AD163" s="28"/>
     </row>
-    <row r="164" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="70" t="s">
         <v>562</v>
       </c>
@@ -26626,7 +26708,7 @@
       <c r="AC164" s="28"/>
       <c r="AD164" s="28"/>
     </row>
-    <row r="165" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="66" t="s">
         <v>565</v>
       </c>
@@ -26710,7 +26792,7 @@
       <c r="AC165" s="28"/>
       <c r="AD165" s="28"/>
     </row>
-    <row r="166" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="70" t="s">
         <v>568</v>
       </c>
@@ -26794,7 +26876,7 @@
       <c r="AC166" s="28"/>
       <c r="AD166" s="28"/>
     </row>
-    <row r="167" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="66" t="s">
         <v>571</v>
       </c>
@@ -26878,7 +26960,7 @@
       <c r="AC167" s="28"/>
       <c r="AD167" s="28"/>
     </row>
-    <row r="168" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="70" t="s">
         <v>574</v>
       </c>
@@ -26962,7 +27044,7 @@
       <c r="AC168" s="28"/>
       <c r="AD168" s="28"/>
     </row>
-    <row r="169" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="66" t="s">
         <v>577</v>
       </c>
@@ -27046,7 +27128,7 @@
       <c r="AC169" s="28"/>
       <c r="AD169" s="28"/>
     </row>
-    <row r="170" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="66" t="s">
         <v>579</v>
       </c>
@@ -27130,7 +27212,7 @@
       <c r="AC170" s="28"/>
       <c r="AD170" s="28"/>
     </row>
-    <row r="171" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="66" t="s">
         <v>581</v>
       </c>
@@ -27214,7 +27296,7 @@
       <c r="AC171" s="28"/>
       <c r="AD171" s="28"/>
     </row>
-    <row r="172" spans="1:30" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="66" t="s">
         <v>584</v>
       </c>
@@ -27298,7 +27380,7 @@
       <c r="AC172" s="28"/>
       <c r="AD172" s="28"/>
     </row>
-    <row r="173" spans="1:30" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="76" t="s">
         <v>919</v>
       </c>
@@ -27382,7 +27464,7 @@
       <c r="AC173" s="28"/>
       <c r="AD173" s="28"/>
     </row>
-    <row r="174" spans="1:30" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="76" t="s">
         <v>922</v>
       </c>
@@ -27466,7 +27548,7 @@
       <c r="AC174" s="28"/>
       <c r="AD174" s="28"/>
     </row>
-    <row r="175" spans="1:30" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="76" t="s">
         <v>925</v>
       </c>
@@ -27550,7 +27632,7 @@
       <c r="AC175" s="48"/>
       <c r="AD175" s="48"/>
     </row>
-    <row r="176" spans="1:30" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:30" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="70" t="s">
         <v>601</v>
       </c>
@@ -27642,7 +27724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="177" spans="1:32" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="70" t="s">
         <v>604</v>
       </c>
@@ -27734,7 +27816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="178" spans="1:32" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="70" t="s">
         <v>606</v>
       </c>
@@ -27826,7 +27908,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:32" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="70" t="s">
         <v>607</v>
       </c>
@@ -27918,7 +28000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="180" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="70" t="s">
         <v>609</v>
       </c>
@@ -28010,7 +28092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:32" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="70" t="s">
         <v>610</v>
       </c>
@@ -28102,7 +28184,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="70" t="s">
         <v>611</v>
       </c>
@@ -28194,7 +28276,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="70" t="s">
         <v>615</v>
       </c>
@@ -28286,7 +28368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="184" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="70" t="s">
         <v>614</v>
       </c>
@@ -28378,7 +28460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="185" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="70" t="s">
         <v>619</v>
       </c>
@@ -28473,7 +28555,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="186" spans="1:32" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="70" t="s">
         <v>623</v>
       </c>
@@ -28568,7 +28650,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="187" spans="1:32" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="70" t="s">
         <v>629</v>
       </c>
@@ -28663,7 +28745,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="188" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="70" t="s">
         <v>630</v>
       </c>
@@ -28758,7 +28840,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="189" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="70" t="s">
         <v>636</v>
       </c>
@@ -28850,7 +28932,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="190" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="70" t="s">
         <v>849</v>
       </c>
@@ -28942,7 +29024,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="191" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="70" t="s">
         <v>850</v>
       </c>
@@ -29034,7 +29116,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="192" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="70" t="s">
         <v>640</v>
       </c>
@@ -29126,7 +29208,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="193" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="70" t="s">
         <v>642</v>
       </c>
@@ -29218,7 +29300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="70" t="s">
         <v>648</v>
       </c>
@@ -29310,7 +29392,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="70" t="s">
         <v>649</v>
       </c>
@@ -29402,7 +29484,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="70" t="s">
         <v>654</v>
       </c>
@@ -29494,7 +29576,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="197" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="70" t="s">
         <v>656</v>
       </c>
@@ -29586,7 +29668,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="70" t="s">
         <v>662</v>
       </c>
@@ -29678,7 +29760,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="199" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="70" t="s">
         <v>665</v>
       </c>
@@ -29770,7 +29852,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="200" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="70" t="s">
         <v>666</v>
       </c>
@@ -29862,7 +29944,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="201" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="70" t="s">
         <v>671</v>
       </c>
@@ -29954,7 +30036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="202" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="70" t="s">
         <v>676</v>
       </c>
@@ -30046,7 +30128,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="203" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="70" t="s">
         <v>677</v>
       </c>
@@ -30138,7 +30220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="204" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="70" t="s">
         <v>879</v>
       </c>
@@ -30230,7 +30312,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="205" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="70" t="s">
         <v>882</v>
       </c>
@@ -30322,7 +30404,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="206" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="70" t="s">
         <v>883</v>
       </c>
@@ -30414,7 +30496,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="207" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="70" t="s">
         <v>732</v>
       </c>
@@ -30506,7 +30588,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="208" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="70" t="s">
         <v>735</v>
       </c>
@@ -30598,7 +30680,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="209" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="70" t="s">
         <v>737</v>
       </c>
@@ -30690,7 +30772,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="70" t="s">
         <v>777</v>
       </c>
@@ -30782,7 +30864,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="211" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="70" t="s">
         <v>866</v>
       </c>
@@ -30874,7 +30956,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="212" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="70" t="s">
         <v>867</v>
       </c>
@@ -30966,7 +31048,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="213" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="70" t="s">
         <v>742</v>
       </c>
@@ -31058,7 +31140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="214" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="70" t="s">
         <v>748</v>
       </c>
@@ -31150,7 +31232,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="215" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="70" t="s">
         <v>749</v>
       </c>
@@ -31242,7 +31324,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="216" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="70" t="s">
         <v>754</v>
       </c>
@@ -31334,7 +31416,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="70" t="s">
         <v>755</v>
       </c>
@@ -31426,7 +31508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="218" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="70" t="s">
         <v>756</v>
       </c>
@@ -31518,7 +31600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="219" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="70" t="s">
         <v>761</v>
       </c>
@@ -31610,7 +31692,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="220" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="70" t="s">
         <v>764</v>
       </c>
@@ -31702,7 +31784,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="221" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="70" t="s">
         <v>769</v>
       </c>
@@ -31794,7 +31876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="222" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="70" t="s">
         <v>772</v>
       </c>
@@ -31886,7 +31968,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="223" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="70" t="s">
         <v>773</v>
       </c>
@@ -31978,7 +32060,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="224" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="70" t="s">
         <v>779</v>
       </c>
@@ -32070,7 +32152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="225" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="70" t="s">
         <v>791</v>
       </c>
@@ -32162,7 +32244,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="226" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="70" t="s">
         <v>796</v>
       </c>
@@ -32254,7 +32336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="227" spans="1:30" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:30" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="70" t="s">
         <v>801</v>
       </c>
@@ -32346,7 +32428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="228" spans="1:30" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:30" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="70" t="s">
         <v>803</v>
       </c>
@@ -32438,7 +32520,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="229" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="70" t="s">
         <v>805</v>
       </c>
@@ -32530,7 +32612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="70" t="s">
         <v>810</v>
       </c>
@@ -32622,7 +32704,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="231" spans="1:30" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:30" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="70" t="s">
         <v>812</v>
       </c>
@@ -32714,7 +32796,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="232" spans="1:30" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:30" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="70" t="s">
         <v>816</v>
       </c>
@@ -32806,7 +32888,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:30" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="70" t="s">
         <v>821</v>
       </c>
@@ -32898,7 +32980,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="70" t="s">
         <v>824</v>
       </c>
@@ -32990,7 +33072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="70" t="s">
         <v>825</v>
       </c>
@@ -33082,7 +33164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="70" t="s">
         <v>830</v>
       </c>
@@ -33174,7 +33256,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" spans="1:30" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="70" t="s">
         <v>928</v>
       </c>
@@ -33266,831 +33348,1015 @@
         <v>22</v>
       </c>
     </row>
-    <row r="238" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="70" t="s">
+        <v>930</v>
+      </c>
+      <c r="B238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S238" s="49" t="s">
+        <v>906</v>
+      </c>
+      <c r="T238" s="49" t="s">
+        <v>915</v>
+      </c>
+      <c r="U238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V238" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W238" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X238" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA238" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB238" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC238" s="73" t="s">
+        <v>831</v>
+      </c>
+      <c r="AD238" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="239" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A239" s="70" t="s">
+        <v>931</v>
+      </c>
+      <c r="B239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S239" s="49" t="s">
+        <v>906</v>
+      </c>
+      <c r="T239" s="49" t="s">
+        <v>908</v>
+      </c>
+      <c r="U239" s="49" t="s">
+        <v>915</v>
+      </c>
+      <c r="V239" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W239" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X239" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA239" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB239" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC239" s="73" t="s">
+        <v>831</v>
+      </c>
+      <c r="AD239" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="240" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A240" s="70" t="s">
         <v>870</v>
       </c>
-      <c r="B238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V238" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W238" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X238" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB238" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC238" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD238" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="239" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="70" t="s">
+      <c r="B240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V240" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W240" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X240" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB240" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC240" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD240" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="241" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A241" s="70" t="s">
         <v>874</v>
       </c>
-      <c r="B239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V239" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W239" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X239" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB239" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC239" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD239" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="240" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="70" t="s">
+      <c r="B241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V241" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W241" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X241" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB241" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC241" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD241" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="242" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A242" s="70" t="s">
         <v>840</v>
       </c>
-      <c r="B240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V240" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W240" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X240" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB240" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC240" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD240" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="241" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="70" t="s">
+      <c r="B242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V242" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W242" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X242" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB242" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC242" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD242" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="243" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A243" s="70" t="s">
         <v>844</v>
       </c>
-      <c r="B241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S241" s="49" t="s">
+      <c r="B243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S243" s="49" t="s">
         <v>906</v>
       </c>
-      <c r="T241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V241" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W241" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X241" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB241" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC241" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD241" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="242" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="70" t="s">
+      <c r="T243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V243" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W243" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X243" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB243" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC243" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD243" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="244" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="70" t="s">
         <v>846</v>
       </c>
-      <c r="B242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V242" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W242" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X242" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA242" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB242" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC242" s="73" t="s">
+      <c r="B244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V244" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W244" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X244" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA244" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB244" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC244" s="73" t="s">
         <v>831</v>
       </c>
-      <c r="AD242" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="243" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="70" t="s">
+      <c r="AD244" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="245" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A245" s="70" t="s">
         <v>859</v>
       </c>
-      <c r="B243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V243" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W243" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X243" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA243" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB243" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC243" s="73" t="s">
+      <c r="B245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V245" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W245" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X245" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA245" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB245" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC245" s="73" t="s">
         <v>860</v>
       </c>
-      <c r="AD243" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="244" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="70" t="s">
+      <c r="AD245" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="246" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="70" t="s">
         <v>861</v>
       </c>
-      <c r="B244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V244" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W244" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X244" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA244" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB244" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC244" s="73" t="s">
+      <c r="B246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V246" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W246" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X246" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA246" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB246" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC246" s="73" t="s">
         <v>860</v>
       </c>
-      <c r="AD244" s="48" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="245" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
+      <c r="AD246" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="247" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
         <v>887</v>
       </c>
-      <c r="B245" t="s">
-        <v>22</v>
-      </c>
-      <c r="C245" t="s">
-        <v>22</v>
-      </c>
-      <c r="D245" t="s">
-        <v>22</v>
-      </c>
-      <c r="E245" t="s">
-        <v>22</v>
-      </c>
-      <c r="F245" t="s">
-        <v>22</v>
-      </c>
-      <c r="G245" t="s">
-        <v>22</v>
-      </c>
-      <c r="H245" t="s">
-        <v>22</v>
-      </c>
-      <c r="I245" t="s">
-        <v>22</v>
-      </c>
-      <c r="J245" t="s">
-        <v>22</v>
-      </c>
-      <c r="K245" t="s">
-        <v>22</v>
-      </c>
-      <c r="L245" t="s">
-        <v>22</v>
-      </c>
-      <c r="M245" t="s">
-        <v>22</v>
-      </c>
-      <c r="N245" t="s">
-        <v>22</v>
-      </c>
-      <c r="O245" t="s">
-        <v>22</v>
-      </c>
-      <c r="P245" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q245" t="s">
-        <v>22</v>
-      </c>
-      <c r="R245" t="s">
-        <v>22</v>
-      </c>
-      <c r="S245" t="s">
+      <c r="B247" t="s">
+        <v>22</v>
+      </c>
+      <c r="C247" t="s">
+        <v>22</v>
+      </c>
+      <c r="D247" t="s">
+        <v>22</v>
+      </c>
+      <c r="E247" t="s">
+        <v>22</v>
+      </c>
+      <c r="F247" t="s">
+        <v>22</v>
+      </c>
+      <c r="G247" t="s">
+        <v>22</v>
+      </c>
+      <c r="H247" t="s">
+        <v>22</v>
+      </c>
+      <c r="I247" t="s">
+        <v>22</v>
+      </c>
+      <c r="J247" t="s">
+        <v>22</v>
+      </c>
+      <c r="K247" t="s">
+        <v>22</v>
+      </c>
+      <c r="L247" t="s">
+        <v>22</v>
+      </c>
+      <c r="M247" t="s">
+        <v>22</v>
+      </c>
+      <c r="N247" t="s">
+        <v>22</v>
+      </c>
+      <c r="O247" t="s">
+        <v>22</v>
+      </c>
+      <c r="P247" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>22</v>
+      </c>
+      <c r="R247" t="s">
+        <v>22</v>
+      </c>
+      <c r="S247" t="s">
         <v>896</v>
       </c>
-      <c r="T245" t="s">
-        <v>22</v>
-      </c>
-      <c r="U245" t="s">
-        <v>22</v>
-      </c>
-      <c r="V245" t="s">
-        <v>22</v>
-      </c>
-      <c r="W245" t="s">
-        <v>22</v>
-      </c>
-      <c r="X245" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y245" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z245" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA245" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB245" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC245" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD245" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="246" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
+      <c r="T247" t="s">
+        <v>22</v>
+      </c>
+      <c r="U247" t="s">
+        <v>22</v>
+      </c>
+      <c r="V247" t="s">
+        <v>22</v>
+      </c>
+      <c r="W247" t="s">
+        <v>22</v>
+      </c>
+      <c r="X247" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y247" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z247" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA247" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB247" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC247" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD247" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="248" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
         <v>894</v>
       </c>
-      <c r="B246" t="s">
-        <v>22</v>
-      </c>
-      <c r="C246" t="s">
-        <v>22</v>
-      </c>
-      <c r="D246" t="s">
-        <v>22</v>
-      </c>
-      <c r="E246" t="s">
-        <v>22</v>
-      </c>
-      <c r="F246" t="s">
-        <v>22</v>
-      </c>
-      <c r="G246" t="s">
-        <v>22</v>
-      </c>
-      <c r="H246" t="s">
-        <v>22</v>
-      </c>
-      <c r="I246" t="s">
-        <v>22</v>
-      </c>
-      <c r="J246" t="s">
-        <v>22</v>
-      </c>
-      <c r="K246" t="s">
-        <v>22</v>
-      </c>
-      <c r="L246" t="s">
-        <v>22</v>
-      </c>
-      <c r="M246" t="s">
-        <v>22</v>
-      </c>
-      <c r="N246" t="s">
-        <v>22</v>
-      </c>
-      <c r="O246" t="s">
-        <v>22</v>
-      </c>
-      <c r="P246" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q246" t="s">
-        <v>22</v>
-      </c>
-      <c r="R246" t="s">
-        <v>22</v>
-      </c>
-      <c r="S246" t="s">
+      <c r="B248" t="s">
+        <v>22</v>
+      </c>
+      <c r="C248" t="s">
+        <v>22</v>
+      </c>
+      <c r="D248" t="s">
+        <v>22</v>
+      </c>
+      <c r="E248" t="s">
+        <v>22</v>
+      </c>
+      <c r="F248" t="s">
+        <v>22</v>
+      </c>
+      <c r="G248" t="s">
+        <v>22</v>
+      </c>
+      <c r="H248" t="s">
+        <v>22</v>
+      </c>
+      <c r="I248" t="s">
+        <v>22</v>
+      </c>
+      <c r="J248" t="s">
+        <v>22</v>
+      </c>
+      <c r="K248" t="s">
+        <v>22</v>
+      </c>
+      <c r="L248" t="s">
+        <v>22</v>
+      </c>
+      <c r="M248" t="s">
+        <v>22</v>
+      </c>
+      <c r="N248" t="s">
+        <v>22</v>
+      </c>
+      <c r="O248" t="s">
+        <v>22</v>
+      </c>
+      <c r="P248" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>22</v>
+      </c>
+      <c r="R248" t="s">
+        <v>22</v>
+      </c>
+      <c r="S248" t="s">
         <v>896</v>
       </c>
-      <c r="T246" t="s">
-        <v>22</v>
-      </c>
-      <c r="U246" t="s">
-        <v>22</v>
-      </c>
-      <c r="V246" t="s">
-        <v>22</v>
-      </c>
-      <c r="W246" t="s">
-        <v>22</v>
-      </c>
-      <c r="X246" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y246" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z246" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA246" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB246" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC246" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD246" t="s">
+      <c r="T248" t="s">
+        <v>22</v>
+      </c>
+      <c r="U248" t="s">
+        <v>22</v>
+      </c>
+      <c r="V248" t="s">
+        <v>22</v>
+      </c>
+      <c r="W248" t="s">
+        <v>22</v>
+      </c>
+      <c r="X248" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y248" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z248" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA248" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB248" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC248" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD248" t="s">
         <v>22</v>
       </c>
     </row>
@@ -34249,23 +34515,27 @@
     <hyperlink ref="AC177" r:id="rId46" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{7BE8FE18-5C75-431B-8488-FBDEF16485E5}"/>
     <hyperlink ref="AC178" r:id="rId47" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{FF640DAE-0F42-4B2A-A086-F1C73287AD75}"/>
     <hyperlink ref="AC181" r:id="rId48" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{B625AA61-E1E0-4964-9CDD-901824C6555F}"/>
-    <hyperlink ref="AC242" r:id="rId49" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
+    <hyperlink ref="AC244" r:id="rId49" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
     <hyperlink ref="T211" r:id="rId50" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
     <hyperlink ref="T212" r:id="rId51" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
     <hyperlink ref="S199" r:id="rId52" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
     <hyperlink ref="AC225" r:id="rId53" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{CD96CCCF-BE60-40A1-BA2F-93729430B99A}"/>
-    <hyperlink ref="AC226:AC237" r:id="rId54" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
+    <hyperlink ref="AC226:AC239" r:id="rId54" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
     <hyperlink ref="S219" r:id="rId55" display="https://qa.zlta.testingserver8.com/admin/payment-pending" xr:uid="{37E5E50E-434D-4FC0-B9A6-C0648E88FF97}"/>
     <hyperlink ref="S206" r:id="rId56" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
     <hyperlink ref="S204" r:id="rId57" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
     <hyperlink ref="S205" r:id="rId58" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
     <hyperlink ref="S196" r:id="rId59" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
-    <hyperlink ref="S241" r:id="rId60" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
+    <hyperlink ref="S243" r:id="rId60" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
     <hyperlink ref="T236" r:id="rId61" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
     <hyperlink ref="S226" r:id="rId62" display="https://console.zlaata.com/admin/cancel-order" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
-    <hyperlink ref="S237" r:id="rId63" xr:uid="{34D22F7E-DB9E-4075-BA35-4715BDF656B0}"/>
+    <hyperlink ref="AC237" r:id="rId63" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{B5FFBFD3-2AEB-43E2-A088-AA986500C94C}"/>
+    <hyperlink ref="S237" r:id="rId64" xr:uid="{E29AE273-A13B-4FDA-99DA-66C3FC3DF993}"/>
+    <hyperlink ref="S239" r:id="rId65" xr:uid="{E5A47A78-2C35-4A72-A585-72E3D18CC556}"/>
+    <hyperlink ref="AC238" r:id="rId66" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{A40E89D1-5252-43A0-AF9C-1AAAC503CE8E}"/>
+    <hyperlink ref="S238" r:id="rId67" xr:uid="{EFD712A1-7827-446F-B5F1-9CC652078EB0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId64"/>
+  <pageSetup orientation="portrait" r:id="rId68"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever33\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E36DF9F-D7F0-46FC-A476-9C8DD4D9A55E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D79C80-E0A1-4515-AC74-AECCA4B449D7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -2713,72 +2713,6 @@
     <t>TD_UI_Zlaata_ATL_02</t>
   </si>
   <si>
-    <t>https://qa.adm.testingserver8.com/admin/home-page-banner</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/product</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/special-timer-event</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/categories</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/product-collection</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/product-style</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/product-search-keyword</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/collection-search-keyword</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/style-search-keyword</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/track-inventory</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/coupon</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/order</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/return-order</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/exchange-order</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/cancel-order</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/return-cancel</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/exchange-cancel</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/payment-pending</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/payment-refund</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/payment-failed</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/rto-orders</t>
-  </si>
-  <si>
-    <t>https://qa.adm.testingserver8.com/admin/all-orders</t>
-  </si>
-  <si>
     <t>TC_UI_Zlaata_CP_19</t>
   </si>
   <si>
@@ -2815,9 +2749,6 @@
     <t>TD_UI_Admin_OEV_13</t>
   </si>
   <si>
-    <t>https://qa.adm.testingserver8.com/admin/subscriber</t>
-  </si>
-  <si>
     <t>TD_UI_Admin_OEV_14</t>
   </si>
   <si>
@@ -2834,6 +2765,75 @@
   </si>
   <si>
     <t>Verify the RTO Order Flow for an exchange order before delivered.</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/cancel-order</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/home-page-banner</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/product</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/special-timer-event</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/categories</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/product-collection</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/product-style</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/product-search-keyword</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/collection-search-keyword</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/style-search-keyword</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/track-inventory</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/coupon</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/order</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/return-order</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/exchange-order</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/return-cancel</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/exchange-cancel</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/payment-pending</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/payment-refund</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/payment-failed</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/rto-orders</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/all-orders</t>
+  </si>
+  <si>
+    <t>https://console.zlaata.com/admin/subscriber</t>
   </si>
 </sst>
 </file>
@@ -3493,24 +3493,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3537,6 +3519,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5091,18 +5091,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="97" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="99"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -5489,18 +5489,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="91" t="s">
+      <c r="A37" s="100" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="92"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="93"/>
+      <c r="B37" s="101"/>
+      <c r="C37" s="101"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="101"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="102"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -6047,18 +6047,18 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="91" t="s">
+      <c r="A55" s="100" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="92"/>
-      <c r="C55" s="92"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="92"/>
-      <c r="F55" s="92"/>
-      <c r="G55" s="92"/>
-      <c r="H55" s="92"/>
-      <c r="I55" s="92"/>
-      <c r="J55" s="93"/>
+      <c r="B55" s="101"/>
+      <c r="C55" s="101"/>
+      <c r="D55" s="101"/>
+      <c r="E55" s="101"/>
+      <c r="F55" s="101"/>
+      <c r="G55" s="101"/>
+      <c r="H55" s="101"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="102"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
@@ -6381,18 +6381,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="91" t="s">
+      <c r="A66" s="100" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="92"/>
-      <c r="C66" s="92"/>
-      <c r="D66" s="92"/>
-      <c r="E66" s="92"/>
-      <c r="F66" s="92"/>
-      <c r="G66" s="92"/>
-      <c r="H66" s="92"/>
-      <c r="I66" s="92"/>
-      <c r="J66" s="93"/>
+      <c r="B66" s="101"/>
+      <c r="C66" s="101"/>
+      <c r="D66" s="101"/>
+      <c r="E66" s="101"/>
+      <c r="F66" s="101"/>
+      <c r="G66" s="101"/>
+      <c r="H66" s="101"/>
+      <c r="I66" s="101"/>
+      <c r="J66" s="102"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
@@ -6747,18 +6747,18 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="91" t="s">
+      <c r="A78" s="100" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="92"/>
-      <c r="C78" s="92"/>
-      <c r="D78" s="92"/>
-      <c r="E78" s="92"/>
-      <c r="F78" s="92"/>
-      <c r="G78" s="92"/>
-      <c r="H78" s="92"/>
-      <c r="I78" s="92"/>
-      <c r="J78" s="93"/>
+      <c r="B78" s="101"/>
+      <c r="C78" s="101"/>
+      <c r="D78" s="101"/>
+      <c r="E78" s="101"/>
+      <c r="F78" s="101"/>
+      <c r="G78" s="101"/>
+      <c r="H78" s="101"/>
+      <c r="I78" s="101"/>
+      <c r="J78" s="102"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
@@ -7625,18 +7625,18 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="94" t="s">
+      <c r="A106" s="88" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="94"/>
-      <c r="C106" s="94"/>
-      <c r="D106" s="94"/>
-      <c r="E106" s="94"/>
-      <c r="F106" s="94"/>
-      <c r="G106" s="94"/>
-      <c r="H106" s="94"/>
-      <c r="I106" s="94"/>
-      <c r="J106" s="94"/>
+      <c r="B106" s="88"/>
+      <c r="C106" s="88"/>
+      <c r="D106" s="88"/>
+      <c r="E106" s="88"/>
+      <c r="F106" s="88"/>
+      <c r="G106" s="88"/>
+      <c r="H106" s="88"/>
+      <c r="I106" s="88"/>
+      <c r="J106" s="88"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -8129,18 +8129,18 @@
       <c r="X120" s="58"/>
     </row>
     <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="95" t="s">
+      <c r="A121" s="89" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="95"/>
-      <c r="C121" s="95"/>
-      <c r="D121" s="95"/>
-      <c r="E121" s="95"/>
-      <c r="F121" s="95"/>
-      <c r="G121" s="95"/>
-      <c r="H121" s="95"/>
-      <c r="I121" s="95"/>
-      <c r="J121" s="95"/>
+      <c r="B121" s="89"/>
+      <c r="C121" s="89"/>
+      <c r="D121" s="89"/>
+      <c r="E121" s="89"/>
+      <c r="F121" s="89"/>
+      <c r="G121" s="89"/>
+      <c r="H121" s="89"/>
+      <c r="I121" s="89"/>
+      <c r="J121" s="89"/>
       <c r="K121" s="57"/>
       <c r="L121" s="58"/>
       <c r="M121" s="58"/>
@@ -8203,18 +8203,18 @@
       <c r="X122" s="58"/>
     </row>
     <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="95" t="s">
+      <c r="A123" s="89" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="95"/>
-      <c r="C123" s="95"/>
-      <c r="D123" s="95"/>
-      <c r="E123" s="95"/>
-      <c r="F123" s="95"/>
-      <c r="G123" s="95"/>
-      <c r="H123" s="95"/>
-      <c r="I123" s="95"/>
-      <c r="J123" s="95"/>
+      <c r="B123" s="89"/>
+      <c r="C123" s="89"/>
+      <c r="D123" s="89"/>
+      <c r="E123" s="89"/>
+      <c r="F123" s="89"/>
+      <c r="G123" s="89"/>
+      <c r="H123" s="89"/>
+      <c r="I123" s="89"/>
+      <c r="J123" s="89"/>
       <c r="K123" s="57"/>
       <c r="L123" s="58"/>
       <c r="M123" s="58"/>
@@ -8277,18 +8277,18 @@
       <c r="X124" s="58"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="95" t="s">
+      <c r="A125" s="89" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="95"/>
-      <c r="C125" s="95"/>
-      <c r="D125" s="95"/>
-      <c r="E125" s="95"/>
-      <c r="F125" s="95"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="95"/>
-      <c r="I125" s="95"/>
-      <c r="J125" s="95"/>
+      <c r="B125" s="89"/>
+      <c r="C125" s="89"/>
+      <c r="D125" s="89"/>
+      <c r="E125" s="89"/>
+      <c r="F125" s="89"/>
+      <c r="G125" s="89"/>
+      <c r="H125" s="89"/>
+      <c r="I125" s="89"/>
+      <c r="J125" s="89"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -8613,18 +8613,18 @@
       <c r="X132" s="58"/>
     </row>
     <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="95" t="s">
+      <c r="A133" s="89" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="95"/>
-      <c r="C133" s="95"/>
-      <c r="D133" s="96"/>
-      <c r="E133" s="96"/>
-      <c r="F133" s="96"/>
-      <c r="G133" s="96"/>
-      <c r="H133" s="96"/>
-      <c r="I133" s="96"/>
-      <c r="J133" s="96"/>
+      <c r="B133" s="89"/>
+      <c r="C133" s="89"/>
+      <c r="D133" s="90"/>
+      <c r="E133" s="90"/>
+      <c r="F133" s="90"/>
+      <c r="G133" s="90"/>
+      <c r="H133" s="90"/>
+      <c r="I133" s="90"/>
+      <c r="J133" s="90"/>
       <c r="K133" s="58"/>
       <c r="L133" s="58"/>
       <c r="M133" s="58"/>
@@ -9119,18 +9119,18 @@
       <c r="X144" s="58"/>
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="100" t="s">
+      <c r="A145" s="94" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="101"/>
-      <c r="C145" s="101"/>
-      <c r="D145" s="101"/>
-      <c r="E145" s="101"/>
-      <c r="F145" s="101"/>
-      <c r="G145" s="101"/>
-      <c r="H145" s="101"/>
-      <c r="I145" s="101"/>
-      <c r="J145" s="102"/>
+      <c r="B145" s="95"/>
+      <c r="C145" s="95"/>
+      <c r="D145" s="95"/>
+      <c r="E145" s="95"/>
+      <c r="F145" s="95"/>
+      <c r="G145" s="95"/>
+      <c r="H145" s="95"/>
+      <c r="I145" s="95"/>
+      <c r="J145" s="96"/>
       <c r="K145" s="58"/>
       <c r="L145" s="58"/>
       <c r="M145" s="58"/>
@@ -9577,18 +9577,18 @@
       <c r="Z155" s="58"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="95" t="s">
+      <c r="A156" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="95"/>
-      <c r="C156" s="95"/>
-      <c r="D156" s="95"/>
-      <c r="E156" s="95"/>
-      <c r="F156" s="95"/>
-      <c r="G156" s="95"/>
-      <c r="H156" s="95"/>
-      <c r="I156" s="95"/>
-      <c r="J156" s="95"/>
+      <c r="B156" s="89"/>
+      <c r="C156" s="89"/>
+      <c r="D156" s="89"/>
+      <c r="E156" s="89"/>
+      <c r="F156" s="89"/>
+      <c r="G156" s="89"/>
+      <c r="H156" s="89"/>
+      <c r="I156" s="89"/>
+      <c r="J156" s="89"/>
       <c r="K156" s="58"/>
       <c r="L156" s="58"/>
       <c r="M156" s="58"/>
@@ -9655,18 +9655,18 @@
       <c r="Z157" s="58"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="95" t="s">
+      <c r="A158" s="89" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="95"/>
-      <c r="C158" s="95"/>
-      <c r="D158" s="95"/>
-      <c r="E158" s="95"/>
-      <c r="F158" s="95"/>
-      <c r="G158" s="95"/>
-      <c r="H158" s="95"/>
-      <c r="I158" s="95"/>
-      <c r="J158" s="95"/>
+      <c r="B158" s="89"/>
+      <c r="C158" s="89"/>
+      <c r="D158" s="89"/>
+      <c r="E158" s="89"/>
+      <c r="F158" s="89"/>
+      <c r="G158" s="89"/>
+      <c r="H158" s="89"/>
+      <c r="I158" s="89"/>
+      <c r="J158" s="89"/>
       <c r="K158" s="58"/>
       <c r="L158" s="58"/>
       <c r="M158" s="58"/>
@@ -10412,16 +10412,16 @@
         <v>10</v>
       </c>
       <c r="C177" s="70" t="s">
-        <v>917</v>
+        <v>895</v>
       </c>
       <c r="D177" s="71" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="E177" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F177" s="70" t="s">
-        <v>919</v>
+        <v>897</v>
       </c>
       <c r="G177" s="69" t="s">
         <v>11</v>
@@ -10444,16 +10444,16 @@
         <v>10</v>
       </c>
       <c r="C178" s="70" t="s">
-        <v>920</v>
+        <v>898</v>
       </c>
       <c r="D178" s="71" t="s">
-        <v>921</v>
+        <v>899</v>
       </c>
       <c r="E178" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F178" s="70" t="s">
-        <v>922</v>
+        <v>900</v>
       </c>
       <c r="G178" s="69" t="s">
         <v>11</v>
@@ -10476,16 +10476,16 @@
         <v>10</v>
       </c>
       <c r="C179" s="70" t="s">
-        <v>923</v>
+        <v>901</v>
       </c>
       <c r="D179" s="71" t="s">
-        <v>924</v>
+        <v>902</v>
       </c>
       <c r="E179" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F179" s="70" t="s">
-        <v>925</v>
+        <v>903</v>
       </c>
       <c r="G179" s="69" t="s">
         <v>11</v>
@@ -10501,18 +10501,18 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="95" t="s">
+      <c r="A180" s="89" t="s">
         <v>715</v>
       </c>
-      <c r="B180" s="95"/>
-      <c r="C180" s="95"/>
+      <c r="B180" s="89"/>
+      <c r="C180" s="89"/>
       <c r="D180" s="87"/>
-      <c r="E180" s="95"/>
-      <c r="F180" s="95"/>
-      <c r="G180" s="95"/>
-      <c r="H180" s="95"/>
-      <c r="I180" s="95"/>
-      <c r="J180" s="95"/>
+      <c r="E180" s="89"/>
+      <c r="F180" s="89"/>
+      <c r="G180" s="89"/>
+      <c r="H180" s="89"/>
+      <c r="I180" s="89"/>
+      <c r="J180" s="89"/>
     </row>
     <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="68">
@@ -10803,18 +10803,18 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="97" t="s">
+      <c r="A190" s="91" t="s">
         <v>617</v>
       </c>
-      <c r="B190" s="98"/>
-      <c r="C190" s="98"/>
-      <c r="D190" s="98"/>
-      <c r="E190" s="98"/>
-      <c r="F190" s="98"/>
-      <c r="G190" s="98"/>
-      <c r="H190" s="98"/>
-      <c r="I190" s="98"/>
-      <c r="J190" s="99"/>
+      <c r="B190" s="92"/>
+      <c r="C190" s="92"/>
+      <c r="D190" s="92"/>
+      <c r="E190" s="92"/>
+      <c r="F190" s="92"/>
+      <c r="G190" s="92"/>
+      <c r="H190" s="92"/>
+      <c r="I190" s="92"/>
+      <c r="J190" s="93"/>
     </row>
     <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="68">
@@ -12646,16 +12646,16 @@
         <v>10</v>
       </c>
       <c r="C253" s="79" t="s">
-        <v>926</v>
+        <v>904</v>
       </c>
       <c r="D253" s="78" t="s">
-        <v>927</v>
+        <v>905</v>
       </c>
       <c r="E253" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F253" s="79" t="s">
-        <v>928</v>
+        <v>906</v>
       </c>
       <c r="G253" s="48" t="s">
         <v>11</v>
@@ -12678,16 +12678,16 @@
         <v>10</v>
       </c>
       <c r="C254" s="79" t="s">
-        <v>932</v>
+        <v>909</v>
       </c>
       <c r="D254" s="78" t="s">
-        <v>933</v>
+        <v>910</v>
       </c>
       <c r="E254" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F254" s="79" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="G254" s="48" t="s">
         <v>11</v>
@@ -12710,16 +12710,16 @@
         <v>10</v>
       </c>
       <c r="C255" s="79" t="s">
-        <v>934</v>
+        <v>911</v>
       </c>
       <c r="D255" s="78" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="E255" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F255" s="79" t="s">
-        <v>931</v>
+        <v>908</v>
       </c>
       <c r="G255" s="48" t="s">
         <v>11</v>
@@ -12988,6 +12988,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
     <mergeCell ref="A259:J259"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
@@ -13004,14 +13012,6 @@
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
     <mergeCell ref="A238:J238"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -27382,7 +27382,7 @@
     </row>
     <row r="173" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="76" t="s">
-        <v>919</v>
+        <v>897</v>
       </c>
       <c r="B173" s="48" t="s">
         <v>22</v>
@@ -27436,7 +27436,7 @@
         <v>22</v>
       </c>
       <c r="S173" s="48" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="T173" s="48" t="s">
         <v>22</v>
@@ -27466,7 +27466,7 @@
     </row>
     <row r="174" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="76" t="s">
-        <v>922</v>
+        <v>900</v>
       </c>
       <c r="B174" s="48" t="s">
         <v>22</v>
@@ -27520,7 +27520,7 @@
         <v>22</v>
       </c>
       <c r="S174" s="48" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="T174" s="48" t="s">
         <v>22</v>
@@ -27550,7 +27550,7 @@
     </row>
     <row r="175" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="76" t="s">
-        <v>925</v>
+        <v>903</v>
       </c>
       <c r="B175" s="48" t="s">
         <v>22</v>
@@ -27604,7 +27604,7 @@
         <v>22</v>
       </c>
       <c r="S175" s="48" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="T175" s="48" t="s">
         <v>22</v>
@@ -27688,7 +27688,7 @@
         <v>22</v>
       </c>
       <c r="S176" s="49" t="s">
-        <v>895</v>
+        <v>914</v>
       </c>
       <c r="T176" s="48" t="s">
         <v>22</v>
@@ -27780,7 +27780,7 @@
         <v>22</v>
       </c>
       <c r="S177" s="49" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T177" s="48" t="s">
         <v>22</v>
@@ -27872,7 +27872,7 @@
         <v>22</v>
       </c>
       <c r="S178" s="49" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T178" s="48" t="s">
         <v>22</v>
@@ -27964,7 +27964,7 @@
         <v>22</v>
       </c>
       <c r="S179" s="49" t="s">
-        <v>895</v>
+        <v>914</v>
       </c>
       <c r="T179" s="48" t="s">
         <v>22</v>
@@ -28056,7 +28056,7 @@
         <v>22</v>
       </c>
       <c r="S180" s="49" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T180" s="48" t="s">
         <v>22</v>
@@ -28148,7 +28148,7 @@
         <v>22</v>
       </c>
       <c r="S181" s="49" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T181" s="48" t="s">
         <v>22</v>
@@ -28240,7 +28240,7 @@
         <v>22</v>
       </c>
       <c r="S182" s="49" t="s">
-        <v>897</v>
+        <v>916</v>
       </c>
       <c r="T182" s="48" t="s">
         <v>22</v>
@@ -28332,7 +28332,7 @@
         <v>22</v>
       </c>
       <c r="S183" s="49" t="s">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="T183" s="48" t="s">
         <v>22</v>
@@ -28424,7 +28424,7 @@
         <v>22</v>
       </c>
       <c r="S184" s="49" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="T184" s="48" t="s">
         <v>22</v>
@@ -28516,7 +28516,7 @@
         <v>22</v>
       </c>
       <c r="S185" s="49" t="s">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="T185" s="48" t="s">
         <v>22</v>
@@ -28611,7 +28611,7 @@
         <v>22</v>
       </c>
       <c r="S186" s="49" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="T186" s="48" t="s">
         <v>22</v>
@@ -29540,7 +29540,7 @@
         <v>22</v>
       </c>
       <c r="S196" s="49" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T196" s="48" t="s">
         <v>22</v>
@@ -29632,7 +29632,7 @@
         <v>22</v>
       </c>
       <c r="S197" s="49" t="s">
-        <v>898</v>
+        <v>917</v>
       </c>
       <c r="T197" s="48" t="s">
         <v>22</v>
@@ -29724,7 +29724,7 @@
         <v>22</v>
       </c>
       <c r="S198" s="49" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
       <c r="T198" s="48" t="s">
         <v>22</v>
@@ -29816,7 +29816,7 @@
         <v>22</v>
       </c>
       <c r="S199" s="49" t="s">
-        <v>900</v>
+        <v>919</v>
       </c>
       <c r="T199" s="48" t="s">
         <v>22</v>
@@ -29908,7 +29908,7 @@
         <v>22</v>
       </c>
       <c r="S200" s="49" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T200" s="48" t="s">
         <v>22</v>
@@ -30000,7 +30000,7 @@
         <v>22</v>
       </c>
       <c r="S201" s="49" t="s">
-        <v>901</v>
+        <v>920</v>
       </c>
       <c r="T201" s="48" t="s">
         <v>22</v>
@@ -30092,7 +30092,7 @@
         <v>22</v>
       </c>
       <c r="S202" s="49" t="s">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="T202" s="48" t="s">
         <v>22</v>
@@ -30184,7 +30184,7 @@
         <v>22</v>
       </c>
       <c r="S203" s="49" t="s">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="T203" s="48" t="s">
         <v>22</v>
@@ -30276,7 +30276,7 @@
         <v>22</v>
       </c>
       <c r="S204" s="49" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="T204" s="48" t="s">
         <v>22</v>
@@ -30368,7 +30368,7 @@
         <v>22</v>
       </c>
       <c r="S205" s="49" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="T205" s="48" t="s">
         <v>22</v>
@@ -30460,7 +30460,7 @@
         <v>22</v>
       </c>
       <c r="S206" s="49" t="s">
-        <v>904</v>
+        <v>923</v>
       </c>
       <c r="T206" s="48" t="s">
         <v>22</v>
@@ -30552,7 +30552,7 @@
         <v>22</v>
       </c>
       <c r="S207" s="49" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T207" s="48" t="s">
         <v>22</v>
@@ -30644,7 +30644,7 @@
         <v>22</v>
       </c>
       <c r="S208" s="49" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="T208" s="48" t="s">
         <v>22</v>
@@ -30736,7 +30736,7 @@
         <v>22</v>
       </c>
       <c r="S209" s="49" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="T209" s="48" t="s">
         <v>22</v>
@@ -30828,7 +30828,7 @@
         <v>22</v>
       </c>
       <c r="S210" s="49" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="T210" s="48" t="s">
         <v>22</v>
@@ -30920,10 +30920,10 @@
         <v>22</v>
       </c>
       <c r="S211" s="49" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="T211" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="U211" s="48" t="s">
         <v>22</v>
@@ -31012,10 +31012,10 @@
         <v>22</v>
       </c>
       <c r="S212" s="49" t="s">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="T212" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="U212" s="48" t="s">
         <v>22</v>
@@ -31104,7 +31104,7 @@
         <v>22</v>
       </c>
       <c r="S213" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T213" s="48" t="s">
         <v>22</v>
@@ -31196,7 +31196,7 @@
         <v>22</v>
       </c>
       <c r="S214" s="49" t="s">
-        <v>907</v>
+        <v>926</v>
       </c>
       <c r="T214" s="48" t="s">
         <v>22</v>
@@ -31288,7 +31288,7 @@
         <v>22</v>
       </c>
       <c r="S215" s="49" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="T215" s="48" t="s">
         <v>22</v>
@@ -31380,7 +31380,7 @@
         <v>22</v>
       </c>
       <c r="S216" s="49" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="T216" s="48" t="s">
         <v>22</v>
@@ -31472,7 +31472,7 @@
         <v>22</v>
       </c>
       <c r="S217" s="49" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="T217" s="48" t="s">
         <v>22</v>
@@ -31564,7 +31564,7 @@
         <v>22</v>
       </c>
       <c r="S218" s="49" t="s">
-        <v>911</v>
+        <v>929</v>
       </c>
       <c r="T218" s="48" t="s">
         <v>22</v>
@@ -31656,7 +31656,7 @@
         <v>22</v>
       </c>
       <c r="S219" s="49" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
       <c r="T219" s="48" t="s">
         <v>22</v>
@@ -31748,7 +31748,7 @@
         <v>22</v>
       </c>
       <c r="S220" s="49" t="s">
-        <v>913</v>
+        <v>931</v>
       </c>
       <c r="T220" s="48" t="s">
         <v>22</v>
@@ -31840,7 +31840,7 @@
         <v>22</v>
       </c>
       <c r="S221" s="49" t="s">
-        <v>914</v>
+        <v>932</v>
       </c>
       <c r="T221" s="48" t="s">
         <v>22</v>
@@ -31932,7 +31932,7 @@
         <v>22</v>
       </c>
       <c r="S222" s="49" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
       <c r="T222" s="48" t="s">
         <v>22</v>
@@ -32024,7 +32024,7 @@
         <v>22</v>
       </c>
       <c r="S223" s="49" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="T223" s="48" t="s">
         <v>22</v>
@@ -32116,7 +32116,7 @@
         <v>22</v>
       </c>
       <c r="S224" s="49" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T224" s="48" t="s">
         <v>22</v>
@@ -32208,7 +32208,7 @@
         <v>22</v>
       </c>
       <c r="S225" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T225" s="48" t="s">
         <v>22</v>
@@ -32300,7 +32300,7 @@
         <v>22</v>
       </c>
       <c r="S226" s="49" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="T226" s="48" t="s">
         <v>22</v>
@@ -32392,10 +32392,10 @@
         <v>22</v>
       </c>
       <c r="S227" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T227" s="49" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="U227" s="48" t="s">
         <v>22</v>
@@ -32484,10 +32484,10 @@
         <v>22</v>
       </c>
       <c r="S228" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T228" s="49" t="s">
-        <v>907</v>
+        <v>926</v>
       </c>
       <c r="U228" s="48" t="s">
         <v>22</v>
@@ -32576,10 +32576,10 @@
         <v>22</v>
       </c>
       <c r="S229" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T229" s="48" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="U229" s="48" t="s">
         <v>22</v>
@@ -32668,7 +32668,7 @@
         <v>22</v>
       </c>
       <c r="S230" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T230" s="48" t="s">
         <v>22</v>
@@ -32760,10 +32760,10 @@
         <v>22</v>
       </c>
       <c r="S231" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T231" s="49" t="s">
-        <v>907</v>
+        <v>926</v>
       </c>
       <c r="U231" s="48" t="s">
         <v>22</v>
@@ -32852,10 +32852,10 @@
         <v>22</v>
       </c>
       <c r="S232" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T232" s="49" t="s">
-        <v>907</v>
+        <v>926</v>
       </c>
       <c r="U232" s="48" t="s">
         <v>22</v>
@@ -32944,7 +32944,7 @@
         <v>22</v>
       </c>
       <c r="S233" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T233" s="48" t="s">
         <v>22</v>
@@ -33036,10 +33036,10 @@
         <v>22</v>
       </c>
       <c r="S234" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T234" s="49" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="U234" s="48" t="s">
         <v>22</v>
@@ -33128,10 +33128,10 @@
         <v>22</v>
       </c>
       <c r="S235" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T235" s="49" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="U235" s="48" t="s">
         <v>22</v>
@@ -33220,10 +33220,10 @@
         <v>22</v>
       </c>
       <c r="S236" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T236" s="49" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="U236" s="48" t="s">
         <v>22</v>
@@ -33258,7 +33258,7 @@
     </row>
     <row r="237" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="70" t="s">
-        <v>928</v>
+        <v>906</v>
       </c>
       <c r="B237" s="48" t="s">
         <v>22</v>
@@ -33312,10 +33312,10 @@
         <v>22</v>
       </c>
       <c r="S237" s="49" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="T237" s="49" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="U237" s="48" t="s">
         <v>22</v>
@@ -33350,7 +33350,7 @@
     </row>
     <row r="238" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="70" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="B238" s="48" t="s">
         <v>22</v>
@@ -33404,10 +33404,10 @@
         <v>22</v>
       </c>
       <c r="S238" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T238" s="49" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
       <c r="U238" s="48" t="s">
         <v>22</v>
@@ -33442,7 +33442,7 @@
     </row>
     <row r="239" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="70" t="s">
-        <v>931</v>
+        <v>908</v>
       </c>
       <c r="B239" s="48" t="s">
         <v>22</v>
@@ -33496,13 +33496,13 @@
         <v>22</v>
       </c>
       <c r="S239" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T239" s="49" t="s">
-        <v>908</v>
+        <v>927</v>
       </c>
       <c r="U239" s="49" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
       <c r="V239" s="28" t="s">
         <v>22</v>
@@ -33864,7 +33864,7 @@
         <v>22</v>
       </c>
       <c r="S243" s="49" t="s">
-        <v>906</v>
+        <v>925</v>
       </c>
       <c r="T243" s="48" t="s">
         <v>22</v>
@@ -34232,7 +34232,7 @@
         <v>22</v>
       </c>
       <c r="S247" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T247" t="s">
         <v>22</v>
@@ -34324,7 +34324,7 @@
         <v>22</v>
       </c>
       <c r="S248" t="s">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="T248" t="s">
         <v>22</v>
@@ -34485,8 +34485,8 @@
     <hyperlink ref="D142" r:id="rId16" xr:uid="{8898BD8E-2CA4-4CDE-890B-D65B515E0457}"/>
     <hyperlink ref="G172" r:id="rId17" xr:uid="{E0CF340A-567A-4979-87DE-4F467618A03F}"/>
     <hyperlink ref="AC196" r:id="rId18" tooltip="Beige testing new" display="https://qa.zlta.testingserver8.com/product-detail/beige-testing-new" xr:uid="{2D91ED96-A11F-44E8-A3F9-04D2C908E6C3}"/>
-    <hyperlink ref="S186" r:id="rId19" xr:uid="{7E9C7A94-A136-40F4-8926-E175506C0FB0}"/>
-    <hyperlink ref="S200" r:id="rId20" xr:uid="{6E155B27-A1F3-4634-AF94-EA4AFCBB6FA8}"/>
+    <hyperlink ref="S186" r:id="rId19" display="https://qa.adm.testingserver8.com/admin/product-collection" xr:uid="{7E9C7A94-A136-40F4-8926-E175506C0FB0}"/>
+    <hyperlink ref="S200" r:id="rId20" display="https://qa.adm.testingserver8.com/admin/product" xr:uid="{6E155B27-A1F3-4634-AF94-EA4AFCBB6FA8}"/>
     <hyperlink ref="S178" r:id="rId21" display="https://opt.adm.testingserver8.com/admin/product" xr:uid="{FE84E4EC-8AD8-4353-9CF9-0FFD7AF22EC6}"/>
     <hyperlink ref="S179" r:id="rId22" display="https://opt.adm.testingserver8.com/admin/home-page-banner" xr:uid="{FE688102-71E6-4D5D-8C26-E4A5C88965AB}"/>
     <hyperlink ref="S180" r:id="rId23" display="https://opt.adm.testingserver8.com/admin/product" xr:uid="{75833417-6442-4309-8418-D565356A22B6}"/>
@@ -34496,44 +34496,44 @@
     <hyperlink ref="S183" r:id="rId27" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{6E9132F4-992B-46D1-9A28-5D473938DFF8}"/>
     <hyperlink ref="S184" r:id="rId28" display="https://opt.adm.testingserver8.com/admin/product-collection" xr:uid="{B7714AD9-0B49-4F19-B276-CBDABCB03633}"/>
     <hyperlink ref="S185" r:id="rId29" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{965BF565-0242-4239-B278-6E574AF5D044}"/>
-    <hyperlink ref="S214" r:id="rId30" xr:uid="{C1127956-48DF-433C-AD28-9DA999FBCC26}"/>
-    <hyperlink ref="S213" r:id="rId31" xr:uid="{C9182A01-C96D-4110-9CA5-C017A54856E8}"/>
-    <hyperlink ref="S225" r:id="rId32" xr:uid="{6C20156C-B7E3-4D33-B99C-3A1821930139}"/>
-    <hyperlink ref="S230" r:id="rId33" xr:uid="{BAC34349-31E9-4520-A81D-6EEDD88BD29C}"/>
-    <hyperlink ref="S228" r:id="rId34" xr:uid="{95A32C29-884B-4748-92B0-EDDF6C5CE209}"/>
-    <hyperlink ref="S227" r:id="rId35" xr:uid="{118D0710-0BF2-49C8-888F-870ACC682CB5}"/>
-    <hyperlink ref="S231" r:id="rId36" xr:uid="{95BCE644-FF9B-472B-8145-F31A886E4FC4}"/>
-    <hyperlink ref="T231" r:id="rId37" xr:uid="{89BBFA7B-AD6E-4F93-BFD3-447AE8F7C502}"/>
-    <hyperlink ref="S232" r:id="rId38" xr:uid="{C8BD3F97-CFD5-4E09-8346-C525E3D0F983}"/>
-    <hyperlink ref="T232" r:id="rId39" display="https://console.zlaata.com/admin/return-order" xr:uid="{7EB489AF-7DBE-4776-BCF8-60461A79DB05}"/>
-    <hyperlink ref="S233" r:id="rId40" xr:uid="{570ACAD2-9993-464C-95C3-A0F384F535D4}"/>
-    <hyperlink ref="S234" r:id="rId41" xr:uid="{A5E4F190-F60E-4C69-A7BF-9E5AD6674C56}"/>
-    <hyperlink ref="S235" r:id="rId42" xr:uid="{0DD56580-2553-4B3D-AC00-0568BF6AD0B9}"/>
-    <hyperlink ref="S236" r:id="rId43" xr:uid="{16CBC571-4EE4-4D66-B8C3-CE0279FDD836}"/>
-    <hyperlink ref="T234" r:id="rId44" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{5FB45239-0134-4C16-87DB-11C106356D92}"/>
+    <hyperlink ref="S214" r:id="rId30" display="https://qa.adm.testingserver8.com/admin/return-order" xr:uid="{C1127956-48DF-433C-AD28-9DA999FBCC26}"/>
+    <hyperlink ref="S213" r:id="rId31" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{C9182A01-C96D-4110-9CA5-C017A54856E8}"/>
+    <hyperlink ref="S225" r:id="rId32" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{6C20156C-B7E3-4D33-B99C-3A1821930139}"/>
+    <hyperlink ref="S230" r:id="rId33" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{BAC34349-31E9-4520-A81D-6EEDD88BD29C}"/>
+    <hyperlink ref="S228" r:id="rId34" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{95A32C29-884B-4748-92B0-EDDF6C5CE209}"/>
+    <hyperlink ref="S227" r:id="rId35" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{118D0710-0BF2-49C8-888F-870ACC682CB5}"/>
+    <hyperlink ref="S231" r:id="rId36" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{95BCE644-FF9B-472B-8145-F31A886E4FC4}"/>
+    <hyperlink ref="T231" r:id="rId37" display="https://qa.adm.testingserver8.com/admin/return-order" xr:uid="{89BBFA7B-AD6E-4F93-BFD3-447AE8F7C502}"/>
+    <hyperlink ref="S232" r:id="rId38" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{C8BD3F97-CFD5-4E09-8346-C525E3D0F983}"/>
+    <hyperlink ref="T232" r:id="rId39" xr:uid="{7EB489AF-7DBE-4776-BCF8-60461A79DB05}"/>
+    <hyperlink ref="S233" r:id="rId40" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{570ACAD2-9993-464C-95C3-A0F384F535D4}"/>
+    <hyperlink ref="S234" r:id="rId41" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{A5E4F190-F60E-4C69-A7BF-9E5AD6674C56}"/>
+    <hyperlink ref="S235" r:id="rId42" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{0DD56580-2553-4B3D-AC00-0568BF6AD0B9}"/>
+    <hyperlink ref="S236" r:id="rId43" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{16CBC571-4EE4-4D66-B8C3-CE0279FDD836}"/>
+    <hyperlink ref="T234" r:id="rId44" xr:uid="{5FB45239-0134-4C16-87DB-11C106356D92}"/>
     <hyperlink ref="AD231" r:id="rId45" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{79B826CA-7F44-45A6-9BD2-CC8919CFA12A}"/>
     <hyperlink ref="AC177" r:id="rId46" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{7BE8FE18-5C75-431B-8488-FBDEF16485E5}"/>
     <hyperlink ref="AC178" r:id="rId47" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{FF640DAE-0F42-4B2A-A086-F1C73287AD75}"/>
     <hyperlink ref="AC181" r:id="rId48" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{B625AA61-E1E0-4964-9CDD-901824C6555F}"/>
     <hyperlink ref="AC244" r:id="rId49" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
-    <hyperlink ref="T211" r:id="rId50" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
-    <hyperlink ref="T212" r:id="rId51" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
-    <hyperlink ref="S199" r:id="rId52" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
+    <hyperlink ref="T211" r:id="rId50" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
+    <hyperlink ref="T212" r:id="rId51" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
+    <hyperlink ref="S199" r:id="rId52" display="https://qa.adm.testingserver8.com/admin/product-style" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
     <hyperlink ref="AC225" r:id="rId53" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{CD96CCCF-BE60-40A1-BA2F-93729430B99A}"/>
     <hyperlink ref="AC226:AC239" r:id="rId54" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
     <hyperlink ref="S219" r:id="rId55" display="https://qa.zlta.testingserver8.com/admin/payment-pending" xr:uid="{37E5E50E-434D-4FC0-B9A6-C0648E88FF97}"/>
-    <hyperlink ref="S206" r:id="rId56" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
-    <hyperlink ref="S204" r:id="rId57" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
-    <hyperlink ref="S205" r:id="rId58" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
-    <hyperlink ref="S196" r:id="rId59" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
-    <hyperlink ref="S243" r:id="rId60" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
-    <hyperlink ref="T236" r:id="rId61" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
-    <hyperlink ref="S226" r:id="rId62" display="https://console.zlaata.com/admin/cancel-order" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
+    <hyperlink ref="S206" r:id="rId56" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
+    <hyperlink ref="S204" r:id="rId57" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
+    <hyperlink ref="S205" r:id="rId58" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
+    <hyperlink ref="S196" r:id="rId59" display="https://qa.adm.testingserver8.com/admin/product" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
+    <hyperlink ref="S243" r:id="rId60" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
+    <hyperlink ref="T236" r:id="rId61" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
+    <hyperlink ref="S226" r:id="rId62" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
     <hyperlink ref="AC237" r:id="rId63" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{B5FFBFD3-2AEB-43E2-A088-AA986500C94C}"/>
-    <hyperlink ref="S237" r:id="rId64" xr:uid="{E29AE273-A13B-4FDA-99DA-66C3FC3DF993}"/>
-    <hyperlink ref="S239" r:id="rId65" xr:uid="{E5A47A78-2C35-4A72-A585-72E3D18CC556}"/>
+    <hyperlink ref="S237" r:id="rId64" display="https://qa.adm.testingserver8.com/admin/subscriber" xr:uid="{E29AE273-A13B-4FDA-99DA-66C3FC3DF993}"/>
+    <hyperlink ref="S239" r:id="rId65" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{E5A47A78-2C35-4A72-A585-72E3D18CC556}"/>
     <hyperlink ref="AC238" r:id="rId66" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{A40E89D1-5252-43A0-AF9C-1AAAC503CE8E}"/>
-    <hyperlink ref="S238" r:id="rId67" xr:uid="{EFD712A1-7827-446F-B5F1-9CC652078EB0}"/>
+    <hyperlink ref="S238" r:id="rId67" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{EFD712A1-7827-446F-B5F1-9CC652078EB0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId68"/>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever33\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D79C80-E0A1-4515-AC74-AECCA4B449D7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768F455F-656B-4FB4-A847-494F47C44DC9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8810" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8850" uniqueCount="941">
   <si>
     <t>S.No</t>
   </si>
@@ -2834,6 +2834,21 @@
   </si>
   <si>
     <t>https://console.zlaata.com/admin/subscriber</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_TO_01</t>
+  </si>
+  <si>
+    <t>Regression Track Order Page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_TO_01</t>
+  </si>
+  <si>
+    <t>Verify Track Order with valid and invalid Track ID</t>
+  </si>
+  <si>
+    <t>TrackOrder</t>
   </si>
 </sst>
 </file>
@@ -4340,7 +4355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z264"/>
+  <dimension ref="A1:Z266"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -12986,8 +13001,55 @@
         <v>13</v>
       </c>
     </row>
+    <row r="265" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A265" s="87" t="s">
+        <v>937</v>
+      </c>
+      <c r="B265" s="87"/>
+      <c r="C265" s="87"/>
+      <c r="D265" s="87"/>
+      <c r="E265" s="87"/>
+      <c r="F265" s="87"/>
+      <c r="G265" s="87"/>
+      <c r="H265" s="87"/>
+      <c r="I265" s="87"/>
+      <c r="J265" s="87"/>
+    </row>
+    <row r="266" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="48">
+        <v>1</v>
+      </c>
+      <c r="B266" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C266" s="79" t="s">
+        <v>938</v>
+      </c>
+      <c r="D266" s="78" t="s">
+        <v>939</v>
+      </c>
+      <c r="E266" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F266" s="70" t="s">
+        <v>936</v>
+      </c>
+      <c r="G266" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H266" s="48" t="s">
+        <v>940</v>
+      </c>
+      <c r="I266" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J266" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
+    <mergeCell ref="A265:J265"/>
     <mergeCell ref="A220:J220"/>
     <mergeCell ref="A205:J205"/>
     <mergeCell ref="A226:J226"/>
@@ -13109,7 +13171,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AF248"/>
+  <dimension ref="A1:AF249"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -33504,8 +33566,8 @@
       <c r="U239" s="49" t="s">
         <v>933</v>
       </c>
-      <c r="V239" s="28" t="s">
-        <v>22</v>
+      <c r="V239" s="48" t="s">
+        <v>913</v>
       </c>
       <c r="W239" s="28" t="s">
         <v>22</v>
@@ -34357,6 +34419,98 @@
         <v>22</v>
       </c>
       <c r="AD248" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="249" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>936</v>
+      </c>
+      <c r="B249" t="s">
+        <v>22</v>
+      </c>
+      <c r="C249" t="s">
+        <v>22</v>
+      </c>
+      <c r="D249" t="s">
+        <v>22</v>
+      </c>
+      <c r="E249" t="s">
+        <v>22</v>
+      </c>
+      <c r="F249" t="s">
+        <v>22</v>
+      </c>
+      <c r="G249" t="s">
+        <v>22</v>
+      </c>
+      <c r="H249" t="s">
+        <v>22</v>
+      </c>
+      <c r="I249" t="s">
+        <v>22</v>
+      </c>
+      <c r="J249" t="s">
+        <v>22</v>
+      </c>
+      <c r="K249" t="s">
+        <v>22</v>
+      </c>
+      <c r="L249" t="s">
+        <v>22</v>
+      </c>
+      <c r="M249" t="s">
+        <v>22</v>
+      </c>
+      <c r="N249" t="s">
+        <v>22</v>
+      </c>
+      <c r="O249" t="s">
+        <v>22</v>
+      </c>
+      <c r="P249" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>22</v>
+      </c>
+      <c r="R249" t="s">
+        <v>22</v>
+      </c>
+      <c r="S249" t="s">
+        <v>22</v>
+      </c>
+      <c r="T249" t="s">
+        <v>22</v>
+      </c>
+      <c r="U249" t="s">
+        <v>22</v>
+      </c>
+      <c r="V249" t="s">
+        <v>22</v>
+      </c>
+      <c r="W249" t="s">
+        <v>22</v>
+      </c>
+      <c r="X249" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y249" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z249" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA249" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB249" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC249" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD249" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever33\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever0\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768F455F-656B-4FB4-A847-494F47C44DC9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FB05D3-7159-4978-BBE6-926CAB299AC5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -2767,75 +2767,6 @@
     <t>Verify the RTO Order Flow for an exchange order before delivered.</t>
   </si>
   <si>
-    <t>https://console.zlaata.com/admin/cancel-order</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/home-page-banner</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/product</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/special-timer-event</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/categories</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/product-collection</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/product-style</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/product-search-keyword</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/collection-search-keyword</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/style-search-keyword</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/track-inventory</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/coupon</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/order</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/return-order</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/exchange-order</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/return-cancel</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/exchange-cancel</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/payment-pending</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/payment-refund</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/payment-failed</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/rto-orders</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/all-orders</t>
-  </si>
-  <si>
-    <t>https://console.zlaata.com/admin/subscriber</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_TO_01</t>
   </si>
   <si>
@@ -2849,6 +2780,75 @@
   </si>
   <si>
     <t>TrackOrder</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/cancel-order</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/home-page-banner</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/product</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/special-timer-event</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/categories</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/product-collection</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/product-style</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/product-search-keyword</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/collection-search-keyword</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/style-search-keyword</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/track-inventory</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/coupon</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/order</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/return-order</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/exchange-order</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/return-cancel</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/exchange-cancel</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/payment-pending</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/payment-refund</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/payment-failed</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/rto-orders</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/all-orders</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/subscriber</t>
   </si>
 </sst>
 </file>
@@ -3508,6 +3508,24 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3534,24 +3552,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5106,18 +5106,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="97" t="s">
+      <c r="A24" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="99"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -5504,18 +5504,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="100" t="s">
+      <c r="A37" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="101"/>
-      <c r="H37" s="101"/>
-      <c r="I37" s="101"/>
-      <c r="J37" s="102"/>
+      <c r="B37" s="92"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="93"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -6062,18 +6062,18 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="100" t="s">
+      <c r="A55" s="91" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="101"/>
-      <c r="C55" s="101"/>
-      <c r="D55" s="101"/>
-      <c r="E55" s="101"/>
-      <c r="F55" s="101"/>
-      <c r="G55" s="101"/>
-      <c r="H55" s="101"/>
-      <c r="I55" s="101"/>
-      <c r="J55" s="102"/>
+      <c r="B55" s="92"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="92"/>
+      <c r="F55" s="92"/>
+      <c r="G55" s="92"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="92"/>
+      <c r="J55" s="93"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
@@ -6396,18 +6396,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="100" t="s">
+      <c r="A66" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="101"/>
-      <c r="C66" s="101"/>
-      <c r="D66" s="101"/>
-      <c r="E66" s="101"/>
-      <c r="F66" s="101"/>
-      <c r="G66" s="101"/>
-      <c r="H66" s="101"/>
-      <c r="I66" s="101"/>
-      <c r="J66" s="102"/>
+      <c r="B66" s="92"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="92"/>
+      <c r="E66" s="92"/>
+      <c r="F66" s="92"/>
+      <c r="G66" s="92"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="92"/>
+      <c r="J66" s="93"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
@@ -6762,18 +6762,18 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="100" t="s">
+      <c r="A78" s="91" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="101"/>
-      <c r="C78" s="101"/>
-      <c r="D78" s="101"/>
-      <c r="E78" s="101"/>
-      <c r="F78" s="101"/>
-      <c r="G78" s="101"/>
-      <c r="H78" s="101"/>
-      <c r="I78" s="101"/>
-      <c r="J78" s="102"/>
+      <c r="B78" s="92"/>
+      <c r="C78" s="92"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="92"/>
+      <c r="F78" s="92"/>
+      <c r="G78" s="92"/>
+      <c r="H78" s="92"/>
+      <c r="I78" s="92"/>
+      <c r="J78" s="93"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
@@ -7640,18 +7640,18 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="88" t="s">
+      <c r="A106" s="94" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="88"/>
-      <c r="C106" s="88"/>
-      <c r="D106" s="88"/>
-      <c r="E106" s="88"/>
-      <c r="F106" s="88"/>
-      <c r="G106" s="88"/>
-      <c r="H106" s="88"/>
-      <c r="I106" s="88"/>
-      <c r="J106" s="88"/>
+      <c r="B106" s="94"/>
+      <c r="C106" s="94"/>
+      <c r="D106" s="94"/>
+      <c r="E106" s="94"/>
+      <c r="F106" s="94"/>
+      <c r="G106" s="94"/>
+      <c r="H106" s="94"/>
+      <c r="I106" s="94"/>
+      <c r="J106" s="94"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -8144,18 +8144,18 @@
       <c r="X120" s="58"/>
     </row>
     <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="89" t="s">
+      <c r="A121" s="95" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="89"/>
-      <c r="C121" s="89"/>
-      <c r="D121" s="89"/>
-      <c r="E121" s="89"/>
-      <c r="F121" s="89"/>
-      <c r="G121" s="89"/>
-      <c r="H121" s="89"/>
-      <c r="I121" s="89"/>
-      <c r="J121" s="89"/>
+      <c r="B121" s="95"/>
+      <c r="C121" s="95"/>
+      <c r="D121" s="95"/>
+      <c r="E121" s="95"/>
+      <c r="F121" s="95"/>
+      <c r="G121" s="95"/>
+      <c r="H121" s="95"/>
+      <c r="I121" s="95"/>
+      <c r="J121" s="95"/>
       <c r="K121" s="57"/>
       <c r="L121" s="58"/>
       <c r="M121" s="58"/>
@@ -8218,18 +8218,18 @@
       <c r="X122" s="58"/>
     </row>
     <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="89" t="s">
+      <c r="A123" s="95" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="89"/>
-      <c r="C123" s="89"/>
-      <c r="D123" s="89"/>
-      <c r="E123" s="89"/>
-      <c r="F123" s="89"/>
-      <c r="G123" s="89"/>
-      <c r="H123" s="89"/>
-      <c r="I123" s="89"/>
-      <c r="J123" s="89"/>
+      <c r="B123" s="95"/>
+      <c r="C123" s="95"/>
+      <c r="D123" s="95"/>
+      <c r="E123" s="95"/>
+      <c r="F123" s="95"/>
+      <c r="G123" s="95"/>
+      <c r="H123" s="95"/>
+      <c r="I123" s="95"/>
+      <c r="J123" s="95"/>
       <c r="K123" s="57"/>
       <c r="L123" s="58"/>
       <c r="M123" s="58"/>
@@ -8292,18 +8292,18 @@
       <c r="X124" s="58"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="89" t="s">
+      <c r="A125" s="95" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="89"/>
-      <c r="C125" s="89"/>
-      <c r="D125" s="89"/>
-      <c r="E125" s="89"/>
-      <c r="F125" s="89"/>
-      <c r="G125" s="89"/>
-      <c r="H125" s="89"/>
-      <c r="I125" s="89"/>
-      <c r="J125" s="89"/>
+      <c r="B125" s="95"/>
+      <c r="C125" s="95"/>
+      <c r="D125" s="95"/>
+      <c r="E125" s="95"/>
+      <c r="F125" s="95"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="95"/>
+      <c r="I125" s="95"/>
+      <c r="J125" s="95"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -8628,18 +8628,18 @@
       <c r="X132" s="58"/>
     </row>
     <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="89" t="s">
+      <c r="A133" s="95" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="89"/>
-      <c r="C133" s="89"/>
-      <c r="D133" s="90"/>
-      <c r="E133" s="90"/>
-      <c r="F133" s="90"/>
-      <c r="G133" s="90"/>
-      <c r="H133" s="90"/>
-      <c r="I133" s="90"/>
-      <c r="J133" s="90"/>
+      <c r="B133" s="95"/>
+      <c r="C133" s="95"/>
+      <c r="D133" s="96"/>
+      <c r="E133" s="96"/>
+      <c r="F133" s="96"/>
+      <c r="G133" s="96"/>
+      <c r="H133" s="96"/>
+      <c r="I133" s="96"/>
+      <c r="J133" s="96"/>
       <c r="K133" s="58"/>
       <c r="L133" s="58"/>
       <c r="M133" s="58"/>
@@ -9134,18 +9134,18 @@
       <c r="X144" s="58"/>
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="94" t="s">
+      <c r="A145" s="100" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="95"/>
-      <c r="C145" s="95"/>
-      <c r="D145" s="95"/>
-      <c r="E145" s="95"/>
-      <c r="F145" s="95"/>
-      <c r="G145" s="95"/>
-      <c r="H145" s="95"/>
-      <c r="I145" s="95"/>
-      <c r="J145" s="96"/>
+      <c r="B145" s="101"/>
+      <c r="C145" s="101"/>
+      <c r="D145" s="101"/>
+      <c r="E145" s="101"/>
+      <c r="F145" s="101"/>
+      <c r="G145" s="101"/>
+      <c r="H145" s="101"/>
+      <c r="I145" s="101"/>
+      <c r="J145" s="102"/>
       <c r="K145" s="58"/>
       <c r="L145" s="58"/>
       <c r="M145" s="58"/>
@@ -9592,18 +9592,18 @@
       <c r="Z155" s="58"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="89" t="s">
+      <c r="A156" s="95" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="89"/>
-      <c r="C156" s="89"/>
-      <c r="D156" s="89"/>
-      <c r="E156" s="89"/>
-      <c r="F156" s="89"/>
-      <c r="G156" s="89"/>
-      <c r="H156" s="89"/>
-      <c r="I156" s="89"/>
-      <c r="J156" s="89"/>
+      <c r="B156" s="95"/>
+      <c r="C156" s="95"/>
+      <c r="D156" s="95"/>
+      <c r="E156" s="95"/>
+      <c r="F156" s="95"/>
+      <c r="G156" s="95"/>
+      <c r="H156" s="95"/>
+      <c r="I156" s="95"/>
+      <c r="J156" s="95"/>
       <c r="K156" s="58"/>
       <c r="L156" s="58"/>
       <c r="M156" s="58"/>
@@ -9670,18 +9670,18 @@
       <c r="Z157" s="58"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="89" t="s">
+      <c r="A158" s="95" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="89"/>
-      <c r="C158" s="89"/>
-      <c r="D158" s="89"/>
-      <c r="E158" s="89"/>
-      <c r="F158" s="89"/>
-      <c r="G158" s="89"/>
-      <c r="H158" s="89"/>
-      <c r="I158" s="89"/>
-      <c r="J158" s="89"/>
+      <c r="B158" s="95"/>
+      <c r="C158" s="95"/>
+      <c r="D158" s="95"/>
+      <c r="E158" s="95"/>
+      <c r="F158" s="95"/>
+      <c r="G158" s="95"/>
+      <c r="H158" s="95"/>
+      <c r="I158" s="95"/>
+      <c r="J158" s="95"/>
       <c r="K158" s="58"/>
       <c r="L158" s="58"/>
       <c r="M158" s="58"/>
@@ -10516,18 +10516,18 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="89" t="s">
+      <c r="A180" s="95" t="s">
         <v>715</v>
       </c>
-      <c r="B180" s="89"/>
-      <c r="C180" s="89"/>
+      <c r="B180" s="95"/>
+      <c r="C180" s="95"/>
       <c r="D180" s="87"/>
-      <c r="E180" s="89"/>
-      <c r="F180" s="89"/>
-      <c r="G180" s="89"/>
-      <c r="H180" s="89"/>
-      <c r="I180" s="89"/>
-      <c r="J180" s="89"/>
+      <c r="E180" s="95"/>
+      <c r="F180" s="95"/>
+      <c r="G180" s="95"/>
+      <c r="H180" s="95"/>
+      <c r="I180" s="95"/>
+      <c r="J180" s="95"/>
     </row>
     <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="68">
@@ -10818,18 +10818,18 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="91" t="s">
+      <c r="A190" s="97" t="s">
         <v>617</v>
       </c>
-      <c r="B190" s="92"/>
-      <c r="C190" s="92"/>
-      <c r="D190" s="92"/>
-      <c r="E190" s="92"/>
-      <c r="F190" s="92"/>
-      <c r="G190" s="92"/>
-      <c r="H190" s="92"/>
-      <c r="I190" s="92"/>
-      <c r="J190" s="93"/>
+      <c r="B190" s="98"/>
+      <c r="C190" s="98"/>
+      <c r="D190" s="98"/>
+      <c r="E190" s="98"/>
+      <c r="F190" s="98"/>
+      <c r="G190" s="98"/>
+      <c r="H190" s="98"/>
+      <c r="I190" s="98"/>
+      <c r="J190" s="99"/>
     </row>
     <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="68">
@@ -13003,7 +13003,7 @@
     </row>
     <row r="265" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="87" t="s">
-        <v>937</v>
+        <v>914</v>
       </c>
       <c r="B265" s="87"/>
       <c r="C265" s="87"/>
@@ -13023,22 +13023,22 @@
         <v>10</v>
       </c>
       <c r="C266" s="79" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="D266" s="78" t="s">
-        <v>939</v>
+        <v>916</v>
       </c>
       <c r="E266" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F266" s="70" t="s">
-        <v>936</v>
+        <v>913</v>
       </c>
       <c r="G266" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H266" s="48" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
       <c r="I266" s="48" t="s">
         <v>12</v>
@@ -13049,6 +13049,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A240:J240"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A190:J190"/>
+    <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A158:J158"/>
+    <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A238:J238"/>
     <mergeCell ref="A265:J265"/>
     <mergeCell ref="A220:J220"/>
     <mergeCell ref="A205:J205"/>
@@ -13065,15 +13074,6 @@
     <mergeCell ref="A125:J125"/>
     <mergeCell ref="A203:J203"/>
     <mergeCell ref="A198:J198"/>
-    <mergeCell ref="A256:J256"/>
-    <mergeCell ref="A240:J240"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="A190:J190"/>
-    <mergeCell ref="A145:J145"/>
-    <mergeCell ref="A156:J156"/>
-    <mergeCell ref="A158:J158"/>
-    <mergeCell ref="A180:J180"/>
-    <mergeCell ref="A238:J238"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -27498,7 +27498,7 @@
         <v>22</v>
       </c>
       <c r="S173" s="48" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="T173" s="48" t="s">
         <v>22</v>
@@ -27582,7 +27582,7 @@
         <v>22</v>
       </c>
       <c r="S174" s="48" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="T174" s="48" t="s">
         <v>22</v>
@@ -27666,7 +27666,7 @@
         <v>22</v>
       </c>
       <c r="S175" s="48" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="T175" s="48" t="s">
         <v>22</v>
@@ -27750,7 +27750,7 @@
         <v>22</v>
       </c>
       <c r="S176" s="49" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="T176" s="48" t="s">
         <v>22</v>
@@ -27842,7 +27842,7 @@
         <v>22</v>
       </c>
       <c r="S177" s="49" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T177" s="48" t="s">
         <v>22</v>
@@ -27934,7 +27934,7 @@
         <v>22</v>
       </c>
       <c r="S178" s="49" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T178" s="48" t="s">
         <v>22</v>
@@ -28026,7 +28026,7 @@
         <v>22</v>
       </c>
       <c r="S179" s="49" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="T179" s="48" t="s">
         <v>22</v>
@@ -28118,7 +28118,7 @@
         <v>22</v>
       </c>
       <c r="S180" s="49" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T180" s="48" t="s">
         <v>22</v>
@@ -28210,7 +28210,7 @@
         <v>22</v>
       </c>
       <c r="S181" s="49" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T181" s="48" t="s">
         <v>22</v>
@@ -28302,7 +28302,7 @@
         <v>22</v>
       </c>
       <c r="S182" s="49" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="T182" s="48" t="s">
         <v>22</v>
@@ -28394,7 +28394,7 @@
         <v>22</v>
       </c>
       <c r="S183" s="49" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="T183" s="48" t="s">
         <v>22</v>
@@ -28486,7 +28486,7 @@
         <v>22</v>
       </c>
       <c r="S184" s="49" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="T184" s="48" t="s">
         <v>22</v>
@@ -28578,7 +28578,7 @@
         <v>22</v>
       </c>
       <c r="S185" s="49" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="T185" s="48" t="s">
         <v>22</v>
@@ -28673,7 +28673,7 @@
         <v>22</v>
       </c>
       <c r="S186" s="49" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="T186" s="48" t="s">
         <v>22</v>
@@ -29602,7 +29602,7 @@
         <v>22</v>
       </c>
       <c r="S196" s="49" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T196" s="48" t="s">
         <v>22</v>
@@ -29694,7 +29694,7 @@
         <v>22</v>
       </c>
       <c r="S197" s="49" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="T197" s="48" t="s">
         <v>22</v>
@@ -29786,7 +29786,7 @@
         <v>22</v>
       </c>
       <c r="S198" s="49" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="T198" s="48" t="s">
         <v>22</v>
@@ -29878,7 +29878,7 @@
         <v>22</v>
       </c>
       <c r="S199" s="49" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="T199" s="48" t="s">
         <v>22</v>
@@ -29970,7 +29970,7 @@
         <v>22</v>
       </c>
       <c r="S200" s="49" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T200" s="48" t="s">
         <v>22</v>
@@ -30062,7 +30062,7 @@
         <v>22</v>
       </c>
       <c r="S201" s="49" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="T201" s="48" t="s">
         <v>22</v>
@@ -30154,7 +30154,7 @@
         <v>22</v>
       </c>
       <c r="S202" s="49" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="T202" s="48" t="s">
         <v>22</v>
@@ -30246,7 +30246,7 @@
         <v>22</v>
       </c>
       <c r="S203" s="49" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="T203" s="48" t="s">
         <v>22</v>
@@ -30338,7 +30338,7 @@
         <v>22</v>
       </c>
       <c r="S204" s="49" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="T204" s="48" t="s">
         <v>22</v>
@@ -30430,7 +30430,7 @@
         <v>22</v>
       </c>
       <c r="S205" s="49" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="T205" s="48" t="s">
         <v>22</v>
@@ -30522,7 +30522,7 @@
         <v>22</v>
       </c>
       <c r="S206" s="49" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="T206" s="48" t="s">
         <v>22</v>
@@ -30614,7 +30614,7 @@
         <v>22</v>
       </c>
       <c r="S207" s="49" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T207" s="48" t="s">
         <v>22</v>
@@ -30706,7 +30706,7 @@
         <v>22</v>
       </c>
       <c r="S208" s="49" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="T208" s="48" t="s">
         <v>22</v>
@@ -30798,7 +30798,7 @@
         <v>22</v>
       </c>
       <c r="S209" s="49" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="T209" s="48" t="s">
         <v>22</v>
@@ -30890,7 +30890,7 @@
         <v>22</v>
       </c>
       <c r="S210" s="49" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="T210" s="48" t="s">
         <v>22</v>
@@ -30982,10 +30982,10 @@
         <v>22</v>
       </c>
       <c r="S211" s="49" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="T211" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="U211" s="48" t="s">
         <v>22</v>
@@ -31074,10 +31074,10 @@
         <v>22</v>
       </c>
       <c r="S212" s="49" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="T212" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="U212" s="48" t="s">
         <v>22</v>
@@ -31166,7 +31166,7 @@
         <v>22</v>
       </c>
       <c r="S213" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T213" s="48" t="s">
         <v>22</v>
@@ -31258,7 +31258,7 @@
         <v>22</v>
       </c>
       <c r="S214" s="49" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="T214" s="48" t="s">
         <v>22</v>
@@ -31350,7 +31350,7 @@
         <v>22</v>
       </c>
       <c r="S215" s="49" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="T215" s="48" t="s">
         <v>22</v>
@@ -31442,7 +31442,7 @@
         <v>22</v>
       </c>
       <c r="S216" s="49" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="T216" s="48" t="s">
         <v>22</v>
@@ -31534,7 +31534,7 @@
         <v>22</v>
       </c>
       <c r="S217" s="49" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="T217" s="48" t="s">
         <v>22</v>
@@ -31626,7 +31626,7 @@
         <v>22</v>
       </c>
       <c r="S218" s="49" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="T218" s="48" t="s">
         <v>22</v>
@@ -31718,7 +31718,7 @@
         <v>22</v>
       </c>
       <c r="S219" s="49" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="T219" s="48" t="s">
         <v>22</v>
@@ -31810,7 +31810,7 @@
         <v>22</v>
       </c>
       <c r="S220" s="49" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="T220" s="48" t="s">
         <v>22</v>
@@ -31902,7 +31902,7 @@
         <v>22</v>
       </c>
       <c r="S221" s="49" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="T221" s="48" t="s">
         <v>22</v>
@@ -31994,7 +31994,7 @@
         <v>22</v>
       </c>
       <c r="S222" s="49" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="T222" s="48" t="s">
         <v>22</v>
@@ -32086,7 +32086,7 @@
         <v>22</v>
       </c>
       <c r="S223" s="49" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="T223" s="48" t="s">
         <v>22</v>
@@ -32178,7 +32178,7 @@
         <v>22</v>
       </c>
       <c r="S224" s="49" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T224" s="48" t="s">
         <v>22</v>
@@ -32270,7 +32270,7 @@
         <v>22</v>
       </c>
       <c r="S225" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T225" s="48" t="s">
         <v>22</v>
@@ -32362,7 +32362,7 @@
         <v>22</v>
       </c>
       <c r="S226" s="49" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="T226" s="48" t="s">
         <v>22</v>
@@ -32454,10 +32454,10 @@
         <v>22</v>
       </c>
       <c r="S227" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T227" s="49" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="U227" s="48" t="s">
         <v>22</v>
@@ -32546,10 +32546,10 @@
         <v>22</v>
       </c>
       <c r="S228" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T228" s="49" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="U228" s="48" t="s">
         <v>22</v>
@@ -32638,10 +32638,10 @@
         <v>22</v>
       </c>
       <c r="S229" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T229" s="48" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="U229" s="48" t="s">
         <v>22</v>
@@ -32730,7 +32730,7 @@
         <v>22</v>
       </c>
       <c r="S230" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T230" s="48" t="s">
         <v>22</v>
@@ -32822,10 +32822,10 @@
         <v>22</v>
       </c>
       <c r="S231" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T231" s="49" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="U231" s="48" t="s">
         <v>22</v>
@@ -32914,10 +32914,10 @@
         <v>22</v>
       </c>
       <c r="S232" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T232" s="49" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="U232" s="48" t="s">
         <v>22</v>
@@ -33006,7 +33006,7 @@
         <v>22</v>
       </c>
       <c r="S233" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T233" s="48" t="s">
         <v>22</v>
@@ -33098,10 +33098,10 @@
         <v>22</v>
       </c>
       <c r="S234" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T234" s="49" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="U234" s="48" t="s">
         <v>22</v>
@@ -33190,10 +33190,10 @@
         <v>22</v>
       </c>
       <c r="S235" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T235" s="49" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="U235" s="48" t="s">
         <v>22</v>
@@ -33282,10 +33282,10 @@
         <v>22</v>
       </c>
       <c r="S236" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T236" s="49" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="U236" s="48" t="s">
         <v>22</v>
@@ -33374,10 +33374,10 @@
         <v>22</v>
       </c>
       <c r="S237" s="49" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="T237" s="49" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="U237" s="48" t="s">
         <v>22</v>
@@ -33466,10 +33466,10 @@
         <v>22</v>
       </c>
       <c r="S238" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T238" s="49" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="U238" s="48" t="s">
         <v>22</v>
@@ -33558,16 +33558,16 @@
         <v>22</v>
       </c>
       <c r="S239" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T239" s="49" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="U239" s="49" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="V239" s="48" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="W239" s="28" t="s">
         <v>22</v>
@@ -33926,7 +33926,7 @@
         <v>22</v>
       </c>
       <c r="S243" s="49" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="T243" s="48" t="s">
         <v>22</v>
@@ -34294,7 +34294,7 @@
         <v>22</v>
       </c>
       <c r="S247" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T247" t="s">
         <v>22</v>
@@ -34386,7 +34386,7 @@
         <v>22</v>
       </c>
       <c r="S248" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="T248" t="s">
         <v>22</v>
@@ -34424,7 +34424,7 @@
     </row>
     <row r="249" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>936</v>
+        <v>913</v>
       </c>
       <c r="B249" t="s">
         <v>22</v>
@@ -34639,8 +34639,8 @@
     <hyperlink ref="D142" r:id="rId16" xr:uid="{8898BD8E-2CA4-4CDE-890B-D65B515E0457}"/>
     <hyperlink ref="G172" r:id="rId17" xr:uid="{E0CF340A-567A-4979-87DE-4F467618A03F}"/>
     <hyperlink ref="AC196" r:id="rId18" tooltip="Beige testing new" display="https://qa.zlta.testingserver8.com/product-detail/beige-testing-new" xr:uid="{2D91ED96-A11F-44E8-A3F9-04D2C908E6C3}"/>
-    <hyperlink ref="S186" r:id="rId19" display="https://qa.adm.testingserver8.com/admin/product-collection" xr:uid="{7E9C7A94-A136-40F4-8926-E175506C0FB0}"/>
-    <hyperlink ref="S200" r:id="rId20" display="https://qa.adm.testingserver8.com/admin/product" xr:uid="{6E155B27-A1F3-4634-AF94-EA4AFCBB6FA8}"/>
+    <hyperlink ref="S186" r:id="rId19" xr:uid="{7E9C7A94-A136-40F4-8926-E175506C0FB0}"/>
+    <hyperlink ref="S200" r:id="rId20" xr:uid="{6E155B27-A1F3-4634-AF94-EA4AFCBB6FA8}"/>
     <hyperlink ref="S178" r:id="rId21" display="https://opt.adm.testingserver8.com/admin/product" xr:uid="{FE84E4EC-8AD8-4353-9CF9-0FFD7AF22EC6}"/>
     <hyperlink ref="S179" r:id="rId22" display="https://opt.adm.testingserver8.com/admin/home-page-banner" xr:uid="{FE688102-71E6-4D5D-8C26-E4A5C88965AB}"/>
     <hyperlink ref="S180" r:id="rId23" display="https://opt.adm.testingserver8.com/admin/product" xr:uid="{75833417-6442-4309-8418-D565356A22B6}"/>
@@ -34650,44 +34650,44 @@
     <hyperlink ref="S183" r:id="rId27" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{6E9132F4-992B-46D1-9A28-5D473938DFF8}"/>
     <hyperlink ref="S184" r:id="rId28" display="https://opt.adm.testingserver8.com/admin/product-collection" xr:uid="{B7714AD9-0B49-4F19-B276-CBDABCB03633}"/>
     <hyperlink ref="S185" r:id="rId29" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{965BF565-0242-4239-B278-6E574AF5D044}"/>
-    <hyperlink ref="S214" r:id="rId30" display="https://qa.adm.testingserver8.com/admin/return-order" xr:uid="{C1127956-48DF-433C-AD28-9DA999FBCC26}"/>
-    <hyperlink ref="S213" r:id="rId31" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{C9182A01-C96D-4110-9CA5-C017A54856E8}"/>
-    <hyperlink ref="S225" r:id="rId32" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{6C20156C-B7E3-4D33-B99C-3A1821930139}"/>
-    <hyperlink ref="S230" r:id="rId33" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{BAC34349-31E9-4520-A81D-6EEDD88BD29C}"/>
-    <hyperlink ref="S228" r:id="rId34" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{95A32C29-884B-4748-92B0-EDDF6C5CE209}"/>
-    <hyperlink ref="S227" r:id="rId35" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{118D0710-0BF2-49C8-888F-870ACC682CB5}"/>
-    <hyperlink ref="S231" r:id="rId36" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{95BCE644-FF9B-472B-8145-F31A886E4FC4}"/>
-    <hyperlink ref="T231" r:id="rId37" display="https://qa.adm.testingserver8.com/admin/return-order" xr:uid="{89BBFA7B-AD6E-4F93-BFD3-447AE8F7C502}"/>
-    <hyperlink ref="S232" r:id="rId38" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{C8BD3F97-CFD5-4E09-8346-C525E3D0F983}"/>
-    <hyperlink ref="T232" r:id="rId39" xr:uid="{7EB489AF-7DBE-4776-BCF8-60461A79DB05}"/>
-    <hyperlink ref="S233" r:id="rId40" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{570ACAD2-9993-464C-95C3-A0F384F535D4}"/>
-    <hyperlink ref="S234" r:id="rId41" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{A5E4F190-F60E-4C69-A7BF-9E5AD6674C56}"/>
-    <hyperlink ref="S235" r:id="rId42" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{0DD56580-2553-4B3D-AC00-0568BF6AD0B9}"/>
-    <hyperlink ref="S236" r:id="rId43" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{16CBC571-4EE4-4D66-B8C3-CE0279FDD836}"/>
-    <hyperlink ref="T234" r:id="rId44" xr:uid="{5FB45239-0134-4C16-87DB-11C106356D92}"/>
+    <hyperlink ref="S214" r:id="rId30" xr:uid="{C1127956-48DF-433C-AD28-9DA999FBCC26}"/>
+    <hyperlink ref="S213" r:id="rId31" xr:uid="{C9182A01-C96D-4110-9CA5-C017A54856E8}"/>
+    <hyperlink ref="S225" r:id="rId32" xr:uid="{6C20156C-B7E3-4D33-B99C-3A1821930139}"/>
+    <hyperlink ref="S230" r:id="rId33" xr:uid="{BAC34349-31E9-4520-A81D-6EEDD88BD29C}"/>
+    <hyperlink ref="S228" r:id="rId34" xr:uid="{95A32C29-884B-4748-92B0-EDDF6C5CE209}"/>
+    <hyperlink ref="S227" r:id="rId35" xr:uid="{118D0710-0BF2-49C8-888F-870ACC682CB5}"/>
+    <hyperlink ref="S231" r:id="rId36" xr:uid="{95BCE644-FF9B-472B-8145-F31A886E4FC4}"/>
+    <hyperlink ref="T231" r:id="rId37" xr:uid="{89BBFA7B-AD6E-4F93-BFD3-447AE8F7C502}"/>
+    <hyperlink ref="S232" r:id="rId38" xr:uid="{C8BD3F97-CFD5-4E09-8346-C525E3D0F983}"/>
+    <hyperlink ref="T232" r:id="rId39" display="https://console.zlaata.com/admin/return-order" xr:uid="{7EB489AF-7DBE-4776-BCF8-60461A79DB05}"/>
+    <hyperlink ref="S233" r:id="rId40" xr:uid="{570ACAD2-9993-464C-95C3-A0F384F535D4}"/>
+    <hyperlink ref="S234" r:id="rId41" xr:uid="{A5E4F190-F60E-4C69-A7BF-9E5AD6674C56}"/>
+    <hyperlink ref="S235" r:id="rId42" xr:uid="{0DD56580-2553-4B3D-AC00-0568BF6AD0B9}"/>
+    <hyperlink ref="S236" r:id="rId43" xr:uid="{16CBC571-4EE4-4D66-B8C3-CE0279FDD836}"/>
+    <hyperlink ref="T234" r:id="rId44" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{5FB45239-0134-4C16-87DB-11C106356D92}"/>
     <hyperlink ref="AD231" r:id="rId45" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{79B826CA-7F44-45A6-9BD2-CC8919CFA12A}"/>
     <hyperlink ref="AC177" r:id="rId46" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{7BE8FE18-5C75-431B-8488-FBDEF16485E5}"/>
     <hyperlink ref="AC178" r:id="rId47" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{FF640DAE-0F42-4B2A-A086-F1C73287AD75}"/>
     <hyperlink ref="AC181" r:id="rId48" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{B625AA61-E1E0-4964-9CDD-901824C6555F}"/>
     <hyperlink ref="AC244" r:id="rId49" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
-    <hyperlink ref="T211" r:id="rId50" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
-    <hyperlink ref="T212" r:id="rId51" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
-    <hyperlink ref="S199" r:id="rId52" display="https://qa.adm.testingserver8.com/admin/product-style" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
+    <hyperlink ref="T211" r:id="rId50" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
+    <hyperlink ref="T212" r:id="rId51" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
+    <hyperlink ref="S199" r:id="rId52" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
     <hyperlink ref="AC225" r:id="rId53" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{CD96CCCF-BE60-40A1-BA2F-93729430B99A}"/>
     <hyperlink ref="AC226:AC239" r:id="rId54" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
     <hyperlink ref="S219" r:id="rId55" display="https://qa.zlta.testingserver8.com/admin/payment-pending" xr:uid="{37E5E50E-434D-4FC0-B9A6-C0648E88FF97}"/>
-    <hyperlink ref="S206" r:id="rId56" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
-    <hyperlink ref="S204" r:id="rId57" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
-    <hyperlink ref="S205" r:id="rId58" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
-    <hyperlink ref="S196" r:id="rId59" display="https://qa.adm.testingserver8.com/admin/product" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
-    <hyperlink ref="S243" r:id="rId60" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
-    <hyperlink ref="T236" r:id="rId61" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
-    <hyperlink ref="S226" r:id="rId62" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
+    <hyperlink ref="S206" r:id="rId56" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
+    <hyperlink ref="S204" r:id="rId57" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
+    <hyperlink ref="S205" r:id="rId58" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
+    <hyperlink ref="S196" r:id="rId59" display="https://console.zlaata.com/admin/product" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
+    <hyperlink ref="S243" r:id="rId60" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
+    <hyperlink ref="T236" r:id="rId61" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
+    <hyperlink ref="S226" r:id="rId62" display="https://console.zlaata.com/admin/cancel-order" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
     <hyperlink ref="AC237" r:id="rId63" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{B5FFBFD3-2AEB-43E2-A088-AA986500C94C}"/>
-    <hyperlink ref="S237" r:id="rId64" display="https://qa.adm.testingserver8.com/admin/subscriber" xr:uid="{E29AE273-A13B-4FDA-99DA-66C3FC3DF993}"/>
-    <hyperlink ref="S239" r:id="rId65" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{E5A47A78-2C35-4A72-A585-72E3D18CC556}"/>
+    <hyperlink ref="S237" r:id="rId64" xr:uid="{E29AE273-A13B-4FDA-99DA-66C3FC3DF993}"/>
+    <hyperlink ref="S239" r:id="rId65" xr:uid="{E5A47A78-2C35-4A72-A585-72E3D18CC556}"/>
     <hyperlink ref="AC238" r:id="rId66" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{A40E89D1-5252-43A0-AF9C-1AAAC503CE8E}"/>
-    <hyperlink ref="S238" r:id="rId67" display="https://qa.adm.testingserver8.com/admin/order" xr:uid="{EFD712A1-7827-446F-B5F1-9CC652078EB0}"/>
+    <hyperlink ref="S238" r:id="rId67" xr:uid="{EFD712A1-7827-446F-B5F1-9CC652078EB0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId68"/>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever0\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FB05D3-7159-4978-BBE6-926CAB299AC5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92531965-EB6F-4F05-B63C-5CB101AE9452}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8850" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8927" uniqueCount="935">
   <si>
     <t>S.No</t>
   </si>
@@ -1831,36 +1831,18 @@
     <t>Verify Accessories, Recently Viewed, and Top Selling buttons on Checkout page</t>
   </si>
   <si>
-    <t>TD_UI_Zlaata_ADM_01</t>
-  </si>
-  <si>
     <t>Sort by</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>TD_UI_Zlaata_ADM_02</t>
-  </si>
-  <si>
     <t>ProductListingName</t>
   </si>
   <si>
-    <t>TD_UI_Zlaata_ADM_03</t>
-  </si>
-  <si>
-    <t>TD_UI_Zlaata_ADM_04</t>
-  </si>
-  <si>
     <t>Banner Title</t>
   </si>
   <si>
-    <t>TD_UI_Zlaata_ADM_05</t>
-  </si>
-  <si>
-    <t>TD_UI_Zlaata_ADM_06</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_ADM_07</t>
   </si>
   <si>
@@ -2176,42 +2158,9 @@
     <t>Admin Page</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_ADM_01</t>
-  </si>
-  <si>
-    <t>Verify banner upload on home page section</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_ADM_02</t>
-  </si>
-  <si>
-    <t>Verify Top Selling Section Product Display on Homepage.</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_ADM_03</t>
-  </si>
-  <si>
     <t>Verify New Arrivals Section Product Display on Homepage.</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_ADM_04</t>
-  </si>
-  <si>
-    <t>Verify Category Section Display on Website.</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_ADM_05</t>
-  </si>
-  <si>
-    <t>Verify bulk product upload and visibility.</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_ADM_06</t>
-  </si>
-  <si>
-    <t>Remove product SKU from Top Selling and verify on User App.</t>
-  </si>
-  <si>
     <t>TC_UI_Zlaata_ADM_07</t>
   </si>
   <si>
@@ -2248,12 +2197,6 @@
     <t>Verify Admin can create a special coupon and it appears in Admin and User App.</t>
   </si>
   <si>
-    <t>Home Page  Banner Automation</t>
-  </si>
-  <si>
-    <t>Test Automation</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_APE_01</t>
   </si>
   <si>
@@ -2785,9 +2728,6 @@
     <t>https://qa.adm.testingserver8.com/admin/cancel-order</t>
   </si>
   <si>
-    <t>https://qa.adm.testingserver8.com/admin/home-page-banner</t>
-  </si>
-  <si>
     <t>https://qa.adm.testingserver8.com/admin/product</t>
   </si>
   <si>
@@ -2849,6 +2789,48 @@
   </si>
   <si>
     <t>https://qa.adm.testingserver8.com/admin/subscriber</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_LP_01</t>
+  </si>
+  <si>
+    <t>Landing Page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_LP_01</t>
+  </si>
+  <si>
+    <t>Verify category created in Admin ZL Menu is displayed on App Landing Page.</t>
+  </si>
+  <si>
+    <t>Landing</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_LP_02</t>
+  </si>
+  <si>
+    <t>Verify Boss Lady category created in Admin ZL Menu is displayed on App Landing Page.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_LP_02</t>
+  </si>
+  <si>
+    <t>https://qa.adm.testingserver8.com/admin/zl-banner</t>
+  </si>
+  <si>
+    <t>Verify the Zlaata India banner upload in Admin and its display on the Zlaata India home page section.</t>
+  </si>
+  <si>
+    <t>Verify the Boss Lady banner upload in Admin and its display on the Boss Lady home page section.</t>
+  </si>
+  <si>
+    <t>Verify Zlaata India Category Section Display on Website.</t>
+  </si>
+  <si>
+    <t>Verify Boss Lady Category Section Display on Website.</t>
+  </si>
+  <si>
+    <t>Verify Zlaata India Collection Section Display on Website.</t>
   </si>
 </sst>
 </file>
@@ -4355,7 +4337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z266"/>
+  <dimension ref="A1:Z269"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -5784,7 +5766,7 @@
         <v>197</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E46" s="47" t="s">
         <v>14</v>
@@ -5941,10 +5923,10 @@
         <v>10</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="D51" s="80" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="E51" s="48" t="s">
         <v>14</v>
@@ -5973,10 +5955,10 @@
         <v>10</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D52" s="80" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>14</v>
@@ -6005,10 +5987,10 @@
         <v>10</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="D53" s="80" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>14</v>
@@ -6037,16 +6019,16 @@
         <v>10</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D54" s="80" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F54" s="47" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="G54" s="48" t="s">
         <v>11</v>
@@ -7920,7 +7902,7 @@
         <v>370</v>
       </c>
       <c r="D115" s="48" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="E115" s="48" t="s">
         <v>14</v>
@@ -7981,16 +7963,16 @@
         <v>10</v>
       </c>
       <c r="C117" s="48" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="D117" s="48" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="E117" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F117" s="48" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="G117" s="48" t="s">
         <v>11</v>
@@ -8013,16 +7995,16 @@
         <v>10</v>
       </c>
       <c r="C118" s="48" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D118" s="48" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="E118" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F118" s="48" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="G118" s="48" t="s">
         <v>11</v>
@@ -8059,16 +8041,16 @@
         <v>10</v>
       </c>
       <c r="C119" s="48" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D119" s="48" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="E119" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F119" s="48" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="G119" s="48" t="s">
         <v>11</v>
@@ -8105,16 +8087,16 @@
         <v>10</v>
       </c>
       <c r="C120" s="48" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D120" s="48" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="E120" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="48" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="G120" s="48" t="s">
         <v>11</v>
@@ -9052,7 +9034,7 @@
         <v>437</v>
       </c>
       <c r="D143" s="27" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="E143" s="27" t="s">
         <v>14</v>
@@ -9095,16 +9077,16 @@
         <v>10</v>
       </c>
       <c r="C144" s="48" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D144" s="27" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="E144" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F144" s="48" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="G144" s="27" t="s">
         <v>11</v>
@@ -10427,16 +10409,16 @@
         <v>10</v>
       </c>
       <c r="C177" s="70" t="s">
-        <v>895</v>
+        <v>876</v>
       </c>
       <c r="D177" s="71" t="s">
-        <v>896</v>
+        <v>877</v>
       </c>
       <c r="E177" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F177" s="70" t="s">
-        <v>897</v>
+        <v>878</v>
       </c>
       <c r="G177" s="69" t="s">
         <v>11</v>
@@ -10459,16 +10441,16 @@
         <v>10</v>
       </c>
       <c r="C178" s="70" t="s">
-        <v>898</v>
+        <v>879</v>
       </c>
       <c r="D178" s="71" t="s">
-        <v>899</v>
+        <v>880</v>
       </c>
       <c r="E178" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F178" s="70" t="s">
-        <v>900</v>
+        <v>881</v>
       </c>
       <c r="G178" s="69" t="s">
         <v>11</v>
@@ -10491,16 +10473,16 @@
         <v>10</v>
       </c>
       <c r="C179" s="70" t="s">
-        <v>901</v>
+        <v>882</v>
       </c>
       <c r="D179" s="71" t="s">
-        <v>902</v>
+        <v>883</v>
       </c>
       <c r="E179" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F179" s="70" t="s">
-        <v>903</v>
+        <v>884</v>
       </c>
       <c r="G179" s="69" t="s">
         <v>11</v>
@@ -10517,7 +10499,7 @@
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="95" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="B180" s="95"/>
       <c r="C180" s="95"/>
@@ -10537,22 +10519,22 @@
         <v>10</v>
       </c>
       <c r="C181" s="74" t="s">
-        <v>716</v>
+        <v>173</v>
       </c>
       <c r="D181" s="77" t="s">
-        <v>717</v>
+        <v>930</v>
       </c>
       <c r="E181" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F181" s="70" t="s">
-        <v>601</v>
+        <v>175</v>
       </c>
       <c r="G181" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H181" s="69" t="s">
-        <v>782</v>
+        <v>176</v>
       </c>
       <c r="I181" s="69" t="s">
         <v>12</v>
@@ -10569,22 +10551,22 @@
         <v>10</v>
       </c>
       <c r="C182" s="74" t="s">
-        <v>718</v>
+        <v>177</v>
       </c>
       <c r="D182" s="77" t="s">
-        <v>719</v>
+        <v>931</v>
       </c>
       <c r="E182" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F182" s="70" t="s">
-        <v>604</v>
+        <v>179</v>
       </c>
       <c r="G182" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H182" s="69" t="s">
-        <v>782</v>
+        <v>176</v>
       </c>
       <c r="I182" s="69" t="s">
         <v>12</v>
@@ -10601,22 +10583,22 @@
         <v>10</v>
       </c>
       <c r="C183" s="74" t="s">
-        <v>720</v>
+        <v>180</v>
       </c>
       <c r="D183" s="77" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="E183" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F183" s="70" t="s">
-        <v>606</v>
+        <v>182</v>
       </c>
       <c r="G183" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H183" s="69" t="s">
-        <v>782</v>
+        <v>176</v>
       </c>
       <c r="I183" s="69" t="s">
         <v>12</v>
@@ -10627,28 +10609,28 @@
     </row>
     <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B184" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C184" s="74" t="s">
-        <v>722</v>
-      </c>
-      <c r="D184" s="64" t="s">
-        <v>723</v>
+        <v>183</v>
+      </c>
+      <c r="D184" s="77" t="s">
+        <v>932</v>
       </c>
       <c r="E184" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F184" s="70" t="s">
-        <v>607</v>
+        <v>185</v>
       </c>
       <c r="G184" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H184" s="69" t="s">
-        <v>782</v>
+        <v>176</v>
       </c>
       <c r="I184" s="69" t="s">
         <v>12</v>
@@ -10659,28 +10641,28 @@
     </row>
     <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B185" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C185" s="74" t="s">
-        <v>724</v>
-      </c>
-      <c r="D185" s="64" t="s">
-        <v>725</v>
+        <v>186</v>
+      </c>
+      <c r="D185" s="77" t="s">
+        <v>933</v>
       </c>
       <c r="E185" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F185" s="70" t="s">
-        <v>609</v>
+        <v>188</v>
       </c>
       <c r="G185" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H185" s="69" t="s">
-        <v>782</v>
+        <v>176</v>
       </c>
       <c r="I185" s="69" t="s">
         <v>12</v>
@@ -10691,28 +10673,28 @@
     </row>
     <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="68">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B186" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C186" s="74" t="s">
-        <v>726</v>
+        <v>189</v>
       </c>
       <c r="D186" s="77" t="s">
-        <v>727</v>
+        <v>934</v>
       </c>
       <c r="E186" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F186" s="70" t="s">
-        <v>610</v>
+        <v>190</v>
       </c>
       <c r="G186" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H186" s="69" t="s">
-        <v>782</v>
+        <v>176</v>
       </c>
       <c r="I186" s="69" t="s">
         <v>12</v>
@@ -10729,22 +10711,22 @@
         <v>10</v>
       </c>
       <c r="C187" s="74" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="D187" s="64" t="s">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="E187" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F187" s="70" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="G187" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H187" s="69" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="I187" s="69" t="s">
         <v>12</v>
@@ -10761,22 +10743,22 @@
         <v>10</v>
       </c>
       <c r="C188" s="74" t="s">
-        <v>730</v>
+        <v>713</v>
       </c>
       <c r="D188" s="78" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="E188" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F188" s="70" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="G188" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H188" s="69" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="I188" s="69" t="s">
         <v>12</v>
@@ -10793,22 +10775,22 @@
         <v>10</v>
       </c>
       <c r="C189" s="74" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D189" s="64" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="E189" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F189" s="70" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="G189" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H189" s="69" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="I189" s="69" t="s">
         <v>12</v>
@@ -10819,7 +10801,7 @@
     </row>
     <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="97" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B190" s="98"/>
       <c r="C190" s="98"/>
@@ -10839,22 +10821,22 @@
         <v>10</v>
       </c>
       <c r="C191" s="74" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D191" s="77" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="E191" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F191" s="70" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="G191" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H191" s="69" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="I191" s="69" t="s">
         <v>12</v>
@@ -10871,22 +10853,22 @@
         <v>10</v>
       </c>
       <c r="C192" s="74" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="D192" s="77" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="E192" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F192" s="70" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="G192" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H192" s="69" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="I192" s="69" t="s">
         <v>12</v>
@@ -10903,22 +10885,22 @@
         <v>10</v>
       </c>
       <c r="C193" s="74" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="D193" s="78" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E193" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F193" s="70" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="G193" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H193" s="69" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="I193" s="69" t="s">
         <v>12</v>
@@ -10935,22 +10917,22 @@
         <v>10</v>
       </c>
       <c r="C194" s="74" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="D194" s="78" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="E194" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F194" s="70" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="G194" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H194" s="69" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="I194" s="69" t="s">
         <v>12</v>
@@ -10967,22 +10949,22 @@
         <v>10</v>
       </c>
       <c r="C195" s="74" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D195" s="78" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="E195" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F195" s="70" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="G195" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H195" s="69" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="I195" s="69" t="s">
         <v>12</v>
@@ -10999,22 +10981,22 @@
         <v>10</v>
       </c>
       <c r="C196" s="74" t="s">
-        <v>852</v>
+        <v>833</v>
       </c>
       <c r="D196" s="78" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="E196" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F196" s="70" t="s">
-        <v>849</v>
+        <v>830</v>
       </c>
       <c r="G196" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H196" s="69" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="I196" s="69" t="s">
         <v>12</v>
@@ -11031,22 +11013,22 @@
         <v>10</v>
       </c>
       <c r="C197" s="74" t="s">
-        <v>853</v>
+        <v>834</v>
       </c>
       <c r="D197" s="78" t="s">
-        <v>856</v>
+        <v>837</v>
       </c>
       <c r="E197" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F197" s="70" t="s">
-        <v>850</v>
+        <v>831</v>
       </c>
       <c r="G197" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H197" s="69" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="I197" s="69" t="s">
         <v>12</v>
@@ -11057,7 +11039,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="87" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="B198" s="87"/>
       <c r="C198" s="87"/>
@@ -11077,22 +11059,22 @@
         <v>10</v>
       </c>
       <c r="C199" s="79" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="D199" s="64" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="E199" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F199" s="79" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="G199" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H199" s="48" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="I199" s="48" t="s">
         <v>12</v>
@@ -11109,22 +11091,22 @@
         <v>10</v>
       </c>
       <c r="C200" s="79" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="D200" s="78" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="E200" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F200" s="79" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="G200" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H200" s="48" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="I200" s="48" t="s">
         <v>12</v>
@@ -11141,22 +11123,22 @@
         <v>10</v>
       </c>
       <c r="C201" s="79" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D201" s="78" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="E201" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F201" s="79" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="G201" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H201" s="48" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="I201" s="48" t="s">
         <v>12</v>
@@ -11173,22 +11155,22 @@
         <v>10</v>
       </c>
       <c r="C202" s="79" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D202" s="78" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="E202" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F202" s="79" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="G202" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H202" s="48" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="I202" s="48" t="s">
         <v>12</v>
@@ -11199,7 +11181,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="87" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B203" s="87"/>
       <c r="C203" s="87"/>
@@ -11219,22 +11201,22 @@
         <v>10</v>
       </c>
       <c r="C204" s="79" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="D204" s="78" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="E204" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F204" s="79" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="G204" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H204" s="48" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="I204" s="48" t="s">
         <v>12</v>
@@ -11245,7 +11227,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="87" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B205" s="87"/>
       <c r="C205" s="87"/>
@@ -11265,22 +11247,22 @@
         <v>10</v>
       </c>
       <c r="C206" s="79" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D206" s="78" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="E206" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F206" s="79" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="G206" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H206" s="48" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="I206" s="48" t="s">
         <v>12</v>
@@ -11297,22 +11279,22 @@
         <v>10</v>
       </c>
       <c r="C207" s="79" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="D207" s="78" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="E207" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F207" s="79" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="G207" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H207" s="48" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="I207" s="48" t="s">
         <v>12</v>
@@ -11329,22 +11311,22 @@
         <v>10</v>
       </c>
       <c r="C208" s="79" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="D208" s="78" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E208" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F208" s="79" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="G208" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H208" s="48" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="I208" s="48" t="s">
         <v>12</v>
@@ -11361,22 +11343,22 @@
         <v>10</v>
       </c>
       <c r="C209" s="79" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D209" s="78" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="E209" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F209" s="79" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="G209" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H209" s="48" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="I209" s="48" t="s">
         <v>12</v>
@@ -11393,22 +11375,22 @@
         <v>10</v>
       </c>
       <c r="C210" s="79" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="D210" s="78" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="E210" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F210" s="79" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="G210" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H210" s="48" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="I210" s="48" t="s">
         <v>12</v>
@@ -11425,22 +11407,22 @@
         <v>10</v>
       </c>
       <c r="C211" s="79" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D211" s="78" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="E211" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F211" s="79" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="G211" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H211" s="48" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="I211" s="48" t="s">
         <v>12</v>
@@ -11457,22 +11439,22 @@
         <v>10</v>
       </c>
       <c r="C212" s="79" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D212" s="78" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="E212" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F212" s="79" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="G212" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H212" s="48" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="I212" s="48" t="s">
         <v>12</v>
@@ -11489,22 +11471,22 @@
         <v>10</v>
       </c>
       <c r="C213" s="79" t="s">
-        <v>877</v>
+        <v>858</v>
       </c>
       <c r="D213" s="78" t="s">
-        <v>878</v>
+        <v>859</v>
       </c>
       <c r="E213" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F213" s="79" t="s">
-        <v>879</v>
+        <v>860</v>
       </c>
       <c r="G213" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H213" s="48" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="I213" s="48" t="s">
         <v>12</v>
@@ -11521,22 +11503,22 @@
         <v>10</v>
       </c>
       <c r="C214" s="79" t="s">
-        <v>880</v>
+        <v>861</v>
       </c>
       <c r="D214" s="78" t="s">
-        <v>881</v>
+        <v>862</v>
       </c>
       <c r="E214" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F214" s="79" t="s">
-        <v>882</v>
+        <v>863</v>
       </c>
       <c r="G214" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H214" s="48" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="I214" s="48" t="s">
         <v>12</v>
@@ -11550,7 +11532,7 @@
       <c r="B215" s="85"/>
       <c r="C215" s="85"/>
       <c r="D215" s="85" t="s">
-        <v>889</v>
+        <v>870</v>
       </c>
       <c r="E215" s="85"/>
       <c r="F215" s="85"/>
@@ -11567,22 +11549,22 @@
         <v>10</v>
       </c>
       <c r="C216" s="79" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="D216" s="78" t="s">
-        <v>891</v>
+        <v>872</v>
       </c>
       <c r="E216" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F216" s="79" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="G216" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H216" s="48" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="I216" s="48" t="s">
         <v>12</v>
@@ -11596,7 +11578,7 @@
       <c r="B217" s="83"/>
       <c r="C217" s="83"/>
       <c r="D217" s="83" t="s">
-        <v>884</v>
+        <v>865</v>
       </c>
       <c r="E217" s="83"/>
       <c r="F217" s="83"/>
@@ -11613,22 +11595,22 @@
         <v>10</v>
       </c>
       <c r="C218" s="79" t="s">
-        <v>885</v>
+        <v>866</v>
       </c>
       <c r="D218" s="78" t="s">
-        <v>886</v>
+        <v>867</v>
       </c>
       <c r="E218" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F218" s="79" t="s">
-        <v>887</v>
+        <v>868</v>
       </c>
       <c r="G218" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H218" s="48" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="I218" s="48" t="s">
         <v>12</v>
@@ -11645,22 +11627,22 @@
         <v>10</v>
       </c>
       <c r="C219" s="79" t="s">
-        <v>892</v>
+        <v>873</v>
       </c>
       <c r="D219" s="78" t="s">
-        <v>893</v>
+        <v>874</v>
       </c>
       <c r="E219" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F219" s="79" t="s">
-        <v>894</v>
+        <v>875</v>
       </c>
       <c r="G219" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H219" s="48" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="I219" s="48" t="s">
         <v>12</v>
@@ -11671,7 +11653,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="87" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
       <c r="B220" s="87"/>
       <c r="C220" s="87"/>
@@ -11691,22 +11673,22 @@
         <v>10</v>
       </c>
       <c r="C221" s="79" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="D221" s="78" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
       <c r="E221" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F221" s="79" t="s">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="G221" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H221" s="48" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="I221" s="48" t="s">
         <v>12</v>
@@ -11723,22 +11705,22 @@
         <v>10</v>
       </c>
       <c r="C222" s="79" t="s">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="D222" s="78" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
       <c r="E222" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F222" s="79" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
       <c r="G222" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H222" s="48" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="I222" s="48" t="s">
         <v>12</v>
@@ -11755,22 +11737,22 @@
         <v>10</v>
       </c>
       <c r="C223" s="79" t="s">
-        <v>778</v>
+        <v>759</v>
       </c>
       <c r="D223" s="78" t="s">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="E223" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F223" s="79" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="G223" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H223" s="48" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="I223" s="48" t="s">
         <v>12</v>
@@ -11787,22 +11769,22 @@
         <v>10</v>
       </c>
       <c r="C224" s="79" t="s">
-        <v>864</v>
+        <v>845</v>
       </c>
       <c r="D224" s="78" t="s">
-        <v>865</v>
+        <v>846</v>
       </c>
       <c r="E224" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F224" s="79" t="s">
-        <v>866</v>
+        <v>847</v>
       </c>
       <c r="G224" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H224" s="48" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="I224" s="48" t="s">
         <v>12</v>
@@ -11819,22 +11801,22 @@
         <v>10</v>
       </c>
       <c r="C225" s="79" t="s">
-        <v>868</v>
+        <v>849</v>
       </c>
       <c r="D225" s="78" t="s">
-        <v>869</v>
+        <v>850</v>
       </c>
       <c r="E225" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F225" s="79" t="s">
-        <v>867</v>
+        <v>848</v>
       </c>
       <c r="G225" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H225" s="48" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="I225" s="48" t="s">
         <v>12</v>
@@ -11845,7 +11827,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="87" t="s">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="B226" s="87"/>
       <c r="C226" s="87"/>
@@ -11865,22 +11847,22 @@
         <v>10</v>
       </c>
       <c r="C227" s="79" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="D227" s="78" t="s">
-        <v>745</v>
+        <v>726</v>
       </c>
       <c r="E227" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F227" s="79" t="s">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="G227" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H227" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I227" s="48" t="s">
         <v>12</v>
@@ -11897,22 +11879,22 @@
         <v>10</v>
       </c>
       <c r="C228" s="79" t="s">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="D228" s="78" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="E228" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F228" s="79" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="G228" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H228" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I228" s="48" t="s">
         <v>12</v>
@@ -11929,22 +11911,22 @@
         <v>10</v>
       </c>
       <c r="C229" s="79" t="s">
-        <v>750</v>
+        <v>731</v>
       </c>
       <c r="D229" s="78" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="E229" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F229" s="79" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="G229" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H229" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I229" s="48" t="s">
         <v>12</v>
@@ -11961,22 +11943,22 @@
         <v>10</v>
       </c>
       <c r="C230" s="79" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="D230" s="78" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E230" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F230" s="79" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="G230" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H230" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I230" s="48" t="s">
         <v>12</v>
@@ -11993,22 +11975,22 @@
         <v>10</v>
       </c>
       <c r="C231" s="79" t="s">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="D231" s="78" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="E231" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F231" s="79" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
       <c r="G231" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H231" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I231" s="48" t="s">
         <v>12</v>
@@ -12025,22 +12007,22 @@
         <v>10</v>
       </c>
       <c r="C232" s="79" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="D232" s="78" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="E232" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F232" s="79" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="G232" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H232" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I232" s="48" t="s">
         <v>12</v>
@@ -12057,22 +12039,22 @@
         <v>10</v>
       </c>
       <c r="C233" s="79" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="D233" s="78" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="E233" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F233" s="79" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="G233" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H233" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I233" s="48" t="s">
         <v>12</v>
@@ -12089,22 +12071,22 @@
         <v>10</v>
       </c>
       <c r="C234" s="79" t="s">
-        <v>765</v>
+        <v>746</v>
       </c>
       <c r="D234" s="78" t="s">
-        <v>766</v>
+        <v>747</v>
       </c>
       <c r="E234" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F234" s="79" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="G234" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H234" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I234" s="48" t="s">
         <v>12</v>
@@ -12121,22 +12103,22 @@
         <v>10</v>
       </c>
       <c r="C235" s="79" t="s">
-        <v>767</v>
+        <v>748</v>
       </c>
       <c r="D235" s="78" t="s">
-        <v>768</v>
+        <v>749</v>
       </c>
       <c r="E235" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F235" s="79" t="s">
-        <v>769</v>
+        <v>750</v>
       </c>
       <c r="G235" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H235" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I235" s="48" t="s">
         <v>12</v>
@@ -12153,22 +12135,22 @@
         <v>10</v>
       </c>
       <c r="C236" s="79" t="s">
-        <v>770</v>
+        <v>751</v>
       </c>
       <c r="D236" s="78" t="s">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="E236" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F236" s="79" t="s">
-        <v>772</v>
+        <v>753</v>
       </c>
       <c r="G236" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H236" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I236" s="48" t="s">
         <v>12</v>
@@ -12185,22 +12167,22 @@
         <v>10</v>
       </c>
       <c r="C237" s="79" t="s">
-        <v>774</v>
+        <v>755</v>
       </c>
       <c r="D237" s="78" t="s">
-        <v>775</v>
+        <v>756</v>
       </c>
       <c r="E237" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F237" s="79" t="s">
-        <v>773</v>
+        <v>754</v>
       </c>
       <c r="G237" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H237" s="48" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I237" s="48" t="s">
         <v>12</v>
@@ -12211,7 +12193,7 @@
     </row>
     <row r="238" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="87" t="s">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="B238" s="87"/>
       <c r="C238" s="87"/>
@@ -12231,22 +12213,22 @@
         <v>10</v>
       </c>
       <c r="C239" s="79" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="D239" s="78" t="s">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="E239" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F239" s="70" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="G239" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H239" s="48" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="I239" s="48" t="s">
         <v>12</v>
@@ -12257,7 +12239,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="87" t="s">
-        <v>792</v>
+        <v>773</v>
       </c>
       <c r="B240" s="87"/>
       <c r="C240" s="87"/>
@@ -12277,22 +12259,22 @@
         <v>10</v>
       </c>
       <c r="C241" s="79" t="s">
-        <v>793</v>
+        <v>774</v>
       </c>
       <c r="D241" s="78" t="s">
-        <v>794</v>
+        <v>775</v>
       </c>
       <c r="E241" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F241" s="79" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="G241" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H241" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I241" s="48" t="s">
         <v>12</v>
@@ -12309,22 +12291,22 @@
         <v>10</v>
       </c>
       <c r="C242" s="79" t="s">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="D242" s="78" t="s">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="E242" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F242" s="79" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
       <c r="G242" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H242" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I242" s="48" t="s">
         <v>12</v>
@@ -12341,22 +12323,22 @@
         <v>10</v>
       </c>
       <c r="C243" s="79" t="s">
-        <v>799</v>
+        <v>780</v>
       </c>
       <c r="D243" s="78" t="s">
-        <v>800</v>
+        <v>781</v>
       </c>
       <c r="E243" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F243" s="79" t="s">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="G243" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H243" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I243" s="48" t="s">
         <v>12</v>
@@ -12373,22 +12355,22 @@
         <v>10</v>
       </c>
       <c r="C244" s="79" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="D244" s="78" t="s">
-        <v>802</v>
+        <v>783</v>
       </c>
       <c r="E244" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F244" s="79" t="s">
-        <v>803</v>
+        <v>784</v>
       </c>
       <c r="G244" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H244" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I244" s="48" t="s">
         <v>12</v>
@@ -12405,22 +12387,22 @@
         <v>10</v>
       </c>
       <c r="C245" s="79" t="s">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="D245" s="78" t="s">
-        <v>807</v>
+        <v>788</v>
       </c>
       <c r="E245" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F245" s="79" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="G245" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H245" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I245" s="48" t="s">
         <v>12</v>
@@ -12437,22 +12419,22 @@
         <v>10</v>
       </c>
       <c r="C246" s="79" t="s">
-        <v>808</v>
+        <v>789</v>
       </c>
       <c r="D246" s="78" t="s">
-        <v>809</v>
+        <v>790</v>
       </c>
       <c r="E246" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F246" s="79" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="G246" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H246" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I246" s="48" t="s">
         <v>12</v>
@@ -12469,22 +12451,22 @@
         <v>10</v>
       </c>
       <c r="C247" s="79" t="s">
-        <v>813</v>
+        <v>794</v>
       </c>
       <c r="D247" s="78" t="s">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="E247" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F247" s="79" t="s">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="G247" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H247" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I247" s="48" t="s">
         <v>12</v>
@@ -12501,22 +12483,22 @@
         <v>10</v>
       </c>
       <c r="C248" s="79" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="D248" s="78" t="s">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="E248" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F248" s="79" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="G248" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H248" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I248" s="48" t="s">
         <v>12</v>
@@ -12533,22 +12515,22 @@
         <v>10</v>
       </c>
       <c r="C249" s="79" t="s">
-        <v>819</v>
+        <v>800</v>
       </c>
       <c r="D249" s="78" t="s">
-        <v>820</v>
+        <v>801</v>
       </c>
       <c r="E249" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F249" s="79" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="G249" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H249" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I249" s="48" t="s">
         <v>12</v>
@@ -12565,22 +12547,22 @@
         <v>10</v>
       </c>
       <c r="C250" s="79" t="s">
-        <v>822</v>
+        <v>803</v>
       </c>
       <c r="D250" s="78" t="s">
-        <v>823</v>
+        <v>804</v>
       </c>
       <c r="E250" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F250" s="79" t="s">
-        <v>824</v>
+        <v>805</v>
       </c>
       <c r="G250" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H250" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I250" s="48" t="s">
         <v>12</v>
@@ -12597,22 +12579,22 @@
         <v>10</v>
       </c>
       <c r="C251" s="79" t="s">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="D251" s="78" t="s">
-        <v>827</v>
+        <v>808</v>
       </c>
       <c r="E251" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F251" s="79" t="s">
-        <v>825</v>
+        <v>806</v>
       </c>
       <c r="G251" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H251" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I251" s="48" t="s">
         <v>12</v>
@@ -12629,22 +12611,22 @@
         <v>10</v>
       </c>
       <c r="C252" s="79" t="s">
-        <v>828</v>
+        <v>809</v>
       </c>
       <c r="D252" s="78" t="s">
-        <v>829</v>
+        <v>810</v>
       </c>
       <c r="E252" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F252" s="79" t="s">
-        <v>830</v>
+        <v>811</v>
       </c>
       <c r="G252" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H252" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I252" s="48" t="s">
         <v>12</v>
@@ -12661,22 +12643,22 @@
         <v>10</v>
       </c>
       <c r="C253" s="79" t="s">
-        <v>904</v>
+        <v>885</v>
       </c>
       <c r="D253" s="78" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="E253" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F253" s="79" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G253" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H253" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I253" s="48" t="s">
         <v>12</v>
@@ -12693,22 +12675,22 @@
         <v>10</v>
       </c>
       <c r="C254" s="79" t="s">
-        <v>909</v>
+        <v>890</v>
       </c>
       <c r="D254" s="78" t="s">
-        <v>910</v>
+        <v>891</v>
       </c>
       <c r="E254" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F254" s="79" t="s">
-        <v>907</v>
+        <v>888</v>
       </c>
       <c r="G254" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H254" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I254" s="48" t="s">
         <v>12</v>
@@ -12725,22 +12707,22 @@
         <v>10</v>
       </c>
       <c r="C255" s="79" t="s">
-        <v>911</v>
+        <v>892</v>
       </c>
       <c r="D255" s="78" t="s">
-        <v>912</v>
+        <v>893</v>
       </c>
       <c r="E255" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F255" s="79" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G255" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H255" s="48" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="I255" s="48" t="s">
         <v>12</v>
@@ -12751,7 +12733,7 @@
     </row>
     <row r="256" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="87" t="s">
-        <v>837</v>
+        <v>818</v>
       </c>
       <c r="B256" s="87"/>
       <c r="C256" s="87"/>
@@ -12771,22 +12753,22 @@
         <v>10</v>
       </c>
       <c r="C257" s="79" t="s">
-        <v>871</v>
+        <v>852</v>
       </c>
       <c r="D257" s="78" t="s">
-        <v>872</v>
+        <v>853</v>
       </c>
       <c r="E257" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F257" s="70" t="s">
-        <v>870</v>
+        <v>851</v>
       </c>
       <c r="G257" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H257" s="48" t="s">
-        <v>873</v>
+        <v>854</v>
       </c>
       <c r="I257" s="48" t="s">
         <v>12</v>
@@ -12803,22 +12785,22 @@
         <v>10</v>
       </c>
       <c r="C258" s="79" t="s">
-        <v>875</v>
+        <v>856</v>
       </c>
       <c r="D258" s="78" t="s">
-        <v>876</v>
+        <v>857</v>
       </c>
       <c r="E258" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F258" s="70" t="s">
-        <v>874</v>
+        <v>855</v>
       </c>
       <c r="G258" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H258" s="48" t="s">
-        <v>873</v>
+        <v>854</v>
       </c>
       <c r="I258" s="48" t="s">
         <v>12</v>
@@ -12829,7 +12811,7 @@
     </row>
     <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="87" t="s">
-        <v>838</v>
+        <v>819</v>
       </c>
       <c r="B259" s="87"/>
       <c r="C259" s="87"/>
@@ -12849,22 +12831,22 @@
         <v>10</v>
       </c>
       <c r="C260" s="79" t="s">
-        <v>839</v>
+        <v>820</v>
       </c>
       <c r="D260" s="78" t="s">
-        <v>842</v>
+        <v>823</v>
       </c>
       <c r="E260" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F260" s="70" t="s">
-        <v>840</v>
+        <v>821</v>
       </c>
       <c r="G260" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H260" s="48" t="s">
-        <v>841</v>
+        <v>822</v>
       </c>
       <c r="I260" s="48" t="s">
         <v>12</v>
@@ -12881,22 +12863,22 @@
         <v>10</v>
       </c>
       <c r="C261" s="79" t="s">
-        <v>843</v>
+        <v>824</v>
       </c>
       <c r="D261" s="78" t="s">
-        <v>845</v>
+        <v>826</v>
       </c>
       <c r="E261" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F261" s="70" t="s">
-        <v>844</v>
+        <v>825</v>
       </c>
       <c r="G261" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H261" s="48" t="s">
-        <v>841</v>
+        <v>822</v>
       </c>
       <c r="I261" s="48" t="s">
         <v>12</v>
@@ -12913,22 +12895,22 @@
         <v>10</v>
       </c>
       <c r="C262" s="79" t="s">
-        <v>847</v>
+        <v>828</v>
       </c>
       <c r="D262" s="78" t="s">
-        <v>848</v>
+        <v>829</v>
       </c>
       <c r="E262" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F262" s="70" t="s">
-        <v>846</v>
+        <v>827</v>
       </c>
       <c r="G262" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H262" s="48" t="s">
-        <v>841</v>
+        <v>822</v>
       </c>
       <c r="I262" s="48" t="s">
         <v>12</v>
@@ -12945,22 +12927,22 @@
         <v>10</v>
       </c>
       <c r="C263" s="79" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
       <c r="D263" s="78" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="E263" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F263" s="70" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="G263" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H263" s="48" t="s">
-        <v>841</v>
+        <v>822</v>
       </c>
       <c r="I263" s="48" t="s">
         <v>12</v>
@@ -12977,22 +12959,22 @@
         <v>10</v>
       </c>
       <c r="C264" s="79" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="D264" s="78" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="E264" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F264" s="70" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="G264" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H264" s="48" t="s">
-        <v>841</v>
+        <v>822</v>
       </c>
       <c r="I264" s="48" t="s">
         <v>12</v>
@@ -13003,7 +12985,7 @@
     </row>
     <row r="265" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="87" t="s">
-        <v>914</v>
+        <v>895</v>
       </c>
       <c r="B265" s="87"/>
       <c r="C265" s="87"/>
@@ -13023,22 +13005,22 @@
         <v>10</v>
       </c>
       <c r="C266" s="79" t="s">
-        <v>915</v>
+        <v>896</v>
       </c>
       <c r="D266" s="78" t="s">
-        <v>916</v>
+        <v>897</v>
       </c>
       <c r="E266" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F266" s="70" t="s">
-        <v>913</v>
+        <v>894</v>
       </c>
       <c r="G266" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H266" s="48" t="s">
-        <v>917</v>
+        <v>898</v>
       </c>
       <c r="I266" s="48" t="s">
         <v>12</v>
@@ -13047,33 +13029,112 @@
         <v>13</v>
       </c>
     </row>
+    <row r="267" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="87" t="s">
+        <v>922</v>
+      </c>
+      <c r="B267" s="87"/>
+      <c r="C267" s="87"/>
+      <c r="D267" s="87"/>
+      <c r="E267" s="87"/>
+      <c r="F267" s="87"/>
+      <c r="G267" s="87"/>
+      <c r="H267" s="87"/>
+      <c r="I267" s="87"/>
+      <c r="J267" s="87"/>
+    </row>
+    <row r="268" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="48">
+        <v>1</v>
+      </c>
+      <c r="B268" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C268" s="79" t="s">
+        <v>923</v>
+      </c>
+      <c r="D268" s="78" t="s">
+        <v>924</v>
+      </c>
+      <c r="E268" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F268" s="70" t="s">
+        <v>921</v>
+      </c>
+      <c r="G268" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H268" s="48" t="s">
+        <v>925</v>
+      </c>
+      <c r="I268" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J268" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="48">
+        <v>2</v>
+      </c>
+      <c r="B269" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C269" s="79" t="s">
+        <v>926</v>
+      </c>
+      <c r="D269" s="78" t="s">
+        <v>927</v>
+      </c>
+      <c r="E269" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F269" s="70" t="s">
+        <v>928</v>
+      </c>
+      <c r="G269" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H269" s="48" t="s">
+        <v>925</v>
+      </c>
+      <c r="I269" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J269" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A256:J256"/>
-    <mergeCell ref="A240:J240"/>
+  <mergeCells count="26">
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="A121:J121"/>
+    <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A203:J203"/>
+    <mergeCell ref="A198:J198"/>
     <mergeCell ref="A133:J133"/>
     <mergeCell ref="A190:J190"/>
     <mergeCell ref="A145:J145"/>
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
-    <mergeCell ref="A238:J238"/>
-    <mergeCell ref="A265:J265"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A37:J37"/>
     <mergeCell ref="A55:J55"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A267:J267"/>
+    <mergeCell ref="A265:J265"/>
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A226:J226"/>
     <mergeCell ref="A259:J259"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="A121:J121"/>
-    <mergeCell ref="A123:J123"/>
-    <mergeCell ref="A125:J125"/>
-    <mergeCell ref="A203:J203"/>
-    <mergeCell ref="A198:J198"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A240:J240"/>
+    <mergeCell ref="A238:J238"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13171,7 +13232,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AF249"/>
+  <dimension ref="A1:AF251"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -13259,37 +13320,37 @@
         <v>134</v>
       </c>
       <c r="T1" s="30" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="U1" s="30" t="s">
         <v>490</v>
       </c>
       <c r="V1" s="30" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="W1" s="30" t="s">
         <v>346</v>
       </c>
       <c r="X1" s="30" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="Y1" s="31" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="Z1" s="31" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="AA1" s="31" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="AB1" s="31" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AC1" s="31" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AD1" s="31" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
@@ -17406,7 +17467,7 @@
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A53" s="47" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B53" s="48" t="s">
         <v>22</v>
@@ -22320,7 +22381,7 @@
     </row>
     <row r="112" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A112" s="48" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="B112" s="48" t="s">
         <v>22</v>
@@ -22383,7 +22444,7 @@
         <v>22</v>
       </c>
       <c r="V112" s="36" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="W112" s="28" t="s">
         <v>22</v>
@@ -22404,7 +22465,7 @@
     </row>
     <row r="113" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="B113" s="48" t="s">
         <v>22</v>
@@ -22488,7 +22549,7 @@
     </row>
     <row r="114" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A114" s="48" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="B114" s="48" t="s">
         <v>22</v>
@@ -22554,13 +22615,13 @@
         <v>22</v>
       </c>
       <c r="W114" s="28" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="X114" s="28" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="Y114" s="48" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="Z114" s="48" t="s">
         <v>22</v>
@@ -22572,7 +22633,7 @@
     </row>
     <row r="115" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A115" s="48" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="B115" s="48" t="s">
         <v>22</v>
@@ -22647,7 +22708,7 @@
         <v>22</v>
       </c>
       <c r="Z115" s="36" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="AA115" s="28"/>
       <c r="AB115" s="28"/>
@@ -24336,7 +24397,7 @@
     </row>
     <row r="136" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A136" s="48" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B136" s="48" t="s">
         <v>22</v>
@@ -25824,7 +25885,7 @@
         <v>22</v>
       </c>
       <c r="U153" s="48" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="V153" s="48" t="s">
         <v>22</v>
@@ -27444,7 +27505,7 @@
     </row>
     <row r="173" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="76" t="s">
-        <v>897</v>
+        <v>878</v>
       </c>
       <c r="B173" s="48" t="s">
         <v>22</v>
@@ -27498,7 +27559,7 @@
         <v>22</v>
       </c>
       <c r="S173" s="48" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="T173" s="48" t="s">
         <v>22</v>
@@ -27528,7 +27589,7 @@
     </row>
     <row r="174" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="76" t="s">
-        <v>900</v>
+        <v>881</v>
       </c>
       <c r="B174" s="48" t="s">
         <v>22</v>
@@ -27582,7 +27643,7 @@
         <v>22</v>
       </c>
       <c r="S174" s="48" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="T174" s="48" t="s">
         <v>22</v>
@@ -27612,7 +27673,7 @@
     </row>
     <row r="175" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="76" t="s">
-        <v>903</v>
+        <v>884</v>
       </c>
       <c r="B175" s="48" t="s">
         <v>22</v>
@@ -27666,7 +27727,7 @@
         <v>22</v>
       </c>
       <c r="S175" s="48" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="T175" s="48" t="s">
         <v>22</v>
@@ -27694,9 +27755,9 @@
       <c r="AC175" s="48"/>
       <c r="AD175" s="48"/>
     </row>
-    <row r="176" spans="1:30" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="70" t="s">
-        <v>601</v>
+        <v>175</v>
       </c>
       <c r="B176" s="48" t="s">
         <v>22</v>
@@ -27750,7 +27811,7 @@
         <v>22</v>
       </c>
       <c r="S176" s="49" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="T176" s="48" t="s">
         <v>22</v>
@@ -27773,11 +27834,9 @@
       <c r="Z176" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="AA176" s="48" t="s">
-        <v>740</v>
-      </c>
+      <c r="AA176" s="48"/>
       <c r="AB176" s="36" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AC176" s="48" t="s">
         <v>22</v>
@@ -27788,7 +27847,7 @@
     </row>
     <row r="177" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="70" t="s">
-        <v>604</v>
+        <v>179</v>
       </c>
       <c r="B177" s="48" t="s">
         <v>22</v>
@@ -27842,7 +27901,7 @@
         <v>22</v>
       </c>
       <c r="S177" s="49" t="s">
-        <v>920</v>
+        <v>929</v>
       </c>
       <c r="T177" s="48" t="s">
         <v>22</v>
@@ -27872,7 +27931,7 @@
         <v>22</v>
       </c>
       <c r="AC177" s="73" t="s">
-        <v>832</v>
+        <v>813</v>
       </c>
       <c r="AD177" s="48" t="s">
         <v>22</v>
@@ -27880,7 +27939,7 @@
     </row>
     <row r="178" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="70" t="s">
-        <v>606</v>
+        <v>182</v>
       </c>
       <c r="B178" s="48" t="s">
         <v>22</v>
@@ -27934,7 +27993,7 @@
         <v>22</v>
       </c>
       <c r="S178" s="49" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="T178" s="48" t="s">
         <v>22</v>
@@ -27964,15 +28023,15 @@
         <v>22</v>
       </c>
       <c r="AC178" s="73" t="s">
-        <v>832</v>
+        <v>813</v>
       </c>
       <c r="AD178" s="48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="70" t="s">
-        <v>607</v>
+        <v>185</v>
       </c>
       <c r="B179" s="48" t="s">
         <v>22</v>
@@ -28026,7 +28085,7 @@
         <v>22</v>
       </c>
       <c r="S179" s="49" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="T179" s="48" t="s">
         <v>22</v>
@@ -28049,11 +28108,9 @@
       <c r="Z179" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="AA179" s="48" t="s">
-        <v>741</v>
-      </c>
+      <c r="AA179" s="48"/>
       <c r="AB179" s="36" t="s">
-        <v>22</v>
+        <v>602</v>
       </c>
       <c r="AC179" s="48" t="s">
         <v>22</v>
@@ -28064,7 +28121,7 @@
     </row>
     <row r="180" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="70" t="s">
-        <v>609</v>
+        <v>188</v>
       </c>
       <c r="B180" s="48" t="s">
         <v>22</v>
@@ -28118,7 +28175,7 @@
         <v>22</v>
       </c>
       <c r="S180" s="49" t="s">
-        <v>920</v>
+        <v>929</v>
       </c>
       <c r="T180" s="48" t="s">
         <v>22</v>
@@ -28147,8 +28204,8 @@
       <c r="AB180" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="AC180" s="48" t="s">
-        <v>22</v>
+      <c r="AC180" s="73" t="s">
+        <v>813</v>
       </c>
       <c r="AD180" s="48" t="s">
         <v>22</v>
@@ -28156,7 +28213,7 @@
     </row>
     <row r="181" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="70" t="s">
-        <v>610</v>
+        <v>190</v>
       </c>
       <c r="B181" s="48" t="s">
         <v>22</v>
@@ -28210,7 +28267,7 @@
         <v>22</v>
       </c>
       <c r="S181" s="49" t="s">
-        <v>920</v>
+        <v>929</v>
       </c>
       <c r="T181" s="48" t="s">
         <v>22</v>
@@ -28240,7 +28297,7 @@
         <v>22</v>
       </c>
       <c r="AC181" s="73" t="s">
-        <v>832</v>
+        <v>813</v>
       </c>
       <c r="AD181" s="48" t="s">
         <v>22</v>
@@ -28248,7 +28305,7 @@
     </row>
     <row r="182" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="70" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B182" s="48" t="s">
         <v>22</v>
@@ -28302,7 +28359,7 @@
         <v>22</v>
       </c>
       <c r="S182" s="49" t="s">
-        <v>921</v>
+        <v>901</v>
       </c>
       <c r="T182" s="48" t="s">
         <v>22</v>
@@ -28340,7 +28397,7 @@
     </row>
     <row r="183" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="70" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B183" s="48" t="s">
         <v>22</v>
@@ -28394,7 +28451,7 @@
         <v>22</v>
       </c>
       <c r="S183" s="49" t="s">
-        <v>922</v>
+        <v>902</v>
       </c>
       <c r="T183" s="48" t="s">
         <v>22</v>
@@ -28432,7 +28489,7 @@
     </row>
     <row r="184" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="70" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B184" s="48" t="s">
         <v>22</v>
@@ -28486,7 +28543,7 @@
         <v>22</v>
       </c>
       <c r="S184" s="49" t="s">
-        <v>923</v>
+        <v>903</v>
       </c>
       <c r="T184" s="48" t="s">
         <v>22</v>
@@ -28524,7 +28581,7 @@
     </row>
     <row r="185" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="70" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B185" s="48" t="s">
         <v>22</v>
@@ -28578,7 +28635,7 @@
         <v>22</v>
       </c>
       <c r="S185" s="49" t="s">
-        <v>922</v>
+        <v>902</v>
       </c>
       <c r="T185" s="48" t="s">
         <v>22</v>
@@ -28611,15 +28668,15 @@
         <v>22</v>
       </c>
       <c r="AD185" s="81" t="s">
-        <v>833</v>
+        <v>814</v>
       </c>
       <c r="AF185" s="48" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="186" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="70" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B186" s="48" t="s">
         <v>22</v>
@@ -28673,7 +28730,7 @@
         <v>22</v>
       </c>
       <c r="S186" s="49" t="s">
-        <v>923</v>
+        <v>903</v>
       </c>
       <c r="T186" s="48" t="s">
         <v>22</v>
@@ -28706,15 +28763,15 @@
         <v>22</v>
       </c>
       <c r="AD186" s="81" t="s">
-        <v>834</v>
+        <v>815</v>
       </c>
       <c r="AF186" s="48" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="187" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="70" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B187" s="48" t="s">
         <v>22</v>
@@ -28801,15 +28858,15 @@
         <v>22</v>
       </c>
       <c r="AD187" s="82" t="s">
-        <v>835</v>
+        <v>816</v>
       </c>
       <c r="AF187" s="48" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="188" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="70" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B188" s="48" t="s">
         <v>22</v>
@@ -28896,15 +28953,15 @@
         <v>22</v>
       </c>
       <c r="AD188" s="78" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="AE188" s="78" t="s">
-        <v>836</v>
+        <v>817</v>
       </c>
     </row>
     <row r="189" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="70" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B189" s="48" t="s">
         <v>22</v>
@@ -28991,12 +29048,12 @@
         <v>22</v>
       </c>
       <c r="AD189" s="78" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="190" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="70" t="s">
-        <v>849</v>
+        <v>830</v>
       </c>
       <c r="B190" s="48" t="s">
         <v>22</v>
@@ -29083,12 +29140,12 @@
         <v>22</v>
       </c>
       <c r="AD190" s="78" t="s">
-        <v>851</v>
+        <v>832</v>
       </c>
     </row>
     <row r="191" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="70" t="s">
-        <v>850</v>
+        <v>831</v>
       </c>
       <c r="B191" s="48" t="s">
         <v>22</v>
@@ -29175,12 +29232,12 @@
         <v>22</v>
       </c>
       <c r="AD191" s="78" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
     </row>
     <row r="192" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="70" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B192" s="48" t="s">
         <v>22</v>
@@ -29272,7 +29329,7 @@
     </row>
     <row r="193" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="70" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B193" s="48" t="s">
         <v>22</v>
@@ -29364,7 +29421,7 @@
     </row>
     <row r="194" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="70" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B194" s="48" t="s">
         <v>22</v>
@@ -29456,7 +29513,7 @@
     </row>
     <row r="195" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="70" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B195" s="48" t="s">
         <v>22</v>
@@ -29548,7 +29605,7 @@
     </row>
     <row r="196" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="70" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B196" s="48" t="s">
         <v>22</v>
@@ -29602,7 +29659,7 @@
         <v>22</v>
       </c>
       <c r="S196" s="49" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="T196" s="48" t="s">
         <v>22</v>
@@ -29632,7 +29689,7 @@
         <v>22</v>
       </c>
       <c r="AC196" s="73" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="AD196" s="48" t="s">
         <v>22</v>
@@ -29640,7 +29697,7 @@
     </row>
     <row r="197" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="70" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="B197" s="48" t="s">
         <v>22</v>
@@ -29694,7 +29751,7 @@
         <v>22</v>
       </c>
       <c r="S197" s="49" t="s">
-        <v>922</v>
+        <v>902</v>
       </c>
       <c r="T197" s="48" t="s">
         <v>22</v>
@@ -29732,7 +29789,7 @@
     </row>
     <row r="198" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="70" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="B198" s="48" t="s">
         <v>22</v>
@@ -29786,7 +29843,7 @@
         <v>22</v>
       </c>
       <c r="S198" s="49" t="s">
-        <v>923</v>
+        <v>903</v>
       </c>
       <c r="T198" s="48" t="s">
         <v>22</v>
@@ -29824,7 +29881,7 @@
     </row>
     <row r="199" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="70" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B199" s="48" t="s">
         <v>22</v>
@@ -29878,7 +29935,7 @@
         <v>22</v>
       </c>
       <c r="S199" s="49" t="s">
-        <v>924</v>
+        <v>904</v>
       </c>
       <c r="T199" s="48" t="s">
         <v>22</v>
@@ -29916,7 +29973,7 @@
     </row>
     <row r="200" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="70" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="B200" s="48" t="s">
         <v>22</v>
@@ -29970,7 +30027,7 @@
         <v>22</v>
       </c>
       <c r="S200" s="49" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="T200" s="48" t="s">
         <v>22</v>
@@ -30008,7 +30065,7 @@
     </row>
     <row r="201" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="70" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B201" s="48" t="s">
         <v>22</v>
@@ -30062,7 +30119,7 @@
         <v>22</v>
       </c>
       <c r="S201" s="49" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="T201" s="48" t="s">
         <v>22</v>
@@ -30100,7 +30157,7 @@
     </row>
     <row r="202" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="70" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="B202" s="48" t="s">
         <v>22</v>
@@ -30154,7 +30211,7 @@
         <v>22</v>
       </c>
       <c r="S202" s="49" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="T202" s="48" t="s">
         <v>22</v>
@@ -30192,7 +30249,7 @@
     </row>
     <row r="203" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="70" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B203" s="48" t="s">
         <v>22</v>
@@ -30246,7 +30303,7 @@
         <v>22</v>
       </c>
       <c r="S203" s="49" t="s">
-        <v>927</v>
+        <v>907</v>
       </c>
       <c r="T203" s="48" t="s">
         <v>22</v>
@@ -30284,7 +30341,7 @@
     </row>
     <row r="204" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="70" t="s">
-        <v>879</v>
+        <v>860</v>
       </c>
       <c r="B204" s="48" t="s">
         <v>22</v>
@@ -30338,7 +30395,7 @@
         <v>22</v>
       </c>
       <c r="S204" s="49" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="T204" s="48" t="s">
         <v>22</v>
@@ -30376,7 +30433,7 @@
     </row>
     <row r="205" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="70" t="s">
-        <v>882</v>
+        <v>863</v>
       </c>
       <c r="B205" s="48" t="s">
         <v>22</v>
@@ -30430,7 +30487,7 @@
         <v>22</v>
       </c>
       <c r="S205" s="49" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="T205" s="48" t="s">
         <v>22</v>
@@ -30468,7 +30525,7 @@
     </row>
     <row r="206" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="70" t="s">
-        <v>883</v>
+        <v>864</v>
       </c>
       <c r="B206" s="48" t="s">
         <v>22</v>
@@ -30522,7 +30579,7 @@
         <v>22</v>
       </c>
       <c r="S206" s="49" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="T206" s="48" t="s">
         <v>22</v>
@@ -30560,7 +30617,7 @@
     </row>
     <row r="207" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="70" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="B207" s="48" t="s">
         <v>22</v>
@@ -30614,7 +30671,7 @@
         <v>22</v>
       </c>
       <c r="S207" s="49" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="T207" s="48" t="s">
         <v>22</v>
@@ -30652,7 +30709,7 @@
     </row>
     <row r="208" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="70" t="s">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="B208" s="48" t="s">
         <v>22</v>
@@ -30706,7 +30763,7 @@
         <v>22</v>
       </c>
       <c r="S208" s="49" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
       <c r="T208" s="48" t="s">
         <v>22</v>
@@ -30744,7 +30801,7 @@
     </row>
     <row r="209" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="70" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
       <c r="B209" s="48" t="s">
         <v>22</v>
@@ -30798,7 +30855,7 @@
         <v>22</v>
       </c>
       <c r="S209" s="49" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
       <c r="T209" s="48" t="s">
         <v>22</v>
@@ -30836,7 +30893,7 @@
     </row>
     <row r="210" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="70" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="B210" s="48" t="s">
         <v>22</v>
@@ -30890,7 +30947,7 @@
         <v>22</v>
       </c>
       <c r="S210" s="49" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
       <c r="T210" s="48" t="s">
         <v>22</v>
@@ -30928,7 +30985,7 @@
     </row>
     <row r="211" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="70" t="s">
-        <v>866</v>
+        <v>847</v>
       </c>
       <c r="B211" s="48" t="s">
         <v>22</v>
@@ -30982,10 +31039,10 @@
         <v>22</v>
       </c>
       <c r="S211" s="49" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
       <c r="T211" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="U211" s="48" t="s">
         <v>22</v>
@@ -31020,7 +31077,7 @@
     </row>
     <row r="212" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="70" t="s">
-        <v>867</v>
+        <v>848</v>
       </c>
       <c r="B212" s="48" t="s">
         <v>22</v>
@@ -31074,10 +31131,10 @@
         <v>22</v>
       </c>
       <c r="S212" s="49" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
       <c r="T212" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="U212" s="48" t="s">
         <v>22</v>
@@ -31112,7 +31169,7 @@
     </row>
     <row r="213" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="70" t="s">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="B213" s="48" t="s">
         <v>22</v>
@@ -31166,7 +31223,7 @@
         <v>22</v>
       </c>
       <c r="S213" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T213" s="48" t="s">
         <v>22</v>
@@ -31204,7 +31261,7 @@
     </row>
     <row r="214" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="70" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="B214" s="48" t="s">
         <v>22</v>
@@ -31258,7 +31315,7 @@
         <v>22</v>
       </c>
       <c r="S214" s="49" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="T214" s="48" t="s">
         <v>22</v>
@@ -31296,7 +31353,7 @@
     </row>
     <row r="215" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="70" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="B215" s="48" t="s">
         <v>22</v>
@@ -31350,7 +31407,7 @@
         <v>22</v>
       </c>
       <c r="S215" s="49" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="T215" s="48" t="s">
         <v>22</v>
@@ -31388,7 +31445,7 @@
     </row>
     <row r="216" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="70" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="B216" s="48" t="s">
         <v>22</v>
@@ -31442,7 +31499,7 @@
         <v>22</v>
       </c>
       <c r="S216" s="49" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="T216" s="48" t="s">
         <v>22</v>
@@ -31480,7 +31537,7 @@
     </row>
     <row r="217" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="70" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
       <c r="B217" s="48" t="s">
         <v>22</v>
@@ -31534,7 +31591,7 @@
         <v>22</v>
       </c>
       <c r="S217" s="49" t="s">
-        <v>933</v>
+        <v>913</v>
       </c>
       <c r="T217" s="48" t="s">
         <v>22</v>
@@ -31572,7 +31629,7 @@
     </row>
     <row r="218" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="70" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="B218" s="48" t="s">
         <v>22</v>
@@ -31626,7 +31683,7 @@
         <v>22</v>
       </c>
       <c r="S218" s="49" t="s">
-        <v>934</v>
+        <v>914</v>
       </c>
       <c r="T218" s="48" t="s">
         <v>22</v>
@@ -31664,7 +31721,7 @@
     </row>
     <row r="219" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="70" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="B219" s="48" t="s">
         <v>22</v>
@@ -31718,7 +31775,7 @@
         <v>22</v>
       </c>
       <c r="S219" s="49" t="s">
-        <v>935</v>
+        <v>915</v>
       </c>
       <c r="T219" s="48" t="s">
         <v>22</v>
@@ -31756,7 +31813,7 @@
     </row>
     <row r="220" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="70" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="B220" s="48" t="s">
         <v>22</v>
@@ -31810,7 +31867,7 @@
         <v>22</v>
       </c>
       <c r="S220" s="49" t="s">
-        <v>936</v>
+        <v>916</v>
       </c>
       <c r="T220" s="48" t="s">
         <v>22</v>
@@ -31848,7 +31905,7 @@
     </row>
     <row r="221" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="70" t="s">
-        <v>769</v>
+        <v>750</v>
       </c>
       <c r="B221" s="48" t="s">
         <v>22</v>
@@ -31902,7 +31959,7 @@
         <v>22</v>
       </c>
       <c r="S221" s="49" t="s">
-        <v>937</v>
+        <v>917</v>
       </c>
       <c r="T221" s="48" t="s">
         <v>22</v>
@@ -31940,7 +31997,7 @@
     </row>
     <row r="222" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="70" t="s">
-        <v>772</v>
+        <v>753</v>
       </c>
       <c r="B222" s="48" t="s">
         <v>22</v>
@@ -31994,7 +32051,7 @@
         <v>22</v>
       </c>
       <c r="S222" s="49" t="s">
-        <v>938</v>
+        <v>918</v>
       </c>
       <c r="T222" s="48" t="s">
         <v>22</v>
@@ -32032,7 +32089,7 @@
     </row>
     <row r="223" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="70" t="s">
-        <v>773</v>
+        <v>754</v>
       </c>
       <c r="B223" s="48" t="s">
         <v>22</v>
@@ -32086,7 +32143,7 @@
         <v>22</v>
       </c>
       <c r="S223" s="49" t="s">
-        <v>939</v>
+        <v>919</v>
       </c>
       <c r="T223" s="48" t="s">
         <v>22</v>
@@ -32124,7 +32181,7 @@
     </row>
     <row r="224" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="70" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="B224" s="48" t="s">
         <v>22</v>
@@ -32178,7 +32235,7 @@
         <v>22</v>
       </c>
       <c r="S224" s="49" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="T224" s="48" t="s">
         <v>22</v>
@@ -32216,7 +32273,7 @@
     </row>
     <row r="225" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="70" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="B225" s="48" t="s">
         <v>22</v>
@@ -32270,7 +32327,7 @@
         <v>22</v>
       </c>
       <c r="S225" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T225" s="48" t="s">
         <v>22</v>
@@ -32300,15 +32357,15 @@
         <v>22</v>
       </c>
       <c r="AC225" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD225" s="73" t="s">
-        <v>815</v>
+        <v>796</v>
       </c>
     </row>
     <row r="226" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="70" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
       <c r="B226" s="48" t="s">
         <v>22</v>
@@ -32362,7 +32419,7 @@
         <v>22</v>
       </c>
       <c r="S226" s="49" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="T226" s="48" t="s">
         <v>22</v>
@@ -32392,7 +32449,7 @@
         <v>22</v>
       </c>
       <c r="AC226" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD226" s="48" t="s">
         <v>22</v>
@@ -32400,7 +32457,7 @@
     </row>
     <row r="227" spans="1:30" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="70" t="s">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="B227" s="48" t="s">
         <v>22</v>
@@ -32454,10 +32511,10 @@
         <v>22</v>
       </c>
       <c r="S227" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T227" s="49" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="U227" s="48" t="s">
         <v>22</v>
@@ -32484,7 +32541,7 @@
         <v>22</v>
       </c>
       <c r="AC227" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD227" s="48" t="s">
         <v>22</v>
@@ -32492,7 +32549,7 @@
     </row>
     <row r="228" spans="1:30" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="70" t="s">
-        <v>803</v>
+        <v>784</v>
       </c>
       <c r="B228" s="48" t="s">
         <v>22</v>
@@ -32546,10 +32603,10 @@
         <v>22</v>
       </c>
       <c r="S228" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T228" s="49" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="U228" s="48" t="s">
         <v>22</v>
@@ -32576,7 +32633,7 @@
         <v>22</v>
       </c>
       <c r="AC228" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD228" s="48" t="s">
         <v>22</v>
@@ -32584,7 +32641,7 @@
     </row>
     <row r="229" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="70" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="B229" s="48" t="s">
         <v>22</v>
@@ -32638,10 +32695,10 @@
         <v>22</v>
       </c>
       <c r="S229" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T229" s="48" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="U229" s="48" t="s">
         <v>22</v>
@@ -32668,7 +32725,7 @@
         <v>22</v>
       </c>
       <c r="AC229" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD229" s="48" t="s">
         <v>22</v>
@@ -32676,7 +32733,7 @@
     </row>
     <row r="230" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="70" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="B230" s="48" t="s">
         <v>22</v>
@@ -32730,7 +32787,7 @@
         <v>22</v>
       </c>
       <c r="S230" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T230" s="48" t="s">
         <v>22</v>
@@ -32760,7 +32817,7 @@
         <v>22</v>
       </c>
       <c r="AC230" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD230" s="48" t="s">
         <v>22</v>
@@ -32768,99 +32825,99 @@
     </row>
     <row r="231" spans="1:30" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="70" t="s">
+        <v>793</v>
+      </c>
+      <c r="B231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S231" s="49" t="s">
+        <v>910</v>
+      </c>
+      <c r="T231" s="49" t="s">
+        <v>911</v>
+      </c>
+      <c r="U231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V231" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W231" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X231" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA231" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB231" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC231" s="73" t="s">
         <v>812</v>
       </c>
-      <c r="B231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S231" s="49" t="s">
-        <v>930</v>
-      </c>
-      <c r="T231" s="49" t="s">
-        <v>931</v>
-      </c>
-      <c r="U231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V231" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W231" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X231" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA231" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB231" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC231" s="73" t="s">
-        <v>831</v>
-      </c>
       <c r="AD231" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
     </row>
     <row r="232" spans="1:30" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="70" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="B232" s="48" t="s">
         <v>22</v>
@@ -32914,10 +32971,10 @@
         <v>22</v>
       </c>
       <c r="S232" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T232" s="49" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="U232" s="48" t="s">
         <v>22</v>
@@ -32944,7 +33001,7 @@
         <v>22</v>
       </c>
       <c r="AC232" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD232" s="48" t="s">
         <v>22</v>
@@ -32952,7 +33009,7 @@
     </row>
     <row r="233" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="70" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="B233" s="48" t="s">
         <v>22</v>
@@ -33006,7 +33063,7 @@
         <v>22</v>
       </c>
       <c r="S233" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T233" s="48" t="s">
         <v>22</v>
@@ -33036,7 +33093,7 @@
         <v>22</v>
       </c>
       <c r="AC233" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD233" s="48" t="s">
         <v>22</v>
@@ -33044,7 +33101,7 @@
     </row>
     <row r="234" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="70" t="s">
-        <v>824</v>
+        <v>805</v>
       </c>
       <c r="B234" s="48" t="s">
         <v>22</v>
@@ -33098,10 +33155,10 @@
         <v>22</v>
       </c>
       <c r="S234" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T234" s="49" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="U234" s="48" t="s">
         <v>22</v>
@@ -33128,7 +33185,7 @@
         <v>22</v>
       </c>
       <c r="AC234" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD234" s="48" t="s">
         <v>22</v>
@@ -33136,7 +33193,7 @@
     </row>
     <row r="235" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="70" t="s">
-        <v>825</v>
+        <v>806</v>
       </c>
       <c r="B235" s="48" t="s">
         <v>22</v>
@@ -33190,10 +33247,10 @@
         <v>22</v>
       </c>
       <c r="S235" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T235" s="49" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="U235" s="48" t="s">
         <v>22</v>
@@ -33220,7 +33277,7 @@
         <v>22</v>
       </c>
       <c r="AC235" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD235" s="48" t="s">
         <v>22</v>
@@ -33228,7 +33285,7 @@
     </row>
     <row r="236" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="70" t="s">
-        <v>830</v>
+        <v>811</v>
       </c>
       <c r="B236" s="48" t="s">
         <v>22</v>
@@ -33282,10 +33339,10 @@
         <v>22</v>
       </c>
       <c r="S236" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T236" s="49" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="U236" s="48" t="s">
         <v>22</v>
@@ -33312,7 +33369,7 @@
         <v>22</v>
       </c>
       <c r="AC236" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD236" s="48" t="s">
         <v>22</v>
@@ -33320,7 +33377,7 @@
     </row>
     <row r="237" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="70" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="B237" s="48" t="s">
         <v>22</v>
@@ -33374,10 +33431,10 @@
         <v>22</v>
       </c>
       <c r="S237" s="49" t="s">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="T237" s="49" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="U237" s="48" t="s">
         <v>22</v>
@@ -33404,7 +33461,7 @@
         <v>22</v>
       </c>
       <c r="AC237" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD237" s="48" t="s">
         <v>22</v>
@@ -33412,7 +33469,7 @@
     </row>
     <row r="238" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="70" t="s">
-        <v>907</v>
+        <v>888</v>
       </c>
       <c r="B238" s="48" t="s">
         <v>22</v>
@@ -33466,10 +33523,10 @@
         <v>22</v>
       </c>
       <c r="S238" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T238" s="49" t="s">
-        <v>938</v>
+        <v>918</v>
       </c>
       <c r="U238" s="48" t="s">
         <v>22</v>
@@ -33496,7 +33553,7 @@
         <v>22</v>
       </c>
       <c r="AC238" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD238" s="48" t="s">
         <v>22</v>
@@ -33504,7 +33561,7 @@
     </row>
     <row r="239" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="70" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="B239" s="48" t="s">
         <v>22</v>
@@ -33558,16 +33615,16 @@
         <v>22</v>
       </c>
       <c r="S239" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T239" s="49" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="U239" s="49" t="s">
-        <v>938</v>
+        <v>918</v>
       </c>
       <c r="V239" s="48" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="W239" s="28" t="s">
         <v>22</v>
@@ -33588,7 +33645,7 @@
         <v>22</v>
       </c>
       <c r="AC239" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD239" s="48" t="s">
         <v>22</v>
@@ -33596,7 +33653,7 @@
     </row>
     <row r="240" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="70" t="s">
-        <v>870</v>
+        <v>851</v>
       </c>
       <c r="B240" s="48" t="s">
         <v>22</v>
@@ -33688,7 +33745,7 @@
     </row>
     <row r="241" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="70" t="s">
-        <v>874</v>
+        <v>855</v>
       </c>
       <c r="B241" s="48" t="s">
         <v>22</v>
@@ -33780,7 +33837,7 @@
     </row>
     <row r="242" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="70" t="s">
-        <v>840</v>
+        <v>821</v>
       </c>
       <c r="B242" s="48" t="s">
         <v>22</v>
@@ -33872,7 +33929,7 @@
     </row>
     <row r="243" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="70" t="s">
-        <v>844</v>
+        <v>825</v>
       </c>
       <c r="B243" s="48" t="s">
         <v>22</v>
@@ -33926,7 +33983,7 @@
         <v>22</v>
       </c>
       <c r="S243" s="49" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="T243" s="48" t="s">
         <v>22</v>
@@ -33964,7 +34021,7 @@
     </row>
     <row r="244" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="70" t="s">
-        <v>846</v>
+        <v>827</v>
       </c>
       <c r="B244" s="48" t="s">
         <v>22</v>
@@ -34048,7 +34105,7 @@
         <v>22</v>
       </c>
       <c r="AC244" s="73" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="AD244" s="48" t="s">
         <v>22</v>
@@ -34056,7 +34113,7 @@
     </row>
     <row r="245" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="70" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="B245" s="48" t="s">
         <v>22</v>
@@ -34140,7 +34197,7 @@
         <v>22</v>
       </c>
       <c r="AC245" s="73" t="s">
-        <v>860</v>
+        <v>841</v>
       </c>
       <c r="AD245" s="48" t="s">
         <v>22</v>
@@ -34148,7 +34205,7 @@
     </row>
     <row r="246" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="70" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="B246" s="48" t="s">
         <v>22</v>
@@ -34232,7 +34289,7 @@
         <v>22</v>
       </c>
       <c r="AC246" s="73" t="s">
-        <v>860</v>
+        <v>841</v>
       </c>
       <c r="AD246" s="48" t="s">
         <v>22</v>
@@ -34240,7 +34297,7 @@
     </row>
     <row r="247" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>887</v>
+        <v>868</v>
       </c>
       <c r="B247" t="s">
         <v>22</v>
@@ -34294,7 +34351,7 @@
         <v>22</v>
       </c>
       <c r="S247" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="T247" t="s">
         <v>22</v>
@@ -34332,7 +34389,7 @@
     </row>
     <row r="248" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>894</v>
+        <v>875</v>
       </c>
       <c r="B248" t="s">
         <v>22</v>
@@ -34386,7 +34443,7 @@
         <v>22</v>
       </c>
       <c r="S248" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="T248" t="s">
         <v>22</v>
@@ -34424,7 +34481,7 @@
     </row>
     <row r="249" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>913</v>
+        <v>894</v>
       </c>
       <c r="B249" t="s">
         <v>22</v>
@@ -34511,6 +34568,190 @@
         <v>22</v>
       </c>
       <c r="AD249" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="250" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>921</v>
+      </c>
+      <c r="B250" t="s">
+        <v>22</v>
+      </c>
+      <c r="C250" t="s">
+        <v>22</v>
+      </c>
+      <c r="D250" t="s">
+        <v>22</v>
+      </c>
+      <c r="E250" t="s">
+        <v>22</v>
+      </c>
+      <c r="F250" t="s">
+        <v>22</v>
+      </c>
+      <c r="G250" t="s">
+        <v>22</v>
+      </c>
+      <c r="H250" t="s">
+        <v>22</v>
+      </c>
+      <c r="I250" t="s">
+        <v>22</v>
+      </c>
+      <c r="J250" t="s">
+        <v>22</v>
+      </c>
+      <c r="K250" t="s">
+        <v>22</v>
+      </c>
+      <c r="L250" t="s">
+        <v>22</v>
+      </c>
+      <c r="M250" t="s">
+        <v>22</v>
+      </c>
+      <c r="N250" t="s">
+        <v>22</v>
+      </c>
+      <c r="O250" t="s">
+        <v>22</v>
+      </c>
+      <c r="P250" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>22</v>
+      </c>
+      <c r="R250" t="s">
+        <v>22</v>
+      </c>
+      <c r="S250" t="s">
+        <v>22</v>
+      </c>
+      <c r="T250" t="s">
+        <v>22</v>
+      </c>
+      <c r="U250" t="s">
+        <v>22</v>
+      </c>
+      <c r="V250" t="s">
+        <v>22</v>
+      </c>
+      <c r="W250" t="s">
+        <v>22</v>
+      </c>
+      <c r="X250" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y250" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z250" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA250" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB250" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC250" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD250" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="251" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>928</v>
+      </c>
+      <c r="B251" t="s">
+        <v>22</v>
+      </c>
+      <c r="C251" t="s">
+        <v>22</v>
+      </c>
+      <c r="D251" t="s">
+        <v>22</v>
+      </c>
+      <c r="E251" t="s">
+        <v>22</v>
+      </c>
+      <c r="F251" t="s">
+        <v>22</v>
+      </c>
+      <c r="G251" t="s">
+        <v>22</v>
+      </c>
+      <c r="H251" t="s">
+        <v>22</v>
+      </c>
+      <c r="I251" t="s">
+        <v>22</v>
+      </c>
+      <c r="J251" t="s">
+        <v>22</v>
+      </c>
+      <c r="K251" t="s">
+        <v>22</v>
+      </c>
+      <c r="L251" t="s">
+        <v>22</v>
+      </c>
+      <c r="M251" t="s">
+        <v>22</v>
+      </c>
+      <c r="N251" t="s">
+        <v>22</v>
+      </c>
+      <c r="O251" t="s">
+        <v>22</v>
+      </c>
+      <c r="P251" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>22</v>
+      </c>
+      <c r="R251" t="s">
+        <v>22</v>
+      </c>
+      <c r="S251" t="s">
+        <v>22</v>
+      </c>
+      <c r="T251" t="s">
+        <v>22</v>
+      </c>
+      <c r="U251" t="s">
+        <v>22</v>
+      </c>
+      <c r="V251" t="s">
+        <v>22</v>
+      </c>
+      <c r="W251" t="s">
+        <v>22</v>
+      </c>
+      <c r="X251" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y251" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z251" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA251" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB251" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC251" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD251" t="s">
         <v>22</v>
       </c>
     </row>
@@ -34642,54 +34883,51 @@
     <hyperlink ref="S186" r:id="rId19" xr:uid="{7E9C7A94-A136-40F4-8926-E175506C0FB0}"/>
     <hyperlink ref="S200" r:id="rId20" xr:uid="{6E155B27-A1F3-4634-AF94-EA4AFCBB6FA8}"/>
     <hyperlink ref="S178" r:id="rId21" display="https://opt.adm.testingserver8.com/admin/product" xr:uid="{FE84E4EC-8AD8-4353-9CF9-0FFD7AF22EC6}"/>
-    <hyperlink ref="S179" r:id="rId22" display="https://opt.adm.testingserver8.com/admin/home-page-banner" xr:uid="{FE688102-71E6-4D5D-8C26-E4A5C88965AB}"/>
-    <hyperlink ref="S180" r:id="rId23" display="https://opt.adm.testingserver8.com/admin/product" xr:uid="{75833417-6442-4309-8418-D565356A22B6}"/>
-    <hyperlink ref="S177" r:id="rId24" display="https://opt.adm.testingserver8.com/admin/product" xr:uid="{CF1B8F79-F4E1-4AB9-B852-9B1E92C5988C}"/>
-    <hyperlink ref="S181" r:id="rId25" display="https://opt.adm.testingserver8.com/admin/product" xr:uid="{B4C89834-3581-4298-A312-1087A98E46BC}"/>
-    <hyperlink ref="S182" r:id="rId26" display="https://opt.adm.testingserver8.com/admin/special-timer-event" xr:uid="{DC091BA2-1053-4AEE-9250-D6D43A208977}"/>
-    <hyperlink ref="S183" r:id="rId27" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{6E9132F4-992B-46D1-9A28-5D473938DFF8}"/>
-    <hyperlink ref="S184" r:id="rId28" display="https://opt.adm.testingserver8.com/admin/product-collection" xr:uid="{B7714AD9-0B49-4F19-B276-CBDABCB03633}"/>
-    <hyperlink ref="S185" r:id="rId29" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{965BF565-0242-4239-B278-6E574AF5D044}"/>
-    <hyperlink ref="S214" r:id="rId30" xr:uid="{C1127956-48DF-433C-AD28-9DA999FBCC26}"/>
-    <hyperlink ref="S213" r:id="rId31" xr:uid="{C9182A01-C96D-4110-9CA5-C017A54856E8}"/>
-    <hyperlink ref="S225" r:id="rId32" xr:uid="{6C20156C-B7E3-4D33-B99C-3A1821930139}"/>
-    <hyperlink ref="S230" r:id="rId33" xr:uid="{BAC34349-31E9-4520-A81D-6EEDD88BD29C}"/>
-    <hyperlink ref="S228" r:id="rId34" xr:uid="{95A32C29-884B-4748-92B0-EDDF6C5CE209}"/>
-    <hyperlink ref="S227" r:id="rId35" xr:uid="{118D0710-0BF2-49C8-888F-870ACC682CB5}"/>
-    <hyperlink ref="S231" r:id="rId36" xr:uid="{95BCE644-FF9B-472B-8145-F31A886E4FC4}"/>
-    <hyperlink ref="T231" r:id="rId37" xr:uid="{89BBFA7B-AD6E-4F93-BFD3-447AE8F7C502}"/>
-    <hyperlink ref="S232" r:id="rId38" xr:uid="{C8BD3F97-CFD5-4E09-8346-C525E3D0F983}"/>
-    <hyperlink ref="T232" r:id="rId39" display="https://console.zlaata.com/admin/return-order" xr:uid="{7EB489AF-7DBE-4776-BCF8-60461A79DB05}"/>
-    <hyperlink ref="S233" r:id="rId40" xr:uid="{570ACAD2-9993-464C-95C3-A0F384F535D4}"/>
-    <hyperlink ref="S234" r:id="rId41" xr:uid="{A5E4F190-F60E-4C69-A7BF-9E5AD6674C56}"/>
-    <hyperlink ref="S235" r:id="rId42" xr:uid="{0DD56580-2553-4B3D-AC00-0568BF6AD0B9}"/>
-    <hyperlink ref="S236" r:id="rId43" xr:uid="{16CBC571-4EE4-4D66-B8C3-CE0279FDD836}"/>
-    <hyperlink ref="T234" r:id="rId44" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{5FB45239-0134-4C16-87DB-11C106356D92}"/>
-    <hyperlink ref="AD231" r:id="rId45" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{79B826CA-7F44-45A6-9BD2-CC8919CFA12A}"/>
-    <hyperlink ref="AC177" r:id="rId46" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{7BE8FE18-5C75-431B-8488-FBDEF16485E5}"/>
-    <hyperlink ref="AC178" r:id="rId47" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{FF640DAE-0F42-4B2A-A086-F1C73287AD75}"/>
-    <hyperlink ref="AC181" r:id="rId48" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{B625AA61-E1E0-4964-9CDD-901824C6555F}"/>
-    <hyperlink ref="AC244" r:id="rId49" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
-    <hyperlink ref="T211" r:id="rId50" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
-    <hyperlink ref="T212" r:id="rId51" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
-    <hyperlink ref="S199" r:id="rId52" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
-    <hyperlink ref="AC225" r:id="rId53" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{CD96CCCF-BE60-40A1-BA2F-93729430B99A}"/>
-    <hyperlink ref="AC226:AC239" r:id="rId54" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
-    <hyperlink ref="S219" r:id="rId55" display="https://qa.zlta.testingserver8.com/admin/payment-pending" xr:uid="{37E5E50E-434D-4FC0-B9A6-C0648E88FF97}"/>
-    <hyperlink ref="S206" r:id="rId56" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
-    <hyperlink ref="S204" r:id="rId57" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
-    <hyperlink ref="S205" r:id="rId58" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
-    <hyperlink ref="S196" r:id="rId59" display="https://console.zlaata.com/admin/product" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
-    <hyperlink ref="S243" r:id="rId60" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
-    <hyperlink ref="T236" r:id="rId61" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
-    <hyperlink ref="S226" r:id="rId62" display="https://console.zlaata.com/admin/cancel-order" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
-    <hyperlink ref="AC237" r:id="rId63" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{B5FFBFD3-2AEB-43E2-A088-AA986500C94C}"/>
-    <hyperlink ref="S237" r:id="rId64" xr:uid="{E29AE273-A13B-4FDA-99DA-66C3FC3DF993}"/>
-    <hyperlink ref="S239" r:id="rId65" xr:uid="{E5A47A78-2C35-4A72-A585-72E3D18CC556}"/>
-    <hyperlink ref="AC238" r:id="rId66" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{A40E89D1-5252-43A0-AF9C-1AAAC503CE8E}"/>
-    <hyperlink ref="S238" r:id="rId67" xr:uid="{EFD712A1-7827-446F-B5F1-9CC652078EB0}"/>
+    <hyperlink ref="S182" r:id="rId22" display="https://opt.adm.testingserver8.com/admin/special-timer-event" xr:uid="{DC091BA2-1053-4AEE-9250-D6D43A208977}"/>
+    <hyperlink ref="S183" r:id="rId23" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{6E9132F4-992B-46D1-9A28-5D473938DFF8}"/>
+    <hyperlink ref="S184" r:id="rId24" display="https://opt.adm.testingserver8.com/admin/product-collection" xr:uid="{B7714AD9-0B49-4F19-B276-CBDABCB03633}"/>
+    <hyperlink ref="S185" r:id="rId25" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{965BF565-0242-4239-B278-6E574AF5D044}"/>
+    <hyperlink ref="S214" r:id="rId26" xr:uid="{C1127956-48DF-433C-AD28-9DA999FBCC26}"/>
+    <hyperlink ref="S213" r:id="rId27" xr:uid="{C9182A01-C96D-4110-9CA5-C017A54856E8}"/>
+    <hyperlink ref="S225" r:id="rId28" xr:uid="{6C20156C-B7E3-4D33-B99C-3A1821930139}"/>
+    <hyperlink ref="S230" r:id="rId29" xr:uid="{BAC34349-31E9-4520-A81D-6EEDD88BD29C}"/>
+    <hyperlink ref="S228" r:id="rId30" xr:uid="{95A32C29-884B-4748-92B0-EDDF6C5CE209}"/>
+    <hyperlink ref="S227" r:id="rId31" xr:uid="{118D0710-0BF2-49C8-888F-870ACC682CB5}"/>
+    <hyperlink ref="S231" r:id="rId32" xr:uid="{95BCE644-FF9B-472B-8145-F31A886E4FC4}"/>
+    <hyperlink ref="T231" r:id="rId33" xr:uid="{89BBFA7B-AD6E-4F93-BFD3-447AE8F7C502}"/>
+    <hyperlink ref="S232" r:id="rId34" xr:uid="{C8BD3F97-CFD5-4E09-8346-C525E3D0F983}"/>
+    <hyperlink ref="T232" r:id="rId35" display="https://console.zlaata.com/admin/return-order" xr:uid="{7EB489AF-7DBE-4776-BCF8-60461A79DB05}"/>
+    <hyperlink ref="S233" r:id="rId36" xr:uid="{570ACAD2-9993-464C-95C3-A0F384F535D4}"/>
+    <hyperlink ref="S234" r:id="rId37" xr:uid="{A5E4F190-F60E-4C69-A7BF-9E5AD6674C56}"/>
+    <hyperlink ref="S235" r:id="rId38" xr:uid="{0DD56580-2553-4B3D-AC00-0568BF6AD0B9}"/>
+    <hyperlink ref="S236" r:id="rId39" xr:uid="{16CBC571-4EE4-4D66-B8C3-CE0279FDD836}"/>
+    <hyperlink ref="T234" r:id="rId40" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{5FB45239-0134-4C16-87DB-11C106356D92}"/>
+    <hyperlink ref="AD231" r:id="rId41" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{79B826CA-7F44-45A6-9BD2-CC8919CFA12A}"/>
+    <hyperlink ref="AC177" r:id="rId42" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{7BE8FE18-5C75-431B-8488-FBDEF16485E5}"/>
+    <hyperlink ref="AC178" r:id="rId43" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{FF640DAE-0F42-4B2A-A086-F1C73287AD75}"/>
+    <hyperlink ref="AC244" r:id="rId44" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
+    <hyperlink ref="T211" r:id="rId45" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
+    <hyperlink ref="T212" r:id="rId46" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
+    <hyperlink ref="S199" r:id="rId47" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
+    <hyperlink ref="AC225" r:id="rId48" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{CD96CCCF-BE60-40A1-BA2F-93729430B99A}"/>
+    <hyperlink ref="AC226:AC239" r:id="rId49" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
+    <hyperlink ref="S219" r:id="rId50" display="https://qa.zlta.testingserver8.com/admin/payment-pending" xr:uid="{37E5E50E-434D-4FC0-B9A6-C0648E88FF97}"/>
+    <hyperlink ref="S206" r:id="rId51" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
+    <hyperlink ref="S204" r:id="rId52" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
+    <hyperlink ref="S205" r:id="rId53" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
+    <hyperlink ref="S196" r:id="rId54" display="https://console.zlaata.com/admin/product" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
+    <hyperlink ref="S243" r:id="rId55" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
+    <hyperlink ref="T236" r:id="rId56" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
+    <hyperlink ref="S226" r:id="rId57" display="https://console.zlaata.com/admin/cancel-order" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
+    <hyperlink ref="AC237" r:id="rId58" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{B5FFBFD3-2AEB-43E2-A088-AA986500C94C}"/>
+    <hyperlink ref="S237" r:id="rId59" xr:uid="{E29AE273-A13B-4FDA-99DA-66C3FC3DF993}"/>
+    <hyperlink ref="S239" r:id="rId60" xr:uid="{E5A47A78-2C35-4A72-A585-72E3D18CC556}"/>
+    <hyperlink ref="AC238" r:id="rId61" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{A40E89D1-5252-43A0-AF9C-1AAAC503CE8E}"/>
+    <hyperlink ref="S238" r:id="rId62" xr:uid="{EFD712A1-7827-446F-B5F1-9CC652078EB0}"/>
+    <hyperlink ref="AC180" r:id="rId63" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{6262B2DA-10A4-449F-8938-AC96E529EF5A}"/>
+    <hyperlink ref="AC181" r:id="rId64" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{A98207AA-9B31-4A4E-BB36-48E505D5F843}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId68"/>
+  <pageSetup orientation="portrait" r:id="rId65"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever0\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92531965-EB6F-4F05-B63C-5CB101AE9452}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A917436F-BB33-48DA-AC97-72962E686F43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8927" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8927" uniqueCount="931">
   <si>
     <t>S.No</t>
   </si>
@@ -1843,9 +1843,6 @@
     <t>Banner Title</t>
   </si>
   <si>
-    <t>TD_UI_Zlaata_ADM_07</t>
-  </si>
-  <si>
     <t>TC_UI_Zlaata_ADM_09</t>
   </si>
   <si>
@@ -1855,9 +1852,6 @@
     <t>TD_UI_Zlaata_ADM_09</t>
   </si>
   <si>
-    <t>TD_UI_Zlaata_ADM_08</t>
-  </si>
-  <si>
     <t>Verify New Product added match between two exports.</t>
   </si>
   <si>
@@ -2161,18 +2155,9 @@
     <t>Verify New Arrivals Section Product Display on Homepage.</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_ADM_07</t>
-  </si>
-  <si>
     <t>Verify all uploaded Special Timer products appear in Admin and User App.</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_ADM_08</t>
-  </si>
-  <si>
-    <t>Verify uploaded categories appear in Admin and User App.</t>
-  </si>
-  <si>
     <t>TD_UI_Zlaata_ADMI_01</t>
   </si>
   <si>
@@ -2831,6 +2816,9 @@
   </si>
   <si>
     <t>Verify Zlaata India Collection Section Display on Website.</t>
+  </si>
+  <si>
+    <t>Create and verify Influencer Pointer for product on homepage.</t>
   </si>
 </sst>
 </file>
@@ -3487,31 +3475,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3534,6 +3504,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5088,18 +5076,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="97" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="99"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -5486,18 +5474,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="91" t="s">
+      <c r="A37" s="100" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="92"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="93"/>
+      <c r="B37" s="101"/>
+      <c r="C37" s="101"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="101"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="102"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -5766,7 +5754,7 @@
         <v>197</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E46" s="47" t="s">
         <v>14</v>
@@ -5923,10 +5911,10 @@
         <v>10</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D51" s="80" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E51" s="48" t="s">
         <v>14</v>
@@ -5955,10 +5943,10 @@
         <v>10</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D52" s="80" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E52" s="48" t="s">
         <v>14</v>
@@ -5987,10 +5975,10 @@
         <v>10</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D53" s="80" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E53" s="48" t="s">
         <v>14</v>
@@ -6019,16 +6007,16 @@
         <v>10</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D54" s="80" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E54" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F54" s="47" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G54" s="48" t="s">
         <v>11</v>
@@ -6044,18 +6032,18 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="91" t="s">
+      <c r="A55" s="100" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="92"/>
-      <c r="C55" s="92"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="92"/>
-      <c r="F55" s="92"/>
-      <c r="G55" s="92"/>
-      <c r="H55" s="92"/>
-      <c r="I55" s="92"/>
-      <c r="J55" s="93"/>
+      <c r="B55" s="101"/>
+      <c r="C55" s="101"/>
+      <c r="D55" s="101"/>
+      <c r="E55" s="101"/>
+      <c r="F55" s="101"/>
+      <c r="G55" s="101"/>
+      <c r="H55" s="101"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="102"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
@@ -6378,18 +6366,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="91" t="s">
+      <c r="A66" s="100" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="92"/>
-      <c r="C66" s="92"/>
-      <c r="D66" s="92"/>
-      <c r="E66" s="92"/>
-      <c r="F66" s="92"/>
-      <c r="G66" s="92"/>
-      <c r="H66" s="92"/>
-      <c r="I66" s="92"/>
-      <c r="J66" s="93"/>
+      <c r="B66" s="101"/>
+      <c r="C66" s="101"/>
+      <c r="D66" s="101"/>
+      <c r="E66" s="101"/>
+      <c r="F66" s="101"/>
+      <c r="G66" s="101"/>
+      <c r="H66" s="101"/>
+      <c r="I66" s="101"/>
+      <c r="J66" s="102"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
@@ -6744,18 +6732,18 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="91" t="s">
+      <c r="A78" s="100" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="92"/>
-      <c r="C78" s="92"/>
-      <c r="D78" s="92"/>
-      <c r="E78" s="92"/>
-      <c r="F78" s="92"/>
-      <c r="G78" s="92"/>
-      <c r="H78" s="92"/>
-      <c r="I78" s="92"/>
-      <c r="J78" s="93"/>
+      <c r="B78" s="101"/>
+      <c r="C78" s="101"/>
+      <c r="D78" s="101"/>
+      <c r="E78" s="101"/>
+      <c r="F78" s="101"/>
+      <c r="G78" s="101"/>
+      <c r="H78" s="101"/>
+      <c r="I78" s="101"/>
+      <c r="J78" s="102"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
@@ -7622,18 +7610,18 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="94" t="s">
+      <c r="A106" s="87" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="94"/>
-      <c r="C106" s="94"/>
-      <c r="D106" s="94"/>
-      <c r="E106" s="94"/>
-      <c r="F106" s="94"/>
-      <c r="G106" s="94"/>
-      <c r="H106" s="94"/>
-      <c r="I106" s="94"/>
-      <c r="J106" s="94"/>
+      <c r="B106" s="87"/>
+      <c r="C106" s="87"/>
+      <c r="D106" s="87"/>
+      <c r="E106" s="87"/>
+      <c r="F106" s="87"/>
+      <c r="G106" s="87"/>
+      <c r="H106" s="87"/>
+      <c r="I106" s="87"/>
+      <c r="J106" s="87"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -7902,7 +7890,7 @@
         <v>370</v>
       </c>
       <c r="D115" s="48" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E115" s="48" t="s">
         <v>14</v>
@@ -7963,16 +7951,16 @@
         <v>10</v>
       </c>
       <c r="C117" s="48" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D117" s="48" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E117" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F117" s="48" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="G117" s="48" t="s">
         <v>11</v>
@@ -7995,16 +7983,16 @@
         <v>10</v>
       </c>
       <c r="C118" s="48" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D118" s="48" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E118" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F118" s="48" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G118" s="48" t="s">
         <v>11</v>
@@ -8041,16 +8029,16 @@
         <v>10</v>
       </c>
       <c r="C119" s="48" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D119" s="48" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E119" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F119" s="48" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G119" s="48" t="s">
         <v>11</v>
@@ -8087,16 +8075,16 @@
         <v>10</v>
       </c>
       <c r="C120" s="48" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D120" s="48" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E120" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="48" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G120" s="48" t="s">
         <v>11</v>
@@ -8126,18 +8114,18 @@
       <c r="X120" s="58"/>
     </row>
     <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="95" t="s">
+      <c r="A121" s="88" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="95"/>
-      <c r="C121" s="95"/>
-      <c r="D121" s="95"/>
-      <c r="E121" s="95"/>
-      <c r="F121" s="95"/>
-      <c r="G121" s="95"/>
-      <c r="H121" s="95"/>
-      <c r="I121" s="95"/>
-      <c r="J121" s="95"/>
+      <c r="B121" s="88"/>
+      <c r="C121" s="88"/>
+      <c r="D121" s="88"/>
+      <c r="E121" s="88"/>
+      <c r="F121" s="88"/>
+      <c r="G121" s="88"/>
+      <c r="H121" s="88"/>
+      <c r="I121" s="88"/>
+      <c r="J121" s="88"/>
       <c r="K121" s="57"/>
       <c r="L121" s="58"/>
       <c r="M121" s="58"/>
@@ -8200,18 +8188,18 @@
       <c r="X122" s="58"/>
     </row>
     <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="95" t="s">
+      <c r="A123" s="88" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="95"/>
-      <c r="C123" s="95"/>
-      <c r="D123" s="95"/>
-      <c r="E123" s="95"/>
-      <c r="F123" s="95"/>
-      <c r="G123" s="95"/>
-      <c r="H123" s="95"/>
-      <c r="I123" s="95"/>
-      <c r="J123" s="95"/>
+      <c r="B123" s="88"/>
+      <c r="C123" s="88"/>
+      <c r="D123" s="88"/>
+      <c r="E123" s="88"/>
+      <c r="F123" s="88"/>
+      <c r="G123" s="88"/>
+      <c r="H123" s="88"/>
+      <c r="I123" s="88"/>
+      <c r="J123" s="88"/>
       <c r="K123" s="57"/>
       <c r="L123" s="58"/>
       <c r="M123" s="58"/>
@@ -8274,18 +8262,18 @@
       <c r="X124" s="58"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="95" t="s">
+      <c r="A125" s="88" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="95"/>
-      <c r="C125" s="95"/>
-      <c r="D125" s="95"/>
-      <c r="E125" s="95"/>
-      <c r="F125" s="95"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="95"/>
-      <c r="I125" s="95"/>
-      <c r="J125" s="95"/>
+      <c r="B125" s="88"/>
+      <c r="C125" s="88"/>
+      <c r="D125" s="88"/>
+      <c r="E125" s="88"/>
+      <c r="F125" s="88"/>
+      <c r="G125" s="88"/>
+      <c r="H125" s="88"/>
+      <c r="I125" s="88"/>
+      <c r="J125" s="88"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -8610,18 +8598,18 @@
       <c r="X132" s="58"/>
     </row>
     <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="95" t="s">
+      <c r="A133" s="88" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="95"/>
-      <c r="C133" s="95"/>
-      <c r="D133" s="96"/>
-      <c r="E133" s="96"/>
-      <c r="F133" s="96"/>
-      <c r="G133" s="96"/>
-      <c r="H133" s="96"/>
-      <c r="I133" s="96"/>
-      <c r="J133" s="96"/>
+      <c r="B133" s="88"/>
+      <c r="C133" s="88"/>
+      <c r="D133" s="90"/>
+      <c r="E133" s="90"/>
+      <c r="F133" s="90"/>
+      <c r="G133" s="90"/>
+      <c r="H133" s="90"/>
+      <c r="I133" s="90"/>
+      <c r="J133" s="90"/>
       <c r="K133" s="58"/>
       <c r="L133" s="58"/>
       <c r="M133" s="58"/>
@@ -9034,7 +9022,7 @@
         <v>437</v>
       </c>
       <c r="D143" s="27" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E143" s="27" t="s">
         <v>14</v>
@@ -9077,16 +9065,16 @@
         <v>10</v>
       </c>
       <c r="C144" s="48" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D144" s="27" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E144" s="27" t="s">
         <v>14</v>
       </c>
       <c r="F144" s="48" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G144" s="27" t="s">
         <v>11</v>
@@ -9116,18 +9104,18 @@
       <c r="X144" s="58"/>
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="100" t="s">
+      <c r="A145" s="94" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="101"/>
-      <c r="C145" s="101"/>
-      <c r="D145" s="101"/>
-      <c r="E145" s="101"/>
-      <c r="F145" s="101"/>
-      <c r="G145" s="101"/>
-      <c r="H145" s="101"/>
-      <c r="I145" s="101"/>
-      <c r="J145" s="102"/>
+      <c r="B145" s="95"/>
+      <c r="C145" s="95"/>
+      <c r="D145" s="95"/>
+      <c r="E145" s="95"/>
+      <c r="F145" s="95"/>
+      <c r="G145" s="95"/>
+      <c r="H145" s="95"/>
+      <c r="I145" s="95"/>
+      <c r="J145" s="96"/>
       <c r="K145" s="58"/>
       <c r="L145" s="58"/>
       <c r="M145" s="58"/>
@@ -9574,18 +9562,18 @@
       <c r="Z155" s="58"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="95" t="s">
+      <c r="A156" s="88" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="95"/>
-      <c r="C156" s="95"/>
-      <c r="D156" s="95"/>
-      <c r="E156" s="95"/>
-      <c r="F156" s="95"/>
-      <c r="G156" s="95"/>
-      <c r="H156" s="95"/>
-      <c r="I156" s="95"/>
-      <c r="J156" s="95"/>
+      <c r="B156" s="88"/>
+      <c r="C156" s="88"/>
+      <c r="D156" s="88"/>
+      <c r="E156" s="88"/>
+      <c r="F156" s="88"/>
+      <c r="G156" s="88"/>
+      <c r="H156" s="88"/>
+      <c r="I156" s="88"/>
+      <c r="J156" s="88"/>
       <c r="K156" s="58"/>
       <c r="L156" s="58"/>
       <c r="M156" s="58"/>
@@ -9652,18 +9640,18 @@
       <c r="Z157" s="58"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="95" t="s">
+      <c r="A158" s="88" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="95"/>
-      <c r="C158" s="95"/>
-      <c r="D158" s="95"/>
-      <c r="E158" s="95"/>
-      <c r="F158" s="95"/>
-      <c r="G158" s="95"/>
-      <c r="H158" s="95"/>
-      <c r="I158" s="95"/>
-      <c r="J158" s="95"/>
+      <c r="B158" s="88"/>
+      <c r="C158" s="88"/>
+      <c r="D158" s="88"/>
+      <c r="E158" s="88"/>
+      <c r="F158" s="88"/>
+      <c r="G158" s="88"/>
+      <c r="H158" s="88"/>
+      <c r="I158" s="88"/>
+      <c r="J158" s="88"/>
       <c r="K158" s="58"/>
       <c r="L158" s="58"/>
       <c r="M158" s="58"/>
@@ -10409,16 +10397,16 @@
         <v>10</v>
       </c>
       <c r="C177" s="70" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="D177" s="71" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="E177" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F177" s="70" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="G177" s="69" t="s">
         <v>11</v>
@@ -10441,16 +10429,16 @@
         <v>10</v>
       </c>
       <c r="C178" s="70" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="D178" s="71" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="E178" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F178" s="70" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G178" s="69" t="s">
         <v>11</v>
@@ -10473,16 +10461,16 @@
         <v>10</v>
       </c>
       <c r="C179" s="70" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="D179" s="71" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="E179" s="69" t="s">
         <v>14</v>
       </c>
       <c r="F179" s="70" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G179" s="69" t="s">
         <v>11</v>
@@ -10498,18 +10486,18 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="95" t="s">
-        <v>709</v>
-      </c>
-      <c r="B180" s="95"/>
-      <c r="C180" s="95"/>
-      <c r="D180" s="87"/>
-      <c r="E180" s="95"/>
-      <c r="F180" s="95"/>
-      <c r="G180" s="95"/>
-      <c r="H180" s="95"/>
-      <c r="I180" s="95"/>
-      <c r="J180" s="95"/>
+      <c r="A180" s="88" t="s">
+        <v>707</v>
+      </c>
+      <c r="B180" s="88"/>
+      <c r="C180" s="88"/>
+      <c r="D180" s="89"/>
+      <c r="E180" s="88"/>
+      <c r="F180" s="88"/>
+      <c r="G180" s="88"/>
+      <c r="H180" s="88"/>
+      <c r="I180" s="88"/>
+      <c r="J180" s="88"/>
     </row>
     <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="68">
@@ -10522,7 +10510,7 @@
         <v>173</v>
       </c>
       <c r="D181" s="77" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="E181" s="75" t="s">
         <v>14</v>
@@ -10554,7 +10542,7 @@
         <v>177</v>
       </c>
       <c r="D182" s="77" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="E182" s="75" t="s">
         <v>14</v>
@@ -10586,7 +10574,7 @@
         <v>180</v>
       </c>
       <c r="D183" s="77" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E183" s="75" t="s">
         <v>14</v>
@@ -10609,7 +10597,7 @@
     </row>
     <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B184" s="69" t="s">
         <v>10</v>
@@ -10618,7 +10606,7 @@
         <v>183</v>
       </c>
       <c r="D184" s="77" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="E184" s="75" t="s">
         <v>14</v>
@@ -10641,7 +10629,7 @@
     </row>
     <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B185" s="69" t="s">
         <v>10</v>
@@ -10650,7 +10638,7 @@
         <v>186</v>
       </c>
       <c r="D185" s="77" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="E185" s="75" t="s">
         <v>14</v>
@@ -10673,7 +10661,7 @@
     </row>
     <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="68">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B186" s="69" t="s">
         <v>10</v>
@@ -10682,7 +10670,7 @@
         <v>189</v>
       </c>
       <c r="D186" s="77" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="E186" s="75" t="s">
         <v>14</v>
@@ -10711,22 +10699,22 @@
         <v>10</v>
       </c>
       <c r="C187" s="74" t="s">
-        <v>711</v>
-      </c>
-      <c r="D187" s="64" t="s">
-        <v>712</v>
+        <v>191</v>
+      </c>
+      <c r="D187" s="77" t="s">
+        <v>930</v>
       </c>
       <c r="E187" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F187" s="70" t="s">
-        <v>605</v>
+        <v>193</v>
       </c>
       <c r="G187" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H187" s="69" t="s">
-        <v>763</v>
+        <v>176</v>
       </c>
       <c r="I187" s="69" t="s">
         <v>12</v>
@@ -10737,28 +10725,28 @@
     </row>
     <row r="188" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="68">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B188" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C188" s="74" t="s">
-        <v>713</v>
-      </c>
-      <c r="D188" s="78" t="s">
-        <v>714</v>
+        <v>194</v>
+      </c>
+      <c r="D188" s="77" t="s">
+        <v>709</v>
       </c>
       <c r="E188" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F188" s="70" t="s">
-        <v>609</v>
+        <v>196</v>
       </c>
       <c r="G188" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H188" s="69" t="s">
-        <v>763</v>
+        <v>176</v>
       </c>
       <c r="I188" s="69" t="s">
         <v>12</v>
@@ -10775,22 +10763,22 @@
         <v>10</v>
       </c>
       <c r="C189" s="74" t="s">
+        <v>605</v>
+      </c>
+      <c r="D189" s="64" t="s">
         <v>606</v>
-      </c>
-      <c r="D189" s="64" t="s">
-        <v>607</v>
       </c>
       <c r="E189" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F189" s="70" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G189" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H189" s="69" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="I189" s="69" t="s">
         <v>12</v>
@@ -10800,18 +10788,18 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="97" t="s">
-        <v>611</v>
-      </c>
-      <c r="B190" s="98"/>
-      <c r="C190" s="98"/>
-      <c r="D190" s="98"/>
-      <c r="E190" s="98"/>
-      <c r="F190" s="98"/>
-      <c r="G190" s="98"/>
-      <c r="H190" s="98"/>
-      <c r="I190" s="98"/>
-      <c r="J190" s="99"/>
+      <c r="A190" s="91" t="s">
+        <v>609</v>
+      </c>
+      <c r="B190" s="92"/>
+      <c r="C190" s="92"/>
+      <c r="D190" s="92"/>
+      <c r="E190" s="92"/>
+      <c r="F190" s="92"/>
+      <c r="G190" s="92"/>
+      <c r="H190" s="92"/>
+      <c r="I190" s="92"/>
+      <c r="J190" s="93"/>
     </row>
     <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="68">
@@ -10821,22 +10809,22 @@
         <v>10</v>
       </c>
       <c r="C191" s="74" t="s">
+        <v>610</v>
+      </c>
+      <c r="D191" s="77" t="s">
         <v>612</v>
-      </c>
-      <c r="D191" s="77" t="s">
-        <v>614</v>
       </c>
       <c r="E191" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F191" s="70" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G191" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H191" s="69" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="I191" s="69" t="s">
         <v>12</v>
@@ -10853,22 +10841,22 @@
         <v>10</v>
       </c>
       <c r="C192" s="74" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D192" s="77" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E192" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F192" s="70" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G192" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H192" s="69" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="I192" s="69" t="s">
         <v>12</v>
@@ -10885,22 +10873,22 @@
         <v>10</v>
       </c>
       <c r="C193" s="74" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D193" s="78" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E193" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F193" s="70" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G193" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H193" s="69" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="I193" s="69" t="s">
         <v>12</v>
@@ -10917,22 +10905,22 @@
         <v>10</v>
       </c>
       <c r="C194" s="74" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D194" s="78" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E194" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F194" s="70" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G194" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H194" s="69" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="I194" s="69" t="s">
         <v>12</v>
@@ -10949,22 +10937,22 @@
         <v>10</v>
       </c>
       <c r="C195" s="74" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D195" s="78" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E195" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F195" s="70" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G195" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H195" s="69" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="I195" s="69" t="s">
         <v>12</v>
@@ -10981,22 +10969,22 @@
         <v>10</v>
       </c>
       <c r="C196" s="74" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="D196" s="78" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="E196" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F196" s="70" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="G196" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H196" s="69" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="I196" s="69" t="s">
         <v>12</v>
@@ -11013,22 +11001,22 @@
         <v>10</v>
       </c>
       <c r="C197" s="74" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="D197" s="78" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="E197" s="75" t="s">
         <v>14</v>
       </c>
       <c r="F197" s="70" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="G197" s="69" t="s">
         <v>11</v>
       </c>
       <c r="H197" s="69" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="I197" s="69" t="s">
         <v>12</v>
@@ -11038,18 +11026,18 @@
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A198" s="87" t="s">
-        <v>632</v>
-      </c>
-      <c r="B198" s="87"/>
-      <c r="C198" s="87"/>
-      <c r="D198" s="87"/>
-      <c r="E198" s="87"/>
-      <c r="F198" s="87"/>
-      <c r="G198" s="87"/>
-      <c r="H198" s="87"/>
-      <c r="I198" s="87"/>
-      <c r="J198" s="87"/>
+      <c r="A198" s="89" t="s">
+        <v>630</v>
+      </c>
+      <c r="B198" s="89"/>
+      <c r="C198" s="89"/>
+      <c r="D198" s="89"/>
+      <c r="E198" s="89"/>
+      <c r="F198" s="89"/>
+      <c r="G198" s="89"/>
+      <c r="H198" s="89"/>
+      <c r="I198" s="89"/>
+      <c r="J198" s="89"/>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="48">
@@ -11059,22 +11047,22 @@
         <v>10</v>
       </c>
       <c r="C199" s="79" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D199" s="64" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E199" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F199" s="79" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G199" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H199" s="48" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="I199" s="48" t="s">
         <v>12</v>
@@ -11091,22 +11079,22 @@
         <v>10</v>
       </c>
       <c r="C200" s="79" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D200" s="78" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E200" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F200" s="79" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G200" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H200" s="48" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="I200" s="48" t="s">
         <v>12</v>
@@ -11123,22 +11111,22 @@
         <v>10</v>
       </c>
       <c r="C201" s="79" t="s">
+        <v>637</v>
+      </c>
+      <c r="D201" s="78" t="s">
         <v>639</v>
-      </c>
-      <c r="D201" s="78" t="s">
-        <v>641</v>
       </c>
       <c r="E201" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F201" s="79" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G201" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H201" s="48" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="I201" s="48" t="s">
         <v>12</v>
@@ -11155,22 +11143,22 @@
         <v>10</v>
       </c>
       <c r="C202" s="79" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D202" s="78" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E202" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F202" s="79" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G202" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H202" s="48" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="I202" s="48" t="s">
         <v>12</v>
@@ -11180,18 +11168,18 @@
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A203" s="87" t="s">
-        <v>645</v>
-      </c>
-      <c r="B203" s="87"/>
-      <c r="C203" s="87"/>
-      <c r="D203" s="87"/>
-      <c r="E203" s="87"/>
-      <c r="F203" s="87"/>
-      <c r="G203" s="87"/>
-      <c r="H203" s="87"/>
-      <c r="I203" s="87"/>
-      <c r="J203" s="87"/>
+      <c r="A203" s="89" t="s">
+        <v>643</v>
+      </c>
+      <c r="B203" s="89"/>
+      <c r="C203" s="89"/>
+      <c r="D203" s="89"/>
+      <c r="E203" s="89"/>
+      <c r="F203" s="89"/>
+      <c r="G203" s="89"/>
+      <c r="H203" s="89"/>
+      <c r="I203" s="89"/>
+      <c r="J203" s="89"/>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="48">
@@ -11201,22 +11189,22 @@
         <v>10</v>
       </c>
       <c r="C204" s="79" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D204" s="78" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E204" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F204" s="79" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G204" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H204" s="48" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="I204" s="48" t="s">
         <v>12</v>
@@ -11226,18 +11214,18 @@
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A205" s="87" t="s">
-        <v>651</v>
-      </c>
-      <c r="B205" s="87"/>
-      <c r="C205" s="87"/>
-      <c r="D205" s="87"/>
-      <c r="E205" s="87"/>
-      <c r="F205" s="87"/>
-      <c r="G205" s="87"/>
-      <c r="H205" s="87"/>
-      <c r="I205" s="87"/>
-      <c r="J205" s="87"/>
+      <c r="A205" s="89" t="s">
+        <v>649</v>
+      </c>
+      <c r="B205" s="89"/>
+      <c r="C205" s="89"/>
+      <c r="D205" s="89"/>
+      <c r="E205" s="89"/>
+      <c r="F205" s="89"/>
+      <c r="G205" s="89"/>
+      <c r="H205" s="89"/>
+      <c r="I205" s="89"/>
+      <c r="J205" s="89"/>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="48">
@@ -11247,22 +11235,22 @@
         <v>10</v>
       </c>
       <c r="C206" s="79" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D206" s="78" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E206" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F206" s="79" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G206" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H206" s="48" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I206" s="48" t="s">
         <v>12</v>
@@ -11279,22 +11267,22 @@
         <v>10</v>
       </c>
       <c r="C207" s="79" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D207" s="78" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E207" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F207" s="79" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G207" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H207" s="48" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I207" s="48" t="s">
         <v>12</v>
@@ -11311,22 +11299,22 @@
         <v>10</v>
       </c>
       <c r="C208" s="79" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D208" s="78" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E208" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F208" s="79" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G208" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H208" s="48" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I208" s="48" t="s">
         <v>12</v>
@@ -11343,22 +11331,22 @@
         <v>10</v>
       </c>
       <c r="C209" s="79" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D209" s="78" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E209" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F209" s="79" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G209" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H209" s="48" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I209" s="48" t="s">
         <v>12</v>
@@ -11375,22 +11363,22 @@
         <v>10</v>
       </c>
       <c r="C210" s="79" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D210" s="78" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E210" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F210" s="79" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G210" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H210" s="48" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I210" s="48" t="s">
         <v>12</v>
@@ -11407,22 +11395,22 @@
         <v>10</v>
       </c>
       <c r="C211" s="79" t="s">
+        <v>664</v>
+      </c>
+      <c r="D211" s="78" t="s">
         <v>666</v>
-      </c>
-      <c r="D211" s="78" t="s">
-        <v>668</v>
       </c>
       <c r="E211" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F211" s="79" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="G211" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H211" s="48" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I211" s="48" t="s">
         <v>12</v>
@@ -11439,22 +11427,22 @@
         <v>10</v>
       </c>
       <c r="C212" s="79" t="s">
+        <v>665</v>
+      </c>
+      <c r="D212" s="78" t="s">
         <v>667</v>
-      </c>
-      <c r="D212" s="78" t="s">
-        <v>669</v>
       </c>
       <c r="E212" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F212" s="79" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G212" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H212" s="48" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I212" s="48" t="s">
         <v>12</v>
@@ -11471,22 +11459,22 @@
         <v>10</v>
       </c>
       <c r="C213" s="79" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="D213" s="78" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="E213" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F213" s="79" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G213" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H213" s="48" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I213" s="48" t="s">
         <v>12</v>
@@ -11503,22 +11491,22 @@
         <v>10</v>
       </c>
       <c r="C214" s="79" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="D214" s="78" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="E214" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F214" s="79" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="G214" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H214" s="48" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I214" s="48" t="s">
         <v>12</v>
@@ -11532,7 +11520,7 @@
       <c r="B215" s="85"/>
       <c r="C215" s="85"/>
       <c r="D215" s="85" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="E215" s="85"/>
       <c r="F215" s="85"/>
@@ -11549,22 +11537,22 @@
         <v>10</v>
       </c>
       <c r="C216" s="79" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="D216" s="78" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="E216" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F216" s="79" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="G216" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H216" s="48" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="I216" s="48" t="s">
         <v>12</v>
@@ -11578,7 +11566,7 @@
       <c r="B217" s="83"/>
       <c r="C217" s="83"/>
       <c r="D217" s="83" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="E217" s="83"/>
       <c r="F217" s="83"/>
@@ -11595,22 +11583,22 @@
         <v>10</v>
       </c>
       <c r="C218" s="79" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="D218" s="78" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="E218" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F218" s="79" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="G218" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H218" s="48" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="I218" s="48" t="s">
         <v>12</v>
@@ -11627,22 +11615,22 @@
         <v>10</v>
       </c>
       <c r="C219" s="79" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="D219" s="78" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="E219" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F219" s="79" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="G219" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H219" s="48" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="I219" s="48" t="s">
         <v>12</v>
@@ -11652,18 +11640,18 @@
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A220" s="87" t="s">
-        <v>716</v>
-      </c>
-      <c r="B220" s="87"/>
-      <c r="C220" s="87"/>
-      <c r="D220" s="87"/>
-      <c r="E220" s="87"/>
-      <c r="F220" s="87"/>
-      <c r="G220" s="87"/>
-      <c r="H220" s="87"/>
-      <c r="I220" s="87"/>
-      <c r="J220" s="87"/>
+      <c r="A220" s="89" t="s">
+        <v>711</v>
+      </c>
+      <c r="B220" s="89"/>
+      <c r="C220" s="89"/>
+      <c r="D220" s="89"/>
+      <c r="E220" s="89"/>
+      <c r="F220" s="89"/>
+      <c r="G220" s="89"/>
+      <c r="H220" s="89"/>
+      <c r="I220" s="89"/>
+      <c r="J220" s="89"/>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="48">
@@ -11673,22 +11661,22 @@
         <v>10</v>
       </c>
       <c r="C221" s="79" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="D221" s="78" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="E221" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F221" s="79" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="G221" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H221" s="48" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="I221" s="48" t="s">
         <v>12</v>
@@ -11705,22 +11693,22 @@
         <v>10</v>
       </c>
       <c r="C222" s="79" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="D222" s="78" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="E222" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F222" s="79" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="G222" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H222" s="48" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="I222" s="48" t="s">
         <v>12</v>
@@ -11737,22 +11725,22 @@
         <v>10</v>
       </c>
       <c r="C223" s="79" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="D223" s="78" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="E223" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F223" s="79" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="G223" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H223" s="48" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="I223" s="48" t="s">
         <v>12</v>
@@ -11769,22 +11757,22 @@
         <v>10</v>
       </c>
       <c r="C224" s="79" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D224" s="78" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="E224" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F224" s="79" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="G224" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H224" s="48" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="I224" s="48" t="s">
         <v>12</v>
@@ -11801,22 +11789,22 @@
         <v>10</v>
       </c>
       <c r="C225" s="79" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="D225" s="78" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="E225" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F225" s="79" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="G225" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H225" s="48" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="I225" s="48" t="s">
         <v>12</v>
@@ -11826,18 +11814,18 @@
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A226" s="87" t="s">
-        <v>724</v>
-      </c>
-      <c r="B226" s="87"/>
-      <c r="C226" s="87"/>
-      <c r="D226" s="87"/>
-      <c r="E226" s="87"/>
-      <c r="F226" s="87"/>
-      <c r="G226" s="87"/>
-      <c r="H226" s="87"/>
-      <c r="I226" s="87"/>
-      <c r="J226" s="87"/>
+      <c r="A226" s="89" t="s">
+        <v>719</v>
+      </c>
+      <c r="B226" s="89"/>
+      <c r="C226" s="89"/>
+      <c r="D226" s="89"/>
+      <c r="E226" s="89"/>
+      <c r="F226" s="89"/>
+      <c r="G226" s="89"/>
+      <c r="H226" s="89"/>
+      <c r="I226" s="89"/>
+      <c r="J226" s="89"/>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="48">
@@ -11847,22 +11835,22 @@
         <v>10</v>
       </c>
       <c r="C227" s="79" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="D227" s="78" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="E227" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F227" s="79" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="G227" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H227" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I227" s="48" t="s">
         <v>12</v>
@@ -11879,22 +11867,22 @@
         <v>10</v>
       </c>
       <c r="C228" s="79" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D228" s="78" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="E228" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F228" s="79" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="G228" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H228" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I228" s="48" t="s">
         <v>12</v>
@@ -11911,22 +11899,22 @@
         <v>10</v>
       </c>
       <c r="C229" s="79" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="D229" s="78" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="E229" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F229" s="79" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="G229" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H229" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I229" s="48" t="s">
         <v>12</v>
@@ -11943,22 +11931,22 @@
         <v>10</v>
       </c>
       <c r="C230" s="79" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="D230" s="78" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="E230" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F230" s="79" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="G230" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H230" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I230" s="48" t="s">
         <v>12</v>
@@ -11975,22 +11963,22 @@
         <v>10</v>
       </c>
       <c r="C231" s="79" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="D231" s="78" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="E231" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F231" s="79" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="G231" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H231" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I231" s="48" t="s">
         <v>12</v>
@@ -12007,22 +11995,22 @@
         <v>10</v>
       </c>
       <c r="C232" s="79" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D232" s="78" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="E232" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F232" s="79" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="G232" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H232" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I232" s="48" t="s">
         <v>12</v>
@@ -12039,22 +12027,22 @@
         <v>10</v>
       </c>
       <c r="C233" s="79" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="D233" s="78" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="E233" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F233" s="79" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G233" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H233" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I233" s="48" t="s">
         <v>12</v>
@@ -12071,22 +12059,22 @@
         <v>10</v>
       </c>
       <c r="C234" s="79" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="D234" s="78" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="E234" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F234" s="79" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="G234" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H234" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I234" s="48" t="s">
         <v>12</v>
@@ -12103,22 +12091,22 @@
         <v>10</v>
       </c>
       <c r="C235" s="79" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="D235" s="78" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="E235" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F235" s="79" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="G235" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H235" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I235" s="48" t="s">
         <v>12</v>
@@ -12135,22 +12123,22 @@
         <v>10</v>
       </c>
       <c r="C236" s="79" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="D236" s="78" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="E236" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F236" s="79" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="G236" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H236" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I236" s="48" t="s">
         <v>12</v>
@@ -12167,22 +12155,22 @@
         <v>10</v>
       </c>
       <c r="C237" s="79" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="D237" s="78" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="E237" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F237" s="79" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="G237" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H237" s="48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="I237" s="48" t="s">
         <v>12</v>
@@ -12192,18 +12180,18 @@
       </c>
     </row>
     <row r="238" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="87" t="s">
-        <v>761</v>
-      </c>
-      <c r="B238" s="87"/>
-      <c r="C238" s="87"/>
-      <c r="D238" s="87"/>
-      <c r="E238" s="87"/>
-      <c r="F238" s="87"/>
-      <c r="G238" s="87"/>
-      <c r="H238" s="87"/>
-      <c r="I238" s="87"/>
-      <c r="J238" s="87"/>
+      <c r="A238" s="89" t="s">
+        <v>756</v>
+      </c>
+      <c r="B238" s="89"/>
+      <c r="C238" s="89"/>
+      <c r="D238" s="89"/>
+      <c r="E238" s="89"/>
+      <c r="F238" s="89"/>
+      <c r="G238" s="89"/>
+      <c r="H238" s="89"/>
+      <c r="I238" s="89"/>
+      <c r="J238" s="89"/>
     </row>
     <row r="239" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="48">
@@ -12213,22 +12201,22 @@
         <v>10</v>
       </c>
       <c r="C239" s="79" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="D239" s="78" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E239" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F239" s="70" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="G239" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H239" s="48" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="I239" s="48" t="s">
         <v>12</v>
@@ -12238,18 +12226,18 @@
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A240" s="87" t="s">
-        <v>773</v>
-      </c>
-      <c r="B240" s="87"/>
-      <c r="C240" s="87"/>
-      <c r="D240" s="87"/>
-      <c r="E240" s="87"/>
-      <c r="F240" s="87"/>
-      <c r="G240" s="87"/>
-      <c r="H240" s="87"/>
-      <c r="I240" s="87"/>
-      <c r="J240" s="87"/>
+      <c r="A240" s="89" t="s">
+        <v>768</v>
+      </c>
+      <c r="B240" s="89"/>
+      <c r="C240" s="89"/>
+      <c r="D240" s="89"/>
+      <c r="E240" s="89"/>
+      <c r="F240" s="89"/>
+      <c r="G240" s="89"/>
+      <c r="H240" s="89"/>
+      <c r="I240" s="89"/>
+      <c r="J240" s="89"/>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="48">
@@ -12259,22 +12247,22 @@
         <v>10</v>
       </c>
       <c r="C241" s="79" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="D241" s="78" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="E241" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F241" s="79" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="G241" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H241" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I241" s="48" t="s">
         <v>12</v>
@@ -12291,22 +12279,22 @@
         <v>10</v>
       </c>
       <c r="C242" s="79" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="D242" s="78" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="E242" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F242" s="79" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="G242" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H242" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I242" s="48" t="s">
         <v>12</v>
@@ -12323,22 +12311,22 @@
         <v>10</v>
       </c>
       <c r="C243" s="79" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="D243" s="78" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="E243" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F243" s="79" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="G243" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H243" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I243" s="48" t="s">
         <v>12</v>
@@ -12355,22 +12343,22 @@
         <v>10</v>
       </c>
       <c r="C244" s="79" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="D244" s="78" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="E244" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F244" s="79" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="G244" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H244" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I244" s="48" t="s">
         <v>12</v>
@@ -12387,22 +12375,22 @@
         <v>10</v>
       </c>
       <c r="C245" s="79" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="D245" s="78" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="E245" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F245" s="79" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="G245" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H245" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I245" s="48" t="s">
         <v>12</v>
@@ -12419,22 +12407,22 @@
         <v>10</v>
       </c>
       <c r="C246" s="79" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="D246" s="78" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="E246" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F246" s="79" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="G246" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H246" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I246" s="48" t="s">
         <v>12</v>
@@ -12451,22 +12439,22 @@
         <v>10</v>
       </c>
       <c r="C247" s="79" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="D247" s="78" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="E247" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F247" s="79" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="G247" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H247" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I247" s="48" t="s">
         <v>12</v>
@@ -12483,22 +12471,22 @@
         <v>10</v>
       </c>
       <c r="C248" s="79" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="D248" s="78" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="E248" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F248" s="79" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="G248" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H248" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I248" s="48" t="s">
         <v>12</v>
@@ -12515,22 +12503,22 @@
         <v>10</v>
       </c>
       <c r="C249" s="79" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="D249" s="78" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="E249" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F249" s="79" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="G249" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H249" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I249" s="48" t="s">
         <v>12</v>
@@ -12547,22 +12535,22 @@
         <v>10</v>
       </c>
       <c r="C250" s="79" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="D250" s="78" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="E250" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F250" s="79" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="G250" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H250" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I250" s="48" t="s">
         <v>12</v>
@@ -12579,22 +12567,22 @@
         <v>10</v>
       </c>
       <c r="C251" s="79" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="D251" s="78" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="E251" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F251" s="79" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="G251" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H251" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I251" s="48" t="s">
         <v>12</v>
@@ -12611,22 +12599,22 @@
         <v>10</v>
       </c>
       <c r="C252" s="79" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="D252" s="78" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="E252" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F252" s="79" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="G252" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H252" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I252" s="48" t="s">
         <v>12</v>
@@ -12643,22 +12631,22 @@
         <v>10</v>
       </c>
       <c r="C253" s="79" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="D253" s="78" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E253" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F253" s="79" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="G253" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H253" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I253" s="48" t="s">
         <v>12</v>
@@ -12675,22 +12663,22 @@
         <v>10</v>
       </c>
       <c r="C254" s="79" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="D254" s="78" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="E254" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F254" s="79" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="G254" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H254" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I254" s="48" t="s">
         <v>12</v>
@@ -12707,22 +12695,22 @@
         <v>10</v>
       </c>
       <c r="C255" s="79" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="D255" s="78" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="E255" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F255" s="79" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="G255" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H255" s="48" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I255" s="48" t="s">
         <v>12</v>
@@ -12732,18 +12720,18 @@
       </c>
     </row>
     <row r="256" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="87" t="s">
-        <v>818</v>
-      </c>
-      <c r="B256" s="87"/>
-      <c r="C256" s="87"/>
-      <c r="D256" s="87"/>
-      <c r="E256" s="87"/>
-      <c r="F256" s="87"/>
-      <c r="G256" s="87"/>
-      <c r="H256" s="87"/>
-      <c r="I256" s="87"/>
-      <c r="J256" s="87"/>
+      <c r="A256" s="89" t="s">
+        <v>813</v>
+      </c>
+      <c r="B256" s="89"/>
+      <c r="C256" s="89"/>
+      <c r="D256" s="89"/>
+      <c r="E256" s="89"/>
+      <c r="F256" s="89"/>
+      <c r="G256" s="89"/>
+      <c r="H256" s="89"/>
+      <c r="I256" s="89"/>
+      <c r="J256" s="89"/>
     </row>
     <row r="257" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="48">
@@ -12753,22 +12741,22 @@
         <v>10</v>
       </c>
       <c r="C257" s="79" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="D257" s="78" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="E257" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F257" s="70" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="G257" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H257" s="48" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="I257" s="48" t="s">
         <v>12</v>
@@ -12785,22 +12773,22 @@
         <v>10</v>
       </c>
       <c r="C258" s="79" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="D258" s="78" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="E258" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F258" s="70" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="G258" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H258" s="48" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="I258" s="48" t="s">
         <v>12</v>
@@ -12810,18 +12798,18 @@
       </c>
     </row>
     <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A259" s="87" t="s">
-        <v>819</v>
-      </c>
-      <c r="B259" s="87"/>
-      <c r="C259" s="87"/>
-      <c r="D259" s="87"/>
-      <c r="E259" s="87"/>
-      <c r="F259" s="87"/>
-      <c r="G259" s="87"/>
-      <c r="H259" s="87"/>
-      <c r="I259" s="87"/>
-      <c r="J259" s="87"/>
+      <c r="A259" s="89" t="s">
+        <v>814</v>
+      </c>
+      <c r="B259" s="89"/>
+      <c r="C259" s="89"/>
+      <c r="D259" s="89"/>
+      <c r="E259" s="89"/>
+      <c r="F259" s="89"/>
+      <c r="G259" s="89"/>
+      <c r="H259" s="89"/>
+      <c r="I259" s="89"/>
+      <c r="J259" s="89"/>
     </row>
     <row r="260" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="48">
@@ -12831,22 +12819,22 @@
         <v>10</v>
       </c>
       <c r="C260" s="79" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="D260" s="78" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="E260" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F260" s="70" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="G260" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H260" s="48" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="I260" s="48" t="s">
         <v>12</v>
@@ -12863,22 +12851,22 @@
         <v>10</v>
       </c>
       <c r="C261" s="79" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="D261" s="78" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="E261" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F261" s="70" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="G261" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H261" s="48" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="I261" s="48" t="s">
         <v>12</v>
@@ -12895,22 +12883,22 @@
         <v>10</v>
       </c>
       <c r="C262" s="79" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="D262" s="78" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="E262" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F262" s="70" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="G262" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H262" s="48" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="I262" s="48" t="s">
         <v>12</v>
@@ -12927,22 +12915,22 @@
         <v>10</v>
       </c>
       <c r="C263" s="79" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="D263" s="78" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="E263" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F263" s="70" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="G263" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H263" s="48" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="I263" s="48" t="s">
         <v>12</v>
@@ -12959,22 +12947,22 @@
         <v>10</v>
       </c>
       <c r="C264" s="79" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="D264" s="78" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="E264" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F264" s="70" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="G264" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H264" s="48" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="I264" s="48" t="s">
         <v>12</v>
@@ -12984,18 +12972,18 @@
       </c>
     </row>
     <row r="265" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A265" s="87" t="s">
-        <v>895</v>
-      </c>
-      <c r="B265" s="87"/>
-      <c r="C265" s="87"/>
-      <c r="D265" s="87"/>
-      <c r="E265" s="87"/>
-      <c r="F265" s="87"/>
-      <c r="G265" s="87"/>
-      <c r="H265" s="87"/>
-      <c r="I265" s="87"/>
-      <c r="J265" s="87"/>
+      <c r="A265" s="89" t="s">
+        <v>890</v>
+      </c>
+      <c r="B265" s="89"/>
+      <c r="C265" s="89"/>
+      <c r="D265" s="89"/>
+      <c r="E265" s="89"/>
+      <c r="F265" s="89"/>
+      <c r="G265" s="89"/>
+      <c r="H265" s="89"/>
+      <c r="I265" s="89"/>
+      <c r="J265" s="89"/>
     </row>
     <row r="266" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="48">
@@ -13005,22 +12993,22 @@
         <v>10</v>
       </c>
       <c r="C266" s="79" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="D266" s="78" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="E266" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F266" s="70" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="G266" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H266" s="48" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="I266" s="48" t="s">
         <v>12</v>
@@ -13030,18 +13018,18 @@
       </c>
     </row>
     <row r="267" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="87" t="s">
-        <v>922</v>
-      </c>
-      <c r="B267" s="87"/>
-      <c r="C267" s="87"/>
-      <c r="D267" s="87"/>
-      <c r="E267" s="87"/>
-      <c r="F267" s="87"/>
-      <c r="G267" s="87"/>
-      <c r="H267" s="87"/>
-      <c r="I267" s="87"/>
-      <c r="J267" s="87"/>
+      <c r="A267" s="89" t="s">
+        <v>917</v>
+      </c>
+      <c r="B267" s="89"/>
+      <c r="C267" s="89"/>
+      <c r="D267" s="89"/>
+      <c r="E267" s="89"/>
+      <c r="F267" s="89"/>
+      <c r="G267" s="89"/>
+      <c r="H267" s="89"/>
+      <c r="I267" s="89"/>
+      <c r="J267" s="89"/>
     </row>
     <row r="268" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="48">
@@ -13051,22 +13039,22 @@
         <v>10</v>
       </c>
       <c r="C268" s="79" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="D268" s="78" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="E268" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F268" s="70" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="G268" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H268" s="48" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="I268" s="48" t="s">
         <v>12</v>
@@ -13083,22 +13071,22 @@
         <v>10</v>
       </c>
       <c r="C269" s="79" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="D269" s="78" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="E269" s="48" t="s">
         <v>14</v>
       </c>
       <c r="F269" s="70" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="G269" s="48" t="s">
         <v>11</v>
       </c>
       <c r="H269" s="48" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="I269" s="48" t="s">
         <v>12</v>
@@ -13109,6 +13097,20 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A267:J267"/>
+    <mergeCell ref="A265:J265"/>
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A259:J259"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A240:J240"/>
+    <mergeCell ref="A238:J238"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A123:J123"/>
@@ -13121,20 +13123,6 @@
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A267:J267"/>
-    <mergeCell ref="A265:J265"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="A259:J259"/>
-    <mergeCell ref="A256:J256"/>
-    <mergeCell ref="A240:J240"/>
-    <mergeCell ref="A238:J238"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13320,25 +13308,25 @@
         <v>134</v>
       </c>
       <c r="T1" s="30" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="U1" s="30" t="s">
         <v>490</v>
       </c>
       <c r="V1" s="30" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="W1" s="30" t="s">
         <v>346</v>
       </c>
       <c r="X1" s="30" t="s">
+        <v>703</v>
+      </c>
+      <c r="Y1" s="31" t="s">
+        <v>704</v>
+      </c>
+      <c r="Z1" s="31" t="s">
         <v>705</v>
-      </c>
-      <c r="Y1" s="31" t="s">
-        <v>706</v>
-      </c>
-      <c r="Z1" s="31" t="s">
-        <v>707</v>
       </c>
       <c r="AA1" s="31" t="s">
         <v>604</v>
@@ -13350,7 +13338,7 @@
         <v>603</v>
       </c>
       <c r="AD1" s="31" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
@@ -17467,7 +17455,7 @@
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A53" s="47" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B53" s="48" t="s">
         <v>22</v>
@@ -22381,7 +22369,7 @@
     </row>
     <row r="112" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A112" s="48" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B112" s="48" t="s">
         <v>22</v>
@@ -22444,7 +22432,7 @@
         <v>22</v>
       </c>
       <c r="V112" s="36" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="W112" s="28" t="s">
         <v>22</v>
@@ -22465,7 +22453,7 @@
     </row>
     <row r="113" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B113" s="48" t="s">
         <v>22</v>
@@ -22549,7 +22537,7 @@
     </row>
     <row r="114" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A114" s="48" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B114" s="48" t="s">
         <v>22</v>
@@ -22615,13 +22603,13 @@
         <v>22</v>
       </c>
       <c r="W114" s="28" t="s">
+        <v>697</v>
+      </c>
+      <c r="X114" s="28" t="s">
+        <v>698</v>
+      </c>
+      <c r="Y114" s="48" t="s">
         <v>699</v>
-      </c>
-      <c r="X114" s="28" t="s">
-        <v>700</v>
-      </c>
-      <c r="Y114" s="48" t="s">
-        <v>701</v>
       </c>
       <c r="Z114" s="48" t="s">
         <v>22</v>
@@ -22633,7 +22621,7 @@
     </row>
     <row r="115" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A115" s="48" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B115" s="48" t="s">
         <v>22</v>
@@ -22708,7 +22696,7 @@
         <v>22</v>
       </c>
       <c r="Z115" s="36" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="AA115" s="28"/>
       <c r="AB115" s="28"/>
@@ -24397,7 +24385,7 @@
     </row>
     <row r="136" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A136" s="48" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B136" s="48" t="s">
         <v>22</v>
@@ -25885,7 +25873,7 @@
         <v>22</v>
       </c>
       <c r="U153" s="48" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="V153" s="48" t="s">
         <v>22</v>
@@ -27505,7 +27493,7 @@
     </row>
     <row r="173" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="76" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="B173" s="48" t="s">
         <v>22</v>
@@ -27559,7 +27547,7 @@
         <v>22</v>
       </c>
       <c r="S173" s="48" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="T173" s="48" t="s">
         <v>22</v>
@@ -27589,7 +27577,7 @@
     </row>
     <row r="174" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="76" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="B174" s="48" t="s">
         <v>22</v>
@@ -27643,7 +27631,7 @@
         <v>22</v>
       </c>
       <c r="S174" s="48" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="T174" s="48" t="s">
         <v>22</v>
@@ -27673,7 +27661,7 @@
     </row>
     <row r="175" spans="1:30" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="76" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="B175" s="48" t="s">
         <v>22</v>
@@ -27727,7 +27715,7 @@
         <v>22</v>
       </c>
       <c r="S175" s="48" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="T175" s="48" t="s">
         <v>22</v>
@@ -27811,7 +27799,7 @@
         <v>22</v>
       </c>
       <c r="S176" s="49" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="T176" s="48" t="s">
         <v>22</v>
@@ -27901,7 +27889,7 @@
         <v>22</v>
       </c>
       <c r="S177" s="49" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="T177" s="48" t="s">
         <v>22</v>
@@ -27931,7 +27919,7 @@
         <v>22</v>
       </c>
       <c r="AC177" s="73" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="AD177" s="48" t="s">
         <v>22</v>
@@ -27993,7 +27981,7 @@
         <v>22</v>
       </c>
       <c r="S178" s="49" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="T178" s="48" t="s">
         <v>22</v>
@@ -28023,7 +28011,7 @@
         <v>22</v>
       </c>
       <c r="AC178" s="73" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="AD178" s="48" t="s">
         <v>22</v>
@@ -28085,7 +28073,7 @@
         <v>22</v>
       </c>
       <c r="S179" s="49" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="T179" s="48" t="s">
         <v>22</v>
@@ -28175,7 +28163,7 @@
         <v>22</v>
       </c>
       <c r="S180" s="49" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="T180" s="48" t="s">
         <v>22</v>
@@ -28205,7 +28193,7 @@
         <v>22</v>
       </c>
       <c r="AC180" s="73" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="AD180" s="48" t="s">
         <v>22</v>
@@ -28267,7 +28255,7 @@
         <v>22</v>
       </c>
       <c r="S181" s="49" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="T181" s="48" t="s">
         <v>22</v>
@@ -28297,7 +28285,7 @@
         <v>22</v>
       </c>
       <c r="AC181" s="73" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="AD181" s="48" t="s">
         <v>22</v>
@@ -28305,7 +28293,7 @@
     </row>
     <row r="182" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="70" t="s">
-        <v>605</v>
+        <v>193</v>
       </c>
       <c r="B182" s="48" t="s">
         <v>22</v>
@@ -28359,7 +28347,7 @@
         <v>22</v>
       </c>
       <c r="S182" s="49" t="s">
-        <v>901</v>
+        <v>924</v>
       </c>
       <c r="T182" s="48" t="s">
         <v>22</v>
@@ -28388,8 +28376,8 @@
       <c r="AB182" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="AC182" s="48" t="s">
-        <v>22</v>
+      <c r="AC182" s="73" t="s">
+        <v>808</v>
       </c>
       <c r="AD182" s="48" t="s">
         <v>22</v>
@@ -28397,7 +28385,7 @@
     </row>
     <row r="183" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="70" t="s">
-        <v>609</v>
+        <v>196</v>
       </c>
       <c r="B183" s="48" t="s">
         <v>22</v>
@@ -28451,7 +28439,7 @@
         <v>22</v>
       </c>
       <c r="S183" s="49" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="T183" s="48" t="s">
         <v>22</v>
@@ -28489,7 +28477,7 @@
     </row>
     <row r="184" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="70" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B184" s="48" t="s">
         <v>22</v>
@@ -28543,7 +28531,7 @@
         <v>22</v>
       </c>
       <c r="S184" s="49" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="T184" s="48" t="s">
         <v>22</v>
@@ -28581,7 +28569,7 @@
     </row>
     <row r="185" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="70" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B185" s="48" t="s">
         <v>22</v>
@@ -28635,7 +28623,7 @@
         <v>22</v>
       </c>
       <c r="S185" s="49" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="T185" s="48" t="s">
         <v>22</v>
@@ -28668,15 +28656,15 @@
         <v>22</v>
       </c>
       <c r="AD185" s="81" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="AF185" s="48" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="186" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="70" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B186" s="48" t="s">
         <v>22</v>
@@ -28730,7 +28718,7 @@
         <v>22</v>
       </c>
       <c r="S186" s="49" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="T186" s="48" t="s">
         <v>22</v>
@@ -28763,15 +28751,15 @@
         <v>22</v>
       </c>
       <c r="AD186" s="81" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="AF186" s="48" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="187" spans="1:32" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="70" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B187" s="48" t="s">
         <v>22</v>
@@ -28858,15 +28846,15 @@
         <v>22</v>
       </c>
       <c r="AD187" s="82" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="AF187" s="48" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="188" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="70" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B188" s="48" t="s">
         <v>22</v>
@@ -28953,15 +28941,15 @@
         <v>22</v>
       </c>
       <c r="AD188" s="78" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="AE188" s="78" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
     </row>
     <row r="189" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="70" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B189" s="48" t="s">
         <v>22</v>
@@ -29048,12 +29036,12 @@
         <v>22</v>
       </c>
       <c r="AD189" s="78" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="190" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="70" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="B190" s="48" t="s">
         <v>22</v>
@@ -29140,104 +29128,104 @@
         <v>22</v>
       </c>
       <c r="AD190" s="78" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="191" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="70" t="s">
+        <v>826</v>
+      </c>
+      <c r="B191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="D191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="H191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="I191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="L191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="O191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="R191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="T191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="U191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="V191" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W191" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X191" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB191" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC191" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD191" s="78" t="s">
         <v>831</v>
-      </c>
-      <c r="B191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="G191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="H191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="L191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="O191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="P191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="R191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="S191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="T191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="U191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V191" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W191" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X191" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB191" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC191" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD191" s="78" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="192" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="70" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B192" s="48" t="s">
         <v>22</v>
@@ -29329,7 +29317,7 @@
     </row>
     <row r="193" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="70" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B193" s="48" t="s">
         <v>22</v>
@@ -29421,7 +29409,7 @@
     </row>
     <row r="194" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="70" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B194" s="48" t="s">
         <v>22</v>
@@ -29513,7 +29501,7 @@
     </row>
     <row r="195" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="70" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B195" s="48" t="s">
         <v>22</v>
@@ -29605,7 +29593,7 @@
     </row>
     <row r="196" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="70" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B196" s="48" t="s">
         <v>22</v>
@@ -29659,7 +29647,7 @@
         <v>22</v>
       </c>
       <c r="S196" s="49" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="T196" s="48" t="s">
         <v>22</v>
@@ -29689,7 +29677,7 @@
         <v>22</v>
       </c>
       <c r="AC196" s="73" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AD196" s="48" t="s">
         <v>22</v>
@@ -29697,7 +29685,7 @@
     </row>
     <row r="197" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="70" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B197" s="48" t="s">
         <v>22</v>
@@ -29751,7 +29739,7 @@
         <v>22</v>
       </c>
       <c r="S197" s="49" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="T197" s="48" t="s">
         <v>22</v>
@@ -29789,7 +29777,7 @@
     </row>
     <row r="198" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="70" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B198" s="48" t="s">
         <v>22</v>
@@ -29843,7 +29831,7 @@
         <v>22</v>
       </c>
       <c r="S198" s="49" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="T198" s="48" t="s">
         <v>22</v>
@@ -29881,7 +29869,7 @@
     </row>
     <row r="199" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="70" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B199" s="48" t="s">
         <v>22</v>
@@ -29935,7 +29923,7 @@
         <v>22</v>
       </c>
       <c r="S199" s="49" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="T199" s="48" t="s">
         <v>22</v>
@@ -29973,7 +29961,7 @@
     </row>
     <row r="200" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="70" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B200" s="48" t="s">
         <v>22</v>
@@ -30027,7 +30015,7 @@
         <v>22</v>
       </c>
       <c r="S200" s="49" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="T200" s="48" t="s">
         <v>22</v>
@@ -30065,7 +30053,7 @@
     </row>
     <row r="201" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="70" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B201" s="48" t="s">
         <v>22</v>
@@ -30119,7 +30107,7 @@
         <v>22</v>
       </c>
       <c r="S201" s="49" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="T201" s="48" t="s">
         <v>22</v>
@@ -30157,7 +30145,7 @@
     </row>
     <row r="202" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="70" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B202" s="48" t="s">
         <v>22</v>
@@ -30211,7 +30199,7 @@
         <v>22</v>
       </c>
       <c r="S202" s="49" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="T202" s="48" t="s">
         <v>22</v>
@@ -30249,7 +30237,7 @@
     </row>
     <row r="203" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="70" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B203" s="48" t="s">
         <v>22</v>
@@ -30303,7 +30291,7 @@
         <v>22</v>
       </c>
       <c r="S203" s="49" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="T203" s="48" t="s">
         <v>22</v>
@@ -30341,7 +30329,7 @@
     </row>
     <row r="204" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="70" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="B204" s="48" t="s">
         <v>22</v>
@@ -30395,7 +30383,7 @@
         <v>22</v>
       </c>
       <c r="S204" s="49" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="T204" s="48" t="s">
         <v>22</v>
@@ -30433,7 +30421,7 @@
     </row>
     <row r="205" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="70" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="B205" s="48" t="s">
         <v>22</v>
@@ -30487,7 +30475,7 @@
         <v>22</v>
       </c>
       <c r="S205" s="49" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="T205" s="48" t="s">
         <v>22</v>
@@ -30525,7 +30513,7 @@
     </row>
     <row r="206" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="70" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="B206" s="48" t="s">
         <v>22</v>
@@ -30579,7 +30567,7 @@
         <v>22</v>
       </c>
       <c r="S206" s="49" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="T206" s="48" t="s">
         <v>22</v>
@@ -30617,7 +30605,7 @@
     </row>
     <row r="207" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="70" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="B207" s="48" t="s">
         <v>22</v>
@@ -30671,7 +30659,7 @@
         <v>22</v>
       </c>
       <c r="S207" s="49" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="T207" s="48" t="s">
         <v>22</v>
@@ -30709,7 +30697,7 @@
     </row>
     <row r="208" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="70" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B208" s="48" t="s">
         <v>22</v>
@@ -30763,7 +30751,7 @@
         <v>22</v>
       </c>
       <c r="S208" s="49" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="T208" s="48" t="s">
         <v>22</v>
@@ -30801,7 +30789,7 @@
     </row>
     <row r="209" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="70" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B209" s="48" t="s">
         <v>22</v>
@@ -30855,7 +30843,7 @@
         <v>22</v>
       </c>
       <c r="S209" s="49" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="T209" s="48" t="s">
         <v>22</v>
@@ -30893,7 +30881,7 @@
     </row>
     <row r="210" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="70" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="B210" s="48" t="s">
         <v>22</v>
@@ -30947,7 +30935,7 @@
         <v>22</v>
       </c>
       <c r="S210" s="49" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="T210" s="48" t="s">
         <v>22</v>
@@ -30985,7 +30973,7 @@
     </row>
     <row r="211" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="70" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="B211" s="48" t="s">
         <v>22</v>
@@ -31039,10 +31027,10 @@
         <v>22</v>
       </c>
       <c r="S211" s="49" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="T211" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="U211" s="48" t="s">
         <v>22</v>
@@ -31077,7 +31065,7 @@
     </row>
     <row r="212" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="70" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="B212" s="48" t="s">
         <v>22</v>
@@ -31131,10 +31119,10 @@
         <v>22</v>
       </c>
       <c r="S212" s="49" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="T212" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="U212" s="48" t="s">
         <v>22</v>
@@ -31169,7 +31157,7 @@
     </row>
     <row r="213" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="70" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B213" s="48" t="s">
         <v>22</v>
@@ -31223,7 +31211,7 @@
         <v>22</v>
       </c>
       <c r="S213" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T213" s="48" t="s">
         <v>22</v>
@@ -31261,7 +31249,7 @@
     </row>
     <row r="214" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="70" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="B214" s="48" t="s">
         <v>22</v>
@@ -31315,7 +31303,7 @@
         <v>22</v>
       </c>
       <c r="S214" s="49" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="T214" s="48" t="s">
         <v>22</v>
@@ -31353,7 +31341,7 @@
     </row>
     <row r="215" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="70" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="B215" s="48" t="s">
         <v>22</v>
@@ -31407,7 +31395,7 @@
         <v>22</v>
       </c>
       <c r="S215" s="49" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="T215" s="48" t="s">
         <v>22</v>
@@ -31445,7 +31433,7 @@
     </row>
     <row r="216" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="70" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B216" s="48" t="s">
         <v>22</v>
@@ -31499,7 +31487,7 @@
         <v>22</v>
       </c>
       <c r="S216" s="49" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="T216" s="48" t="s">
         <v>22</v>
@@ -31537,7 +31525,7 @@
     </row>
     <row r="217" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="70" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="B217" s="48" t="s">
         <v>22</v>
@@ -31591,7 +31579,7 @@
         <v>22</v>
       </c>
       <c r="S217" s="49" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="T217" s="48" t="s">
         <v>22</v>
@@ -31629,7 +31617,7 @@
     </row>
     <row r="218" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="70" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="B218" s="48" t="s">
         <v>22</v>
@@ -31683,7 +31671,7 @@
         <v>22</v>
       </c>
       <c r="S218" s="49" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="T218" s="48" t="s">
         <v>22</v>
@@ -31721,7 +31709,7 @@
     </row>
     <row r="219" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="70" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="B219" s="48" t="s">
         <v>22</v>
@@ -31775,7 +31763,7 @@
         <v>22</v>
       </c>
       <c r="S219" s="49" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="T219" s="48" t="s">
         <v>22</v>
@@ -31813,7 +31801,7 @@
     </row>
     <row r="220" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="70" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="B220" s="48" t="s">
         <v>22</v>
@@ -31867,7 +31855,7 @@
         <v>22</v>
       </c>
       <c r="S220" s="49" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="T220" s="48" t="s">
         <v>22</v>
@@ -31905,7 +31893,7 @@
     </row>
     <row r="221" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="70" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B221" s="48" t="s">
         <v>22</v>
@@ -31959,7 +31947,7 @@
         <v>22</v>
       </c>
       <c r="S221" s="49" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="T221" s="48" t="s">
         <v>22</v>
@@ -31997,7 +31985,7 @@
     </row>
     <row r="222" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="70" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B222" s="48" t="s">
         <v>22</v>
@@ -32051,7 +32039,7 @@
         <v>22</v>
       </c>
       <c r="S222" s="49" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="T222" s="48" t="s">
         <v>22</v>
@@ -32089,7 +32077,7 @@
     </row>
     <row r="223" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="70" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="B223" s="48" t="s">
         <v>22</v>
@@ -32143,7 +32131,7 @@
         <v>22</v>
       </c>
       <c r="S223" s="49" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="T223" s="48" t="s">
         <v>22</v>
@@ -32181,7 +32169,7 @@
     </row>
     <row r="224" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="70" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B224" s="48" t="s">
         <v>22</v>
@@ -32235,7 +32223,7 @@
         <v>22</v>
       </c>
       <c r="S224" s="49" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="T224" s="48" t="s">
         <v>22</v>
@@ -32273,7 +32261,7 @@
     </row>
     <row r="225" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="70" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="B225" s="48" t="s">
         <v>22</v>
@@ -32327,7 +32315,7 @@
         <v>22</v>
       </c>
       <c r="S225" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T225" s="48" t="s">
         <v>22</v>
@@ -32357,15 +32345,15 @@
         <v>22</v>
       </c>
       <c r="AC225" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD225" s="73" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
     </row>
     <row r="226" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="70" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="B226" s="48" t="s">
         <v>22</v>
@@ -32419,7 +32407,7 @@
         <v>22</v>
       </c>
       <c r="S226" s="49" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="T226" s="48" t="s">
         <v>22</v>
@@ -32449,7 +32437,7 @@
         <v>22</v>
       </c>
       <c r="AC226" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD226" s="48" t="s">
         <v>22</v>
@@ -32457,7 +32445,7 @@
     </row>
     <row r="227" spans="1:30" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="70" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="B227" s="48" t="s">
         <v>22</v>
@@ -32511,10 +32499,10 @@
         <v>22</v>
       </c>
       <c r="S227" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T227" s="49" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="U227" s="48" t="s">
         <v>22</v>
@@ -32541,7 +32529,7 @@
         <v>22</v>
       </c>
       <c r="AC227" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD227" s="48" t="s">
         <v>22</v>
@@ -32549,7 +32537,7 @@
     </row>
     <row r="228" spans="1:30" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="70" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="B228" s="48" t="s">
         <v>22</v>
@@ -32603,10 +32591,10 @@
         <v>22</v>
       </c>
       <c r="S228" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T228" s="49" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="U228" s="48" t="s">
         <v>22</v>
@@ -32633,7 +32621,7 @@
         <v>22</v>
       </c>
       <c r="AC228" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD228" s="48" t="s">
         <v>22</v>
@@ -32641,7 +32629,7 @@
     </row>
     <row r="229" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="70" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B229" s="48" t="s">
         <v>22</v>
@@ -32695,10 +32683,10 @@
         <v>22</v>
       </c>
       <c r="S229" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T229" s="48" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="U229" s="48" t="s">
         <v>22</v>
@@ -32725,7 +32713,7 @@
         <v>22</v>
       </c>
       <c r="AC229" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD229" s="48" t="s">
         <v>22</v>
@@ -32733,7 +32721,7 @@
     </row>
     <row r="230" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="70" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="B230" s="48" t="s">
         <v>22</v>
@@ -32787,7 +32775,7 @@
         <v>22</v>
       </c>
       <c r="S230" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T230" s="48" t="s">
         <v>22</v>
@@ -32817,7 +32805,7 @@
         <v>22</v>
       </c>
       <c r="AC230" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD230" s="48" t="s">
         <v>22</v>
@@ -32825,7 +32813,7 @@
     </row>
     <row r="231" spans="1:30" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="70" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="B231" s="48" t="s">
         <v>22</v>
@@ -32879,10 +32867,10 @@
         <v>22</v>
       </c>
       <c r="S231" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T231" s="49" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="U231" s="48" t="s">
         <v>22</v>
@@ -32909,15 +32897,15 @@
         <v>22</v>
       </c>
       <c r="AC231" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD231" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
     </row>
     <row r="232" spans="1:30" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="70" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="B232" s="48" t="s">
         <v>22</v>
@@ -32971,10 +32959,10 @@
         <v>22</v>
       </c>
       <c r="S232" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T232" s="49" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="U232" s="48" t="s">
         <v>22</v>
@@ -33001,7 +32989,7 @@
         <v>22</v>
       </c>
       <c r="AC232" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD232" s="48" t="s">
         <v>22</v>
@@ -33009,7 +32997,7 @@
     </row>
     <row r="233" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="70" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="B233" s="48" t="s">
         <v>22</v>
@@ -33063,7 +33051,7 @@
         <v>22</v>
       </c>
       <c r="S233" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T233" s="48" t="s">
         <v>22</v>
@@ -33093,7 +33081,7 @@
         <v>22</v>
       </c>
       <c r="AC233" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD233" s="48" t="s">
         <v>22</v>
@@ -33101,7 +33089,7 @@
     </row>
     <row r="234" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="70" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="B234" s="48" t="s">
         <v>22</v>
@@ -33155,10 +33143,10 @@
         <v>22</v>
       </c>
       <c r="S234" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T234" s="49" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="U234" s="48" t="s">
         <v>22</v>
@@ -33185,7 +33173,7 @@
         <v>22</v>
       </c>
       <c r="AC234" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD234" s="48" t="s">
         <v>22</v>
@@ -33193,7 +33181,7 @@
     </row>
     <row r="235" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="70" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="B235" s="48" t="s">
         <v>22</v>
@@ -33247,10 +33235,10 @@
         <v>22</v>
       </c>
       <c r="S235" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T235" s="49" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="U235" s="48" t="s">
         <v>22</v>
@@ -33277,7 +33265,7 @@
         <v>22</v>
       </c>
       <c r="AC235" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD235" s="48" t="s">
         <v>22</v>
@@ -33285,7 +33273,7 @@
     </row>
     <row r="236" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="70" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="B236" s="48" t="s">
         <v>22</v>
@@ -33339,10 +33327,10 @@
         <v>22</v>
       </c>
       <c r="S236" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T236" s="49" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="U236" s="48" t="s">
         <v>22</v>
@@ -33369,7 +33357,7 @@
         <v>22</v>
       </c>
       <c r="AC236" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD236" s="48" t="s">
         <v>22</v>
@@ -33377,7 +33365,7 @@
     </row>
     <row r="237" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="70" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="B237" s="48" t="s">
         <v>22</v>
@@ -33431,10 +33419,10 @@
         <v>22</v>
       </c>
       <c r="S237" s="49" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="T237" s="49" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="U237" s="48" t="s">
         <v>22</v>
@@ -33461,7 +33449,7 @@
         <v>22</v>
       </c>
       <c r="AC237" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD237" s="48" t="s">
         <v>22</v>
@@ -33469,7 +33457,7 @@
     </row>
     <row r="238" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="70" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="B238" s="48" t="s">
         <v>22</v>
@@ -33523,10 +33511,10 @@
         <v>22</v>
       </c>
       <c r="S238" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T238" s="49" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="U238" s="48" t="s">
         <v>22</v>
@@ -33553,7 +33541,7 @@
         <v>22</v>
       </c>
       <c r="AC238" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD238" s="48" t="s">
         <v>22</v>
@@ -33561,7 +33549,7 @@
     </row>
     <row r="239" spans="1:30" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="70" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B239" s="48" t="s">
         <v>22</v>
@@ -33615,16 +33603,16 @@
         <v>22</v>
       </c>
       <c r="S239" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T239" s="49" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="U239" s="49" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="V239" s="48" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="W239" s="28" t="s">
         <v>22</v>
@@ -33645,7 +33633,7 @@
         <v>22</v>
       </c>
       <c r="AC239" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD239" s="48" t="s">
         <v>22</v>
@@ -33653,7 +33641,7 @@
     </row>
     <row r="240" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="70" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="B240" s="48" t="s">
         <v>22</v>
@@ -33745,7 +33733,7 @@
     </row>
     <row r="241" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="70" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B241" s="48" t="s">
         <v>22</v>
@@ -33837,7 +33825,7 @@
     </row>
     <row r="242" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="70" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="B242" s="48" t="s">
         <v>22</v>
@@ -33929,7 +33917,7 @@
     </row>
     <row r="243" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="70" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="B243" s="48" t="s">
         <v>22</v>
@@ -33983,7 +33971,7 @@
         <v>22</v>
       </c>
       <c r="S243" s="49" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="T243" s="48" t="s">
         <v>22</v>
@@ -34021,7 +34009,7 @@
     </row>
     <row r="244" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="70" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="B244" s="48" t="s">
         <v>22</v>
@@ -34105,7 +34093,7 @@
         <v>22</v>
       </c>
       <c r="AC244" s="73" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="AD244" s="48" t="s">
         <v>22</v>
@@ -34113,7 +34101,7 @@
     </row>
     <row r="245" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="70" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="B245" s="48" t="s">
         <v>22</v>
@@ -34197,7 +34185,7 @@
         <v>22</v>
       </c>
       <c r="AC245" s="73" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="AD245" s="48" t="s">
         <v>22</v>
@@ -34205,7 +34193,7 @@
     </row>
     <row r="246" spans="1:30" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="70" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="B246" s="48" t="s">
         <v>22</v>
@@ -34289,7 +34277,7 @@
         <v>22</v>
       </c>
       <c r="AC246" s="73" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="AD246" s="48" t="s">
         <v>22</v>
@@ -34297,7 +34285,7 @@
     </row>
     <row r="247" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="B247" t="s">
         <v>22</v>
@@ -34351,7 +34339,7 @@
         <v>22</v>
       </c>
       <c r="S247" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="T247" t="s">
         <v>22</v>
@@ -34389,7 +34377,7 @@
     </row>
     <row r="248" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="B248" t="s">
         <v>22</v>
@@ -34443,7 +34431,7 @@
         <v>22</v>
       </c>
       <c r="S248" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="T248" t="s">
         <v>22</v>
@@ -34481,7 +34469,7 @@
     </row>
     <row r="249" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B249" t="s">
         <v>22</v>
@@ -34573,7 +34561,7 @@
     </row>
     <row r="250" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="B250" t="s">
         <v>22</v>
@@ -34665,7 +34653,7 @@
     </row>
     <row r="251" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="B251" t="s">
         <v>22</v>
@@ -34883,49 +34871,49 @@
     <hyperlink ref="S186" r:id="rId19" xr:uid="{7E9C7A94-A136-40F4-8926-E175506C0FB0}"/>
     <hyperlink ref="S200" r:id="rId20" xr:uid="{6E155B27-A1F3-4634-AF94-EA4AFCBB6FA8}"/>
     <hyperlink ref="S178" r:id="rId21" display="https://opt.adm.testingserver8.com/admin/product" xr:uid="{FE84E4EC-8AD8-4353-9CF9-0FFD7AF22EC6}"/>
-    <hyperlink ref="S182" r:id="rId22" display="https://opt.adm.testingserver8.com/admin/special-timer-event" xr:uid="{DC091BA2-1053-4AEE-9250-D6D43A208977}"/>
-    <hyperlink ref="S183" r:id="rId23" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{6E9132F4-992B-46D1-9A28-5D473938DFF8}"/>
-    <hyperlink ref="S184" r:id="rId24" display="https://opt.adm.testingserver8.com/admin/product-collection" xr:uid="{B7714AD9-0B49-4F19-B276-CBDABCB03633}"/>
-    <hyperlink ref="S185" r:id="rId25" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{965BF565-0242-4239-B278-6E574AF5D044}"/>
-    <hyperlink ref="S214" r:id="rId26" xr:uid="{C1127956-48DF-433C-AD28-9DA999FBCC26}"/>
-    <hyperlink ref="S213" r:id="rId27" xr:uid="{C9182A01-C96D-4110-9CA5-C017A54856E8}"/>
-    <hyperlink ref="S225" r:id="rId28" xr:uid="{6C20156C-B7E3-4D33-B99C-3A1821930139}"/>
-    <hyperlink ref="S230" r:id="rId29" xr:uid="{BAC34349-31E9-4520-A81D-6EEDD88BD29C}"/>
-    <hyperlink ref="S228" r:id="rId30" xr:uid="{95A32C29-884B-4748-92B0-EDDF6C5CE209}"/>
-    <hyperlink ref="S227" r:id="rId31" xr:uid="{118D0710-0BF2-49C8-888F-870ACC682CB5}"/>
-    <hyperlink ref="S231" r:id="rId32" xr:uid="{95BCE644-FF9B-472B-8145-F31A886E4FC4}"/>
-    <hyperlink ref="T231" r:id="rId33" xr:uid="{89BBFA7B-AD6E-4F93-BFD3-447AE8F7C502}"/>
-    <hyperlink ref="S232" r:id="rId34" xr:uid="{C8BD3F97-CFD5-4E09-8346-C525E3D0F983}"/>
-    <hyperlink ref="T232" r:id="rId35" display="https://console.zlaata.com/admin/return-order" xr:uid="{7EB489AF-7DBE-4776-BCF8-60461A79DB05}"/>
-    <hyperlink ref="S233" r:id="rId36" xr:uid="{570ACAD2-9993-464C-95C3-A0F384F535D4}"/>
-    <hyperlink ref="S234" r:id="rId37" xr:uid="{A5E4F190-F60E-4C69-A7BF-9E5AD6674C56}"/>
-    <hyperlink ref="S235" r:id="rId38" xr:uid="{0DD56580-2553-4B3D-AC00-0568BF6AD0B9}"/>
-    <hyperlink ref="S236" r:id="rId39" xr:uid="{16CBC571-4EE4-4D66-B8C3-CE0279FDD836}"/>
-    <hyperlink ref="T234" r:id="rId40" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{5FB45239-0134-4C16-87DB-11C106356D92}"/>
-    <hyperlink ref="AD231" r:id="rId41" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{79B826CA-7F44-45A6-9BD2-CC8919CFA12A}"/>
-    <hyperlink ref="AC177" r:id="rId42" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{7BE8FE18-5C75-431B-8488-FBDEF16485E5}"/>
-    <hyperlink ref="AC178" r:id="rId43" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{FF640DAE-0F42-4B2A-A086-F1C73287AD75}"/>
-    <hyperlink ref="AC244" r:id="rId44" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
-    <hyperlink ref="T211" r:id="rId45" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
-    <hyperlink ref="T212" r:id="rId46" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
-    <hyperlink ref="S199" r:id="rId47" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
-    <hyperlink ref="AC225" r:id="rId48" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{CD96CCCF-BE60-40A1-BA2F-93729430B99A}"/>
-    <hyperlink ref="AC226:AC239" r:id="rId49" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
-    <hyperlink ref="S219" r:id="rId50" display="https://qa.zlta.testingserver8.com/admin/payment-pending" xr:uid="{37E5E50E-434D-4FC0-B9A6-C0648E88FF97}"/>
-    <hyperlink ref="S206" r:id="rId51" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
-    <hyperlink ref="S204" r:id="rId52" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
-    <hyperlink ref="S205" r:id="rId53" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
-    <hyperlink ref="S196" r:id="rId54" display="https://console.zlaata.com/admin/product" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
-    <hyperlink ref="S243" r:id="rId55" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
-    <hyperlink ref="T236" r:id="rId56" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
-    <hyperlink ref="S226" r:id="rId57" display="https://console.zlaata.com/admin/cancel-order" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
-    <hyperlink ref="AC237" r:id="rId58" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{B5FFBFD3-2AEB-43E2-A088-AA986500C94C}"/>
-    <hyperlink ref="S237" r:id="rId59" xr:uid="{E29AE273-A13B-4FDA-99DA-66C3FC3DF993}"/>
-    <hyperlink ref="S239" r:id="rId60" xr:uid="{E5A47A78-2C35-4A72-A585-72E3D18CC556}"/>
-    <hyperlink ref="AC238" r:id="rId61" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{A40E89D1-5252-43A0-AF9C-1AAAC503CE8E}"/>
-    <hyperlink ref="S238" r:id="rId62" xr:uid="{EFD712A1-7827-446F-B5F1-9CC652078EB0}"/>
-    <hyperlink ref="AC180" r:id="rId63" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{6262B2DA-10A4-449F-8938-AC96E529EF5A}"/>
-    <hyperlink ref="AC181" r:id="rId64" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{A98207AA-9B31-4A4E-BB36-48E505D5F843}"/>
+    <hyperlink ref="S183" r:id="rId22" xr:uid="{6E9132F4-992B-46D1-9A28-5D473938DFF8}"/>
+    <hyperlink ref="S184" r:id="rId23" display="https://opt.adm.testingserver8.com/admin/product-collection" xr:uid="{B7714AD9-0B49-4F19-B276-CBDABCB03633}"/>
+    <hyperlink ref="S185" r:id="rId24" display="https://opt.adm.testingserver8.com/admin/categories" xr:uid="{965BF565-0242-4239-B278-6E574AF5D044}"/>
+    <hyperlink ref="S214" r:id="rId25" xr:uid="{C1127956-48DF-433C-AD28-9DA999FBCC26}"/>
+    <hyperlink ref="S213" r:id="rId26" xr:uid="{C9182A01-C96D-4110-9CA5-C017A54856E8}"/>
+    <hyperlink ref="S225" r:id="rId27" xr:uid="{6C20156C-B7E3-4D33-B99C-3A1821930139}"/>
+    <hyperlink ref="S230" r:id="rId28" xr:uid="{BAC34349-31E9-4520-A81D-6EEDD88BD29C}"/>
+    <hyperlink ref="S228" r:id="rId29" xr:uid="{95A32C29-884B-4748-92B0-EDDF6C5CE209}"/>
+    <hyperlink ref="S227" r:id="rId30" xr:uid="{118D0710-0BF2-49C8-888F-870ACC682CB5}"/>
+    <hyperlink ref="S231" r:id="rId31" xr:uid="{95BCE644-FF9B-472B-8145-F31A886E4FC4}"/>
+    <hyperlink ref="T231" r:id="rId32" xr:uid="{89BBFA7B-AD6E-4F93-BFD3-447AE8F7C502}"/>
+    <hyperlink ref="S232" r:id="rId33" xr:uid="{C8BD3F97-CFD5-4E09-8346-C525E3D0F983}"/>
+    <hyperlink ref="T232" r:id="rId34" display="https://console.zlaata.com/admin/return-order" xr:uid="{7EB489AF-7DBE-4776-BCF8-60461A79DB05}"/>
+    <hyperlink ref="S233" r:id="rId35" xr:uid="{570ACAD2-9993-464C-95C3-A0F384F535D4}"/>
+    <hyperlink ref="S234" r:id="rId36" xr:uid="{A5E4F190-F60E-4C69-A7BF-9E5AD6674C56}"/>
+    <hyperlink ref="S235" r:id="rId37" xr:uid="{0DD56580-2553-4B3D-AC00-0568BF6AD0B9}"/>
+    <hyperlink ref="S236" r:id="rId38" xr:uid="{16CBC571-4EE4-4D66-B8C3-CE0279FDD836}"/>
+    <hyperlink ref="T234" r:id="rId39" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{5FB45239-0134-4C16-87DB-11C106356D92}"/>
+    <hyperlink ref="AD231" r:id="rId40" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{79B826CA-7F44-45A6-9BD2-CC8919CFA12A}"/>
+    <hyperlink ref="AC177" r:id="rId41" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{7BE8FE18-5C75-431B-8488-FBDEF16485E5}"/>
+    <hyperlink ref="AC178" r:id="rId42" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{FF640DAE-0F42-4B2A-A086-F1C73287AD75}"/>
+    <hyperlink ref="AC244" r:id="rId43" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{622FD3BA-2464-4E1D-99AB-AE1AAC131875}"/>
+    <hyperlink ref="T211" r:id="rId44" xr:uid="{7F5A23D3-57AD-40E6-ACE3-9B9EA550F6A6}"/>
+    <hyperlink ref="T212" r:id="rId45" xr:uid="{7C8D8F70-AFD1-452B-AFB6-66EC6F975597}"/>
+    <hyperlink ref="S199" r:id="rId46" xr:uid="{279698D4-2A41-4BBD-838A-CBE141EE3D50}"/>
+    <hyperlink ref="AC225" r:id="rId47" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{CD96CCCF-BE60-40A1-BA2F-93729430B99A}"/>
+    <hyperlink ref="AC226:AC239" r:id="rId48" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{C68B94AD-4CFE-4AB2-9431-B829C1D5A48C}"/>
+    <hyperlink ref="S219" r:id="rId49" display="https://qa.zlta.testingserver8.com/admin/payment-pending" xr:uid="{37E5E50E-434D-4FC0-B9A6-C0648E88FF97}"/>
+    <hyperlink ref="S206" r:id="rId50" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{C356118E-7CF8-4DBB-80E8-2AC4DA83F153}"/>
+    <hyperlink ref="S204" r:id="rId51" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{51EDB8E8-7B87-48E3-AE6E-CF4598B89047}"/>
+    <hyperlink ref="S205" r:id="rId52" display="https://console.zlaata.com/admin/track-inventory" xr:uid="{F9518A74-6EB1-4B3C-A794-D43A85FC89FC}"/>
+    <hyperlink ref="S196" r:id="rId53" display="https://console.zlaata.com/admin/product" xr:uid="{A066661C-4711-4794-9163-A0D6D45D12E9}"/>
+    <hyperlink ref="S243" r:id="rId54" xr:uid="{0CC1540C-B1B3-46DB-BCD2-8D3B9125A244}"/>
+    <hyperlink ref="T236" r:id="rId55" display="https://console.zlaata.com/admin/exchange-order" xr:uid="{23A771F7-7B93-4572-9760-49587EB1BBAA}"/>
+    <hyperlink ref="S226" r:id="rId56" display="https://console.zlaata.com/admin/cancel-order" xr:uid="{36065242-70A6-4880-B09A-02C4BF11269E}"/>
+    <hyperlink ref="AC237" r:id="rId57" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{B5FFBFD3-2AEB-43E2-A088-AA986500C94C}"/>
+    <hyperlink ref="S237" r:id="rId58" xr:uid="{E29AE273-A13B-4FDA-99DA-66C3FC3DF993}"/>
+    <hyperlink ref="S239" r:id="rId59" xr:uid="{E5A47A78-2C35-4A72-A585-72E3D18CC556}"/>
+    <hyperlink ref="AC238" r:id="rId60" tooltip="Crop Waistcoat Set" display="https://testing.zlaata.com/product-detail/purple-ikat-waistcoat-pant-cotton-co-ord-set" xr:uid="{A40E89D1-5252-43A0-AF9C-1AAAC503CE8E}"/>
+    <hyperlink ref="S238" r:id="rId61" xr:uid="{EFD712A1-7827-446F-B5F1-9CC652078EB0}"/>
+    <hyperlink ref="AC180" r:id="rId62" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{6262B2DA-10A4-449F-8938-AC96E529EF5A}"/>
+    <hyperlink ref="AC181" r:id="rId63" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{A98207AA-9B31-4A4E-BB36-48E505D5F843}"/>
+    <hyperlink ref="AC182" r:id="rId64" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{B19B4716-3A72-4609-978F-A41A7047AD51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId65"/>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever0\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever1235\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A917436F-BB33-48DA-AC97-72962E686F43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA13683-36D3-4F57-9A59-9403343E4DEF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8927" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8967" uniqueCount="936">
   <si>
     <t>S.No</t>
   </si>
@@ -2819,6 +2819,21 @@
   </si>
   <si>
     <t>Create and verify Influencer Pointer for product on homepage.</t>
+  </si>
+  <si>
+    <t>Stock Quantity</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Stock_01</t>
+  </si>
+  <si>
+    <t>Place order when stock is available.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Stock_01</t>
+  </si>
+  <si>
+    <t>Stock</t>
   </si>
 </sst>
 </file>
@@ -3475,13 +3490,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4325,7 +4340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z269"/>
+  <dimension ref="A1:Z271"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -7610,18 +7625,18 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="87" t="s">
+      <c r="A106" s="88" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="87"/>
-      <c r="C106" s="87"/>
-      <c r="D106" s="87"/>
-      <c r="E106" s="87"/>
-      <c r="F106" s="87"/>
-      <c r="G106" s="87"/>
-      <c r="H106" s="87"/>
-      <c r="I106" s="87"/>
-      <c r="J106" s="87"/>
+      <c r="B106" s="88"/>
+      <c r="C106" s="88"/>
+      <c r="D106" s="88"/>
+      <c r="E106" s="88"/>
+      <c r="F106" s="88"/>
+      <c r="G106" s="88"/>
+      <c r="H106" s="88"/>
+      <c r="I106" s="88"/>
+      <c r="J106" s="88"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -8114,18 +8129,18 @@
       <c r="X120" s="58"/>
     </row>
     <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="88" t="s">
+      <c r="A121" s="89" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="88"/>
-      <c r="C121" s="88"/>
-      <c r="D121" s="88"/>
-      <c r="E121" s="88"/>
-      <c r="F121" s="88"/>
-      <c r="G121" s="88"/>
-      <c r="H121" s="88"/>
-      <c r="I121" s="88"/>
-      <c r="J121" s="88"/>
+      <c r="B121" s="89"/>
+      <c r="C121" s="89"/>
+      <c r="D121" s="89"/>
+      <c r="E121" s="89"/>
+      <c r="F121" s="89"/>
+      <c r="G121" s="89"/>
+      <c r="H121" s="89"/>
+      <c r="I121" s="89"/>
+      <c r="J121" s="89"/>
       <c r="K121" s="57"/>
       <c r="L121" s="58"/>
       <c r="M121" s="58"/>
@@ -8188,18 +8203,18 @@
       <c r="X122" s="58"/>
     </row>
     <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="88" t="s">
+      <c r="A123" s="89" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="88"/>
-      <c r="C123" s="88"/>
-      <c r="D123" s="88"/>
-      <c r="E123" s="88"/>
-      <c r="F123" s="88"/>
-      <c r="G123" s="88"/>
-      <c r="H123" s="88"/>
-      <c r="I123" s="88"/>
-      <c r="J123" s="88"/>
+      <c r="B123" s="89"/>
+      <c r="C123" s="89"/>
+      <c r="D123" s="89"/>
+      <c r="E123" s="89"/>
+      <c r="F123" s="89"/>
+      <c r="G123" s="89"/>
+      <c r="H123" s="89"/>
+      <c r="I123" s="89"/>
+      <c r="J123" s="89"/>
       <c r="K123" s="57"/>
       <c r="L123" s="58"/>
       <c r="M123" s="58"/>
@@ -8262,18 +8277,18 @@
       <c r="X124" s="58"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="88" t="s">
+      <c r="A125" s="89" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="88"/>
-      <c r="C125" s="88"/>
-      <c r="D125" s="88"/>
-      <c r="E125" s="88"/>
-      <c r="F125" s="88"/>
-      <c r="G125" s="88"/>
-      <c r="H125" s="88"/>
-      <c r="I125" s="88"/>
-      <c r="J125" s="88"/>
+      <c r="B125" s="89"/>
+      <c r="C125" s="89"/>
+      <c r="D125" s="89"/>
+      <c r="E125" s="89"/>
+      <c r="F125" s="89"/>
+      <c r="G125" s="89"/>
+      <c r="H125" s="89"/>
+      <c r="I125" s="89"/>
+      <c r="J125" s="89"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -8598,11 +8613,11 @@
       <c r="X132" s="58"/>
     </row>
     <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="88" t="s">
+      <c r="A133" s="89" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="88"/>
-      <c r="C133" s="88"/>
+      <c r="B133" s="89"/>
+      <c r="C133" s="89"/>
       <c r="D133" s="90"/>
       <c r="E133" s="90"/>
       <c r="F133" s="90"/>
@@ -9562,18 +9577,18 @@
       <c r="Z155" s="58"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="88" t="s">
+      <c r="A156" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="88"/>
-      <c r="C156" s="88"/>
-      <c r="D156" s="88"/>
-      <c r="E156" s="88"/>
-      <c r="F156" s="88"/>
-      <c r="G156" s="88"/>
-      <c r="H156" s="88"/>
-      <c r="I156" s="88"/>
-      <c r="J156" s="88"/>
+      <c r="B156" s="89"/>
+      <c r="C156" s="89"/>
+      <c r="D156" s="89"/>
+      <c r="E156" s="89"/>
+      <c r="F156" s="89"/>
+      <c r="G156" s="89"/>
+      <c r="H156" s="89"/>
+      <c r="I156" s="89"/>
+      <c r="J156" s="89"/>
       <c r="K156" s="58"/>
       <c r="L156" s="58"/>
       <c r="M156" s="58"/>
@@ -9640,18 +9655,18 @@
       <c r="Z157" s="58"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="88" t="s">
+      <c r="A158" s="89" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="88"/>
-      <c r="C158" s="88"/>
-      <c r="D158" s="88"/>
-      <c r="E158" s="88"/>
-      <c r="F158" s="88"/>
-      <c r="G158" s="88"/>
-      <c r="H158" s="88"/>
-      <c r="I158" s="88"/>
-      <c r="J158" s="88"/>
+      <c r="B158" s="89"/>
+      <c r="C158" s="89"/>
+      <c r="D158" s="89"/>
+      <c r="E158" s="89"/>
+      <c r="F158" s="89"/>
+      <c r="G158" s="89"/>
+      <c r="H158" s="89"/>
+      <c r="I158" s="89"/>
+      <c r="J158" s="89"/>
       <c r="K158" s="58"/>
       <c r="L158" s="58"/>
       <c r="M158" s="58"/>
@@ -10486,18 +10501,18 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="88" t="s">
+      <c r="A180" s="89" t="s">
         <v>707</v>
       </c>
-      <c r="B180" s="88"/>
-      <c r="C180" s="88"/>
-      <c r="D180" s="89"/>
-      <c r="E180" s="88"/>
-      <c r="F180" s="88"/>
-      <c r="G180" s="88"/>
-      <c r="H180" s="88"/>
-      <c r="I180" s="88"/>
-      <c r="J180" s="88"/>
+      <c r="B180" s="89"/>
+      <c r="C180" s="89"/>
+      <c r="D180" s="87"/>
+      <c r="E180" s="89"/>
+      <c r="F180" s="89"/>
+      <c r="G180" s="89"/>
+      <c r="H180" s="89"/>
+      <c r="I180" s="89"/>
+      <c r="J180" s="89"/>
     </row>
     <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="68">
@@ -11026,18 +11041,18 @@
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A198" s="89" t="s">
+      <c r="A198" s="87" t="s">
         <v>630</v>
       </c>
-      <c r="B198" s="89"/>
-      <c r="C198" s="89"/>
-      <c r="D198" s="89"/>
-      <c r="E198" s="89"/>
-      <c r="F198" s="89"/>
-      <c r="G198" s="89"/>
-      <c r="H198" s="89"/>
-      <c r="I198" s="89"/>
-      <c r="J198" s="89"/>
+      <c r="B198" s="87"/>
+      <c r="C198" s="87"/>
+      <c r="D198" s="87"/>
+      <c r="E198" s="87"/>
+      <c r="F198" s="87"/>
+      <c r="G198" s="87"/>
+      <c r="H198" s="87"/>
+      <c r="I198" s="87"/>
+      <c r="J198" s="87"/>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="48">
@@ -11168,18 +11183,18 @@
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A203" s="89" t="s">
+      <c r="A203" s="87" t="s">
         <v>643</v>
       </c>
-      <c r="B203" s="89"/>
-      <c r="C203" s="89"/>
-      <c r="D203" s="89"/>
-      <c r="E203" s="89"/>
-      <c r="F203" s="89"/>
-      <c r="G203" s="89"/>
-      <c r="H203" s="89"/>
-      <c r="I203" s="89"/>
-      <c r="J203" s="89"/>
+      <c r="B203" s="87"/>
+      <c r="C203" s="87"/>
+      <c r="D203" s="87"/>
+      <c r="E203" s="87"/>
+      <c r="F203" s="87"/>
+      <c r="G203" s="87"/>
+      <c r="H203" s="87"/>
+      <c r="I203" s="87"/>
+      <c r="J203" s="87"/>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="48">
@@ -11214,18 +11229,18 @@
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A205" s="89" t="s">
+      <c r="A205" s="87" t="s">
         <v>649</v>
       </c>
-      <c r="B205" s="89"/>
-      <c r="C205" s="89"/>
-      <c r="D205" s="89"/>
-      <c r="E205" s="89"/>
-      <c r="F205" s="89"/>
-      <c r="G205" s="89"/>
-      <c r="H205" s="89"/>
-      <c r="I205" s="89"/>
-      <c r="J205" s="89"/>
+      <c r="B205" s="87"/>
+      <c r="C205" s="87"/>
+      <c r="D205" s="87"/>
+      <c r="E205" s="87"/>
+      <c r="F205" s="87"/>
+      <c r="G205" s="87"/>
+      <c r="H205" s="87"/>
+      <c r="I205" s="87"/>
+      <c r="J205" s="87"/>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="48">
@@ -11640,18 +11655,18 @@
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A220" s="89" t="s">
+      <c r="A220" s="87" t="s">
         <v>711</v>
       </c>
-      <c r="B220" s="89"/>
-      <c r="C220" s="89"/>
-      <c r="D220" s="89"/>
-      <c r="E220" s="89"/>
-      <c r="F220" s="89"/>
-      <c r="G220" s="89"/>
-      <c r="H220" s="89"/>
-      <c r="I220" s="89"/>
-      <c r="J220" s="89"/>
+      <c r="B220" s="87"/>
+      <c r="C220" s="87"/>
+      <c r="D220" s="87"/>
+      <c r="E220" s="87"/>
+      <c r="F220" s="87"/>
+      <c r="G220" s="87"/>
+      <c r="H220" s="87"/>
+      <c r="I220" s="87"/>
+      <c r="J220" s="87"/>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="48">
@@ -11814,18 +11829,18 @@
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A226" s="89" t="s">
+      <c r="A226" s="87" t="s">
         <v>719</v>
       </c>
-      <c r="B226" s="89"/>
-      <c r="C226" s="89"/>
-      <c r="D226" s="89"/>
-      <c r="E226" s="89"/>
-      <c r="F226" s="89"/>
-      <c r="G226" s="89"/>
-      <c r="H226" s="89"/>
-      <c r="I226" s="89"/>
-      <c r="J226" s="89"/>
+      <c r="B226" s="87"/>
+      <c r="C226" s="87"/>
+      <c r="D226" s="87"/>
+      <c r="E226" s="87"/>
+      <c r="F226" s="87"/>
+      <c r="G226" s="87"/>
+      <c r="H226" s="87"/>
+      <c r="I226" s="87"/>
+      <c r="J226" s="87"/>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="48">
@@ -12180,18 +12195,18 @@
       </c>
     </row>
     <row r="238" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A238" s="89" t="s">
+      <c r="A238" s="87" t="s">
         <v>756</v>
       </c>
-      <c r="B238" s="89"/>
-      <c r="C238" s="89"/>
-      <c r="D238" s="89"/>
-      <c r="E238" s="89"/>
-      <c r="F238" s="89"/>
-      <c r="G238" s="89"/>
-      <c r="H238" s="89"/>
-      <c r="I238" s="89"/>
-      <c r="J238" s="89"/>
+      <c r="B238" s="87"/>
+      <c r="C238" s="87"/>
+      <c r="D238" s="87"/>
+      <c r="E238" s="87"/>
+      <c r="F238" s="87"/>
+      <c r="G238" s="87"/>
+      <c r="H238" s="87"/>
+      <c r="I238" s="87"/>
+      <c r="J238" s="87"/>
     </row>
     <row r="239" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="48">
@@ -12226,18 +12241,18 @@
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A240" s="89" t="s">
+      <c r="A240" s="87" t="s">
         <v>768</v>
       </c>
-      <c r="B240" s="89"/>
-      <c r="C240" s="89"/>
-      <c r="D240" s="89"/>
-      <c r="E240" s="89"/>
-      <c r="F240" s="89"/>
-      <c r="G240" s="89"/>
-      <c r="H240" s="89"/>
-      <c r="I240" s="89"/>
-      <c r="J240" s="89"/>
+      <c r="B240" s="87"/>
+      <c r="C240" s="87"/>
+      <c r="D240" s="87"/>
+      <c r="E240" s="87"/>
+      <c r="F240" s="87"/>
+      <c r="G240" s="87"/>
+      <c r="H240" s="87"/>
+      <c r="I240" s="87"/>
+      <c r="J240" s="87"/>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="48">
@@ -12720,18 +12735,18 @@
       </c>
     </row>
     <row r="256" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="89" t="s">
+      <c r="A256" s="87" t="s">
         <v>813</v>
       </c>
-      <c r="B256" s="89"/>
-      <c r="C256" s="89"/>
-      <c r="D256" s="89"/>
-      <c r="E256" s="89"/>
-      <c r="F256" s="89"/>
-      <c r="G256" s="89"/>
-      <c r="H256" s="89"/>
-      <c r="I256" s="89"/>
-      <c r="J256" s="89"/>
+      <c r="B256" s="87"/>
+      <c r="C256" s="87"/>
+      <c r="D256" s="87"/>
+      <c r="E256" s="87"/>
+      <c r="F256" s="87"/>
+      <c r="G256" s="87"/>
+      <c r="H256" s="87"/>
+      <c r="I256" s="87"/>
+      <c r="J256" s="87"/>
     </row>
     <row r="257" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="48">
@@ -12798,18 +12813,18 @@
       </c>
     </row>
     <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A259" s="89" t="s">
+      <c r="A259" s="87" t="s">
         <v>814</v>
       </c>
-      <c r="B259" s="89"/>
-      <c r="C259" s="89"/>
-      <c r="D259" s="89"/>
-      <c r="E259" s="89"/>
-      <c r="F259" s="89"/>
-      <c r="G259" s="89"/>
-      <c r="H259" s="89"/>
-      <c r="I259" s="89"/>
-      <c r="J259" s="89"/>
+      <c r="B259" s="87"/>
+      <c r="C259" s="87"/>
+      <c r="D259" s="87"/>
+      <c r="E259" s="87"/>
+      <c r="F259" s="87"/>
+      <c r="G259" s="87"/>
+      <c r="H259" s="87"/>
+      <c r="I259" s="87"/>
+      <c r="J259" s="87"/>
     </row>
     <row r="260" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="48">
@@ -12972,18 +12987,18 @@
       </c>
     </row>
     <row r="265" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A265" s="89" t="s">
+      <c r="A265" s="87" t="s">
         <v>890</v>
       </c>
-      <c r="B265" s="89"/>
-      <c r="C265" s="89"/>
-      <c r="D265" s="89"/>
-      <c r="E265" s="89"/>
-      <c r="F265" s="89"/>
-      <c r="G265" s="89"/>
-      <c r="H265" s="89"/>
-      <c r="I265" s="89"/>
-      <c r="J265" s="89"/>
+      <c r="B265" s="87"/>
+      <c r="C265" s="87"/>
+      <c r="D265" s="87"/>
+      <c r="E265" s="87"/>
+      <c r="F265" s="87"/>
+      <c r="G265" s="87"/>
+      <c r="H265" s="87"/>
+      <c r="I265" s="87"/>
+      <c r="J265" s="87"/>
     </row>
     <row r="266" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="48">
@@ -13018,18 +13033,18 @@
       </c>
     </row>
     <row r="267" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="89" t="s">
+      <c r="A267" s="87" t="s">
         <v>917</v>
       </c>
-      <c r="B267" s="89"/>
-      <c r="C267" s="89"/>
-      <c r="D267" s="89"/>
-      <c r="E267" s="89"/>
-      <c r="F267" s="89"/>
-      <c r="G267" s="89"/>
-      <c r="H267" s="89"/>
-      <c r="I267" s="89"/>
-      <c r="J267" s="89"/>
+      <c r="B267" s="87"/>
+      <c r="C267" s="87"/>
+      <c r="D267" s="87"/>
+      <c r="E267" s="87"/>
+      <c r="F267" s="87"/>
+      <c r="G267" s="87"/>
+      <c r="H267" s="87"/>
+      <c r="I267" s="87"/>
+      <c r="J267" s="87"/>
     </row>
     <row r="268" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="48">
@@ -13095,11 +13110,54 @@
         <v>13</v>
       </c>
     </row>
+    <row r="270" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A270" s="87" t="s">
+        <v>931</v>
+      </c>
+      <c r="B270" s="87"/>
+      <c r="C270" s="87"/>
+      <c r="D270" s="87"/>
+      <c r="E270" s="87"/>
+      <c r="F270" s="87"/>
+      <c r="G270" s="87"/>
+      <c r="H270" s="87"/>
+      <c r="I270" s="87"/>
+      <c r="J270" s="87"/>
+    </row>
+    <row r="271" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A271" s="48">
+        <v>1</v>
+      </c>
+      <c r="B271" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C271" s="79" t="s">
+        <v>932</v>
+      </c>
+      <c r="D271" s="78" t="s">
+        <v>933</v>
+      </c>
+      <c r="E271" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F271" s="70" t="s">
+        <v>934</v>
+      </c>
+      <c r="G271" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H271" s="48" t="s">
+        <v>935</v>
+      </c>
+      <c r="I271" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J271" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A267:J267"/>
-    <mergeCell ref="A265:J265"/>
-    <mergeCell ref="A220:J220"/>
+  <mergeCells count="27">
     <mergeCell ref="A205:J205"/>
     <mergeCell ref="A226:J226"/>
     <mergeCell ref="A259:J259"/>
@@ -13111,6 +13169,7 @@
     <mergeCell ref="A55:J55"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A270:J270"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A123:J123"/>
@@ -13123,6 +13182,9 @@
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A267:J267"/>
+    <mergeCell ref="A265:J265"/>
+    <mergeCell ref="A220:J220"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13220,7 +13282,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AF251"/>
+  <dimension ref="A1:AF252"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -34740,6 +34802,98 @@
         <v>22</v>
       </c>
       <c r="AD251" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="252" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>934</v>
+      </c>
+      <c r="B252" t="s">
+        <v>22</v>
+      </c>
+      <c r="C252" t="s">
+        <v>22</v>
+      </c>
+      <c r="D252" t="s">
+        <v>22</v>
+      </c>
+      <c r="E252" t="s">
+        <v>22</v>
+      </c>
+      <c r="F252" t="s">
+        <v>22</v>
+      </c>
+      <c r="G252" t="s">
+        <v>22</v>
+      </c>
+      <c r="H252" t="s">
+        <v>22</v>
+      </c>
+      <c r="I252" t="s">
+        <v>22</v>
+      </c>
+      <c r="J252" t="s">
+        <v>22</v>
+      </c>
+      <c r="K252" t="s">
+        <v>22</v>
+      </c>
+      <c r="L252" t="s">
+        <v>22</v>
+      </c>
+      <c r="M252" t="s">
+        <v>22</v>
+      </c>
+      <c r="N252" t="s">
+        <v>22</v>
+      </c>
+      <c r="O252" t="s">
+        <v>22</v>
+      </c>
+      <c r="P252" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>22</v>
+      </c>
+      <c r="R252" t="s">
+        <v>22</v>
+      </c>
+      <c r="S252" t="s">
+        <v>903</v>
+      </c>
+      <c r="T252" t="s">
+        <v>22</v>
+      </c>
+      <c r="U252" t="s">
+        <v>22</v>
+      </c>
+      <c r="V252" t="s">
+        <v>22</v>
+      </c>
+      <c r="W252" t="s">
+        <v>22</v>
+      </c>
+      <c r="X252" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y252" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z252" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA252" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB252" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC252" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD252" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever1235\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA13683-36D3-4F57-9A59-9403343E4DEF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043FE4DB-DE73-4944-89A4-967908FC4E4F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8967" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9007" uniqueCount="941">
   <si>
     <t>S.No</t>
   </si>
@@ -2834,6 +2834,21 @@
   </si>
   <si>
     <t>Stock</t>
+  </si>
+  <si>
+    <t>My Review</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Review_01</t>
+  </si>
+  <si>
+    <t>Verify user able to  give review in user app.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Review_01</t>
+  </si>
+  <si>
+    <t>Review</t>
   </si>
 </sst>
 </file>
@@ -3493,6 +3508,24 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3519,24 +3552,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4340,7 +4355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z271"/>
+  <dimension ref="A1:Z273"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -5091,18 +5106,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="97" t="s">
+      <c r="A24" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="99"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -5489,18 +5504,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="100" t="s">
+      <c r="A37" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="101"/>
-      <c r="H37" s="101"/>
-      <c r="I37" s="101"/>
-      <c r="J37" s="102"/>
+      <c r="B37" s="92"/>
+      <c r="C37" s="92"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="93"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -6047,18 +6062,18 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="100" t="s">
+      <c r="A55" s="91" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="101"/>
-      <c r="C55" s="101"/>
-      <c r="D55" s="101"/>
-      <c r="E55" s="101"/>
-      <c r="F55" s="101"/>
-      <c r="G55" s="101"/>
-      <c r="H55" s="101"/>
-      <c r="I55" s="101"/>
-      <c r="J55" s="102"/>
+      <c r="B55" s="92"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="92"/>
+      <c r="F55" s="92"/>
+      <c r="G55" s="92"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="92"/>
+      <c r="J55" s="93"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
@@ -6381,18 +6396,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="100" t="s">
+      <c r="A66" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="101"/>
-      <c r="C66" s="101"/>
-      <c r="D66" s="101"/>
-      <c r="E66" s="101"/>
-      <c r="F66" s="101"/>
-      <c r="G66" s="101"/>
-      <c r="H66" s="101"/>
-      <c r="I66" s="101"/>
-      <c r="J66" s="102"/>
+      <c r="B66" s="92"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="92"/>
+      <c r="E66" s="92"/>
+      <c r="F66" s="92"/>
+      <c r="G66" s="92"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="92"/>
+      <c r="J66" s="93"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
@@ -6747,18 +6762,18 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="100" t="s">
+      <c r="A78" s="91" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="101"/>
-      <c r="C78" s="101"/>
-      <c r="D78" s="101"/>
-      <c r="E78" s="101"/>
-      <c r="F78" s="101"/>
-      <c r="G78" s="101"/>
-      <c r="H78" s="101"/>
-      <c r="I78" s="101"/>
-      <c r="J78" s="102"/>
+      <c r="B78" s="92"/>
+      <c r="C78" s="92"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="92"/>
+      <c r="F78" s="92"/>
+      <c r="G78" s="92"/>
+      <c r="H78" s="92"/>
+      <c r="I78" s="92"/>
+      <c r="J78" s="93"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
@@ -7625,18 +7640,18 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="88" t="s">
+      <c r="A106" s="94" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="88"/>
-      <c r="C106" s="88"/>
-      <c r="D106" s="88"/>
-      <c r="E106" s="88"/>
-      <c r="F106" s="88"/>
-      <c r="G106" s="88"/>
-      <c r="H106" s="88"/>
-      <c r="I106" s="88"/>
-      <c r="J106" s="88"/>
+      <c r="B106" s="94"/>
+      <c r="C106" s="94"/>
+      <c r="D106" s="94"/>
+      <c r="E106" s="94"/>
+      <c r="F106" s="94"/>
+      <c r="G106" s="94"/>
+      <c r="H106" s="94"/>
+      <c r="I106" s="94"/>
+      <c r="J106" s="94"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -8129,18 +8144,18 @@
       <c r="X120" s="58"/>
     </row>
     <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="89" t="s">
+      <c r="A121" s="95" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="89"/>
-      <c r="C121" s="89"/>
-      <c r="D121" s="89"/>
-      <c r="E121" s="89"/>
-      <c r="F121" s="89"/>
-      <c r="G121" s="89"/>
-      <c r="H121" s="89"/>
-      <c r="I121" s="89"/>
-      <c r="J121" s="89"/>
+      <c r="B121" s="95"/>
+      <c r="C121" s="95"/>
+      <c r="D121" s="95"/>
+      <c r="E121" s="95"/>
+      <c r="F121" s="95"/>
+      <c r="G121" s="95"/>
+      <c r="H121" s="95"/>
+      <c r="I121" s="95"/>
+      <c r="J121" s="95"/>
       <c r="K121" s="57"/>
       <c r="L121" s="58"/>
       <c r="M121" s="58"/>
@@ -8203,18 +8218,18 @@
       <c r="X122" s="58"/>
     </row>
     <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="89" t="s">
+      <c r="A123" s="95" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="89"/>
-      <c r="C123" s="89"/>
-      <c r="D123" s="89"/>
-      <c r="E123" s="89"/>
-      <c r="F123" s="89"/>
-      <c r="G123" s="89"/>
-      <c r="H123" s="89"/>
-      <c r="I123" s="89"/>
-      <c r="J123" s="89"/>
+      <c r="B123" s="95"/>
+      <c r="C123" s="95"/>
+      <c r="D123" s="95"/>
+      <c r="E123" s="95"/>
+      <c r="F123" s="95"/>
+      <c r="G123" s="95"/>
+      <c r="H123" s="95"/>
+      <c r="I123" s="95"/>
+      <c r="J123" s="95"/>
       <c r="K123" s="57"/>
       <c r="L123" s="58"/>
       <c r="M123" s="58"/>
@@ -8277,18 +8292,18 @@
       <c r="X124" s="58"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="89" t="s">
+      <c r="A125" s="95" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="89"/>
-      <c r="C125" s="89"/>
-      <c r="D125" s="89"/>
-      <c r="E125" s="89"/>
-      <c r="F125" s="89"/>
-      <c r="G125" s="89"/>
-      <c r="H125" s="89"/>
-      <c r="I125" s="89"/>
-      <c r="J125" s="89"/>
+      <c r="B125" s="95"/>
+      <c r="C125" s="95"/>
+      <c r="D125" s="95"/>
+      <c r="E125" s="95"/>
+      <c r="F125" s="95"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="95"/>
+      <c r="I125" s="95"/>
+      <c r="J125" s="95"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -8613,18 +8628,18 @@
       <c r="X132" s="58"/>
     </row>
     <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="89" t="s">
+      <c r="A133" s="95" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="89"/>
-      <c r="C133" s="89"/>
-      <c r="D133" s="90"/>
-      <c r="E133" s="90"/>
-      <c r="F133" s="90"/>
-      <c r="G133" s="90"/>
-      <c r="H133" s="90"/>
-      <c r="I133" s="90"/>
-      <c r="J133" s="90"/>
+      <c r="B133" s="95"/>
+      <c r="C133" s="95"/>
+      <c r="D133" s="96"/>
+      <c r="E133" s="96"/>
+      <c r="F133" s="96"/>
+      <c r="G133" s="96"/>
+      <c r="H133" s="96"/>
+      <c r="I133" s="96"/>
+      <c r="J133" s="96"/>
       <c r="K133" s="58"/>
       <c r="L133" s="58"/>
       <c r="M133" s="58"/>
@@ -9119,18 +9134,18 @@
       <c r="X144" s="58"/>
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="94" t="s">
+      <c r="A145" s="100" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="95"/>
-      <c r="C145" s="95"/>
-      <c r="D145" s="95"/>
-      <c r="E145" s="95"/>
-      <c r="F145" s="95"/>
-      <c r="G145" s="95"/>
-      <c r="H145" s="95"/>
-      <c r="I145" s="95"/>
-      <c r="J145" s="96"/>
+      <c r="B145" s="101"/>
+      <c r="C145" s="101"/>
+      <c r="D145" s="101"/>
+      <c r="E145" s="101"/>
+      <c r="F145" s="101"/>
+      <c r="G145" s="101"/>
+      <c r="H145" s="101"/>
+      <c r="I145" s="101"/>
+      <c r="J145" s="102"/>
       <c r="K145" s="58"/>
       <c r="L145" s="58"/>
       <c r="M145" s="58"/>
@@ -9577,18 +9592,18 @@
       <c r="Z155" s="58"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="89" t="s">
+      <c r="A156" s="95" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="89"/>
-      <c r="C156" s="89"/>
-      <c r="D156" s="89"/>
-      <c r="E156" s="89"/>
-      <c r="F156" s="89"/>
-      <c r="G156" s="89"/>
-      <c r="H156" s="89"/>
-      <c r="I156" s="89"/>
-      <c r="J156" s="89"/>
+      <c r="B156" s="95"/>
+      <c r="C156" s="95"/>
+      <c r="D156" s="95"/>
+      <c r="E156" s="95"/>
+      <c r="F156" s="95"/>
+      <c r="G156" s="95"/>
+      <c r="H156" s="95"/>
+      <c r="I156" s="95"/>
+      <c r="J156" s="95"/>
       <c r="K156" s="58"/>
       <c r="L156" s="58"/>
       <c r="M156" s="58"/>
@@ -9655,18 +9670,18 @@
       <c r="Z157" s="58"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="89" t="s">
+      <c r="A158" s="95" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="89"/>
-      <c r="C158" s="89"/>
-      <c r="D158" s="89"/>
-      <c r="E158" s="89"/>
-      <c r="F158" s="89"/>
-      <c r="G158" s="89"/>
-      <c r="H158" s="89"/>
-      <c r="I158" s="89"/>
-      <c r="J158" s="89"/>
+      <c r="B158" s="95"/>
+      <c r="C158" s="95"/>
+      <c r="D158" s="95"/>
+      <c r="E158" s="95"/>
+      <c r="F158" s="95"/>
+      <c r="G158" s="95"/>
+      <c r="H158" s="95"/>
+      <c r="I158" s="95"/>
+      <c r="J158" s="95"/>
       <c r="K158" s="58"/>
       <c r="L158" s="58"/>
       <c r="M158" s="58"/>
@@ -10501,18 +10516,18 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="89" t="s">
+      <c r="A180" s="95" t="s">
         <v>707</v>
       </c>
-      <c r="B180" s="89"/>
-      <c r="C180" s="89"/>
+      <c r="B180" s="95"/>
+      <c r="C180" s="95"/>
       <c r="D180" s="87"/>
-      <c r="E180" s="89"/>
-      <c r="F180" s="89"/>
-      <c r="G180" s="89"/>
-      <c r="H180" s="89"/>
-      <c r="I180" s="89"/>
-      <c r="J180" s="89"/>
+      <c r="E180" s="95"/>
+      <c r="F180" s="95"/>
+      <c r="G180" s="95"/>
+      <c r="H180" s="95"/>
+      <c r="I180" s="95"/>
+      <c r="J180" s="95"/>
     </row>
     <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="68">
@@ -10803,18 +10818,18 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="91" t="s">
+      <c r="A190" s="97" t="s">
         <v>609</v>
       </c>
-      <c r="B190" s="92"/>
-      <c r="C190" s="92"/>
-      <c r="D190" s="92"/>
-      <c r="E190" s="92"/>
-      <c r="F190" s="92"/>
-      <c r="G190" s="92"/>
-      <c r="H190" s="92"/>
-      <c r="I190" s="92"/>
-      <c r="J190" s="93"/>
+      <c r="B190" s="98"/>
+      <c r="C190" s="98"/>
+      <c r="D190" s="98"/>
+      <c r="E190" s="98"/>
+      <c r="F190" s="98"/>
+      <c r="G190" s="98"/>
+      <c r="H190" s="98"/>
+      <c r="I190" s="98"/>
+      <c r="J190" s="99"/>
     </row>
     <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="68">
@@ -13156,19 +13171,55 @@
         <v>13</v>
       </c>
     </row>
+    <row r="272" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A272" s="87" t="s">
+        <v>936</v>
+      </c>
+      <c r="B272" s="87"/>
+      <c r="C272" s="87"/>
+      <c r="D272" s="87"/>
+      <c r="E272" s="87"/>
+      <c r="F272" s="87"/>
+      <c r="G272" s="87"/>
+      <c r="H272" s="87"/>
+      <c r="I272" s="87"/>
+      <c r="J272" s="87"/>
+    </row>
+    <row r="273" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="48">
+        <v>1</v>
+      </c>
+      <c r="B273" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C273" s="79" t="s">
+        <v>937</v>
+      </c>
+      <c r="D273" s="78" t="s">
+        <v>938</v>
+      </c>
+      <c r="E273" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F273" s="70" t="s">
+        <v>939</v>
+      </c>
+      <c r="G273" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H273" s="48" t="s">
+        <v>940</v>
+      </c>
+      <c r="I273" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J273" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="A259:J259"/>
-    <mergeCell ref="A256:J256"/>
-    <mergeCell ref="A240:J240"/>
-    <mergeCell ref="A238:J238"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
+  <mergeCells count="28">
+    <mergeCell ref="A272:J272"/>
     <mergeCell ref="A270:J270"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
@@ -13185,6 +13236,17 @@
     <mergeCell ref="A267:J267"/>
     <mergeCell ref="A265:J265"/>
     <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A259:J259"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A240:J240"/>
+    <mergeCell ref="A238:J238"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13282,7 +13344,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AF252"/>
+  <dimension ref="A1:AF253"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -34894,6 +34956,98 @@
         <v>22</v>
       </c>
       <c r="AD252" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="253" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>939</v>
+      </c>
+      <c r="B253" t="s">
+        <v>22</v>
+      </c>
+      <c r="C253" t="s">
+        <v>22</v>
+      </c>
+      <c r="D253" t="s">
+        <v>22</v>
+      </c>
+      <c r="E253" t="s">
+        <v>22</v>
+      </c>
+      <c r="F253" t="s">
+        <v>22</v>
+      </c>
+      <c r="G253" t="s">
+        <v>22</v>
+      </c>
+      <c r="H253" t="s">
+        <v>22</v>
+      </c>
+      <c r="I253" t="s">
+        <v>22</v>
+      </c>
+      <c r="J253" t="s">
+        <v>22</v>
+      </c>
+      <c r="K253" t="s">
+        <v>22</v>
+      </c>
+      <c r="L253" t="s">
+        <v>22</v>
+      </c>
+      <c r="M253" t="s">
+        <v>22</v>
+      </c>
+      <c r="N253" t="s">
+        <v>22</v>
+      </c>
+      <c r="O253" t="s">
+        <v>22</v>
+      </c>
+      <c r="P253" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>22</v>
+      </c>
+      <c r="R253" t="s">
+        <v>22</v>
+      </c>
+      <c r="S253" t="s">
+        <v>22</v>
+      </c>
+      <c r="T253" t="s">
+        <v>22</v>
+      </c>
+      <c r="U253" t="s">
+        <v>22</v>
+      </c>
+      <c r="V253" t="s">
+        <v>22</v>
+      </c>
+      <c r="W253" t="s">
+        <v>22</v>
+      </c>
+      <c r="X253" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y253" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z253" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA253" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB253" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC253" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD253" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever1235\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever6\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043FE4DB-DE73-4944-89A4-967908FC4E4F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152C37B5-C93B-4CE3-B910-059CC034F58E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9007" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9085" uniqueCount="947">
   <si>
     <t>S.No</t>
   </si>
@@ -2849,6 +2849,24 @@
   </si>
   <si>
     <t>Review</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Review_02</t>
+  </si>
+  <si>
+    <t>Verify user able to  give My Order review in user app.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Review_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Stock_02</t>
+  </si>
+  <si>
+    <t>Verify Almost Sold Out message on Product Details Page.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Stock_02</t>
   </si>
 </sst>
 </file>
@@ -3508,24 +3526,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3552,6 +3552,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4355,7 +4373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z273"/>
+  <dimension ref="A1:Z275"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -5106,18 +5124,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="97" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="99"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -5504,18 +5522,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="91" t="s">
+      <c r="A37" s="100" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="92"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="93"/>
+      <c r="B37" s="101"/>
+      <c r="C37" s="101"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="101"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="102"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -6062,18 +6080,18 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="91" t="s">
+      <c r="A55" s="100" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="92"/>
-      <c r="C55" s="92"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="92"/>
-      <c r="F55" s="92"/>
-      <c r="G55" s="92"/>
-      <c r="H55" s="92"/>
-      <c r="I55" s="92"/>
-      <c r="J55" s="93"/>
+      <c r="B55" s="101"/>
+      <c r="C55" s="101"/>
+      <c r="D55" s="101"/>
+      <c r="E55" s="101"/>
+      <c r="F55" s="101"/>
+      <c r="G55" s="101"/>
+      <c r="H55" s="101"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="102"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
@@ -6396,18 +6414,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="91" t="s">
+      <c r="A66" s="100" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="92"/>
-      <c r="C66" s="92"/>
-      <c r="D66" s="92"/>
-      <c r="E66" s="92"/>
-      <c r="F66" s="92"/>
-      <c r="G66" s="92"/>
-      <c r="H66" s="92"/>
-      <c r="I66" s="92"/>
-      <c r="J66" s="93"/>
+      <c r="B66" s="101"/>
+      <c r="C66" s="101"/>
+      <c r="D66" s="101"/>
+      <c r="E66" s="101"/>
+      <c r="F66" s="101"/>
+      <c r="G66" s="101"/>
+      <c r="H66" s="101"/>
+      <c r="I66" s="101"/>
+      <c r="J66" s="102"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
@@ -6762,18 +6780,18 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="91" t="s">
+      <c r="A78" s="100" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="92"/>
-      <c r="C78" s="92"/>
-      <c r="D78" s="92"/>
-      <c r="E78" s="92"/>
-      <c r="F78" s="92"/>
-      <c r="G78" s="92"/>
-      <c r="H78" s="92"/>
-      <c r="I78" s="92"/>
-      <c r="J78" s="93"/>
+      <c r="B78" s="101"/>
+      <c r="C78" s="101"/>
+      <c r="D78" s="101"/>
+      <c r="E78" s="101"/>
+      <c r="F78" s="101"/>
+      <c r="G78" s="101"/>
+      <c r="H78" s="101"/>
+      <c r="I78" s="101"/>
+      <c r="J78" s="102"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
@@ -7640,18 +7658,18 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="94" t="s">
+      <c r="A106" s="88" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="94"/>
-      <c r="C106" s="94"/>
-      <c r="D106" s="94"/>
-      <c r="E106" s="94"/>
-      <c r="F106" s="94"/>
-      <c r="G106" s="94"/>
-      <c r="H106" s="94"/>
-      <c r="I106" s="94"/>
-      <c r="J106" s="94"/>
+      <c r="B106" s="88"/>
+      <c r="C106" s="88"/>
+      <c r="D106" s="88"/>
+      <c r="E106" s="88"/>
+      <c r="F106" s="88"/>
+      <c r="G106" s="88"/>
+      <c r="H106" s="88"/>
+      <c r="I106" s="88"/>
+      <c r="J106" s="88"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -8144,18 +8162,18 @@
       <c r="X120" s="58"/>
     </row>
     <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="95" t="s">
+      <c r="A121" s="89" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="95"/>
-      <c r="C121" s="95"/>
-      <c r="D121" s="95"/>
-      <c r="E121" s="95"/>
-      <c r="F121" s="95"/>
-      <c r="G121" s="95"/>
-      <c r="H121" s="95"/>
-      <c r="I121" s="95"/>
-      <c r="J121" s="95"/>
+      <c r="B121" s="89"/>
+      <c r="C121" s="89"/>
+      <c r="D121" s="89"/>
+      <c r="E121" s="89"/>
+      <c r="F121" s="89"/>
+      <c r="G121" s="89"/>
+      <c r="H121" s="89"/>
+      <c r="I121" s="89"/>
+      <c r="J121" s="89"/>
       <c r="K121" s="57"/>
       <c r="L121" s="58"/>
       <c r="M121" s="58"/>
@@ -8218,18 +8236,18 @@
       <c r="X122" s="58"/>
     </row>
     <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="95" t="s">
+      <c r="A123" s="89" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="95"/>
-      <c r="C123" s="95"/>
-      <c r="D123" s="95"/>
-      <c r="E123" s="95"/>
-      <c r="F123" s="95"/>
-      <c r="G123" s="95"/>
-      <c r="H123" s="95"/>
-      <c r="I123" s="95"/>
-      <c r="J123" s="95"/>
+      <c r="B123" s="89"/>
+      <c r="C123" s="89"/>
+      <c r="D123" s="89"/>
+      <c r="E123" s="89"/>
+      <c r="F123" s="89"/>
+      <c r="G123" s="89"/>
+      <c r="H123" s="89"/>
+      <c r="I123" s="89"/>
+      <c r="J123" s="89"/>
       <c r="K123" s="57"/>
       <c r="L123" s="58"/>
       <c r="M123" s="58"/>
@@ -8292,18 +8310,18 @@
       <c r="X124" s="58"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="95" t="s">
+      <c r="A125" s="89" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="95"/>
-      <c r="C125" s="95"/>
-      <c r="D125" s="95"/>
-      <c r="E125" s="95"/>
-      <c r="F125" s="95"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="95"/>
-      <c r="I125" s="95"/>
-      <c r="J125" s="95"/>
+      <c r="B125" s="89"/>
+      <c r="C125" s="89"/>
+      <c r="D125" s="89"/>
+      <c r="E125" s="89"/>
+      <c r="F125" s="89"/>
+      <c r="G125" s="89"/>
+      <c r="H125" s="89"/>
+      <c r="I125" s="89"/>
+      <c r="J125" s="89"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -8628,18 +8646,18 @@
       <c r="X132" s="58"/>
     </row>
     <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="95" t="s">
+      <c r="A133" s="89" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="95"/>
-      <c r="C133" s="95"/>
-      <c r="D133" s="96"/>
-      <c r="E133" s="96"/>
-      <c r="F133" s="96"/>
-      <c r="G133" s="96"/>
-      <c r="H133" s="96"/>
-      <c r="I133" s="96"/>
-      <c r="J133" s="96"/>
+      <c r="B133" s="89"/>
+      <c r="C133" s="89"/>
+      <c r="D133" s="90"/>
+      <c r="E133" s="90"/>
+      <c r="F133" s="90"/>
+      <c r="G133" s="90"/>
+      <c r="H133" s="90"/>
+      <c r="I133" s="90"/>
+      <c r="J133" s="90"/>
       <c r="K133" s="58"/>
       <c r="L133" s="58"/>
       <c r="M133" s="58"/>
@@ -9134,18 +9152,18 @@
       <c r="X144" s="58"/>
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="100" t="s">
+      <c r="A145" s="94" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="101"/>
-      <c r="C145" s="101"/>
-      <c r="D145" s="101"/>
-      <c r="E145" s="101"/>
-      <c r="F145" s="101"/>
-      <c r="G145" s="101"/>
-      <c r="H145" s="101"/>
-      <c r="I145" s="101"/>
-      <c r="J145" s="102"/>
+      <c r="B145" s="95"/>
+      <c r="C145" s="95"/>
+      <c r="D145" s="95"/>
+      <c r="E145" s="95"/>
+      <c r="F145" s="95"/>
+      <c r="G145" s="95"/>
+      <c r="H145" s="95"/>
+      <c r="I145" s="95"/>
+      <c r="J145" s="96"/>
       <c r="K145" s="58"/>
       <c r="L145" s="58"/>
       <c r="M145" s="58"/>
@@ -9592,18 +9610,18 @@
       <c r="Z155" s="58"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="95" t="s">
+      <c r="A156" s="89" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="95"/>
-      <c r="C156" s="95"/>
-      <c r="D156" s="95"/>
-      <c r="E156" s="95"/>
-      <c r="F156" s="95"/>
-      <c r="G156" s="95"/>
-      <c r="H156" s="95"/>
-      <c r="I156" s="95"/>
-      <c r="J156" s="95"/>
+      <c r="B156" s="89"/>
+      <c r="C156" s="89"/>
+      <c r="D156" s="89"/>
+      <c r="E156" s="89"/>
+      <c r="F156" s="89"/>
+      <c r="G156" s="89"/>
+      <c r="H156" s="89"/>
+      <c r="I156" s="89"/>
+      <c r="J156" s="89"/>
       <c r="K156" s="58"/>
       <c r="L156" s="58"/>
       <c r="M156" s="58"/>
@@ -9670,18 +9688,18 @@
       <c r="Z157" s="58"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="95" t="s">
+      <c r="A158" s="89" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="95"/>
-      <c r="C158" s="95"/>
-      <c r="D158" s="95"/>
-      <c r="E158" s="95"/>
-      <c r="F158" s="95"/>
-      <c r="G158" s="95"/>
-      <c r="H158" s="95"/>
-      <c r="I158" s="95"/>
-      <c r="J158" s="95"/>
+      <c r="B158" s="89"/>
+      <c r="C158" s="89"/>
+      <c r="D158" s="89"/>
+      <c r="E158" s="89"/>
+      <c r="F158" s="89"/>
+      <c r="G158" s="89"/>
+      <c r="H158" s="89"/>
+      <c r="I158" s="89"/>
+      <c r="J158" s="89"/>
       <c r="K158" s="58"/>
       <c r="L158" s="58"/>
       <c r="M158" s="58"/>
@@ -10516,18 +10534,18 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="95" t="s">
+      <c r="A180" s="89" t="s">
         <v>707</v>
       </c>
-      <c r="B180" s="95"/>
-      <c r="C180" s="95"/>
+      <c r="B180" s="89"/>
+      <c r="C180" s="89"/>
       <c r="D180" s="87"/>
-      <c r="E180" s="95"/>
-      <c r="F180" s="95"/>
-      <c r="G180" s="95"/>
-      <c r="H180" s="95"/>
-      <c r="I180" s="95"/>
-      <c r="J180" s="95"/>
+      <c r="E180" s="89"/>
+      <c r="F180" s="89"/>
+      <c r="G180" s="89"/>
+      <c r="H180" s="89"/>
+      <c r="I180" s="89"/>
+      <c r="J180" s="89"/>
     </row>
     <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="68">
@@ -10818,18 +10836,18 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="97" t="s">
+      <c r="A190" s="91" t="s">
         <v>609</v>
       </c>
-      <c r="B190" s="98"/>
-      <c r="C190" s="98"/>
-      <c r="D190" s="98"/>
-      <c r="E190" s="98"/>
-      <c r="F190" s="98"/>
-      <c r="G190" s="98"/>
-      <c r="H190" s="98"/>
-      <c r="I190" s="98"/>
-      <c r="J190" s="99"/>
+      <c r="B190" s="92"/>
+      <c r="C190" s="92"/>
+      <c r="D190" s="92"/>
+      <c r="E190" s="92"/>
+      <c r="F190" s="92"/>
+      <c r="G190" s="92"/>
+      <c r="H190" s="92"/>
+      <c r="I190" s="92"/>
+      <c r="J190" s="93"/>
     </row>
     <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="68">
@@ -13172,54 +13190,130 @@
       </c>
     </row>
     <row r="272" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="87" t="s">
+      <c r="A272" s="48">
+        <v>2</v>
+      </c>
+      <c r="B272" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C272" s="79" t="s">
+        <v>944</v>
+      </c>
+      <c r="D272" s="78" t="s">
+        <v>945</v>
+      </c>
+      <c r="E272" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F272" s="70" t="s">
+        <v>946</v>
+      </c>
+      <c r="G272" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H272" s="48" t="s">
+        <v>935</v>
+      </c>
+      <c r="I272" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J272" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="87" t="s">
         <v>936</v>
       </c>
-      <c r="B272" s="87"/>
-      <c r="C272" s="87"/>
-      <c r="D272" s="87"/>
-      <c r="E272" s="87"/>
-      <c r="F272" s="87"/>
-      <c r="G272" s="87"/>
-      <c r="H272" s="87"/>
-      <c r="I272" s="87"/>
-      <c r="J272" s="87"/>
-    </row>
-    <row r="273" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="48">
+      <c r="B273" s="87"/>
+      <c r="C273" s="87"/>
+      <c r="D273" s="87"/>
+      <c r="E273" s="87"/>
+      <c r="F273" s="87"/>
+      <c r="G273" s="87"/>
+      <c r="H273" s="87"/>
+      <c r="I273" s="87"/>
+      <c r="J273" s="87"/>
+    </row>
+    <row r="274" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A274" s="48">
         <v>1</v>
       </c>
-      <c r="B273" s="48" t="s">
+      <c r="B274" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C273" s="79" t="s">
+      <c r="C274" s="79" t="s">
         <v>937</v>
       </c>
-      <c r="D273" s="78" t="s">
+      <c r="D274" s="78" t="s">
         <v>938</v>
       </c>
-      <c r="E273" s="48" t="s">
+      <c r="E274" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="F273" s="70" t="s">
+      <c r="F274" s="70" t="s">
         <v>939</v>
       </c>
-      <c r="G273" s="48" t="s">
+      <c r="G274" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="H273" s="48" t="s">
+      <c r="H274" s="48" t="s">
         <v>940</v>
       </c>
-      <c r="I273" s="48" t="s">
+      <c r="I274" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="J273" s="48" t="s">
+      <c r="J274" s="48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A275" s="48">
+        <v>2</v>
+      </c>
+      <c r="B275" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C275" s="79" t="s">
+        <v>941</v>
+      </c>
+      <c r="D275" s="78" t="s">
+        <v>942</v>
+      </c>
+      <c r="E275" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F275" s="70" t="s">
+        <v>943</v>
+      </c>
+      <c r="G275" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H275" s="48" t="s">
+        <v>940</v>
+      </c>
+      <c r="I275" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J275" s="48" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A272:J272"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A259:J259"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A240:J240"/>
+    <mergeCell ref="A238:J238"/>
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A273:J273"/>
     <mergeCell ref="A270:J270"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
@@ -13235,18 +13329,6 @@
     <mergeCell ref="A180:J180"/>
     <mergeCell ref="A267:J267"/>
     <mergeCell ref="A265:J265"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="A259:J259"/>
-    <mergeCell ref="A256:J256"/>
-    <mergeCell ref="A240:J240"/>
-    <mergeCell ref="A238:J238"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13344,7 +13426,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AF253"/>
+  <dimension ref="A1:AF255"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -35048,6 +35130,190 @@
         <v>22</v>
       </c>
       <c r="AD253" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="254" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>943</v>
+      </c>
+      <c r="B254" t="s">
+        <v>22</v>
+      </c>
+      <c r="C254" t="s">
+        <v>22</v>
+      </c>
+      <c r="D254" t="s">
+        <v>22</v>
+      </c>
+      <c r="E254" t="s">
+        <v>22</v>
+      </c>
+      <c r="F254" t="s">
+        <v>22</v>
+      </c>
+      <c r="G254" t="s">
+        <v>22</v>
+      </c>
+      <c r="H254" t="s">
+        <v>22</v>
+      </c>
+      <c r="I254" t="s">
+        <v>22</v>
+      </c>
+      <c r="J254" t="s">
+        <v>22</v>
+      </c>
+      <c r="K254" t="s">
+        <v>22</v>
+      </c>
+      <c r="L254" t="s">
+        <v>22</v>
+      </c>
+      <c r="M254" t="s">
+        <v>22</v>
+      </c>
+      <c r="N254" t="s">
+        <v>22</v>
+      </c>
+      <c r="O254" t="s">
+        <v>22</v>
+      </c>
+      <c r="P254" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>22</v>
+      </c>
+      <c r="R254" t="s">
+        <v>22</v>
+      </c>
+      <c r="S254" t="s">
+        <v>22</v>
+      </c>
+      <c r="T254" t="s">
+        <v>22</v>
+      </c>
+      <c r="U254" t="s">
+        <v>22</v>
+      </c>
+      <c r="V254" t="s">
+        <v>22</v>
+      </c>
+      <c r="W254" t="s">
+        <v>22</v>
+      </c>
+      <c r="X254" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y254" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z254" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA254" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB254" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC254" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD254" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="255" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>946</v>
+      </c>
+      <c r="B255" t="s">
+        <v>22</v>
+      </c>
+      <c r="C255" t="s">
+        <v>22</v>
+      </c>
+      <c r="D255" t="s">
+        <v>22</v>
+      </c>
+      <c r="E255" t="s">
+        <v>22</v>
+      </c>
+      <c r="F255" t="s">
+        <v>22</v>
+      </c>
+      <c r="G255" t="s">
+        <v>22</v>
+      </c>
+      <c r="H255" t="s">
+        <v>22</v>
+      </c>
+      <c r="I255" t="s">
+        <v>22</v>
+      </c>
+      <c r="J255" t="s">
+        <v>22</v>
+      </c>
+      <c r="K255" t="s">
+        <v>22</v>
+      </c>
+      <c r="L255" t="s">
+        <v>22</v>
+      </c>
+      <c r="M255" t="s">
+        <v>22</v>
+      </c>
+      <c r="N255" t="s">
+        <v>22</v>
+      </c>
+      <c r="O255" t="s">
+        <v>22</v>
+      </c>
+      <c r="P255" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>22</v>
+      </c>
+      <c r="R255" t="s">
+        <v>22</v>
+      </c>
+      <c r="S255" t="s">
+        <v>903</v>
+      </c>
+      <c r="T255" t="s">
+        <v>22</v>
+      </c>
+      <c r="U255" t="s">
+        <v>22</v>
+      </c>
+      <c r="V255" t="s">
+        <v>22</v>
+      </c>
+      <c r="W255" t="s">
+        <v>22</v>
+      </c>
+      <c r="X255" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y255" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z255" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA255" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB255" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC255" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD255" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataQAseverNew04052026\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\ZlaataQAsever1\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30559E81-9CB9-4A8B-A1FC-4106879548E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DB4FB4-FF38-4030-B325-8FE1D00C9123}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9210" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9379" uniqueCount="980">
   <si>
     <t>S.No</t>
   </si>
@@ -2924,6 +2924,48 @@
   </si>
   <si>
     <t>https://dev.adm.testingserver8.com/admin/general-setting</t>
+  </si>
+  <si>
+    <t>Flash Notification</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FN_01</t>
+  </si>
+  <si>
+    <t>Verify flash notification validation and adding for Landing Page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FN_01</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FN_02</t>
+  </si>
+  <si>
+    <t>Verify flash notification on Zlaata India or Boss Lady Home Page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FN_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FN_03</t>
+  </si>
+  <si>
+    <t>Verify editing flash notification reflects in UI</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FN_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_FN_04</t>
+  </si>
+  <si>
+    <t>Verify scheduled flash notification with toggle behavior</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_FN_04</t>
   </si>
 </sst>
 </file>
@@ -3562,26 +3604,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3610,7 +3635,24 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4413,21 +4455,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z280"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z285"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" customWidth="1"/>
-    <col min="4" max="4" width="118.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" customWidth="1"/>
+    <col min="4" max="4" width="118.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4459,7 +4501,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="28">
         <v>1</v>
       </c>
@@ -4491,7 +4533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="28">
         <v>2</v>
       </c>
@@ -4523,7 +4565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="28">
         <v>3</v>
       </c>
@@ -4555,7 +4597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="28">
         <v>4</v>
       </c>
@@ -4587,7 +4629,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="28">
         <v>5</v>
       </c>
@@ -4619,7 +4661,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="28">
         <v>6</v>
       </c>
@@ -4651,7 +4693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="28">
         <v>7</v>
       </c>
@@ -4683,7 +4725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="28">
         <v>8</v>
       </c>
@@ -4715,7 +4757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="28">
         <v>9</v>
       </c>
@@ -4747,7 +4789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="28">
         <v>10</v>
       </c>
@@ -4779,7 +4821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="28">
         <v>11</v>
       </c>
@@ -4811,7 +4853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="28">
         <v>12</v>
       </c>
@@ -4843,7 +4885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="28">
         <v>13</v>
       </c>
@@ -4875,7 +4917,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="28">
         <v>14</v>
       </c>
@@ -4907,7 +4949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="28">
         <v>15</v>
       </c>
@@ -4939,7 +4981,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="28">
         <v>16</v>
       </c>
@@ -4971,7 +5013,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="28">
         <v>17</v>
       </c>
@@ -5003,7 +5045,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="28">
         <v>18</v>
       </c>
@@ -5035,7 +5077,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="28">
         <v>19</v>
       </c>
@@ -5067,7 +5109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="28">
         <v>20</v>
       </c>
@@ -5099,7 +5141,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="28">
         <v>21</v>
       </c>
@@ -5131,7 +5173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>22</v>
       </c>
@@ -5163,21 +5205,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="85" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="86"/>
-      <c r="J24" s="87"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="97"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>1</v>
       </c>
@@ -5209,7 +5251,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>2</v>
       </c>
@@ -5241,7 +5283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>3</v>
       </c>
@@ -5273,7 +5315,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>4</v>
       </c>
@@ -5305,7 +5347,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>5</v>
       </c>
@@ -5337,7 +5379,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>6</v>
       </c>
@@ -5369,7 +5411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>7</v>
       </c>
@@ -5401,7 +5443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>8</v>
       </c>
@@ -5433,7 +5475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>9</v>
       </c>
@@ -5465,7 +5507,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>10</v>
       </c>
@@ -5497,7 +5539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>11</v>
       </c>
@@ -5529,7 +5571,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>12</v>
       </c>
@@ -5561,21 +5603,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="88" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="98" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="89"/>
-      <c r="C37" s="89"/>
-      <c r="D37" s="89"/>
-      <c r="E37" s="89"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="89"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="90"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="100"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>1</v>
       </c>
@@ -5607,7 +5649,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -5639,7 +5681,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>3</v>
       </c>
@@ -5671,7 +5713,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>4</v>
       </c>
@@ -5703,7 +5745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>5</v>
       </c>
@@ -5735,7 +5777,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>6</v>
       </c>
@@ -5767,7 +5809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>7</v>
       </c>
@@ -5799,7 +5841,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>8</v>
       </c>
@@ -5831,7 +5873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>9</v>
       </c>
@@ -5863,7 +5905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>10</v>
       </c>
@@ -5895,7 +5937,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>11</v>
       </c>
@@ -5927,7 +5969,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>12</v>
       </c>
@@ -5959,7 +6001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>13</v>
       </c>
@@ -5991,7 +6033,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>14</v>
       </c>
@@ -6023,7 +6065,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>15</v>
       </c>
@@ -6055,7 +6097,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>16</v>
       </c>
@@ -6087,7 +6129,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>16</v>
       </c>
@@ -6119,21 +6161,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="88" t="s">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="98" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="89"/>
-      <c r="C55" s="89"/>
-      <c r="D55" s="89"/>
-      <c r="E55" s="89"/>
-      <c r="F55" s="89"/>
-      <c r="G55" s="89"/>
-      <c r="H55" s="89"/>
-      <c r="I55" s="89"/>
-      <c r="J55" s="90"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="99"/>
+      <c r="C55" s="99"/>
+      <c r="D55" s="99"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="99"/>
+      <c r="G55" s="99"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="99"/>
+      <c r="J55" s="100"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
         <v>1</v>
       </c>
@@ -6165,7 +6207,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="25">
         <v>2</v>
       </c>
@@ -6197,7 +6239,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="25">
         <v>3</v>
       </c>
@@ -6229,7 +6271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="25">
         <v>4</v>
       </c>
@@ -6261,7 +6303,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="25">
         <v>5</v>
       </c>
@@ -6293,7 +6335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="25">
         <v>6</v>
       </c>
@@ -6325,7 +6367,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="25">
         <v>7</v>
       </c>
@@ -6357,7 +6399,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="25">
         <v>8</v>
       </c>
@@ -6389,7 +6431,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="25">
         <v>9</v>
       </c>
@@ -6421,7 +6463,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="25">
         <v>10</v>
       </c>
@@ -6453,21 +6495,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="88" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="98" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="89"/>
-      <c r="C66" s="89"/>
-      <c r="D66" s="89"/>
-      <c r="E66" s="89"/>
-      <c r="F66" s="89"/>
-      <c r="G66" s="89"/>
-      <c r="H66" s="89"/>
-      <c r="I66" s="89"/>
-      <c r="J66" s="90"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="99"/>
+      <c r="C66" s="99"/>
+      <c r="D66" s="99"/>
+      <c r="E66" s="99"/>
+      <c r="F66" s="99"/>
+      <c r="G66" s="99"/>
+      <c r="H66" s="99"/>
+      <c r="I66" s="99"/>
+      <c r="J66" s="100"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
         <v>1</v>
       </c>
@@ -6499,7 +6541,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="25">
         <v>2</v>
       </c>
@@ -6531,7 +6573,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="25">
         <v>3</v>
       </c>
@@ -6563,7 +6605,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="25">
         <v>4</v>
       </c>
@@ -6595,7 +6637,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="25">
         <v>5</v>
       </c>
@@ -6627,7 +6669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="25">
         <v>6</v>
       </c>
@@ -6659,7 +6701,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="25">
         <v>7</v>
       </c>
@@ -6691,7 +6733,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="25">
         <v>8</v>
       </c>
@@ -6723,7 +6765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="25">
         <v>9</v>
       </c>
@@ -6755,7 +6797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="25">
         <v>10</v>
       </c>
@@ -6787,7 +6829,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="25">
         <v>11</v>
       </c>
@@ -6819,21 +6861,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="88" t="s">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="98" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="89"/>
-      <c r="C78" s="89"/>
-      <c r="D78" s="89"/>
-      <c r="E78" s="89"/>
-      <c r="F78" s="89"/>
-      <c r="G78" s="89"/>
-      <c r="H78" s="89"/>
-      <c r="I78" s="89"/>
-      <c r="J78" s="90"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B78" s="99"/>
+      <c r="C78" s="99"/>
+      <c r="D78" s="99"/>
+      <c r="E78" s="99"/>
+      <c r="F78" s="99"/>
+      <c r="G78" s="99"/>
+      <c r="H78" s="99"/>
+      <c r="I78" s="99"/>
+      <c r="J78" s="100"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
         <v>1</v>
       </c>
@@ -6865,7 +6907,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="25">
         <v>2</v>
       </c>
@@ -6897,7 +6939,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="25">
         <v>3</v>
       </c>
@@ -6929,7 +6971,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="25">
         <v>4</v>
       </c>
@@ -6961,7 +7003,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="25">
         <v>5</v>
       </c>
@@ -6993,7 +7035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="25">
         <v>6</v>
       </c>
@@ -7025,7 +7067,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="25">
         <v>7</v>
       </c>
@@ -7057,7 +7099,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="25">
         <v>8</v>
       </c>
@@ -7089,7 +7131,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="25">
         <v>9</v>
       </c>
@@ -7121,7 +7163,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="25">
         <v>10</v>
       </c>
@@ -7153,7 +7195,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="25">
         <v>11</v>
       </c>
@@ -7185,7 +7227,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="25">
         <v>12</v>
       </c>
@@ -7217,7 +7259,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="25">
         <v>13</v>
       </c>
@@ -7249,7 +7291,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="25">
         <v>14</v>
       </c>
@@ -7281,7 +7323,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="25">
         <v>15</v>
       </c>
@@ -7313,7 +7355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="25">
         <v>16</v>
       </c>
@@ -7345,7 +7387,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="25">
         <v>17</v>
       </c>
@@ -7377,7 +7419,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="25">
         <v>18</v>
       </c>
@@ -7409,7 +7451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="25">
         <v>19</v>
       </c>
@@ -7441,7 +7483,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="25">
         <v>20</v>
       </c>
@@ -7473,7 +7515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="25">
         <v>21</v>
       </c>
@@ -7505,7 +7547,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="25">
         <v>22</v>
       </c>
@@ -7537,7 +7579,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="25">
         <v>23</v>
       </c>
@@ -7569,7 +7611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="25">
         <v>24</v>
       </c>
@@ -7601,7 +7643,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="25">
         <v>25</v>
       </c>
@@ -7633,7 +7675,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="25">
         <v>27</v>
       </c>
@@ -7665,7 +7707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="25">
         <v>28</v>
       </c>
@@ -7697,21 +7739,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="91" t="s">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" s="86" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="91"/>
-      <c r="C106" s="91"/>
-      <c r="D106" s="91"/>
-      <c r="E106" s="91"/>
-      <c r="F106" s="91"/>
-      <c r="G106" s="91"/>
-      <c r="H106" s="91"/>
-      <c r="I106" s="91"/>
-      <c r="J106" s="91"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B106" s="86"/>
+      <c r="C106" s="86"/>
+      <c r="D106" s="86"/>
+      <c r="E106" s="86"/>
+      <c r="F106" s="86"/>
+      <c r="G106" s="86"/>
+      <c r="H106" s="86"/>
+      <c r="I106" s="86"/>
+      <c r="J106" s="86"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
         <v>1</v>
       </c>
@@ -7743,7 +7785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="25">
         <v>2</v>
       </c>
@@ -7775,7 +7817,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="25">
         <v>3</v>
       </c>
@@ -7807,7 +7849,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="25">
         <v>4</v>
       </c>
@@ -7839,7 +7881,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="25">
         <v>5</v>
       </c>
@@ -7871,7 +7913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="25">
         <v>6</v>
       </c>
@@ -7903,7 +7945,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="25">
         <v>7</v>
       </c>
@@ -7935,7 +7977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="25">
         <v>8</v>
       </c>
@@ -7967,7 +8009,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="25">
         <v>9</v>
       </c>
@@ -7999,7 +8041,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="25">
         <v>10</v>
       </c>
@@ -8031,7 +8073,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="25">
         <v>11</v>
       </c>
@@ -8063,7 +8105,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="25">
         <v>12</v>
       </c>
@@ -8109,7 +8151,7 @@
       <c r="W118" s="52"/>
       <c r="X118" s="52"/>
     </row>
-    <row r="119" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="25">
         <v>13</v>
       </c>
@@ -8155,7 +8197,7 @@
       <c r="W119" s="52"/>
       <c r="X119" s="52"/>
     </row>
-    <row r="120" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="25">
         <v>14</v>
       </c>
@@ -8201,19 +8243,19 @@
       <c r="W120" s="52"/>
       <c r="X120" s="52"/>
     </row>
-    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="92" t="s">
+    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="87" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="92"/>
-      <c r="C121" s="92"/>
-      <c r="D121" s="92"/>
-      <c r="E121" s="92"/>
-      <c r="F121" s="92"/>
-      <c r="G121" s="92"/>
-      <c r="H121" s="92"/>
-      <c r="I121" s="92"/>
-      <c r="J121" s="92"/>
+      <c r="B121" s="87"/>
+      <c r="C121" s="87"/>
+      <c r="D121" s="87"/>
+      <c r="E121" s="87"/>
+      <c r="F121" s="87"/>
+      <c r="G121" s="87"/>
+      <c r="H121" s="87"/>
+      <c r="I121" s="87"/>
+      <c r="J121" s="87"/>
       <c r="K121" s="51"/>
       <c r="L121" s="52"/>
       <c r="M121" s="52"/>
@@ -8229,7 +8271,7 @@
       <c r="W121" s="52"/>
       <c r="X121" s="52"/>
     </row>
-    <row r="122" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="25">
         <v>1</v>
       </c>
@@ -8275,19 +8317,19 @@
       <c r="W122" s="52"/>
       <c r="X122" s="52"/>
     </row>
-    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="92" t="s">
+    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="87" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="92"/>
-      <c r="C123" s="92"/>
-      <c r="D123" s="92"/>
-      <c r="E123" s="92"/>
-      <c r="F123" s="92"/>
-      <c r="G123" s="92"/>
-      <c r="H123" s="92"/>
-      <c r="I123" s="92"/>
-      <c r="J123" s="92"/>
+      <c r="B123" s="87"/>
+      <c r="C123" s="87"/>
+      <c r="D123" s="87"/>
+      <c r="E123" s="87"/>
+      <c r="F123" s="87"/>
+      <c r="G123" s="87"/>
+      <c r="H123" s="87"/>
+      <c r="I123" s="87"/>
+      <c r="J123" s="87"/>
       <c r="K123" s="51"/>
       <c r="L123" s="52"/>
       <c r="M123" s="52"/>
@@ -8303,7 +8345,7 @@
       <c r="W123" s="52"/>
       <c r="X123" s="52"/>
     </row>
-    <row r="124" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="25">
         <v>1</v>
       </c>
@@ -8349,21 +8391,21 @@
       <c r="W124" s="52"/>
       <c r="X124" s="52"/>
     </row>
-    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="92" t="s">
+    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="87" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="92"/>
-      <c r="C125" s="92"/>
-      <c r="D125" s="92"/>
-      <c r="E125" s="92"/>
-      <c r="F125" s="92"/>
-      <c r="G125" s="92"/>
-      <c r="H125" s="92"/>
-      <c r="I125" s="92"/>
-      <c r="J125" s="92"/>
-    </row>
-    <row r="126" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="87"/>
+      <c r="C125" s="87"/>
+      <c r="D125" s="87"/>
+      <c r="E125" s="87"/>
+      <c r="F125" s="87"/>
+      <c r="G125" s="87"/>
+      <c r="H125" s="87"/>
+      <c r="I125" s="87"/>
+      <c r="J125" s="87"/>
+    </row>
+    <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
         <v>1</v>
       </c>
@@ -8409,7 +8451,7 @@
       <c r="W126" s="55"/>
       <c r="X126" s="55"/>
     </row>
-    <row r="127" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="25">
         <v>2</v>
       </c>
@@ -8455,7 +8497,7 @@
       <c r="W127" s="52"/>
       <c r="X127" s="52"/>
     </row>
-    <row r="128" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="25">
         <v>3</v>
       </c>
@@ -8501,7 +8543,7 @@
       <c r="W128" s="52"/>
       <c r="X128" s="52"/>
     </row>
-    <row r="129" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="25">
         <v>4</v>
       </c>
@@ -8547,7 +8589,7 @@
       <c r="W129" s="52"/>
       <c r="X129" s="52"/>
     </row>
-    <row r="130" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="25">
         <v>5</v>
       </c>
@@ -8593,7 +8635,7 @@
       <c r="W130" s="52"/>
       <c r="X130" s="52"/>
     </row>
-    <row r="131" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="25">
         <v>6</v>
       </c>
@@ -8639,7 +8681,7 @@
       <c r="W131" s="52"/>
       <c r="X131" s="52"/>
     </row>
-    <row r="132" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="25">
         <v>7</v>
       </c>
@@ -8685,19 +8727,19 @@
       <c r="W132" s="52"/>
       <c r="X132" s="52"/>
     </row>
-    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="92" t="s">
+    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="87" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="92"/>
-      <c r="C133" s="92"/>
-      <c r="D133" s="93"/>
-      <c r="E133" s="93"/>
-      <c r="F133" s="93"/>
-      <c r="G133" s="93"/>
-      <c r="H133" s="93"/>
-      <c r="I133" s="93"/>
-      <c r="J133" s="93"/>
+      <c r="B133" s="87"/>
+      <c r="C133" s="87"/>
+      <c r="D133" s="88"/>
+      <c r="E133" s="88"/>
+      <c r="F133" s="88"/>
+      <c r="G133" s="88"/>
+      <c r="H133" s="88"/>
+      <c r="I133" s="88"/>
+      <c r="J133" s="88"/>
       <c r="K133" s="52"/>
       <c r="L133" s="52"/>
       <c r="M133" s="52"/>
@@ -8713,7 +8755,7 @@
       <c r="W133" s="52"/>
       <c r="X133" s="52"/>
     </row>
-    <row r="134" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="53">
         <v>11</v>
       </c>
@@ -8759,7 +8801,7 @@
       <c r="W134" s="52"/>
       <c r="X134" s="52"/>
     </row>
-    <row r="135" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="26">
         <v>2</v>
       </c>
@@ -8805,7 +8847,7 @@
       <c r="W135" s="52"/>
       <c r="X135" s="52"/>
     </row>
-    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="26">
         <v>3</v>
       </c>
@@ -8837,7 +8879,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="26">
         <v>4</v>
       </c>
@@ -8883,7 +8925,7 @@
       <c r="W137" s="52"/>
       <c r="X137" s="52"/>
     </row>
-    <row r="138" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="26">
         <v>5</v>
       </c>
@@ -8929,7 +8971,7 @@
       <c r="W138" s="52"/>
       <c r="X138" s="52"/>
     </row>
-    <row r="139" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="26">
         <v>6</v>
       </c>
@@ -8975,7 +9017,7 @@
       <c r="W139" s="52"/>
       <c r="X139" s="52"/>
     </row>
-    <row r="140" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="26">
         <v>7</v>
       </c>
@@ -9007,7 +9049,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="26">
         <v>8</v>
       </c>
@@ -9053,7 +9095,7 @@
       <c r="W141" s="52"/>
       <c r="X141" s="52"/>
     </row>
-    <row r="142" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="26">
         <v>9</v>
       </c>
@@ -9099,7 +9141,7 @@
       <c r="W142" s="52"/>
       <c r="X142" s="52"/>
     </row>
-    <row r="143" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="26">
         <v>10</v>
       </c>
@@ -9145,7 +9187,7 @@
       <c r="W143" s="52"/>
       <c r="X143" s="52"/>
     </row>
-    <row r="144" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="26">
         <v>11</v>
       </c>
@@ -9191,19 +9233,19 @@
       <c r="W144" s="52"/>
       <c r="X144" s="52"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="97" t="s">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="92" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="98"/>
-      <c r="C145" s="98"/>
-      <c r="D145" s="98"/>
-      <c r="E145" s="98"/>
-      <c r="F145" s="98"/>
-      <c r="G145" s="98"/>
-      <c r="H145" s="98"/>
-      <c r="I145" s="98"/>
-      <c r="J145" s="99"/>
+      <c r="B145" s="93"/>
+      <c r="C145" s="93"/>
+      <c r="D145" s="93"/>
+      <c r="E145" s="93"/>
+      <c r="F145" s="93"/>
+      <c r="G145" s="93"/>
+      <c r="H145" s="93"/>
+      <c r="I145" s="93"/>
+      <c r="J145" s="94"/>
       <c r="K145" s="52"/>
       <c r="L145" s="52"/>
       <c r="M145" s="52"/>
@@ -9219,7 +9261,7 @@
       <c r="W145" s="52"/>
       <c r="X145" s="52"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="25">
         <v>1</v>
       </c>
@@ -9265,7 +9307,7 @@
       <c r="W146" s="52"/>
       <c r="X146" s="52"/>
     </row>
-    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="25">
         <v>2</v>
       </c>
@@ -9297,7 +9339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A148" s="25">
         <v>3</v>
       </c>
@@ -9329,7 +9371,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="25">
         <v>4</v>
       </c>
@@ -9361,7 +9403,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="25">
         <v>5</v>
       </c>
@@ -9409,7 +9451,7 @@
       <c r="Y150" s="52"/>
       <c r="Z150" s="52"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="25">
         <v>6</v>
       </c>
@@ -9457,7 +9499,7 @@
       <c r="Y151" s="52"/>
       <c r="Z151" s="52"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="25">
         <v>7</v>
       </c>
@@ -9505,7 +9547,7 @@
       <c r="Y152" s="52"/>
       <c r="Z152" s="52"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="25">
         <v>8</v>
       </c>
@@ -9553,7 +9595,7 @@
       <c r="Y153" s="52"/>
       <c r="Z153" s="52"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="25">
         <v>9</v>
       </c>
@@ -9601,7 +9643,7 @@
       <c r="Y154" s="52"/>
       <c r="Z154" s="52"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="25">
         <v>10</v>
       </c>
@@ -9649,19 +9691,19 @@
       <c r="Y155" s="52"/>
       <c r="Z155" s="52"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="92" t="s">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="87" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="92"/>
-      <c r="C156" s="92"/>
-      <c r="D156" s="92"/>
-      <c r="E156" s="92"/>
-      <c r="F156" s="92"/>
-      <c r="G156" s="92"/>
-      <c r="H156" s="92"/>
-      <c r="I156" s="92"/>
-      <c r="J156" s="92"/>
+      <c r="B156" s="87"/>
+      <c r="C156" s="87"/>
+      <c r="D156" s="87"/>
+      <c r="E156" s="87"/>
+      <c r="F156" s="87"/>
+      <c r="G156" s="87"/>
+      <c r="H156" s="87"/>
+      <c r="I156" s="87"/>
+      <c r="J156" s="87"/>
       <c r="K156" s="52"/>
       <c r="L156" s="52"/>
       <c r="M156" s="52"/>
@@ -9679,7 +9721,7 @@
       <c r="Y156" s="52"/>
       <c r="Z156" s="52"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="25">
         <v>1</v>
       </c>
@@ -9727,19 +9769,19 @@
       <c r="Y157" s="52"/>
       <c r="Z157" s="52"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="92" t="s">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="87" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="92"/>
-      <c r="C158" s="92"/>
-      <c r="D158" s="92"/>
-      <c r="E158" s="92"/>
-      <c r="F158" s="92"/>
-      <c r="G158" s="92"/>
-      <c r="H158" s="92"/>
-      <c r="I158" s="92"/>
-      <c r="J158" s="92"/>
+      <c r="B158" s="87"/>
+      <c r="C158" s="87"/>
+      <c r="D158" s="87"/>
+      <c r="E158" s="87"/>
+      <c r="F158" s="87"/>
+      <c r="G158" s="87"/>
+      <c r="H158" s="87"/>
+      <c r="I158" s="87"/>
+      <c r="J158" s="87"/>
       <c r="K158" s="52"/>
       <c r="L158" s="52"/>
       <c r="M158" s="52"/>
@@ -9757,7 +9799,7 @@
       <c r="Y158" s="52"/>
       <c r="Z158" s="52"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="61">
         <v>1</v>
       </c>
@@ -9805,7 +9847,7 @@
       <c r="Y159" s="52"/>
       <c r="Z159" s="52"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="62">
         <v>2</v>
       </c>
@@ -9853,7 +9895,7 @@
       <c r="Y160" s="52"/>
       <c r="Z160" s="52"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="62">
         <v>3</v>
       </c>
@@ -9901,7 +9943,7 @@
       <c r="Y161" s="52"/>
       <c r="Z161" s="52"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="62">
         <v>4</v>
       </c>
@@ -9949,7 +9991,7 @@
       <c r="Y162" s="52"/>
       <c r="Z162" s="52"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="62">
         <v>5</v>
       </c>
@@ -9997,7 +10039,7 @@
       <c r="Y163" s="52"/>
       <c r="Z163" s="52"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="62">
         <v>6</v>
       </c>
@@ -10045,7 +10087,7 @@
       <c r="Y164" s="52"/>
       <c r="Z164" s="52"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="62">
         <v>7</v>
       </c>
@@ -10093,7 +10135,7 @@
       <c r="Y165" s="52"/>
       <c r="Z165" s="52"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="62">
         <v>8</v>
       </c>
@@ -10141,7 +10183,7 @@
       <c r="Y166" s="52"/>
       <c r="Z166" s="52"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="61">
         <v>9</v>
       </c>
@@ -10189,7 +10231,7 @@
       <c r="Y167" s="52"/>
       <c r="Z167" s="52"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="62">
         <v>10</v>
       </c>
@@ -10221,7 +10263,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="61">
         <v>11</v>
       </c>
@@ -10253,7 +10295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="62">
         <v>12</v>
       </c>
@@ -10285,7 +10327,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="61">
         <v>13</v>
       </c>
@@ -10317,7 +10359,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="62">
         <v>14</v>
       </c>
@@ -10349,7 +10391,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="61">
         <v>15</v>
       </c>
@@ -10381,7 +10423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="62">
         <v>16</v>
       </c>
@@ -10413,7 +10455,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="175" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="61">
         <v>17</v>
       </c>
@@ -10445,7 +10487,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="62">
         <v>18</v>
       </c>
@@ -10477,7 +10519,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="76">
         <v>19</v>
       </c>
@@ -10509,7 +10551,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="76">
         <v>20</v>
       </c>
@@ -10541,7 +10583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="76">
         <v>21</v>
       </c>
@@ -10573,21 +10615,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="92" t="s">
+    <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="87" t="s">
         <v>707</v>
       </c>
-      <c r="B180" s="92"/>
-      <c r="C180" s="92"/>
-      <c r="D180" s="84"/>
-      <c r="E180" s="92"/>
-      <c r="F180" s="92"/>
-      <c r="G180" s="92"/>
-      <c r="H180" s="92"/>
-      <c r="I180" s="92"/>
-      <c r="J180" s="92"/>
-    </row>
-    <row r="181" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B180" s="87"/>
+      <c r="C180" s="87"/>
+      <c r="D180" s="85"/>
+      <c r="E180" s="87"/>
+      <c r="F180" s="87"/>
+      <c r="G180" s="87"/>
+      <c r="H180" s="87"/>
+      <c r="I180" s="87"/>
+      <c r="J180" s="87"/>
+    </row>
+    <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="62">
         <v>1</v>
       </c>
@@ -10619,7 +10661,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="62">
         <v>2</v>
       </c>
@@ -10651,7 +10693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="62">
         <v>3</v>
       </c>
@@ -10683,7 +10725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="62">
         <v>4</v>
       </c>
@@ -10715,7 +10757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="62">
         <v>5</v>
       </c>
@@ -10747,7 +10789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="62">
         <v>6</v>
       </c>
@@ -10779,7 +10821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="62">
         <v>7</v>
       </c>
@@ -10811,7 +10853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="62">
         <v>7</v>
       </c>
@@ -10843,7 +10885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="1:10" s="28" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="62">
         <v>9</v>
       </c>
@@ -10875,21 +10917,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="94" t="s">
+    <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="89" t="s">
         <v>609</v>
       </c>
-      <c r="B190" s="95"/>
-      <c r="C190" s="95"/>
-      <c r="D190" s="95"/>
-      <c r="E190" s="95"/>
-      <c r="F190" s="95"/>
-      <c r="G190" s="95"/>
-      <c r="H190" s="95"/>
-      <c r="I190" s="95"/>
-      <c r="J190" s="96"/>
-    </row>
-    <row r="191" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B190" s="90"/>
+      <c r="C190" s="90"/>
+      <c r="D190" s="90"/>
+      <c r="E190" s="90"/>
+      <c r="F190" s="90"/>
+      <c r="G190" s="90"/>
+      <c r="H190" s="90"/>
+      <c r="I190" s="90"/>
+      <c r="J190" s="91"/>
+    </row>
+    <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="62">
         <v>1</v>
       </c>
@@ -10921,7 +10963,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="62">
         <v>2</v>
       </c>
@@ -10953,7 +10995,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="62">
         <v>3</v>
       </c>
@@ -10985,7 +11027,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="62">
         <v>4</v>
       </c>
@@ -11017,7 +11059,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="62">
         <v>5</v>
       </c>
@@ -11049,7 +11091,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="62">
         <v>6</v>
       </c>
@@ -11081,7 +11123,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="62">
         <v>7</v>
       </c>
@@ -11113,21 +11155,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198" s="84" t="s">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A198" s="85" t="s">
         <v>630</v>
       </c>
-      <c r="B198" s="84"/>
-      <c r="C198" s="84"/>
-      <c r="D198" s="84"/>
-      <c r="E198" s="84"/>
-      <c r="F198" s="84"/>
-      <c r="G198" s="84"/>
-      <c r="H198" s="84"/>
-      <c r="I198" s="84"/>
-      <c r="J198" s="84"/>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B198" s="85"/>
+      <c r="C198" s="85"/>
+      <c r="D198" s="85"/>
+      <c r="E198" s="85"/>
+      <c r="F198" s="85"/>
+      <c r="G198" s="85"/>
+      <c r="H198" s="85"/>
+      <c r="I198" s="85"/>
+      <c r="J198" s="85"/>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="43">
         <v>1</v>
       </c>
@@ -11159,7 +11201,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="43">
         <v>2</v>
       </c>
@@ -11191,7 +11233,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="43">
         <v>3</v>
       </c>
@@ -11223,7 +11265,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="43">
         <v>4</v>
       </c>
@@ -11255,21 +11297,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203" s="84" t="s">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A203" s="85" t="s">
         <v>643</v>
       </c>
-      <c r="B203" s="84"/>
-      <c r="C203" s="84"/>
-      <c r="D203" s="84"/>
-      <c r="E203" s="84"/>
-      <c r="F203" s="84"/>
-      <c r="G203" s="84"/>
-      <c r="H203" s="84"/>
-      <c r="I203" s="84"/>
-      <c r="J203" s="84"/>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B203" s="85"/>
+      <c r="C203" s="85"/>
+      <c r="D203" s="85"/>
+      <c r="E203" s="85"/>
+      <c r="F203" s="85"/>
+      <c r="G203" s="85"/>
+      <c r="H203" s="85"/>
+      <c r="I203" s="85"/>
+      <c r="J203" s="85"/>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="43">
         <v>1</v>
       </c>
@@ -11301,21 +11343,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205" s="84" t="s">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A205" s="85" t="s">
         <v>649</v>
       </c>
-      <c r="B205" s="84"/>
-      <c r="C205" s="84"/>
-      <c r="D205" s="84"/>
-      <c r="E205" s="84"/>
-      <c r="F205" s="84"/>
-      <c r="G205" s="84"/>
-      <c r="H205" s="84"/>
-      <c r="I205" s="84"/>
-      <c r="J205" s="84"/>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B205" s="85"/>
+      <c r="C205" s="85"/>
+      <c r="D205" s="85"/>
+      <c r="E205" s="85"/>
+      <c r="F205" s="85"/>
+      <c r="G205" s="85"/>
+      <c r="H205" s="85"/>
+      <c r="I205" s="85"/>
+      <c r="J205" s="85"/>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="43">
         <v>1</v>
       </c>
@@ -11347,7 +11389,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="43">
         <v>2</v>
       </c>
@@ -11379,7 +11421,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="43">
         <v>3</v>
       </c>
@@ -11411,7 +11453,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="43">
         <v>4</v>
       </c>
@@ -11443,7 +11485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="43">
         <v>5</v>
       </c>
@@ -11475,7 +11517,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="43">
         <v>6</v>
       </c>
@@ -11507,7 +11549,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="43">
         <v>7</v>
       </c>
@@ -11539,7 +11581,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="43">
         <v>8</v>
       </c>
@@ -11571,7 +11613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="43">
         <v>9</v>
       </c>
@@ -11603,7 +11645,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="75"/>
       <c r="B215" s="75"/>
       <c r="C215" s="75"/>
@@ -11617,7 +11659,7 @@
       <c r="I215" s="75"/>
       <c r="J215" s="75"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="43">
         <v>1</v>
       </c>
@@ -11649,7 +11691,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="73"/>
       <c r="B217" s="73"/>
       <c r="C217" s="73"/>
@@ -11663,7 +11705,7 @@
       <c r="I217" s="73"/>
       <c r="J217" s="73"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="43">
         <v>1</v>
       </c>
@@ -11695,7 +11737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="43">
         <v>2</v>
       </c>
@@ -11727,21 +11769,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A220" s="84" t="s">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A220" s="85" t="s">
         <v>711</v>
       </c>
-      <c r="B220" s="84"/>
-      <c r="C220" s="84"/>
-      <c r="D220" s="84"/>
-      <c r="E220" s="84"/>
-      <c r="F220" s="84"/>
-      <c r="G220" s="84"/>
-      <c r="H220" s="84"/>
-      <c r="I220" s="84"/>
-      <c r="J220" s="84"/>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B220" s="85"/>
+      <c r="C220" s="85"/>
+      <c r="D220" s="85"/>
+      <c r="E220" s="85"/>
+      <c r="F220" s="85"/>
+      <c r="G220" s="85"/>
+      <c r="H220" s="85"/>
+      <c r="I220" s="85"/>
+      <c r="J220" s="85"/>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="43">
         <v>1</v>
       </c>
@@ -11773,7 +11815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="43">
         <v>2</v>
       </c>
@@ -11805,7 +11847,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="43">
         <v>3</v>
       </c>
@@ -11837,7 +11879,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="43">
         <v>4</v>
       </c>
@@ -11869,7 +11911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="43">
         <v>5</v>
       </c>
@@ -11901,21 +11943,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A226" s="84" t="s">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A226" s="85" t="s">
         <v>719</v>
       </c>
-      <c r="B226" s="84"/>
-      <c r="C226" s="84"/>
-      <c r="D226" s="84"/>
-      <c r="E226" s="84"/>
-      <c r="F226" s="84"/>
-      <c r="G226" s="84"/>
-      <c r="H226" s="84"/>
-      <c r="I226" s="84"/>
-      <c r="J226" s="84"/>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B226" s="85"/>
+      <c r="C226" s="85"/>
+      <c r="D226" s="85"/>
+      <c r="E226" s="85"/>
+      <c r="F226" s="85"/>
+      <c r="G226" s="85"/>
+      <c r="H226" s="85"/>
+      <c r="I226" s="85"/>
+      <c r="J226" s="85"/>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="43">
         <v>1</v>
       </c>
@@ -11947,7 +11989,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="43">
         <v>2</v>
       </c>
@@ -11979,7 +12021,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="43">
         <v>3</v>
       </c>
@@ -12011,7 +12053,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="43">
         <v>4</v>
       </c>
@@ -12043,7 +12085,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="43">
         <v>5</v>
       </c>
@@ -12075,7 +12117,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="43">
         <v>6</v>
       </c>
@@ -12107,7 +12149,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="43">
         <v>7</v>
       </c>
@@ -12139,7 +12181,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="43">
         <v>8</v>
       </c>
@@ -12171,7 +12213,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="43">
         <v>9</v>
       </c>
@@ -12203,7 +12245,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="43">
         <v>10</v>
       </c>
@@ -12235,7 +12277,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="43">
         <v>11</v>
       </c>
@@ -12267,21 +12309,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="84" t="s">
+    <row r="238" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A238" s="85" t="s">
         <v>756</v>
       </c>
-      <c r="B238" s="84"/>
-      <c r="C238" s="84"/>
-      <c r="D238" s="84"/>
-      <c r="E238" s="84"/>
-      <c r="F238" s="84"/>
-      <c r="G238" s="84"/>
-      <c r="H238" s="84"/>
-      <c r="I238" s="84"/>
-      <c r="J238" s="84"/>
-    </row>
-    <row r="239" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B238" s="85"/>
+      <c r="C238" s="85"/>
+      <c r="D238" s="85"/>
+      <c r="E238" s="85"/>
+      <c r="F238" s="85"/>
+      <c r="G238" s="85"/>
+      <c r="H238" s="85"/>
+      <c r="I238" s="85"/>
+      <c r="J238" s="85"/>
+    </row>
+    <row r="239" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="43">
         <v>1</v>
       </c>
@@ -12313,21 +12355,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A240" s="84" t="s">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A240" s="85" t="s">
         <v>768</v>
       </c>
-      <c r="B240" s="84"/>
-      <c r="C240" s="84"/>
-      <c r="D240" s="84"/>
-      <c r="E240" s="84"/>
-      <c r="F240" s="84"/>
-      <c r="G240" s="84"/>
-      <c r="H240" s="84"/>
-      <c r="I240" s="84"/>
-      <c r="J240" s="84"/>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B240" s="85"/>
+      <c r="C240" s="85"/>
+      <c r="D240" s="85"/>
+      <c r="E240" s="85"/>
+      <c r="F240" s="85"/>
+      <c r="G240" s="85"/>
+      <c r="H240" s="85"/>
+      <c r="I240" s="85"/>
+      <c r="J240" s="85"/>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="43">
         <v>1</v>
       </c>
@@ -12359,7 +12401,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="43">
         <v>2</v>
       </c>
@@ -12391,7 +12433,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="43">
         <v>3</v>
       </c>
@@ -12423,7 +12465,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="43">
         <v>4</v>
       </c>
@@ -12455,7 +12497,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="43">
         <v>5</v>
       </c>
@@ -12487,7 +12529,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="43">
         <v>6</v>
       </c>
@@ -12519,7 +12561,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="43">
         <v>7</v>
       </c>
@@ -12551,7 +12593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="43">
         <v>8</v>
       </c>
@@ -12583,7 +12625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="43">
         <v>9</v>
       </c>
@@ -12615,7 +12657,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="43">
         <v>10</v>
       </c>
@@ -12647,7 +12689,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="43">
         <v>11</v>
       </c>
@@ -12679,7 +12721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="43">
         <v>12</v>
       </c>
@@ -12711,7 +12753,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="43">
         <v>13</v>
       </c>
@@ -12743,7 +12785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="43">
         <v>14</v>
       </c>
@@ -12775,7 +12817,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="43">
         <v>15</v>
       </c>
@@ -12807,21 +12849,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="84" t="s">
+    <row r="256" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A256" s="85" t="s">
         <v>813</v>
       </c>
-      <c r="B256" s="84"/>
-      <c r="C256" s="84"/>
-      <c r="D256" s="84"/>
-      <c r="E256" s="84"/>
-      <c r="F256" s="84"/>
-      <c r="G256" s="84"/>
-      <c r="H256" s="84"/>
-      <c r="I256" s="84"/>
-      <c r="J256" s="84"/>
-    </row>
-    <row r="257" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B256" s="85"/>
+      <c r="C256" s="85"/>
+      <c r="D256" s="85"/>
+      <c r="E256" s="85"/>
+      <c r="F256" s="85"/>
+      <c r="G256" s="85"/>
+      <c r="H256" s="85"/>
+      <c r="I256" s="85"/>
+      <c r="J256" s="85"/>
+    </row>
+    <row r="257" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="43">
         <v>1</v>
       </c>
@@ -12853,7 +12895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="43">
         <v>2</v>
       </c>
@@ -12885,21 +12927,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="84" t="s">
+    <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A259" s="85" t="s">
         <v>814</v>
       </c>
-      <c r="B259" s="84"/>
-      <c r="C259" s="84"/>
-      <c r="D259" s="84"/>
-      <c r="E259" s="84"/>
-      <c r="F259" s="84"/>
-      <c r="G259" s="84"/>
-      <c r="H259" s="84"/>
-      <c r="I259" s="84"/>
-      <c r="J259" s="84"/>
-    </row>
-    <row r="260" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B259" s="85"/>
+      <c r="C259" s="85"/>
+      <c r="D259" s="85"/>
+      <c r="E259" s="85"/>
+      <c r="F259" s="85"/>
+      <c r="G259" s="85"/>
+      <c r="H259" s="85"/>
+      <c r="I259" s="85"/>
+      <c r="J259" s="85"/>
+    </row>
+    <row r="260" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="43">
         <v>1</v>
       </c>
@@ -12931,7 +12973,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="43">
         <v>2</v>
       </c>
@@ -12963,7 +13005,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="43">
         <v>3</v>
       </c>
@@ -12995,7 +13037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="43">
         <v>4</v>
       </c>
@@ -13027,7 +13069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="43">
         <v>5</v>
       </c>
@@ -13059,21 +13101,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="84" t="s">
+    <row r="265" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A265" s="85" t="s">
         <v>890</v>
       </c>
-      <c r="B265" s="84"/>
-      <c r="C265" s="84"/>
-      <c r="D265" s="84"/>
-      <c r="E265" s="84"/>
-      <c r="F265" s="84"/>
-      <c r="G265" s="84"/>
-      <c r="H265" s="84"/>
-      <c r="I265" s="84"/>
-      <c r="J265" s="84"/>
-    </row>
-    <row r="266" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B265" s="85"/>
+      <c r="C265" s="85"/>
+      <c r="D265" s="85"/>
+      <c r="E265" s="85"/>
+      <c r="F265" s="85"/>
+      <c r="G265" s="85"/>
+      <c r="H265" s="85"/>
+      <c r="I265" s="85"/>
+      <c r="J265" s="85"/>
+    </row>
+    <row r="266" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="43">
         <v>1</v>
       </c>
@@ -13105,21 +13147,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="84" t="s">
+    <row r="267" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="85" t="s">
         <v>917</v>
       </c>
-      <c r="B267" s="84"/>
-      <c r="C267" s="84"/>
-      <c r="D267" s="84"/>
-      <c r="E267" s="84"/>
-      <c r="F267" s="84"/>
-      <c r="G267" s="84"/>
-      <c r="H267" s="84"/>
-      <c r="I267" s="84"/>
-      <c r="J267" s="84"/>
-    </row>
-    <row r="268" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B267" s="85"/>
+      <c r="C267" s="85"/>
+      <c r="D267" s="85"/>
+      <c r="E267" s="85"/>
+      <c r="F267" s="85"/>
+      <c r="G267" s="85"/>
+      <c r="H267" s="85"/>
+      <c r="I267" s="85"/>
+      <c r="J267" s="85"/>
+    </row>
+    <row r="268" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="43">
         <v>1</v>
       </c>
@@ -13151,7 +13193,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="43">
         <v>2</v>
       </c>
@@ -13183,21 +13225,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="84" t="s">
+    <row r="270" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A270" s="85" t="s">
         <v>931</v>
       </c>
-      <c r="B270" s="84"/>
-      <c r="C270" s="84"/>
-      <c r="D270" s="84"/>
-      <c r="E270" s="84"/>
-      <c r="F270" s="84"/>
-      <c r="G270" s="84"/>
-      <c r="H270" s="84"/>
-      <c r="I270" s="84"/>
-      <c r="J270" s="84"/>
-    </row>
-    <row r="271" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B270" s="85"/>
+      <c r="C270" s="85"/>
+      <c r="D270" s="85"/>
+      <c r="E270" s="85"/>
+      <c r="F270" s="85"/>
+      <c r="G270" s="85"/>
+      <c r="H270" s="85"/>
+      <c r="I270" s="85"/>
+      <c r="J270" s="85"/>
+    </row>
+    <row r="271" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="43">
         <v>1</v>
       </c>
@@ -13229,7 +13271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="272" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" s="43">
         <v>2</v>
       </c>
@@ -13261,21 +13303,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="273" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="84" t="s">
+    <row r="273" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="85" t="s">
         <v>936</v>
       </c>
-      <c r="B273" s="84"/>
-      <c r="C273" s="84"/>
-      <c r="D273" s="84"/>
-      <c r="E273" s="84"/>
-      <c r="F273" s="84"/>
-      <c r="G273" s="84"/>
-      <c r="H273" s="84"/>
-      <c r="I273" s="84"/>
-      <c r="J273" s="84"/>
-    </row>
-    <row r="274" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B273" s="85"/>
+      <c r="C273" s="85"/>
+      <c r="D273" s="85"/>
+      <c r="E273" s="85"/>
+      <c r="F273" s="85"/>
+      <c r="G273" s="85"/>
+      <c r="H273" s="85"/>
+      <c r="I273" s="85"/>
+      <c r="J273" s="85"/>
+    </row>
+    <row r="274" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="43">
         <v>1</v>
       </c>
@@ -13307,7 +13349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" s="43">
         <v>2</v>
       </c>
@@ -13339,21 +13381,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A276" s="84" t="s">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A276" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="B276" s="84"/>
-      <c r="C276" s="84"/>
-      <c r="D276" s="84"/>
-      <c r="E276" s="84"/>
-      <c r="F276" s="84"/>
-      <c r="G276" s="84"/>
-      <c r="H276" s="84"/>
-      <c r="I276" s="84"/>
-      <c r="J276" s="84"/>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B276" s="85"/>
+      <c r="C276" s="85"/>
+      <c r="D276" s="85"/>
+      <c r="E276" s="85"/>
+      <c r="F276" s="85"/>
+      <c r="G276" s="85"/>
+      <c r="H276" s="85"/>
+      <c r="I276" s="85"/>
+      <c r="J276" s="85"/>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="77">
         <v>1</v>
       </c>
@@ -13385,7 +13427,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="77">
         <v>2</v>
       </c>
@@ -13417,21 +13459,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A279" s="84" t="s">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A279" s="85" t="s">
         <v>955</v>
       </c>
-      <c r="B279" s="84"/>
-      <c r="C279" s="84"/>
-      <c r="D279" s="84"/>
-      <c r="E279" s="84"/>
-      <c r="F279" s="84"/>
-      <c r="G279" s="84"/>
-      <c r="H279" s="84"/>
-      <c r="I279" s="84"/>
-      <c r="J279" s="84"/>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B279" s="85"/>
+      <c r="C279" s="85"/>
+      <c r="D279" s="85"/>
+      <c r="E279" s="85"/>
+      <c r="F279" s="85"/>
+      <c r="G279" s="85"/>
+      <c r="H279" s="85"/>
+      <c r="I279" s="85"/>
+      <c r="J279" s="85"/>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="77">
         <v>1</v>
       </c>
@@ -13463,22 +13505,151 @@
         <v>13</v>
       </c>
     </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A281" s="85" t="s">
+        <v>966</v>
+      </c>
+      <c r="B281" s="85"/>
+      <c r="C281" s="85"/>
+      <c r="D281" s="85"/>
+      <c r="E281" s="85"/>
+      <c r="F281" s="85"/>
+      <c r="G281" s="85"/>
+      <c r="H281" s="85"/>
+      <c r="I281" s="85"/>
+      <c r="J281" s="85"/>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>1</v>
+      </c>
+      <c r="B282" t="s">
+        <v>10</v>
+      </c>
+      <c r="C282" t="s">
+        <v>967</v>
+      </c>
+      <c r="D282" t="s">
+        <v>968</v>
+      </c>
+      <c r="E282" t="s">
+        <v>14</v>
+      </c>
+      <c r="F282" t="s">
+        <v>969</v>
+      </c>
+      <c r="G282" t="s">
+        <v>11</v>
+      </c>
+      <c r="H282" t="s">
+        <v>970</v>
+      </c>
+      <c r="I282" t="s">
+        <v>12</v>
+      </c>
+      <c r="J282" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>2</v>
+      </c>
+      <c r="B283" t="s">
+        <v>10</v>
+      </c>
+      <c r="C283" t="s">
+        <v>971</v>
+      </c>
+      <c r="D283" t="s">
+        <v>972</v>
+      </c>
+      <c r="E283" t="s">
+        <v>14</v>
+      </c>
+      <c r="F283" t="s">
+        <v>973</v>
+      </c>
+      <c r="G283" t="s">
+        <v>11</v>
+      </c>
+      <c r="H283" t="s">
+        <v>970</v>
+      </c>
+      <c r="I283" t="s">
+        <v>12</v>
+      </c>
+      <c r="J283" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>3</v>
+      </c>
+      <c r="B284" t="s">
+        <v>10</v>
+      </c>
+      <c r="C284" t="s">
+        <v>974</v>
+      </c>
+      <c r="D284" t="s">
+        <v>975</v>
+      </c>
+      <c r="E284" t="s">
+        <v>14</v>
+      </c>
+      <c r="F284" t="s">
+        <v>976</v>
+      </c>
+      <c r="G284" t="s">
+        <v>11</v>
+      </c>
+      <c r="H284" t="s">
+        <v>970</v>
+      </c>
+      <c r="I284" t="s">
+        <v>12</v>
+      </c>
+      <c r="J284" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>4</v>
+      </c>
+      <c r="B285" t="s">
+        <v>10</v>
+      </c>
+      <c r="C285" t="s">
+        <v>977</v>
+      </c>
+      <c r="D285" t="s">
+        <v>978</v>
+      </c>
+      <c r="E285" t="s">
+        <v>14</v>
+      </c>
+      <c r="F285" t="s">
+        <v>979</v>
+      </c>
+      <c r="G285" t="s">
+        <v>11</v>
+      </c>
+      <c r="H285" t="s">
+        <v>970</v>
+      </c>
+      <c r="I285" t="s">
+        <v>12</v>
+      </c>
+      <c r="J285" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A270:J270"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="A121:J121"/>
-    <mergeCell ref="A123:J123"/>
-    <mergeCell ref="A125:J125"/>
-    <mergeCell ref="A203:J203"/>
-    <mergeCell ref="A198:J198"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="A190:J190"/>
-    <mergeCell ref="A145:J145"/>
-    <mergeCell ref="A156:J156"/>
-    <mergeCell ref="A158:J158"/>
-    <mergeCell ref="A180:J180"/>
-    <mergeCell ref="A267:J267"/>
+  <mergeCells count="31">
+    <mergeCell ref="A281:J281"/>
     <mergeCell ref="A279:J279"/>
     <mergeCell ref="A265:J265"/>
     <mergeCell ref="A220:J220"/>
@@ -13495,6 +13666,20 @@
     <mergeCell ref="A238:J238"/>
     <mergeCell ref="A276:J276"/>
     <mergeCell ref="A273:J273"/>
+    <mergeCell ref="A270:J270"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="A121:J121"/>
+    <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A203:J203"/>
+    <mergeCell ref="A198:J198"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A190:J190"/>
+    <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A158:J158"/>
+    <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A267:J267"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13592,36 +13777,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG258"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AG262"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.85546875" customWidth="1"/>
-    <col min="2" max="2" width="45.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="54.28515625" customWidth="1"/>
+    <col min="1" max="1" width="48.88671875" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="54.33203125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" customWidth="1"/>
-    <col min="12" max="12" width="53.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" customWidth="1"/>
+    <col min="12" max="12" width="53.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="52.28515625" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" customWidth="1"/>
+    <col min="17" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="71.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="52.33203125" customWidth="1"/>
+    <col min="21" max="21" width="20.88671875" customWidth="1"/>
     <col min="22" max="22" width="27" customWidth="1"/>
     <col min="24" max="25" width="29" customWidth="1"/>
-    <col min="26" max="26" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.42578125" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" customWidth="1"/>
+    <col min="26" max="26" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.44140625" customWidth="1"/>
+    <col min="29" max="29" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.6640625" customWidth="1"/>
+    <col min="31" max="31" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>5</v>
       </c>
@@ -13722,7 +13907,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>23</v>
       </c>
@@ -13805,7 +13990,7 @@
       <c r="AF2" s="28"/>
       <c r="AG2" s="28"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>25</v>
       </c>
@@ -13888,7 +14073,7 @@
       <c r="AF3" s="28"/>
       <c r="AG3" s="28"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
         <v>28</v>
       </c>
@@ -13971,7 +14156,7 @@
       <c r="AF4" s="28"/>
       <c r="AG4" s="28"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="31" t="s">
         <v>58</v>
       </c>
@@ -14054,7 +14239,7 @@
       <c r="AF5" s="28"/>
       <c r="AG5" s="28"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
         <v>69</v>
       </c>
@@ -14137,7 +14322,7 @@
       <c r="AF6" s="28"/>
       <c r="AG6" s="28"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
         <v>73</v>
       </c>
@@ -14220,7 +14405,7 @@
       <c r="AF7" s="28"/>
       <c r="AG7" s="28"/>
     </row>
-    <row r="8" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36" t="s">
         <v>77</v>
       </c>
@@ -14303,7 +14488,7 @@
       <c r="AF8" s="28"/>
       <c r="AG8" s="28"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="36" t="s">
         <v>79</v>
       </c>
@@ -14386,7 +14571,7 @@
       <c r="AF9" s="28"/>
       <c r="AG9" s="28"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="36" t="s">
         <v>80</v>
       </c>
@@ -14469,7 +14654,7 @@
       <c r="AF10" s="28"/>
       <c r="AG10" s="28"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
         <v>81</v>
       </c>
@@ -14552,7 +14737,7 @@
       <c r="AF11" s="28"/>
       <c r="AG11" s="28"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
         <v>83</v>
       </c>
@@ -14635,7 +14820,7 @@
       <c r="AF12" s="28"/>
       <c r="AG12" s="28"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="36" t="s">
         <v>84</v>
       </c>
@@ -14718,7 +14903,7 @@
       <c r="AF13" s="28"/>
       <c r="AG13" s="28"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" s="36" t="s">
         <v>85</v>
       </c>
@@ -14801,7 +14986,7 @@
       <c r="AF14" s="28"/>
       <c r="AG14" s="28"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>86</v>
       </c>
@@ -14884,7 +15069,7 @@
       <c r="AF15" s="28"/>
       <c r="AG15" s="28"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="36" t="s">
         <v>87</v>
       </c>
@@ -14967,7 +15152,7 @@
       <c r="AF16" s="28"/>
       <c r="AG16" s="28"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="36" t="s">
         <v>88</v>
       </c>
@@ -15050,7 +15235,7 @@
       <c r="AF17" s="28"/>
       <c r="AG17" s="28"/>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="36" t="s">
         <v>89</v>
       </c>
@@ -15133,7 +15318,7 @@
       <c r="AF18" s="28"/>
       <c r="AG18" s="28"/>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19" s="36" t="s">
         <v>91</v>
       </c>
@@ -15216,7 +15401,7 @@
       <c r="AF19" s="28"/>
       <c r="AG19" s="28"/>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" s="36" t="s">
         <v>93</v>
       </c>
@@ -15299,7 +15484,7 @@
       <c r="AF20" s="28"/>
       <c r="AG20" s="28"/>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>94</v>
       </c>
@@ -15382,7 +15567,7 @@
       <c r="AF21" s="28"/>
       <c r="AG21" s="28"/>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" s="36" t="s">
         <v>135</v>
       </c>
@@ -15465,7 +15650,7 @@
       <c r="AF22" s="28"/>
       <c r="AG22" s="28"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" s="36" t="s">
         <v>140</v>
       </c>
@@ -15548,7 +15733,7 @@
       <c r="AF23" s="28"/>
       <c r="AG23" s="28"/>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
         <v>63</v>
       </c>
@@ -15631,7 +15816,7 @@
       <c r="AF24" s="28"/>
       <c r="AG24" s="28"/>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" s="41" t="s">
         <v>144</v>
       </c>
@@ -15714,7 +15899,7 @@
       <c r="AF25" s="28"/>
       <c r="AG25" s="28"/>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>145</v>
       </c>
@@ -15797,7 +15982,7 @@
       <c r="AF26" s="28"/>
       <c r="AG26" s="28"/>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="41" t="s">
         <v>146</v>
       </c>
@@ -15880,7 +16065,7 @@
       <c r="AF27" s="28"/>
       <c r="AG27" s="28"/>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" s="41" t="s">
         <v>147</v>
       </c>
@@ -15963,7 +16148,7 @@
       <c r="AF28" s="28"/>
       <c r="AG28" s="28"/>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" s="41" t="s">
         <v>148</v>
       </c>
@@ -16046,7 +16231,7 @@
       <c r="AF29" s="28"/>
       <c r="AG29" s="28"/>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
         <v>150</v>
       </c>
@@ -16129,7 +16314,7 @@
       <c r="AF30" s="28"/>
       <c r="AG30" s="28"/>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31" s="41" t="s">
         <v>151</v>
       </c>
@@ -16212,7 +16397,7 @@
       <c r="AF31" s="28"/>
       <c r="AG31" s="28"/>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" s="41" t="s">
         <v>152</v>
       </c>
@@ -16295,7 +16480,7 @@
       <c r="AF32" s="28"/>
       <c r="AG32" s="28"/>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33" s="41" t="s">
         <v>153</v>
       </c>
@@ -16378,7 +16563,7 @@
       <c r="AF33" s="28"/>
       <c r="AG33" s="28"/>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" s="41" t="s">
         <v>154</v>
       </c>
@@ -16461,7 +16646,7 @@
       <c r="AF34" s="28"/>
       <c r="AG34" s="28"/>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" s="41" t="s">
         <v>155</v>
       </c>
@@ -16544,7 +16729,7 @@
       <c r="AF35" s="28"/>
       <c r="AG35" s="28"/>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" s="31" t="s">
         <v>64</v>
       </c>
@@ -16627,7 +16812,7 @@
       <c r="AF36" s="28"/>
       <c r="AG36" s="28"/>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" s="48" t="s">
         <v>175</v>
       </c>
@@ -16712,7 +16897,7 @@
       <c r="AF37" s="28"/>
       <c r="AG37" s="28"/>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A38" s="42" t="s">
         <v>179</v>
       </c>
@@ -16797,7 +16982,7 @@
       <c r="AF38" s="28"/>
       <c r="AG38" s="28"/>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="42" t="s">
         <v>182</v>
       </c>
@@ -16882,7 +17067,7 @@
       <c r="AF39" s="28"/>
       <c r="AG39" s="28"/>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" s="42" t="s">
         <v>185</v>
       </c>
@@ -16967,7 +17152,7 @@
       <c r="AF40" s="28"/>
       <c r="AG40" s="28"/>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" s="42" t="s">
         <v>188</v>
       </c>
@@ -17052,7 +17237,7 @@
       <c r="AF41" s="28"/>
       <c r="AG41" s="28"/>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" s="42" t="s">
         <v>190</v>
       </c>
@@ -17137,7 +17322,7 @@
       <c r="AF42" s="28"/>
       <c r="AG42" s="28"/>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" s="42" t="s">
         <v>193</v>
       </c>
@@ -17222,7 +17407,7 @@
       <c r="AF43" s="28"/>
       <c r="AG43" s="28"/>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44" s="42" t="s">
         <v>196</v>
       </c>
@@ -17307,7 +17492,7 @@
       <c r="AF44" s="28"/>
       <c r="AG44" s="28"/>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
         <v>198</v>
       </c>
@@ -17392,7 +17577,7 @@
       <c r="AF45" s="28"/>
       <c r="AG45" s="28"/>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
         <v>200</v>
       </c>
@@ -17477,7 +17662,7 @@
       <c r="AF46" s="28"/>
       <c r="AG46" s="28"/>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
         <v>202</v>
       </c>
@@ -17562,7 +17747,7 @@
       <c r="AF47" s="28"/>
       <c r="AG47" s="28"/>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
         <v>204</v>
       </c>
@@ -17647,7 +17832,7 @@
       <c r="AF48" s="28"/>
       <c r="AG48" s="28"/>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
         <v>206</v>
       </c>
@@ -17732,7 +17917,7 @@
       <c r="AF49" s="28"/>
       <c r="AG49" s="28"/>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
         <v>208</v>
       </c>
@@ -17817,7 +18002,7 @@
       <c r="AF50" s="28"/>
       <c r="AG50" s="28"/>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
         <v>210</v>
       </c>
@@ -17902,7 +18087,7 @@
       <c r="AF51" s="28"/>
       <c r="AG51" s="28"/>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
         <v>212</v>
       </c>
@@ -17987,7 +18172,7 @@
       <c r="AF52" s="28"/>
       <c r="AG52" s="28"/>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
         <v>679</v>
       </c>
@@ -18072,7 +18257,7 @@
       <c r="AF53" s="28"/>
       <c r="AG53" s="28"/>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54" s="49" t="s">
         <v>213</v>
       </c>
@@ -18157,7 +18342,7 @@
       <c r="AF54" s="28"/>
       <c r="AG54" s="28"/>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55" s="43" t="s">
         <v>214</v>
       </c>
@@ -18242,7 +18427,7 @@
       <c r="AF55" s="28"/>
       <c r="AG55" s="28"/>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="43" t="s">
         <v>215</v>
       </c>
@@ -18327,7 +18512,7 @@
       <c r="AF56" s="28"/>
       <c r="AG56" s="28"/>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="43" t="s">
         <v>216</v>
       </c>
@@ -18412,7 +18597,7 @@
       <c r="AF57" s="28"/>
       <c r="AG57" s="28"/>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58" s="43" t="s">
         <v>217</v>
       </c>
@@ -18497,7 +18682,7 @@
       <c r="AF58" s="28"/>
       <c r="AG58" s="28"/>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59" s="43" t="s">
         <v>218</v>
       </c>
@@ -18582,7 +18767,7 @@
       <c r="AF59" s="28"/>
       <c r="AG59" s="28"/>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60" s="43" t="s">
         <v>219</v>
       </c>
@@ -18667,7 +18852,7 @@
       <c r="AF60" s="28"/>
       <c r="AG60" s="28"/>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61" s="43" t="s">
         <v>220</v>
       </c>
@@ -18752,7 +18937,7 @@
       <c r="AF61" s="28"/>
       <c r="AG61" s="28"/>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A62" s="43" t="s">
         <v>221</v>
       </c>
@@ -18837,7 +19022,7 @@
       <c r="AF62" s="28"/>
       <c r="AG62" s="28"/>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="43" t="s">
         <v>222</v>
       </c>
@@ -18922,7 +19107,7 @@
       <c r="AF63" s="28"/>
       <c r="AG63" s="28"/>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A64" s="50" t="s">
         <v>249</v>
       </c>
@@ -19007,7 +19192,7 @@
       <c r="AF64" s="28"/>
       <c r="AG64" s="28"/>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65" s="43" t="s">
         <v>253</v>
       </c>
@@ -19092,7 +19277,7 @@
       <c r="AF65" s="28"/>
       <c r="AG65" s="28"/>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A66" s="43" t="s">
         <v>256</v>
       </c>
@@ -19177,7 +19362,7 @@
       <c r="AF66" s="28"/>
       <c r="AG66" s="28"/>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A67" s="43" t="s">
         <v>259</v>
       </c>
@@ -19262,7 +19447,7 @@
       <c r="AF67" s="28"/>
       <c r="AG67" s="28"/>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A68" s="43" t="s">
         <v>262</v>
       </c>
@@ -19347,7 +19532,7 @@
       <c r="AF68" s="28"/>
       <c r="AG68" s="28"/>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A69" s="43" t="s">
         <v>265</v>
       </c>
@@ -19432,7 +19617,7 @@
       <c r="AF69" s="28"/>
       <c r="AG69" s="28"/>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A70" s="43" t="s">
         <v>268</v>
       </c>
@@ -19517,7 +19702,7 @@
       <c r="AF70" s="28"/>
       <c r="AG70" s="28"/>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A71" s="43" t="s">
         <v>271</v>
       </c>
@@ -19602,7 +19787,7 @@
       <c r="AF71" s="28"/>
       <c r="AG71" s="28"/>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A72" s="43" t="s">
         <v>274</v>
       </c>
@@ -19687,7 +19872,7 @@
       <c r="AF72" s="28"/>
       <c r="AG72" s="28"/>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A73" s="43" t="s">
         <v>277</v>
       </c>
@@ -19772,7 +19957,7 @@
       <c r="AF73" s="28"/>
       <c r="AG73" s="28"/>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A74" s="43" t="s">
         <v>280</v>
       </c>
@@ -19859,7 +20044,7 @@
       <c r="AF74" s="28"/>
       <c r="AG74" s="28"/>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A75" s="56" t="s">
         <v>282</v>
       </c>
@@ -19946,7 +20131,7 @@
       <c r="AF75" s="28"/>
       <c r="AG75" s="28"/>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A76" s="43" t="s">
         <v>285</v>
       </c>
@@ -20033,7 +20218,7 @@
       <c r="AF76" s="28"/>
       <c r="AG76" s="28"/>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A77" s="43" t="s">
         <v>287</v>
       </c>
@@ -20120,7 +20305,7 @@
       <c r="AF77" s="28"/>
       <c r="AG77" s="28"/>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A78" s="43" t="s">
         <v>289</v>
       </c>
@@ -20207,7 +20392,7 @@
       <c r="AF78" s="28"/>
       <c r="AG78" s="28"/>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A79" s="43" t="s">
         <v>292</v>
       </c>
@@ -20294,7 +20479,7 @@
       <c r="AF79" s="28"/>
       <c r="AG79" s="28"/>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A80" s="43" t="s">
         <v>295</v>
       </c>
@@ -20381,7 +20566,7 @@
       <c r="AF80" s="28"/>
       <c r="AG80" s="28"/>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A81" s="43" t="s">
         <v>298</v>
       </c>
@@ -20468,7 +20653,7 @@
       <c r="AF81" s="28"/>
       <c r="AG81" s="28"/>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A82" s="43" t="s">
         <v>301</v>
       </c>
@@ -20555,7 +20740,7 @@
       <c r="AF82" s="28"/>
       <c r="AG82" s="28"/>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A83" s="43" t="s">
         <v>304</v>
       </c>
@@ -20642,7 +20827,7 @@
       <c r="AF83" s="28"/>
       <c r="AG83" s="28"/>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A84" s="43" t="s">
         <v>306</v>
       </c>
@@ -20729,7 +20914,7 @@
       <c r="AF84" s="28"/>
       <c r="AG84" s="28"/>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A85" s="43" t="s">
         <v>308</v>
       </c>
@@ -20816,7 +21001,7 @@
       <c r="AF85" s="28"/>
       <c r="AG85" s="28"/>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A86" s="43" t="s">
         <v>310</v>
       </c>
@@ -20903,7 +21088,7 @@
       <c r="AF86" s="28"/>
       <c r="AG86" s="28"/>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A87" s="43" t="s">
         <v>313</v>
       </c>
@@ -20990,7 +21175,7 @@
       <c r="AF87" s="28"/>
       <c r="AG87" s="28"/>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A88" s="43" t="s">
         <v>316</v>
       </c>
@@ -21077,7 +21262,7 @@
       <c r="AF88" s="28"/>
       <c r="AG88" s="28"/>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A89" s="43" t="s">
         <v>319</v>
       </c>
@@ -21164,7 +21349,7 @@
       <c r="AF89" s="28"/>
       <c r="AG89" s="28"/>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A90" s="43" t="s">
         <v>322</v>
       </c>
@@ -21251,7 +21436,7 @@
       <c r="AF90" s="28"/>
       <c r="AG90" s="28"/>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A91" s="43" t="s">
         <v>324</v>
       </c>
@@ -21338,7 +21523,7 @@
       <c r="AF91" s="28"/>
       <c r="AG91" s="28"/>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A92" s="43" t="s">
         <v>327</v>
       </c>
@@ -21425,7 +21610,7 @@
       <c r="AF92" s="28"/>
       <c r="AG92" s="28"/>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A93" s="43" t="s">
         <v>330</v>
       </c>
@@ -21512,7 +21697,7 @@
       <c r="AF93" s="28"/>
       <c r="AG93" s="28"/>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A94" s="43" t="s">
         <v>332</v>
       </c>
@@ -21599,7 +21784,7 @@
       <c r="AF94" s="28"/>
       <c r="AG94" s="28"/>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A95" s="43" t="s">
         <v>334</v>
       </c>
@@ -21686,7 +21871,7 @@
       <c r="AF95" s="28"/>
       <c r="AG95" s="28"/>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A96" s="43" t="s">
         <v>336</v>
       </c>
@@ -21773,7 +21958,7 @@
       <c r="AF96" s="28"/>
       <c r="AG96" s="28"/>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A97" s="43" t="s">
         <v>338</v>
       </c>
@@ -21860,7 +22045,7 @@
       <c r="AF97" s="28"/>
       <c r="AG97" s="28"/>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A98" s="43" t="s">
         <v>340</v>
       </c>
@@ -21947,7 +22132,7 @@
       <c r="AF98" s="28"/>
       <c r="AG98" s="28"/>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A99" s="43" t="s">
         <v>342</v>
       </c>
@@ -22034,7 +22219,7 @@
       <c r="AF99" s="28"/>
       <c r="AG99" s="28"/>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A100" s="43" t="s">
         <v>344</v>
       </c>
@@ -22121,7 +22306,7 @@
       <c r="AF100" s="28"/>
       <c r="AG100" s="28"/>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A101" s="43" t="s">
         <v>597</v>
       </c>
@@ -22208,7 +22393,7 @@
       <c r="AF101" s="28"/>
       <c r="AG101" s="28"/>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A102" s="43" t="s">
         <v>348</v>
       </c>
@@ -22295,7 +22480,7 @@
       <c r="AF102" s="28"/>
       <c r="AG102" s="28"/>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A103" s="43" t="s">
         <v>352</v>
       </c>
@@ -22382,7 +22567,7 @@
       <c r="AF103" s="28"/>
       <c r="AG103" s="28"/>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A104" s="43" t="s">
         <v>355</v>
       </c>
@@ -22469,7 +22654,7 @@
       <c r="AF104" s="28"/>
       <c r="AG104" s="28"/>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A105" s="43" t="s">
         <v>358</v>
       </c>
@@ -22556,7 +22741,7 @@
       <c r="AF105" s="28"/>
       <c r="AG105" s="28"/>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A106" s="43" t="s">
         <v>361</v>
       </c>
@@ -22643,7 +22828,7 @@
       <c r="AF106" s="28"/>
       <c r="AG106" s="28"/>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A107" s="43" t="s">
         <v>364</v>
       </c>
@@ -22730,7 +22915,7 @@
       <c r="AF107" s="28"/>
       <c r="AG107" s="28"/>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A108" s="43" t="s">
         <v>367</v>
       </c>
@@ -22817,7 +23002,7 @@
       <c r="AF108" s="28"/>
       <c r="AG108" s="28"/>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A109" s="43" t="s">
         <v>369</v>
       </c>
@@ -22904,7 +23089,7 @@
       <c r="AF109" s="28"/>
       <c r="AG109" s="28"/>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A110" s="43" t="s">
         <v>371</v>
       </c>
@@ -22991,7 +23176,7 @@
       <c r="AF110" s="28"/>
       <c r="AG110" s="28"/>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A111" s="43" t="s">
         <v>598</v>
       </c>
@@ -23078,7 +23263,7 @@
       <c r="AF111" s="28"/>
       <c r="AG111" s="28"/>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A112" s="43" t="s">
         <v>682</v>
       </c>
@@ -23165,7 +23350,7 @@
       <c r="AF112" s="28"/>
       <c r="AG112" s="28"/>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A113" s="43" t="s">
         <v>685</v>
       </c>
@@ -23252,7 +23437,7 @@
       <c r="AF113" s="28"/>
       <c r="AG113" s="28"/>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A114" s="43" t="s">
         <v>688</v>
       </c>
@@ -23339,7 +23524,7 @@
       <c r="AF114" s="28"/>
       <c r="AG114" s="28"/>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A115" s="43" t="s">
         <v>691</v>
       </c>
@@ -23426,7 +23611,7 @@
       <c r="AF115" s="28"/>
       <c r="AG115" s="28"/>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A116" s="43" t="s">
         <v>378</v>
       </c>
@@ -23513,7 +23698,7 @@
       <c r="AF116" s="28"/>
       <c r="AG116" s="28"/>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A117" s="43" t="s">
         <v>383</v>
       </c>
@@ -23600,7 +23785,7 @@
       <c r="AF117" s="28"/>
       <c r="AG117" s="28"/>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A118" s="43" t="s">
         <v>397</v>
       </c>
@@ -23687,7 +23872,7 @@
       <c r="AF118" s="28"/>
       <c r="AG118" s="28"/>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A119" s="43" t="s">
         <v>399</v>
       </c>
@@ -23774,7 +23959,7 @@
       <c r="AF119" s="28"/>
       <c r="AG119" s="28"/>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A120" s="43" t="s">
         <v>400</v>
       </c>
@@ -23861,7 +24046,7 @@
       <c r="AF120" s="28"/>
       <c r="AG120" s="28"/>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A121" s="43" t="s">
         <v>401</v>
       </c>
@@ -23948,7 +24133,7 @@
       <c r="AF121" s="28"/>
       <c r="AG121" s="28"/>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A122" s="43" t="s">
         <v>402</v>
       </c>
@@ -24035,7 +24220,7 @@
       <c r="AF122" s="28"/>
       <c r="AG122" s="28"/>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A123" s="43" t="s">
         <v>403</v>
       </c>
@@ -24122,7 +24307,7 @@
       <c r="AF123" s="28"/>
       <c r="AG123" s="28"/>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A124" s="43" t="s">
         <v>405</v>
       </c>
@@ -24209,7 +24394,7 @@
       <c r="AF124" s="28"/>
       <c r="AG124" s="28"/>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A125" s="43" t="s">
         <v>407</v>
       </c>
@@ -24296,7 +24481,7 @@
       <c r="AF125" s="28"/>
       <c r="AG125" s="28"/>
     </row>
-    <row r="126" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A126" s="56" t="s">
         <v>413</v>
       </c>
@@ -24383,7 +24568,7 @@
       <c r="AF126" s="28"/>
       <c r="AG126" s="28"/>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A127" s="43" t="s">
         <v>417</v>
       </c>
@@ -24470,7 +24655,7 @@
       <c r="AF127" s="28"/>
       <c r="AG127" s="28"/>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A128" s="43" t="s">
         <v>420</v>
       </c>
@@ -24557,7 +24742,7 @@
       <c r="AF128" s="28"/>
       <c r="AG128" s="28"/>
     </row>
-    <row r="129" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A129" s="43" t="s">
         <v>422</v>
       </c>
@@ -24644,7 +24829,7 @@
       <c r="AF129" s="28"/>
       <c r="AG129" s="28"/>
     </row>
-    <row r="130" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A130" s="43" t="s">
         <v>424</v>
       </c>
@@ -24731,7 +24916,7 @@
       <c r="AF130" s="28"/>
       <c r="AG130" s="28"/>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A131" s="43" t="s">
         <v>427</v>
       </c>
@@ -24818,7 +25003,7 @@
       <c r="AF131" s="28"/>
       <c r="AG131" s="28"/>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A132" s="43" t="s">
         <v>430</v>
       </c>
@@ -24905,7 +25090,7 @@
       <c r="AF132" s="28"/>
       <c r="AG132" s="28"/>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A133" s="43" t="s">
         <v>433</v>
       </c>
@@ -24992,7 +25177,7 @@
       <c r="AF133" s="28"/>
       <c r="AG133" s="28"/>
     </row>
-    <row r="134" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A134" s="43" t="s">
         <v>436</v>
       </c>
@@ -25079,7 +25264,7 @@
       <c r="AF134" s="28"/>
       <c r="AG134" s="28"/>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A135" s="43" t="s">
         <v>438</v>
       </c>
@@ -25166,7 +25351,7 @@
       <c r="AF135" s="28"/>
       <c r="AG135" s="28"/>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A136" s="43" t="s">
         <v>695</v>
       </c>
@@ -25253,7 +25438,7 @@
       <c r="AF136" s="28"/>
       <c r="AG136" s="28"/>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A137" s="43" t="s">
         <v>397</v>
       </c>
@@ -25340,7 +25525,7 @@
       <c r="AF137" s="28"/>
       <c r="AG137" s="28"/>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A138" s="43" t="s">
         <v>399</v>
       </c>
@@ -25427,7 +25612,7 @@
       <c r="AF138" s="28"/>
       <c r="AG138" s="28"/>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A139" s="43" t="s">
         <v>400</v>
       </c>
@@ -25514,7 +25699,7 @@
       <c r="AF139" s="28"/>
       <c r="AG139" s="28"/>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A140" s="43" t="s">
         <v>401</v>
       </c>
@@ -25601,7 +25786,7 @@
       <c r="AF140" s="28"/>
       <c r="AG140" s="28"/>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A141" s="43" t="s">
         <v>402</v>
       </c>
@@ -25688,7 +25873,7 @@
       <c r="AF141" s="28"/>
       <c r="AG141" s="28"/>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A142" s="43" t="s">
         <v>403</v>
       </c>
@@ -25775,7 +25960,7 @@
       <c r="AF142" s="28"/>
       <c r="AG142" s="28"/>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A143" s="43" t="s">
         <v>405</v>
       </c>
@@ -25862,7 +26047,7 @@
       <c r="AF143" s="28"/>
       <c r="AG143" s="28"/>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A144" s="43" t="s">
         <v>442</v>
       </c>
@@ -25949,7 +26134,7 @@
       <c r="AF144" s="28"/>
       <c r="AG144" s="28"/>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A145" s="43" t="s">
         <v>446</v>
       </c>
@@ -26036,7 +26221,7 @@
       <c r="AF145" s="28"/>
       <c r="AG145" s="28"/>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A146" s="43" t="s">
         <v>449</v>
       </c>
@@ -26123,7 +26308,7 @@
       <c r="AF146" s="28"/>
       <c r="AG146" s="28"/>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A147" s="43" t="s">
         <v>451</v>
       </c>
@@ -26210,7 +26395,7 @@
       <c r="AF147" s="28"/>
       <c r="AG147" s="28"/>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A148" s="43" t="s">
         <v>454</v>
       </c>
@@ -26297,7 +26482,7 @@
       <c r="AF148" s="28"/>
       <c r="AG148" s="28"/>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A149" s="43" t="s">
         <v>457</v>
       </c>
@@ -26384,7 +26569,7 @@
       <c r="AF149" s="28"/>
       <c r="AG149" s="28"/>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A150" s="43" t="s">
         <v>460</v>
       </c>
@@ -26471,7 +26656,7 @@
       <c r="AF150" s="28"/>
       <c r="AG150" s="28"/>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A151" s="43" t="s">
         <v>463</v>
       </c>
@@ -26558,7 +26743,7 @@
       <c r="AF151" s="28"/>
       <c r="AG151" s="28"/>
     </row>
-    <row r="152" spans="1:33" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="43" t="s">
         <v>466</v>
       </c>
@@ -26645,7 +26830,7 @@
       <c r="AF152" s="28"/>
       <c r="AG152" s="28"/>
     </row>
-    <row r="153" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="43" t="s">
         <v>469</v>
       </c>
@@ -26732,7 +26917,7 @@
       <c r="AF153" s="28"/>
       <c r="AG153" s="28"/>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A154" s="43" t="s">
         <v>509</v>
       </c>
@@ -26819,7 +27004,7 @@
       <c r="AF154" s="28"/>
       <c r="AG154" s="28"/>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A155" s="71" t="s">
         <v>539</v>
       </c>
@@ -26906,7 +27091,7 @@
       <c r="AF155" s="28"/>
       <c r="AG155" s="28"/>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A156" s="71" t="s">
         <v>543</v>
       </c>
@@ -26993,7 +27178,7 @@
       <c r="AF156" s="28"/>
       <c r="AG156" s="28"/>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A157" s="71" t="s">
         <v>546</v>
       </c>
@@ -27080,7 +27265,7 @@
       <c r="AF157" s="28"/>
       <c r="AG157" s="28"/>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A158" s="71" t="s">
         <v>549</v>
       </c>
@@ -27167,7 +27352,7 @@
       <c r="AF158" s="28"/>
       <c r="AG158" s="28"/>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A159" s="71" t="s">
         <v>551</v>
       </c>
@@ -27254,7 +27439,7 @@
       <c r="AF159" s="28"/>
       <c r="AG159" s="28"/>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A160" s="71" t="s">
         <v>553</v>
       </c>
@@ -27341,7 +27526,7 @@
       <c r="AF160" s="28"/>
       <c r="AG160" s="28"/>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A161" s="71" t="s">
         <v>555</v>
       </c>
@@ -27428,7 +27613,7 @@
       <c r="AF161" s="28"/>
       <c r="AG161" s="28"/>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A162" s="71" t="s">
         <v>557</v>
       </c>
@@ -27515,7 +27700,7 @@
       <c r="AF162" s="28"/>
       <c r="AG162" s="28"/>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A163" s="71" t="s">
         <v>559</v>
       </c>
@@ -27602,7 +27787,7 @@
       <c r="AF163" s="28"/>
       <c r="AG163" s="28"/>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A164" s="71" t="s">
         <v>562</v>
       </c>
@@ -27689,7 +27874,7 @@
       <c r="AF164" s="28"/>
       <c r="AG164" s="28"/>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A165" s="71" t="s">
         <v>565</v>
       </c>
@@ -27776,7 +27961,7 @@
       <c r="AF165" s="28"/>
       <c r="AG165" s="28"/>
     </row>
-    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A166" s="71" t="s">
         <v>568</v>
       </c>
@@ -27863,7 +28048,7 @@
       <c r="AF166" s="28"/>
       <c r="AG166" s="28"/>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A167" s="71" t="s">
         <v>571</v>
       </c>
@@ -27950,7 +28135,7 @@
       <c r="AF167" s="28"/>
       <c r="AG167" s="28"/>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A168" s="71" t="s">
         <v>574</v>
       </c>
@@ -28037,7 +28222,7 @@
       <c r="AF168" s="28"/>
       <c r="AG168" s="28"/>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A169" s="71" t="s">
         <v>577</v>
       </c>
@@ -28124,7 +28309,7 @@
       <c r="AF169" s="28"/>
       <c r="AG169" s="28"/>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A170" s="71" t="s">
         <v>579</v>
       </c>
@@ -28211,7 +28396,7 @@
       <c r="AF170" s="28"/>
       <c r="AG170" s="28"/>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A171" s="71" t="s">
         <v>581</v>
       </c>
@@ -28298,7 +28483,7 @@
       <c r="AF171" s="28"/>
       <c r="AG171" s="28"/>
     </row>
-    <row r="172" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A172" s="71" t="s">
         <v>584</v>
       </c>
@@ -28385,7 +28570,7 @@
       <c r="AF172" s="28"/>
       <c r="AG172" s="28"/>
     </row>
-    <row r="173" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A173" s="71" t="s">
         <v>873</v>
       </c>
@@ -28472,7 +28657,7 @@
       <c r="AF173" s="28"/>
       <c r="AG173" s="28"/>
     </row>
-    <row r="174" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A174" s="71" t="s">
         <v>876</v>
       </c>
@@ -28559,7 +28744,7 @@
       <c r="AF174" s="28"/>
       <c r="AG174" s="28"/>
     </row>
-    <row r="175" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A175" s="71" t="s">
         <v>879</v>
       </c>
@@ -28646,7 +28831,7 @@
       <c r="AF175" s="28"/>
       <c r="AG175" s="28"/>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A176" s="71" t="s">
         <v>175</v>
       </c>
@@ -28739,7 +28924,7 @@
       <c r="AF176" s="28"/>
       <c r="AG176" s="28"/>
     </row>
-    <row r="177" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A177" s="71" t="s">
         <v>179</v>
       </c>
@@ -28834,7 +29019,7 @@
       <c r="AF177" s="28"/>
       <c r="AG177" s="28"/>
     </row>
-    <row r="178" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A178" s="71" t="s">
         <v>182</v>
       </c>
@@ -28929,7 +29114,7 @@
       <c r="AF178" s="28"/>
       <c r="AG178" s="28"/>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A179" s="71" t="s">
         <v>185</v>
       </c>
@@ -29022,7 +29207,7 @@
       <c r="AF179" s="28"/>
       <c r="AG179" s="28"/>
     </row>
-    <row r="180" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A180" s="71" t="s">
         <v>188</v>
       </c>
@@ -29117,7 +29302,7 @@
       <c r="AF180" s="28"/>
       <c r="AG180" s="28"/>
     </row>
-    <row r="181" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A181" s="71" t="s">
         <v>190</v>
       </c>
@@ -29212,7 +29397,7 @@
       <c r="AF181" s="28"/>
       <c r="AG181" s="28"/>
     </row>
-    <row r="182" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A182" s="71" t="s">
         <v>193</v>
       </c>
@@ -29307,7 +29492,7 @@
       <c r="AF182" s="28"/>
       <c r="AG182" s="28"/>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A183" s="71" t="s">
         <v>196</v>
       </c>
@@ -29402,7 +29587,7 @@
       <c r="AF183" s="28"/>
       <c r="AG183" s="28"/>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A184" s="71" t="s">
         <v>607</v>
       </c>
@@ -29497,7 +29682,7 @@
       <c r="AF184" s="28"/>
       <c r="AG184" s="28"/>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A185" s="71" t="s">
         <v>611</v>
       </c>
@@ -29594,7 +29779,7 @@
       </c>
       <c r="AG185" s="28"/>
     </row>
-    <row r="186" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A186" s="71" t="s">
         <v>615</v>
       </c>
@@ -29691,7 +29876,7 @@
       </c>
       <c r="AG186" s="28"/>
     </row>
-    <row r="187" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A187" s="71" t="s">
         <v>621</v>
       </c>
@@ -29788,7 +29973,7 @@
       </c>
       <c r="AG187" s="28"/>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A188" s="71" t="s">
         <v>622</v>
       </c>
@@ -29885,7 +30070,7 @@
       <c r="AF188" s="28"/>
       <c r="AG188" s="28"/>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A189" s="71" t="s">
         <v>628</v>
       </c>
@@ -29980,7 +30165,7 @@
       <c r="AF189" s="28"/>
       <c r="AG189" s="28"/>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A190" s="71" t="s">
         <v>825</v>
       </c>
@@ -30075,7 +30260,7 @@
       <c r="AF190" s="28"/>
       <c r="AG190" s="28"/>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A191" s="71" t="s">
         <v>826</v>
       </c>
@@ -30170,7 +30355,7 @@
       <c r="AF191" s="28"/>
       <c r="AG191" s="28"/>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A192" s="71" t="s">
         <v>632</v>
       </c>
@@ -30265,7 +30450,7 @@
       <c r="AF192" s="28"/>
       <c r="AG192" s="28"/>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A193" s="71" t="s">
         <v>634</v>
       </c>
@@ -30360,7 +30545,7 @@
       <c r="AF193" s="28"/>
       <c r="AG193" s="28"/>
     </row>
-    <row r="194" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A194" s="71" t="s">
         <v>640</v>
       </c>
@@ -30455,7 +30640,7 @@
       <c r="AF194" s="28"/>
       <c r="AG194" s="28"/>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A195" s="71" t="s">
         <v>641</v>
       </c>
@@ -30550,7 +30735,7 @@
       <c r="AF195" s="28"/>
       <c r="AG195" s="28"/>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A196" s="71" t="s">
         <v>646</v>
       </c>
@@ -30645,7 +30830,7 @@
       <c r="AF196" s="28"/>
       <c r="AG196" s="28"/>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A197" s="71" t="s">
         <v>648</v>
       </c>
@@ -30740,7 +30925,7 @@
       <c r="AF197" s="28"/>
       <c r="AG197" s="28"/>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A198" s="71" t="s">
         <v>654</v>
       </c>
@@ -30835,7 +31020,7 @@
       <c r="AF198" s="28"/>
       <c r="AG198" s="28"/>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A199" s="71" t="s">
         <v>657</v>
       </c>
@@ -30930,7 +31115,7 @@
       <c r="AF199" s="28"/>
       <c r="AG199" s="28"/>
     </row>
-    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A200" s="71" t="s">
         <v>658</v>
       </c>
@@ -31025,7 +31210,7 @@
       <c r="AF200" s="28"/>
       <c r="AG200" s="28"/>
     </row>
-    <row r="201" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A201" s="71" t="s">
         <v>663</v>
       </c>
@@ -31120,7 +31305,7 @@
       <c r="AF201" s="28"/>
       <c r="AG201" s="28"/>
     </row>
-    <row r="202" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A202" s="71" t="s">
         <v>668</v>
       </c>
@@ -31215,7 +31400,7 @@
       <c r="AF202" s="28"/>
       <c r="AG202" s="28"/>
     </row>
-    <row r="203" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A203" s="71" t="s">
         <v>669</v>
       </c>
@@ -31310,7 +31495,7 @@
       <c r="AF203" s="28"/>
       <c r="AG203" s="28"/>
     </row>
-    <row r="204" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A204" s="71" t="s">
         <v>855</v>
       </c>
@@ -31405,7 +31590,7 @@
       <c r="AF204" s="28"/>
       <c r="AG204" s="28"/>
     </row>
-    <row r="205" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A205" s="71" t="s">
         <v>858</v>
       </c>
@@ -31500,7 +31685,7 @@
       <c r="AF205" s="28"/>
       <c r="AG205" s="28"/>
     </row>
-    <row r="206" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A206" s="71" t="s">
         <v>859</v>
       </c>
@@ -31595,7 +31780,7 @@
       <c r="AF206" s="28"/>
       <c r="AG206" s="28"/>
     </row>
-    <row r="207" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A207" s="71" t="s">
         <v>710</v>
       </c>
@@ -31690,7 +31875,7 @@
       <c r="AF207" s="28"/>
       <c r="AG207" s="28"/>
     </row>
-    <row r="208" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A208" s="71" t="s">
         <v>713</v>
       </c>
@@ -31785,7 +31970,7 @@
       <c r="AF208" s="28"/>
       <c r="AG208" s="28"/>
     </row>
-    <row r="209" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A209" s="71" t="s">
         <v>715</v>
       </c>
@@ -31880,7 +32065,7 @@
       <c r="AF209" s="28"/>
       <c r="AG209" s="28"/>
     </row>
-    <row r="210" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A210" s="71" t="s">
         <v>753</v>
       </c>
@@ -31975,7 +32160,7 @@
       <c r="AF210" s="28"/>
       <c r="AG210" s="28"/>
     </row>
-    <row r="211" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A211" s="71" t="s">
         <v>842</v>
       </c>
@@ -32070,7 +32255,7 @@
       <c r="AF211" s="28"/>
       <c r="AG211" s="28"/>
     </row>
-    <row r="212" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A212" s="71" t="s">
         <v>843</v>
       </c>
@@ -32165,7 +32350,7 @@
       <c r="AF212" s="28"/>
       <c r="AG212" s="28"/>
     </row>
-    <row r="213" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A213" s="71" t="s">
         <v>718</v>
       </c>
@@ -32260,7 +32445,7 @@
       <c r="AF213" s="28"/>
       <c r="AG213" s="28"/>
     </row>
-    <row r="214" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A214" s="71" t="s">
         <v>724</v>
       </c>
@@ -32355,7 +32540,7 @@
       <c r="AF214" s="28"/>
       <c r="AG214" s="28"/>
     </row>
-    <row r="215" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A215" s="71" t="s">
         <v>725</v>
       </c>
@@ -32450,7 +32635,7 @@
       <c r="AF215" s="28"/>
       <c r="AG215" s="28"/>
     </row>
-    <row r="216" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A216" s="71" t="s">
         <v>730</v>
       </c>
@@ -32545,7 +32730,7 @@
       <c r="AF216" s="28"/>
       <c r="AG216" s="28"/>
     </row>
-    <row r="217" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A217" s="71" t="s">
         <v>731</v>
       </c>
@@ -32640,7 +32825,7 @@
       <c r="AF217" s="28"/>
       <c r="AG217" s="28"/>
     </row>
-    <row r="218" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A218" s="71" t="s">
         <v>732</v>
       </c>
@@ -32735,7 +32920,7 @@
       <c r="AF218" s="28"/>
       <c r="AG218" s="28"/>
     </row>
-    <row r="219" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A219" s="71" t="s">
         <v>737</v>
       </c>
@@ -32830,7 +33015,7 @@
       <c r="AF219" s="28"/>
       <c r="AG219" s="28"/>
     </row>
-    <row r="220" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A220" s="71" t="s">
         <v>740</v>
       </c>
@@ -32925,7 +33110,7 @@
       <c r="AF220" s="28"/>
       <c r="AG220" s="28"/>
     </row>
-    <row r="221" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A221" s="71" t="s">
         <v>745</v>
       </c>
@@ -33020,7 +33205,7 @@
       <c r="AF221" s="28"/>
       <c r="AG221" s="28"/>
     </row>
-    <row r="222" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A222" s="71" t="s">
         <v>748</v>
       </c>
@@ -33115,7 +33300,7 @@
       <c r="AF222" s="28"/>
       <c r="AG222" s="28"/>
     </row>
-    <row r="223" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A223" s="71" t="s">
         <v>749</v>
       </c>
@@ -33210,7 +33395,7 @@
       <c r="AF223" s="28"/>
       <c r="AG223" s="28"/>
     </row>
-    <row r="224" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A224" s="71" t="s">
         <v>755</v>
       </c>
@@ -33305,7 +33490,7 @@
       <c r="AF224" s="28"/>
       <c r="AG224" s="28"/>
     </row>
-    <row r="225" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A225" s="71" t="s">
         <v>767</v>
       </c>
@@ -33400,7 +33585,7 @@
       <c r="AF225" s="28"/>
       <c r="AG225" s="28"/>
     </row>
-    <row r="226" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A226" s="71" t="s">
         <v>772</v>
       </c>
@@ -33495,7 +33680,7 @@
       <c r="AF226" s="28"/>
       <c r="AG226" s="28"/>
     </row>
-    <row r="227" spans="1:33" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:33" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="71" t="s">
         <v>777</v>
       </c>
@@ -33590,7 +33775,7 @@
       <c r="AF227" s="28"/>
       <c r="AG227" s="28"/>
     </row>
-    <row r="228" spans="1:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:33" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="71" t="s">
         <v>779</v>
       </c>
@@ -33685,7 +33870,7 @@
       <c r="AF228" s="28"/>
       <c r="AG228" s="28"/>
     </row>
-    <row r="229" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A229" s="71" t="s">
         <v>781</v>
       </c>
@@ -33780,7 +33965,7 @@
       <c r="AF229" s="28"/>
       <c r="AG229" s="28"/>
     </row>
-    <row r="230" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A230" s="71" t="s">
         <v>786</v>
       </c>
@@ -33875,7 +34060,7 @@
       <c r="AF230" s="28"/>
       <c r="AG230" s="28"/>
     </row>
-    <row r="231" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="71" t="s">
         <v>788</v>
       </c>
@@ -33970,7 +34155,7 @@
       <c r="AF231" s="28"/>
       <c r="AG231" s="28"/>
     </row>
-    <row r="232" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="71" t="s">
         <v>792</v>
       </c>
@@ -34065,7 +34250,7 @@
       <c r="AF232" s="28"/>
       <c r="AG232" s="28"/>
     </row>
-    <row r="233" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A233" s="71" t="s">
         <v>797</v>
       </c>
@@ -34160,7 +34345,7 @@
       <c r="AF233" s="28"/>
       <c r="AG233" s="28"/>
     </row>
-    <row r="234" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="71" t="s">
         <v>800</v>
       </c>
@@ -34255,7 +34440,7 @@
       <c r="AF234" s="28"/>
       <c r="AG234" s="28"/>
     </row>
-    <row r="235" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="71" t="s">
         <v>801</v>
       </c>
@@ -34350,7 +34535,7 @@
       <c r="AF235" s="28"/>
       <c r="AG235" s="28"/>
     </row>
-    <row r="236" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="71" t="s">
         <v>806</v>
       </c>
@@ -34445,7 +34630,7 @@
       <c r="AF236" s="28"/>
       <c r="AG236" s="28"/>
     </row>
-    <row r="237" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="71" t="s">
         <v>882</v>
       </c>
@@ -34540,7 +34725,7 @@
       <c r="AF237" s="28"/>
       <c r="AG237" s="28"/>
     </row>
-    <row r="238" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="71" t="s">
         <v>883</v>
       </c>
@@ -34635,7 +34820,7 @@
       <c r="AF238" s="28"/>
       <c r="AG238" s="28"/>
     </row>
-    <row r="239" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="71" t="s">
         <v>884</v>
       </c>
@@ -34730,7 +34915,7 @@
       <c r="AF239" s="28"/>
       <c r="AG239" s="28"/>
     </row>
-    <row r="240" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="71" t="s">
         <v>846</v>
       </c>
@@ -34825,7 +35010,7 @@
       <c r="AF240" s="28"/>
       <c r="AG240" s="28"/>
     </row>
-    <row r="241" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="71" t="s">
         <v>850</v>
       </c>
@@ -34920,7 +35105,7 @@
       <c r="AF241" s="28"/>
       <c r="AG241" s="28"/>
     </row>
-    <row r="242" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="71" t="s">
         <v>816</v>
       </c>
@@ -35015,7 +35200,7 @@
       <c r="AF242" s="28"/>
       <c r="AG242" s="28"/>
     </row>
-    <row r="243" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="71" t="s">
         <v>820</v>
       </c>
@@ -35110,7 +35295,7 @@
       <c r="AF243" s="28"/>
       <c r="AG243" s="28"/>
     </row>
-    <row r="244" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="71" t="s">
         <v>822</v>
       </c>
@@ -35205,7 +35390,7 @@
       <c r="AF244" s="28"/>
       <c r="AG244" s="28"/>
     </row>
-    <row r="245" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="71" t="s">
         <v>835</v>
       </c>
@@ -35300,7 +35485,7 @@
       <c r="AF245" s="28"/>
       <c r="AG245" s="28"/>
     </row>
-    <row r="246" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="71" t="s">
         <v>837</v>
       </c>
@@ -35395,7 +35580,7 @@
       <c r="AF246" s="28"/>
       <c r="AG246" s="28"/>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A247" s="28" t="s">
         <v>863</v>
       </c>
@@ -35490,7 +35675,7 @@
       <c r="AF247" s="28"/>
       <c r="AG247" s="28"/>
     </row>
-    <row r="248" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A248" s="28" t="s">
         <v>870</v>
       </c>
@@ -35585,7 +35770,7 @@
       <c r="AF248" s="28"/>
       <c r="AG248" s="28"/>
     </row>
-    <row r="249" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A249" s="28" t="s">
         <v>889</v>
       </c>
@@ -35680,7 +35865,7 @@
       <c r="AF249" s="28"/>
       <c r="AG249" s="28"/>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A250" s="28" t="s">
         <v>916</v>
       </c>
@@ -35775,7 +35960,7 @@
       <c r="AF250" s="28"/>
       <c r="AG250" s="28"/>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A251" s="28" t="s">
         <v>923</v>
       </c>
@@ -35870,7 +36055,7 @@
       <c r="AF251" s="28"/>
       <c r="AG251" s="28"/>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A252" s="28" t="s">
         <v>934</v>
       </c>
@@ -35965,7 +36150,7 @@
       <c r="AF252" s="28"/>
       <c r="AG252" s="28"/>
     </row>
-    <row r="253" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A253" s="28" t="s">
         <v>939</v>
       </c>
@@ -36060,7 +36245,7 @@
       <c r="AF253" s="28"/>
       <c r="AG253" s="28"/>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A254" s="28" t="s">
         <v>943</v>
       </c>
@@ -36155,7 +36340,7 @@
       <c r="AF254" s="28"/>
       <c r="AG254" s="28"/>
     </row>
-    <row r="255" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A255" s="28" t="s">
         <v>946</v>
       </c>
@@ -36250,7 +36435,7 @@
       <c r="AF255" s="28"/>
       <c r="AG255" s="28"/>
     </row>
-    <row r="256" spans="1:33" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:33" ht="18" x14ac:dyDescent="0.35">
       <c r="A256" s="83" t="s">
         <v>950</v>
       </c>
@@ -36345,7 +36530,7 @@
       <c r="AF256" s="28"/>
       <c r="AG256" s="28"/>
     </row>
-    <row r="257" spans="1:33" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:33" ht="18" x14ac:dyDescent="0.35">
       <c r="A257" s="83" t="s">
         <v>954</v>
       </c>
@@ -36440,7 +36625,7 @@
       <c r="AF257" s="28"/>
       <c r="AG257" s="28"/>
     </row>
-    <row r="258" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A258" s="28" t="s">
         <v>958</v>
       </c>
@@ -36495,7 +36680,7 @@
       <c r="R258" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="S258" s="100" t="s">
+      <c r="S258" s="84" t="s">
         <v>965</v>
       </c>
       <c r="T258" s="28" t="s">
@@ -36538,6 +36723,410 @@
         <v>961</v>
       </c>
       <c r="AG258" s="28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="259" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>969</v>
+      </c>
+      <c r="B259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE259" s="28" t="s">
+        <v>960</v>
+      </c>
+      <c r="AF259" s="28" t="s">
+        <v>961</v>
+      </c>
+      <c r="AG259" s="28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="260" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>973</v>
+      </c>
+      <c r="B260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD260" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE260" s="28" t="s">
+        <v>960</v>
+      </c>
+      <c r="AF260" s="28" t="s">
+        <v>961</v>
+      </c>
+      <c r="AG260" s="28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="261" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>976</v>
+      </c>
+      <c r="B261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD261" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE261" s="28" t="s">
+        <v>960</v>
+      </c>
+      <c r="AF261" s="28" t="s">
+        <v>961</v>
+      </c>
+      <c r="AG261" s="28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="262" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>979</v>
+      </c>
+      <c r="B262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD262" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE262" s="28" t="s">
+        <v>960</v>
+      </c>
+      <c r="AF262" s="28" t="s">
+        <v>961</v>
+      </c>
+      <c r="AG262" s="28" t="s">
         <v>131</v>
       </c>
     </row>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\ZlaataQAsever1\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever22\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DB4FB4-FF38-4030-B325-8FE1D00C9123}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F339B353-5A4D-41C9-842C-C755647C05BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9379" uniqueCount="980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9422" uniqueCount="985">
   <si>
     <t>S.No</t>
   </si>
@@ -2966,6 +2966,21 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_FN_04</t>
+  </si>
+  <si>
+    <t>Estimate Delivery</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Verify that Estimate delivery date functionality is working fine</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Estimate_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Estimate_01</t>
   </si>
 </sst>
 </file>
@@ -3608,6 +3623,24 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3634,24 +3667,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4455,7 +4470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z285"/>
+  <dimension ref="A1:Z287"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -5206,18 +5221,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="97"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="88"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -5604,18 +5619,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="98" t="s">
+      <c r="A37" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="99"/>
-      <c r="C37" s="99"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="100"/>
+      <c r="B37" s="90"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="90"/>
+      <c r="I37" s="90"/>
+      <c r="J37" s="91"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -6162,18 +6177,18 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="98" t="s">
+      <c r="A55" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="99"/>
-      <c r="C55" s="99"/>
-      <c r="D55" s="99"/>
-      <c r="E55" s="99"/>
-      <c r="F55" s="99"/>
-      <c r="G55" s="99"/>
-      <c r="H55" s="99"/>
-      <c r="I55" s="99"/>
-      <c r="J55" s="100"/>
+      <c r="B55" s="90"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
+      <c r="H55" s="90"/>
+      <c r="I55" s="90"/>
+      <c r="J55" s="91"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
@@ -6496,18 +6511,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="98" t="s">
+      <c r="A66" s="89" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="99"/>
-      <c r="C66" s="99"/>
-      <c r="D66" s="99"/>
-      <c r="E66" s="99"/>
-      <c r="F66" s="99"/>
-      <c r="G66" s="99"/>
-      <c r="H66" s="99"/>
-      <c r="I66" s="99"/>
-      <c r="J66" s="100"/>
+      <c r="B66" s="90"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="90"/>
+      <c r="E66" s="90"/>
+      <c r="F66" s="90"/>
+      <c r="G66" s="90"/>
+      <c r="H66" s="90"/>
+      <c r="I66" s="90"/>
+      <c r="J66" s="91"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
@@ -6862,18 +6877,18 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="98" t="s">
+      <c r="A78" s="89" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="99"/>
-      <c r="C78" s="99"/>
-      <c r="D78" s="99"/>
-      <c r="E78" s="99"/>
-      <c r="F78" s="99"/>
-      <c r="G78" s="99"/>
-      <c r="H78" s="99"/>
-      <c r="I78" s="99"/>
-      <c r="J78" s="100"/>
+      <c r="B78" s="90"/>
+      <c r="C78" s="90"/>
+      <c r="D78" s="90"/>
+      <c r="E78" s="90"/>
+      <c r="F78" s="90"/>
+      <c r="G78" s="90"/>
+      <c r="H78" s="90"/>
+      <c r="I78" s="90"/>
+      <c r="J78" s="91"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
@@ -7740,18 +7755,18 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="86" t="s">
+      <c r="A106" s="92" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="86"/>
-      <c r="C106" s="86"/>
-      <c r="D106" s="86"/>
-      <c r="E106" s="86"/>
-      <c r="F106" s="86"/>
-      <c r="G106" s="86"/>
-      <c r="H106" s="86"/>
-      <c r="I106" s="86"/>
-      <c r="J106" s="86"/>
+      <c r="B106" s="92"/>
+      <c r="C106" s="92"/>
+      <c r="D106" s="92"/>
+      <c r="E106" s="92"/>
+      <c r="F106" s="92"/>
+      <c r="G106" s="92"/>
+      <c r="H106" s="92"/>
+      <c r="I106" s="92"/>
+      <c r="J106" s="92"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -8244,18 +8259,18 @@
       <c r="X120" s="52"/>
     </row>
     <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="87" t="s">
+      <c r="A121" s="93" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="87"/>
-      <c r="C121" s="87"/>
-      <c r="D121" s="87"/>
-      <c r="E121" s="87"/>
-      <c r="F121" s="87"/>
-      <c r="G121" s="87"/>
-      <c r="H121" s="87"/>
-      <c r="I121" s="87"/>
-      <c r="J121" s="87"/>
+      <c r="B121" s="93"/>
+      <c r="C121" s="93"/>
+      <c r="D121" s="93"/>
+      <c r="E121" s="93"/>
+      <c r="F121" s="93"/>
+      <c r="G121" s="93"/>
+      <c r="H121" s="93"/>
+      <c r="I121" s="93"/>
+      <c r="J121" s="93"/>
       <c r="K121" s="51"/>
       <c r="L121" s="52"/>
       <c r="M121" s="52"/>
@@ -8318,18 +8333,18 @@
       <c r="X122" s="52"/>
     </row>
     <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="87" t="s">
+      <c r="A123" s="93" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="87"/>
-      <c r="C123" s="87"/>
-      <c r="D123" s="87"/>
-      <c r="E123" s="87"/>
-      <c r="F123" s="87"/>
-      <c r="G123" s="87"/>
-      <c r="H123" s="87"/>
-      <c r="I123" s="87"/>
-      <c r="J123" s="87"/>
+      <c r="B123" s="93"/>
+      <c r="C123" s="93"/>
+      <c r="D123" s="93"/>
+      <c r="E123" s="93"/>
+      <c r="F123" s="93"/>
+      <c r="G123" s="93"/>
+      <c r="H123" s="93"/>
+      <c r="I123" s="93"/>
+      <c r="J123" s="93"/>
       <c r="K123" s="51"/>
       <c r="L123" s="52"/>
       <c r="M123" s="52"/>
@@ -8392,18 +8407,18 @@
       <c r="X124" s="52"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="87" t="s">
+      <c r="A125" s="93" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="87"/>
-      <c r="C125" s="87"/>
-      <c r="D125" s="87"/>
-      <c r="E125" s="87"/>
-      <c r="F125" s="87"/>
-      <c r="G125" s="87"/>
-      <c r="H125" s="87"/>
-      <c r="I125" s="87"/>
-      <c r="J125" s="87"/>
+      <c r="B125" s="93"/>
+      <c r="C125" s="93"/>
+      <c r="D125" s="93"/>
+      <c r="E125" s="93"/>
+      <c r="F125" s="93"/>
+      <c r="G125" s="93"/>
+      <c r="H125" s="93"/>
+      <c r="I125" s="93"/>
+      <c r="J125" s="93"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -8728,18 +8743,18 @@
       <c r="X132" s="52"/>
     </row>
     <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="87" t="s">
+      <c r="A133" s="93" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="87"/>
-      <c r="C133" s="87"/>
-      <c r="D133" s="88"/>
-      <c r="E133" s="88"/>
-      <c r="F133" s="88"/>
-      <c r="G133" s="88"/>
-      <c r="H133" s="88"/>
-      <c r="I133" s="88"/>
-      <c r="J133" s="88"/>
+      <c r="B133" s="93"/>
+      <c r="C133" s="93"/>
+      <c r="D133" s="94"/>
+      <c r="E133" s="94"/>
+      <c r="F133" s="94"/>
+      <c r="G133" s="94"/>
+      <c r="H133" s="94"/>
+      <c r="I133" s="94"/>
+      <c r="J133" s="94"/>
       <c r="K133" s="52"/>
       <c r="L133" s="52"/>
       <c r="M133" s="52"/>
@@ -9234,18 +9249,18 @@
       <c r="X144" s="52"/>
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="92" t="s">
+      <c r="A145" s="98" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="93"/>
-      <c r="C145" s="93"/>
-      <c r="D145" s="93"/>
-      <c r="E145" s="93"/>
-      <c r="F145" s="93"/>
-      <c r="G145" s="93"/>
-      <c r="H145" s="93"/>
-      <c r="I145" s="93"/>
-      <c r="J145" s="94"/>
+      <c r="B145" s="99"/>
+      <c r="C145" s="99"/>
+      <c r="D145" s="99"/>
+      <c r="E145" s="99"/>
+      <c r="F145" s="99"/>
+      <c r="G145" s="99"/>
+      <c r="H145" s="99"/>
+      <c r="I145" s="99"/>
+      <c r="J145" s="100"/>
       <c r="K145" s="52"/>
       <c r="L145" s="52"/>
       <c r="M145" s="52"/>
@@ -9692,18 +9707,18 @@
       <c r="Z155" s="52"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="87" t="s">
+      <c r="A156" s="93" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="87"/>
-      <c r="C156" s="87"/>
-      <c r="D156" s="87"/>
-      <c r="E156" s="87"/>
-      <c r="F156" s="87"/>
-      <c r="G156" s="87"/>
-      <c r="H156" s="87"/>
-      <c r="I156" s="87"/>
-      <c r="J156" s="87"/>
+      <c r="B156" s="93"/>
+      <c r="C156" s="93"/>
+      <c r="D156" s="93"/>
+      <c r="E156" s="93"/>
+      <c r="F156" s="93"/>
+      <c r="G156" s="93"/>
+      <c r="H156" s="93"/>
+      <c r="I156" s="93"/>
+      <c r="J156" s="93"/>
       <c r="K156" s="52"/>
       <c r="L156" s="52"/>
       <c r="M156" s="52"/>
@@ -9770,18 +9785,18 @@
       <c r="Z157" s="52"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="87" t="s">
+      <c r="A158" s="93" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="87"/>
-      <c r="C158" s="87"/>
-      <c r="D158" s="87"/>
-      <c r="E158" s="87"/>
-      <c r="F158" s="87"/>
-      <c r="G158" s="87"/>
-      <c r="H158" s="87"/>
-      <c r="I158" s="87"/>
-      <c r="J158" s="87"/>
+      <c r="B158" s="93"/>
+      <c r="C158" s="93"/>
+      <c r="D158" s="93"/>
+      <c r="E158" s="93"/>
+      <c r="F158" s="93"/>
+      <c r="G158" s="93"/>
+      <c r="H158" s="93"/>
+      <c r="I158" s="93"/>
+      <c r="J158" s="93"/>
       <c r="K158" s="52"/>
       <c r="L158" s="52"/>
       <c r="M158" s="52"/>
@@ -10616,18 +10631,18 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="87" t="s">
+      <c r="A180" s="93" t="s">
         <v>707</v>
       </c>
-      <c r="B180" s="87"/>
-      <c r="C180" s="87"/>
+      <c r="B180" s="93"/>
+      <c r="C180" s="93"/>
       <c r="D180" s="85"/>
-      <c r="E180" s="87"/>
-      <c r="F180" s="87"/>
-      <c r="G180" s="87"/>
-      <c r="H180" s="87"/>
-      <c r="I180" s="87"/>
-      <c r="J180" s="87"/>
+      <c r="E180" s="93"/>
+      <c r="F180" s="93"/>
+      <c r="G180" s="93"/>
+      <c r="H180" s="93"/>
+      <c r="I180" s="93"/>
+      <c r="J180" s="93"/>
     </row>
     <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="62">
@@ -10918,18 +10933,18 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="89" t="s">
+      <c r="A190" s="95" t="s">
         <v>609</v>
       </c>
-      <c r="B190" s="90"/>
-      <c r="C190" s="90"/>
-      <c r="D190" s="90"/>
-      <c r="E190" s="90"/>
-      <c r="F190" s="90"/>
-      <c r="G190" s="90"/>
-      <c r="H190" s="90"/>
-      <c r="I190" s="90"/>
-      <c r="J190" s="91"/>
+      <c r="B190" s="96"/>
+      <c r="C190" s="96"/>
+      <c r="D190" s="96"/>
+      <c r="E190" s="96"/>
+      <c r="F190" s="96"/>
+      <c r="G190" s="96"/>
+      <c r="H190" s="96"/>
+      <c r="I190" s="96"/>
+      <c r="J190" s="97"/>
     </row>
     <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="62">
@@ -13647,8 +13662,70 @@
         <v>13</v>
       </c>
     </row>
+    <row r="286" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="85" t="s">
+        <v>980</v>
+      </c>
+      <c r="B286" s="85"/>
+      <c r="C286" s="85"/>
+      <c r="D286" s="85"/>
+      <c r="E286" s="85"/>
+      <c r="F286" s="85"/>
+      <c r="G286" s="85"/>
+      <c r="H286" s="85"/>
+      <c r="I286" s="85"/>
+      <c r="J286" s="85"/>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A287" s="77">
+        <v>1</v>
+      </c>
+      <c r="B287" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C287" s="71" t="s">
+        <v>983</v>
+      </c>
+      <c r="D287" s="78" t="s">
+        <v>982</v>
+      </c>
+      <c r="E287" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F287" s="71" t="s">
+        <v>984</v>
+      </c>
+      <c r="G287" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="H287" s="77" t="s">
+        <v>981</v>
+      </c>
+      <c r="I287" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="J287" s="77" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
+    <mergeCell ref="A286:J286"/>
+    <mergeCell ref="A273:J273"/>
+    <mergeCell ref="A270:J270"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="A121:J121"/>
+    <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A203:J203"/>
+    <mergeCell ref="A198:J198"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A190:J190"/>
+    <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A158:J158"/>
+    <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A267:J267"/>
     <mergeCell ref="A281:J281"/>
     <mergeCell ref="A279:J279"/>
     <mergeCell ref="A265:J265"/>
@@ -13665,21 +13742,6 @@
     <mergeCell ref="A240:J240"/>
     <mergeCell ref="A238:J238"/>
     <mergeCell ref="A276:J276"/>
-    <mergeCell ref="A273:J273"/>
-    <mergeCell ref="A270:J270"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="A121:J121"/>
-    <mergeCell ref="A123:J123"/>
-    <mergeCell ref="A125:J125"/>
-    <mergeCell ref="A203:J203"/>
-    <mergeCell ref="A198:J198"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="A190:J190"/>
-    <mergeCell ref="A145:J145"/>
-    <mergeCell ref="A156:J156"/>
-    <mergeCell ref="A158:J158"/>
-    <mergeCell ref="A180:J180"/>
-    <mergeCell ref="A267:J267"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13777,7 +13839,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG262"/>
+  <dimension ref="A1:AG263"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -37128,6 +37190,107 @@
       </c>
       <c r="AG262" s="28" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="263" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>984</v>
+      </c>
+      <c r="B263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF263" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG263" s="28" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever22\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataQAsever070526\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F339B353-5A4D-41C9-842C-C755647C05BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCC2C29-5F85-43B7-BBCA-AE2B92B03440}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9422" uniqueCount="985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9464" uniqueCount="988">
   <si>
     <t>S.No</t>
   </si>
@@ -2981,6 +2981,15 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_Estimate_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Estimate_02</t>
+  </si>
+  <si>
+    <t>Verify that Estimate delivery date functionality is working fine two Product</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Estimate_02</t>
   </si>
 </sst>
 </file>
@@ -3623,24 +3632,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3667,6 +3658,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4470,21 +4479,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z287"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Z288"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" customWidth="1"/>
-    <col min="4" max="4" width="118.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
+    <col min="4" max="4" width="118.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4516,7 +4525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="28">
         <v>1</v>
       </c>
@@ -4548,7 +4557,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>2</v>
       </c>
@@ -4580,7 +4589,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>3</v>
       </c>
@@ -4612,7 +4621,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
         <v>4</v>
       </c>
@@ -4644,7 +4653,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="28">
         <v>5</v>
       </c>
@@ -4676,7 +4685,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="28">
         <v>6</v>
       </c>
@@ -4708,7 +4717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="28">
         <v>7</v>
       </c>
@@ -4740,7 +4749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="28">
         <v>8</v>
       </c>
@@ -4772,7 +4781,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="28">
         <v>9</v>
       </c>
@@ -4804,7 +4813,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="28">
         <v>10</v>
       </c>
@@ -4836,7 +4845,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="28">
         <v>11</v>
       </c>
@@ -4868,7 +4877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="28">
         <v>12</v>
       </c>
@@ -4900,7 +4909,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="28">
         <v>13</v>
       </c>
@@ -4932,7 +4941,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="28">
         <v>14</v>
       </c>
@@ -4964,7 +4973,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="28">
         <v>15</v>
       </c>
@@ -4996,7 +5005,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="28">
         <v>16</v>
       </c>
@@ -5028,7 +5037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="28">
         <v>17</v>
       </c>
@@ -5060,7 +5069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="28">
         <v>18</v>
       </c>
@@ -5092,7 +5101,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="28">
         <v>19</v>
       </c>
@@ -5124,7 +5133,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="28">
         <v>20</v>
       </c>
@@ -5156,7 +5165,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="28">
         <v>21</v>
       </c>
@@ -5188,7 +5197,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>22</v>
       </c>
@@ -5220,21 +5229,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="86" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="87"/>
-      <c r="C24" s="87"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="88"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="97"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
         <v>1</v>
       </c>
@@ -5266,7 +5275,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>2</v>
       </c>
@@ -5298,7 +5307,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>3</v>
       </c>
@@ -5330,7 +5339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>4</v>
       </c>
@@ -5362,7 +5371,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>5</v>
       </c>
@@ -5394,7 +5403,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>6</v>
       </c>
@@ -5426,7 +5435,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>7</v>
       </c>
@@ -5458,7 +5467,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>8</v>
       </c>
@@ -5490,7 +5499,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>9</v>
       </c>
@@ -5522,7 +5531,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>10</v>
       </c>
@@ -5554,7 +5563,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>11</v>
       </c>
@@ -5586,7 +5595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>12</v>
       </c>
@@ -5618,21 +5627,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="89" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="98" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="90"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="90"/>
-      <c r="I37" s="90"/>
-      <c r="J37" s="91"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="100"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>1</v>
       </c>
@@ -5664,7 +5673,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -5696,7 +5705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>3</v>
       </c>
@@ -5728,7 +5737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>4</v>
       </c>
@@ -5760,7 +5769,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>5</v>
       </c>
@@ -5792,7 +5801,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>6</v>
       </c>
@@ -5824,7 +5833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>7</v>
       </c>
@@ -5856,7 +5865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>8</v>
       </c>
@@ -5888,7 +5897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>9</v>
       </c>
@@ -5920,7 +5929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>10</v>
       </c>
@@ -5952,7 +5961,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>11</v>
       </c>
@@ -5984,7 +5993,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>12</v>
       </c>
@@ -6016,7 +6025,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>13</v>
       </c>
@@ -6048,7 +6057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>14</v>
       </c>
@@ -6080,7 +6089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>15</v>
       </c>
@@ -6112,7 +6121,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>16</v>
       </c>
@@ -6144,7 +6153,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>16</v>
       </c>
@@ -6176,21 +6185,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="89" t="s">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="98" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="90"/>
-      <c r="C55" s="90"/>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
-      <c r="H55" s="90"/>
-      <c r="I55" s="90"/>
-      <c r="J55" s="91"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B55" s="99"/>
+      <c r="C55" s="99"/>
+      <c r="D55" s="99"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="99"/>
+      <c r="G55" s="99"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="99"/>
+      <c r="J55" s="100"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="25">
         <v>1</v>
       </c>
@@ -6222,7 +6231,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="25">
         <v>2</v>
       </c>
@@ -6254,7 +6263,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="25">
         <v>3</v>
       </c>
@@ -6286,7 +6295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="25">
         <v>4</v>
       </c>
@@ -6318,7 +6327,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="25">
         <v>5</v>
       </c>
@@ -6350,7 +6359,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="25">
         <v>6</v>
       </c>
@@ -6382,7 +6391,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="25">
         <v>7</v>
       </c>
@@ -6414,7 +6423,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="25">
         <v>8</v>
       </c>
@@ -6446,7 +6455,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="25">
         <v>9</v>
       </c>
@@ -6478,7 +6487,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="25">
         <v>10</v>
       </c>
@@ -6510,21 +6519,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="89" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="98" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="90"/>
-      <c r="C66" s="90"/>
-      <c r="D66" s="90"/>
-      <c r="E66" s="90"/>
-      <c r="F66" s="90"/>
-      <c r="G66" s="90"/>
-      <c r="H66" s="90"/>
-      <c r="I66" s="90"/>
-      <c r="J66" s="91"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B66" s="99"/>
+      <c r="C66" s="99"/>
+      <c r="D66" s="99"/>
+      <c r="E66" s="99"/>
+      <c r="F66" s="99"/>
+      <c r="G66" s="99"/>
+      <c r="H66" s="99"/>
+      <c r="I66" s="99"/>
+      <c r="J66" s="100"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="25">
         <v>1</v>
       </c>
@@ -6556,7 +6565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="25">
         <v>2</v>
       </c>
@@ -6588,7 +6597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="25">
         <v>3</v>
       </c>
@@ -6620,7 +6629,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="25">
         <v>4</v>
       </c>
@@ -6652,7 +6661,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="25">
         <v>5</v>
       </c>
@@ -6684,7 +6693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="25">
         <v>6</v>
       </c>
@@ -6716,7 +6725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="25">
         <v>7</v>
       </c>
@@ -6748,7 +6757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="25">
         <v>8</v>
       </c>
@@ -6780,7 +6789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="25">
         <v>9</v>
       </c>
@@ -6812,7 +6821,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="25">
         <v>10</v>
       </c>
@@ -6844,7 +6853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="25">
         <v>11</v>
       </c>
@@ -6876,21 +6885,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="89" t="s">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="98" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="90"/>
-      <c r="C78" s="90"/>
-      <c r="D78" s="90"/>
-      <c r="E78" s="90"/>
-      <c r="F78" s="90"/>
-      <c r="G78" s="90"/>
-      <c r="H78" s="90"/>
-      <c r="I78" s="90"/>
-      <c r="J78" s="91"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B78" s="99"/>
+      <c r="C78" s="99"/>
+      <c r="D78" s="99"/>
+      <c r="E78" s="99"/>
+      <c r="F78" s="99"/>
+      <c r="G78" s="99"/>
+      <c r="H78" s="99"/>
+      <c r="I78" s="99"/>
+      <c r="J78" s="100"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="25">
         <v>1</v>
       </c>
@@ -6922,7 +6931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="25">
         <v>2</v>
       </c>
@@ -6954,7 +6963,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="25">
         <v>3</v>
       </c>
@@ -6986,7 +6995,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="25">
         <v>4</v>
       </c>
@@ -7018,7 +7027,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="25">
         <v>5</v>
       </c>
@@ -7050,7 +7059,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="25">
         <v>6</v>
       </c>
@@ -7082,7 +7091,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="25">
         <v>7</v>
       </c>
@@ -7114,7 +7123,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="25">
         <v>8</v>
       </c>
@@ -7146,7 +7155,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="25">
         <v>9</v>
       </c>
@@ -7178,7 +7187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="25">
         <v>10</v>
       </c>
@@ -7210,7 +7219,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="25">
         <v>11</v>
       </c>
@@ -7242,7 +7251,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="25">
         <v>12</v>
       </c>
@@ -7274,7 +7283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="25">
         <v>13</v>
       </c>
@@ -7306,7 +7315,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="25">
         <v>14</v>
       </c>
@@ -7338,7 +7347,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="25">
         <v>15</v>
       </c>
@@ -7370,7 +7379,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="25">
         <v>16</v>
       </c>
@@ -7402,7 +7411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="25">
         <v>17</v>
       </c>
@@ -7434,7 +7443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="25">
         <v>18</v>
       </c>
@@ -7466,7 +7475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="25">
         <v>19</v>
       </c>
@@ -7498,7 +7507,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="25">
         <v>20</v>
       </c>
@@ -7530,7 +7539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="25">
         <v>21</v>
       </c>
@@ -7562,7 +7571,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="25">
         <v>22</v>
       </c>
@@ -7594,7 +7603,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="25">
         <v>23</v>
       </c>
@@ -7626,7 +7635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="25">
         <v>24</v>
       </c>
@@ -7658,7 +7667,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="25">
         <v>25</v>
       </c>
@@ -7690,7 +7699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="25">
         <v>27</v>
       </c>
@@ -7722,7 +7731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="25">
         <v>28</v>
       </c>
@@ -7754,21 +7763,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="92" t="s">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="86" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="92"/>
-      <c r="C106" s="92"/>
-      <c r="D106" s="92"/>
-      <c r="E106" s="92"/>
-      <c r="F106" s="92"/>
-      <c r="G106" s="92"/>
-      <c r="H106" s="92"/>
-      <c r="I106" s="92"/>
-      <c r="J106" s="92"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B106" s="86"/>
+      <c r="C106" s="86"/>
+      <c r="D106" s="86"/>
+      <c r="E106" s="86"/>
+      <c r="F106" s="86"/>
+      <c r="G106" s="86"/>
+      <c r="H106" s="86"/>
+      <c r="I106" s="86"/>
+      <c r="J106" s="86"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="25">
         <v>1</v>
       </c>
@@ -7800,7 +7809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="25">
         <v>2</v>
       </c>
@@ -7832,7 +7841,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="25">
         <v>3</v>
       </c>
@@ -7864,7 +7873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="25">
         <v>4</v>
       </c>
@@ -7896,7 +7905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="25">
         <v>5</v>
       </c>
@@ -7928,7 +7937,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="25">
         <v>6</v>
       </c>
@@ -7960,7 +7969,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="25">
         <v>7</v>
       </c>
@@ -7992,7 +8001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" s="25">
         <v>8</v>
       </c>
@@ -8024,7 +8033,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="25">
         <v>9</v>
       </c>
@@ -8056,7 +8065,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" s="25">
         <v>10</v>
       </c>
@@ -8088,7 +8097,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="25">
         <v>11</v>
       </c>
@@ -8120,7 +8129,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="25">
         <v>12</v>
       </c>
@@ -8166,7 +8175,7 @@
       <c r="W118" s="52"/>
       <c r="X118" s="52"/>
     </row>
-    <row r="119" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="25">
         <v>13</v>
       </c>
@@ -8212,7 +8221,7 @@
       <c r="W119" s="52"/>
       <c r="X119" s="52"/>
     </row>
-    <row r="120" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="25">
         <v>14</v>
       </c>
@@ -8258,19 +8267,19 @@
       <c r="W120" s="52"/>
       <c r="X120" s="52"/>
     </row>
-    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="93" t="s">
+    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="87" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="93"/>
-      <c r="C121" s="93"/>
-      <c r="D121" s="93"/>
-      <c r="E121" s="93"/>
-      <c r="F121" s="93"/>
-      <c r="G121" s="93"/>
-      <c r="H121" s="93"/>
-      <c r="I121" s="93"/>
-      <c r="J121" s="93"/>
+      <c r="B121" s="87"/>
+      <c r="C121" s="87"/>
+      <c r="D121" s="87"/>
+      <c r="E121" s="87"/>
+      <c r="F121" s="87"/>
+      <c r="G121" s="87"/>
+      <c r="H121" s="87"/>
+      <c r="I121" s="87"/>
+      <c r="J121" s="87"/>
       <c r="K121" s="51"/>
       <c r="L121" s="52"/>
       <c r="M121" s="52"/>
@@ -8286,7 +8295,7 @@
       <c r="W121" s="52"/>
       <c r="X121" s="52"/>
     </row>
-    <row r="122" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="25">
         <v>1</v>
       </c>
@@ -8332,19 +8341,19 @@
       <c r="W122" s="52"/>
       <c r="X122" s="52"/>
     </row>
-    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="93" t="s">
+    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="87" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="93"/>
-      <c r="C123" s="93"/>
-      <c r="D123" s="93"/>
-      <c r="E123" s="93"/>
-      <c r="F123" s="93"/>
-      <c r="G123" s="93"/>
-      <c r="H123" s="93"/>
-      <c r="I123" s="93"/>
-      <c r="J123" s="93"/>
+      <c r="B123" s="87"/>
+      <c r="C123" s="87"/>
+      <c r="D123" s="87"/>
+      <c r="E123" s="87"/>
+      <c r="F123" s="87"/>
+      <c r="G123" s="87"/>
+      <c r="H123" s="87"/>
+      <c r="I123" s="87"/>
+      <c r="J123" s="87"/>
       <c r="K123" s="51"/>
       <c r="L123" s="52"/>
       <c r="M123" s="52"/>
@@ -8360,7 +8369,7 @@
       <c r="W123" s="52"/>
       <c r="X123" s="52"/>
     </row>
-    <row r="124" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="25">
         <v>1</v>
       </c>
@@ -8406,21 +8415,21 @@
       <c r="W124" s="52"/>
       <c r="X124" s="52"/>
     </row>
-    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="93" t="s">
+    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="87" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="93"/>
-      <c r="C125" s="93"/>
-      <c r="D125" s="93"/>
-      <c r="E125" s="93"/>
-      <c r="F125" s="93"/>
-      <c r="G125" s="93"/>
-      <c r="H125" s="93"/>
-      <c r="I125" s="93"/>
-      <c r="J125" s="93"/>
-    </row>
-    <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="87"/>
+      <c r="C125" s="87"/>
+      <c r="D125" s="87"/>
+      <c r="E125" s="87"/>
+      <c r="F125" s="87"/>
+      <c r="G125" s="87"/>
+      <c r="H125" s="87"/>
+      <c r="I125" s="87"/>
+      <c r="J125" s="87"/>
+    </row>
+    <row r="126" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="25">
         <v>1</v>
       </c>
@@ -8466,7 +8475,7 @@
       <c r="W126" s="55"/>
       <c r="X126" s="55"/>
     </row>
-    <row r="127" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="25">
         <v>2</v>
       </c>
@@ -8512,7 +8521,7 @@
       <c r="W127" s="52"/>
       <c r="X127" s="52"/>
     </row>
-    <row r="128" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="25">
         <v>3</v>
       </c>
@@ -8558,7 +8567,7 @@
       <c r="W128" s="52"/>
       <c r="X128" s="52"/>
     </row>
-    <row r="129" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="25">
         <v>4</v>
       </c>
@@ -8604,7 +8613,7 @@
       <c r="W129" s="52"/>
       <c r="X129" s="52"/>
     </row>
-    <row r="130" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="25">
         <v>5</v>
       </c>
@@ -8650,7 +8659,7 @@
       <c r="W130" s="52"/>
       <c r="X130" s="52"/>
     </row>
-    <row r="131" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="25">
         <v>6</v>
       </c>
@@ -8696,7 +8705,7 @@
       <c r="W131" s="52"/>
       <c r="X131" s="52"/>
     </row>
-    <row r="132" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="25">
         <v>7</v>
       </c>
@@ -8742,19 +8751,19 @@
       <c r="W132" s="52"/>
       <c r="X132" s="52"/>
     </row>
-    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="93" t="s">
+    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="87" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="93"/>
-      <c r="C133" s="93"/>
-      <c r="D133" s="94"/>
-      <c r="E133" s="94"/>
-      <c r="F133" s="94"/>
-      <c r="G133" s="94"/>
-      <c r="H133" s="94"/>
-      <c r="I133" s="94"/>
-      <c r="J133" s="94"/>
+      <c r="B133" s="87"/>
+      <c r="C133" s="87"/>
+      <c r="D133" s="88"/>
+      <c r="E133" s="88"/>
+      <c r="F133" s="88"/>
+      <c r="G133" s="88"/>
+      <c r="H133" s="88"/>
+      <c r="I133" s="88"/>
+      <c r="J133" s="88"/>
       <c r="K133" s="52"/>
       <c r="L133" s="52"/>
       <c r="M133" s="52"/>
@@ -8770,7 +8779,7 @@
       <c r="W133" s="52"/>
       <c r="X133" s="52"/>
     </row>
-    <row r="134" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="53">
         <v>11</v>
       </c>
@@ -8816,7 +8825,7 @@
       <c r="W134" s="52"/>
       <c r="X134" s="52"/>
     </row>
-    <row r="135" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="26">
         <v>2</v>
       </c>
@@ -8862,7 +8871,7 @@
       <c r="W135" s="52"/>
       <c r="X135" s="52"/>
     </row>
-    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="26">
         <v>3</v>
       </c>
@@ -8894,7 +8903,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="26">
         <v>4</v>
       </c>
@@ -8940,7 +8949,7 @@
       <c r="W137" s="52"/>
       <c r="X137" s="52"/>
     </row>
-    <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="26">
         <v>5</v>
       </c>
@@ -8986,7 +8995,7 @@
       <c r="W138" s="52"/>
       <c r="X138" s="52"/>
     </row>
-    <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="26">
         <v>6</v>
       </c>
@@ -9032,7 +9041,7 @@
       <c r="W139" s="52"/>
       <c r="X139" s="52"/>
     </row>
-    <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="26">
         <v>7</v>
       </c>
@@ -9064,7 +9073,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="26">
         <v>8</v>
       </c>
@@ -9110,7 +9119,7 @@
       <c r="W141" s="52"/>
       <c r="X141" s="52"/>
     </row>
-    <row r="142" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="26">
         <v>9</v>
       </c>
@@ -9156,7 +9165,7 @@
       <c r="W142" s="52"/>
       <c r="X142" s="52"/>
     </row>
-    <row r="143" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="26">
         <v>10</v>
       </c>
@@ -9202,7 +9211,7 @@
       <c r="W143" s="52"/>
       <c r="X143" s="52"/>
     </row>
-    <row r="144" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="26">
         <v>11</v>
       </c>
@@ -9248,19 +9257,19 @@
       <c r="W144" s="52"/>
       <c r="X144" s="52"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="98" t="s">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="92" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="99"/>
-      <c r="C145" s="99"/>
-      <c r="D145" s="99"/>
-      <c r="E145" s="99"/>
-      <c r="F145" s="99"/>
-      <c r="G145" s="99"/>
-      <c r="H145" s="99"/>
-      <c r="I145" s="99"/>
-      <c r="J145" s="100"/>
+      <c r="B145" s="93"/>
+      <c r="C145" s="93"/>
+      <c r="D145" s="93"/>
+      <c r="E145" s="93"/>
+      <c r="F145" s="93"/>
+      <c r="G145" s="93"/>
+      <c r="H145" s="93"/>
+      <c r="I145" s="93"/>
+      <c r="J145" s="94"/>
       <c r="K145" s="52"/>
       <c r="L145" s="52"/>
       <c r="M145" s="52"/>
@@ -9276,7 +9285,7 @@
       <c r="W145" s="52"/>
       <c r="X145" s="52"/>
     </row>
-    <row r="146" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="25">
         <v>1</v>
       </c>
@@ -9322,7 +9331,7 @@
       <c r="W146" s="52"/>
       <c r="X146" s="52"/>
     </row>
-    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="25">
         <v>2</v>
       </c>
@@ -9354,7 +9363,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="25">
         <v>3</v>
       </c>
@@ -9386,7 +9395,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="25">
         <v>4</v>
       </c>
@@ -9418,7 +9427,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="25">
         <v>5</v>
       </c>
@@ -9466,7 +9475,7 @@
       <c r="Y150" s="52"/>
       <c r="Z150" s="52"/>
     </row>
-    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="25">
         <v>6</v>
       </c>
@@ -9514,7 +9523,7 @@
       <c r="Y151" s="52"/>
       <c r="Z151" s="52"/>
     </row>
-    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="25">
         <v>7</v>
       </c>
@@ -9562,7 +9571,7 @@
       <c r="Y152" s="52"/>
       <c r="Z152" s="52"/>
     </row>
-    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="25">
         <v>8</v>
       </c>
@@ -9610,7 +9619,7 @@
       <c r="Y153" s="52"/>
       <c r="Z153" s="52"/>
     </row>
-    <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="25">
         <v>9</v>
       </c>
@@ -9658,7 +9667,7 @@
       <c r="Y154" s="52"/>
       <c r="Z154" s="52"/>
     </row>
-    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="25">
         <v>10</v>
       </c>
@@ -9706,19 +9715,19 @@
       <c r="Y155" s="52"/>
       <c r="Z155" s="52"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="93" t="s">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="87" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="93"/>
-      <c r="C156" s="93"/>
-      <c r="D156" s="93"/>
-      <c r="E156" s="93"/>
-      <c r="F156" s="93"/>
-      <c r="G156" s="93"/>
-      <c r="H156" s="93"/>
-      <c r="I156" s="93"/>
-      <c r="J156" s="93"/>
+      <c r="B156" s="87"/>
+      <c r="C156" s="87"/>
+      <c r="D156" s="87"/>
+      <c r="E156" s="87"/>
+      <c r="F156" s="87"/>
+      <c r="G156" s="87"/>
+      <c r="H156" s="87"/>
+      <c r="I156" s="87"/>
+      <c r="J156" s="87"/>
       <c r="K156" s="52"/>
       <c r="L156" s="52"/>
       <c r="M156" s="52"/>
@@ -9736,7 +9745,7 @@
       <c r="Y156" s="52"/>
       <c r="Z156" s="52"/>
     </row>
-    <row r="157" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="25">
         <v>1</v>
       </c>
@@ -9784,19 +9793,19 @@
       <c r="Y157" s="52"/>
       <c r="Z157" s="52"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="93" t="s">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="87" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="93"/>
-      <c r="C158" s="93"/>
-      <c r="D158" s="93"/>
-      <c r="E158" s="93"/>
-      <c r="F158" s="93"/>
-      <c r="G158" s="93"/>
-      <c r="H158" s="93"/>
-      <c r="I158" s="93"/>
-      <c r="J158" s="93"/>
+      <c r="B158" s="87"/>
+      <c r="C158" s="87"/>
+      <c r="D158" s="87"/>
+      <c r="E158" s="87"/>
+      <c r="F158" s="87"/>
+      <c r="G158" s="87"/>
+      <c r="H158" s="87"/>
+      <c r="I158" s="87"/>
+      <c r="J158" s="87"/>
       <c r="K158" s="52"/>
       <c r="L158" s="52"/>
       <c r="M158" s="52"/>
@@ -9814,7 +9823,7 @@
       <c r="Y158" s="52"/>
       <c r="Z158" s="52"/>
     </row>
-    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="61">
         <v>1</v>
       </c>
@@ -9862,7 +9871,7 @@
       <c r="Y159" s="52"/>
       <c r="Z159" s="52"/>
     </row>
-    <row r="160" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="62">
         <v>2</v>
       </c>
@@ -9910,7 +9919,7 @@
       <c r="Y160" s="52"/>
       <c r="Z160" s="52"/>
     </row>
-    <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="62">
         <v>3</v>
       </c>
@@ -9958,7 +9967,7 @@
       <c r="Y161" s="52"/>
       <c r="Z161" s="52"/>
     </row>
-    <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="62">
         <v>4</v>
       </c>
@@ -10006,7 +10015,7 @@
       <c r="Y162" s="52"/>
       <c r="Z162" s="52"/>
     </row>
-    <row r="163" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="62">
         <v>5</v>
       </c>
@@ -10054,7 +10063,7 @@
       <c r="Y163" s="52"/>
       <c r="Z163" s="52"/>
     </row>
-    <row r="164" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="62">
         <v>6</v>
       </c>
@@ -10102,7 +10111,7 @@
       <c r="Y164" s="52"/>
       <c r="Z164" s="52"/>
     </row>
-    <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="62">
         <v>7</v>
       </c>
@@ -10150,7 +10159,7 @@
       <c r="Y165" s="52"/>
       <c r="Z165" s="52"/>
     </row>
-    <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="62">
         <v>8</v>
       </c>
@@ -10198,7 +10207,7 @@
       <c r="Y166" s="52"/>
       <c r="Z166" s="52"/>
     </row>
-    <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="61">
         <v>9</v>
       </c>
@@ -10246,7 +10255,7 @@
       <c r="Y167" s="52"/>
       <c r="Z167" s="52"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="62">
         <v>10</v>
       </c>
@@ -10278,7 +10287,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="61">
         <v>11</v>
       </c>
@@ -10310,7 +10319,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="62">
         <v>12</v>
       </c>
@@ -10342,7 +10351,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="61">
         <v>13</v>
       </c>
@@ -10374,7 +10383,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="62">
         <v>14</v>
       </c>
@@ -10406,7 +10415,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="61">
         <v>15</v>
       </c>
@@ -10438,7 +10447,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="62">
         <v>16</v>
       </c>
@@ -10470,7 +10479,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="61">
         <v>17</v>
       </c>
@@ -10502,7 +10511,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="62">
         <v>18</v>
       </c>
@@ -10534,7 +10543,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="76">
         <v>19</v>
       </c>
@@ -10566,7 +10575,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="76">
         <v>20</v>
       </c>
@@ -10598,7 +10607,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="76">
         <v>21</v>
       </c>
@@ -10630,21 +10639,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="93" t="s">
+    <row r="180" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="87" t="s">
         <v>707</v>
       </c>
-      <c r="B180" s="93"/>
-      <c r="C180" s="93"/>
+      <c r="B180" s="87"/>
+      <c r="C180" s="87"/>
       <c r="D180" s="85"/>
-      <c r="E180" s="93"/>
-      <c r="F180" s="93"/>
-      <c r="G180" s="93"/>
-      <c r="H180" s="93"/>
-      <c r="I180" s="93"/>
-      <c r="J180" s="93"/>
-    </row>
-    <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E180" s="87"/>
+      <c r="F180" s="87"/>
+      <c r="G180" s="87"/>
+      <c r="H180" s="87"/>
+      <c r="I180" s="87"/>
+      <c r="J180" s="87"/>
+    </row>
+    <row r="181" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="62">
         <v>1</v>
       </c>
@@ -10676,7 +10685,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="62">
         <v>2</v>
       </c>
@@ -10708,7 +10717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="62">
         <v>3</v>
       </c>
@@ -10740,7 +10749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="62">
         <v>4</v>
       </c>
@@ -10772,7 +10781,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="62">
         <v>5</v>
       </c>
@@ -10804,7 +10813,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="62">
         <v>6</v>
       </c>
@@ -10836,7 +10845,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="62">
         <v>7</v>
       </c>
@@ -10868,7 +10877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="62">
         <v>7</v>
       </c>
@@ -10900,7 +10909,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="1:10" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:10" s="28" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="62">
         <v>9</v>
       </c>
@@ -10932,21 +10941,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="95" t="s">
+    <row r="190" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="89" t="s">
         <v>609</v>
       </c>
-      <c r="B190" s="96"/>
-      <c r="C190" s="96"/>
-      <c r="D190" s="96"/>
-      <c r="E190" s="96"/>
-      <c r="F190" s="96"/>
-      <c r="G190" s="96"/>
-      <c r="H190" s="96"/>
-      <c r="I190" s="96"/>
-      <c r="J190" s="97"/>
-    </row>
-    <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B190" s="90"/>
+      <c r="C190" s="90"/>
+      <c r="D190" s="90"/>
+      <c r="E190" s="90"/>
+      <c r="F190" s="90"/>
+      <c r="G190" s="90"/>
+      <c r="H190" s="90"/>
+      <c r="I190" s="90"/>
+      <c r="J190" s="91"/>
+    </row>
+    <row r="191" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="62">
         <v>1</v>
       </c>
@@ -10978,7 +10987,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="62">
         <v>2</v>
       </c>
@@ -11010,7 +11019,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="62">
         <v>3</v>
       </c>
@@ -11042,7 +11051,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="62">
         <v>4</v>
       </c>
@@ -11074,7 +11083,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="62">
         <v>5</v>
       </c>
@@ -11106,7 +11115,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="62">
         <v>6</v>
       </c>
@@ -11138,7 +11147,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="62">
         <v>7</v>
       </c>
@@ -11170,7 +11179,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="85" t="s">
         <v>630</v>
       </c>
@@ -11184,7 +11193,7 @@
       <c r="I198" s="85"/>
       <c r="J198" s="85"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="43">
         <v>1</v>
       </c>
@@ -11216,7 +11225,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="43">
         <v>2</v>
       </c>
@@ -11248,7 +11257,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="43">
         <v>3</v>
       </c>
@@ -11280,7 +11289,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="43">
         <v>4</v>
       </c>
@@ -11312,7 +11321,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="85" t="s">
         <v>643</v>
       </c>
@@ -11326,7 +11335,7 @@
       <c r="I203" s="85"/>
       <c r="J203" s="85"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="43">
         <v>1</v>
       </c>
@@ -11358,7 +11367,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="85" t="s">
         <v>649</v>
       </c>
@@ -11372,7 +11381,7 @@
       <c r="I205" s="85"/>
       <c r="J205" s="85"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="43">
         <v>1</v>
       </c>
@@ -11404,7 +11413,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="43">
         <v>2</v>
       </c>
@@ -11436,7 +11445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="43">
         <v>3</v>
       </c>
@@ -11468,7 +11477,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="43">
         <v>4</v>
       </c>
@@ -11500,7 +11509,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="43">
         <v>5</v>
       </c>
@@ -11532,7 +11541,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="43">
         <v>6</v>
       </c>
@@ -11564,7 +11573,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="43">
         <v>7</v>
       </c>
@@ -11596,7 +11605,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="43">
         <v>8</v>
       </c>
@@ -11628,7 +11637,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="43">
         <v>9</v>
       </c>
@@ -11660,7 +11669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="75"/>
       <c r="B215" s="75"/>
       <c r="C215" s="75"/>
@@ -11674,7 +11683,7 @@
       <c r="I215" s="75"/>
       <c r="J215" s="75"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="43">
         <v>1</v>
       </c>
@@ -11706,7 +11715,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="73"/>
       <c r="B217" s="73"/>
       <c r="C217" s="73"/>
@@ -11720,7 +11729,7 @@
       <c r="I217" s="73"/>
       <c r="J217" s="73"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="43">
         <v>1</v>
       </c>
@@ -11752,7 +11761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="43">
         <v>2</v>
       </c>
@@ -11784,7 +11793,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="85" t="s">
         <v>711</v>
       </c>
@@ -11798,7 +11807,7 @@
       <c r="I220" s="85"/>
       <c r="J220" s="85"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="43">
         <v>1</v>
       </c>
@@ -11830,7 +11839,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="43">
         <v>2</v>
       </c>
@@ -11862,7 +11871,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="43">
         <v>3</v>
       </c>
@@ -11894,7 +11903,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="43">
         <v>4</v>
       </c>
@@ -11926,7 +11935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="43">
         <v>5</v>
       </c>
@@ -11958,7 +11967,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="85" t="s">
         <v>719</v>
       </c>
@@ -11972,7 +11981,7 @@
       <c r="I226" s="85"/>
       <c r="J226" s="85"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="43">
         <v>1</v>
       </c>
@@ -12004,7 +12013,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="43">
         <v>2</v>
       </c>
@@ -12036,7 +12045,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="43">
         <v>3</v>
       </c>
@@ -12068,7 +12077,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="43">
         <v>4</v>
       </c>
@@ -12100,7 +12109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="43">
         <v>5</v>
       </c>
@@ -12132,7 +12141,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="43">
         <v>6</v>
       </c>
@@ -12164,7 +12173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="43">
         <v>7</v>
       </c>
@@ -12196,7 +12205,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="43">
         <v>8</v>
       </c>
@@ -12228,7 +12237,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="43">
         <v>9</v>
       </c>
@@ -12260,7 +12269,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="43">
         <v>10</v>
       </c>
@@ -12292,7 +12301,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="43">
         <v>11</v>
       </c>
@@ -12324,7 +12333,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="85" t="s">
         <v>756</v>
       </c>
@@ -12338,7 +12347,7 @@
       <c r="I238" s="85"/>
       <c r="J238" s="85"/>
     </row>
-    <row r="239" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="43">
         <v>1</v>
       </c>
@@ -12370,7 +12379,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="85" t="s">
         <v>768</v>
       </c>
@@ -12384,7 +12393,7 @@
       <c r="I240" s="85"/>
       <c r="J240" s="85"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="43">
         <v>1</v>
       </c>
@@ -12416,7 +12425,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="43">
         <v>2</v>
       </c>
@@ -12448,7 +12457,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="43">
         <v>3</v>
       </c>
@@ -12480,7 +12489,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="43">
         <v>4</v>
       </c>
@@ -12512,7 +12521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="43">
         <v>5</v>
       </c>
@@ -12544,7 +12553,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="43">
         <v>6</v>
       </c>
@@ -12576,7 +12585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="43">
         <v>7</v>
       </c>
@@ -12608,7 +12617,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="43">
         <v>8</v>
       </c>
@@ -12640,7 +12649,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="43">
         <v>9</v>
       </c>
@@ -12672,7 +12681,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="43">
         <v>10</v>
       </c>
@@ -12704,7 +12713,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="43">
         <v>11</v>
       </c>
@@ -12736,7 +12745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="43">
         <v>12</v>
       </c>
@@ -12768,7 +12777,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="43">
         <v>13</v>
       </c>
@@ -12800,7 +12809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="43">
         <v>14</v>
       </c>
@@ -12832,7 +12841,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="43">
         <v>15</v>
       </c>
@@ -12864,7 +12873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="85" t="s">
         <v>813</v>
       </c>
@@ -12878,7 +12887,7 @@
       <c r="I256" s="85"/>
       <c r="J256" s="85"/>
     </row>
-    <row r="257" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="43">
         <v>1</v>
       </c>
@@ -12910,7 +12919,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="43">
         <v>2</v>
       </c>
@@ -12942,7 +12951,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="85" t="s">
         <v>814</v>
       </c>
@@ -12956,7 +12965,7 @@
       <c r="I259" s="85"/>
       <c r="J259" s="85"/>
     </row>
-    <row r="260" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="43">
         <v>1</v>
       </c>
@@ -12988,7 +12997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="43">
         <v>2</v>
       </c>
@@ -13020,7 +13029,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="43">
         <v>3</v>
       </c>
@@ -13052,7 +13061,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="43">
         <v>4</v>
       </c>
@@ -13084,7 +13093,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="43">
         <v>5</v>
       </c>
@@ -13116,7 +13125,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="85" t="s">
         <v>890</v>
       </c>
@@ -13130,7 +13139,7 @@
       <c r="I265" s="85"/>
       <c r="J265" s="85"/>
     </row>
-    <row r="266" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="43">
         <v>1</v>
       </c>
@@ -13162,7 +13171,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="85" t="s">
         <v>917</v>
       </c>
@@ -13176,7 +13185,7 @@
       <c r="I267" s="85"/>
       <c r="J267" s="85"/>
     </row>
-    <row r="268" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="43">
         <v>1</v>
       </c>
@@ -13208,7 +13217,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="43">
         <v>2</v>
       </c>
@@ -13240,7 +13249,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="85" t="s">
         <v>931</v>
       </c>
@@ -13254,7 +13263,7 @@
       <c r="I270" s="85"/>
       <c r="J270" s="85"/>
     </row>
-    <row r="271" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="43">
         <v>1</v>
       </c>
@@ -13286,7 +13295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="272" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="43">
         <v>2</v>
       </c>
@@ -13318,7 +13327,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="273" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="85" t="s">
         <v>936</v>
       </c>
@@ -13332,7 +13341,7 @@
       <c r="I273" s="85"/>
       <c r="J273" s="85"/>
     </row>
-    <row r="274" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="43">
         <v>1</v>
       </c>
@@ -13364,7 +13373,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="43">
         <v>2</v>
       </c>
@@ -13396,7 +13405,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="85" t="s">
         <v>947</v>
       </c>
@@ -13410,7 +13419,7 @@
       <c r="I276" s="85"/>
       <c r="J276" s="85"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="77">
         <v>1</v>
       </c>
@@ -13442,7 +13451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="77">
         <v>2</v>
       </c>
@@ -13474,7 +13483,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="85" t="s">
         <v>955</v>
       </c>
@@ -13488,7 +13497,7 @@
       <c r="I279" s="85"/>
       <c r="J279" s="85"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="77">
         <v>1</v>
       </c>
@@ -13520,7 +13529,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="85" t="s">
         <v>966</v>
       </c>
@@ -13534,7 +13543,7 @@
       <c r="I281" s="85"/>
       <c r="J281" s="85"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>1</v>
       </c>
@@ -13566,7 +13575,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>2</v>
       </c>
@@ -13598,7 +13607,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>3</v>
       </c>
@@ -13630,7 +13639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>4</v>
       </c>
@@ -13662,7 +13671,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="286" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="85" t="s">
         <v>980</v>
       </c>
@@ -13676,7 +13685,7 @@
       <c r="I286" s="85"/>
       <c r="J286" s="85"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="77">
         <v>1</v>
       </c>
@@ -13708,8 +13717,56 @@
         <v>13</v>
       </c>
     </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>2</v>
+      </c>
+      <c r="B288" t="s">
+        <v>10</v>
+      </c>
+      <c r="C288" t="s">
+        <v>985</v>
+      </c>
+      <c r="D288" t="s">
+        <v>986</v>
+      </c>
+      <c r="E288" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F288" s="71" t="s">
+        <v>987</v>
+      </c>
+      <c r="G288" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="H288" s="77" t="s">
+        <v>981</v>
+      </c>
+      <c r="I288" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="J288" s="77" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A281:J281"/>
+    <mergeCell ref="A279:J279"/>
+    <mergeCell ref="A265:J265"/>
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A259:J259"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A240:J240"/>
+    <mergeCell ref="A238:J238"/>
+    <mergeCell ref="A276:J276"/>
     <mergeCell ref="A286:J286"/>
     <mergeCell ref="A273:J273"/>
     <mergeCell ref="A270:J270"/>
@@ -13726,22 +13783,6 @@
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
     <mergeCell ref="A267:J267"/>
-    <mergeCell ref="A281:J281"/>
-    <mergeCell ref="A279:J279"/>
-    <mergeCell ref="A265:J265"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="A259:J259"/>
-    <mergeCell ref="A256:J256"/>
-    <mergeCell ref="A240:J240"/>
-    <mergeCell ref="A238:J238"/>
-    <mergeCell ref="A276:J276"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13839,36 +13880,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG263"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AG264"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.88671875" customWidth="1"/>
-    <col min="2" max="2" width="45.6640625" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="54.33203125" customWidth="1"/>
+    <col min="1" max="1" width="48.85546875" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="54.28515625" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.44140625" customWidth="1"/>
-    <col min="12" max="12" width="53.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.42578125" customWidth="1"/>
+    <col min="12" max="12" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="71.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="52.33203125" customWidth="1"/>
-    <col min="21" max="21" width="20.88671875" customWidth="1"/>
+    <col min="17" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="71.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="52.28515625" customWidth="1"/>
+    <col min="21" max="21" width="20.85546875" customWidth="1"/>
     <col min="22" max="22" width="27" customWidth="1"/>
     <col min="24" max="25" width="29" customWidth="1"/>
-    <col min="26" max="26" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.44140625" customWidth="1"/>
-    <col min="29" max="29" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.6640625" customWidth="1"/>
-    <col min="31" max="31" width="12.33203125" customWidth="1"/>
+    <col min="26" max="26" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.42578125" customWidth="1"/>
+    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>5</v>
       </c>
@@ -13969,7 +14010,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
         <v>23</v>
       </c>
@@ -14052,7 +14093,7 @@
       <c r="AF2" s="28"/>
       <c r="AG2" s="28"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
         <v>25</v>
       </c>
@@ -14135,7 +14176,7 @@
       <c r="AF3" s="28"/>
       <c r="AG3" s="28"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
         <v>28</v>
       </c>
@@ -14218,7 +14259,7 @@
       <c r="AF4" s="28"/>
       <c r="AG4" s="28"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
         <v>58</v>
       </c>
@@ -14301,7 +14342,7 @@
       <c r="AF5" s="28"/>
       <c r="AG5" s="28"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
         <v>69</v>
       </c>
@@ -14384,7 +14425,7 @@
       <c r="AF6" s="28"/>
       <c r="AG6" s="28"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
         <v>73</v>
       </c>
@@ -14467,7 +14508,7 @@
       <c r="AF7" s="28"/>
       <c r="AG7" s="28"/>
     </row>
-    <row r="8" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
         <v>77</v>
       </c>
@@ -14550,7 +14591,7 @@
       <c r="AF8" s="28"/>
       <c r="AG8" s="28"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
         <v>79</v>
       </c>
@@ -14633,7 +14674,7 @@
       <c r="AF9" s="28"/>
       <c r="AG9" s="28"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
         <v>80</v>
       </c>
@@ -14716,7 +14757,7 @@
       <c r="AF10" s="28"/>
       <c r="AG10" s="28"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
         <v>81</v>
       </c>
@@ -14799,7 +14840,7 @@
       <c r="AF11" s="28"/>
       <c r="AG11" s="28"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
         <v>83</v>
       </c>
@@ -14882,7 +14923,7 @@
       <c r="AF12" s="28"/>
       <c r="AG12" s="28"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
         <v>84</v>
       </c>
@@ -14965,7 +15006,7 @@
       <c r="AF13" s="28"/>
       <c r="AG13" s="28"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
         <v>85</v>
       </c>
@@ -15048,7 +15089,7 @@
       <c r="AF14" s="28"/>
       <c r="AG14" s="28"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
         <v>86</v>
       </c>
@@ -15131,7 +15172,7 @@
       <c r="AF15" s="28"/>
       <c r="AG15" s="28"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
         <v>87</v>
       </c>
@@ -15214,7 +15255,7 @@
       <c r="AF16" s="28"/>
       <c r="AG16" s="28"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
         <v>88</v>
       </c>
@@ -15297,7 +15338,7 @@
       <c r="AF17" s="28"/>
       <c r="AG17" s="28"/>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
         <v>89</v>
       </c>
@@ -15380,7 +15421,7 @@
       <c r="AF18" s="28"/>
       <c r="AG18" s="28"/>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="36" t="s">
         <v>91</v>
       </c>
@@ -15463,7 +15504,7 @@
       <c r="AF19" s="28"/>
       <c r="AG19" s="28"/>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
         <v>93</v>
       </c>
@@ -15546,7 +15587,7 @@
       <c r="AF20" s="28"/>
       <c r="AG20" s="28"/>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
         <v>94</v>
       </c>
@@ -15629,7 +15670,7 @@
       <c r="AF21" s="28"/>
       <c r="AG21" s="28"/>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
         <v>135</v>
       </c>
@@ -15712,7 +15753,7 @@
       <c r="AF22" s="28"/>
       <c r="AG22" s="28"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
         <v>140</v>
       </c>
@@ -15795,7 +15836,7 @@
       <c r="AF23" s="28"/>
       <c r="AG23" s="28"/>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="47" t="s">
         <v>63</v>
       </c>
@@ -15878,7 +15919,7 @@
       <c r="AF24" s="28"/>
       <c r="AG24" s="28"/>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="41" t="s">
         <v>144</v>
       </c>
@@ -15961,7 +16002,7 @@
       <c r="AF25" s="28"/>
       <c r="AG25" s="28"/>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>145</v>
       </c>
@@ -16044,7 +16085,7 @@
       <c r="AF26" s="28"/>
       <c r="AG26" s="28"/>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="41" t="s">
         <v>146</v>
       </c>
@@ -16127,7 +16168,7 @@
       <c r="AF27" s="28"/>
       <c r="AG27" s="28"/>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
         <v>147</v>
       </c>
@@ -16210,7 +16251,7 @@
       <c r="AF28" s="28"/>
       <c r="AG28" s="28"/>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="41" t="s">
         <v>148</v>
       </c>
@@ -16293,7 +16334,7 @@
       <c r="AF29" s="28"/>
       <c r="AG29" s="28"/>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="41" t="s">
         <v>150</v>
       </c>
@@ -16376,7 +16417,7 @@
       <c r="AF30" s="28"/>
       <c r="AG30" s="28"/>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="41" t="s">
         <v>151</v>
       </c>
@@ -16459,7 +16500,7 @@
       <c r="AF31" s="28"/>
       <c r="AG31" s="28"/>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="41" t="s">
         <v>152</v>
       </c>
@@ -16542,7 +16583,7 @@
       <c r="AF32" s="28"/>
       <c r="AG32" s="28"/>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="41" t="s">
         <v>153</v>
       </c>
@@ -16625,7 +16666,7 @@
       <c r="AF33" s="28"/>
       <c r="AG33" s="28"/>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="41" t="s">
         <v>154</v>
       </c>
@@ -16708,7 +16749,7 @@
       <c r="AF34" s="28"/>
       <c r="AG34" s="28"/>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="41" t="s">
         <v>155</v>
       </c>
@@ -16791,7 +16832,7 @@
       <c r="AF35" s="28"/>
       <c r="AG35" s="28"/>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="31" t="s">
         <v>64</v>
       </c>
@@ -16874,7 +16915,7 @@
       <c r="AF36" s="28"/>
       <c r="AG36" s="28"/>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="48" t="s">
         <v>175</v>
       </c>
@@ -16959,7 +17000,7 @@
       <c r="AF37" s="28"/>
       <c r="AG37" s="28"/>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="42" t="s">
         <v>179</v>
       </c>
@@ -17044,7 +17085,7 @@
       <c r="AF38" s="28"/>
       <c r="AG38" s="28"/>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="42" t="s">
         <v>182</v>
       </c>
@@ -17129,7 +17170,7 @@
       <c r="AF39" s="28"/>
       <c r="AG39" s="28"/>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="42" t="s">
         <v>185</v>
       </c>
@@ -17214,7 +17255,7 @@
       <c r="AF40" s="28"/>
       <c r="AG40" s="28"/>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="42" t="s">
         <v>188</v>
       </c>
@@ -17299,7 +17340,7 @@
       <c r="AF41" s="28"/>
       <c r="AG41" s="28"/>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="42" t="s">
         <v>190</v>
       </c>
@@ -17384,7 +17425,7 @@
       <c r="AF42" s="28"/>
       <c r="AG42" s="28"/>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="42" t="s">
         <v>193</v>
       </c>
@@ -17469,7 +17510,7 @@
       <c r="AF43" s="28"/>
       <c r="AG43" s="28"/>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="42" t="s">
         <v>196</v>
       </c>
@@ -17554,7 +17595,7 @@
       <c r="AF44" s="28"/>
       <c r="AG44" s="28"/>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="42" t="s">
         <v>198</v>
       </c>
@@ -17639,7 +17680,7 @@
       <c r="AF45" s="28"/>
       <c r="AG45" s="28"/>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="42" t="s">
         <v>200</v>
       </c>
@@ -17724,7 +17765,7 @@
       <c r="AF46" s="28"/>
       <c r="AG46" s="28"/>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" s="42" t="s">
         <v>202</v>
       </c>
@@ -17809,7 +17850,7 @@
       <c r="AF47" s="28"/>
       <c r="AG47" s="28"/>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" s="42" t="s">
         <v>204</v>
       </c>
@@ -17894,7 +17935,7 @@
       <c r="AF48" s="28"/>
       <c r="AG48" s="28"/>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="42" t="s">
         <v>206</v>
       </c>
@@ -17979,7 +18020,7 @@
       <c r="AF49" s="28"/>
       <c r="AG49" s="28"/>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" s="42" t="s">
         <v>208</v>
       </c>
@@ -18064,7 +18105,7 @@
       <c r="AF50" s="28"/>
       <c r="AG50" s="28"/>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="42" t="s">
         <v>210</v>
       </c>
@@ -18149,7 +18190,7 @@
       <c r="AF51" s="28"/>
       <c r="AG51" s="28"/>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" s="42" t="s">
         <v>212</v>
       </c>
@@ -18234,7 +18275,7 @@
       <c r="AF52" s="28"/>
       <c r="AG52" s="28"/>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" s="42" t="s">
         <v>679</v>
       </c>
@@ -18319,7 +18360,7 @@
       <c r="AF53" s="28"/>
       <c r="AG53" s="28"/>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" s="49" t="s">
         <v>213</v>
       </c>
@@ -18404,7 +18445,7 @@
       <c r="AF54" s="28"/>
       <c r="AG54" s="28"/>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" s="43" t="s">
         <v>214</v>
       </c>
@@ -18489,7 +18530,7 @@
       <c r="AF55" s="28"/>
       <c r="AG55" s="28"/>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" s="43" t="s">
         <v>215</v>
       </c>
@@ -18574,7 +18615,7 @@
       <c r="AF56" s="28"/>
       <c r="AG56" s="28"/>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
         <v>216</v>
       </c>
@@ -18659,7 +18700,7 @@
       <c r="AF57" s="28"/>
       <c r="AG57" s="28"/>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
         <v>217</v>
       </c>
@@ -18744,7 +18785,7 @@
       <c r="AF58" s="28"/>
       <c r="AG58" s="28"/>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="43" t="s">
         <v>218</v>
       </c>
@@ -18829,7 +18870,7 @@
       <c r="AF59" s="28"/>
       <c r="AG59" s="28"/>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" s="43" t="s">
         <v>219</v>
       </c>
@@ -18914,7 +18955,7 @@
       <c r="AF60" s="28"/>
       <c r="AG60" s="28"/>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
         <v>220</v>
       </c>
@@ -18999,7 +19040,7 @@
       <c r="AF61" s="28"/>
       <c r="AG61" s="28"/>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" s="43" t="s">
         <v>221</v>
       </c>
@@ -19084,7 +19125,7 @@
       <c r="AF62" s="28"/>
       <c r="AG62" s="28"/>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" s="43" t="s">
         <v>222</v>
       </c>
@@ -19169,7 +19210,7 @@
       <c r="AF63" s="28"/>
       <c r="AG63" s="28"/>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" s="50" t="s">
         <v>249</v>
       </c>
@@ -19254,7 +19295,7 @@
       <c r="AF64" s="28"/>
       <c r="AG64" s="28"/>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" s="43" t="s">
         <v>253</v>
       </c>
@@ -19339,7 +19380,7 @@
       <c r="AF65" s="28"/>
       <c r="AG65" s="28"/>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" s="43" t="s">
         <v>256</v>
       </c>
@@ -19424,7 +19465,7 @@
       <c r="AF66" s="28"/>
       <c r="AG66" s="28"/>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" s="43" t="s">
         <v>259</v>
       </c>
@@ -19509,7 +19550,7 @@
       <c r="AF67" s="28"/>
       <c r="AG67" s="28"/>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
         <v>262</v>
       </c>
@@ -19594,7 +19635,7 @@
       <c r="AF68" s="28"/>
       <c r="AG68" s="28"/>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="43" t="s">
         <v>265</v>
       </c>
@@ -19679,7 +19720,7 @@
       <c r="AF69" s="28"/>
       <c r="AG69" s="28"/>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" s="43" t="s">
         <v>268</v>
       </c>
@@ -19764,7 +19805,7 @@
       <c r="AF70" s="28"/>
       <c r="AG70" s="28"/>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" s="43" t="s">
         <v>271</v>
       </c>
@@ -19849,7 +19890,7 @@
       <c r="AF71" s="28"/>
       <c r="AG71" s="28"/>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" s="43" t="s">
         <v>274</v>
       </c>
@@ -19934,7 +19975,7 @@
       <c r="AF72" s="28"/>
       <c r="AG72" s="28"/>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="43" t="s">
         <v>277</v>
       </c>
@@ -20019,7 +20060,7 @@
       <c r="AF73" s="28"/>
       <c r="AG73" s="28"/>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="43" t="s">
         <v>280</v>
       </c>
@@ -20106,7 +20147,7 @@
       <c r="AF74" s="28"/>
       <c r="AG74" s="28"/>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="56" t="s">
         <v>282</v>
       </c>
@@ -20193,7 +20234,7 @@
       <c r="AF75" s="28"/>
       <c r="AG75" s="28"/>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="43" t="s">
         <v>285</v>
       </c>
@@ -20280,7 +20321,7 @@
       <c r="AF76" s="28"/>
       <c r="AG76" s="28"/>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="43" t="s">
         <v>287</v>
       </c>
@@ -20367,7 +20408,7 @@
       <c r="AF77" s="28"/>
       <c r="AG77" s="28"/>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="43" t="s">
         <v>289</v>
       </c>
@@ -20454,7 +20495,7 @@
       <c r="AF78" s="28"/>
       <c r="AG78" s="28"/>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="43" t="s">
         <v>292</v>
       </c>
@@ -20541,7 +20582,7 @@
       <c r="AF79" s="28"/>
       <c r="AG79" s="28"/>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="43" t="s">
         <v>295</v>
       </c>
@@ -20628,7 +20669,7 @@
       <c r="AF80" s="28"/>
       <c r="AG80" s="28"/>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" s="43" t="s">
         <v>298</v>
       </c>
@@ -20715,7 +20756,7 @@
       <c r="AF81" s="28"/>
       <c r="AG81" s="28"/>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" s="43" t="s">
         <v>301</v>
       </c>
@@ -20802,7 +20843,7 @@
       <c r="AF82" s="28"/>
       <c r="AG82" s="28"/>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" s="43" t="s">
         <v>304</v>
       </c>
@@ -20889,7 +20930,7 @@
       <c r="AF83" s="28"/>
       <c r="AG83" s="28"/>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" s="43" t="s">
         <v>306</v>
       </c>
@@ -20976,7 +21017,7 @@
       <c r="AF84" s="28"/>
       <c r="AG84" s="28"/>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" s="43" t="s">
         <v>308</v>
       </c>
@@ -21063,7 +21104,7 @@
       <c r="AF85" s="28"/>
       <c r="AG85" s="28"/>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" s="43" t="s">
         <v>310</v>
       </c>
@@ -21150,7 +21191,7 @@
       <c r="AF86" s="28"/>
       <c r="AG86" s="28"/>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" s="43" t="s">
         <v>313</v>
       </c>
@@ -21237,7 +21278,7 @@
       <c r="AF87" s="28"/>
       <c r="AG87" s="28"/>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" s="43" t="s">
         <v>316</v>
       </c>
@@ -21324,7 +21365,7 @@
       <c r="AF88" s="28"/>
       <c r="AG88" s="28"/>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" s="43" t="s">
         <v>319</v>
       </c>
@@ -21411,7 +21452,7 @@
       <c r="AF89" s="28"/>
       <c r="AG89" s="28"/>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" s="43" t="s">
         <v>322</v>
       </c>
@@ -21498,7 +21539,7 @@
       <c r="AF90" s="28"/>
       <c r="AG90" s="28"/>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" s="43" t="s">
         <v>324</v>
       </c>
@@ -21585,7 +21626,7 @@
       <c r="AF91" s="28"/>
       <c r="AG91" s="28"/>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" s="43" t="s">
         <v>327</v>
       </c>
@@ -21672,7 +21713,7 @@
       <c r="AF92" s="28"/>
       <c r="AG92" s="28"/>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" s="43" t="s">
         <v>330</v>
       </c>
@@ -21759,7 +21800,7 @@
       <c r="AF93" s="28"/>
       <c r="AG93" s="28"/>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" s="43" t="s">
         <v>332</v>
       </c>
@@ -21846,7 +21887,7 @@
       <c r="AF94" s="28"/>
       <c r="AG94" s="28"/>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" s="43" t="s">
         <v>334</v>
       </c>
@@ -21933,7 +21974,7 @@
       <c r="AF95" s="28"/>
       <c r="AG95" s="28"/>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" s="43" t="s">
         <v>336</v>
       </c>
@@ -22020,7 +22061,7 @@
       <c r="AF96" s="28"/>
       <c r="AG96" s="28"/>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" s="43" t="s">
         <v>338</v>
       </c>
@@ -22107,7 +22148,7 @@
       <c r="AF97" s="28"/>
       <c r="AG97" s="28"/>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" s="43" t="s">
         <v>340</v>
       </c>
@@ -22194,7 +22235,7 @@
       <c r="AF98" s="28"/>
       <c r="AG98" s="28"/>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" s="43" t="s">
         <v>342</v>
       </c>
@@ -22281,7 +22322,7 @@
       <c r="AF99" s="28"/>
       <c r="AG99" s="28"/>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" s="43" t="s">
         <v>344</v>
       </c>
@@ -22368,7 +22409,7 @@
       <c r="AF100" s="28"/>
       <c r="AG100" s="28"/>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" s="43" t="s">
         <v>597</v>
       </c>
@@ -22455,7 +22496,7 @@
       <c r="AF101" s="28"/>
       <c r="AG101" s="28"/>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" s="43" t="s">
         <v>348</v>
       </c>
@@ -22542,7 +22583,7 @@
       <c r="AF102" s="28"/>
       <c r="AG102" s="28"/>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" s="43" t="s">
         <v>352</v>
       </c>
@@ -22629,7 +22670,7 @@
       <c r="AF103" s="28"/>
       <c r="AG103" s="28"/>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" s="43" t="s">
         <v>355</v>
       </c>
@@ -22716,7 +22757,7 @@
       <c r="AF104" s="28"/>
       <c r="AG104" s="28"/>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" s="43" t="s">
         <v>358</v>
       </c>
@@ -22803,7 +22844,7 @@
       <c r="AF105" s="28"/>
       <c r="AG105" s="28"/>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" s="43" t="s">
         <v>361</v>
       </c>
@@ -22890,7 +22931,7 @@
       <c r="AF106" s="28"/>
       <c r="AG106" s="28"/>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" s="43" t="s">
         <v>364</v>
       </c>
@@ -22977,7 +23018,7 @@
       <c r="AF107" s="28"/>
       <c r="AG107" s="28"/>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" s="43" t="s">
         <v>367</v>
       </c>
@@ -23064,7 +23105,7 @@
       <c r="AF108" s="28"/>
       <c r="AG108" s="28"/>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" s="43" t="s">
         <v>369</v>
       </c>
@@ -23151,7 +23192,7 @@
       <c r="AF109" s="28"/>
       <c r="AG109" s="28"/>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" s="43" t="s">
         <v>371</v>
       </c>
@@ -23238,7 +23279,7 @@
       <c r="AF110" s="28"/>
       <c r="AG110" s="28"/>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" s="43" t="s">
         <v>598</v>
       </c>
@@ -23325,7 +23366,7 @@
       <c r="AF111" s="28"/>
       <c r="AG111" s="28"/>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" s="43" t="s">
         <v>682</v>
       </c>
@@ -23412,7 +23453,7 @@
       <c r="AF112" s="28"/>
       <c r="AG112" s="28"/>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" s="43" t="s">
         <v>685</v>
       </c>
@@ -23499,7 +23540,7 @@
       <c r="AF113" s="28"/>
       <c r="AG113" s="28"/>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" s="43" t="s">
         <v>688</v>
       </c>
@@ -23586,7 +23627,7 @@
       <c r="AF114" s="28"/>
       <c r="AG114" s="28"/>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" s="43" t="s">
         <v>691</v>
       </c>
@@ -23673,7 +23714,7 @@
       <c r="AF115" s="28"/>
       <c r="AG115" s="28"/>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" s="43" t="s">
         <v>378</v>
       </c>
@@ -23760,7 +23801,7 @@
       <c r="AF116" s="28"/>
       <c r="AG116" s="28"/>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" s="43" t="s">
         <v>383</v>
       </c>
@@ -23847,7 +23888,7 @@
       <c r="AF117" s="28"/>
       <c r="AG117" s="28"/>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" s="43" t="s">
         <v>397</v>
       </c>
@@ -23934,7 +23975,7 @@
       <c r="AF118" s="28"/>
       <c r="AG118" s="28"/>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" s="43" t="s">
         <v>399</v>
       </c>
@@ -24021,7 +24062,7 @@
       <c r="AF119" s="28"/>
       <c r="AG119" s="28"/>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" s="43" t="s">
         <v>400</v>
       </c>
@@ -24108,7 +24149,7 @@
       <c r="AF120" s="28"/>
       <c r="AG120" s="28"/>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" s="43" t="s">
         <v>401</v>
       </c>
@@ -24195,7 +24236,7 @@
       <c r="AF121" s="28"/>
       <c r="AG121" s="28"/>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" s="43" t="s">
         <v>402</v>
       </c>
@@ -24282,7 +24323,7 @@
       <c r="AF122" s="28"/>
       <c r="AG122" s="28"/>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" s="43" t="s">
         <v>403</v>
       </c>
@@ -24369,7 +24410,7 @@
       <c r="AF123" s="28"/>
       <c r="AG123" s="28"/>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" s="43" t="s">
         <v>405</v>
       </c>
@@ -24456,7 +24497,7 @@
       <c r="AF124" s="28"/>
       <c r="AG124" s="28"/>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" s="43" t="s">
         <v>407</v>
       </c>
@@ -24543,7 +24584,7 @@
       <c r="AF125" s="28"/>
       <c r="AG125" s="28"/>
     </row>
-    <row r="126" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A126" s="56" t="s">
         <v>413</v>
       </c>
@@ -24630,7 +24671,7 @@
       <c r="AF126" s="28"/>
       <c r="AG126" s="28"/>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" s="43" t="s">
         <v>417</v>
       </c>
@@ -24717,7 +24758,7 @@
       <c r="AF127" s="28"/>
       <c r="AG127" s="28"/>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" s="43" t="s">
         <v>420</v>
       </c>
@@ -24804,7 +24845,7 @@
       <c r="AF128" s="28"/>
       <c r="AG128" s="28"/>
     </row>
-    <row r="129" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A129" s="43" t="s">
         <v>422</v>
       </c>
@@ -24891,7 +24932,7 @@
       <c r="AF129" s="28"/>
       <c r="AG129" s="28"/>
     </row>
-    <row r="130" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A130" s="43" t="s">
         <v>424</v>
       </c>
@@ -24978,7 +25019,7 @@
       <c r="AF130" s="28"/>
       <c r="AG130" s="28"/>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" s="43" t="s">
         <v>427</v>
       </c>
@@ -25065,7 +25106,7 @@
       <c r="AF131" s="28"/>
       <c r="AG131" s="28"/>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" s="43" t="s">
         <v>430</v>
       </c>
@@ -25152,7 +25193,7 @@
       <c r="AF132" s="28"/>
       <c r="AG132" s="28"/>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" s="43" t="s">
         <v>433</v>
       </c>
@@ -25239,7 +25280,7 @@
       <c r="AF133" s="28"/>
       <c r="AG133" s="28"/>
     </row>
-    <row r="134" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A134" s="43" t="s">
         <v>436</v>
       </c>
@@ -25326,7 +25367,7 @@
       <c r="AF134" s="28"/>
       <c r="AG134" s="28"/>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" s="43" t="s">
         <v>438</v>
       </c>
@@ -25413,7 +25454,7 @@
       <c r="AF135" s="28"/>
       <c r="AG135" s="28"/>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" s="43" t="s">
         <v>695</v>
       </c>
@@ -25500,7 +25541,7 @@
       <c r="AF136" s="28"/>
       <c r="AG136" s="28"/>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" s="43" t="s">
         <v>397</v>
       </c>
@@ -25587,7 +25628,7 @@
       <c r="AF137" s="28"/>
       <c r="AG137" s="28"/>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" s="43" t="s">
         <v>399</v>
       </c>
@@ -25674,7 +25715,7 @@
       <c r="AF138" s="28"/>
       <c r="AG138" s="28"/>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" s="43" t="s">
         <v>400</v>
       </c>
@@ -25761,7 +25802,7 @@
       <c r="AF139" s="28"/>
       <c r="AG139" s="28"/>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" s="43" t="s">
         <v>401</v>
       </c>
@@ -25848,7 +25889,7 @@
       <c r="AF140" s="28"/>
       <c r="AG140" s="28"/>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" s="43" t="s">
         <v>402</v>
       </c>
@@ -25935,7 +25976,7 @@
       <c r="AF141" s="28"/>
       <c r="AG141" s="28"/>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" s="43" t="s">
         <v>403</v>
       </c>
@@ -26022,7 +26063,7 @@
       <c r="AF142" s="28"/>
       <c r="AG142" s="28"/>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" s="43" t="s">
         <v>405</v>
       </c>
@@ -26109,7 +26150,7 @@
       <c r="AF143" s="28"/>
       <c r="AG143" s="28"/>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" s="43" t="s">
         <v>442</v>
       </c>
@@ -26196,7 +26237,7 @@
       <c r="AF144" s="28"/>
       <c r="AG144" s="28"/>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" s="43" t="s">
         <v>446</v>
       </c>
@@ -26283,7 +26324,7 @@
       <c r="AF145" s="28"/>
       <c r="AG145" s="28"/>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" s="43" t="s">
         <v>449</v>
       </c>
@@ -26370,7 +26411,7 @@
       <c r="AF146" s="28"/>
       <c r="AG146" s="28"/>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" s="43" t="s">
         <v>451</v>
       </c>
@@ -26457,7 +26498,7 @@
       <c r="AF147" s="28"/>
       <c r="AG147" s="28"/>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" s="43" t="s">
         <v>454</v>
       </c>
@@ -26544,7 +26585,7 @@
       <c r="AF148" s="28"/>
       <c r="AG148" s="28"/>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" s="43" t="s">
         <v>457</v>
       </c>
@@ -26631,7 +26672,7 @@
       <c r="AF149" s="28"/>
       <c r="AG149" s="28"/>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" s="43" t="s">
         <v>460</v>
       </c>
@@ -26718,7 +26759,7 @@
       <c r="AF150" s="28"/>
       <c r="AG150" s="28"/>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" s="43" t="s">
         <v>463</v>
       </c>
@@ -26805,7 +26846,7 @@
       <c r="AF151" s="28"/>
       <c r="AG151" s="28"/>
     </row>
-    <row r="152" spans="1:33" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:33" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="43" t="s">
         <v>466</v>
       </c>
@@ -26892,7 +26933,7 @@
       <c r="AF152" s="28"/>
       <c r="AG152" s="28"/>
     </row>
-    <row r="153" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="43" t="s">
         <v>469</v>
       </c>
@@ -26979,7 +27020,7 @@
       <c r="AF153" s="28"/>
       <c r="AG153" s="28"/>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" s="43" t="s">
         <v>509</v>
       </c>
@@ -27066,7 +27107,7 @@
       <c r="AF154" s="28"/>
       <c r="AG154" s="28"/>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" s="71" t="s">
         <v>539</v>
       </c>
@@ -27153,7 +27194,7 @@
       <c r="AF155" s="28"/>
       <c r="AG155" s="28"/>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" s="71" t="s">
         <v>543</v>
       </c>
@@ -27240,7 +27281,7 @@
       <c r="AF156" s="28"/>
       <c r="AG156" s="28"/>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" s="71" t="s">
         <v>546</v>
       </c>
@@ -27327,7 +27368,7 @@
       <c r="AF157" s="28"/>
       <c r="AG157" s="28"/>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" s="71" t="s">
         <v>549</v>
       </c>
@@ -27414,7 +27455,7 @@
       <c r="AF158" s="28"/>
       <c r="AG158" s="28"/>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" s="71" t="s">
         <v>551</v>
       </c>
@@ -27501,7 +27542,7 @@
       <c r="AF159" s="28"/>
       <c r="AG159" s="28"/>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160" s="71" t="s">
         <v>553</v>
       </c>
@@ -27588,7 +27629,7 @@
       <c r="AF160" s="28"/>
       <c r="AG160" s="28"/>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161" s="71" t="s">
         <v>555</v>
       </c>
@@ -27675,7 +27716,7 @@
       <c r="AF161" s="28"/>
       <c r="AG161" s="28"/>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162" s="71" t="s">
         <v>557</v>
       </c>
@@ -27762,7 +27803,7 @@
       <c r="AF162" s="28"/>
       <c r="AG162" s="28"/>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163" s="71" t="s">
         <v>559</v>
       </c>
@@ -27849,7 +27890,7 @@
       <c r="AF163" s="28"/>
       <c r="AG163" s="28"/>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164" s="71" t="s">
         <v>562</v>
       </c>
@@ -27936,7 +27977,7 @@
       <c r="AF164" s="28"/>
       <c r="AG164" s="28"/>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A165" s="71" t="s">
         <v>565</v>
       </c>
@@ -28023,7 +28064,7 @@
       <c r="AF165" s="28"/>
       <c r="AG165" s="28"/>
     </row>
-    <row r="166" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A166" s="71" t="s">
         <v>568</v>
       </c>
@@ -28110,7 +28151,7 @@
       <c r="AF166" s="28"/>
       <c r="AG166" s="28"/>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A167" s="71" t="s">
         <v>571</v>
       </c>
@@ -28197,7 +28238,7 @@
       <c r="AF167" s="28"/>
       <c r="AG167" s="28"/>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A168" s="71" t="s">
         <v>574</v>
       </c>
@@ -28284,7 +28325,7 @@
       <c r="AF168" s="28"/>
       <c r="AG168" s="28"/>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A169" s="71" t="s">
         <v>577</v>
       </c>
@@ -28371,7 +28412,7 @@
       <c r="AF169" s="28"/>
       <c r="AG169" s="28"/>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A170" s="71" t="s">
         <v>579</v>
       </c>
@@ -28458,7 +28499,7 @@
       <c r="AF170" s="28"/>
       <c r="AG170" s="28"/>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A171" s="71" t="s">
         <v>581</v>
       </c>
@@ -28545,7 +28586,7 @@
       <c r="AF171" s="28"/>
       <c r="AG171" s="28"/>
     </row>
-    <row r="172" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A172" s="71" t="s">
         <v>584</v>
       </c>
@@ -28632,7 +28673,7 @@
       <c r="AF172" s="28"/>
       <c r="AG172" s="28"/>
     </row>
-    <row r="173" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A173" s="71" t="s">
         <v>873</v>
       </c>
@@ -28719,7 +28760,7 @@
       <c r="AF173" s="28"/>
       <c r="AG173" s="28"/>
     </row>
-    <row r="174" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A174" s="71" t="s">
         <v>876</v>
       </c>
@@ -28806,7 +28847,7 @@
       <c r="AF174" s="28"/>
       <c r="AG174" s="28"/>
     </row>
-    <row r="175" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A175" s="71" t="s">
         <v>879</v>
       </c>
@@ -28893,7 +28934,7 @@
       <c r="AF175" s="28"/>
       <c r="AG175" s="28"/>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A176" s="71" t="s">
         <v>175</v>
       </c>
@@ -28986,7 +29027,7 @@
       <c r="AF176" s="28"/>
       <c r="AG176" s="28"/>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="71" t="s">
         <v>179</v>
       </c>
@@ -29081,7 +29122,7 @@
       <c r="AF177" s="28"/>
       <c r="AG177" s="28"/>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A178" s="71" t="s">
         <v>182</v>
       </c>
@@ -29176,7 +29217,7 @@
       <c r="AF178" s="28"/>
       <c r="AG178" s="28"/>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A179" s="71" t="s">
         <v>185</v>
       </c>
@@ -29269,7 +29310,7 @@
       <c r="AF179" s="28"/>
       <c r="AG179" s="28"/>
     </row>
-    <row r="180" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="71" t="s">
         <v>188</v>
       </c>
@@ -29364,7 +29405,7 @@
       <c r="AF180" s="28"/>
       <c r="AG180" s="28"/>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="71" t="s">
         <v>190</v>
       </c>
@@ -29459,7 +29500,7 @@
       <c r="AF181" s="28"/>
       <c r="AG181" s="28"/>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A182" s="71" t="s">
         <v>193</v>
       </c>
@@ -29554,7 +29595,7 @@
       <c r="AF182" s="28"/>
       <c r="AG182" s="28"/>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A183" s="71" t="s">
         <v>196</v>
       </c>
@@ -29649,7 +29690,7 @@
       <c r="AF183" s="28"/>
       <c r="AG183" s="28"/>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A184" s="71" t="s">
         <v>607</v>
       </c>
@@ -29744,7 +29785,7 @@
       <c r="AF184" s="28"/>
       <c r="AG184" s="28"/>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A185" s="71" t="s">
         <v>611</v>
       </c>
@@ -29841,7 +29882,7 @@
       </c>
       <c r="AG185" s="28"/>
     </row>
-    <row r="186" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A186" s="71" t="s">
         <v>615</v>
       </c>
@@ -29938,7 +29979,7 @@
       </c>
       <c r="AG186" s="28"/>
     </row>
-    <row r="187" spans="1:33" ht="27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A187" s="71" t="s">
         <v>621</v>
       </c>
@@ -30035,7 +30076,7 @@
       </c>
       <c r="AG187" s="28"/>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A188" s="71" t="s">
         <v>622</v>
       </c>
@@ -30132,7 +30173,7 @@
       <c r="AF188" s="28"/>
       <c r="AG188" s="28"/>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A189" s="71" t="s">
         <v>628</v>
       </c>
@@ -30227,7 +30268,7 @@
       <c r="AF189" s="28"/>
       <c r="AG189" s="28"/>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A190" s="71" t="s">
         <v>825</v>
       </c>
@@ -30322,7 +30363,7 @@
       <c r="AF190" s="28"/>
       <c r="AG190" s="28"/>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A191" s="71" t="s">
         <v>826</v>
       </c>
@@ -30417,7 +30458,7 @@
       <c r="AF191" s="28"/>
       <c r="AG191" s="28"/>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A192" s="71" t="s">
         <v>632</v>
       </c>
@@ -30512,7 +30553,7 @@
       <c r="AF192" s="28"/>
       <c r="AG192" s="28"/>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A193" s="71" t="s">
         <v>634</v>
       </c>
@@ -30607,7 +30648,7 @@
       <c r="AF193" s="28"/>
       <c r="AG193" s="28"/>
     </row>
-    <row r="194" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A194" s="71" t="s">
         <v>640</v>
       </c>
@@ -30702,7 +30743,7 @@
       <c r="AF194" s="28"/>
       <c r="AG194" s="28"/>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A195" s="71" t="s">
         <v>641</v>
       </c>
@@ -30797,7 +30838,7 @@
       <c r="AF195" s="28"/>
       <c r="AG195" s="28"/>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A196" s="71" t="s">
         <v>646</v>
       </c>
@@ -30892,7 +30933,7 @@
       <c r="AF196" s="28"/>
       <c r="AG196" s="28"/>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A197" s="71" t="s">
         <v>648</v>
       </c>
@@ -30987,7 +31028,7 @@
       <c r="AF197" s="28"/>
       <c r="AG197" s="28"/>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A198" s="71" t="s">
         <v>654</v>
       </c>
@@ -31082,7 +31123,7 @@
       <c r="AF198" s="28"/>
       <c r="AG198" s="28"/>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A199" s="71" t="s">
         <v>657</v>
       </c>
@@ -31177,7 +31218,7 @@
       <c r="AF199" s="28"/>
       <c r="AG199" s="28"/>
     </row>
-    <row r="200" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A200" s="71" t="s">
         <v>658</v>
       </c>
@@ -31272,7 +31313,7 @@
       <c r="AF200" s="28"/>
       <c r="AG200" s="28"/>
     </row>
-    <row r="201" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A201" s="71" t="s">
         <v>663</v>
       </c>
@@ -31367,7 +31408,7 @@
       <c r="AF201" s="28"/>
       <c r="AG201" s="28"/>
     </row>
-    <row r="202" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A202" s="71" t="s">
         <v>668</v>
       </c>
@@ -31462,7 +31503,7 @@
       <c r="AF202" s="28"/>
       <c r="AG202" s="28"/>
     </row>
-    <row r="203" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A203" s="71" t="s">
         <v>669</v>
       </c>
@@ -31557,7 +31598,7 @@
       <c r="AF203" s="28"/>
       <c r="AG203" s="28"/>
     </row>
-    <row r="204" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A204" s="71" t="s">
         <v>855</v>
       </c>
@@ -31652,7 +31693,7 @@
       <c r="AF204" s="28"/>
       <c r="AG204" s="28"/>
     </row>
-    <row r="205" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A205" s="71" t="s">
         <v>858</v>
       </c>
@@ -31747,7 +31788,7 @@
       <c r="AF205" s="28"/>
       <c r="AG205" s="28"/>
     </row>
-    <row r="206" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A206" s="71" t="s">
         <v>859</v>
       </c>
@@ -31842,7 +31883,7 @@
       <c r="AF206" s="28"/>
       <c r="AG206" s="28"/>
     </row>
-    <row r="207" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A207" s="71" t="s">
         <v>710</v>
       </c>
@@ -31937,7 +31978,7 @@
       <c r="AF207" s="28"/>
       <c r="AG207" s="28"/>
     </row>
-    <row r="208" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A208" s="71" t="s">
         <v>713</v>
       </c>
@@ -32032,7 +32073,7 @@
       <c r="AF208" s="28"/>
       <c r="AG208" s="28"/>
     </row>
-    <row r="209" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A209" s="71" t="s">
         <v>715</v>
       </c>
@@ -32127,7 +32168,7 @@
       <c r="AF209" s="28"/>
       <c r="AG209" s="28"/>
     </row>
-    <row r="210" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A210" s="71" t="s">
         <v>753</v>
       </c>
@@ -32222,7 +32263,7 @@
       <c r="AF210" s="28"/>
       <c r="AG210" s="28"/>
     </row>
-    <row r="211" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A211" s="71" t="s">
         <v>842</v>
       </c>
@@ -32317,7 +32358,7 @@
       <c r="AF211" s="28"/>
       <c r="AG211" s="28"/>
     </row>
-    <row r="212" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A212" s="71" t="s">
         <v>843</v>
       </c>
@@ -32412,7 +32453,7 @@
       <c r="AF212" s="28"/>
       <c r="AG212" s="28"/>
     </row>
-    <row r="213" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A213" s="71" t="s">
         <v>718</v>
       </c>
@@ -32507,7 +32548,7 @@
       <c r="AF213" s="28"/>
       <c r="AG213" s="28"/>
     </row>
-    <row r="214" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A214" s="71" t="s">
         <v>724</v>
       </c>
@@ -32602,7 +32643,7 @@
       <c r="AF214" s="28"/>
       <c r="AG214" s="28"/>
     </row>
-    <row r="215" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A215" s="71" t="s">
         <v>725</v>
       </c>
@@ -32697,7 +32738,7 @@
       <c r="AF215" s="28"/>
       <c r="AG215" s="28"/>
     </row>
-    <row r="216" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A216" s="71" t="s">
         <v>730</v>
       </c>
@@ -32792,7 +32833,7 @@
       <c r="AF216" s="28"/>
       <c r="AG216" s="28"/>
     </row>
-    <row r="217" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A217" s="71" t="s">
         <v>731</v>
       </c>
@@ -32887,7 +32928,7 @@
       <c r="AF217" s="28"/>
       <c r="AG217" s="28"/>
     </row>
-    <row r="218" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A218" s="71" t="s">
         <v>732</v>
       </c>
@@ -32982,7 +33023,7 @@
       <c r="AF218" s="28"/>
       <c r="AG218" s="28"/>
     </row>
-    <row r="219" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A219" s="71" t="s">
         <v>737</v>
       </c>
@@ -33077,7 +33118,7 @@
       <c r="AF219" s="28"/>
       <c r="AG219" s="28"/>
     </row>
-    <row r="220" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A220" s="71" t="s">
         <v>740</v>
       </c>
@@ -33172,7 +33213,7 @@
       <c r="AF220" s="28"/>
       <c r="AG220" s="28"/>
     </row>
-    <row r="221" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A221" s="71" t="s">
         <v>745</v>
       </c>
@@ -33267,7 +33308,7 @@
       <c r="AF221" s="28"/>
       <c r="AG221" s="28"/>
     </row>
-    <row r="222" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A222" s="71" t="s">
         <v>748</v>
       </c>
@@ -33362,7 +33403,7 @@
       <c r="AF222" s="28"/>
       <c r="AG222" s="28"/>
     </row>
-    <row r="223" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A223" s="71" t="s">
         <v>749</v>
       </c>
@@ -33457,7 +33498,7 @@
       <c r="AF223" s="28"/>
       <c r="AG223" s="28"/>
     </row>
-    <row r="224" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A224" s="71" t="s">
         <v>755</v>
       </c>
@@ -33552,7 +33593,7 @@
       <c r="AF224" s="28"/>
       <c r="AG224" s="28"/>
     </row>
-    <row r="225" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A225" s="71" t="s">
         <v>767</v>
       </c>
@@ -33647,7 +33688,7 @@
       <c r="AF225" s="28"/>
       <c r="AG225" s="28"/>
     </row>
-    <row r="226" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A226" s="71" t="s">
         <v>772</v>
       </c>
@@ -33742,7 +33783,7 @@
       <c r="AF226" s="28"/>
       <c r="AG226" s="28"/>
     </row>
-    <row r="227" spans="1:33" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:33" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="71" t="s">
         <v>777</v>
       </c>
@@ -33837,7 +33878,7 @@
       <c r="AF227" s="28"/>
       <c r="AG227" s="28"/>
     </row>
-    <row r="228" spans="1:33" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="71" t="s">
         <v>779</v>
       </c>
@@ -33932,7 +33973,7 @@
       <c r="AF228" s="28"/>
       <c r="AG228" s="28"/>
     </row>
-    <row r="229" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A229" s="71" t="s">
         <v>781</v>
       </c>
@@ -34027,7 +34068,7 @@
       <c r="AF229" s="28"/>
       <c r="AG229" s="28"/>
     </row>
-    <row r="230" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A230" s="71" t="s">
         <v>786</v>
       </c>
@@ -34122,7 +34163,7 @@
       <c r="AF230" s="28"/>
       <c r="AG230" s="28"/>
     </row>
-    <row r="231" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="71" t="s">
         <v>788</v>
       </c>
@@ -34217,7 +34258,7 @@
       <c r="AF231" s="28"/>
       <c r="AG231" s="28"/>
     </row>
-    <row r="232" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="71" t="s">
         <v>792</v>
       </c>
@@ -34312,7 +34353,7 @@
       <c r="AF232" s="28"/>
       <c r="AG232" s="28"/>
     </row>
-    <row r="233" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:33" ht="30" x14ac:dyDescent="0.25">
       <c r="A233" s="71" t="s">
         <v>797</v>
       </c>
@@ -34407,7 +34448,7 @@
       <c r="AF233" s="28"/>
       <c r="AG233" s="28"/>
     </row>
-    <row r="234" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="71" t="s">
         <v>800</v>
       </c>
@@ -34502,7 +34543,7 @@
       <c r="AF234" s="28"/>
       <c r="AG234" s="28"/>
     </row>
-    <row r="235" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="71" t="s">
         <v>801</v>
       </c>
@@ -34597,7 +34638,7 @@
       <c r="AF235" s="28"/>
       <c r="AG235" s="28"/>
     </row>
-    <row r="236" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="71" t="s">
         <v>806</v>
       </c>
@@ -34692,7 +34733,7 @@
       <c r="AF236" s="28"/>
       <c r="AG236" s="28"/>
     </row>
-    <row r="237" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="71" t="s">
         <v>882</v>
       </c>
@@ -34787,7 +34828,7 @@
       <c r="AF237" s="28"/>
       <c r="AG237" s="28"/>
     </row>
-    <row r="238" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="71" t="s">
         <v>883</v>
       </c>
@@ -34882,7 +34923,7 @@
       <c r="AF238" s="28"/>
       <c r="AG238" s="28"/>
     </row>
-    <row r="239" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="71" t="s">
         <v>884</v>
       </c>
@@ -34977,7 +35018,7 @@
       <c r="AF239" s="28"/>
       <c r="AG239" s="28"/>
     </row>
-    <row r="240" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="71" t="s">
         <v>846</v>
       </c>
@@ -35072,7 +35113,7 @@
       <c r="AF240" s="28"/>
       <c r="AG240" s="28"/>
     </row>
-    <row r="241" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="71" t="s">
         <v>850</v>
       </c>
@@ -35167,7 +35208,7 @@
       <c r="AF241" s="28"/>
       <c r="AG241" s="28"/>
     </row>
-    <row r="242" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="71" t="s">
         <v>816</v>
       </c>
@@ -35262,7 +35303,7 @@
       <c r="AF242" s="28"/>
       <c r="AG242" s="28"/>
     </row>
-    <row r="243" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="71" t="s">
         <v>820</v>
       </c>
@@ -35357,7 +35398,7 @@
       <c r="AF243" s="28"/>
       <c r="AG243" s="28"/>
     </row>
-    <row r="244" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="71" t="s">
         <v>822</v>
       </c>
@@ -35452,7 +35493,7 @@
       <c r="AF244" s="28"/>
       <c r="AG244" s="28"/>
     </row>
-    <row r="245" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="71" t="s">
         <v>835</v>
       </c>
@@ -35547,7 +35588,7 @@
       <c r="AF245" s="28"/>
       <c r="AG245" s="28"/>
     </row>
-    <row r="246" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="71" t="s">
         <v>837</v>
       </c>
@@ -35642,7 +35683,7 @@
       <c r="AF246" s="28"/>
       <c r="AG246" s="28"/>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A247" s="28" t="s">
         <v>863</v>
       </c>
@@ -35737,7 +35778,7 @@
       <c r="AF247" s="28"/>
       <c r="AG247" s="28"/>
     </row>
-    <row r="248" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A248" s="28" t="s">
         <v>870</v>
       </c>
@@ -35832,7 +35873,7 @@
       <c r="AF248" s="28"/>
       <c r="AG248" s="28"/>
     </row>
-    <row r="249" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A249" s="28" t="s">
         <v>889</v>
       </c>
@@ -35927,7 +35968,7 @@
       <c r="AF249" s="28"/>
       <c r="AG249" s="28"/>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A250" s="28" t="s">
         <v>916</v>
       </c>
@@ -36022,7 +36063,7 @@
       <c r="AF250" s="28"/>
       <c r="AG250" s="28"/>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A251" s="28" t="s">
         <v>923</v>
       </c>
@@ -36117,7 +36158,7 @@
       <c r="AF251" s="28"/>
       <c r="AG251" s="28"/>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A252" s="28" t="s">
         <v>934</v>
       </c>
@@ -36212,7 +36253,7 @@
       <c r="AF252" s="28"/>
       <c r="AG252" s="28"/>
     </row>
-    <row r="253" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A253" s="28" t="s">
         <v>939</v>
       </c>
@@ -36307,7 +36348,7 @@
       <c r="AF253" s="28"/>
       <c r="AG253" s="28"/>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A254" s="28" t="s">
         <v>943</v>
       </c>
@@ -36402,7 +36443,7 @@
       <c r="AF254" s="28"/>
       <c r="AG254" s="28"/>
     </row>
-    <row r="255" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A255" s="28" t="s">
         <v>946</v>
       </c>
@@ -36497,7 +36538,7 @@
       <c r="AF255" s="28"/>
       <c r="AG255" s="28"/>
     </row>
-    <row r="256" spans="1:33" ht="18" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:33" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A256" s="83" t="s">
         <v>950</v>
       </c>
@@ -36592,7 +36633,7 @@
       <c r="AF256" s="28"/>
       <c r="AG256" s="28"/>
     </row>
-    <row r="257" spans="1:33" ht="18" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:33" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A257" s="83" t="s">
         <v>954</v>
       </c>
@@ -36687,7 +36728,7 @@
       <c r="AF257" s="28"/>
       <c r="AG257" s="28"/>
     </row>
-    <row r="258" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A258" s="28" t="s">
         <v>958</v>
       </c>
@@ -36788,7 +36829,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="259" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>969</v>
       </c>
@@ -36889,7 +36930,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="260" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>973</v>
       </c>
@@ -36990,7 +37031,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="261" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>976</v>
       </c>
@@ -37091,7 +37132,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="262" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>979</v>
       </c>
@@ -37192,7 +37233,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="263" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>984</v>
       </c>
@@ -37290,6 +37331,107 @@
         <v>22</v>
       </c>
       <c r="AG263" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="264" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>987</v>
+      </c>
+      <c r="B264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF264" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG264" s="28" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gowthamraj\git\ZlaataQAsever070526\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever36\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCC2C29-5F85-43B7-BBCA-AE2B92B03440}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B14D6B7-D4B2-4272-ABC4-BD75FD510A3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9464" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9507" uniqueCount="993">
   <si>
     <t>S.No</t>
   </si>
@@ -2990,6 +2990,21 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_Estimate_02</t>
+  </si>
+  <si>
+    <t>New Label</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_New_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_New_01</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Verify New Label functionality in user app.</t>
   </si>
 </sst>
 </file>
@@ -4479,21 +4494,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z288"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z290"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" customWidth="1"/>
-    <col min="4" max="4" width="118.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" customWidth="1"/>
+    <col min="4" max="4" width="118.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4525,7 +4540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="28">
         <v>1</v>
       </c>
@@ -4557,7 +4572,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="28">
         <v>2</v>
       </c>
@@ -4589,7 +4604,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="28">
         <v>3</v>
       </c>
@@ -4621,7 +4636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="28">
         <v>4</v>
       </c>
@@ -4653,7 +4668,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="28">
         <v>5</v>
       </c>
@@ -4685,7 +4700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="28">
         <v>6</v>
       </c>
@@ -4717,7 +4732,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="28">
         <v>7</v>
       </c>
@@ -4749,7 +4764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="28">
         <v>8</v>
       </c>
@@ -4781,7 +4796,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="28">
         <v>9</v>
       </c>
@@ -4813,7 +4828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="28">
         <v>10</v>
       </c>
@@ -4845,7 +4860,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="28">
         <v>11</v>
       </c>
@@ -4877,7 +4892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="28">
         <v>12</v>
       </c>
@@ -4909,7 +4924,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="28">
         <v>13</v>
       </c>
@@ -4941,7 +4956,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="28">
         <v>14</v>
       </c>
@@ -4973,7 +4988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="28">
         <v>15</v>
       </c>
@@ -5005,7 +5020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="28">
         <v>16</v>
       </c>
@@ -5037,7 +5052,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="28">
         <v>17</v>
       </c>
@@ -5069,7 +5084,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="28">
         <v>18</v>
       </c>
@@ -5101,7 +5116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="28">
         <v>19</v>
       </c>
@@ -5133,7 +5148,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="28">
         <v>20</v>
       </c>
@@ -5165,7 +5180,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="28">
         <v>21</v>
       </c>
@@ -5197,7 +5212,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>22</v>
       </c>
@@ -5229,7 +5244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="95" t="s">
         <v>156</v>
       </c>
@@ -5243,7 +5258,7 @@
       <c r="I24" s="96"/>
       <c r="J24" s="97"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>1</v>
       </c>
@@ -5275,7 +5290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>2</v>
       </c>
@@ -5307,7 +5322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>3</v>
       </c>
@@ -5339,7 +5354,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>4</v>
       </c>
@@ -5371,7 +5386,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>5</v>
       </c>
@@ -5403,7 +5418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>6</v>
       </c>
@@ -5435,7 +5450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>7</v>
       </c>
@@ -5467,7 +5482,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>8</v>
       </c>
@@ -5499,7 +5514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>9</v>
       </c>
@@ -5531,7 +5546,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>10</v>
       </c>
@@ -5563,7 +5578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>11</v>
       </c>
@@ -5595,7 +5610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>12</v>
       </c>
@@ -5627,7 +5642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="98" t="s">
         <v>172</v>
       </c>
@@ -5641,7 +5656,7 @@
       <c r="I37" s="99"/>
       <c r="J37" s="100"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>1</v>
       </c>
@@ -5673,7 +5688,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -5705,7 +5720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>3</v>
       </c>
@@ -5737,7 +5752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>4</v>
       </c>
@@ -5769,7 +5784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>5</v>
       </c>
@@ -5801,7 +5816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>6</v>
       </c>
@@ -5833,7 +5848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>7</v>
       </c>
@@ -5865,7 +5880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>8</v>
       </c>
@@ -5897,7 +5912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>9</v>
       </c>
@@ -5929,7 +5944,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>10</v>
       </c>
@@ -5961,7 +5976,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>11</v>
       </c>
@@ -5993,7 +6008,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>12</v>
       </c>
@@ -6025,7 +6040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>13</v>
       </c>
@@ -6057,7 +6072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>14</v>
       </c>
@@ -6089,7 +6104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>15</v>
       </c>
@@ -6121,7 +6136,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>16</v>
       </c>
@@ -6153,7 +6168,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>16</v>
       </c>
@@ -6185,7 +6200,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="98" t="s">
         <v>244</v>
       </c>
@@ -6199,7 +6214,7 @@
       <c r="I55" s="99"/>
       <c r="J55" s="100"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
         <v>1</v>
       </c>
@@ -6231,7 +6246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="25">
         <v>2</v>
       </c>
@@ -6263,7 +6278,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="25">
         <v>3</v>
       </c>
@@ -6295,7 +6310,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="25">
         <v>4</v>
       </c>
@@ -6327,7 +6342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="25">
         <v>5</v>
       </c>
@@ -6359,7 +6374,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="25">
         <v>6</v>
       </c>
@@ -6391,7 +6406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="25">
         <v>7</v>
       </c>
@@ -6423,7 +6438,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="25">
         <v>8</v>
       </c>
@@ -6455,7 +6470,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="25">
         <v>9</v>
       </c>
@@ -6487,7 +6502,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="25">
         <v>10</v>
       </c>
@@ -6519,7 +6534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="98" t="s">
         <v>246</v>
       </c>
@@ -6533,7 +6548,7 @@
       <c r="I66" s="99"/>
       <c r="J66" s="100"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
         <v>1</v>
       </c>
@@ -6565,7 +6580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="25">
         <v>2</v>
       </c>
@@ -6597,7 +6612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="25">
         <v>3</v>
       </c>
@@ -6629,7 +6644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="25">
         <v>4</v>
       </c>
@@ -6661,7 +6676,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="25">
         <v>5</v>
       </c>
@@ -6693,7 +6708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="25">
         <v>6</v>
       </c>
@@ -6725,7 +6740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="25">
         <v>7</v>
       </c>
@@ -6757,7 +6772,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="25">
         <v>8</v>
       </c>
@@ -6789,7 +6804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="25">
         <v>9</v>
       </c>
@@ -6821,7 +6836,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="25">
         <v>10</v>
       </c>
@@ -6853,7 +6868,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="25">
         <v>11</v>
       </c>
@@ -6885,7 +6900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="98" t="s">
         <v>345</v>
       </c>
@@ -6899,7 +6914,7 @@
       <c r="I78" s="99"/>
       <c r="J78" s="100"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
         <v>1</v>
       </c>
@@ -6931,7 +6946,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="25">
         <v>2</v>
       </c>
@@ -6963,7 +6978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="25">
         <v>3</v>
       </c>
@@ -6995,7 +7010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="25">
         <v>4</v>
       </c>
@@ -7027,7 +7042,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="25">
         <v>5</v>
       </c>
@@ -7059,7 +7074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="25">
         <v>6</v>
       </c>
@@ -7091,7 +7106,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="25">
         <v>7</v>
       </c>
@@ -7123,7 +7138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="25">
         <v>8</v>
       </c>
@@ -7155,7 +7170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="25">
         <v>9</v>
       </c>
@@ -7187,7 +7202,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="25">
         <v>10</v>
       </c>
@@ -7219,7 +7234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="25">
         <v>11</v>
       </c>
@@ -7251,7 +7266,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="25">
         <v>12</v>
       </c>
@@ -7283,7 +7298,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="25">
         <v>13</v>
       </c>
@@ -7315,7 +7330,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="25">
         <v>14</v>
       </c>
@@ -7347,7 +7362,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="25">
         <v>15</v>
       </c>
@@ -7379,7 +7394,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="25">
         <v>16</v>
       </c>
@@ -7411,7 +7426,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="25">
         <v>17</v>
       </c>
@@ -7443,7 +7458,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="25">
         <v>18</v>
       </c>
@@ -7475,7 +7490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="25">
         <v>19</v>
       </c>
@@ -7507,7 +7522,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="25">
         <v>20</v>
       </c>
@@ -7539,7 +7554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="25">
         <v>21</v>
       </c>
@@ -7571,7 +7586,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="25">
         <v>22</v>
       </c>
@@ -7603,7 +7618,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="25">
         <v>23</v>
       </c>
@@ -7635,7 +7650,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="25">
         <v>24</v>
       </c>
@@ -7667,7 +7682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="25">
         <v>25</v>
       </c>
@@ -7699,7 +7714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="25">
         <v>27</v>
       </c>
@@ -7731,7 +7746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="25">
         <v>28</v>
       </c>
@@ -7763,7 +7778,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="86" t="s">
         <v>374</v>
       </c>
@@ -7777,7 +7792,7 @@
       <c r="I106" s="86"/>
       <c r="J106" s="86"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
         <v>1</v>
       </c>
@@ -7809,7 +7824,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="25">
         <v>2</v>
       </c>
@@ -7841,7 +7856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="25">
         <v>3</v>
       </c>
@@ -7873,7 +7888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="25">
         <v>4</v>
       </c>
@@ -7905,7 +7920,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="25">
         <v>5</v>
       </c>
@@ -7937,7 +7952,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="25">
         <v>6</v>
       </c>
@@ -7969,7 +7984,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="25">
         <v>7</v>
       </c>
@@ -8001,7 +8016,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="25">
         <v>8</v>
       </c>
@@ -8033,7 +8048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="25">
         <v>9</v>
       </c>
@@ -8065,7 +8080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="25">
         <v>10</v>
       </c>
@@ -8097,7 +8112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="25">
         <v>11</v>
       </c>
@@ -8129,7 +8144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="25">
         <v>12</v>
       </c>
@@ -8175,7 +8190,7 @@
       <c r="W118" s="52"/>
       <c r="X118" s="52"/>
     </row>
-    <row r="119" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="25">
         <v>13</v>
       </c>
@@ -8221,7 +8236,7 @@
       <c r="W119" s="52"/>
       <c r="X119" s="52"/>
     </row>
-    <row r="120" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="25">
         <v>14</v>
       </c>
@@ -8267,7 +8282,7 @@
       <c r="W120" s="52"/>
       <c r="X120" s="52"/>
     </row>
-    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="87" t="s">
         <v>376</v>
       </c>
@@ -8295,7 +8310,7 @@
       <c r="W121" s="52"/>
       <c r="X121" s="52"/>
     </row>
-    <row r="122" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="25">
         <v>1</v>
       </c>
@@ -8341,7 +8356,7 @@
       <c r="W122" s="52"/>
       <c r="X122" s="52"/>
     </row>
-    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="87" t="s">
         <v>381</v>
       </c>
@@ -8369,7 +8384,7 @@
       <c r="W123" s="52"/>
       <c r="X123" s="52"/>
     </row>
-    <row r="124" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="25">
         <v>1</v>
       </c>
@@ -8415,7 +8430,7 @@
       <c r="W124" s="52"/>
       <c r="X124" s="52"/>
     </row>
-    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="87" t="s">
         <v>394</v>
       </c>
@@ -8429,7 +8444,7 @@
       <c r="I125" s="87"/>
       <c r="J125" s="87"/>
     </row>
-    <row r="126" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
         <v>1</v>
       </c>
@@ -8475,7 +8490,7 @@
       <c r="W126" s="55"/>
       <c r="X126" s="55"/>
     </row>
-    <row r="127" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="25">
         <v>2</v>
       </c>
@@ -8521,7 +8536,7 @@
       <c r="W127" s="52"/>
       <c r="X127" s="52"/>
     </row>
-    <row r="128" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="25">
         <v>3</v>
       </c>
@@ -8567,7 +8582,7 @@
       <c r="W128" s="52"/>
       <c r="X128" s="52"/>
     </row>
-    <row r="129" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="25">
         <v>4</v>
       </c>
@@ -8613,7 +8628,7 @@
       <c r="W129" s="52"/>
       <c r="X129" s="52"/>
     </row>
-    <row r="130" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="25">
         <v>5</v>
       </c>
@@ -8659,7 +8674,7 @@
       <c r="W130" s="52"/>
       <c r="X130" s="52"/>
     </row>
-    <row r="131" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="25">
         <v>6</v>
       </c>
@@ -8705,7 +8720,7 @@
       <c r="W131" s="52"/>
       <c r="X131" s="52"/>
     </row>
-    <row r="132" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="25">
         <v>7</v>
       </c>
@@ -8751,7 +8766,7 @@
       <c r="W132" s="52"/>
       <c r="X132" s="52"/>
     </row>
-    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="87" t="s">
         <v>411</v>
       </c>
@@ -8779,7 +8794,7 @@
       <c r="W133" s="52"/>
       <c r="X133" s="52"/>
     </row>
-    <row r="134" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="53">
         <v>11</v>
       </c>
@@ -8825,7 +8840,7 @@
       <c r="W134" s="52"/>
       <c r="X134" s="52"/>
     </row>
-    <row r="135" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="26">
         <v>2</v>
       </c>
@@ -8871,7 +8886,7 @@
       <c r="W135" s="52"/>
       <c r="X135" s="52"/>
     </row>
-    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="26">
         <v>3</v>
       </c>
@@ -8903,7 +8918,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="26">
         <v>4</v>
       </c>
@@ -8949,7 +8964,7 @@
       <c r="W137" s="52"/>
       <c r="X137" s="52"/>
     </row>
-    <row r="138" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="26">
         <v>5</v>
       </c>
@@ -8995,7 +9010,7 @@
       <c r="W138" s="52"/>
       <c r="X138" s="52"/>
     </row>
-    <row r="139" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="26">
         <v>6</v>
       </c>
@@ -9041,7 +9056,7 @@
       <c r="W139" s="52"/>
       <c r="X139" s="52"/>
     </row>
-    <row r="140" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="26">
         <v>7</v>
       </c>
@@ -9073,7 +9088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="26">
         <v>8</v>
       </c>
@@ -9119,7 +9134,7 @@
       <c r="W141" s="52"/>
       <c r="X141" s="52"/>
     </row>
-    <row r="142" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="26">
         <v>9</v>
       </c>
@@ -9165,7 +9180,7 @@
       <c r="W142" s="52"/>
       <c r="X142" s="52"/>
     </row>
-    <row r="143" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="26">
         <v>10</v>
       </c>
@@ -9211,7 +9226,7 @@
       <c r="W143" s="52"/>
       <c r="X143" s="52"/>
     </row>
-    <row r="144" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="26">
         <v>11</v>
       </c>
@@ -9257,7 +9272,7 @@
       <c r="W144" s="52"/>
       <c r="X144" s="52"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="92" t="s">
         <v>439</v>
       </c>
@@ -9285,7 +9300,7 @@
       <c r="W145" s="52"/>
       <c r="X145" s="52"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="25">
         <v>1</v>
       </c>
@@ -9331,7 +9346,7 @@
       <c r="W146" s="52"/>
       <c r="X146" s="52"/>
     </row>
-    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="25">
         <v>2</v>
       </c>
@@ -9363,7 +9378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A148" s="25">
         <v>3</v>
       </c>
@@ -9395,7 +9410,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="25">
         <v>4</v>
       </c>
@@ -9427,7 +9442,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="25">
         <v>5</v>
       </c>
@@ -9475,7 +9490,7 @@
       <c r="Y150" s="52"/>
       <c r="Z150" s="52"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="25">
         <v>6</v>
       </c>
@@ -9523,7 +9538,7 @@
       <c r="Y151" s="52"/>
       <c r="Z151" s="52"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="25">
         <v>7</v>
       </c>
@@ -9571,7 +9586,7 @@
       <c r="Y152" s="52"/>
       <c r="Z152" s="52"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="25">
         <v>8</v>
       </c>
@@ -9619,7 +9634,7 @@
       <c r="Y153" s="52"/>
       <c r="Z153" s="52"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="25">
         <v>9</v>
       </c>
@@ -9667,7 +9682,7 @@
       <c r="Y154" s="52"/>
       <c r="Z154" s="52"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="25">
         <v>10</v>
       </c>
@@ -9715,7 +9730,7 @@
       <c r="Y155" s="52"/>
       <c r="Z155" s="52"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="87" t="s">
         <v>510</v>
       </c>
@@ -9745,7 +9760,7 @@
       <c r="Y156" s="52"/>
       <c r="Z156" s="52"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="25">
         <v>1</v>
       </c>
@@ -9793,7 +9808,7 @@
       <c r="Y157" s="52"/>
       <c r="Z157" s="52"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="87" t="s">
         <v>536</v>
       </c>
@@ -9823,7 +9838,7 @@
       <c r="Y158" s="52"/>
       <c r="Z158" s="52"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="61">
         <v>1</v>
       </c>
@@ -9871,7 +9886,7 @@
       <c r="Y159" s="52"/>
       <c r="Z159" s="52"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="62">
         <v>2</v>
       </c>
@@ -9919,7 +9934,7 @@
       <c r="Y160" s="52"/>
       <c r="Z160" s="52"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="62">
         <v>3</v>
       </c>
@@ -9967,7 +9982,7 @@
       <c r="Y161" s="52"/>
       <c r="Z161" s="52"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="62">
         <v>4</v>
       </c>
@@ -10015,7 +10030,7 @@
       <c r="Y162" s="52"/>
       <c r="Z162" s="52"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="62">
         <v>5</v>
       </c>
@@ -10063,7 +10078,7 @@
       <c r="Y163" s="52"/>
       <c r="Z163" s="52"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="62">
         <v>6</v>
       </c>
@@ -10111,7 +10126,7 @@
       <c r="Y164" s="52"/>
       <c r="Z164" s="52"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="62">
         <v>7</v>
       </c>
@@ -10159,7 +10174,7 @@
       <c r="Y165" s="52"/>
       <c r="Z165" s="52"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="62">
         <v>8</v>
       </c>
@@ -10207,7 +10222,7 @@
       <c r="Y166" s="52"/>
       <c r="Z166" s="52"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="61">
         <v>9</v>
       </c>
@@ -10255,7 +10270,7 @@
       <c r="Y167" s="52"/>
       <c r="Z167" s="52"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="62">
         <v>10</v>
       </c>
@@ -10287,7 +10302,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="61">
         <v>11</v>
       </c>
@@ -10319,7 +10334,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="62">
         <v>12</v>
       </c>
@@ -10351,7 +10366,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="61">
         <v>13</v>
       </c>
@@ -10383,7 +10398,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="62">
         <v>14</v>
       </c>
@@ -10415,7 +10430,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="61">
         <v>15</v>
       </c>
@@ -10447,7 +10462,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="174" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="62">
         <v>16</v>
       </c>
@@ -10479,7 +10494,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="175" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="61">
         <v>17</v>
       </c>
@@ -10511,7 +10526,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="176" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="62">
         <v>18</v>
       </c>
@@ -10543,7 +10558,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="76">
         <v>19</v>
       </c>
@@ -10575,7 +10590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="76">
         <v>20</v>
       </c>
@@ -10607,7 +10622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="76">
         <v>21</v>
       </c>
@@ -10639,7 +10654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="87" t="s">
         <v>707</v>
       </c>
@@ -10653,7 +10668,7 @@
       <c r="I180" s="87"/>
       <c r="J180" s="87"/>
     </row>
-    <row r="181" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="62">
         <v>1</v>
       </c>
@@ -10685,7 +10700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="62">
         <v>2</v>
       </c>
@@ -10717,7 +10732,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="62">
         <v>3</v>
       </c>
@@ -10749,7 +10764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="62">
         <v>4</v>
       </c>
@@ -10781,7 +10796,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="62">
         <v>5</v>
       </c>
@@ -10813,7 +10828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="62">
         <v>6</v>
       </c>
@@ -10845,7 +10860,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="62">
         <v>7</v>
       </c>
@@ -10877,7 +10892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="62">
         <v>7</v>
       </c>
@@ -10909,7 +10924,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="1:10" s="28" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" s="28" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="62">
         <v>9</v>
       </c>
@@ -10941,7 +10956,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="89" t="s">
         <v>609</v>
       </c>
@@ -10955,7 +10970,7 @@
       <c r="I190" s="90"/>
       <c r="J190" s="91"/>
     </row>
-    <row r="191" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="62">
         <v>1</v>
       </c>
@@ -10987,7 +11002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="62">
         <v>2</v>
       </c>
@@ -11019,7 +11034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="62">
         <v>3</v>
       </c>
@@ -11051,7 +11066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="62">
         <v>4</v>
       </c>
@@ -11083,7 +11098,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="62">
         <v>5</v>
       </c>
@@ -11115,7 +11130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="62">
         <v>6</v>
       </c>
@@ -11147,7 +11162,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="62">
         <v>7</v>
       </c>
@@ -11179,7 +11194,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="85" t="s">
         <v>630</v>
       </c>
@@ -11193,7 +11208,7 @@
       <c r="I198" s="85"/>
       <c r="J198" s="85"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="43">
         <v>1</v>
       </c>
@@ -11225,7 +11240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="43">
         <v>2</v>
       </c>
@@ -11257,7 +11272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="43">
         <v>3</v>
       </c>
@@ -11289,7 +11304,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="43">
         <v>4</v>
       </c>
@@ -11321,7 +11336,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="85" t="s">
         <v>643</v>
       </c>
@@ -11335,7 +11350,7 @@
       <c r="I203" s="85"/>
       <c r="J203" s="85"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="43">
         <v>1</v>
       </c>
@@ -11367,7 +11382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="85" t="s">
         <v>649</v>
       </c>
@@ -11381,7 +11396,7 @@
       <c r="I205" s="85"/>
       <c r="J205" s="85"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="43">
         <v>1</v>
       </c>
@@ -11413,7 +11428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="43">
         <v>2</v>
       </c>
@@ -11445,7 +11460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="43">
         <v>3</v>
       </c>
@@ -11477,7 +11492,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="43">
         <v>4</v>
       </c>
@@ -11509,7 +11524,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="43">
         <v>5</v>
       </c>
@@ -11541,7 +11556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="43">
         <v>6</v>
       </c>
@@ -11573,7 +11588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="43">
         <v>7</v>
       </c>
@@ -11605,7 +11620,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="43">
         <v>8</v>
       </c>
@@ -11637,7 +11652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="43">
         <v>9</v>
       </c>
@@ -11669,7 +11684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="75"/>
       <c r="B215" s="75"/>
       <c r="C215" s="75"/>
@@ -11683,7 +11698,7 @@
       <c r="I215" s="75"/>
       <c r="J215" s="75"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="43">
         <v>1</v>
       </c>
@@ -11715,7 +11730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" s="74" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="73"/>
       <c r="B217" s="73"/>
       <c r="C217" s="73"/>
@@ -11729,7 +11744,7 @@
       <c r="I217" s="73"/>
       <c r="J217" s="73"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="43">
         <v>1</v>
       </c>
@@ -11761,7 +11776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="43">
         <v>2</v>
       </c>
@@ -11793,7 +11808,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="85" t="s">
         <v>711</v>
       </c>
@@ -11807,7 +11822,7 @@
       <c r="I220" s="85"/>
       <c r="J220" s="85"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="43">
         <v>1</v>
       </c>
@@ -11839,7 +11854,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="43">
         <v>2</v>
       </c>
@@ -11871,7 +11886,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="43">
         <v>3</v>
       </c>
@@ -11903,7 +11918,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="43">
         <v>4</v>
       </c>
@@ -11935,7 +11950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="43">
         <v>5</v>
       </c>
@@ -11967,7 +11982,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="85" t="s">
         <v>719</v>
       </c>
@@ -11981,7 +11996,7 @@
       <c r="I226" s="85"/>
       <c r="J226" s="85"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="43">
         <v>1</v>
       </c>
@@ -12013,7 +12028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="43">
         <v>2</v>
       </c>
@@ -12045,7 +12060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="43">
         <v>3</v>
       </c>
@@ -12077,7 +12092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="43">
         <v>4</v>
       </c>
@@ -12109,7 +12124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="43">
         <v>5</v>
       </c>
@@ -12141,7 +12156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="43">
         <v>6</v>
       </c>
@@ -12173,7 +12188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="43">
         <v>7</v>
       </c>
@@ -12205,7 +12220,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="43">
         <v>8</v>
       </c>
@@ -12237,7 +12252,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="43">
         <v>9</v>
       </c>
@@ -12269,7 +12284,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="43">
         <v>10</v>
       </c>
@@ -12301,7 +12316,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="43">
         <v>11</v>
       </c>
@@ -12333,7 +12348,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="85" t="s">
         <v>756</v>
       </c>
@@ -12347,7 +12362,7 @@
       <c r="I238" s="85"/>
       <c r="J238" s="85"/>
     </row>
-    <row r="239" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="43">
         <v>1</v>
       </c>
@@ -12379,7 +12394,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="85" t="s">
         <v>768</v>
       </c>
@@ -12393,7 +12408,7 @@
       <c r="I240" s="85"/>
       <c r="J240" s="85"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="43">
         <v>1</v>
       </c>
@@ -12425,7 +12440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="43">
         <v>2</v>
       </c>
@@ -12457,7 +12472,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="43">
         <v>3</v>
       </c>
@@ -12489,7 +12504,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="43">
         <v>4</v>
       </c>
@@ -12521,7 +12536,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="43">
         <v>5</v>
       </c>
@@ -12553,7 +12568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="43">
         <v>6</v>
       </c>
@@ -12585,7 +12600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="43">
         <v>7</v>
       </c>
@@ -12617,7 +12632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="43">
         <v>8</v>
       </c>
@@ -12649,7 +12664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="43">
         <v>9</v>
       </c>
@@ -12681,7 +12696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="43">
         <v>10</v>
       </c>
@@ -12713,7 +12728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="43">
         <v>11</v>
       </c>
@@ -12745,7 +12760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="43">
         <v>12</v>
       </c>
@@ -12777,7 +12792,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="43">
         <v>13</v>
       </c>
@@ -12809,7 +12824,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="43">
         <v>14</v>
       </c>
@@ -12841,7 +12856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="43">
         <v>15</v>
       </c>
@@ -12873,7 +12888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="85" t="s">
         <v>813</v>
       </c>
@@ -12887,7 +12902,7 @@
       <c r="I256" s="85"/>
       <c r="J256" s="85"/>
     </row>
-    <row r="257" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="43">
         <v>1</v>
       </c>
@@ -12919,7 +12934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="43">
         <v>2</v>
       </c>
@@ -12951,7 +12966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="85" t="s">
         <v>814</v>
       </c>
@@ -12965,7 +12980,7 @@
       <c r="I259" s="85"/>
       <c r="J259" s="85"/>
     </row>
-    <row r="260" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="43">
         <v>1</v>
       </c>
@@ -12997,7 +13012,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="43">
         <v>2</v>
       </c>
@@ -13029,7 +13044,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="43">
         <v>3</v>
       </c>
@@ -13061,7 +13076,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="43">
         <v>4</v>
       </c>
@@ -13093,7 +13108,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="43">
         <v>5</v>
       </c>
@@ -13125,7 +13140,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="85" t="s">
         <v>890</v>
       </c>
@@ -13139,7 +13154,7 @@
       <c r="I265" s="85"/>
       <c r="J265" s="85"/>
     </row>
-    <row r="266" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="43">
         <v>1</v>
       </c>
@@ -13171,7 +13186,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="85" t="s">
         <v>917</v>
       </c>
@@ -13185,7 +13200,7 @@
       <c r="I267" s="85"/>
       <c r="J267" s="85"/>
     </row>
-    <row r="268" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="43">
         <v>1</v>
       </c>
@@ -13217,7 +13232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="43">
         <v>2</v>
       </c>
@@ -13249,7 +13264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="85" t="s">
         <v>931</v>
       </c>
@@ -13263,7 +13278,7 @@
       <c r="I270" s="85"/>
       <c r="J270" s="85"/>
     </row>
-    <row r="271" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="43">
         <v>1</v>
       </c>
@@ -13295,7 +13310,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="272" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" s="43">
         <v>2</v>
       </c>
@@ -13327,7 +13342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="273" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="85" t="s">
         <v>936</v>
       </c>
@@ -13341,7 +13356,7 @@
       <c r="I273" s="85"/>
       <c r="J273" s="85"/>
     </row>
-    <row r="274" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="43">
         <v>1</v>
       </c>
@@ -13373,7 +13388,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" s="43">
         <v>2</v>
       </c>
@@ -13405,7 +13420,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="85" t="s">
         <v>947</v>
       </c>
@@ -13419,7 +13434,7 @@
       <c r="I276" s="85"/>
       <c r="J276" s="85"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="77">
         <v>1</v>
       </c>
@@ -13451,7 +13466,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="77">
         <v>2</v>
       </c>
@@ -13483,7 +13498,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="85" t="s">
         <v>955</v>
       </c>
@@ -13497,7 +13512,7 @@
       <c r="I279" s="85"/>
       <c r="J279" s="85"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="77">
         <v>1</v>
       </c>
@@ -13529,7 +13544,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="85" t="s">
         <v>966</v>
       </c>
@@ -13543,7 +13558,7 @@
       <c r="I281" s="85"/>
       <c r="J281" s="85"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>1</v>
       </c>
@@ -13575,7 +13590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>2</v>
       </c>
@@ -13607,7 +13622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>3</v>
       </c>
@@ -13639,7 +13654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>4</v>
       </c>
@@ -13671,7 +13686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="286" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="85" t="s">
         <v>980</v>
       </c>
@@ -13685,7 +13700,7 @@
       <c r="I286" s="85"/>
       <c r="J286" s="85"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="77">
         <v>1</v>
       </c>
@@ -13717,7 +13732,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>2</v>
       </c>
@@ -13749,24 +13764,72 @@
         <v>13</v>
       </c>
     </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A289" s="85" t="s">
+        <v>988</v>
+      </c>
+      <c r="B289" s="85"/>
+      <c r="C289" s="85"/>
+      <c r="D289" s="85"/>
+      <c r="E289" s="85"/>
+      <c r="F289" s="85"/>
+      <c r="G289" s="85"/>
+      <c r="H289" s="85"/>
+      <c r="I289" s="85"/>
+      <c r="J289" s="85"/>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A290" s="77">
+        <v>1</v>
+      </c>
+      <c r="B290" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C290" s="71" t="s">
+        <v>989</v>
+      </c>
+      <c r="D290" s="78" t="s">
+        <v>992</v>
+      </c>
+      <c r="E290" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F290" s="71" t="s">
+        <v>990</v>
+      </c>
+      <c r="G290" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="H290" s="77" t="s">
+        <v>991</v>
+      </c>
+      <c r="I290" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="J290" s="77" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A281:J281"/>
-    <mergeCell ref="A279:J279"/>
-    <mergeCell ref="A265:J265"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
+  <mergeCells count="33">
     <mergeCell ref="A205:J205"/>
     <mergeCell ref="A226:J226"/>
     <mergeCell ref="A259:J259"/>
     <mergeCell ref="A256:J256"/>
     <mergeCell ref="A240:J240"/>
     <mergeCell ref="A238:J238"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A267:J267"/>
+    <mergeCell ref="A281:J281"/>
+    <mergeCell ref="A279:J279"/>
+    <mergeCell ref="A265:J265"/>
+    <mergeCell ref="A220:J220"/>
     <mergeCell ref="A276:J276"/>
+    <mergeCell ref="A289:J289"/>
     <mergeCell ref="A286:J286"/>
     <mergeCell ref="A273:J273"/>
     <mergeCell ref="A270:J270"/>
@@ -13782,7 +13845,6 @@
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
-    <mergeCell ref="A267:J267"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13880,36 +13942,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG264"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AG265"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.85546875" customWidth="1"/>
-    <col min="2" max="2" width="45.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="54.28515625" customWidth="1"/>
+    <col min="1" max="1" width="48.88671875" customWidth="1"/>
+    <col min="2" max="2" width="45.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="54.33203125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" customWidth="1"/>
-    <col min="12" max="12" width="53.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" customWidth="1"/>
+    <col min="12" max="12" width="53.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="52.28515625" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" customWidth="1"/>
+    <col min="17" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="71.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="52.33203125" customWidth="1"/>
+    <col min="21" max="21" width="20.88671875" customWidth="1"/>
     <col min="22" max="22" width="27" customWidth="1"/>
     <col min="24" max="25" width="29" customWidth="1"/>
-    <col min="26" max="26" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.42578125" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" customWidth="1"/>
+    <col min="26" max="26" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.44140625" customWidth="1"/>
+    <col min="29" max="29" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.6640625" customWidth="1"/>
+    <col min="31" max="31" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>5</v>
       </c>
@@ -14010,7 +14072,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>23</v>
       </c>
@@ -14093,7 +14155,7 @@
       <c r="AF2" s="28"/>
       <c r="AG2" s="28"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>25</v>
       </c>
@@ -14176,7 +14238,7 @@
       <c r="AF3" s="28"/>
       <c r="AG3" s="28"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="31" t="s">
         <v>28</v>
       </c>
@@ -14259,7 +14321,7 @@
       <c r="AF4" s="28"/>
       <c r="AG4" s="28"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="31" t="s">
         <v>58</v>
       </c>
@@ -14342,7 +14404,7 @@
       <c r="AF5" s="28"/>
       <c r="AG5" s="28"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
         <v>69</v>
       </c>
@@ -14425,7 +14487,7 @@
       <c r="AF6" s="28"/>
       <c r="AG6" s="28"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
         <v>73</v>
       </c>
@@ -14508,7 +14570,7 @@
       <c r="AF7" s="28"/>
       <c r="AG7" s="28"/>
     </row>
-    <row r="8" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36" t="s">
         <v>77</v>
       </c>
@@ -14591,7 +14653,7 @@
       <c r="AF8" s="28"/>
       <c r="AG8" s="28"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="36" t="s">
         <v>79</v>
       </c>
@@ -14674,7 +14736,7 @@
       <c r="AF9" s="28"/>
       <c r="AG9" s="28"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="36" t="s">
         <v>80</v>
       </c>
@@ -14757,7 +14819,7 @@
       <c r="AF10" s="28"/>
       <c r="AG10" s="28"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
         <v>81</v>
       </c>
@@ -14840,7 +14902,7 @@
       <c r="AF11" s="28"/>
       <c r="AG11" s="28"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
         <v>83</v>
       </c>
@@ -14923,7 +14985,7 @@
       <c r="AF12" s="28"/>
       <c r="AG12" s="28"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="36" t="s">
         <v>84</v>
       </c>
@@ -15006,7 +15068,7 @@
       <c r="AF13" s="28"/>
       <c r="AG13" s="28"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" s="36" t="s">
         <v>85</v>
       </c>
@@ -15089,7 +15151,7 @@
       <c r="AF14" s="28"/>
       <c r="AG14" s="28"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
         <v>86</v>
       </c>
@@ -15172,7 +15234,7 @@
       <c r="AF15" s="28"/>
       <c r="AG15" s="28"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="36" t="s">
         <v>87</v>
       </c>
@@ -15255,7 +15317,7 @@
       <c r="AF16" s="28"/>
       <c r="AG16" s="28"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="36" t="s">
         <v>88</v>
       </c>
@@ -15338,7 +15400,7 @@
       <c r="AF17" s="28"/>
       <c r="AG17" s="28"/>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="36" t="s">
         <v>89</v>
       </c>
@@ -15421,7 +15483,7 @@
       <c r="AF18" s="28"/>
       <c r="AG18" s="28"/>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19" s="36" t="s">
         <v>91</v>
       </c>
@@ -15504,7 +15566,7 @@
       <c r="AF19" s="28"/>
       <c r="AG19" s="28"/>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" s="36" t="s">
         <v>93</v>
       </c>
@@ -15587,7 +15649,7 @@
       <c r="AF20" s="28"/>
       <c r="AG20" s="28"/>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>94</v>
       </c>
@@ -15670,7 +15732,7 @@
       <c r="AF21" s="28"/>
       <c r="AG21" s="28"/>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" s="36" t="s">
         <v>135</v>
       </c>
@@ -15753,7 +15815,7 @@
       <c r="AF22" s="28"/>
       <c r="AG22" s="28"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" s="36" t="s">
         <v>140</v>
       </c>
@@ -15836,7 +15898,7 @@
       <c r="AF23" s="28"/>
       <c r="AG23" s="28"/>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
         <v>63</v>
       </c>
@@ -15919,7 +15981,7 @@
       <c r="AF24" s="28"/>
       <c r="AG24" s="28"/>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" s="41" t="s">
         <v>144</v>
       </c>
@@ -16002,7 +16064,7 @@
       <c r="AF25" s="28"/>
       <c r="AG25" s="28"/>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>145</v>
       </c>
@@ -16085,7 +16147,7 @@
       <c r="AF26" s="28"/>
       <c r="AG26" s="28"/>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="41" t="s">
         <v>146</v>
       </c>
@@ -16168,7 +16230,7 @@
       <c r="AF27" s="28"/>
       <c r="AG27" s="28"/>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" s="41" t="s">
         <v>147</v>
       </c>
@@ -16251,7 +16313,7 @@
       <c r="AF28" s="28"/>
       <c r="AG28" s="28"/>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" s="41" t="s">
         <v>148</v>
       </c>
@@ -16334,7 +16396,7 @@
       <c r="AF29" s="28"/>
       <c r="AG29" s="28"/>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
         <v>150</v>
       </c>
@@ -16417,7 +16479,7 @@
       <c r="AF30" s="28"/>
       <c r="AG30" s="28"/>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31" s="41" t="s">
         <v>151</v>
       </c>
@@ -16500,7 +16562,7 @@
       <c r="AF31" s="28"/>
       <c r="AG31" s="28"/>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" s="41" t="s">
         <v>152</v>
       </c>
@@ -16583,7 +16645,7 @@
       <c r="AF32" s="28"/>
       <c r="AG32" s="28"/>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33" s="41" t="s">
         <v>153</v>
       </c>
@@ -16666,7 +16728,7 @@
       <c r="AF33" s="28"/>
       <c r="AG33" s="28"/>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" s="41" t="s">
         <v>154</v>
       </c>
@@ -16749,7 +16811,7 @@
       <c r="AF34" s="28"/>
       <c r="AG34" s="28"/>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" s="41" t="s">
         <v>155</v>
       </c>
@@ -16832,7 +16894,7 @@
       <c r="AF35" s="28"/>
       <c r="AG35" s="28"/>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" s="31" t="s">
         <v>64</v>
       </c>
@@ -16915,7 +16977,7 @@
       <c r="AF36" s="28"/>
       <c r="AG36" s="28"/>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" s="48" t="s">
         <v>175</v>
       </c>
@@ -17000,7 +17062,7 @@
       <c r="AF37" s="28"/>
       <c r="AG37" s="28"/>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A38" s="42" t="s">
         <v>179</v>
       </c>
@@ -17085,7 +17147,7 @@
       <c r="AF38" s="28"/>
       <c r="AG38" s="28"/>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="42" t="s">
         <v>182</v>
       </c>
@@ -17170,7 +17232,7 @@
       <c r="AF39" s="28"/>
       <c r="AG39" s="28"/>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" s="42" t="s">
         <v>185</v>
       </c>
@@ -17255,7 +17317,7 @@
       <c r="AF40" s="28"/>
       <c r="AG40" s="28"/>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" s="42" t="s">
         <v>188</v>
       </c>
@@ -17340,7 +17402,7 @@
       <c r="AF41" s="28"/>
       <c r="AG41" s="28"/>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" s="42" t="s">
         <v>190</v>
       </c>
@@ -17425,7 +17487,7 @@
       <c r="AF42" s="28"/>
       <c r="AG42" s="28"/>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" s="42" t="s">
         <v>193</v>
       </c>
@@ -17510,7 +17572,7 @@
       <c r="AF43" s="28"/>
       <c r="AG43" s="28"/>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44" s="42" t="s">
         <v>196</v>
       </c>
@@ -17595,7 +17657,7 @@
       <c r="AF44" s="28"/>
       <c r="AG44" s="28"/>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" s="42" t="s">
         <v>198</v>
       </c>
@@ -17680,7 +17742,7 @@
       <c r="AF45" s="28"/>
       <c r="AG45" s="28"/>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" s="42" t="s">
         <v>200</v>
       </c>
@@ -17765,7 +17827,7 @@
       <c r="AF46" s="28"/>
       <c r="AG46" s="28"/>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47" s="42" t="s">
         <v>202</v>
       </c>
@@ -17850,7 +17912,7 @@
       <c r="AF47" s="28"/>
       <c r="AG47" s="28"/>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" s="42" t="s">
         <v>204</v>
       </c>
@@ -17935,7 +17997,7 @@
       <c r="AF48" s="28"/>
       <c r="AG48" s="28"/>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="42" t="s">
         <v>206</v>
       </c>
@@ -18020,7 +18082,7 @@
       <c r="AF49" s="28"/>
       <c r="AG49" s="28"/>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" s="42" t="s">
         <v>208</v>
       </c>
@@ -18105,7 +18167,7 @@
       <c r="AF50" s="28"/>
       <c r="AG50" s="28"/>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="42" t="s">
         <v>210</v>
       </c>
@@ -18190,7 +18252,7 @@
       <c r="AF51" s="28"/>
       <c r="AG51" s="28"/>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="42" t="s">
         <v>212</v>
       </c>
@@ -18275,7 +18337,7 @@
       <c r="AF52" s="28"/>
       <c r="AG52" s="28"/>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53" s="42" t="s">
         <v>679</v>
       </c>
@@ -18360,7 +18422,7 @@
       <c r="AF53" s="28"/>
       <c r="AG53" s="28"/>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54" s="49" t="s">
         <v>213</v>
       </c>
@@ -18445,7 +18507,7 @@
       <c r="AF54" s="28"/>
       <c r="AG54" s="28"/>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55" s="43" t="s">
         <v>214</v>
       </c>
@@ -18530,7 +18592,7 @@
       <c r="AF55" s="28"/>
       <c r="AG55" s="28"/>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="43" t="s">
         <v>215</v>
       </c>
@@ -18615,7 +18677,7 @@
       <c r="AF56" s="28"/>
       <c r="AG56" s="28"/>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="43" t="s">
         <v>216</v>
       </c>
@@ -18700,7 +18762,7 @@
       <c r="AF57" s="28"/>
       <c r="AG57" s="28"/>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58" s="43" t="s">
         <v>217</v>
       </c>
@@ -18785,7 +18847,7 @@
       <c r="AF58" s="28"/>
       <c r="AG58" s="28"/>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59" s="43" t="s">
         <v>218</v>
       </c>
@@ -18870,7 +18932,7 @@
       <c r="AF59" s="28"/>
       <c r="AG59" s="28"/>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60" s="43" t="s">
         <v>219</v>
       </c>
@@ -18955,7 +19017,7 @@
       <c r="AF60" s="28"/>
       <c r="AG60" s="28"/>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61" s="43" t="s">
         <v>220</v>
       </c>
@@ -19040,7 +19102,7 @@
       <c r="AF61" s="28"/>
       <c r="AG61" s="28"/>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A62" s="43" t="s">
         <v>221</v>
       </c>
@@ -19125,7 +19187,7 @@
       <c r="AF62" s="28"/>
       <c r="AG62" s="28"/>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="43" t="s">
         <v>222</v>
       </c>
@@ -19210,7 +19272,7 @@
       <c r="AF63" s="28"/>
       <c r="AG63" s="28"/>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A64" s="50" t="s">
         <v>249</v>
       </c>
@@ -19295,7 +19357,7 @@
       <c r="AF64" s="28"/>
       <c r="AG64" s="28"/>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65" s="43" t="s">
         <v>253</v>
       </c>
@@ -19380,7 +19442,7 @@
       <c r="AF65" s="28"/>
       <c r="AG65" s="28"/>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A66" s="43" t="s">
         <v>256</v>
       </c>
@@ -19465,7 +19527,7 @@
       <c r="AF66" s="28"/>
       <c r="AG66" s="28"/>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A67" s="43" t="s">
         <v>259</v>
       </c>
@@ -19550,7 +19612,7 @@
       <c r="AF67" s="28"/>
       <c r="AG67" s="28"/>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A68" s="43" t="s">
         <v>262</v>
       </c>
@@ -19635,7 +19697,7 @@
       <c r="AF68" s="28"/>
       <c r="AG68" s="28"/>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A69" s="43" t="s">
         <v>265</v>
       </c>
@@ -19720,7 +19782,7 @@
       <c r="AF69" s="28"/>
       <c r="AG69" s="28"/>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A70" s="43" t="s">
         <v>268</v>
       </c>
@@ -19805,7 +19867,7 @@
       <c r="AF70" s="28"/>
       <c r="AG70" s="28"/>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A71" s="43" t="s">
         <v>271</v>
       </c>
@@ -19890,7 +19952,7 @@
       <c r="AF71" s="28"/>
       <c r="AG71" s="28"/>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A72" s="43" t="s">
         <v>274</v>
       </c>
@@ -19975,7 +20037,7 @@
       <c r="AF72" s="28"/>
       <c r="AG72" s="28"/>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A73" s="43" t="s">
         <v>277</v>
       </c>
@@ -20060,7 +20122,7 @@
       <c r="AF73" s="28"/>
       <c r="AG73" s="28"/>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A74" s="43" t="s">
         <v>280</v>
       </c>
@@ -20147,7 +20209,7 @@
       <c r="AF74" s="28"/>
       <c r="AG74" s="28"/>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A75" s="56" t="s">
         <v>282</v>
       </c>
@@ -20234,7 +20296,7 @@
       <c r="AF75" s="28"/>
       <c r="AG75" s="28"/>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A76" s="43" t="s">
         <v>285</v>
       </c>
@@ -20321,7 +20383,7 @@
       <c r="AF76" s="28"/>
       <c r="AG76" s="28"/>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A77" s="43" t="s">
         <v>287</v>
       </c>
@@ -20408,7 +20470,7 @@
       <c r="AF77" s="28"/>
       <c r="AG77" s="28"/>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A78" s="43" t="s">
         <v>289</v>
       </c>
@@ -20495,7 +20557,7 @@
       <c r="AF78" s="28"/>
       <c r="AG78" s="28"/>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A79" s="43" t="s">
         <v>292</v>
       </c>
@@ -20582,7 +20644,7 @@
       <c r="AF79" s="28"/>
       <c r="AG79" s="28"/>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A80" s="43" t="s">
         <v>295</v>
       </c>
@@ -20669,7 +20731,7 @@
       <c r="AF80" s="28"/>
       <c r="AG80" s="28"/>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A81" s="43" t="s">
         <v>298</v>
       </c>
@@ -20756,7 +20818,7 @@
       <c r="AF81" s="28"/>
       <c r="AG81" s="28"/>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A82" s="43" t="s">
         <v>301</v>
       </c>
@@ -20843,7 +20905,7 @@
       <c r="AF82" s="28"/>
       <c r="AG82" s="28"/>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A83" s="43" t="s">
         <v>304</v>
       </c>
@@ -20930,7 +20992,7 @@
       <c r="AF83" s="28"/>
       <c r="AG83" s="28"/>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A84" s="43" t="s">
         <v>306</v>
       </c>
@@ -21017,7 +21079,7 @@
       <c r="AF84" s="28"/>
       <c r="AG84" s="28"/>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A85" s="43" t="s">
         <v>308</v>
       </c>
@@ -21104,7 +21166,7 @@
       <c r="AF85" s="28"/>
       <c r="AG85" s="28"/>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A86" s="43" t="s">
         <v>310</v>
       </c>
@@ -21191,7 +21253,7 @@
       <c r="AF86" s="28"/>
       <c r="AG86" s="28"/>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A87" s="43" t="s">
         <v>313</v>
       </c>
@@ -21278,7 +21340,7 @@
       <c r="AF87" s="28"/>
       <c r="AG87" s="28"/>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A88" s="43" t="s">
         <v>316</v>
       </c>
@@ -21365,7 +21427,7 @@
       <c r="AF88" s="28"/>
       <c r="AG88" s="28"/>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A89" s="43" t="s">
         <v>319</v>
       </c>
@@ -21452,7 +21514,7 @@
       <c r="AF89" s="28"/>
       <c r="AG89" s="28"/>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A90" s="43" t="s">
         <v>322</v>
       </c>
@@ -21539,7 +21601,7 @@
       <c r="AF90" s="28"/>
       <c r="AG90" s="28"/>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A91" s="43" t="s">
         <v>324</v>
       </c>
@@ -21626,7 +21688,7 @@
       <c r="AF91" s="28"/>
       <c r="AG91" s="28"/>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A92" s="43" t="s">
         <v>327</v>
       </c>
@@ -21713,7 +21775,7 @@
       <c r="AF92" s="28"/>
       <c r="AG92" s="28"/>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A93" s="43" t="s">
         <v>330</v>
       </c>
@@ -21800,7 +21862,7 @@
       <c r="AF93" s="28"/>
       <c r="AG93" s="28"/>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A94" s="43" t="s">
         <v>332</v>
       </c>
@@ -21887,7 +21949,7 @@
       <c r="AF94" s="28"/>
       <c r="AG94" s="28"/>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A95" s="43" t="s">
         <v>334</v>
       </c>
@@ -21974,7 +22036,7 @@
       <c r="AF95" s="28"/>
       <c r="AG95" s="28"/>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A96" s="43" t="s">
         <v>336</v>
       </c>
@@ -22061,7 +22123,7 @@
       <c r="AF96" s="28"/>
       <c r="AG96" s="28"/>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A97" s="43" t="s">
         <v>338</v>
       </c>
@@ -22148,7 +22210,7 @@
       <c r="AF97" s="28"/>
       <c r="AG97" s="28"/>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A98" s="43" t="s">
         <v>340</v>
       </c>
@@ -22235,7 +22297,7 @@
       <c r="AF98" s="28"/>
       <c r="AG98" s="28"/>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A99" s="43" t="s">
         <v>342</v>
       </c>
@@ -22322,7 +22384,7 @@
       <c r="AF99" s="28"/>
       <c r="AG99" s="28"/>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A100" s="43" t="s">
         <v>344</v>
       </c>
@@ -22409,7 +22471,7 @@
       <c r="AF100" s="28"/>
       <c r="AG100" s="28"/>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A101" s="43" t="s">
         <v>597</v>
       </c>
@@ -22496,7 +22558,7 @@
       <c r="AF101" s="28"/>
       <c r="AG101" s="28"/>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A102" s="43" t="s">
         <v>348</v>
       </c>
@@ -22583,7 +22645,7 @@
       <c r="AF102" s="28"/>
       <c r="AG102" s="28"/>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A103" s="43" t="s">
         <v>352</v>
       </c>
@@ -22670,7 +22732,7 @@
       <c r="AF103" s="28"/>
       <c r="AG103" s="28"/>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A104" s="43" t="s">
         <v>355</v>
       </c>
@@ -22757,7 +22819,7 @@
       <c r="AF104" s="28"/>
       <c r="AG104" s="28"/>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A105" s="43" t="s">
         <v>358</v>
       </c>
@@ -22844,7 +22906,7 @@
       <c r="AF105" s="28"/>
       <c r="AG105" s="28"/>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A106" s="43" t="s">
         <v>361</v>
       </c>
@@ -22931,7 +22993,7 @@
       <c r="AF106" s="28"/>
       <c r="AG106" s="28"/>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A107" s="43" t="s">
         <v>364</v>
       </c>
@@ -23018,7 +23080,7 @@
       <c r="AF107" s="28"/>
       <c r="AG107" s="28"/>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A108" s="43" t="s">
         <v>367</v>
       </c>
@@ -23105,7 +23167,7 @@
       <c r="AF108" s="28"/>
       <c r="AG108" s="28"/>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A109" s="43" t="s">
         <v>369</v>
       </c>
@@ -23192,7 +23254,7 @@
       <c r="AF109" s="28"/>
       <c r="AG109" s="28"/>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A110" s="43" t="s">
         <v>371</v>
       </c>
@@ -23279,7 +23341,7 @@
       <c r="AF110" s="28"/>
       <c r="AG110" s="28"/>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A111" s="43" t="s">
         <v>598</v>
       </c>
@@ -23366,7 +23428,7 @@
       <c r="AF111" s="28"/>
       <c r="AG111" s="28"/>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A112" s="43" t="s">
         <v>682</v>
       </c>
@@ -23453,7 +23515,7 @@
       <c r="AF112" s="28"/>
       <c r="AG112" s="28"/>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A113" s="43" t="s">
         <v>685</v>
       </c>
@@ -23540,7 +23602,7 @@
       <c r="AF113" s="28"/>
       <c r="AG113" s="28"/>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A114" s="43" t="s">
         <v>688</v>
       </c>
@@ -23627,7 +23689,7 @@
       <c r="AF114" s="28"/>
       <c r="AG114" s="28"/>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A115" s="43" t="s">
         <v>691</v>
       </c>
@@ -23714,7 +23776,7 @@
       <c r="AF115" s="28"/>
       <c r="AG115" s="28"/>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A116" s="43" t="s">
         <v>378</v>
       </c>
@@ -23801,7 +23863,7 @@
       <c r="AF116" s="28"/>
       <c r="AG116" s="28"/>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A117" s="43" t="s">
         <v>383</v>
       </c>
@@ -23888,7 +23950,7 @@
       <c r="AF117" s="28"/>
       <c r="AG117" s="28"/>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A118" s="43" t="s">
         <v>397</v>
       </c>
@@ -23975,7 +24037,7 @@
       <c r="AF118" s="28"/>
       <c r="AG118" s="28"/>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A119" s="43" t="s">
         <v>399</v>
       </c>
@@ -24062,7 +24124,7 @@
       <c r="AF119" s="28"/>
       <c r="AG119" s="28"/>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A120" s="43" t="s">
         <v>400</v>
       </c>
@@ -24149,7 +24211,7 @@
       <c r="AF120" s="28"/>
       <c r="AG120" s="28"/>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A121" s="43" t="s">
         <v>401</v>
       </c>
@@ -24236,7 +24298,7 @@
       <c r="AF121" s="28"/>
       <c r="AG121" s="28"/>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A122" s="43" t="s">
         <v>402</v>
       </c>
@@ -24323,7 +24385,7 @@
       <c r="AF122" s="28"/>
       <c r="AG122" s="28"/>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A123" s="43" t="s">
         <v>403</v>
       </c>
@@ -24410,7 +24472,7 @@
       <c r="AF123" s="28"/>
       <c r="AG123" s="28"/>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A124" s="43" t="s">
         <v>405</v>
       </c>
@@ -24497,7 +24559,7 @@
       <c r="AF124" s="28"/>
       <c r="AG124" s="28"/>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A125" s="43" t="s">
         <v>407</v>
       </c>
@@ -24584,7 +24646,7 @@
       <c r="AF125" s="28"/>
       <c r="AG125" s="28"/>
     </row>
-    <row r="126" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A126" s="56" t="s">
         <v>413</v>
       </c>
@@ -24671,7 +24733,7 @@
       <c r="AF126" s="28"/>
       <c r="AG126" s="28"/>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A127" s="43" t="s">
         <v>417</v>
       </c>
@@ -24758,7 +24820,7 @@
       <c r="AF127" s="28"/>
       <c r="AG127" s="28"/>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A128" s="43" t="s">
         <v>420</v>
       </c>
@@ -24845,7 +24907,7 @@
       <c r="AF128" s="28"/>
       <c r="AG128" s="28"/>
     </row>
-    <row r="129" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A129" s="43" t="s">
         <v>422</v>
       </c>
@@ -24932,7 +24994,7 @@
       <c r="AF129" s="28"/>
       <c r="AG129" s="28"/>
     </row>
-    <row r="130" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A130" s="43" t="s">
         <v>424</v>
       </c>
@@ -25019,7 +25081,7 @@
       <c r="AF130" s="28"/>
       <c r="AG130" s="28"/>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A131" s="43" t="s">
         <v>427</v>
       </c>
@@ -25106,7 +25168,7 @@
       <c r="AF131" s="28"/>
       <c r="AG131" s="28"/>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A132" s="43" t="s">
         <v>430</v>
       </c>
@@ -25193,7 +25255,7 @@
       <c r="AF132" s="28"/>
       <c r="AG132" s="28"/>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A133" s="43" t="s">
         <v>433</v>
       </c>
@@ -25280,7 +25342,7 @@
       <c r="AF133" s="28"/>
       <c r="AG133" s="28"/>
     </row>
-    <row r="134" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A134" s="43" t="s">
         <v>436</v>
       </c>
@@ -25367,7 +25429,7 @@
       <c r="AF134" s="28"/>
       <c r="AG134" s="28"/>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A135" s="43" t="s">
         <v>438</v>
       </c>
@@ -25454,7 +25516,7 @@
       <c r="AF135" s="28"/>
       <c r="AG135" s="28"/>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A136" s="43" t="s">
         <v>695</v>
       </c>
@@ -25541,7 +25603,7 @@
       <c r="AF136" s="28"/>
       <c r="AG136" s="28"/>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A137" s="43" t="s">
         <v>397</v>
       </c>
@@ -25628,7 +25690,7 @@
       <c r="AF137" s="28"/>
       <c r="AG137" s="28"/>
     </row>
-    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A138" s="43" t="s">
         <v>399</v>
       </c>
@@ -25715,7 +25777,7 @@
       <c r="AF138" s="28"/>
       <c r="AG138" s="28"/>
     </row>
-    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A139" s="43" t="s">
         <v>400</v>
       </c>
@@ -25802,7 +25864,7 @@
       <c r="AF139" s="28"/>
       <c r="AG139" s="28"/>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A140" s="43" t="s">
         <v>401</v>
       </c>
@@ -25889,7 +25951,7 @@
       <c r="AF140" s="28"/>
       <c r="AG140" s="28"/>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A141" s="43" t="s">
         <v>402</v>
       </c>
@@ -25976,7 +26038,7 @@
       <c r="AF141" s="28"/>
       <c r="AG141" s="28"/>
     </row>
-    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A142" s="43" t="s">
         <v>403</v>
       </c>
@@ -26063,7 +26125,7 @@
       <c r="AF142" s="28"/>
       <c r="AG142" s="28"/>
     </row>
-    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A143" s="43" t="s">
         <v>405</v>
       </c>
@@ -26150,7 +26212,7 @@
       <c r="AF143" s="28"/>
       <c r="AG143" s="28"/>
     </row>
-    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A144" s="43" t="s">
         <v>442</v>
       </c>
@@ -26237,7 +26299,7 @@
       <c r="AF144" s="28"/>
       <c r="AG144" s="28"/>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A145" s="43" t="s">
         <v>446</v>
       </c>
@@ -26324,7 +26386,7 @@
       <c r="AF145" s="28"/>
       <c r="AG145" s="28"/>
     </row>
-    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A146" s="43" t="s">
         <v>449</v>
       </c>
@@ -26411,7 +26473,7 @@
       <c r="AF146" s="28"/>
       <c r="AG146" s="28"/>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A147" s="43" t="s">
         <v>451</v>
       </c>
@@ -26498,7 +26560,7 @@
       <c r="AF147" s="28"/>
       <c r="AG147" s="28"/>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A148" s="43" t="s">
         <v>454</v>
       </c>
@@ -26585,7 +26647,7 @@
       <c r="AF148" s="28"/>
       <c r="AG148" s="28"/>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A149" s="43" t="s">
         <v>457</v>
       </c>
@@ -26672,7 +26734,7 @@
       <c r="AF149" s="28"/>
       <c r="AG149" s="28"/>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A150" s="43" t="s">
         <v>460</v>
       </c>
@@ -26759,7 +26821,7 @@
       <c r="AF150" s="28"/>
       <c r="AG150" s="28"/>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A151" s="43" t="s">
         <v>463</v>
       </c>
@@ -26846,7 +26908,7 @@
       <c r="AF151" s="28"/>
       <c r="AG151" s="28"/>
     </row>
-    <row r="152" spans="1:33" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="43" t="s">
         <v>466</v>
       </c>
@@ -26933,7 +26995,7 @@
       <c r="AF152" s="28"/>
       <c r="AG152" s="28"/>
     </row>
-    <row r="153" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="43" t="s">
         <v>469</v>
       </c>
@@ -27020,7 +27082,7 @@
       <c r="AF153" s="28"/>
       <c r="AG153" s="28"/>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A154" s="43" t="s">
         <v>509</v>
       </c>
@@ -27107,7 +27169,7 @@
       <c r="AF154" s="28"/>
       <c r="AG154" s="28"/>
     </row>
-    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A155" s="71" t="s">
         <v>539</v>
       </c>
@@ -27194,7 +27256,7 @@
       <c r="AF155" s="28"/>
       <c r="AG155" s="28"/>
     </row>
-    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A156" s="71" t="s">
         <v>543</v>
       </c>
@@ -27281,7 +27343,7 @@
       <c r="AF156" s="28"/>
       <c r="AG156" s="28"/>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A157" s="71" t="s">
         <v>546</v>
       </c>
@@ -27368,7 +27430,7 @@
       <c r="AF157" s="28"/>
       <c r="AG157" s="28"/>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A158" s="71" t="s">
         <v>549</v>
       </c>
@@ -27455,7 +27517,7 @@
       <c r="AF158" s="28"/>
       <c r="AG158" s="28"/>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A159" s="71" t="s">
         <v>551</v>
       </c>
@@ -27542,7 +27604,7 @@
       <c r="AF159" s="28"/>
       <c r="AG159" s="28"/>
     </row>
-    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A160" s="71" t="s">
         <v>553</v>
       </c>
@@ -27629,7 +27691,7 @@
       <c r="AF160" s="28"/>
       <c r="AG160" s="28"/>
     </row>
-    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A161" s="71" t="s">
         <v>555</v>
       </c>
@@ -27716,7 +27778,7 @@
       <c r="AF161" s="28"/>
       <c r="AG161" s="28"/>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A162" s="71" t="s">
         <v>557</v>
       </c>
@@ -27803,7 +27865,7 @@
       <c r="AF162" s="28"/>
       <c r="AG162" s="28"/>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A163" s="71" t="s">
         <v>559</v>
       </c>
@@ -27890,7 +27952,7 @@
       <c r="AF163" s="28"/>
       <c r="AG163" s="28"/>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A164" s="71" t="s">
         <v>562</v>
       </c>
@@ -27977,7 +28039,7 @@
       <c r="AF164" s="28"/>
       <c r="AG164" s="28"/>
     </row>
-    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A165" s="71" t="s">
         <v>565</v>
       </c>
@@ -28064,7 +28126,7 @@
       <c r="AF165" s="28"/>
       <c r="AG165" s="28"/>
     </row>
-    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A166" s="71" t="s">
         <v>568</v>
       </c>
@@ -28151,7 +28213,7 @@
       <c r="AF166" s="28"/>
       <c r="AG166" s="28"/>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A167" s="71" t="s">
         <v>571</v>
       </c>
@@ -28238,7 +28300,7 @@
       <c r="AF167" s="28"/>
       <c r="AG167" s="28"/>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A168" s="71" t="s">
         <v>574</v>
       </c>
@@ -28325,7 +28387,7 @@
       <c r="AF168" s="28"/>
       <c r="AG168" s="28"/>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A169" s="71" t="s">
         <v>577</v>
       </c>
@@ -28412,7 +28474,7 @@
       <c r="AF169" s="28"/>
       <c r="AG169" s="28"/>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A170" s="71" t="s">
         <v>579</v>
       </c>
@@ -28499,7 +28561,7 @@
       <c r="AF170" s="28"/>
       <c r="AG170" s="28"/>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A171" s="71" t="s">
         <v>581</v>
       </c>
@@ -28586,7 +28648,7 @@
       <c r="AF171" s="28"/>
       <c r="AG171" s="28"/>
     </row>
-    <row r="172" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A172" s="71" t="s">
         <v>584</v>
       </c>
@@ -28673,7 +28735,7 @@
       <c r="AF172" s="28"/>
       <c r="AG172" s="28"/>
     </row>
-    <row r="173" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A173" s="71" t="s">
         <v>873</v>
       </c>
@@ -28760,7 +28822,7 @@
       <c r="AF173" s="28"/>
       <c r="AG173" s="28"/>
     </row>
-    <row r="174" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A174" s="71" t="s">
         <v>876</v>
       </c>
@@ -28847,7 +28909,7 @@
       <c r="AF174" s="28"/>
       <c r="AG174" s="28"/>
     </row>
-    <row r="175" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A175" s="71" t="s">
         <v>879</v>
       </c>
@@ -28934,7 +28996,7 @@
       <c r="AF175" s="28"/>
       <c r="AG175" s="28"/>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A176" s="71" t="s">
         <v>175</v>
       </c>
@@ -29027,7 +29089,7 @@
       <c r="AF176" s="28"/>
       <c r="AG176" s="28"/>
     </row>
-    <row r="177" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A177" s="71" t="s">
         <v>179</v>
       </c>
@@ -29122,7 +29184,7 @@
       <c r="AF177" s="28"/>
       <c r="AG177" s="28"/>
     </row>
-    <row r="178" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A178" s="71" t="s">
         <v>182</v>
       </c>
@@ -29217,7 +29279,7 @@
       <c r="AF178" s="28"/>
       <c r="AG178" s="28"/>
     </row>
-    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A179" s="71" t="s">
         <v>185</v>
       </c>
@@ -29310,7 +29372,7 @@
       <c r="AF179" s="28"/>
       <c r="AG179" s="28"/>
     </row>
-    <row r="180" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A180" s="71" t="s">
         <v>188</v>
       </c>
@@ -29405,7 +29467,7 @@
       <c r="AF180" s="28"/>
       <c r="AG180" s="28"/>
     </row>
-    <row r="181" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A181" s="71" t="s">
         <v>190</v>
       </c>
@@ -29500,7 +29562,7 @@
       <c r="AF181" s="28"/>
       <c r="AG181" s="28"/>
     </row>
-    <row r="182" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A182" s="71" t="s">
         <v>193</v>
       </c>
@@ -29595,7 +29657,7 @@
       <c r="AF182" s="28"/>
       <c r="AG182" s="28"/>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A183" s="71" t="s">
         <v>196</v>
       </c>
@@ -29690,7 +29752,7 @@
       <c r="AF183" s="28"/>
       <c r="AG183" s="28"/>
     </row>
-    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A184" s="71" t="s">
         <v>607</v>
       </c>
@@ -29785,7 +29847,7 @@
       <c r="AF184" s="28"/>
       <c r="AG184" s="28"/>
     </row>
-    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A185" s="71" t="s">
         <v>611</v>
       </c>
@@ -29882,7 +29944,7 @@
       </c>
       <c r="AG185" s="28"/>
     </row>
-    <row r="186" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A186" s="71" t="s">
         <v>615</v>
       </c>
@@ -29979,7 +30041,7 @@
       </c>
       <c r="AG186" s="28"/>
     </row>
-    <row r="187" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" ht="27" x14ac:dyDescent="0.3">
       <c r="A187" s="71" t="s">
         <v>621</v>
       </c>
@@ -30076,7 +30138,7 @@
       </c>
       <c r="AG187" s="28"/>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A188" s="71" t="s">
         <v>622</v>
       </c>
@@ -30173,7 +30235,7 @@
       <c r="AF188" s="28"/>
       <c r="AG188" s="28"/>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A189" s="71" t="s">
         <v>628</v>
       </c>
@@ -30268,7 +30330,7 @@
       <c r="AF189" s="28"/>
       <c r="AG189" s="28"/>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A190" s="71" t="s">
         <v>825</v>
       </c>
@@ -30363,7 +30425,7 @@
       <c r="AF190" s="28"/>
       <c r="AG190" s="28"/>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A191" s="71" t="s">
         <v>826</v>
       </c>
@@ -30458,7 +30520,7 @@
       <c r="AF191" s="28"/>
       <c r="AG191" s="28"/>
     </row>
-    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A192" s="71" t="s">
         <v>632</v>
       </c>
@@ -30553,7 +30615,7 @@
       <c r="AF192" s="28"/>
       <c r="AG192" s="28"/>
     </row>
-    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A193" s="71" t="s">
         <v>634</v>
       </c>
@@ -30648,7 +30710,7 @@
       <c r="AF193" s="28"/>
       <c r="AG193" s="28"/>
     </row>
-    <row r="194" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A194" s="71" t="s">
         <v>640</v>
       </c>
@@ -30743,7 +30805,7 @@
       <c r="AF194" s="28"/>
       <c r="AG194" s="28"/>
     </row>
-    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A195" s="71" t="s">
         <v>641</v>
       </c>
@@ -30838,7 +30900,7 @@
       <c r="AF195" s="28"/>
       <c r="AG195" s="28"/>
     </row>
-    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A196" s="71" t="s">
         <v>646</v>
       </c>
@@ -30933,7 +30995,7 @@
       <c r="AF196" s="28"/>
       <c r="AG196" s="28"/>
     </row>
-    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A197" s="71" t="s">
         <v>648</v>
       </c>
@@ -31028,7 +31090,7 @@
       <c r="AF197" s="28"/>
       <c r="AG197" s="28"/>
     </row>
-    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A198" s="71" t="s">
         <v>654</v>
       </c>
@@ -31123,7 +31185,7 @@
       <c r="AF198" s="28"/>
       <c r="AG198" s="28"/>
     </row>
-    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A199" s="71" t="s">
         <v>657</v>
       </c>
@@ -31218,7 +31280,7 @@
       <c r="AF199" s="28"/>
       <c r="AG199" s="28"/>
     </row>
-    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A200" s="71" t="s">
         <v>658</v>
       </c>
@@ -31313,7 +31375,7 @@
       <c r="AF200" s="28"/>
       <c r="AG200" s="28"/>
     </row>
-    <row r="201" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A201" s="71" t="s">
         <v>663</v>
       </c>
@@ -31408,7 +31470,7 @@
       <c r="AF201" s="28"/>
       <c r="AG201" s="28"/>
     </row>
-    <row r="202" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A202" s="71" t="s">
         <v>668</v>
       </c>
@@ -31503,7 +31565,7 @@
       <c r="AF202" s="28"/>
       <c r="AG202" s="28"/>
     </row>
-    <row r="203" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A203" s="71" t="s">
         <v>669</v>
       </c>
@@ -31598,7 +31660,7 @@
       <c r="AF203" s="28"/>
       <c r="AG203" s="28"/>
     </row>
-    <row r="204" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A204" s="71" t="s">
         <v>855</v>
       </c>
@@ -31693,7 +31755,7 @@
       <c r="AF204" s="28"/>
       <c r="AG204" s="28"/>
     </row>
-    <row r="205" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A205" s="71" t="s">
         <v>858</v>
       </c>
@@ -31788,7 +31850,7 @@
       <c r="AF205" s="28"/>
       <c r="AG205" s="28"/>
     </row>
-    <row r="206" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A206" s="71" t="s">
         <v>859</v>
       </c>
@@ -31883,7 +31945,7 @@
       <c r="AF206" s="28"/>
       <c r="AG206" s="28"/>
     </row>
-    <row r="207" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A207" s="71" t="s">
         <v>710</v>
       </c>
@@ -31978,7 +32040,7 @@
       <c r="AF207" s="28"/>
       <c r="AG207" s="28"/>
     </row>
-    <row r="208" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A208" s="71" t="s">
         <v>713</v>
       </c>
@@ -32073,7 +32135,7 @@
       <c r="AF208" s="28"/>
       <c r="AG208" s="28"/>
     </row>
-    <row r="209" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A209" s="71" t="s">
         <v>715</v>
       </c>
@@ -32168,7 +32230,7 @@
       <c r="AF209" s="28"/>
       <c r="AG209" s="28"/>
     </row>
-    <row r="210" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A210" s="71" t="s">
         <v>753</v>
       </c>
@@ -32263,7 +32325,7 @@
       <c r="AF210" s="28"/>
       <c r="AG210" s="28"/>
     </row>
-    <row r="211" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A211" s="71" t="s">
         <v>842</v>
       </c>
@@ -32358,7 +32420,7 @@
       <c r="AF211" s="28"/>
       <c r="AG211" s="28"/>
     </row>
-    <row r="212" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A212" s="71" t="s">
         <v>843</v>
       </c>
@@ -32453,7 +32515,7 @@
       <c r="AF212" s="28"/>
       <c r="AG212" s="28"/>
     </row>
-    <row r="213" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A213" s="71" t="s">
         <v>718</v>
       </c>
@@ -32548,7 +32610,7 @@
       <c r="AF213" s="28"/>
       <c r="AG213" s="28"/>
     </row>
-    <row r="214" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A214" s="71" t="s">
         <v>724</v>
       </c>
@@ -32643,7 +32705,7 @@
       <c r="AF214" s="28"/>
       <c r="AG214" s="28"/>
     </row>
-    <row r="215" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A215" s="71" t="s">
         <v>725</v>
       </c>
@@ -32738,7 +32800,7 @@
       <c r="AF215" s="28"/>
       <c r="AG215" s="28"/>
     </row>
-    <row r="216" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A216" s="71" t="s">
         <v>730</v>
       </c>
@@ -32833,7 +32895,7 @@
       <c r="AF216" s="28"/>
       <c r="AG216" s="28"/>
     </row>
-    <row r="217" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A217" s="71" t="s">
         <v>731</v>
       </c>
@@ -32928,7 +32990,7 @@
       <c r="AF217" s="28"/>
       <c r="AG217" s="28"/>
     </row>
-    <row r="218" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A218" s="71" t="s">
         <v>732</v>
       </c>
@@ -33023,7 +33085,7 @@
       <c r="AF218" s="28"/>
       <c r="AG218" s="28"/>
     </row>
-    <row r="219" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A219" s="71" t="s">
         <v>737</v>
       </c>
@@ -33118,7 +33180,7 @@
       <c r="AF219" s="28"/>
       <c r="AG219" s="28"/>
     </row>
-    <row r="220" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A220" s="71" t="s">
         <v>740</v>
       </c>
@@ -33213,7 +33275,7 @@
       <c r="AF220" s="28"/>
       <c r="AG220" s="28"/>
     </row>
-    <row r="221" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A221" s="71" t="s">
         <v>745</v>
       </c>
@@ -33308,7 +33370,7 @@
       <c r="AF221" s="28"/>
       <c r="AG221" s="28"/>
     </row>
-    <row r="222" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A222" s="71" t="s">
         <v>748</v>
       </c>
@@ -33403,7 +33465,7 @@
       <c r="AF222" s="28"/>
       <c r="AG222" s="28"/>
     </row>
-    <row r="223" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A223" s="71" t="s">
         <v>749</v>
       </c>
@@ -33498,7 +33560,7 @@
       <c r="AF223" s="28"/>
       <c r="AG223" s="28"/>
     </row>
-    <row r="224" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A224" s="71" t="s">
         <v>755</v>
       </c>
@@ -33593,7 +33655,7 @@
       <c r="AF224" s="28"/>
       <c r="AG224" s="28"/>
     </row>
-    <row r="225" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A225" s="71" t="s">
         <v>767</v>
       </c>
@@ -33688,7 +33750,7 @@
       <c r="AF225" s="28"/>
       <c r="AG225" s="28"/>
     </row>
-    <row r="226" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A226" s="71" t="s">
         <v>772</v>
       </c>
@@ -33783,7 +33845,7 @@
       <c r="AF226" s="28"/>
       <c r="AG226" s="28"/>
     </row>
-    <row r="227" spans="1:33" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:33" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="71" t="s">
         <v>777</v>
       </c>
@@ -33878,7 +33940,7 @@
       <c r="AF227" s="28"/>
       <c r="AG227" s="28"/>
     </row>
-    <row r="228" spans="1:33" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:33" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="71" t="s">
         <v>779</v>
       </c>
@@ -33973,7 +34035,7 @@
       <c r="AF228" s="28"/>
       <c r="AG228" s="28"/>
     </row>
-    <row r="229" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A229" s="71" t="s">
         <v>781</v>
       </c>
@@ -34068,7 +34130,7 @@
       <c r="AF229" s="28"/>
       <c r="AG229" s="28"/>
     </row>
-    <row r="230" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A230" s="71" t="s">
         <v>786</v>
       </c>
@@ -34163,7 +34225,7 @@
       <c r="AF230" s="28"/>
       <c r="AG230" s="28"/>
     </row>
-    <row r="231" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="71" t="s">
         <v>788</v>
       </c>
@@ -34258,7 +34320,7 @@
       <c r="AF231" s="28"/>
       <c r="AG231" s="28"/>
     </row>
-    <row r="232" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="71" t="s">
         <v>792</v>
       </c>
@@ -34353,7 +34415,7 @@
       <c r="AF232" s="28"/>
       <c r="AG232" s="28"/>
     </row>
-    <row r="233" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A233" s="71" t="s">
         <v>797</v>
       </c>
@@ -34448,7 +34510,7 @@
       <c r="AF233" s="28"/>
       <c r="AG233" s="28"/>
     </row>
-    <row r="234" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="71" t="s">
         <v>800</v>
       </c>
@@ -34543,7 +34605,7 @@
       <c r="AF234" s="28"/>
       <c r="AG234" s="28"/>
     </row>
-    <row r="235" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="71" t="s">
         <v>801</v>
       </c>
@@ -34638,7 +34700,7 @@
       <c r="AF235" s="28"/>
       <c r="AG235" s="28"/>
     </row>
-    <row r="236" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="71" t="s">
         <v>806</v>
       </c>
@@ -34733,7 +34795,7 @@
       <c r="AF236" s="28"/>
       <c r="AG236" s="28"/>
     </row>
-    <row r="237" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="71" t="s">
         <v>882</v>
       </c>
@@ -34828,7 +34890,7 @@
       <c r="AF237" s="28"/>
       <c r="AG237" s="28"/>
     </row>
-    <row r="238" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="71" t="s">
         <v>883</v>
       </c>
@@ -34923,7 +34985,7 @@
       <c r="AF238" s="28"/>
       <c r="AG238" s="28"/>
     </row>
-    <row r="239" spans="1:33" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:33" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="71" t="s">
         <v>884</v>
       </c>
@@ -35018,7 +35080,7 @@
       <c r="AF239" s="28"/>
       <c r="AG239" s="28"/>
     </row>
-    <row r="240" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="71" t="s">
         <v>846</v>
       </c>
@@ -35113,7 +35175,7 @@
       <c r="AF240" s="28"/>
       <c r="AG240" s="28"/>
     </row>
-    <row r="241" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="71" t="s">
         <v>850</v>
       </c>
@@ -35208,7 +35270,7 @@
       <c r="AF241" s="28"/>
       <c r="AG241" s="28"/>
     </row>
-    <row r="242" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="71" t="s">
         <v>816</v>
       </c>
@@ -35303,7 +35365,7 @@
       <c r="AF242" s="28"/>
       <c r="AG242" s="28"/>
     </row>
-    <row r="243" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="71" t="s">
         <v>820</v>
       </c>
@@ -35398,7 +35460,7 @@
       <c r="AF243" s="28"/>
       <c r="AG243" s="28"/>
     </row>
-    <row r="244" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="71" t="s">
         <v>822</v>
       </c>
@@ -35493,7 +35555,7 @@
       <c r="AF244" s="28"/>
       <c r="AG244" s="28"/>
     </row>
-    <row r="245" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="71" t="s">
         <v>835</v>
       </c>
@@ -35588,7 +35650,7 @@
       <c r="AF245" s="28"/>
       <c r="AG245" s="28"/>
     </row>
-    <row r="246" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:33" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="71" t="s">
         <v>837</v>
       </c>
@@ -35683,7 +35745,7 @@
       <c r="AF246" s="28"/>
       <c r="AG246" s="28"/>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A247" s="28" t="s">
         <v>863</v>
       </c>
@@ -35778,7 +35840,7 @@
       <c r="AF247" s="28"/>
       <c r="AG247" s="28"/>
     </row>
-    <row r="248" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A248" s="28" t="s">
         <v>870</v>
       </c>
@@ -35873,7 +35935,7 @@
       <c r="AF248" s="28"/>
       <c r="AG248" s="28"/>
     </row>
-    <row r="249" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A249" s="28" t="s">
         <v>889</v>
       </c>
@@ -35968,7 +36030,7 @@
       <c r="AF249" s="28"/>
       <c r="AG249" s="28"/>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A250" s="28" t="s">
         <v>916</v>
       </c>
@@ -36063,7 +36125,7 @@
       <c r="AF250" s="28"/>
       <c r="AG250" s="28"/>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A251" s="28" t="s">
         <v>923</v>
       </c>
@@ -36158,7 +36220,7 @@
       <c r="AF251" s="28"/>
       <c r="AG251" s="28"/>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A252" s="28" t="s">
         <v>934</v>
       </c>
@@ -36253,7 +36315,7 @@
       <c r="AF252" s="28"/>
       <c r="AG252" s="28"/>
     </row>
-    <row r="253" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A253" s="28" t="s">
         <v>939</v>
       </c>
@@ -36348,7 +36410,7 @@
       <c r="AF253" s="28"/>
       <c r="AG253" s="28"/>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A254" s="28" t="s">
         <v>943</v>
       </c>
@@ -36443,7 +36505,7 @@
       <c r="AF254" s="28"/>
       <c r="AG254" s="28"/>
     </row>
-    <row r="255" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A255" s="28" t="s">
         <v>946</v>
       </c>
@@ -36538,7 +36600,7 @@
       <c r="AF255" s="28"/>
       <c r="AG255" s="28"/>
     </row>
-    <row r="256" spans="1:33" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:33" ht="18" x14ac:dyDescent="0.35">
       <c r="A256" s="83" t="s">
         <v>950</v>
       </c>
@@ -36633,7 +36695,7 @@
       <c r="AF256" s="28"/>
       <c r="AG256" s="28"/>
     </row>
-    <row r="257" spans="1:33" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:33" ht="18" x14ac:dyDescent="0.35">
       <c r="A257" s="83" t="s">
         <v>954</v>
       </c>
@@ -36728,7 +36790,7 @@
       <c r="AF257" s="28"/>
       <c r="AG257" s="28"/>
     </row>
-    <row r="258" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A258" s="28" t="s">
         <v>958</v>
       </c>
@@ -36829,7 +36891,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="259" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>969</v>
       </c>
@@ -36930,7 +36992,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="260" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>973</v>
       </c>
@@ -37031,7 +37093,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="261" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>976</v>
       </c>
@@ -37132,7 +37194,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="262" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>979</v>
       </c>
@@ -37233,7 +37295,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="263" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>984</v>
       </c>
@@ -37334,7 +37396,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="264" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>987</v>
       </c>
@@ -37432,6 +37494,107 @@
         <v>22</v>
       </c>
       <c r="AG264" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="265" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>990</v>
+      </c>
+      <c r="B265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF265" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG265" s="28" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever36\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\ZlaataQAsever\Ref\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B14D6B7-D4B2-4272-ABC4-BD75FD510A3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64AC72B-81E6-4734-80FF-846547B1781F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9507" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9592" uniqueCount="1000">
   <si>
     <t>S.No</t>
   </si>
@@ -3005,6 +3005,27 @@
   </si>
   <si>
     <t>Verify New Label functionality in user app.</t>
+  </si>
+  <si>
+    <t>Media Library</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ML_01</t>
+  </si>
+  <si>
+    <t>Verify adding a new image to the product in Media Library and checking in UI</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ML_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ML_02</t>
+  </si>
+  <si>
+    <t>Verify that changing the brand type in Media Library is reflected on the product page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ML_02</t>
   </si>
 </sst>
 </file>
@@ -3647,6 +3668,24 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3673,24 +3712,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4494,7 +4515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z290"/>
+  <dimension ref="A1:Z293"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -5245,18 +5266,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="97"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="88"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -5643,18 +5664,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="98" t="s">
+      <c r="A37" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="99"/>
-      <c r="C37" s="99"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="100"/>
+      <c r="B37" s="90"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="90"/>
+      <c r="I37" s="90"/>
+      <c r="J37" s="91"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -6201,18 +6222,18 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="98" t="s">
+      <c r="A55" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="99"/>
-      <c r="C55" s="99"/>
-      <c r="D55" s="99"/>
-      <c r="E55" s="99"/>
-      <c r="F55" s="99"/>
-      <c r="G55" s="99"/>
-      <c r="H55" s="99"/>
-      <c r="I55" s="99"/>
-      <c r="J55" s="100"/>
+      <c r="B55" s="90"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
+      <c r="G55" s="90"/>
+      <c r="H55" s="90"/>
+      <c r="I55" s="90"/>
+      <c r="J55" s="91"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
@@ -6535,18 +6556,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="98" t="s">
+      <c r="A66" s="89" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="99"/>
-      <c r="C66" s="99"/>
-      <c r="D66" s="99"/>
-      <c r="E66" s="99"/>
-      <c r="F66" s="99"/>
-      <c r="G66" s="99"/>
-      <c r="H66" s="99"/>
-      <c r="I66" s="99"/>
-      <c r="J66" s="100"/>
+      <c r="B66" s="90"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="90"/>
+      <c r="E66" s="90"/>
+      <c r="F66" s="90"/>
+      <c r="G66" s="90"/>
+      <c r="H66" s="90"/>
+      <c r="I66" s="90"/>
+      <c r="J66" s="91"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
@@ -6901,18 +6922,18 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="98" t="s">
+      <c r="A78" s="89" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="99"/>
-      <c r="C78" s="99"/>
-      <c r="D78" s="99"/>
-      <c r="E78" s="99"/>
-      <c r="F78" s="99"/>
-      <c r="G78" s="99"/>
-      <c r="H78" s="99"/>
-      <c r="I78" s="99"/>
-      <c r="J78" s="100"/>
+      <c r="B78" s="90"/>
+      <c r="C78" s="90"/>
+      <c r="D78" s="90"/>
+      <c r="E78" s="90"/>
+      <c r="F78" s="90"/>
+      <c r="G78" s="90"/>
+      <c r="H78" s="90"/>
+      <c r="I78" s="90"/>
+      <c r="J78" s="91"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
@@ -7779,18 +7800,18 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="86" t="s">
+      <c r="A106" s="92" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="86"/>
-      <c r="C106" s="86"/>
-      <c r="D106" s="86"/>
-      <c r="E106" s="86"/>
-      <c r="F106" s="86"/>
-      <c r="G106" s="86"/>
-      <c r="H106" s="86"/>
-      <c r="I106" s="86"/>
-      <c r="J106" s="86"/>
+      <c r="B106" s="92"/>
+      <c r="C106" s="92"/>
+      <c r="D106" s="92"/>
+      <c r="E106" s="92"/>
+      <c r="F106" s="92"/>
+      <c r="G106" s="92"/>
+      <c r="H106" s="92"/>
+      <c r="I106" s="92"/>
+      <c r="J106" s="92"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -8283,18 +8304,18 @@
       <c r="X120" s="52"/>
     </row>
     <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="87" t="s">
+      <c r="A121" s="93" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="87"/>
-      <c r="C121" s="87"/>
-      <c r="D121" s="87"/>
-      <c r="E121" s="87"/>
-      <c r="F121" s="87"/>
-      <c r="G121" s="87"/>
-      <c r="H121" s="87"/>
-      <c r="I121" s="87"/>
-      <c r="J121" s="87"/>
+      <c r="B121" s="93"/>
+      <c r="C121" s="93"/>
+      <c r="D121" s="93"/>
+      <c r="E121" s="93"/>
+      <c r="F121" s="93"/>
+      <c r="G121" s="93"/>
+      <c r="H121" s="93"/>
+      <c r="I121" s="93"/>
+      <c r="J121" s="93"/>
       <c r="K121" s="51"/>
       <c r="L121" s="52"/>
       <c r="M121" s="52"/>
@@ -8357,18 +8378,18 @@
       <c r="X122" s="52"/>
     </row>
     <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="87" t="s">
+      <c r="A123" s="93" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="87"/>
-      <c r="C123" s="87"/>
-      <c r="D123" s="87"/>
-      <c r="E123" s="87"/>
-      <c r="F123" s="87"/>
-      <c r="G123" s="87"/>
-      <c r="H123" s="87"/>
-      <c r="I123" s="87"/>
-      <c r="J123" s="87"/>
+      <c r="B123" s="93"/>
+      <c r="C123" s="93"/>
+      <c r="D123" s="93"/>
+      <c r="E123" s="93"/>
+      <c r="F123" s="93"/>
+      <c r="G123" s="93"/>
+      <c r="H123" s="93"/>
+      <c r="I123" s="93"/>
+      <c r="J123" s="93"/>
       <c r="K123" s="51"/>
       <c r="L123" s="52"/>
       <c r="M123" s="52"/>
@@ -8431,18 +8452,18 @@
       <c r="X124" s="52"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="87" t="s">
+      <c r="A125" s="93" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="87"/>
-      <c r="C125" s="87"/>
-      <c r="D125" s="87"/>
-      <c r="E125" s="87"/>
-      <c r="F125" s="87"/>
-      <c r="G125" s="87"/>
-      <c r="H125" s="87"/>
-      <c r="I125" s="87"/>
-      <c r="J125" s="87"/>
+      <c r="B125" s="93"/>
+      <c r="C125" s="93"/>
+      <c r="D125" s="93"/>
+      <c r="E125" s="93"/>
+      <c r="F125" s="93"/>
+      <c r="G125" s="93"/>
+      <c r="H125" s="93"/>
+      <c r="I125" s="93"/>
+      <c r="J125" s="93"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -8767,18 +8788,18 @@
       <c r="X132" s="52"/>
     </row>
     <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="87" t="s">
+      <c r="A133" s="93" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="87"/>
-      <c r="C133" s="87"/>
-      <c r="D133" s="88"/>
-      <c r="E133" s="88"/>
-      <c r="F133" s="88"/>
-      <c r="G133" s="88"/>
-      <c r="H133" s="88"/>
-      <c r="I133" s="88"/>
-      <c r="J133" s="88"/>
+      <c r="B133" s="93"/>
+      <c r="C133" s="93"/>
+      <c r="D133" s="94"/>
+      <c r="E133" s="94"/>
+      <c r="F133" s="94"/>
+      <c r="G133" s="94"/>
+      <c r="H133" s="94"/>
+      <c r="I133" s="94"/>
+      <c r="J133" s="94"/>
       <c r="K133" s="52"/>
       <c r="L133" s="52"/>
       <c r="M133" s="52"/>
@@ -9273,18 +9294,18 @@
       <c r="X144" s="52"/>
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="92" t="s">
+      <c r="A145" s="98" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="93"/>
-      <c r="C145" s="93"/>
-      <c r="D145" s="93"/>
-      <c r="E145" s="93"/>
-      <c r="F145" s="93"/>
-      <c r="G145" s="93"/>
-      <c r="H145" s="93"/>
-      <c r="I145" s="93"/>
-      <c r="J145" s="94"/>
+      <c r="B145" s="99"/>
+      <c r="C145" s="99"/>
+      <c r="D145" s="99"/>
+      <c r="E145" s="99"/>
+      <c r="F145" s="99"/>
+      <c r="G145" s="99"/>
+      <c r="H145" s="99"/>
+      <c r="I145" s="99"/>
+      <c r="J145" s="100"/>
       <c r="K145" s="52"/>
       <c r="L145" s="52"/>
       <c r="M145" s="52"/>
@@ -9731,18 +9752,18 @@
       <c r="Z155" s="52"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="87" t="s">
+      <c r="A156" s="93" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="87"/>
-      <c r="C156" s="87"/>
-      <c r="D156" s="87"/>
-      <c r="E156" s="87"/>
-      <c r="F156" s="87"/>
-      <c r="G156" s="87"/>
-      <c r="H156" s="87"/>
-      <c r="I156" s="87"/>
-      <c r="J156" s="87"/>
+      <c r="B156" s="93"/>
+      <c r="C156" s="93"/>
+      <c r="D156" s="93"/>
+      <c r="E156" s="93"/>
+      <c r="F156" s="93"/>
+      <c r="G156" s="93"/>
+      <c r="H156" s="93"/>
+      <c r="I156" s="93"/>
+      <c r="J156" s="93"/>
       <c r="K156" s="52"/>
       <c r="L156" s="52"/>
       <c r="M156" s="52"/>
@@ -9809,18 +9830,18 @@
       <c r="Z157" s="52"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="87" t="s">
+      <c r="A158" s="93" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="87"/>
-      <c r="C158" s="87"/>
-      <c r="D158" s="87"/>
-      <c r="E158" s="87"/>
-      <c r="F158" s="87"/>
-      <c r="G158" s="87"/>
-      <c r="H158" s="87"/>
-      <c r="I158" s="87"/>
-      <c r="J158" s="87"/>
+      <c r="B158" s="93"/>
+      <c r="C158" s="93"/>
+      <c r="D158" s="93"/>
+      <c r="E158" s="93"/>
+      <c r="F158" s="93"/>
+      <c r="G158" s="93"/>
+      <c r="H158" s="93"/>
+      <c r="I158" s="93"/>
+      <c r="J158" s="93"/>
       <c r="K158" s="52"/>
       <c r="L158" s="52"/>
       <c r="M158" s="52"/>
@@ -10655,18 +10676,18 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="87" t="s">
+      <c r="A180" s="93" t="s">
         <v>707</v>
       </c>
-      <c r="B180" s="87"/>
-      <c r="C180" s="87"/>
+      <c r="B180" s="93"/>
+      <c r="C180" s="93"/>
       <c r="D180" s="85"/>
-      <c r="E180" s="87"/>
-      <c r="F180" s="87"/>
-      <c r="G180" s="87"/>
-      <c r="H180" s="87"/>
-      <c r="I180" s="87"/>
-      <c r="J180" s="87"/>
+      <c r="E180" s="93"/>
+      <c r="F180" s="93"/>
+      <c r="G180" s="93"/>
+      <c r="H180" s="93"/>
+      <c r="I180" s="93"/>
+      <c r="J180" s="93"/>
     </row>
     <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="62">
@@ -10957,18 +10978,18 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="89" t="s">
+      <c r="A190" s="95" t="s">
         <v>609</v>
       </c>
-      <c r="B190" s="90"/>
-      <c r="C190" s="90"/>
-      <c r="D190" s="90"/>
-      <c r="E190" s="90"/>
-      <c r="F190" s="90"/>
-      <c r="G190" s="90"/>
-      <c r="H190" s="90"/>
-      <c r="I190" s="90"/>
-      <c r="J190" s="91"/>
+      <c r="B190" s="96"/>
+      <c r="C190" s="96"/>
+      <c r="D190" s="96"/>
+      <c r="E190" s="96"/>
+      <c r="F190" s="96"/>
+      <c r="G190" s="96"/>
+      <c r="H190" s="96"/>
+      <c r="I190" s="96"/>
+      <c r="J190" s="97"/>
     </row>
     <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="62">
@@ -13810,25 +13831,87 @@
         <v>13</v>
       </c>
     </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A291" s="85" t="s">
+        <v>993</v>
+      </c>
+      <c r="B291" s="85"/>
+      <c r="C291" s="85"/>
+      <c r="D291" s="85"/>
+      <c r="E291" s="85"/>
+      <c r="F291" s="85"/>
+      <c r="G291" s="85"/>
+      <c r="H291" s="85"/>
+      <c r="I291" s="85"/>
+      <c r="J291" s="85"/>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>1</v>
+      </c>
+      <c r="B292" t="s">
+        <v>10</v>
+      </c>
+      <c r="C292" t="s">
+        <v>994</v>
+      </c>
+      <c r="D292" t="s">
+        <v>995</v>
+      </c>
+      <c r="E292" t="s">
+        <v>14</v>
+      </c>
+      <c r="F292" t="s">
+        <v>996</v>
+      </c>
+      <c r="G292" t="s">
+        <v>11</v>
+      </c>
+      <c r="H292" t="s">
+        <v>970</v>
+      </c>
+      <c r="I292" t="s">
+        <v>12</v>
+      </c>
+      <c r="J292" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>2</v>
+      </c>
+      <c r="B293" t="s">
+        <v>10</v>
+      </c>
+      <c r="C293" t="s">
+        <v>997</v>
+      </c>
+      <c r="D293" t="s">
+        <v>998</v>
+      </c>
+      <c r="E293" t="s">
+        <v>14</v>
+      </c>
+      <c r="F293" t="s">
+        <v>999</v>
+      </c>
+      <c r="G293" t="s">
+        <v>11</v>
+      </c>
+      <c r="H293" t="s">
+        <v>970</v>
+      </c>
+      <c r="I293" t="s">
+        <v>12</v>
+      </c>
+      <c r="J293" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="A259:J259"/>
-    <mergeCell ref="A256:J256"/>
-    <mergeCell ref="A240:J240"/>
-    <mergeCell ref="A238:J238"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A267:J267"/>
-    <mergeCell ref="A281:J281"/>
-    <mergeCell ref="A279:J279"/>
-    <mergeCell ref="A265:J265"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A276:J276"/>
+  <mergeCells count="34">
+    <mergeCell ref="A291:J291"/>
     <mergeCell ref="A289:J289"/>
     <mergeCell ref="A286:J286"/>
     <mergeCell ref="A273:J273"/>
@@ -13845,6 +13928,23 @@
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A267:J267"/>
+    <mergeCell ref="A281:J281"/>
+    <mergeCell ref="A279:J279"/>
+    <mergeCell ref="A265:J265"/>
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A276:J276"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A259:J259"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A240:J240"/>
+    <mergeCell ref="A238:J238"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -13942,7 +14042,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG265"/>
+  <dimension ref="A1:AG267"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -37595,6 +37695,208 @@
         <v>22</v>
       </c>
       <c r="AG265" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="266" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>996</v>
+      </c>
+      <c r="B266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF266" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG266" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="267" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>999</v>
+      </c>
+      <c r="B267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG267" s="28" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\ZlaataQAsever\Ref\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64AC72B-81E6-4734-80FF-846547B1781F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CFEE56-EED2-4B2D-8F14-266DB5F7F590}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9592" uniqueCount="1000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9631" uniqueCount="1003">
   <si>
     <t>S.No</t>
   </si>
@@ -3026,6 +3026,15 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_ML_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_ExpressDelivery_03</t>
+  </si>
+  <si>
+    <t>Verify  Delivery Day functionality on Product Listing Page.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_ExpressDelivery_03</t>
   </si>
 </sst>
 </file>
@@ -3668,24 +3677,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3712,6 +3703,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4515,7 +4524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:Z293"/>
+  <dimension ref="A1:Z294"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -5266,18 +5275,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="87"/>
-      <c r="C24" s="87"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="88"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="97"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
@@ -5664,18 +5673,18 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="89" t="s">
+      <c r="A37" s="98" t="s">
         <v>172</v>
       </c>
-      <c r="B37" s="90"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="90"/>
-      <c r="I37" s="90"/>
-      <c r="J37" s="91"/>
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="100"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
@@ -6222,18 +6231,18 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="89" t="s">
+      <c r="A55" s="98" t="s">
         <v>244</v>
       </c>
-      <c r="B55" s="90"/>
-      <c r="C55" s="90"/>
-      <c r="D55" s="90"/>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="90"/>
-      <c r="H55" s="90"/>
-      <c r="I55" s="90"/>
-      <c r="J55" s="91"/>
+      <c r="B55" s="99"/>
+      <c r="C55" s="99"/>
+      <c r="D55" s="99"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="99"/>
+      <c r="G55" s="99"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="99"/>
+      <c r="J55" s="100"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
@@ -6556,18 +6565,18 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="89" t="s">
+      <c r="A66" s="98" t="s">
         <v>246</v>
       </c>
-      <c r="B66" s="90"/>
-      <c r="C66" s="90"/>
-      <c r="D66" s="90"/>
-      <c r="E66" s="90"/>
-      <c r="F66" s="90"/>
-      <c r="G66" s="90"/>
-      <c r="H66" s="90"/>
-      <c r="I66" s="90"/>
-      <c r="J66" s="91"/>
+      <c r="B66" s="99"/>
+      <c r="C66" s="99"/>
+      <c r="D66" s="99"/>
+      <c r="E66" s="99"/>
+      <c r="F66" s="99"/>
+      <c r="G66" s="99"/>
+      <c r="H66" s="99"/>
+      <c r="I66" s="99"/>
+      <c r="J66" s="100"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
@@ -6922,18 +6931,18 @@
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="89" t="s">
+      <c r="A78" s="98" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="90"/>
-      <c r="C78" s="90"/>
-      <c r="D78" s="90"/>
-      <c r="E78" s="90"/>
-      <c r="F78" s="90"/>
-      <c r="G78" s="90"/>
-      <c r="H78" s="90"/>
-      <c r="I78" s="90"/>
-      <c r="J78" s="91"/>
+      <c r="B78" s="99"/>
+      <c r="C78" s="99"/>
+      <c r="D78" s="99"/>
+      <c r="E78" s="99"/>
+      <c r="F78" s="99"/>
+      <c r="G78" s="99"/>
+      <c r="H78" s="99"/>
+      <c r="I78" s="99"/>
+      <c r="J78" s="100"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
@@ -7800,18 +7809,18 @@
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A106" s="92" t="s">
+      <c r="A106" s="86" t="s">
         <v>374</v>
       </c>
-      <c r="B106" s="92"/>
-      <c r="C106" s="92"/>
-      <c r="D106" s="92"/>
-      <c r="E106" s="92"/>
-      <c r="F106" s="92"/>
-      <c r="G106" s="92"/>
-      <c r="H106" s="92"/>
-      <c r="I106" s="92"/>
-      <c r="J106" s="92"/>
+      <c r="B106" s="86"/>
+      <c r="C106" s="86"/>
+      <c r="D106" s="86"/>
+      <c r="E106" s="86"/>
+      <c r="F106" s="86"/>
+      <c r="G106" s="86"/>
+      <c r="H106" s="86"/>
+      <c r="I106" s="86"/>
+      <c r="J106" s="86"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
@@ -8304,18 +8313,18 @@
       <c r="X120" s="52"/>
     </row>
     <row r="121" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="93" t="s">
+      <c r="A121" s="87" t="s">
         <v>376</v>
       </c>
-      <c r="B121" s="93"/>
-      <c r="C121" s="93"/>
-      <c r="D121" s="93"/>
-      <c r="E121" s="93"/>
-      <c r="F121" s="93"/>
-      <c r="G121" s="93"/>
-      <c r="H121" s="93"/>
-      <c r="I121" s="93"/>
-      <c r="J121" s="93"/>
+      <c r="B121" s="87"/>
+      <c r="C121" s="87"/>
+      <c r="D121" s="87"/>
+      <c r="E121" s="87"/>
+      <c r="F121" s="87"/>
+      <c r="G121" s="87"/>
+      <c r="H121" s="87"/>
+      <c r="I121" s="87"/>
+      <c r="J121" s="87"/>
       <c r="K121" s="51"/>
       <c r="L121" s="52"/>
       <c r="M121" s="52"/>
@@ -8378,18 +8387,18 @@
       <c r="X122" s="52"/>
     </row>
     <row r="123" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="93" t="s">
+      <c r="A123" s="87" t="s">
         <v>381</v>
       </c>
-      <c r="B123" s="93"/>
-      <c r="C123" s="93"/>
-      <c r="D123" s="93"/>
-      <c r="E123" s="93"/>
-      <c r="F123" s="93"/>
-      <c r="G123" s="93"/>
-      <c r="H123" s="93"/>
-      <c r="I123" s="93"/>
-      <c r="J123" s="93"/>
+      <c r="B123" s="87"/>
+      <c r="C123" s="87"/>
+      <c r="D123" s="87"/>
+      <c r="E123" s="87"/>
+      <c r="F123" s="87"/>
+      <c r="G123" s="87"/>
+      <c r="H123" s="87"/>
+      <c r="I123" s="87"/>
+      <c r="J123" s="87"/>
       <c r="K123" s="51"/>
       <c r="L123" s="52"/>
       <c r="M123" s="52"/>
@@ -8452,18 +8461,18 @@
       <c r="X124" s="52"/>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="93" t="s">
+      <c r="A125" s="87" t="s">
         <v>394</v>
       </c>
-      <c r="B125" s="93"/>
-      <c r="C125" s="93"/>
-      <c r="D125" s="93"/>
-      <c r="E125" s="93"/>
-      <c r="F125" s="93"/>
-      <c r="G125" s="93"/>
-      <c r="H125" s="93"/>
-      <c r="I125" s="93"/>
-      <c r="J125" s="93"/>
+      <c r="B125" s="87"/>
+      <c r="C125" s="87"/>
+      <c r="D125" s="87"/>
+      <c r="E125" s="87"/>
+      <c r="F125" s="87"/>
+      <c r="G125" s="87"/>
+      <c r="H125" s="87"/>
+      <c r="I125" s="87"/>
+      <c r="J125" s="87"/>
     </row>
     <row r="126" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="25">
@@ -8788,18 +8797,18 @@
       <c r="X132" s="52"/>
     </row>
     <row r="133" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="93" t="s">
+      <c r="A133" s="87" t="s">
         <v>411</v>
       </c>
-      <c r="B133" s="93"/>
-      <c r="C133" s="93"/>
-      <c r="D133" s="94"/>
-      <c r="E133" s="94"/>
-      <c r="F133" s="94"/>
-      <c r="G133" s="94"/>
-      <c r="H133" s="94"/>
-      <c r="I133" s="94"/>
-      <c r="J133" s="94"/>
+      <c r="B133" s="87"/>
+      <c r="C133" s="87"/>
+      <c r="D133" s="88"/>
+      <c r="E133" s="88"/>
+      <c r="F133" s="88"/>
+      <c r="G133" s="88"/>
+      <c r="H133" s="88"/>
+      <c r="I133" s="88"/>
+      <c r="J133" s="88"/>
       <c r="K133" s="52"/>
       <c r="L133" s="52"/>
       <c r="M133" s="52"/>
@@ -9294,18 +9303,18 @@
       <c r="X144" s="52"/>
     </row>
     <row r="145" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="98" t="s">
+      <c r="A145" s="92" t="s">
         <v>439</v>
       </c>
-      <c r="B145" s="99"/>
-      <c r="C145" s="99"/>
-      <c r="D145" s="99"/>
-      <c r="E145" s="99"/>
-      <c r="F145" s="99"/>
-      <c r="G145" s="99"/>
-      <c r="H145" s="99"/>
-      <c r="I145" s="99"/>
-      <c r="J145" s="100"/>
+      <c r="B145" s="93"/>
+      <c r="C145" s="93"/>
+      <c r="D145" s="93"/>
+      <c r="E145" s="93"/>
+      <c r="F145" s="93"/>
+      <c r="G145" s="93"/>
+      <c r="H145" s="93"/>
+      <c r="I145" s="93"/>
+      <c r="J145" s="94"/>
       <c r="K145" s="52"/>
       <c r="L145" s="52"/>
       <c r="M145" s="52"/>
@@ -9752,18 +9761,18 @@
       <c r="Z155" s="52"/>
     </row>
     <row r="156" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="93" t="s">
+      <c r="A156" s="87" t="s">
         <v>510</v>
       </c>
-      <c r="B156" s="93"/>
-      <c r="C156" s="93"/>
-      <c r="D156" s="93"/>
-      <c r="E156" s="93"/>
-      <c r="F156" s="93"/>
-      <c r="G156" s="93"/>
-      <c r="H156" s="93"/>
-      <c r="I156" s="93"/>
-      <c r="J156" s="93"/>
+      <c r="B156" s="87"/>
+      <c r="C156" s="87"/>
+      <c r="D156" s="87"/>
+      <c r="E156" s="87"/>
+      <c r="F156" s="87"/>
+      <c r="G156" s="87"/>
+      <c r="H156" s="87"/>
+      <c r="I156" s="87"/>
+      <c r="J156" s="87"/>
       <c r="K156" s="52"/>
       <c r="L156" s="52"/>
       <c r="M156" s="52"/>
@@ -9830,18 +9839,18 @@
       <c r="Z157" s="52"/>
     </row>
     <row r="158" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="93" t="s">
+      <c r="A158" s="87" t="s">
         <v>536</v>
       </c>
-      <c r="B158" s="93"/>
-      <c r="C158" s="93"/>
-      <c r="D158" s="93"/>
-      <c r="E158" s="93"/>
-      <c r="F158" s="93"/>
-      <c r="G158" s="93"/>
-      <c r="H158" s="93"/>
-      <c r="I158" s="93"/>
-      <c r="J158" s="93"/>
+      <c r="B158" s="87"/>
+      <c r="C158" s="87"/>
+      <c r="D158" s="87"/>
+      <c r="E158" s="87"/>
+      <c r="F158" s="87"/>
+      <c r="G158" s="87"/>
+      <c r="H158" s="87"/>
+      <c r="I158" s="87"/>
+      <c r="J158" s="87"/>
       <c r="K158" s="52"/>
       <c r="L158" s="52"/>
       <c r="M158" s="52"/>
@@ -10676,18 +10685,18 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="93" t="s">
+      <c r="A180" s="87" t="s">
         <v>707</v>
       </c>
-      <c r="B180" s="93"/>
-      <c r="C180" s="93"/>
+      <c r="B180" s="87"/>
+      <c r="C180" s="87"/>
       <c r="D180" s="85"/>
-      <c r="E180" s="93"/>
-      <c r="F180" s="93"/>
-      <c r="G180" s="93"/>
-      <c r="H180" s="93"/>
-      <c r="I180" s="93"/>
-      <c r="J180" s="93"/>
+      <c r="E180" s="87"/>
+      <c r="F180" s="87"/>
+      <c r="G180" s="87"/>
+      <c r="H180" s="87"/>
+      <c r="I180" s="87"/>
+      <c r="J180" s="87"/>
     </row>
     <row r="181" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="62">
@@ -10978,18 +10987,18 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="95" t="s">
+      <c r="A190" s="89" t="s">
         <v>609</v>
       </c>
-      <c r="B190" s="96"/>
-      <c r="C190" s="96"/>
-      <c r="D190" s="96"/>
-      <c r="E190" s="96"/>
-      <c r="F190" s="96"/>
-      <c r="G190" s="96"/>
-      <c r="H190" s="96"/>
-      <c r="I190" s="96"/>
-      <c r="J190" s="97"/>
+      <c r="B190" s="90"/>
+      <c r="C190" s="90"/>
+      <c r="D190" s="90"/>
+      <c r="E190" s="90"/>
+      <c r="F190" s="90"/>
+      <c r="G190" s="90"/>
+      <c r="H190" s="90"/>
+      <c r="I190" s="90"/>
+      <c r="J190" s="91"/>
     </row>
     <row r="191" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="62">
@@ -13520,115 +13529,115 @@
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A279" s="85" t="s">
+      <c r="A279" s="77">
+        <v>3</v>
+      </c>
+      <c r="B279" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C279" s="71" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D279" s="79" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E279" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F279" s="71" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G279" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="H279" s="77" t="s">
+        <v>951</v>
+      </c>
+      <c r="I279" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="J279" s="77" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A280" s="85" t="s">
         <v>955</v>
       </c>
-      <c r="B279" s="85"/>
-      <c r="C279" s="85"/>
-      <c r="D279" s="85"/>
-      <c r="E279" s="85"/>
-      <c r="F279" s="85"/>
-      <c r="G279" s="85"/>
-      <c r="H279" s="85"/>
-      <c r="I279" s="85"/>
-      <c r="J279" s="85"/>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A280" s="77">
+      <c r="B280" s="85"/>
+      <c r="C280" s="85"/>
+      <c r="D280" s="85"/>
+      <c r="E280" s="85"/>
+      <c r="F280" s="85"/>
+      <c r="G280" s="85"/>
+      <c r="H280" s="85"/>
+      <c r="I280" s="85"/>
+      <c r="J280" s="85"/>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A281" s="77">
         <v>1</v>
       </c>
-      <c r="B280" s="77" t="s">
+      <c r="B281" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C280" s="71" t="s">
+      <c r="C281" s="71" t="s">
         <v>956</v>
       </c>
-      <c r="D280" s="78" t="s">
+      <c r="D281" s="78" t="s">
         <v>957</v>
       </c>
-      <c r="E280" s="77" t="s">
+      <c r="E281" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="F280" s="71" t="s">
+      <c r="F281" s="71" t="s">
         <v>958</v>
       </c>
-      <c r="G280" s="77" t="s">
+      <c r="G281" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="H280" s="77" t="s">
+      <c r="H281" s="77" t="s">
         <v>959</v>
       </c>
-      <c r="I280" s="77" t="s">
+      <c r="I281" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="J280" s="77" t="s">
+      <c r="J281" s="77" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A281" s="85" t="s">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A282" s="85" t="s">
         <v>966</v>
       </c>
-      <c r="B281" s="85"/>
-      <c r="C281" s="85"/>
-      <c r="D281" s="85"/>
-      <c r="E281" s="85"/>
-      <c r="F281" s="85"/>
-      <c r="G281" s="85"/>
-      <c r="H281" s="85"/>
-      <c r="I281" s="85"/>
-      <c r="J281" s="85"/>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A282">
-        <v>1</v>
-      </c>
-      <c r="B282" t="s">
-        <v>10</v>
-      </c>
-      <c r="C282" t="s">
-        <v>967</v>
-      </c>
-      <c r="D282" t="s">
-        <v>968</v>
-      </c>
-      <c r="E282" t="s">
-        <v>14</v>
-      </c>
-      <c r="F282" t="s">
-        <v>969</v>
-      </c>
-      <c r="G282" t="s">
-        <v>11</v>
-      </c>
-      <c r="H282" t="s">
-        <v>970</v>
-      </c>
-      <c r="I282" t="s">
-        <v>12</v>
-      </c>
-      <c r="J282" t="s">
-        <v>13</v>
-      </c>
+      <c r="B282" s="85"/>
+      <c r="C282" s="85"/>
+      <c r="D282" s="85"/>
+      <c r="E282" s="85"/>
+      <c r="F282" s="85"/>
+      <c r="G282" s="85"/>
+      <c r="H282" s="85"/>
+      <c r="I282" s="85"/>
+      <c r="J282" s="85"/>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B283" t="s">
         <v>10</v>
       </c>
       <c r="C283" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="D283" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="E283" t="s">
         <v>14</v>
       </c>
       <c r="F283" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="G283" t="s">
         <v>11</v>
@@ -13645,22 +13654,22 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B284" t="s">
         <v>10</v>
       </c>
       <c r="C284" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="D284" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="E284" t="s">
         <v>14</v>
       </c>
       <c r="F284" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="G284" t="s">
         <v>11</v>
@@ -13677,22 +13686,22 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B285" t="s">
         <v>10</v>
       </c>
       <c r="C285" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D285" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="E285" t="s">
         <v>14</v>
       </c>
       <c r="F285" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="G285" t="s">
         <v>11</v>
@@ -13707,70 +13716,70 @@
         <v>13</v>
       </c>
     </row>
-    <row r="286" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="85" t="s">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>4</v>
+      </c>
+      <c r="B286" t="s">
+        <v>10</v>
+      </c>
+      <c r="C286" t="s">
+        <v>977</v>
+      </c>
+      <c r="D286" t="s">
+        <v>978</v>
+      </c>
+      <c r="E286" t="s">
+        <v>14</v>
+      </c>
+      <c r="F286" t="s">
+        <v>979</v>
+      </c>
+      <c r="G286" t="s">
+        <v>11</v>
+      </c>
+      <c r="H286" t="s">
+        <v>970</v>
+      </c>
+      <c r="I286" t="s">
+        <v>12</v>
+      </c>
+      <c r="J286" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="85" t="s">
         <v>980</v>
       </c>
-      <c r="B286" s="85"/>
-      <c r="C286" s="85"/>
-      <c r="D286" s="85"/>
-      <c r="E286" s="85"/>
-      <c r="F286" s="85"/>
-      <c r="G286" s="85"/>
-      <c r="H286" s="85"/>
-      <c r="I286" s="85"/>
-      <c r="J286" s="85"/>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A287" s="77">
+      <c r="B287" s="85"/>
+      <c r="C287" s="85"/>
+      <c r="D287" s="85"/>
+      <c r="E287" s="85"/>
+      <c r="F287" s="85"/>
+      <c r="G287" s="85"/>
+      <c r="H287" s="85"/>
+      <c r="I287" s="85"/>
+      <c r="J287" s="85"/>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A288" s="77">
         <v>1</v>
       </c>
-      <c r="B287" s="77" t="s">
+      <c r="B288" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C287" s="71" t="s">
+      <c r="C288" s="71" t="s">
         <v>983</v>
       </c>
-      <c r="D287" s="78" t="s">
+      <c r="D288" s="78" t="s">
         <v>982</v>
-      </c>
-      <c r="E287" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="F287" s="71" t="s">
-        <v>984</v>
-      </c>
-      <c r="G287" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="H287" s="77" t="s">
-        <v>981</v>
-      </c>
-      <c r="I287" s="77" t="s">
-        <v>12</v>
-      </c>
-      <c r="J287" s="77" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A288">
-        <v>2</v>
-      </c>
-      <c r="B288" t="s">
-        <v>10</v>
-      </c>
-      <c r="C288" t="s">
-        <v>985</v>
-      </c>
-      <c r="D288" t="s">
-        <v>986</v>
       </c>
       <c r="E288" s="77" t="s">
         <v>14</v>
       </c>
       <c r="F288" s="71" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="G288" s="77" t="s">
         <v>11</v>
@@ -13786,115 +13795,115 @@
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A289" s="85" t="s">
+      <c r="A289">
+        <v>2</v>
+      </c>
+      <c r="B289" t="s">
+        <v>10</v>
+      </c>
+      <c r="C289" t="s">
+        <v>985</v>
+      </c>
+      <c r="D289" t="s">
+        <v>986</v>
+      </c>
+      <c r="E289" s="77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F289" s="71" t="s">
+        <v>987</v>
+      </c>
+      <c r="G289" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="H289" s="77" t="s">
+        <v>981</v>
+      </c>
+      <c r="I289" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="J289" s="77" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A290" s="85" t="s">
         <v>988</v>
       </c>
-      <c r="B289" s="85"/>
-      <c r="C289" s="85"/>
-      <c r="D289" s="85"/>
-      <c r="E289" s="85"/>
-      <c r="F289" s="85"/>
-      <c r="G289" s="85"/>
-      <c r="H289" s="85"/>
-      <c r="I289" s="85"/>
-      <c r="J289" s="85"/>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A290" s="77">
+      <c r="B290" s="85"/>
+      <c r="C290" s="85"/>
+      <c r="D290" s="85"/>
+      <c r="E290" s="85"/>
+      <c r="F290" s="85"/>
+      <c r="G290" s="85"/>
+      <c r="H290" s="85"/>
+      <c r="I290" s="85"/>
+      <c r="J290" s="85"/>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A291" s="77">
         <v>1</v>
       </c>
-      <c r="B290" s="77" t="s">
+      <c r="B291" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C290" s="71" t="s">
+      <c r="C291" s="71" t="s">
         <v>989</v>
       </c>
-      <c r="D290" s="78" t="s">
+      <c r="D291" s="78" t="s">
         <v>992</v>
       </c>
-      <c r="E290" s="77" t="s">
+      <c r="E291" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="F290" s="71" t="s">
+      <c r="F291" s="71" t="s">
         <v>990</v>
       </c>
-      <c r="G290" s="77" t="s">
+      <c r="G291" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="H290" s="77" t="s">
+      <c r="H291" s="77" t="s">
         <v>991</v>
       </c>
-      <c r="I290" s="77" t="s">
+      <c r="I291" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="J290" s="77" t="s">
+      <c r="J291" s="77" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A291" s="85" t="s">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A292" s="85" t="s">
         <v>993</v>
       </c>
-      <c r="B291" s="85"/>
-      <c r="C291" s="85"/>
-      <c r="D291" s="85"/>
-      <c r="E291" s="85"/>
-      <c r="F291" s="85"/>
-      <c r="G291" s="85"/>
-      <c r="H291" s="85"/>
-      <c r="I291" s="85"/>
-      <c r="J291" s="85"/>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A292">
-        <v>1</v>
-      </c>
-      <c r="B292" t="s">
-        <v>10</v>
-      </c>
-      <c r="C292" t="s">
-        <v>994</v>
-      </c>
-      <c r="D292" t="s">
-        <v>995</v>
-      </c>
-      <c r="E292" t="s">
-        <v>14</v>
-      </c>
-      <c r="F292" t="s">
-        <v>996</v>
-      </c>
-      <c r="G292" t="s">
-        <v>11</v>
-      </c>
-      <c r="H292" t="s">
-        <v>970</v>
-      </c>
-      <c r="I292" t="s">
-        <v>12</v>
-      </c>
-      <c r="J292" t="s">
-        <v>13</v>
-      </c>
+      <c r="B292" s="85"/>
+      <c r="C292" s="85"/>
+      <c r="D292" s="85"/>
+      <c r="E292" s="85"/>
+      <c r="F292" s="85"/>
+      <c r="G292" s="85"/>
+      <c r="H292" s="85"/>
+      <c r="I292" s="85"/>
+      <c r="J292" s="85"/>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B293" t="s">
         <v>10</v>
       </c>
       <c r="C293" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="D293" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="E293" t="s">
         <v>14</v>
       </c>
       <c r="F293" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="G293" t="s">
         <v>11</v>
@@ -13909,13 +13918,57 @@
         <v>13</v>
       </c>
     </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>2</v>
+      </c>
+      <c r="B294" t="s">
+        <v>10</v>
+      </c>
+      <c r="C294" t="s">
+        <v>997</v>
+      </c>
+      <c r="D294" t="s">
+        <v>998</v>
+      </c>
+      <c r="E294" t="s">
+        <v>14</v>
+      </c>
+      <c r="F294" t="s">
+        <v>999</v>
+      </c>
+      <c r="G294" t="s">
+        <v>11</v>
+      </c>
+      <c r="H294" t="s">
+        <v>970</v>
+      </c>
+      <c r="I294" t="s">
+        <v>12</v>
+      </c>
+      <c r="J294" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A291:J291"/>
-    <mergeCell ref="A289:J289"/>
-    <mergeCell ref="A286:J286"/>
-    <mergeCell ref="A273:J273"/>
-    <mergeCell ref="A270:J270"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A226:J226"/>
+    <mergeCell ref="A259:J259"/>
+    <mergeCell ref="A256:J256"/>
+    <mergeCell ref="A240:J240"/>
+    <mergeCell ref="A238:J238"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A267:J267"/>
+    <mergeCell ref="A282:J282"/>
+    <mergeCell ref="A280:J280"/>
+    <mergeCell ref="A265:J265"/>
+    <mergeCell ref="A220:J220"/>
+    <mergeCell ref="A276:J276"/>
     <mergeCell ref="A106:J106"/>
     <mergeCell ref="A121:J121"/>
     <mergeCell ref="A123:J123"/>
@@ -13928,23 +13981,11 @@
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A180:J180"/>
-    <mergeCell ref="A267:J267"/>
-    <mergeCell ref="A281:J281"/>
-    <mergeCell ref="A279:J279"/>
-    <mergeCell ref="A265:J265"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A276:J276"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A226:J226"/>
-    <mergeCell ref="A259:J259"/>
-    <mergeCell ref="A256:J256"/>
-    <mergeCell ref="A240:J240"/>
-    <mergeCell ref="A238:J238"/>
+    <mergeCell ref="A292:J292"/>
+    <mergeCell ref="A290:J290"/>
+    <mergeCell ref="A287:J287"/>
+    <mergeCell ref="A273:J273"/>
+    <mergeCell ref="A270:J270"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="E2:J2 E8:J21 E23:J23">
@@ -14042,7 +14083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG267"/>
+  <dimension ref="A1:AG268"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -36892,162 +36933,156 @@
     </row>
     <row r="258" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A258" s="28" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD258" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE258" s="28"/>
+      <c r="AF258" s="28"/>
+      <c r="AG258" s="28"/>
+    </row>
+    <row r="259" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A259" s="28" t="s">
         <v>958</v>
       </c>
-      <c r="B258" s="28" t="s">
+      <c r="B259" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D258" s="28" t="s">
+      <c r="C259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D259" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="F258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="H258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="I258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="K258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="L258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="M258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="N258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="O258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="P258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="R258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="S258" s="84" t="s">
+      <c r="E259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R259" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S259" s="84" t="s">
         <v>965</v>
-      </c>
-      <c r="T258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="U258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="V258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE258" s="28" t="s">
-        <v>960</v>
-      </c>
-      <c r="AF258" s="28" t="s">
-        <v>961</v>
-      </c>
-      <c r="AG258" s="28" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="259" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A259" t="s">
-        <v>969</v>
-      </c>
-      <c r="B259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="F259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="H259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="I259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="K259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="L259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="M259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="N259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="O259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="P259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="R259" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="S259" s="28" t="s">
-        <v>22</v>
       </c>
       <c r="T259" s="28" t="s">
         <v>22</v>
@@ -37094,7 +37129,7 @@
     </row>
     <row r="260" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B260" s="28" t="s">
         <v>22</v>
@@ -37195,7 +37230,7 @@
     </row>
     <row r="261" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B261" s="28" t="s">
         <v>22</v>
@@ -37296,7 +37331,7 @@
     </row>
     <row r="262" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B262" s="28" t="s">
         <v>22</v>
@@ -37397,7 +37432,7 @@
     </row>
     <row r="263" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="B263" s="28" t="s">
         <v>22</v>
@@ -37487,18 +37522,18 @@
         <v>22</v>
       </c>
       <c r="AE263" s="28" t="s">
-        <v>22</v>
+        <v>960</v>
       </c>
       <c r="AF263" s="28" t="s">
-        <v>22</v>
+        <v>961</v>
       </c>
       <c r="AG263" s="28" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
     </row>
     <row r="264" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="B264" s="28" t="s">
         <v>22</v>
@@ -37599,7 +37634,7 @@
     </row>
     <row r="265" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="B265" s="28" t="s">
         <v>22</v>
@@ -37700,7 +37735,7 @@
     </row>
     <row r="266" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="B266" s="28" t="s">
         <v>22</v>
@@ -37801,102 +37836,203 @@
     </row>
     <row r="267" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
+        <v>996</v>
+      </c>
+      <c r="B267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF267" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG267" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="268" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
         <v>999</v>
       </c>
-      <c r="B267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="F267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="H267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="I267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="K267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="L267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="M267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="N267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="O267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="P267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="R267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="S267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="T267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="U267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="V267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="W267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="X267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF267" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="AG267" s="28" t="s">
+      <c r="B268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="R268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="S268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="V268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="W268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="X268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF268" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG268" s="28" t="s">
         <v>22</v>
       </c>
     </row>
@@ -38071,7 +38207,7 @@
     <hyperlink ref="AC180" r:id="rId62" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{6262B2DA-10A4-449F-8938-AC96E529EF5A}"/>
     <hyperlink ref="AC181" r:id="rId63" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{A98207AA-9B31-4A4E-BB36-48E505D5F843}"/>
     <hyperlink ref="AC182" r:id="rId64" tooltip="Blue dskjjksdjkdjds" display="https://qa.zlta.testingserver8.com/product-detail/blue-dskjjksdjkdjds" xr:uid="{B19B4716-3A72-4609-978F-A41A7047AD51}"/>
-    <hyperlink ref="S258" r:id="rId65" xr:uid="{A471EC77-F2D6-42C2-91D4-12D766070794}"/>
+    <hyperlink ref="S259" r:id="rId65" xr:uid="{A471EC77-F2D6-42C2-91D4-12D766070794}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId66"/>
